--- a/data/이슈제품.xlsx
+++ b/data/이슈제품.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20337"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\17. claude\po\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OA\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{627BD93C-0AC3-444D-A690-B7D54F5C6975}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="179021"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="641">
   <si>
     <t>오아디머무드등-화이트</t>
   </si>
@@ -74,9 +75,6 @@
     <t>보아르이지전기포트M1(FV)-그레이</t>
   </si>
   <si>
-    <t>협의, 8/10 2000대</t>
-  </si>
-  <si>
     <t>보아르이지전기포트M1(FV)-아이보리</t>
   </si>
   <si>
@@ -92,9 +90,6 @@
     <t>오아턴에어탁상팬</t>
   </si>
   <si>
-    <t>입고X, 리테일출고</t>
-  </si>
-  <si>
     <t>오아턴에어미니탁상팬</t>
   </si>
   <si>
@@ -1914,12 +1909,64 @@
   </si>
   <si>
     <t>오아프리온무선고데기-퍼플</t>
+  </si>
+  <si>
+    <t>입고X, 12월 중순예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>협의, 11월 중순예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입고X, 9/30 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입고X, 10월말 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>협의, 9/30 생산완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입고X, 11/17 생산완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입고X, 10월 초 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입고X, 9월말 예상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입고X, 10월 중순 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입고X, 10월 2일 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>협의, 10월 중순</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>협의, 10월 초</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오아넥스트레쳐S-베이지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2242,350 +2289,352 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J607"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="44.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" t="s">
+      <c r="H1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" t="s">
+      <c r="I1" t="s">
         <v>30</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>31</v>
-      </c>
-      <c r="I1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>36811023</v>
+        <v>60015061</v>
       </c>
       <c r="B2" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I2">
         <v>3636925</v>
       </c>
       <c r="J2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>35149611</v>
+        <v>50723598</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I3">
         <v>3636926</v>
       </c>
       <c r="J3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>66417801</v>
+        <v>76375597</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="H4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I4">
         <v>3636927</v>
       </c>
       <c r="J4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>14719737</v>
+        <v>73893263</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="H5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I5">
         <v>39415252</v>
       </c>
       <c r="J5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>60015061</v>
+        <v>58505144</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="H6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I6">
         <v>19213859</v>
       </c>
       <c r="J6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>11874445</v>
+        <v>50725354</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>210</v>
       </c>
       <c r="C7" t="s">
-        <v>1</v>
+        <v>628</v>
       </c>
       <c r="H7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I7">
         <v>20342327</v>
       </c>
       <c r="J7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>45349063</v>
+        <v>12263239</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>209</v>
       </c>
       <c r="C8" t="s">
-        <v>1</v>
+        <v>629</v>
       </c>
       <c r="H8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I8">
         <v>13004238</v>
       </c>
       <c r="J8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>13195957</v>
+        <v>68880617</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>640</v>
       </c>
       <c r="C9" t="s">
-        <v>1</v>
+        <v>629</v>
       </c>
       <c r="H9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I9">
         <v>20341619</v>
       </c>
       <c r="J9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>40180424</v>
+        <v>60380162</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>429</v>
       </c>
       <c r="C10" t="s">
-        <v>1</v>
+        <v>630</v>
       </c>
       <c r="H10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I10">
         <v>11092035</v>
       </c>
       <c r="J10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>11670520</v>
+        <v>60450424</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>428</v>
       </c>
       <c r="C11" t="s">
-        <v>1</v>
+        <v>630</v>
       </c>
       <c r="H11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I11">
         <v>40852278</v>
       </c>
       <c r="J11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>59927382</v>
+        <v>4125377</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>205</v>
       </c>
       <c r="C12" t="s">
-        <v>1</v>
+        <v>631</v>
       </c>
       <c r="H12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I12">
         <v>29266932</v>
       </c>
       <c r="J12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>16179047</v>
+        <v>26426530</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>206</v>
       </c>
       <c r="C13" t="s">
-        <v>1</v>
+        <v>631</v>
       </c>
       <c r="H13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I13">
         <v>12586373</v>
       </c>
       <c r="J13" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>50723598</v>
+        <v>12439390</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>208</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>638</v>
       </c>
       <c r="H14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I14">
         <v>11055651</v>
       </c>
       <c r="J14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>74693807</v>
+        <v>5332788</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>347</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
+        <v>638</v>
       </c>
       <c r="H15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I15">
         <v>38659485</v>
       </c>
       <c r="J15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>73893263</v>
+        <v>11229298</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>177</v>
       </c>
       <c r="C16" t="s">
-        <v>18</v>
+        <v>638</v>
       </c>
       <c r="H16" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I16">
         <v>9567647</v>
       </c>
       <c r="J16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>58505144</v>
+        <v>27056005</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>332</v>
       </c>
       <c r="C17" t="s">
-        <v>20</v>
+        <v>632</v>
       </c>
       <c r="H17" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I17">
         <v>40180424</v>
@@ -2596,756 +2645,783 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>45701215</v>
+        <v>50153946</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="C18" t="s">
-        <v>22</v>
+        <v>633</v>
       </c>
       <c r="H18" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I18">
         <v>39228155</v>
       </c>
       <c r="J18" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>44996967</v>
+        <v>69096296</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>554</v>
       </c>
       <c r="C19" t="s">
-        <v>22</v>
+        <v>639</v>
       </c>
       <c r="H19" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I19">
         <v>38407975</v>
       </c>
       <c r="J19" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>55356212</v>
+        <v>75741354</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>607</v>
       </c>
       <c r="C20" t="s">
-        <v>22</v>
+        <v>631</v>
       </c>
       <c r="H20" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I20">
         <v>38545387</v>
       </c>
       <c r="J20" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>25512595</v>
+        <v>16303007</v>
       </c>
       <c r="B21" t="s">
-        <v>25</v>
+        <v>276</v>
       </c>
       <c r="C21" t="s">
-        <v>1</v>
+        <v>639</v>
       </c>
       <c r="H21" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I21">
         <v>18816827</v>
       </c>
       <c r="J21" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>76375597</v>
+        <v>60542212</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>440</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>634</v>
       </c>
       <c r="H22" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I22">
         <v>39278162</v>
       </c>
       <c r="J22" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>13101217</v>
+      </c>
+      <c r="B23" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" t="s">
+        <v>635</v>
+      </c>
       <c r="H23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I23">
         <v>13100374</v>
       </c>
       <c r="J23" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>15414324</v>
+      </c>
+      <c r="B24" t="s">
+        <v>201</v>
+      </c>
+      <c r="C24" t="s">
+        <v>636</v>
+      </c>
       <c r="H24" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I24">
         <v>10855225</v>
       </c>
       <c r="J24" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>31743599</v>
+      </c>
+      <c r="B25" t="s">
+        <v>223</v>
+      </c>
+      <c r="C25" t="s">
+        <v>637</v>
+      </c>
       <c r="H25" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I25">
         <v>38490171</v>
       </c>
       <c r="J25" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H26" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I26">
         <v>38490170</v>
       </c>
       <c r="J26" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H27" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I27">
         <v>38417027</v>
       </c>
       <c r="J27" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H28" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I28">
         <v>13099542</v>
       </c>
       <c r="J28" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H29" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I29">
         <v>10324264</v>
       </c>
       <c r="J29" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H30" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I30">
         <v>39229235</v>
       </c>
       <c r="J30" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H31" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I31">
         <v>12775098</v>
       </c>
       <c r="J31" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H32" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I32">
         <v>12775097</v>
       </c>
       <c r="J32" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H33" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I33">
         <v>12775096</v>
       </c>
       <c r="J33" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H34" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I34">
         <v>13151160</v>
       </c>
       <c r="J34" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="35" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H35" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I35">
         <v>13151158</v>
       </c>
       <c r="J35" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H36" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I36">
         <v>35403063</v>
       </c>
       <c r="J36" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="37" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H37" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I37">
         <v>13473750</v>
       </c>
       <c r="J37" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="38" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H38" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I38">
         <v>17014694</v>
       </c>
       <c r="J38" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H39" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I39">
         <v>17014693</v>
       </c>
       <c r="J39" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="40" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H40" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I40">
         <v>13101218</v>
       </c>
       <c r="J40" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="41" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H41" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I41">
         <v>13101217</v>
       </c>
       <c r="J41" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="42" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H42" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I42">
         <v>16981939</v>
       </c>
       <c r="J42" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="43" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H43" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I43">
         <v>12846219</v>
       </c>
       <c r="J43" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="44" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H44" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I44">
         <v>17398556</v>
       </c>
       <c r="J44" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="45" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H45" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I45">
         <v>16972627</v>
       </c>
       <c r="J45" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="46" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H46" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I46">
         <v>12846215</v>
       </c>
       <c r="J46" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="47" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H47" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I47">
         <v>39663616</v>
       </c>
       <c r="J47" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="48" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H48" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I48">
         <v>37843037</v>
       </c>
       <c r="J48" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="49" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H49" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I49">
         <v>12465755</v>
       </c>
       <c r="J49" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H50" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I50">
         <v>11671481</v>
       </c>
       <c r="J50" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="51" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H51" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I51">
         <v>12685386</v>
       </c>
       <c r="J51" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="52" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H52" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I52">
         <v>12674974</v>
       </c>
       <c r="J52" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="53" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H53" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I53">
         <v>12674973</v>
       </c>
       <c r="J53" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="54" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H54" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I54">
         <v>27515992</v>
       </c>
       <c r="J54" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="55" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H55" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I55">
         <v>18928667</v>
       </c>
       <c r="J55" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="56" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H56" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I56">
         <v>14218803</v>
       </c>
       <c r="J56" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="57" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H57" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I57">
         <v>14218802</v>
       </c>
       <c r="J57" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="58" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H58" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I58">
         <v>14473529</v>
       </c>
       <c r="J58" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="59" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H59" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I59">
         <v>25512595</v>
       </c>
       <c r="J59" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="60" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H60" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I60">
         <v>25433097</v>
       </c>
       <c r="J60" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="61" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H61" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I61">
         <v>50012601</v>
       </c>
       <c r="J61" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="62" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H62" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I62">
         <v>52204284</v>
       </c>
       <c r="J62" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="63" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H63" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I63">
         <v>52155531</v>
       </c>
       <c r="J63" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="64" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H64" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I64">
         <v>10814871</v>
       </c>
       <c r="J64" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="65" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H65" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I65">
         <v>31792560</v>
       </c>
       <c r="J65" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="66" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H66" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I66">
         <v>10694343</v>
       </c>
       <c r="J66" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="67" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H67" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I67">
         <v>43431417</v>
       </c>
       <c r="J67" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="68" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H68" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I68">
         <v>10978754</v>
       </c>
       <c r="J68" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="69" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H69" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I69">
         <v>10974363</v>
       </c>
       <c r="J69" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="70" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H70" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I70">
         <v>39376011</v>
       </c>
       <c r="J70" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="71" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H71" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I71">
         <v>38310913</v>
       </c>
       <c r="J71" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="72" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H72" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I72">
         <v>40639939</v>
       </c>
       <c r="J72" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="73" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H73" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I73">
         <v>44581094</v>
       </c>
       <c r="J73" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="74" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H74" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I74">
         <v>39270777</v>
       </c>
       <c r="J74" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="75" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H75" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I75">
         <v>45342904</v>
       </c>
       <c r="J75" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="76" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H76" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I76">
         <v>19619417</v>
       </c>
       <c r="J76" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="77" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H77" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I77">
         <v>36606823</v>
       </c>
       <c r="J77" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="78" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H78" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I78">
         <v>12585217</v>
       </c>
       <c r="J78" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="79" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H79" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I79">
         <v>11511332</v>
       </c>
       <c r="J79" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="80" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H80" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I80">
         <v>12579597</v>
       </c>
       <c r="J80" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="81" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H81" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I81">
         <v>50153946</v>
       </c>
       <c r="J81" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="82" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H82" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I82">
         <v>50723598</v>
@@ -3356,40 +3432,40 @@
     </row>
     <row r="83" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H83" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I83">
         <v>34464589</v>
       </c>
       <c r="J83" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="84" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H84" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I84">
         <v>12029130</v>
       </c>
       <c r="J84" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="85" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H85" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I85">
         <v>46962408</v>
       </c>
       <c r="J85" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="86" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H86" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I86">
         <v>11874445</v>
@@ -3400,106 +3476,106 @@
     </row>
     <row r="87" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H87" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I87">
         <v>25665354</v>
       </c>
       <c r="J87" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="88" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H88" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I88">
         <v>46550390</v>
       </c>
       <c r="J88" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="89" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H89" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I89">
         <v>45573288</v>
       </c>
       <c r="J89" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="90" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H90" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I90">
         <v>34318450</v>
       </c>
       <c r="J90" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="91" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H91" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I91">
         <v>45701215</v>
       </c>
       <c r="J91" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="92" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H92" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I92">
         <v>15004955</v>
       </c>
       <c r="J92" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="93" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H93" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I93">
         <v>25321998</v>
       </c>
       <c r="J93" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="94" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H94" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I94">
         <v>25321996</v>
       </c>
       <c r="J94" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="95" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H95" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I95">
         <v>46191377</v>
       </c>
       <c r="J95" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="96" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H96" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I96">
         <v>45349063</v>
@@ -3510,568 +3586,568 @@
     </row>
     <row r="97" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H97" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I97">
         <v>44996967</v>
       </c>
       <c r="J97" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="98" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H98" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I98">
         <v>15462869</v>
       </c>
       <c r="J98" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="99" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H99" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I99">
         <v>15462868</v>
       </c>
       <c r="J99" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="100" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H100" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I100">
         <v>46671749</v>
       </c>
       <c r="J100" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="101" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H101" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I101">
         <v>35137369</v>
       </c>
       <c r="J101" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="102" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H102" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I102">
         <v>34320929</v>
       </c>
       <c r="J102" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="103" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H103" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I103">
         <v>34320928</v>
       </c>
       <c r="J103" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="104" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H104" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I104">
         <v>23200605</v>
       </c>
       <c r="J104" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="105" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H105" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I105">
         <v>23200603</v>
       </c>
       <c r="J105" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="106" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H106" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I106">
         <v>43571361</v>
       </c>
       <c r="J106" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="107" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H107" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I107">
         <v>43571360</v>
       </c>
       <c r="J107" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="108" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H108" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I108">
         <v>34330469</v>
       </c>
       <c r="J108" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="109" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H109" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I109">
         <v>34331612</v>
       </c>
       <c r="J109" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="110" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H110" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I110">
         <v>34352694</v>
       </c>
       <c r="J110" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="111" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H111" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I111">
         <v>39063227</v>
       </c>
       <c r="J111" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="112" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H112" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I112">
         <v>15831347</v>
       </c>
       <c r="J112" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="113" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H113" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I113">
         <v>12091621</v>
       </c>
       <c r="J113" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="114" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H114" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I114">
         <v>16805855</v>
       </c>
       <c r="J114" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="115" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H115" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I115">
         <v>15812678</v>
       </c>
       <c r="J115" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="116" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H116" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I116">
         <v>12143581</v>
       </c>
       <c r="J116" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="117" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H117" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I117">
         <v>11192165</v>
       </c>
       <c r="J117" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="118" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H118" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I118">
         <v>11192163</v>
       </c>
       <c r="J118" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="119" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H119" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I119">
         <v>12143584</v>
       </c>
       <c r="J119" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="120" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H120" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I120">
         <v>11192167</v>
       </c>
       <c r="J120" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="121" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H121" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I121">
         <v>12673238</v>
       </c>
       <c r="J121" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="122" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H122" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I122">
         <v>15838517</v>
       </c>
       <c r="J122" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="123" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H123" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I123">
         <v>12218847</v>
       </c>
       <c r="J123" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="124" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H124" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I124">
         <v>16171214</v>
       </c>
       <c r="J124" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="125" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H125" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I125">
         <v>11291291</v>
       </c>
       <c r="J125" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="126" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H126" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I126">
         <v>14134779</v>
       </c>
       <c r="J126" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="127" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H127" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I127">
         <v>14134778</v>
       </c>
       <c r="J127" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="128" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H128" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I128">
         <v>37790051</v>
       </c>
       <c r="J128" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="129" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H129" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I129">
         <v>39071990</v>
       </c>
       <c r="J129" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="130" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H130" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I130">
         <v>39006857</v>
       </c>
       <c r="J130" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="131" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H131" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I131">
         <v>39006855</v>
       </c>
       <c r="J131" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="132" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H132" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I132">
         <v>39006854</v>
       </c>
       <c r="J132" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="133" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H133" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I133">
         <v>12434130</v>
       </c>
       <c r="J133" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="134" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H134" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I134">
         <v>11671480</v>
       </c>
       <c r="J134" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="135" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H135" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I135">
         <v>11192166</v>
       </c>
       <c r="J135" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="136" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H136" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I136">
         <v>37594934</v>
       </c>
       <c r="J136" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="137" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H137" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I137">
         <v>32548061</v>
       </c>
       <c r="J137" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="138" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H138" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I138">
         <v>32711387</v>
       </c>
       <c r="J138" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="139" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H139" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I139">
         <v>32710937</v>
       </c>
       <c r="J139" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="140" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H140" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I140">
         <v>35876282</v>
       </c>
       <c r="J140" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="141" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H141" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I141">
         <v>15702671</v>
       </c>
       <c r="J141" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="142" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H142" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I142">
         <v>11229298</v>
       </c>
       <c r="J142" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="143" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H143" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I143">
         <v>50709616</v>
       </c>
       <c r="J143" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="144" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H144" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I144">
         <v>37034524</v>
       </c>
       <c r="J144" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="145" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H145" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I145">
         <v>14299890</v>
       </c>
       <c r="J145" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="146" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H146" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I146">
         <v>13195811</v>
       </c>
       <c r="J146" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="147" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H147" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I147">
         <v>36608029</v>
       </c>
       <c r="J147" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="148" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H148" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I148">
         <v>13195957</v>
@@ -4082,315 +4158,315 @@
     </row>
     <row r="149" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H149" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I149">
         <v>10121189</v>
       </c>
       <c r="J149" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="150" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H150" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I150">
         <v>8122806</v>
       </c>
       <c r="J150" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="151" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H151" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I151">
         <v>48477550</v>
       </c>
       <c r="J151" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="152" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H152" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I152">
         <v>11288089</v>
       </c>
       <c r="J152" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="153" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H153" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I153">
         <v>11104533</v>
       </c>
       <c r="J153" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="154" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H154" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I154">
         <v>10124384</v>
       </c>
       <c r="J154" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="155" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H155" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I155">
         <v>46995055</v>
       </c>
       <c r="J155" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="156" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H156" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I156">
         <v>11744316</v>
       </c>
       <c r="J156" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="157" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H157" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I157">
         <v>13069194</v>
       </c>
       <c r="J157" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="158" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H158" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I158">
         <v>19365568</v>
       </c>
       <c r="J158" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="159" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H159" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I159">
         <v>47861038</v>
       </c>
       <c r="J159" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="160" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H160" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I160">
         <v>43252471</v>
       </c>
       <c r="J160" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="161" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H161" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I161">
         <v>4125381</v>
       </c>
       <c r="J161" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="162" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H162" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I162">
         <v>38183281</v>
       </c>
       <c r="J162" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="163" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H163" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I163">
         <v>14107560</v>
       </c>
       <c r="J163" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="164" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H164" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I164">
         <v>44916947</v>
       </c>
       <c r="J164" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="165" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H165" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I165">
         <v>40640374</v>
       </c>
       <c r="J165" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="166" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H166" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I166">
         <v>13745117</v>
       </c>
       <c r="J166" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="167" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H167" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I167">
         <v>15414324</v>
       </c>
       <c r="J167" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="168" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H168" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I168">
         <v>35192489</v>
       </c>
       <c r="J168" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="169" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H169" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I169">
         <v>40982029</v>
       </c>
       <c r="J169" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="170" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H170" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I170">
         <v>10858043</v>
       </c>
       <c r="J170" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="171" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H171" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I171">
         <v>4125377</v>
       </c>
       <c r="J171" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="172" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H172" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I172">
         <v>26426530</v>
       </c>
       <c r="J172" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="173" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H173" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I173">
         <v>18980681</v>
       </c>
       <c r="J173" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="174" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H174" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I174">
         <v>12439390</v>
       </c>
       <c r="J174" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="175" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H175" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I175">
         <v>12263239</v>
       </c>
       <c r="J175" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="176" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H176" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I176">
         <v>50725354</v>
       </c>
       <c r="J176" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="177" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H177" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I177">
         <v>16179047</v>
@@ -4401,370 +4477,370 @@
     </row>
     <row r="178" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H178" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I178">
         <v>20815743</v>
       </c>
       <c r="J178" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="179" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H179" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I179">
         <v>39651008</v>
       </c>
       <c r="J179" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="180" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H180" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I180">
         <v>42839047</v>
       </c>
       <c r="J180" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="181" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H181" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I181">
         <v>38455497</v>
       </c>
       <c r="J181" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="182" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H182" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I182">
         <v>37173787</v>
       </c>
       <c r="J182" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="183" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H183" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I183">
         <v>42913903</v>
       </c>
       <c r="J183" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="184" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H184" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I184">
         <v>41864123</v>
       </c>
       <c r="J184" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="185" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H185" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I185">
         <v>4152612</v>
       </c>
       <c r="J185" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="186" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H186" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I186">
         <v>4152610</v>
       </c>
       <c r="J186" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="187" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H187" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I187">
         <v>35896315</v>
       </c>
       <c r="J187" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="188" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H188" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I188">
         <v>31743599</v>
       </c>
       <c r="J188" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="189" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H189" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I189">
         <v>4152608</v>
       </c>
       <c r="J189" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="190" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H190" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I190">
         <v>4152606</v>
       </c>
       <c r="J190" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="191" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H191" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I191">
         <v>34098917</v>
       </c>
       <c r="J191" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="192" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H192" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I192">
         <v>34801754</v>
       </c>
       <c r="J192" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="193" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H193" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I193">
         <v>37639889</v>
       </c>
       <c r="J193" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="194" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H194" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I194">
         <v>51533853</v>
       </c>
       <c r="J194" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="195" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H195" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I195">
         <v>49985232</v>
       </c>
       <c r="J195" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="196" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H196" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I196">
         <v>50155408</v>
       </c>
       <c r="J196" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="197" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H197" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I197">
         <v>35401181</v>
       </c>
       <c r="J197" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="198" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H198" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I198">
         <v>38157908</v>
       </c>
       <c r="J198" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="199" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H199" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I199">
         <v>41662266</v>
       </c>
       <c r="J199" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="200" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H200" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I200">
         <v>47936724</v>
       </c>
       <c r="J200" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="201" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H201" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I201">
         <v>38417806</v>
       </c>
       <c r="J201" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="202" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H202" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I202">
         <v>38158208</v>
       </c>
       <c r="J202" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="203" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H203" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I203">
         <v>12263163</v>
       </c>
       <c r="J203" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="204" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H204" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I204">
         <v>15826960</v>
       </c>
       <c r="J204" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="205" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H205" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I205">
         <v>13573385</v>
       </c>
       <c r="J205" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="206" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H206" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I206">
         <v>42871700</v>
       </c>
       <c r="J206" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="207" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H207" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I207">
         <v>39257536</v>
       </c>
       <c r="J207" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="208" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H208" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I208">
         <v>37424126</v>
       </c>
       <c r="J208" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="209" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H209" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I209">
         <v>36802614</v>
       </c>
       <c r="J209" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="210" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H210" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I210">
         <v>36577826</v>
       </c>
       <c r="J210" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="211" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H211" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I211">
         <v>35149611</v>
@@ -4775,128 +4851,128 @@
     </row>
     <row r="212" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H212" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I212">
         <v>26196255</v>
       </c>
       <c r="J212" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="213" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H213" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I213">
         <v>11156528</v>
       </c>
       <c r="J213" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="214" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H214" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I214">
         <v>38415503</v>
       </c>
       <c r="J214" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="215" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H215" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I215">
         <v>37244806</v>
       </c>
       <c r="J215" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="216" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H216" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I216">
         <v>27011098</v>
       </c>
       <c r="J216" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="217" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H217" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I217">
         <v>26019234</v>
       </c>
       <c r="J217" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="218" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H218" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I218">
         <v>13959023</v>
       </c>
       <c r="J218" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="219" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H219" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I219">
         <v>12496637</v>
       </c>
       <c r="J219" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="220" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H220" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I220">
         <v>25411238</v>
       </c>
       <c r="J220" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="221" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H221" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I221">
         <v>38312169</v>
       </c>
       <c r="J221" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="222" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H222" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I222">
         <v>31886592</v>
       </c>
       <c r="J222" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="223" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H223" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I223">
         <v>11670520</v>
@@ -4907,348 +4983,348 @@
     </row>
     <row r="224" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H224" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I224">
         <v>26500515</v>
       </c>
       <c r="J224" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="225" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H225" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I225">
         <v>36162739</v>
       </c>
       <c r="J225" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="226" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H226" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I226">
         <v>39893389</v>
       </c>
       <c r="J226" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="227" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H227" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I227">
         <v>39296173</v>
       </c>
       <c r="J227" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="228" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H228" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I228">
         <v>26491140</v>
       </c>
       <c r="J228" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="229" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H229" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I229">
         <v>49473587</v>
       </c>
       <c r="J229" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="230" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H230" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I230">
         <v>50326931</v>
       </c>
       <c r="J230" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="231" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H231" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I231">
         <v>12095120</v>
       </c>
       <c r="J231" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="232" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H232" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I232">
         <v>11765770</v>
       </c>
       <c r="J232" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="233" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H233" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I233">
         <v>15757638</v>
       </c>
       <c r="J233" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="234" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H234" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I234">
         <v>12038103</v>
       </c>
       <c r="J234" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="235" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H235" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I235">
         <v>46801171</v>
       </c>
       <c r="J235" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="236" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H236" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I236">
         <v>10155238</v>
       </c>
       <c r="J236" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="237" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H237" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I237">
         <v>10816066</v>
       </c>
       <c r="J237" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="238" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H238" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I238">
         <v>8668649</v>
       </c>
       <c r="J238" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="239" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H239" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I239">
         <v>36635604</v>
       </c>
       <c r="J239" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="240" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H240" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I240">
         <v>8837870</v>
       </c>
       <c r="J240" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="241" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H241" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I241">
         <v>5359040</v>
       </c>
       <c r="J241" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="242" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H242" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I242">
         <v>42373723</v>
       </c>
       <c r="J242" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="243" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H243" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I243">
         <v>16303007</v>
       </c>
       <c r="J243" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="244" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H244" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I244">
         <v>27303665</v>
       </c>
       <c r="J244" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="245" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H245" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I245">
         <v>5462299</v>
       </c>
       <c r="J245" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="246" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H246" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I246">
         <v>47220150</v>
       </c>
       <c r="J246" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="247" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H247" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I247">
         <v>42265154</v>
       </c>
       <c r="J247" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="248" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H248" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I248">
         <v>48105600</v>
       </c>
       <c r="J248" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="249" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H249" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I249">
         <v>34991467</v>
       </c>
       <c r="J249" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="250" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H250" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I250">
         <v>34348663</v>
       </c>
       <c r="J250" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="251" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H251" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I251">
         <v>34535085</v>
       </c>
       <c r="J251" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="252" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H252" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I252">
         <v>41140508</v>
       </c>
       <c r="J252" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="253" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H253" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I253">
         <v>22441147</v>
       </c>
       <c r="J253" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="254" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H254" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I254">
         <v>36811022</v>
       </c>
       <c r="J254" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="255" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H255" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I255">
         <v>36811023</v>
@@ -5259,414 +5335,414 @@
     </row>
     <row r="256" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H256" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I256">
         <v>42217758</v>
       </c>
       <c r="J256" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="257" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H257" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I257">
         <v>39384055</v>
       </c>
       <c r="J257" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="258" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H258" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I258">
         <v>11681261</v>
       </c>
       <c r="J258" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="259" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H259" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I259">
         <v>37161537</v>
       </c>
       <c r="J259" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="260" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H260" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I260">
         <v>30405071</v>
       </c>
       <c r="J260" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="261" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H261" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I261">
         <v>22403445</v>
       </c>
       <c r="J261" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="262" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H262" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I262">
         <v>26257716</v>
       </c>
       <c r="J262" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="263" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H263" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I263">
         <v>12481760</v>
       </c>
       <c r="J263" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="264" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H264" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I264">
         <v>12481759</v>
       </c>
       <c r="J264" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="265" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H265" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I265">
         <v>36682232</v>
       </c>
       <c r="J265" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="266" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H266" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I266">
         <v>46727700</v>
       </c>
       <c r="J266" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="267" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H267" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I267">
         <v>40771157</v>
       </c>
       <c r="J267" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="268" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H268" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I268">
         <v>19104731</v>
       </c>
       <c r="J268" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="269" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H269" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I269">
         <v>39944753</v>
       </c>
       <c r="J269" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="270" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H270" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I270">
         <v>48449253</v>
       </c>
       <c r="J270" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="271" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H271" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I271">
         <v>42051062</v>
       </c>
       <c r="J271" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="272" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H272" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I272">
         <v>18291047</v>
       </c>
       <c r="J272" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="273" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H273" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I273">
         <v>10727917</v>
       </c>
       <c r="J273" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="274" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H274" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I274">
         <v>46543317</v>
       </c>
       <c r="J274" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="275" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H275" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I275">
         <v>13644995</v>
       </c>
       <c r="J275" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="276" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H276" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I276">
         <v>42486414</v>
       </c>
       <c r="J276" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="277" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H277" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I277">
         <v>44695653</v>
       </c>
       <c r="J277" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="278" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H278" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I278">
         <v>44374810</v>
       </c>
       <c r="J278" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="279" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H279" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I279">
         <v>29258063</v>
       </c>
       <c r="J279" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="280" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H280" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I280">
         <v>13405604</v>
       </c>
       <c r="J280" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="281" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H281" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I281">
         <v>10646862</v>
       </c>
       <c r="J281" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="282" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H282" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I282">
         <v>12362063</v>
       </c>
       <c r="J282" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="283" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H283" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I283">
         <v>40185196</v>
       </c>
       <c r="J283" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="284" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H284" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I284">
         <v>15825326</v>
       </c>
       <c r="J284" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="285" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H285" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I285">
         <v>26375455</v>
       </c>
       <c r="J285" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="286" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H286" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I286">
         <v>42803850</v>
       </c>
       <c r="J286" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="287" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H287" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I287">
         <v>50154913</v>
       </c>
       <c r="J287" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="288" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H288" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I288">
         <v>16806254</v>
       </c>
       <c r="J288" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="289" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H289" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I289">
         <v>40501253</v>
       </c>
       <c r="J289" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="290" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H290" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I290">
         <v>14878740</v>
       </c>
       <c r="J290" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="291" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H291" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I291">
         <v>12673237</v>
       </c>
       <c r="J291" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="292" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H292" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I292">
         <v>17579662</v>
       </c>
       <c r="J292" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="293" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H293" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I293">
         <v>14719737</v>
@@ -5677,1085 +5753,1085 @@
     </row>
     <row r="294" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H294" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I294">
         <v>22119013</v>
       </c>
       <c r="J294" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="295" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H295" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I295">
         <v>15795597</v>
       </c>
       <c r="J295" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="296" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H296" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I296">
         <v>12126317</v>
       </c>
       <c r="J296" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="297" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H297" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I297">
         <v>39239709</v>
       </c>
       <c r="J297" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="298" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H298" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I298">
         <v>14488275</v>
       </c>
       <c r="J298" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="299" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H299" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I299">
         <v>42519088</v>
       </c>
       <c r="J299" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="300" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H300" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I300">
         <v>17579394</v>
       </c>
       <c r="J300" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="301" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H301" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I301">
         <v>27056005</v>
       </c>
       <c r="J301" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="302" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H302" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I302">
         <v>24832169</v>
       </c>
       <c r="J302" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="303" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H303" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I303">
         <v>39147133</v>
       </c>
       <c r="J303" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="304" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H304" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I304">
         <v>39030281</v>
       </c>
       <c r="J304" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="305" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H305" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I305">
         <v>13373616</v>
       </c>
       <c r="J305" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="306" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H306" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I306">
         <v>12757668</v>
       </c>
       <c r="J306" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="307" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H307" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I307">
         <v>38977260</v>
       </c>
       <c r="J307" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="308" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H308" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I308">
         <v>38676914</v>
       </c>
       <c r="J308" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="309" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H309" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I309">
         <v>39911056</v>
       </c>
       <c r="J309" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="310" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H310" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I310">
         <v>40102936</v>
       </c>
       <c r="J310" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="311" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H311" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I311">
         <v>10929274</v>
       </c>
       <c r="J311" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="312" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H312" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I312">
         <v>10929273</v>
       </c>
       <c r="J312" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="313" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H313" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I313">
         <v>38412071</v>
       </c>
       <c r="J313" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="314" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H314" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I314">
         <v>29280326</v>
       </c>
       <c r="J314" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="315" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H315" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I315">
         <v>38412101</v>
       </c>
       <c r="J315" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="316" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H316" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I316">
         <v>5332788</v>
       </c>
       <c r="J316" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="317" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H317" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I317">
         <v>5332789</v>
       </c>
       <c r="J317" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="318" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H318" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I318">
         <v>51016959</v>
       </c>
       <c r="J318" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="319" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H319" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I319">
         <v>40636333</v>
       </c>
       <c r="J319" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="320" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H320" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I320">
         <v>50875168</v>
       </c>
       <c r="J320" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="321" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H321" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I321">
         <v>51623281</v>
       </c>
       <c r="J321" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="322" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H322" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I322">
         <v>51897600</v>
       </c>
       <c r="J322" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="323" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H323" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I323">
         <v>51989601</v>
       </c>
       <c r="J323" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="324" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H324" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I324">
         <v>52390638</v>
       </c>
       <c r="J324" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="325" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H325" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I325">
         <v>52362395</v>
       </c>
       <c r="J325" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="326" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H326" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I326">
         <v>52155415</v>
       </c>
       <c r="J326" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="327" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H327" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I327">
         <v>52162444</v>
       </c>
       <c r="J327" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="328" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H328" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I328">
         <v>52270898</v>
       </c>
       <c r="J328" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="329" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H329" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I329">
         <v>52211558</v>
       </c>
       <c r="J329" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="330" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H330" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I330">
         <v>52217000</v>
       </c>
       <c r="J330" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="331" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H331" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I331">
         <v>51689222</v>
       </c>
       <c r="J331" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="332" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H332" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I332">
         <v>51684787</v>
       </c>
       <c r="J332" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="333" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H333" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I333">
         <v>51883980</v>
       </c>
       <c r="J333" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="334" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H334" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I334">
         <v>51898514</v>
       </c>
       <c r="J334" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="335" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H335" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I335">
         <v>52990015</v>
       </c>
       <c r="J335" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="336" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H336" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I336">
         <v>52581507</v>
       </c>
       <c r="J336" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="337" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H337" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I337">
         <v>52613211</v>
       </c>
       <c r="J337" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="338" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H338" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I338">
         <v>52578670</v>
       </c>
       <c r="J338" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="339" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H339" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I339">
         <v>52874174</v>
       </c>
       <c r="J339" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="340" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H340" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I340">
         <v>52872566</v>
       </c>
       <c r="J340" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="341" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H341" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I341">
         <v>54145830</v>
       </c>
       <c r="J341" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="342" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H342" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I342">
         <v>53052265</v>
       </c>
       <c r="J342" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="343" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H343" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I343">
         <v>53297446</v>
       </c>
       <c r="J343" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="344" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H344" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I344">
         <v>53583387</v>
       </c>
       <c r="J344" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="345" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H345" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I345">
         <v>53564659</v>
       </c>
       <c r="J345" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="346" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H346" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I346">
         <v>53569741</v>
       </c>
       <c r="J346" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="347" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H347" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I347">
         <v>53680118</v>
       </c>
       <c r="J347" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="348" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H348" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I348">
         <v>53776254</v>
       </c>
       <c r="J348" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="349" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H349" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I349">
         <v>53967042</v>
       </c>
       <c r="J349" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="350" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H350" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I350">
         <v>55275736</v>
       </c>
       <c r="J350" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="351" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H351" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I351">
         <v>56663811</v>
       </c>
       <c r="J351" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="352" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H352" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I352">
         <v>59082806</v>
       </c>
       <c r="J352" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="353" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H353" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I353">
         <v>55369678</v>
       </c>
       <c r="J353" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="354" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H354" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I354">
         <v>55354052</v>
       </c>
       <c r="J354" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="355" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H355" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I355">
         <v>55381383</v>
       </c>
       <c r="J355" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="356" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H356" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I356">
         <v>55609278</v>
       </c>
       <c r="J356" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="357" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H357" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I357">
         <v>55356212</v>
       </c>
       <c r="J357" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="358" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H358" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I358">
         <v>55449180</v>
       </c>
       <c r="J358" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="359" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H359" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I359">
         <v>55357095</v>
       </c>
       <c r="J359" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="360" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H360" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I360">
         <v>55384739</v>
       </c>
       <c r="J360" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="361" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H361" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I361">
         <v>55357155</v>
       </c>
       <c r="J361" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="362" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H362" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I362">
         <v>55389336</v>
       </c>
       <c r="J362" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="363" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H363" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I363">
         <v>55356388</v>
       </c>
       <c r="J363" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="364" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H364" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I364">
         <v>55610213</v>
       </c>
       <c r="J364" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="365" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H365" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I365">
         <v>55462718</v>
       </c>
       <c r="J365" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="366" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H366" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I366">
         <v>58084222</v>
       </c>
       <c r="J366" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="367" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H367" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I367">
         <v>56651433</v>
       </c>
       <c r="J367" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="368" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H368" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I368">
         <v>56479851</v>
       </c>
       <c r="J368" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="369" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H369" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I369">
         <v>56667264</v>
       </c>
       <c r="J369" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="370" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H370" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I370">
         <v>56896464</v>
       </c>
       <c r="J370" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="371" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H371" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I371">
         <v>57592449</v>
       </c>
       <c r="J371" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="372" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H372" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I372">
         <v>56183402</v>
       </c>
       <c r="J372" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="373" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H373" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I373">
         <v>56651667</v>
       </c>
       <c r="J373" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="374" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H374" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I374">
         <v>58987730</v>
       </c>
       <c r="J374" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="375" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H375" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I375">
         <v>57422656</v>
       </c>
       <c r="J375" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="376" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H376" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I376">
         <v>58040260</v>
       </c>
       <c r="J376" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="377" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H377" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I377">
         <v>59070986</v>
       </c>
       <c r="J377" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="378" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H378" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I378">
         <v>59058036</v>
       </c>
       <c r="J378" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="379" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H379" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I379">
         <v>58505144</v>
       </c>
       <c r="J379" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="380" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H380" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I380">
         <v>58610450</v>
       </c>
       <c r="J380" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="381" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H381" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I381">
         <v>59056260</v>
       </c>
       <c r="J381" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="382" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H382" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I382">
         <v>58722261</v>
       </c>
       <c r="J382" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="383" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H383" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I383">
         <v>58716097</v>
       </c>
       <c r="J383" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="384" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H384" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I384">
         <v>58730204</v>
       </c>
       <c r="J384" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="385" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H385" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I385">
         <v>59199875</v>
       </c>
       <c r="J385" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="386" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H386" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I386">
         <v>59759466</v>
       </c>
       <c r="J386" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="387" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H387" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I387">
         <v>59332927</v>
       </c>
       <c r="J387" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="388" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H388" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I388">
         <v>59944694</v>
       </c>
       <c r="J388" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="389" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H389" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I389">
         <v>60019261</v>
       </c>
       <c r="J389" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="390" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H390" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I390">
         <v>59932138</v>
       </c>
       <c r="J390" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="391" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H391" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I391">
         <v>59924956</v>
       </c>
       <c r="J391" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="392" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H392" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I392">
         <v>59927382</v>
@@ -6766,18 +6842,18 @@
     </row>
     <row r="393" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H393" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I393">
         <v>59836396</v>
       </c>
       <c r="J393" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="394" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H394" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I394">
         <v>60015061</v>
@@ -6788,942 +6864,942 @@
     </row>
     <row r="395" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H395" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I395">
         <v>60023938</v>
       </c>
       <c r="J395" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="396" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H396" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I396">
         <v>60025950</v>
       </c>
       <c r="J396" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="397" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H397" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I397">
         <v>60024864</v>
       </c>
       <c r="J397" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="398" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H398" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I398">
         <v>60084208</v>
       </c>
       <c r="J398" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="399" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H399" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I399">
         <v>60085614</v>
       </c>
       <c r="J399" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="400" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H400" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I400">
         <v>60133592</v>
       </c>
       <c r="J400" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="401" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H401" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I401">
         <v>60450424</v>
       </c>
       <c r="J401" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="402" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H402" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I402">
         <v>60380162</v>
       </c>
       <c r="J402" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="403" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H403" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I403">
         <v>60541542</v>
       </c>
       <c r="J403" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="404" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H404" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I404">
         <v>60541171</v>
       </c>
       <c r="J404" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="405" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H405" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I405">
         <v>60543356</v>
       </c>
       <c r="J405" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="406" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H406" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I406">
         <v>60530655</v>
       </c>
       <c r="J406" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="407" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H407" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I407">
         <v>60615380</v>
       </c>
       <c r="J407" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="408" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H408" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I408">
         <v>60725132</v>
       </c>
       <c r="J408" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="409" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H409" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I409">
         <v>62575565</v>
       </c>
       <c r="J409" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="410" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H410" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I410">
         <v>61766007</v>
       </c>
       <c r="J410" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="411" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H411" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I411">
         <v>61089339</v>
       </c>
       <c r="J411" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="412" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H412" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I412">
         <v>62377903</v>
       </c>
       <c r="J412" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="413" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H413" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I413">
         <v>60542212</v>
       </c>
       <c r="J413" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="414" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H414" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I414">
         <v>61044622</v>
       </c>
       <c r="J414" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="415" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H415" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I415">
         <v>61199642</v>
       </c>
       <c r="J415" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="416" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H416" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I416">
         <v>61760291</v>
       </c>
       <c r="J416" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="417" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H417" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I417">
         <v>61923953</v>
       </c>
       <c r="J417" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="418" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H418" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I418">
         <v>61760141</v>
       </c>
       <c r="J418" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="419" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H419" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I419">
         <v>61929592</v>
       </c>
       <c r="J419" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="420" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H420" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I420">
         <v>61929727</v>
       </c>
       <c r="J420" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="421" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H421" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I421">
         <v>61929494</v>
       </c>
       <c r="J421" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="422" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H422" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I422">
         <v>61929493</v>
       </c>
       <c r="J422" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="423" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H423" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I423">
         <v>61879892</v>
       </c>
       <c r="J423" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="424" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H424" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I424">
         <v>62378988</v>
       </c>
       <c r="J424" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="425" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H425" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I425">
         <v>62375802</v>
       </c>
       <c r="J425" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="426" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H426" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I426">
         <v>62379668</v>
       </c>
       <c r="J426" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="427" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H427" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I427">
         <v>62221331</v>
       </c>
       <c r="J427" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="428" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H428" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I428">
         <v>62385013</v>
       </c>
       <c r="J428" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="429" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H429" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I429">
         <v>62380995</v>
       </c>
       <c r="J429" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="430" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H430" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I430">
         <v>62421723</v>
       </c>
       <c r="J430" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="431" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H431" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I431">
         <v>62374813</v>
       </c>
       <c r="J431" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="432" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H432" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I432">
         <v>62499786</v>
       </c>
       <c r="J432" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="433" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H433" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I433">
         <v>62498583</v>
       </c>
       <c r="J433" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="434" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H434" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I434">
         <v>63346456</v>
       </c>
       <c r="J434" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="435" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H435" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I435">
         <v>63100963</v>
       </c>
       <c r="J435" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="436" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H436" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I436">
         <v>63396496</v>
       </c>
       <c r="J436" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="437" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H437" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I437">
         <v>64270608</v>
       </c>
       <c r="J437" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="438" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H438" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I438">
         <v>63573761</v>
       </c>
       <c r="J438" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="439" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H439" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I439">
         <v>64330763</v>
       </c>
       <c r="J439" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="440" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H440" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I440">
         <v>64330764</v>
       </c>
       <c r="J440" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="441" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H441" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I441">
         <v>64212552</v>
       </c>
       <c r="J441" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="442" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H442" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I442">
         <v>64212544</v>
       </c>
       <c r="J442" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="443" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H443" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I443">
         <v>64212543</v>
       </c>
       <c r="J443" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="444" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H444" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I444">
         <v>64212381</v>
       </c>
       <c r="J444" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="445" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H445" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I445">
         <v>64114088</v>
       </c>
       <c r="J445" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="446" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H446" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I446">
         <v>64223250</v>
       </c>
       <c r="J446" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="447" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H447" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I447">
         <v>64214259</v>
       </c>
       <c r="J447" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="448" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H448" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I448">
         <v>64214258</v>
       </c>
       <c r="J448" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="449" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H449" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I449">
         <v>63742200</v>
       </c>
       <c r="J449" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="450" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H450" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I450">
         <v>64606094</v>
       </c>
       <c r="J450" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="451" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H451" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I451">
         <v>64287980</v>
       </c>
       <c r="J451" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="452" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H452" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I452">
         <v>64257297</v>
       </c>
       <c r="J452" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="453" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H453" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I453">
         <v>66097436</v>
       </c>
       <c r="J453" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="454" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H454" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I454">
         <v>64330309</v>
       </c>
       <c r="J454" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="455" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H455" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I455">
         <v>64846264</v>
       </c>
       <c r="J455" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="456" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H456" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I456">
         <v>64753996</v>
       </c>
       <c r="J456" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="457" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H457" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I457">
         <v>64778162</v>
       </c>
       <c r="J457" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="458" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H458" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I458">
         <v>64778161</v>
       </c>
       <c r="J458" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="459" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H459" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I459">
         <v>64808932</v>
       </c>
       <c r="J459" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="460" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H460" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I460">
         <v>64789478</v>
       </c>
       <c r="J460" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="461" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H461" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I461">
         <v>64912430</v>
       </c>
       <c r="J461" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="462" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H462" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I462">
         <v>64971361</v>
       </c>
       <c r="J462" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="463" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H463" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I463">
         <v>65145714</v>
       </c>
       <c r="J463" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="464" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H464" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I464">
         <v>65081124</v>
       </c>
       <c r="J464" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="465" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H465" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I465">
         <v>65181042</v>
       </c>
       <c r="J465" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="466" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H466" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I466">
         <v>65179405</v>
       </c>
       <c r="J466" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="467" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H467" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I467">
         <v>65566244</v>
       </c>
       <c r="J467" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="468" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H468" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I468">
         <v>65566541</v>
       </c>
       <c r="J468" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="469" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H469" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I469">
         <v>65656468</v>
       </c>
       <c r="J469" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="470" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H470" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I470">
         <v>65657039</v>
       </c>
       <c r="J470" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="471" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H471" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I471">
         <v>66217025</v>
       </c>
       <c r="J471" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="472" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H472" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I472">
         <v>66214618</v>
       </c>
       <c r="J472" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="473" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H473" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I473">
         <v>65935700</v>
       </c>
       <c r="J473" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="474" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H474" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I474">
         <v>65934564</v>
       </c>
       <c r="J474" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="475" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H475" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I475">
         <v>65933937</v>
       </c>
       <c r="J475" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="476" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H476" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I476">
         <v>66046959</v>
       </c>
       <c r="J476" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="477" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H477" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I477">
         <v>65969750</v>
       </c>
       <c r="J477" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="478" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H478" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I478">
         <v>66358440</v>
       </c>
       <c r="J478" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="479" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H479" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I479">
         <v>66417803</v>
       </c>
       <c r="J479" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="480" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H480" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I480">
         <v>66417801</v>
@@ -7734,695 +7810,695 @@
     </row>
     <row r="481" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H481" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I481">
         <v>66357977</v>
       </c>
       <c r="J481" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="482" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H482" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I482">
         <v>67191572</v>
       </c>
       <c r="J482" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="483" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H483" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I483">
         <v>66546178</v>
       </c>
       <c r="J483" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="484" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H484" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I484">
         <v>67627331</v>
       </c>
       <c r="J484" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="485" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H485" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I485">
         <v>66778787</v>
       </c>
       <c r="J485" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="486" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H486" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I486">
         <v>66778788</v>
       </c>
       <c r="J486" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="487" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H487" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I487">
         <v>66778789</v>
       </c>
       <c r="J487" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="488" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H488" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I488">
         <v>66896364</v>
       </c>
       <c r="J488" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="489" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H489" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I489">
         <v>66607099</v>
       </c>
       <c r="J489" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="490" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H490" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I490">
         <v>66864708</v>
       </c>
       <c r="J490" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="491" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H491" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I491">
         <v>66850322</v>
       </c>
       <c r="J491" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="492" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H492" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I492">
         <v>67268341</v>
       </c>
       <c r="J492" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="493" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H493" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I493">
         <v>67268348</v>
       </c>
       <c r="J493" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="494" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H494" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I494">
         <v>67268349</v>
       </c>
       <c r="J494" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="495" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H495" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I495">
         <v>67268350</v>
       </c>
       <c r="J495" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="496" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H496" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I496">
         <v>67272047</v>
       </c>
       <c r="J496" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="497" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H497" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I497">
         <v>67272046</v>
       </c>
       <c r="J497" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="498" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H498" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I498">
         <v>67438488</v>
       </c>
       <c r="J498" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="499" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H499" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I499">
         <v>67438487</v>
       </c>
       <c r="J499" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="500" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H500" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I500">
         <v>68253037</v>
       </c>
       <c r="J500" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="501" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H501" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I501">
         <v>67891311</v>
       </c>
       <c r="J501" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="502" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H502" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I502">
         <v>67900090</v>
       </c>
       <c r="J502" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="503" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H503" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I503">
         <v>67630646</v>
       </c>
       <c r="J503" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="504" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H504" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I504">
         <v>67974104</v>
       </c>
       <c r="J504" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="505" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H505" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I505">
         <v>67989839</v>
       </c>
       <c r="J505" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="506" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H506" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I506">
         <v>67988468</v>
       </c>
       <c r="J506" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="507" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H507" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I507">
         <v>68466892</v>
       </c>
       <c r="J507" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="508" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H508" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I508">
         <v>69040158</v>
       </c>
       <c r="J508" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="509" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H509" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I509">
         <v>68462854</v>
       </c>
       <c r="J509" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="510" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H510" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I510" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="J510" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="511" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H511" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I511" t="s">
+        <v>536</v>
+      </c>
+      <c r="J511" t="s">
         <v>538</v>
-      </c>
-      <c r="J511" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="512" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H512" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I512">
         <v>68677002</v>
       </c>
       <c r="J512" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="513" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H513" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I513">
         <v>68880617</v>
       </c>
       <c r="J513" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="514" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H514" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I514">
         <v>68934411</v>
       </c>
       <c r="J514" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="515" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H515" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I515">
         <v>68924611</v>
       </c>
       <c r="J515" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="516" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H516" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I516">
         <v>69039437</v>
       </c>
       <c r="J516" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="517" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H517" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I517">
         <v>69039778</v>
       </c>
       <c r="J517" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="518" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H518" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I518">
         <v>69279032</v>
       </c>
       <c r="J518" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="519" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H519" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I519">
         <v>68938743</v>
       </c>
       <c r="J519" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="520" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H520" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I520">
         <v>69772629</v>
       </c>
       <c r="J520" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="521" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H521" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I521">
         <v>69772627</v>
       </c>
       <c r="J521" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="522" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H522" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I522">
         <v>69772625</v>
       </c>
       <c r="J522" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="523" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H523" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I523">
         <v>69292187</v>
       </c>
       <c r="J523" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="524" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H524" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I524">
         <v>69292186</v>
       </c>
       <c r="J524" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="525" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H525" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I525">
         <v>69292185</v>
       </c>
       <c r="J525" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="526" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H526" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I526">
         <v>69096297</v>
       </c>
       <c r="J526" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="527" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H527" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I527">
         <v>69096296</v>
       </c>
       <c r="J527" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="528" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H528" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I528">
         <v>69594684</v>
       </c>
       <c r="J528" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="529" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H529" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I529">
         <v>70204974</v>
       </c>
       <c r="J529" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="530" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H530" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I530">
         <v>70204975</v>
       </c>
       <c r="J530" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="531" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H531" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I531">
         <v>69767288</v>
       </c>
       <c r="J531" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="532" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H532" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I532">
         <v>69766464</v>
       </c>
       <c r="J532" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="533" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H533" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I533">
         <v>69803799</v>
       </c>
       <c r="J533" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="534" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H534" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I534">
         <v>70251147</v>
       </c>
       <c r="J534" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="535" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H535" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I535">
         <v>69770093</v>
       </c>
       <c r="J535" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="536" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H536" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I536">
         <v>70205079</v>
       </c>
       <c r="J536" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="537" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H537" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I537">
         <v>70530577</v>
       </c>
       <c r="J537" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="538" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H538" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I538">
         <v>70530576</v>
       </c>
       <c r="J538" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="539" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H539" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I539">
         <v>71030052</v>
       </c>
       <c r="J539" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="540" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H540" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I540">
         <v>70770186</v>
       </c>
       <c r="J540" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="541" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H541" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I541">
         <v>71173111</v>
       </c>
       <c r="J541" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="542" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H542" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I542">
         <v>71156871</v>
       </c>
       <c r="J542" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="543" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H543" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I543">
         <v>71291488</v>
       </c>
       <c r="J543" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="544" spans="8:10" x14ac:dyDescent="0.3">
@@ -8430,331 +8506,331 @@
         <v>71042279</v>
       </c>
       <c r="J544" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="545" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H545" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I545">
         <v>71947627</v>
       </c>
       <c r="J545" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="546" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H546" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I546">
         <v>72182444</v>
       </c>
       <c r="J546" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="547" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H547" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I547">
         <v>72300747</v>
       </c>
       <c r="J547" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="548" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H548" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I548">
         <v>72417582</v>
       </c>
       <c r="J548" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="549" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H549" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I549">
         <v>72614935</v>
       </c>
       <c r="J549" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="550" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H550" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I550">
         <v>72614936</v>
       </c>
       <c r="J550" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="551" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H551" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I551">
         <v>72614937</v>
       </c>
       <c r="J551" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="552" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H552" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I552">
         <v>73226633</v>
       </c>
       <c r="J552" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="553" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H553" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I553">
         <v>73226632</v>
       </c>
       <c r="J553" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="554" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H554" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I554">
         <v>73316683</v>
       </c>
       <c r="J554" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="555" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H555" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I555">
         <v>73316684</v>
       </c>
       <c r="J555" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="556" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H556" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I556">
         <v>73316685</v>
       </c>
       <c r="J556" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="557" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H557" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I557">
         <v>72699936</v>
       </c>
       <c r="J557" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="558" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H558" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I558">
         <v>72699935</v>
       </c>
       <c r="J558" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="559" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H559" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I559">
         <v>72828733</v>
       </c>
       <c r="J559" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="560" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H560" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I560">
         <v>72828734</v>
       </c>
       <c r="J560" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="561" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H561" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I561">
         <v>72683872</v>
       </c>
       <c r="J561" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
     </row>
     <row r="562" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H562" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I562">
         <v>72910681</v>
       </c>
       <c r="J562" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="563" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H563" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I563">
         <v>72910683</v>
       </c>
       <c r="J563" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="564" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H564" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I564">
         <v>73523448</v>
       </c>
       <c r="J564" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="565" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H565" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I565">
         <v>73461995</v>
       </c>
       <c r="J565" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="566" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H566" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I566">
         <v>73956460</v>
       </c>
       <c r="J566" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
     </row>
     <row r="567" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H567" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I567">
         <v>73956461</v>
       </c>
       <c r="J567" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="568" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H568" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I568">
         <v>73956459</v>
       </c>
       <c r="J568" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="569" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H569" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I569">
         <v>74685916</v>
       </c>
       <c r="J569" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="570" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H570" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I570">
         <v>73975553</v>
       </c>
       <c r="J570" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="571" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H571" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I571">
         <v>73952843</v>
       </c>
       <c r="J571" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="572" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H572" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I572">
         <v>74550323</v>
       </c>
       <c r="J572" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="573" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H573" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I573">
         <v>75989703</v>
       </c>
       <c r="J573" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="574" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H574" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I574">
         <v>74693807</v>
@@ -8765,325 +8841,326 @@
     </row>
     <row r="575" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H575" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I575">
         <v>73893263</v>
       </c>
       <c r="J575" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="576" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H576" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I576">
         <v>74884452</v>
       </c>
       <c r="J576" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="577" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H577" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I577">
         <v>74826973</v>
       </c>
       <c r="J577" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="578" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H578" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I578">
         <v>74826974</v>
       </c>
       <c r="J578" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="579" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H579" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I579">
         <v>75077119</v>
       </c>
       <c r="J579" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="580" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H580" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I580" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="J580" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="581" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H581" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I581" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="J581" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="582" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H582" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I582">
         <v>75741354</v>
       </c>
       <c r="J582" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="583" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H583" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I583" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="J583" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="584" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H584" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I584">
         <v>76375598</v>
       </c>
       <c r="J584" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="585" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H585" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I585">
         <v>76375597</v>
       </c>
       <c r="J585" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="586" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H586" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I586">
         <v>76374400</v>
       </c>
       <c r="J586" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="587" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H587" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I587">
         <v>76374401</v>
       </c>
       <c r="J587" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="588" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H588" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I588">
         <v>76241042</v>
       </c>
       <c r="J588" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="589" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H589" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I589">
         <v>76533940</v>
       </c>
       <c r="J589" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="590" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H590" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I590">
         <v>77463489</v>
       </c>
       <c r="J590" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="591" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H591" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I591">
         <v>77463490</v>
       </c>
       <c r="J591" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="592" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H592" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I592" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="J592" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="593" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H593" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I593" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="J593" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="594" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H594" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I594" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="J594" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="595" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H595" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I595" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="J595" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="596" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H596" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I596" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="J596" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="601" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H601" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I601" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="J601" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="602" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H602" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I602" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="J602" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="603" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H603" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I603" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="J603" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="604" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H604" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I604" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="J604" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="605" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H605" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I605" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="J605" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="606" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H606" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I606" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="J606" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="607" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H607" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I607" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="J607" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/이슈제품.xlsx
+++ b/data/이슈제품.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OA\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{627BD93C-0AC3-444D-A690-B7D54F5C6975}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{507F2ADA-BACB-41C2-AF58-DC2A8BAB6663}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="647">
   <si>
     <t>오아디머무드등-화이트</t>
   </si>
@@ -76,9 +76,6 @@
   </si>
   <si>
     <t>보아르이지전기포트M1(FV)-아이보리</t>
-  </si>
-  <si>
-    <t>협의, 8/10 5000대</t>
   </si>
   <si>
     <t>보아르터보스티머-아이보리</t>
@@ -1919,10 +1916,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>입고X, 9/30 예정</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>입고X, 10월말 예정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1960,6 +1953,35 @@
   </si>
   <si>
     <t>오아넥스트레쳐S-베이지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오아클린이워터전용제트팁2P-J</t>
+  </si>
+  <si>
+    <t>오아클린이워터전용제트팁2P-B-D-F-Z</t>
+  </si>
+  <si>
+    <t>오아클린이워터전용5종팁세트-B-D-F-Z</t>
+  </si>
+  <si>
+    <t>입고X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>운영X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입고X, 10월 중순</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>협의, 10월 말</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>협의, 11월 초</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1967,7 +1989,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1978,6 +2000,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
@@ -2006,8 +2036,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2305,22 +2338,22 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s">
         <v>26</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>27</v>
       </c>
-      <c r="C1" t="s">
+      <c r="H1" t="s">
         <v>28</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>29</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>30</v>
-      </c>
-      <c r="J1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -2334,13 +2367,13 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I2">
         <v>3636925</v>
       </c>
       <c r="J2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -2354,13 +2387,13 @@
         <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I3">
         <v>3636926</v>
       </c>
       <c r="J3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -2368,273 +2401,273 @@
         <v>76375597</v>
       </c>
       <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
         <v>24</v>
       </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
       <c r="H4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I4">
         <v>3636927</v>
       </c>
       <c r="J4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>73893263</v>
+        <v>58505144</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I5">
         <v>39415252</v>
       </c>
       <c r="J5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>58505144</v>
+        <v>50725354</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>209</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>627</v>
       </c>
       <c r="H6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I6">
         <v>19213859</v>
       </c>
       <c r="J6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>50725354</v>
+        <v>12263239</v>
       </c>
       <c r="B7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C7" t="s">
         <v>628</v>
       </c>
       <c r="H7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I7">
         <v>20342327</v>
       </c>
       <c r="J7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>12263239</v>
+        <v>68880617</v>
       </c>
       <c r="B8" t="s">
-        <v>209</v>
+        <v>638</v>
       </c>
       <c r="C8" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I8">
         <v>13004238</v>
       </c>
       <c r="J8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>68880617</v>
+        <v>42519088</v>
       </c>
       <c r="B9" t="s">
-        <v>640</v>
+        <v>329</v>
       </c>
       <c r="C9" t="s">
-        <v>629</v>
+        <v>644</v>
       </c>
       <c r="H9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I9">
         <v>20341619</v>
       </c>
       <c r="J9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>60380162</v>
+        <v>4152606</v>
       </c>
       <c r="B10" t="s">
-        <v>429</v>
+        <v>224</v>
       </c>
       <c r="C10" t="s">
-        <v>630</v>
+        <v>646</v>
       </c>
       <c r="H10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I10">
         <v>11092035</v>
       </c>
       <c r="J10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>60450424</v>
+        <v>4125377</v>
       </c>
       <c r="B11" t="s">
-        <v>428</v>
+        <v>204</v>
       </c>
       <c r="C11" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I11">
         <v>40852278</v>
       </c>
       <c r="J11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>4125377</v>
+        <v>26426530</v>
       </c>
       <c r="B12" t="s">
         <v>205</v>
       </c>
       <c r="C12" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="H12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I12">
         <v>29266932</v>
       </c>
       <c r="J12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>26426530</v>
+        <v>12439390</v>
       </c>
       <c r="B13" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C13" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="H13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I13">
         <v>12586373</v>
       </c>
       <c r="J13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>12439390</v>
+        <v>5332788</v>
       </c>
       <c r="B14" t="s">
-        <v>208</v>
+        <v>346</v>
       </c>
       <c r="C14" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="H14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I14">
         <v>11055651</v>
       </c>
       <c r="J14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>5332788</v>
+        <v>11229298</v>
       </c>
       <c r="B15" t="s">
-        <v>347</v>
+        <v>176</v>
       </c>
       <c r="C15" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="H15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I15">
         <v>38659485</v>
       </c>
       <c r="J15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>11229298</v>
+        <v>27056005</v>
       </c>
       <c r="B16" t="s">
-        <v>177</v>
+        <v>331</v>
       </c>
       <c r="C16" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="H16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I16">
         <v>9567647</v>
       </c>
       <c r="J16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>27056005</v>
+        <v>50153946</v>
       </c>
       <c r="B17" t="s">
-        <v>332</v>
+        <v>116</v>
       </c>
       <c r="C17" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I17">
         <v>40180424</v>
@@ -2645,783 +2678,1098 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>50153946</v>
+        <v>69096296</v>
       </c>
       <c r="B18" t="s">
-        <v>117</v>
+        <v>553</v>
       </c>
       <c r="C18" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="H18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I18">
         <v>39228155</v>
       </c>
       <c r="J18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>69096296</v>
+        <v>75741354</v>
       </c>
       <c r="B19" t="s">
-        <v>554</v>
+        <v>606</v>
       </c>
       <c r="C19" t="s">
-        <v>639</v>
+        <v>629</v>
       </c>
       <c r="H19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I19">
         <v>38407975</v>
       </c>
       <c r="J19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>75741354</v>
+        <v>16303007</v>
       </c>
       <c r="B20" t="s">
-        <v>607</v>
+        <v>275</v>
       </c>
       <c r="C20" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="H20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I20">
         <v>38545387</v>
       </c>
       <c r="J20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>16303007</v>
+        <v>60542212</v>
       </c>
       <c r="B21" t="s">
-        <v>276</v>
+        <v>439</v>
       </c>
       <c r="C21" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="H21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I21">
         <v>18816827</v>
       </c>
       <c r="J21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>60542212</v>
+        <v>13101217</v>
       </c>
       <c r="B22" t="s">
-        <v>440</v>
+        <v>72</v>
       </c>
       <c r="C22" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I22">
         <v>39278162</v>
       </c>
       <c r="J22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>13101217</v>
+        <v>15414324</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
+        <v>200</v>
       </c>
       <c r="C23" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I23">
         <v>13100374</v>
       </c>
       <c r="J23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>15414324</v>
+        <v>31743599</v>
       </c>
       <c r="B24" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="C24" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I24">
         <v>10855225</v>
       </c>
       <c r="J24" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>31743599</v>
-      </c>
-      <c r="B25" t="s">
-        <v>223</v>
+        <v>51623281</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>640</v>
       </c>
       <c r="C25" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="H25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I25">
         <v>38490171</v>
       </c>
       <c r="J25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>51989601</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="C26" t="s">
+        <v>642</v>
+      </c>
       <c r="H26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I26">
         <v>38490170</v>
       </c>
       <c r="J26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>11192166</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C27" t="s">
+        <v>642</v>
+      </c>
       <c r="H27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I27">
         <v>38417027</v>
       </c>
       <c r="J27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>15812678</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C28" t="s">
+        <v>642</v>
+      </c>
       <c r="H28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I28">
         <v>13099542</v>
       </c>
       <c r="J28" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>12091621</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C29" t="s">
+        <v>642</v>
+      </c>
+      <c r="H29" t="s">
         <v>58</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="H29" t="s">
-        <v>59</v>
       </c>
       <c r="I29">
         <v>10324264</v>
       </c>
       <c r="J29" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>12143584</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C30" t="s">
+        <v>642</v>
+      </c>
+      <c r="H30" t="s">
         <v>60</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="H30" t="s">
-        <v>61</v>
       </c>
       <c r="I30">
         <v>39229235</v>
       </c>
       <c r="J30" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>11192167</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C31" t="s">
+        <v>642</v>
+      </c>
       <c r="H31" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I31">
         <v>12775098</v>
       </c>
       <c r="J31" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>12143581</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C32" t="s">
+        <v>642</v>
+      </c>
       <c r="H32" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I32">
         <v>12775097</v>
       </c>
       <c r="J32" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="33" spans="8:10" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>11192165</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C33" t="s">
+        <v>642</v>
+      </c>
       <c r="H33" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I33">
         <v>12775096</v>
       </c>
       <c r="J33" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="34" spans="8:10" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>11192163</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C34" t="s">
+        <v>642</v>
+      </c>
       <c r="H34" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I34">
         <v>13151160</v>
       </c>
       <c r="J34" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="35" spans="8:10" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>11291291</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C35" t="s">
+        <v>642</v>
+      </c>
       <c r="H35" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I35">
         <v>13151158</v>
       </c>
       <c r="J35" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="36" spans="8:10" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>16171214</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C36" t="s">
+        <v>642</v>
+      </c>
       <c r="H36" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I36">
         <v>35403063</v>
       </c>
       <c r="J36" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="37" spans="8:10" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>12218847</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C37" t="s">
+        <v>642</v>
+      </c>
       <c r="H37" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I37">
         <v>13473750</v>
       </c>
       <c r="J37" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="38" spans="8:10" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>15838517</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C38" t="s">
+        <v>642</v>
+      </c>
       <c r="H38" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I38">
         <v>17014694</v>
       </c>
       <c r="J38" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="39" spans="8:10" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>12673238</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C39" t="s">
+        <v>642</v>
+      </c>
       <c r="H39" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I39">
         <v>17014693</v>
       </c>
       <c r="J39" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="40" spans="8:10" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>37790051</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C40" t="s">
+        <v>642</v>
+      </c>
       <c r="H40" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I40">
         <v>13101218</v>
       </c>
       <c r="J40" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="41" spans="8:10" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>37594934</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C41" t="s">
+        <v>642</v>
+      </c>
       <c r="H41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I41">
         <v>13101217</v>
       </c>
       <c r="J41" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="42" spans="8:10" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>15702671</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C42" t="s">
+        <v>642</v>
+      </c>
       <c r="H42" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I42">
         <v>16981939</v>
       </c>
       <c r="J42" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="43" spans="8:10" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>39071990</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C43" t="s">
+        <v>642</v>
+      </c>
       <c r="H43" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I43">
         <v>12846219</v>
       </c>
       <c r="J43" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="44" spans="8:10" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>52204284</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C44" t="s">
+        <v>642</v>
+      </c>
       <c r="H44" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I44">
         <v>17398556</v>
       </c>
       <c r="J44" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="45" spans="8:10" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>39006854</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C45" t="s">
+        <v>642</v>
+      </c>
       <c r="H45" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I45">
         <v>16972627</v>
       </c>
       <c r="J45" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="46" spans="8:10" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>39006857</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C46" t="s">
+        <v>642</v>
+      </c>
       <c r="H46" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I46">
         <v>12846215</v>
       </c>
       <c r="J46" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="47" spans="8:10" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>39006855</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C47" t="s">
+        <v>642</v>
+      </c>
       <c r="H47" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I47">
         <v>39663616</v>
       </c>
       <c r="J47" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="48" spans="8:10" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>51883980</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C48" t="s">
+        <v>642</v>
+      </c>
       <c r="H48" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I48">
         <v>37843037</v>
       </c>
       <c r="J48" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="49" spans="8:10" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>52578670</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C49" t="s">
+        <v>642</v>
+      </c>
       <c r="H49" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I49">
         <v>12465755</v>
       </c>
       <c r="J49" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="50" spans="8:10" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>52155531</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C50" t="s">
+        <v>642</v>
+      </c>
       <c r="H50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I50">
         <v>11671481</v>
       </c>
       <c r="J50" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="51" spans="8:10" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>15831347</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C51" t="s">
+        <v>642</v>
+      </c>
       <c r="H51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I51">
         <v>12685386</v>
       </c>
       <c r="J51" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="52" spans="8:10" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>32548061</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C52" t="s">
+        <v>642</v>
+      </c>
       <c r="H52" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I52">
         <v>12674974</v>
       </c>
       <c r="J52" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="53" spans="8:10" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>35876282</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C53" t="s">
+        <v>642</v>
+      </c>
       <c r="H53" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I53">
         <v>12674973</v>
       </c>
       <c r="J53" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="54" spans="8:10" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>16805855</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C54" t="s">
+        <v>642</v>
+      </c>
       <c r="H54" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I54">
         <v>27515992</v>
       </c>
       <c r="J54" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="55" spans="8:10" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>55381383</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="C55" t="s">
+        <v>642</v>
+      </c>
       <c r="H55" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I55">
         <v>18928667</v>
       </c>
       <c r="J55" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="56" spans="8:10" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>55449180</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C56" t="s">
+        <v>642</v>
+      </c>
       <c r="H56" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I56">
         <v>14218803</v>
       </c>
       <c r="J56" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="57" spans="8:10" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>55384739</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C57" t="s">
+        <v>642</v>
+      </c>
       <c r="H57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I57">
         <v>14218802</v>
       </c>
       <c r="J57" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="58" spans="8:10" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>55389336</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="C58" t="s">
+        <v>642</v>
+      </c>
       <c r="H58" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I58">
         <v>14473529</v>
       </c>
       <c r="J58" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="59" spans="8:10" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>55609278</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C59" t="s">
+        <v>642</v>
+      </c>
       <c r="H59" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I59">
         <v>25512595</v>
       </c>
       <c r="J59" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="60" spans="8:10" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>71042279</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="C60" t="s">
+        <v>643</v>
+      </c>
       <c r="H60" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I60">
         <v>25433097</v>
       </c>
       <c r="J60" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="61" spans="8:10" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H61" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I61">
         <v>50012601</v>
       </c>
       <c r="J61" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H62" t="s">
         <v>92</v>
-      </c>
-    </row>
-    <row r="62" spans="8:10" x14ac:dyDescent="0.3">
-      <c r="H62" t="s">
-        <v>93</v>
       </c>
       <c r="I62">
         <v>52204284</v>
       </c>
       <c r="J62" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H63" t="s">
         <v>94</v>
-      </c>
-    </row>
-    <row r="63" spans="8:10" x14ac:dyDescent="0.3">
-      <c r="H63" t="s">
-        <v>95</v>
       </c>
       <c r="I63">
         <v>52155531</v>
       </c>
       <c r="J63" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H64" t="s">
         <v>96</v>
-      </c>
-    </row>
-    <row r="64" spans="8:10" x14ac:dyDescent="0.3">
-      <c r="H64" t="s">
-        <v>97</v>
       </c>
       <c r="I64">
         <v>10814871</v>
       </c>
       <c r="J64" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="65" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H65" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I65">
         <v>31792560</v>
       </c>
       <c r="J65" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="66" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H66" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I66">
         <v>10694343</v>
       </c>
       <c r="J66" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="67" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H67" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I67">
         <v>43431417</v>
       </c>
       <c r="J67" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="68" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H68" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I68">
         <v>10978754</v>
       </c>
       <c r="J68" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="69" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H69" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I69">
         <v>10974363</v>
       </c>
       <c r="J69" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="70" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H70" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I70">
         <v>39376011</v>
       </c>
       <c r="J70" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="71" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H71" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I71">
         <v>38310913</v>
       </c>
       <c r="J71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="72" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H72" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I72">
         <v>40639939</v>
       </c>
       <c r="J72" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="73" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H73" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I73">
         <v>44581094</v>
       </c>
       <c r="J73" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="74" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H74" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I74">
         <v>39270777</v>
       </c>
       <c r="J74" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="75" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H75" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I75">
         <v>45342904</v>
       </c>
       <c r="J75" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="76" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H76" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I76">
         <v>19619417</v>
       </c>
       <c r="J76" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="77" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H77" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I77">
         <v>36606823</v>
       </c>
       <c r="J77" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="78" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H78" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I78">
         <v>12585217</v>
       </c>
       <c r="J78" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="79" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H79" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I79">
         <v>11511332</v>
       </c>
       <c r="J79" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="80" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H80" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I80">
         <v>12579597</v>
       </c>
       <c r="J80" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="81" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H81" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I81">
         <v>50153946</v>
       </c>
       <c r="J81" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="82" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H82" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I82">
         <v>50723598</v>
@@ -3432,40 +3780,40 @@
     </row>
     <row r="83" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H83" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I83">
         <v>34464589</v>
       </c>
       <c r="J83" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="84" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H84" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I84">
         <v>12029130</v>
       </c>
       <c r="J84" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="85" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H85" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I85">
         <v>46962408</v>
       </c>
       <c r="J85" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="86" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H86" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I86">
         <v>11874445</v>
@@ -3476,106 +3824,106 @@
     </row>
     <row r="87" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H87" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I87">
         <v>25665354</v>
       </c>
       <c r="J87" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="88" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H88" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I88">
         <v>46550390</v>
       </c>
       <c r="J88" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="89" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H89" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I89">
         <v>45573288</v>
       </c>
       <c r="J89" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="90" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H90" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I90">
         <v>34318450</v>
       </c>
       <c r="J90" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="91" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H91" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I91">
         <v>45701215</v>
       </c>
       <c r="J91" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H92" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I92">
         <v>15004955</v>
       </c>
       <c r="J92" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="93" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H93" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I93">
         <v>25321998</v>
       </c>
       <c r="J93" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="94" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H94" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I94">
         <v>25321996</v>
       </c>
       <c r="J94" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="95" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H95" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I95">
         <v>46191377</v>
       </c>
       <c r="J95" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="96" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H96" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I96">
         <v>45349063</v>
@@ -3586,568 +3934,568 @@
     </row>
     <row r="97" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H97" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I97">
         <v>44996967</v>
       </c>
       <c r="J97" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="98" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H98" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I98">
         <v>15462869</v>
       </c>
       <c r="J98" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="99" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H99" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I99">
         <v>15462868</v>
       </c>
       <c r="J99" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="100" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H100" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I100">
         <v>46671749</v>
       </c>
       <c r="J100" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="101" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H101" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I101">
         <v>35137369</v>
       </c>
       <c r="J101" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="102" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H102" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I102">
         <v>34320929</v>
       </c>
       <c r="J102" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="103" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H103" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I103">
         <v>34320928</v>
       </c>
       <c r="J103" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="104" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H104" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I104">
         <v>23200605</v>
       </c>
       <c r="J104" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="105" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H105" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I105">
         <v>23200603</v>
       </c>
       <c r="J105" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="106" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H106" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I106">
         <v>43571361</v>
       </c>
       <c r="J106" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="107" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H107" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I107">
         <v>43571360</v>
       </c>
       <c r="J107" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="108" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H108" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I108">
         <v>34330469</v>
       </c>
       <c r="J108" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="109" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H109" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I109">
         <v>34331612</v>
       </c>
       <c r="J109" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="110" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H110" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I110">
         <v>34352694</v>
       </c>
       <c r="J110" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="111" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H111" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I111">
         <v>39063227</v>
       </c>
       <c r="J111" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="112" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H112" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I112">
         <v>15831347</v>
       </c>
       <c r="J112" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="113" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H113" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I113">
         <v>12091621</v>
       </c>
       <c r="J113" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="114" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H114" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I114">
         <v>16805855</v>
       </c>
       <c r="J114" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="115" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H115" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I115">
         <v>15812678</v>
       </c>
       <c r="J115" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="116" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H116" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I116">
         <v>12143581</v>
       </c>
       <c r="J116" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="117" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H117" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I117">
         <v>11192165</v>
       </c>
       <c r="J117" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="118" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H118" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I118">
         <v>11192163</v>
       </c>
       <c r="J118" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="119" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H119" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I119">
         <v>12143584</v>
       </c>
       <c r="J119" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="120" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H120" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I120">
         <v>11192167</v>
       </c>
       <c r="J120" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="121" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H121" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I121">
         <v>12673238</v>
       </c>
       <c r="J121" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="122" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H122" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I122">
         <v>15838517</v>
       </c>
       <c r="J122" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="123" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H123" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I123">
         <v>12218847</v>
       </c>
       <c r="J123" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="124" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H124" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I124">
         <v>16171214</v>
       </c>
       <c r="J124" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="125" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H125" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I125">
         <v>11291291</v>
       </c>
       <c r="J125" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="126" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H126" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I126">
         <v>14134779</v>
       </c>
       <c r="J126" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="127" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H127" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I127">
         <v>14134778</v>
       </c>
       <c r="J127" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="128" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H128" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I128">
         <v>37790051</v>
       </c>
       <c r="J128" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="129" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H129" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I129">
         <v>39071990</v>
       </c>
       <c r="J129" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="130" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H130" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I130">
         <v>39006857</v>
       </c>
       <c r="J130" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="131" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H131" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I131">
         <v>39006855</v>
       </c>
       <c r="J131" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="132" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H132" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I132">
         <v>39006854</v>
       </c>
       <c r="J132" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="133" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H133" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I133">
         <v>12434130</v>
       </c>
       <c r="J133" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="134" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H134" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I134">
         <v>11671480</v>
       </c>
       <c r="J134" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="135" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H135" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I135">
         <v>11192166</v>
       </c>
       <c r="J135" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="136" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H136" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I136">
         <v>37594934</v>
       </c>
       <c r="J136" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="137" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H137" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I137">
         <v>32548061</v>
       </c>
       <c r="J137" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="138" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H138" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I138">
         <v>32711387</v>
       </c>
       <c r="J138" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="139" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H139" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I139">
         <v>32710937</v>
       </c>
       <c r="J139" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="140" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H140" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I140">
         <v>35876282</v>
       </c>
       <c r="J140" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="141" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H141" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I141">
         <v>15702671</v>
       </c>
       <c r="J141" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="142" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H142" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I142">
         <v>11229298</v>
       </c>
       <c r="J142" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="143" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H143" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I143">
         <v>50709616</v>
       </c>
       <c r="J143" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="144" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H144" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I144">
         <v>37034524</v>
       </c>
       <c r="J144" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="145" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H145" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I145">
         <v>14299890</v>
       </c>
       <c r="J145" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="146" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H146" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I146">
         <v>13195811</v>
       </c>
       <c r="J146" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="147" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H147" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I147">
         <v>36608029</v>
       </c>
       <c r="J147" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="148" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H148" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I148">
         <v>13195957</v>
@@ -4158,315 +4506,315 @@
     </row>
     <row r="149" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H149" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I149">
         <v>10121189</v>
       </c>
       <c r="J149" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="150" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H150" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I150">
         <v>8122806</v>
       </c>
       <c r="J150" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="151" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H151" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I151">
         <v>48477550</v>
       </c>
       <c r="J151" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="152" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H152" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I152">
         <v>11288089</v>
       </c>
       <c r="J152" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="153" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H153" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I153">
         <v>11104533</v>
       </c>
       <c r="J153" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="154" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H154" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I154">
         <v>10124384</v>
       </c>
       <c r="J154" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="155" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H155" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I155">
         <v>46995055</v>
       </c>
       <c r="J155" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="156" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H156" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I156">
         <v>11744316</v>
       </c>
       <c r="J156" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="157" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H157" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I157">
         <v>13069194</v>
       </c>
       <c r="J157" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="158" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H158" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I158">
         <v>19365568</v>
       </c>
       <c r="J158" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="159" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H159" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I159">
         <v>47861038</v>
       </c>
       <c r="J159" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="160" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H160" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I160">
         <v>43252471</v>
       </c>
       <c r="J160" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="161" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H161" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I161">
         <v>4125381</v>
       </c>
       <c r="J161" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="162" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H162" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I162">
         <v>38183281</v>
       </c>
       <c r="J162" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="163" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H163" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I163">
         <v>14107560</v>
       </c>
       <c r="J163" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="164" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H164" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I164">
         <v>44916947</v>
       </c>
       <c r="J164" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="165" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H165" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I165">
         <v>40640374</v>
       </c>
       <c r="J165" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="166" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H166" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I166">
         <v>13745117</v>
       </c>
       <c r="J166" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="167" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H167" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I167">
         <v>15414324</v>
       </c>
       <c r="J167" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="168" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H168" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I168">
         <v>35192489</v>
       </c>
       <c r="J168" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="169" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H169" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I169">
         <v>40982029</v>
       </c>
       <c r="J169" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="170" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H170" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I170">
         <v>10858043</v>
       </c>
       <c r="J170" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="171" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H171" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I171">
         <v>4125377</v>
       </c>
       <c r="J171" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="172" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H172" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I172">
         <v>26426530</v>
       </c>
       <c r="J172" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="173" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H173" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I173">
         <v>18980681</v>
       </c>
       <c r="J173" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="174" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H174" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I174">
         <v>12439390</v>
       </c>
       <c r="J174" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="175" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H175" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I175">
         <v>12263239</v>
       </c>
       <c r="J175" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="176" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H176" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I176">
         <v>50725354</v>
       </c>
       <c r="J176" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="177" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H177" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I177">
         <v>16179047</v>
@@ -4477,370 +4825,370 @@
     </row>
     <row r="178" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H178" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I178">
         <v>20815743</v>
       </c>
       <c r="J178" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="179" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H179" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I179">
         <v>39651008</v>
       </c>
       <c r="J179" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="180" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H180" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I180">
         <v>42839047</v>
       </c>
       <c r="J180" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="181" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H181" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I181">
         <v>38455497</v>
       </c>
       <c r="J181" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="182" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H182" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I182">
         <v>37173787</v>
       </c>
       <c r="J182" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="183" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H183" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I183">
         <v>42913903</v>
       </c>
       <c r="J183" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="184" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H184" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I184">
         <v>41864123</v>
       </c>
       <c r="J184" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="185" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H185" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I185">
         <v>4152612</v>
       </c>
       <c r="J185" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="186" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H186" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I186">
         <v>4152610</v>
       </c>
       <c r="J186" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="187" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H187" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I187">
         <v>35896315</v>
       </c>
       <c r="J187" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="188" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H188" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I188">
         <v>31743599</v>
       </c>
       <c r="J188" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="189" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H189" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I189">
         <v>4152608</v>
       </c>
       <c r="J189" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="190" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H190" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I190">
         <v>4152606</v>
       </c>
       <c r="J190" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="191" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H191" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I191">
         <v>34098917</v>
       </c>
       <c r="J191" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="192" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H192" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I192">
         <v>34801754</v>
       </c>
       <c r="J192" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="193" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H193" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I193">
         <v>37639889</v>
       </c>
       <c r="J193" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="194" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H194" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I194">
         <v>51533853</v>
       </c>
       <c r="J194" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="195" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H195" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I195">
         <v>49985232</v>
       </c>
       <c r="J195" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="196" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H196" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I196">
         <v>50155408</v>
       </c>
       <c r="J196" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="197" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H197" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I197">
         <v>35401181</v>
       </c>
       <c r="J197" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="198" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H198" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I198">
         <v>38157908</v>
       </c>
       <c r="J198" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="199" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H199" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I199">
         <v>41662266</v>
       </c>
       <c r="J199" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="200" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H200" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I200">
         <v>47936724</v>
       </c>
       <c r="J200" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="201" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H201" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I201">
         <v>38417806</v>
       </c>
       <c r="J201" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="202" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H202" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I202">
         <v>38158208</v>
       </c>
       <c r="J202" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="203" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H203" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I203">
         <v>12263163</v>
       </c>
       <c r="J203" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="204" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H204" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I204">
         <v>15826960</v>
       </c>
       <c r="J204" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="205" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H205" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I205">
         <v>13573385</v>
       </c>
       <c r="J205" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="206" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H206" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I206">
         <v>42871700</v>
       </c>
       <c r="J206" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="207" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H207" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I207">
         <v>39257536</v>
       </c>
       <c r="J207" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="208" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H208" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I208">
         <v>37424126</v>
       </c>
       <c r="J208" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="209" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H209" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I209">
         <v>36802614</v>
       </c>
       <c r="J209" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="210" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H210" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I210">
         <v>36577826</v>
       </c>
       <c r="J210" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="211" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H211" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I211">
         <v>35149611</v>
@@ -4851,128 +5199,128 @@
     </row>
     <row r="212" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H212" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I212">
         <v>26196255</v>
       </c>
       <c r="J212" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="213" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H213" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I213">
         <v>11156528</v>
       </c>
       <c r="J213" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="214" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H214" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I214">
         <v>38415503</v>
       </c>
       <c r="J214" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="215" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H215" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I215">
         <v>37244806</v>
       </c>
       <c r="J215" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="216" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H216" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I216">
         <v>27011098</v>
       </c>
       <c r="J216" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="217" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H217" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I217">
         <v>26019234</v>
       </c>
       <c r="J217" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="218" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H218" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I218">
         <v>13959023</v>
       </c>
       <c r="J218" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="219" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H219" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I219">
         <v>12496637</v>
       </c>
       <c r="J219" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="220" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H220" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I220">
         <v>25411238</v>
       </c>
       <c r="J220" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="221" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H221" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I221">
         <v>38312169</v>
       </c>
       <c r="J221" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="222" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H222" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I222">
         <v>31886592</v>
       </c>
       <c r="J222" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="223" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H223" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I223">
         <v>11670520</v>
@@ -4983,348 +5331,348 @@
     </row>
     <row r="224" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H224" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I224">
         <v>26500515</v>
       </c>
       <c r="J224" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="225" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H225" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I225">
         <v>36162739</v>
       </c>
       <c r="J225" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="226" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H226" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I226">
         <v>39893389</v>
       </c>
       <c r="J226" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="227" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H227" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I227">
         <v>39296173</v>
       </c>
       <c r="J227" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="228" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H228" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I228">
         <v>26491140</v>
       </c>
       <c r="J228" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="229" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H229" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I229">
         <v>49473587</v>
       </c>
       <c r="J229" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="230" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H230" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I230">
         <v>50326931</v>
       </c>
       <c r="J230" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="231" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H231" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I231">
         <v>12095120</v>
       </c>
       <c r="J231" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="232" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H232" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I232">
         <v>11765770</v>
       </c>
       <c r="J232" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="233" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H233" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I233">
         <v>15757638</v>
       </c>
       <c r="J233" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="234" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H234" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I234">
         <v>12038103</v>
       </c>
       <c r="J234" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="235" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H235" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I235">
         <v>46801171</v>
       </c>
       <c r="J235" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="236" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H236" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I236">
         <v>10155238</v>
       </c>
       <c r="J236" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="237" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H237" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I237">
         <v>10816066</v>
       </c>
       <c r="J237" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="238" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H238" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I238">
         <v>8668649</v>
       </c>
       <c r="J238" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="239" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H239" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I239">
         <v>36635604</v>
       </c>
       <c r="J239" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="240" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H240" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I240">
         <v>8837870</v>
       </c>
       <c r="J240" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="241" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H241" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I241">
         <v>5359040</v>
       </c>
       <c r="J241" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="242" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H242" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I242">
         <v>42373723</v>
       </c>
       <c r="J242" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="243" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H243" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I243">
         <v>16303007</v>
       </c>
       <c r="J243" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="244" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H244" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I244">
         <v>27303665</v>
       </c>
       <c r="J244" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="245" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H245" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I245">
         <v>5462299</v>
       </c>
       <c r="J245" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="246" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H246" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I246">
         <v>47220150</v>
       </c>
       <c r="J246" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="247" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H247" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I247">
         <v>42265154</v>
       </c>
       <c r="J247" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="248" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H248" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I248">
         <v>48105600</v>
       </c>
       <c r="J248" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="249" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H249" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I249">
         <v>34991467</v>
       </c>
       <c r="J249" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="250" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H250" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I250">
         <v>34348663</v>
       </c>
       <c r="J250" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="251" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H251" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I251">
         <v>34535085</v>
       </c>
       <c r="J251" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="252" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H252" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I252">
         <v>41140508</v>
       </c>
       <c r="J252" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="253" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H253" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I253">
         <v>22441147</v>
       </c>
       <c r="J253" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="254" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H254" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I254">
         <v>36811022</v>
       </c>
       <c r="J254" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="255" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H255" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I255">
         <v>36811023</v>
@@ -5335,414 +5683,414 @@
     </row>
     <row r="256" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H256" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I256">
         <v>42217758</v>
       </c>
       <c r="J256" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="257" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H257" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I257">
         <v>39384055</v>
       </c>
       <c r="J257" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="258" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H258" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I258">
         <v>11681261</v>
       </c>
       <c r="J258" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="259" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H259" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I259">
         <v>37161537</v>
       </c>
       <c r="J259" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="260" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H260" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I260">
         <v>30405071</v>
       </c>
       <c r="J260" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="261" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H261" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I261">
         <v>22403445</v>
       </c>
       <c r="J261" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="262" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H262" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I262">
         <v>26257716</v>
       </c>
       <c r="J262" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="263" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H263" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I263">
         <v>12481760</v>
       </c>
       <c r="J263" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="264" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H264" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I264">
         <v>12481759</v>
       </c>
       <c r="J264" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="265" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H265" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I265">
         <v>36682232</v>
       </c>
       <c r="J265" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="266" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H266" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I266">
         <v>46727700</v>
       </c>
       <c r="J266" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="267" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H267" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I267">
         <v>40771157</v>
       </c>
       <c r="J267" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="268" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H268" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I268">
         <v>19104731</v>
       </c>
       <c r="J268" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="269" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H269" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I269">
         <v>39944753</v>
       </c>
       <c r="J269" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="270" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H270" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I270">
         <v>48449253</v>
       </c>
       <c r="J270" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="271" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H271" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I271">
         <v>42051062</v>
       </c>
       <c r="J271" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="272" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H272" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I272">
         <v>18291047</v>
       </c>
       <c r="J272" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="273" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H273" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I273">
         <v>10727917</v>
       </c>
       <c r="J273" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="274" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H274" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I274">
         <v>46543317</v>
       </c>
       <c r="J274" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="275" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H275" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I275">
         <v>13644995</v>
       </c>
       <c r="J275" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="276" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H276" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I276">
         <v>42486414</v>
       </c>
       <c r="J276" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="277" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H277" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I277">
         <v>44695653</v>
       </c>
       <c r="J277" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="278" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H278" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I278">
         <v>44374810</v>
       </c>
       <c r="J278" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="279" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H279" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I279">
         <v>29258063</v>
       </c>
       <c r="J279" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="280" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H280" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I280">
         <v>13405604</v>
       </c>
       <c r="J280" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="281" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H281" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I281">
         <v>10646862</v>
       </c>
       <c r="J281" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="282" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H282" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I282">
         <v>12362063</v>
       </c>
       <c r="J282" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="283" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H283" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I283">
         <v>40185196</v>
       </c>
       <c r="J283" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="284" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H284" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I284">
         <v>15825326</v>
       </c>
       <c r="J284" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="285" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H285" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I285">
         <v>26375455</v>
       </c>
       <c r="J285" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="286" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H286" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I286">
         <v>42803850</v>
       </c>
       <c r="J286" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="287" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H287" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I287">
         <v>50154913</v>
       </c>
       <c r="J287" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="288" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H288" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I288">
         <v>16806254</v>
       </c>
       <c r="J288" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="289" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H289" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I289">
         <v>40501253</v>
       </c>
       <c r="J289" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="290" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H290" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I290">
         <v>14878740</v>
       </c>
       <c r="J290" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="291" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H291" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I291">
         <v>12673237</v>
       </c>
       <c r="J291" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="292" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H292" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I292">
         <v>17579662</v>
       </c>
       <c r="J292" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="293" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H293" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I293">
         <v>14719737</v>
@@ -5753,1085 +6101,1085 @@
     </row>
     <row r="294" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H294" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I294">
         <v>22119013</v>
       </c>
       <c r="J294" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="295" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H295" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I295">
         <v>15795597</v>
       </c>
       <c r="J295" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="296" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H296" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I296">
         <v>12126317</v>
       </c>
       <c r="J296" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="297" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H297" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I297">
         <v>39239709</v>
       </c>
       <c r="J297" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="298" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H298" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I298">
         <v>14488275</v>
       </c>
       <c r="J298" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="299" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H299" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I299">
         <v>42519088</v>
       </c>
       <c r="J299" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="300" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H300" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I300">
         <v>17579394</v>
       </c>
       <c r="J300" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="301" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H301" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I301">
         <v>27056005</v>
       </c>
       <c r="J301" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="302" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H302" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I302">
         <v>24832169</v>
       </c>
       <c r="J302" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="303" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H303" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I303">
         <v>39147133</v>
       </c>
       <c r="J303" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="304" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H304" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I304">
         <v>39030281</v>
       </c>
       <c r="J304" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="305" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H305" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I305">
         <v>13373616</v>
       </c>
       <c r="J305" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="306" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H306" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I306">
         <v>12757668</v>
       </c>
       <c r="J306" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="307" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H307" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I307">
         <v>38977260</v>
       </c>
       <c r="J307" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="308" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H308" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I308">
         <v>38676914</v>
       </c>
       <c r="J308" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="309" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H309" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I309">
         <v>39911056</v>
       </c>
       <c r="J309" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="310" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H310" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I310">
         <v>40102936</v>
       </c>
       <c r="J310" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="311" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H311" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I311">
         <v>10929274</v>
       </c>
       <c r="J311" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="312" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H312" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I312">
         <v>10929273</v>
       </c>
       <c r="J312" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="313" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H313" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I313">
         <v>38412071</v>
       </c>
       <c r="J313" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="314" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H314" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I314">
         <v>29280326</v>
       </c>
       <c r="J314" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="315" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H315" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I315">
         <v>38412101</v>
       </c>
       <c r="J315" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="316" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H316" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I316">
         <v>5332788</v>
       </c>
       <c r="J316" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="317" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H317" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I317">
         <v>5332789</v>
       </c>
       <c r="J317" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="318" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H318" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I318">
         <v>51016959</v>
       </c>
       <c r="J318" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="319" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H319" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I319">
         <v>40636333</v>
       </c>
       <c r="J319" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="320" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H320" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I320">
         <v>50875168</v>
       </c>
       <c r="J320" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="321" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H321" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I321">
         <v>51623281</v>
       </c>
       <c r="J321" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="322" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H322" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I322">
         <v>51897600</v>
       </c>
       <c r="J322" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="323" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H323" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I323">
         <v>51989601</v>
       </c>
       <c r="J323" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="324" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H324" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I324">
         <v>52390638</v>
       </c>
       <c r="J324" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="325" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H325" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I325">
         <v>52362395</v>
       </c>
       <c r="J325" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="326" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H326" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I326">
         <v>52155415</v>
       </c>
       <c r="J326" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="327" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H327" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I327">
         <v>52162444</v>
       </c>
       <c r="J327" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="328" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H328" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I328">
         <v>52270898</v>
       </c>
       <c r="J328" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="329" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H329" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I329">
         <v>52211558</v>
       </c>
       <c r="J329" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="330" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H330" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I330">
         <v>52217000</v>
       </c>
       <c r="J330" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="331" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H331" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I331">
         <v>51689222</v>
       </c>
       <c r="J331" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="332" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H332" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I332">
         <v>51684787</v>
       </c>
       <c r="J332" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="333" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H333" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I333">
         <v>51883980</v>
       </c>
       <c r="J333" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="334" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H334" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I334">
         <v>51898514</v>
       </c>
       <c r="J334" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="335" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H335" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I335">
         <v>52990015</v>
       </c>
       <c r="J335" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="336" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H336" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I336">
         <v>52581507</v>
       </c>
       <c r="J336" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="337" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H337" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I337">
         <v>52613211</v>
       </c>
       <c r="J337" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="338" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H338" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I338">
         <v>52578670</v>
       </c>
       <c r="J338" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="339" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H339" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I339">
         <v>52874174</v>
       </c>
       <c r="J339" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="340" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H340" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I340">
         <v>52872566</v>
       </c>
       <c r="J340" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="341" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H341" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I341">
         <v>54145830</v>
       </c>
       <c r="J341" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="342" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H342" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I342">
         <v>53052265</v>
       </c>
       <c r="J342" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="343" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H343" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I343">
         <v>53297446</v>
       </c>
       <c r="J343" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="344" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H344" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I344">
         <v>53583387</v>
       </c>
       <c r="J344" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="345" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H345" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I345">
         <v>53564659</v>
       </c>
       <c r="J345" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="346" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H346" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I346">
         <v>53569741</v>
       </c>
       <c r="J346" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="347" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H347" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I347">
         <v>53680118</v>
       </c>
       <c r="J347" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="348" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H348" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I348">
         <v>53776254</v>
       </c>
       <c r="J348" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="349" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H349" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I349">
         <v>53967042</v>
       </c>
       <c r="J349" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="350" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H350" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I350">
         <v>55275736</v>
       </c>
       <c r="J350" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="351" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H351" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I351">
         <v>56663811</v>
       </c>
       <c r="J351" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="352" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H352" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I352">
         <v>59082806</v>
       </c>
       <c r="J352" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="353" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H353" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I353">
         <v>55369678</v>
       </c>
       <c r="J353" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="354" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H354" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I354">
         <v>55354052</v>
       </c>
       <c r="J354" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="355" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H355" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I355">
         <v>55381383</v>
       </c>
       <c r="J355" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="356" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H356" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I356">
         <v>55609278</v>
       </c>
       <c r="J356" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="357" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H357" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I357">
         <v>55356212</v>
       </c>
       <c r="J357" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="358" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H358" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I358">
         <v>55449180</v>
       </c>
       <c r="J358" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="359" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H359" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I359">
         <v>55357095</v>
       </c>
       <c r="J359" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="360" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H360" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I360">
         <v>55384739</v>
       </c>
       <c r="J360" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="361" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H361" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I361">
         <v>55357155</v>
       </c>
       <c r="J361" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="362" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H362" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I362">
         <v>55389336</v>
       </c>
       <c r="J362" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="363" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H363" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I363">
         <v>55356388</v>
       </c>
       <c r="J363" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="364" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H364" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I364">
         <v>55610213</v>
       </c>
       <c r="J364" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="365" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H365" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I365">
         <v>55462718</v>
       </c>
       <c r="J365" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="366" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H366" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I366">
         <v>58084222</v>
       </c>
       <c r="J366" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="367" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H367" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I367">
         <v>56651433</v>
       </c>
       <c r="J367" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="368" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H368" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I368">
         <v>56479851</v>
       </c>
       <c r="J368" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="369" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H369" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I369">
         <v>56667264</v>
       </c>
       <c r="J369" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="370" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H370" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I370">
         <v>56896464</v>
       </c>
       <c r="J370" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="371" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H371" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I371">
         <v>57592449</v>
       </c>
       <c r="J371" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="372" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H372" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I372">
         <v>56183402</v>
       </c>
       <c r="J372" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="373" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H373" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I373">
         <v>56651667</v>
       </c>
       <c r="J373" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="374" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H374" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I374">
         <v>58987730</v>
       </c>
       <c r="J374" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="375" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H375" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I375">
         <v>57422656</v>
       </c>
       <c r="J375" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="376" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H376" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I376">
         <v>58040260</v>
       </c>
       <c r="J376" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="377" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H377" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I377">
         <v>59070986</v>
       </c>
       <c r="J377" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="378" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H378" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I378">
         <v>59058036</v>
       </c>
       <c r="J378" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="379" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H379" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I379">
         <v>58505144</v>
       </c>
       <c r="J379" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="380" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H380" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I380">
         <v>58610450</v>
       </c>
       <c r="J380" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="381" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H381" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I381">
         <v>59056260</v>
       </c>
       <c r="J381" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="382" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H382" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I382">
         <v>58722261</v>
       </c>
       <c r="J382" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="383" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H383" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I383">
         <v>58716097</v>
       </c>
       <c r="J383" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="384" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H384" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I384">
         <v>58730204</v>
       </c>
       <c r="J384" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="385" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H385" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I385">
         <v>59199875</v>
       </c>
       <c r="J385" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="386" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H386" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I386">
         <v>59759466</v>
       </c>
       <c r="J386" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="387" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H387" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I387">
         <v>59332927</v>
       </c>
       <c r="J387" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="388" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H388" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I388">
         <v>59944694</v>
       </c>
       <c r="J388" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="389" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H389" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I389">
         <v>60019261</v>
       </c>
       <c r="J389" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="390" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H390" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I390">
         <v>59932138</v>
       </c>
       <c r="J390" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="391" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H391" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I391">
         <v>59924956</v>
       </c>
       <c r="J391" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="392" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H392" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I392">
         <v>59927382</v>
@@ -6842,18 +7190,18 @@
     </row>
     <row r="393" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H393" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I393">
         <v>59836396</v>
       </c>
       <c r="J393" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="394" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H394" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I394">
         <v>60015061</v>
@@ -6864,942 +7212,942 @@
     </row>
     <row r="395" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H395" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I395">
         <v>60023938</v>
       </c>
       <c r="J395" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="396" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H396" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I396">
         <v>60025950</v>
       </c>
       <c r="J396" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="397" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H397" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I397">
         <v>60024864</v>
       </c>
       <c r="J397" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="398" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H398" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I398">
         <v>60084208</v>
       </c>
       <c r="J398" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="399" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H399" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I399">
         <v>60085614</v>
       </c>
       <c r="J399" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="400" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H400" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I400">
         <v>60133592</v>
       </c>
       <c r="J400" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="401" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H401" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I401">
         <v>60450424</v>
       </c>
       <c r="J401" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="402" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H402" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I402">
         <v>60380162</v>
       </c>
       <c r="J402" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="403" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H403" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I403">
         <v>60541542</v>
       </c>
       <c r="J403" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="404" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H404" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I404">
         <v>60541171</v>
       </c>
       <c r="J404" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="405" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H405" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I405">
         <v>60543356</v>
       </c>
       <c r="J405" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="406" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H406" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I406">
         <v>60530655</v>
       </c>
       <c r="J406" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="407" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H407" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I407">
         <v>60615380</v>
       </c>
       <c r="J407" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="408" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H408" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I408">
         <v>60725132</v>
       </c>
       <c r="J408" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="409" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H409" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I409">
         <v>62575565</v>
       </c>
       <c r="J409" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="410" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H410" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I410">
         <v>61766007</v>
       </c>
       <c r="J410" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="411" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H411" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I411">
         <v>61089339</v>
       </c>
       <c r="J411" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="412" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H412" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I412">
         <v>62377903</v>
       </c>
       <c r="J412" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="413" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H413" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I413">
         <v>60542212</v>
       </c>
       <c r="J413" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="414" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H414" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I414">
         <v>61044622</v>
       </c>
       <c r="J414" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="415" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H415" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I415">
         <v>61199642</v>
       </c>
       <c r="J415" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="416" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H416" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I416">
         <v>61760291</v>
       </c>
       <c r="J416" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="417" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H417" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I417">
         <v>61923953</v>
       </c>
       <c r="J417" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="418" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H418" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I418">
         <v>61760141</v>
       </c>
       <c r="J418" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="419" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H419" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I419">
         <v>61929592</v>
       </c>
       <c r="J419" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="420" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H420" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I420">
         <v>61929727</v>
       </c>
       <c r="J420" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="421" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H421" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I421">
         <v>61929494</v>
       </c>
       <c r="J421" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="422" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H422" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I422">
         <v>61929493</v>
       </c>
       <c r="J422" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="423" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H423" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I423">
         <v>61879892</v>
       </c>
       <c r="J423" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="424" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H424" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I424">
         <v>62378988</v>
       </c>
       <c r="J424" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="425" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H425" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I425">
         <v>62375802</v>
       </c>
       <c r="J425" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="426" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H426" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I426">
         <v>62379668</v>
       </c>
       <c r="J426" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="427" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H427" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I427">
         <v>62221331</v>
       </c>
       <c r="J427" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="428" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H428" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I428">
         <v>62385013</v>
       </c>
       <c r="J428" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="429" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H429" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I429">
         <v>62380995</v>
       </c>
       <c r="J429" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="430" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H430" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I430">
         <v>62421723</v>
       </c>
       <c r="J430" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="431" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H431" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I431">
         <v>62374813</v>
       </c>
       <c r="J431" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="432" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H432" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I432">
         <v>62499786</v>
       </c>
       <c r="J432" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="433" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H433" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I433">
         <v>62498583</v>
       </c>
       <c r="J433" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="434" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H434" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I434">
         <v>63346456</v>
       </c>
       <c r="J434" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="435" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H435" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I435">
         <v>63100963</v>
       </c>
       <c r="J435" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="436" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H436" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I436">
         <v>63396496</v>
       </c>
       <c r="J436" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="437" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H437" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I437">
         <v>64270608</v>
       </c>
       <c r="J437" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="438" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H438" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I438">
         <v>63573761</v>
       </c>
       <c r="J438" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="439" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H439" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I439">
         <v>64330763</v>
       </c>
       <c r="J439" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="440" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H440" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I440">
         <v>64330764</v>
       </c>
       <c r="J440" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="441" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H441" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I441">
         <v>64212552</v>
       </c>
       <c r="J441" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="442" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H442" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I442">
         <v>64212544</v>
       </c>
       <c r="J442" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="443" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H443" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I443">
         <v>64212543</v>
       </c>
       <c r="J443" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="444" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H444" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I444">
         <v>64212381</v>
       </c>
       <c r="J444" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="445" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H445" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I445">
         <v>64114088</v>
       </c>
       <c r="J445" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="446" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H446" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I446">
         <v>64223250</v>
       </c>
       <c r="J446" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="447" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H447" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I447">
         <v>64214259</v>
       </c>
       <c r="J447" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="448" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H448" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I448">
         <v>64214258</v>
       </c>
       <c r="J448" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="449" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H449" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I449">
         <v>63742200</v>
       </c>
       <c r="J449" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="450" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H450" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I450">
         <v>64606094</v>
       </c>
       <c r="J450" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="451" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H451" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I451">
         <v>64287980</v>
       </c>
       <c r="J451" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="452" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H452" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I452">
         <v>64257297</v>
       </c>
       <c r="J452" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="453" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H453" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I453">
         <v>66097436</v>
       </c>
       <c r="J453" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="454" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H454" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I454">
         <v>64330309</v>
       </c>
       <c r="J454" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="455" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H455" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I455">
         <v>64846264</v>
       </c>
       <c r="J455" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="456" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H456" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I456">
         <v>64753996</v>
       </c>
       <c r="J456" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="457" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H457" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I457">
         <v>64778162</v>
       </c>
       <c r="J457" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="458" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H458" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I458">
         <v>64778161</v>
       </c>
       <c r="J458" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="459" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H459" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I459">
         <v>64808932</v>
       </c>
       <c r="J459" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="460" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H460" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I460">
         <v>64789478</v>
       </c>
       <c r="J460" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="461" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H461" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I461">
         <v>64912430</v>
       </c>
       <c r="J461" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="462" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H462" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I462">
         <v>64971361</v>
       </c>
       <c r="J462" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="463" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H463" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I463">
         <v>65145714</v>
       </c>
       <c r="J463" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="464" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H464" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I464">
         <v>65081124</v>
       </c>
       <c r="J464" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="465" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H465" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I465">
         <v>65181042</v>
       </c>
       <c r="J465" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="466" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H466" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I466">
         <v>65179405</v>
       </c>
       <c r="J466" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="467" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H467" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I467">
         <v>65566244</v>
       </c>
       <c r="J467" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="468" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H468" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I468">
         <v>65566541</v>
       </c>
       <c r="J468" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="469" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H469" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I469">
         <v>65656468</v>
       </c>
       <c r="J469" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="470" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H470" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I470">
         <v>65657039</v>
       </c>
       <c r="J470" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="471" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H471" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I471">
         <v>66217025</v>
       </c>
       <c r="J471" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="472" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H472" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I472">
         <v>66214618</v>
       </c>
       <c r="J472" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="473" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H473" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I473">
         <v>65935700</v>
       </c>
       <c r="J473" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="474" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H474" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I474">
         <v>65934564</v>
       </c>
       <c r="J474" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="475" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H475" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I475">
         <v>65933937</v>
       </c>
       <c r="J475" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="476" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H476" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I476">
         <v>66046959</v>
       </c>
       <c r="J476" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="477" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H477" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I477">
         <v>65969750</v>
       </c>
       <c r="J477" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="478" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H478" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I478">
         <v>66358440</v>
       </c>
       <c r="J478" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="479" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H479" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I479">
         <v>66417803</v>
       </c>
       <c r="J479" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="480" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H480" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I480">
         <v>66417801</v>
@@ -7810,695 +8158,695 @@
     </row>
     <row r="481" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H481" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I481">
         <v>66357977</v>
       </c>
       <c r="J481" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="482" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H482" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I482">
         <v>67191572</v>
       </c>
       <c r="J482" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="483" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H483" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I483">
         <v>66546178</v>
       </c>
       <c r="J483" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="484" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H484" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I484">
         <v>67627331</v>
       </c>
       <c r="J484" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="485" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H485" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I485">
         <v>66778787</v>
       </c>
       <c r="J485" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="486" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H486" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I486">
         <v>66778788</v>
       </c>
       <c r="J486" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="487" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H487" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I487">
         <v>66778789</v>
       </c>
       <c r="J487" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="488" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H488" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I488">
         <v>66896364</v>
       </c>
       <c r="J488" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="489" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H489" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I489">
         <v>66607099</v>
       </c>
       <c r="J489" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="490" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H490" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I490">
         <v>66864708</v>
       </c>
       <c r="J490" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="491" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H491" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I491">
         <v>66850322</v>
       </c>
       <c r="J491" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="492" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H492" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I492">
         <v>67268341</v>
       </c>
       <c r="J492" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="493" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H493" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I493">
         <v>67268348</v>
       </c>
       <c r="J493" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="494" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H494" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I494">
         <v>67268349</v>
       </c>
       <c r="J494" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="495" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H495" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I495">
         <v>67268350</v>
       </c>
       <c r="J495" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="496" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H496" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I496">
         <v>67272047</v>
       </c>
       <c r="J496" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="497" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H497" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I497">
         <v>67272046</v>
       </c>
       <c r="J497" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="498" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H498" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I498">
         <v>67438488</v>
       </c>
       <c r="J498" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="499" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H499" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I499">
         <v>67438487</v>
       </c>
       <c r="J499" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="500" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H500" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I500">
         <v>68253037</v>
       </c>
       <c r="J500" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="501" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H501" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I501">
         <v>67891311</v>
       </c>
       <c r="J501" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="502" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H502" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I502">
         <v>67900090</v>
       </c>
       <c r="J502" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="503" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H503" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I503">
         <v>67630646</v>
       </c>
       <c r="J503" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="504" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H504" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I504">
         <v>67974104</v>
       </c>
       <c r="J504" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="505" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H505" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I505">
         <v>67989839</v>
       </c>
       <c r="J505" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="506" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H506" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I506">
         <v>67988468</v>
       </c>
       <c r="J506" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="507" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H507" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I507">
         <v>68466892</v>
       </c>
       <c r="J507" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="508" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H508" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I508">
         <v>69040158</v>
       </c>
       <c r="J508" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="509" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H509" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I509">
         <v>68462854</v>
       </c>
       <c r="J509" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="510" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H510" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I510" t="s">
+        <v>535</v>
+      </c>
+      <c r="J510" t="s">
         <v>536</v>
-      </c>
-      <c r="J510" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="511" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H511" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I511" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="J511" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="512" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H512" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I512">
         <v>68677002</v>
       </c>
       <c r="J512" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="513" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H513" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I513">
         <v>68880617</v>
       </c>
       <c r="J513" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="514" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H514" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I514">
         <v>68934411</v>
       </c>
       <c r="J514" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="515" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H515" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I515">
         <v>68924611</v>
       </c>
       <c r="J515" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="516" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H516" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I516">
         <v>69039437</v>
       </c>
       <c r="J516" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="517" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H517" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I517">
         <v>69039778</v>
       </c>
       <c r="J517" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="518" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H518" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I518">
         <v>69279032</v>
       </c>
       <c r="J518" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="519" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H519" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I519">
         <v>68938743</v>
       </c>
       <c r="J519" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="520" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H520" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I520">
         <v>69772629</v>
       </c>
       <c r="J520" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="521" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H521" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I521">
         <v>69772627</v>
       </c>
       <c r="J521" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="522" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H522" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I522">
         <v>69772625</v>
       </c>
       <c r="J522" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="523" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H523" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I523">
         <v>69292187</v>
       </c>
       <c r="J523" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="524" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H524" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I524">
         <v>69292186</v>
       </c>
       <c r="J524" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="525" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H525" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I525">
         <v>69292185</v>
       </c>
       <c r="J525" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="526" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H526" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I526">
         <v>69096297</v>
       </c>
       <c r="J526" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="527" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H527" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I527">
         <v>69096296</v>
       </c>
       <c r="J527" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="528" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H528" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I528">
         <v>69594684</v>
       </c>
       <c r="J528" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="529" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H529" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I529">
         <v>70204974</v>
       </c>
       <c r="J529" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="530" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H530" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I530">
         <v>70204975</v>
       </c>
       <c r="J530" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="531" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H531" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I531">
         <v>69767288</v>
       </c>
       <c r="J531" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="532" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H532" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I532">
         <v>69766464</v>
       </c>
       <c r="J532" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="533" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H533" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I533">
         <v>69803799</v>
       </c>
       <c r="J533" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="534" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H534" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I534">
         <v>70251147</v>
       </c>
       <c r="J534" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="535" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H535" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I535">
         <v>69770093</v>
       </c>
       <c r="J535" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="536" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H536" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I536">
         <v>70205079</v>
       </c>
       <c r="J536" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="537" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H537" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I537">
         <v>70530577</v>
       </c>
       <c r="J537" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="538" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H538" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I538">
         <v>70530576</v>
       </c>
       <c r="J538" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="539" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H539" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I539">
         <v>71030052</v>
       </c>
       <c r="J539" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="540" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H540" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I540">
         <v>70770186</v>
       </c>
       <c r="J540" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="541" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H541" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I541">
         <v>71173111</v>
       </c>
       <c r="J541" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="542" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H542" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I542">
         <v>71156871</v>
       </c>
       <c r="J542" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="543" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H543" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I543">
         <v>71291488</v>
       </c>
       <c r="J543" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="544" spans="8:10" x14ac:dyDescent="0.3">
@@ -8506,331 +8854,331 @@
         <v>71042279</v>
       </c>
       <c r="J544" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="545" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H545" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I545">
         <v>71947627</v>
       </c>
       <c r="J545" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="546" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H546" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I546">
         <v>72182444</v>
       </c>
       <c r="J546" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="547" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H547" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I547">
         <v>72300747</v>
       </c>
       <c r="J547" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="548" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H548" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I548">
         <v>72417582</v>
       </c>
       <c r="J548" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="549" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H549" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I549">
         <v>72614935</v>
       </c>
       <c r="J549" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="550" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H550" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I550">
         <v>72614936</v>
       </c>
       <c r="J550" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="551" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H551" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I551">
         <v>72614937</v>
       </c>
       <c r="J551" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="552" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H552" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I552">
         <v>73226633</v>
       </c>
       <c r="J552" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="553" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H553" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I553">
         <v>73226632</v>
       </c>
       <c r="J553" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="554" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H554" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I554">
         <v>73316683</v>
       </c>
       <c r="J554" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="555" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H555" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I555">
         <v>73316684</v>
       </c>
       <c r="J555" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="556" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H556" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I556">
         <v>73316685</v>
       </c>
       <c r="J556" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="557" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H557" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I557">
         <v>72699936</v>
       </c>
       <c r="J557" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="558" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H558" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I558">
         <v>72699935</v>
       </c>
       <c r="J558" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="559" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H559" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I559">
         <v>72828733</v>
       </c>
       <c r="J559" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="560" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H560" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I560">
         <v>72828734</v>
       </c>
       <c r="J560" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="561" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H561" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I561">
         <v>72683872</v>
       </c>
       <c r="J561" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="562" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H562" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I562">
         <v>72910681</v>
       </c>
       <c r="J562" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="563" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H563" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I563">
         <v>72910683</v>
       </c>
       <c r="J563" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="564" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H564" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I564">
         <v>73523448</v>
       </c>
       <c r="J564" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="565" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H565" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I565">
         <v>73461995</v>
       </c>
       <c r="J565" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="566" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H566" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I566">
         <v>73956460</v>
       </c>
       <c r="J566" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="567" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H567" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I567">
         <v>73956461</v>
       </c>
       <c r="J567" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="568" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H568" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I568">
         <v>73956459</v>
       </c>
       <c r="J568" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="569" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H569" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I569">
         <v>74685916</v>
       </c>
       <c r="J569" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="570" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H570" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I570">
         <v>73975553</v>
       </c>
       <c r="J570" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="571" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H571" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I571">
         <v>73952843</v>
       </c>
       <c r="J571" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="572" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H572" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I572">
         <v>74550323</v>
       </c>
       <c r="J572" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="573" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H573" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I573">
         <v>75989703</v>
       </c>
       <c r="J573" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="574" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H574" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I574">
         <v>74693807</v>
@@ -8841,7 +9189,7 @@
     </row>
     <row r="575" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H575" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I575">
         <v>73893263</v>
@@ -8852,310 +9200,310 @@
     </row>
     <row r="576" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H576" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I576">
         <v>74884452</v>
       </c>
       <c r="J576" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="577" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H577" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I577">
         <v>74826973</v>
       </c>
       <c r="J577" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="578" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H578" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I578">
         <v>74826974</v>
       </c>
       <c r="J578" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="579" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H579" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I579">
         <v>75077119</v>
       </c>
       <c r="J579" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="580" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H580" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I580" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="J580" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="581" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H581" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I581" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="J581" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="582" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H582" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I582">
         <v>75741354</v>
       </c>
       <c r="J582" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="583" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H583" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I583" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="J583" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="584" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H584" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I584">
         <v>76375598</v>
       </c>
       <c r="J584" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="585" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H585" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I585">
         <v>76375597</v>
       </c>
       <c r="J585" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="586" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H586" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I586">
         <v>76374400</v>
       </c>
       <c r="J586" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="587" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H587" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I587">
         <v>76374401</v>
       </c>
       <c r="J587" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="588" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H588" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I588">
         <v>76241042</v>
       </c>
       <c r="J588" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="589" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H589" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I589">
         <v>76533940</v>
       </c>
       <c r="J589" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="590" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H590" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I590">
         <v>77463489</v>
       </c>
       <c r="J590" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="591" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H591" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I591">
         <v>77463490</v>
       </c>
       <c r="J591" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="592" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H592" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I592" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="J592" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="593" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H593" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I593" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="J593" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="594" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H594" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I594" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="J594" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="595" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H595" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I595" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="J595" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="596" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H596" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I596" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="J596" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="601" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H601" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I601" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="J601" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="602" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H602" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I602" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="J602" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="603" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H603" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I603" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="J603" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="604" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H604" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I604" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="J604" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="605" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H605" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I605" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="J605" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="606" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H606" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I606" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="J606" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="607" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H607" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I607" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="J607" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
   </sheetData>

--- a/data/이슈제품.xlsx
+++ b/data/이슈제품.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="79">
   <si>
     <t>입고X, 단종신청완료</t>
   </si>
@@ -270,6 +270,13 @@
   </si>
   <si>
     <t>협의, 11월 초</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보아르스마트락텀블러-아이보리</t>
+  </si>
+  <si>
+    <t>협의, 공구 진행으로 윤정님 확인필요</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -611,7 +618,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
@@ -1248,6 +1255,17 @@
         <v>73</v>
       </c>
     </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>79944232</v>
+      </c>
+      <c r="B58" t="s">
+        <v>77</v>
+      </c>
+      <c r="C58" t="s">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/이슈제품.xlsx
+++ b/data/이슈제품.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OA\Desktop\쿠팡업로드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24C4949A-043B-4037-BA44-6F6C2C881AFD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48A0FDCF-8E6E-4B6C-B7E8-42E6F6450ADB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -69,9 +69,6 @@
     <t>보아르슈즈쏙-화이트</t>
   </si>
   <si>
-    <t>협의후 입고</t>
-  </si>
-  <si>
     <t>보아르이지전기포트M1(FV)-그레이</t>
   </si>
   <si>
@@ -1932,10 +1929,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>입고X, 9월말 예상</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>입고X, 10월 중순 예정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1944,10 +1937,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>협의, 10월 초</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>오아넥스트레쳐S-베이지</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1994,6 +1983,18 @@
   </si>
   <si>
     <t>광고OFF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입고X, 타채널 단독운영</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입고X 10/20 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입고X, 10/6 예정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2048,7 +2049,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2056,6 +2057,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2353,22 +2357,22 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
         <v>25</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>26</v>
       </c>
-      <c r="C1" t="s">
+      <c r="H1" t="s">
         <v>27</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>28</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>29</v>
-      </c>
-      <c r="J1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -2382,307 +2386,307 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I2">
         <v>3636925</v>
       </c>
       <c r="J2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>50723598</v>
+        <v>76375597</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="H3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I3">
         <v>3636926</v>
       </c>
       <c r="J3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>76375597</v>
+        <v>58505144</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I4">
         <v>3636927</v>
       </c>
       <c r="J4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>58505144</v>
+        <v>50725354</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>208</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>626</v>
       </c>
       <c r="H5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I5">
         <v>39415252</v>
       </c>
       <c r="J5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>50725354</v>
+        <v>12263239</v>
       </c>
       <c r="B6" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C6" t="s">
         <v>627</v>
       </c>
       <c r="H6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I6">
         <v>19213859</v>
       </c>
       <c r="J6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>12263239</v>
+        <v>68880617</v>
       </c>
       <c r="B7" t="s">
-        <v>208</v>
+        <v>634</v>
       </c>
       <c r="C7" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I7">
         <v>20342327</v>
       </c>
       <c r="J7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>68880617</v>
+        <v>42519088</v>
       </c>
       <c r="B8" t="s">
-        <v>637</v>
+        <v>328</v>
       </c>
       <c r="C8" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="H8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I8">
         <v>13004238</v>
       </c>
       <c r="J8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>42519088</v>
+        <v>4152606</v>
       </c>
       <c r="B9" t="s">
-        <v>329</v>
+        <v>223</v>
       </c>
       <c r="C9" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I9">
         <v>20341619</v>
       </c>
       <c r="J9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>4152606</v>
+        <v>4125377</v>
       </c>
       <c r="B10" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="C10" t="s">
-        <v>645</v>
+        <v>628</v>
       </c>
       <c r="H10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I10">
         <v>11092035</v>
       </c>
       <c r="J10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>4125377</v>
+        <v>26426530</v>
       </c>
       <c r="B11" t="s">
         <v>204</v>
       </c>
       <c r="C11" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I11">
         <v>40852278</v>
       </c>
       <c r="J11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>26426530</v>
+        <v>12439390</v>
       </c>
       <c r="B12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C12" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="H12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I12">
         <v>29266932</v>
       </c>
       <c r="J12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>12439390</v>
+        <v>5332788</v>
       </c>
       <c r="B13" t="s">
-        <v>207</v>
+        <v>345</v>
       </c>
       <c r="C13" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="H13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I13">
         <v>12586373</v>
       </c>
       <c r="J13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>5332788</v>
+        <v>11229298</v>
       </c>
       <c r="B14" t="s">
-        <v>346</v>
+        <v>175</v>
       </c>
       <c r="C14" t="s">
-        <v>644</v>
+        <v>633</v>
       </c>
       <c r="H14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I14">
         <v>11055651</v>
       </c>
       <c r="J14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>11229298</v>
+        <v>27056005</v>
       </c>
       <c r="B15" t="s">
-        <v>176</v>
+        <v>330</v>
       </c>
       <c r="C15" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="H15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I15">
         <v>38659485</v>
       </c>
       <c r="J15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>27056005</v>
+        <v>50153946</v>
       </c>
       <c r="B16" t="s">
-        <v>331</v>
+        <v>115</v>
       </c>
       <c r="C16" t="s">
         <v>630</v>
       </c>
       <c r="H16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I16">
         <v>9567647</v>
       </c>
       <c r="J16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>50153946</v>
+        <v>75741354</v>
       </c>
       <c r="B17" t="s">
-        <v>116</v>
+        <v>605</v>
       </c>
       <c r="C17" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="H17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I17">
         <v>40180424</v>
@@ -2693,1179 +2697,1179 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>75741354</v>
+        <v>60542212</v>
       </c>
       <c r="B18" t="s">
-        <v>606</v>
+        <v>438</v>
       </c>
       <c r="C18" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="H18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I18">
         <v>39228155</v>
       </c>
       <c r="J18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>16303007</v>
-      </c>
-      <c r="B19" t="s">
-        <v>275</v>
-      </c>
-      <c r="C19" t="s">
-        <v>636</v>
+      <c r="A19" s="3">
+        <v>13101217</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>649</v>
       </c>
       <c r="H19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I19">
         <v>38407975</v>
       </c>
       <c r="J19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>60542212</v>
+        <v>15414324</v>
       </c>
       <c r="B20" t="s">
-        <v>439</v>
+        <v>199</v>
       </c>
       <c r="C20" t="s">
         <v>632</v>
       </c>
       <c r="H20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I20">
         <v>38545387</v>
       </c>
       <c r="J20" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>51623281</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="C21" t="s">
+        <v>638</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21" s="3">
+        <v>18816827</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>49</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>13101217</v>
-      </c>
-      <c r="B21" t="s">
-        <v>72</v>
-      </c>
-      <c r="C21" t="s">
-        <v>633</v>
-      </c>
-      <c r="H21" t="s">
-        <v>31</v>
-      </c>
-      <c r="I21">
-        <v>18816827</v>
-      </c>
-      <c r="J21" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>15414324</v>
-      </c>
-      <c r="B22" t="s">
-        <v>200</v>
+        <v>51989601</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>637</v>
       </c>
       <c r="C22" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="H22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I22">
         <v>39278162</v>
       </c>
       <c r="J22" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>51623281</v>
+        <v>11192166</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>639</v>
+        <v>167</v>
       </c>
       <c r="C23" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I23">
         <v>13100374</v>
       </c>
       <c r="J23" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>51989601</v>
+        <v>15812678</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>640</v>
+        <v>146</v>
       </c>
       <c r="C24" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I24">
         <v>10855225</v>
       </c>
       <c r="J24" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>11192166</v>
+        <v>12091621</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="C25" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I25">
         <v>38490171</v>
       </c>
       <c r="J25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>15812678</v>
+        <v>12143584</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C26" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I26">
         <v>38490170</v>
       </c>
       <c r="J26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>12091621</v>
+        <v>11192167</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="C27" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I27">
         <v>38417027</v>
       </c>
       <c r="J27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>12143584</v>
+        <v>12143581</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C28" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I28">
         <v>13099542</v>
       </c>
       <c r="J28" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>11192167</v>
+        <v>11192165</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C29" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I29">
         <v>10324264</v>
       </c>
       <c r="J29" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>12143581</v>
+        <v>11192163</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C30" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I30">
         <v>39229235</v>
       </c>
       <c r="J30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>11192165</v>
+        <v>11291291</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="C31" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H31" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I31">
         <v>12775098</v>
       </c>
       <c r="J31" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>11192163</v>
+        <v>16171214</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C32" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I32">
         <v>12775097</v>
       </c>
       <c r="J32" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>11291291</v>
+        <v>12218847</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C33" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H33" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I33">
         <v>12775096</v>
       </c>
       <c r="J33" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>16171214</v>
+        <v>15838517</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C34" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H34" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I34">
         <v>13151160</v>
       </c>
       <c r="J34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>12218847</v>
+        <v>12673238</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C35" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I35">
         <v>13151158</v>
       </c>
       <c r="J35" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>15838517</v>
+        <v>37790051</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C36" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H36" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I36">
         <v>35403063</v>
       </c>
       <c r="J36" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>12673238</v>
+        <v>37594934</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="C37" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H37" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I37">
         <v>13473750</v>
       </c>
       <c r="J37" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>37790051</v>
+        <v>15702671</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="C38" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I38">
         <v>17014694</v>
       </c>
       <c r="J38" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>37594934</v>
+        <v>39071990</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="C39" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H39" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I39">
         <v>17014693</v>
       </c>
       <c r="J39" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>15702671</v>
+        <v>52204284</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>175</v>
+        <v>92</v>
       </c>
       <c r="C40" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I40">
         <v>13101218</v>
       </c>
       <c r="J40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>39071990</v>
+        <v>39006854</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C41" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H41" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I41">
         <v>13101217</v>
       </c>
       <c r="J41" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>52204284</v>
+        <v>39006857</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>93</v>
+        <v>162</v>
       </c>
       <c r="C42" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H42" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I42">
         <v>16981939</v>
       </c>
       <c r="J42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>39006854</v>
+        <v>39006855</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C43" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H43" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I43">
         <v>12846219</v>
       </c>
       <c r="J43" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>39006857</v>
+        <v>51883980</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>163</v>
+        <v>362</v>
       </c>
       <c r="C44" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H44" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I44">
         <v>17398556</v>
       </c>
       <c r="J44" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>39006855</v>
+        <v>52578670</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>164</v>
+        <v>367</v>
       </c>
       <c r="C45" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H45" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I45">
         <v>16972627</v>
       </c>
       <c r="J45" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>51883980</v>
+        <v>52155531</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>363</v>
+        <v>94</v>
       </c>
       <c r="C46" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H46" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I46">
         <v>12846215</v>
       </c>
       <c r="J46" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>52578670</v>
+        <v>15831347</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>368</v>
+        <v>142</v>
       </c>
       <c r="C47" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H47" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I47">
         <v>39663616</v>
       </c>
       <c r="J47" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>52155531</v>
+        <v>32548061</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>95</v>
+        <v>169</v>
       </c>
       <c r="C48" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H48" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I48">
         <v>37843037</v>
       </c>
       <c r="J48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>15831347</v>
+        <v>35876282</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>143</v>
+        <v>173</v>
       </c>
       <c r="C49" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H49" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I49">
         <v>12465755</v>
       </c>
       <c r="J49" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>32548061</v>
+        <v>16805855</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="C50" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I50">
         <v>11671481</v>
       </c>
       <c r="J50" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>35876282</v>
+        <v>55381383</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>174</v>
+        <v>384</v>
       </c>
       <c r="C51" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H51" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I51">
         <v>12685386</v>
       </c>
       <c r="J51" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>16805855</v>
+        <v>55449180</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>146</v>
+        <v>386</v>
       </c>
       <c r="C52" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H52" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I52">
         <v>12674974</v>
       </c>
       <c r="J52" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>55381383</v>
+        <v>55384739</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C53" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H53" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I53">
         <v>12674973</v>
       </c>
       <c r="J53" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>55449180</v>
+        <v>55389336</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>387</v>
+        <v>635</v>
       </c>
       <c r="C54" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I54">
         <v>27515992</v>
       </c>
       <c r="J54" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>55384739</v>
+        <v>55609278</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C55" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H55" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I55">
         <v>18928667</v>
       </c>
       <c r="J55" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>55389336</v>
+        <v>71042279</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>638</v>
+        <v>569</v>
       </c>
       <c r="C56" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="H56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I56">
         <v>14218803</v>
       </c>
       <c r="J56" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>55609278</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>386</v>
+        <v>67630646</v>
+      </c>
+      <c r="B57" t="s">
+        <v>527</v>
       </c>
       <c r="C57" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="H57" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I57">
         <v>14218802</v>
       </c>
       <c r="J57" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>71042279</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>570</v>
+        <v>64971361</v>
+      </c>
+      <c r="B58" t="s">
+        <v>487</v>
       </c>
       <c r="C58" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="H58" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I58">
         <v>14473529</v>
       </c>
       <c r="J58" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>67630646</v>
+        <v>62421723</v>
       </c>
       <c r="B59" t="s">
-        <v>528</v>
+        <v>455</v>
       </c>
       <c r="C59" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="H59" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I59">
         <v>25512595</v>
       </c>
       <c r="J59" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>64971361</v>
+        <v>62374813</v>
       </c>
       <c r="B60" t="s">
-        <v>488</v>
+        <v>456</v>
       </c>
       <c r="C60" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="H60" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I60">
         <v>25433097</v>
       </c>
       <c r="J60" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>62421723</v>
+        <v>68462854</v>
       </c>
       <c r="B61" t="s">
-        <v>456</v>
+        <v>533</v>
       </c>
       <c r="C61" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="H61" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I61">
         <v>50012601</v>
       </c>
       <c r="J61" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>62374813</v>
+        <v>64114088</v>
       </c>
       <c r="B62" t="s">
-        <v>457</v>
+        <v>470</v>
       </c>
       <c r="C62" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="H62" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I62">
         <v>52204284</v>
       </c>
       <c r="J62" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>68462854</v>
+        <v>19213859</v>
       </c>
       <c r="B63" t="s">
-        <v>534</v>
+        <v>35</v>
       </c>
       <c r="C63" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="H63" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I63">
         <v>52155531</v>
       </c>
       <c r="J63" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>64114088</v>
+        <v>13004238</v>
       </c>
       <c r="B64" t="s">
-        <v>471</v>
+        <v>37</v>
       </c>
       <c r="C64" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="H64" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I64">
         <v>10814871</v>
       </c>
       <c r="J64" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>19213859</v>
+        <v>43252471</v>
       </c>
       <c r="B65" t="s">
-        <v>36</v>
+        <v>192</v>
       </c>
       <c r="C65" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="H65" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I65">
         <v>31792560</v>
       </c>
       <c r="J65" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>13004238</v>
+        <v>75077119</v>
       </c>
       <c r="B66" t="s">
-        <v>38</v>
+        <v>602</v>
       </c>
       <c r="C66" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="H66" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I66">
         <v>10694343</v>
       </c>
       <c r="J66" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>43252471</v>
+        <v>52270898</v>
       </c>
       <c r="B67" t="s">
-        <v>193</v>
+        <v>357</v>
       </c>
       <c r="C67" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H67" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I67">
         <v>43431417</v>
       </c>
       <c r="J67" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>75077119</v>
+        <v>65933937</v>
       </c>
       <c r="B68" t="s">
-        <v>603</v>
+        <v>500</v>
       </c>
       <c r="C68" t="s">
         <v>647</v>
       </c>
       <c r="H68" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I68">
         <v>10978754</v>
       </c>
       <c r="J68" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>52270898</v>
+        <v>53583387</v>
       </c>
       <c r="B69" t="s">
-        <v>358</v>
+        <v>373</v>
       </c>
       <c r="C69" t="s">
         <v>648</v>
       </c>
       <c r="H69" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I69">
         <v>10974363</v>
       </c>
       <c r="J69" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H70" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I70">
         <v>39376011</v>
       </c>
       <c r="J70" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H71" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I71">
         <v>38310913</v>
       </c>
       <c r="J71" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H72" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I72">
         <v>40639939</v>
       </c>
       <c r="J72" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H73" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I73">
         <v>44581094</v>
       </c>
       <c r="J73" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H74" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I74">
         <v>39270777</v>
       </c>
       <c r="J74" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H75" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I75">
         <v>45342904</v>
       </c>
       <c r="J75" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H76" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I76">
         <v>19619417</v>
       </c>
       <c r="J76" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H77" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I77">
         <v>36606823</v>
       </c>
       <c r="J77" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H78" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I78">
         <v>12585217</v>
       </c>
       <c r="J78" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H79" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I79">
         <v>11511332</v>
       </c>
       <c r="J79" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H80" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I80">
         <v>12579597</v>
       </c>
       <c r="J80" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="81" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H81" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I81">
         <v>50153946</v>
       </c>
       <c r="J81" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="82" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H82" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I82">
         <v>50723598</v>
@@ -3876,40 +3880,40 @@
     </row>
     <row r="83" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H83" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I83">
         <v>34464589</v>
       </c>
       <c r="J83" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="84" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H84" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I84">
         <v>12029130</v>
       </c>
       <c r="J84" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="85" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H85" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I85">
         <v>46962408</v>
       </c>
       <c r="J85" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="86" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H86" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I86">
         <v>11874445</v>
@@ -3920,106 +3924,106 @@
     </row>
     <row r="87" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H87" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I87">
         <v>25665354</v>
       </c>
       <c r="J87" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="88" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H88" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I88">
         <v>46550390</v>
       </c>
       <c r="J88" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="89" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H89" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I89">
         <v>45573288</v>
       </c>
       <c r="J89" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="90" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H90" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I90">
         <v>34318450</v>
       </c>
       <c r="J90" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="91" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H91" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I91">
         <v>45701215</v>
       </c>
       <c r="J91" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="92" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H92" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I92">
         <v>15004955</v>
       </c>
       <c r="J92" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="93" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H93" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I93">
         <v>25321998</v>
       </c>
       <c r="J93" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="94" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H94" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I94">
         <v>25321996</v>
       </c>
       <c r="J94" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="95" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H95" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I95">
         <v>46191377</v>
       </c>
       <c r="J95" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="96" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H96" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I96">
         <v>45349063</v>
@@ -4030,568 +4034,568 @@
     </row>
     <row r="97" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H97" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I97">
         <v>44996967</v>
       </c>
       <c r="J97" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H98" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I98">
         <v>15462869</v>
       </c>
       <c r="J98" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="99" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H99" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I99">
         <v>15462868</v>
       </c>
       <c r="J99" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="100" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H100" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I100">
         <v>46671749</v>
       </c>
       <c r="J100" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="101" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H101" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I101">
         <v>35137369</v>
       </c>
       <c r="J101" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="102" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H102" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I102">
         <v>34320929</v>
       </c>
       <c r="J102" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="103" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H103" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I103">
         <v>34320928</v>
       </c>
       <c r="J103" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="104" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H104" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I104">
         <v>23200605</v>
       </c>
       <c r="J104" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="105" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H105" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I105">
         <v>23200603</v>
       </c>
       <c r="J105" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="106" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H106" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I106">
         <v>43571361</v>
       </c>
       <c r="J106" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="107" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H107" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I107">
         <v>43571360</v>
       </c>
       <c r="J107" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="108" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H108" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I108">
         <v>34330469</v>
       </c>
       <c r="J108" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="109" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H109" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I109">
         <v>34331612</v>
       </c>
       <c r="J109" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="110" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H110" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I110">
         <v>34352694</v>
       </c>
       <c r="J110" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="111" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H111" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I111">
         <v>39063227</v>
       </c>
       <c r="J111" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="112" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H112" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I112">
         <v>15831347</v>
       </c>
       <c r="J112" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="113" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H113" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I113">
         <v>12091621</v>
       </c>
       <c r="J113" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="114" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H114" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I114">
         <v>16805855</v>
       </c>
       <c r="J114" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="115" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H115" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I115">
         <v>15812678</v>
       </c>
       <c r="J115" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="116" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H116" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I116">
         <v>12143581</v>
       </c>
       <c r="J116" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="117" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H117" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I117">
         <v>11192165</v>
       </c>
       <c r="J117" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="118" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H118" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I118">
         <v>11192163</v>
       </c>
       <c r="J118" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="119" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H119" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I119">
         <v>12143584</v>
       </c>
       <c r="J119" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="120" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H120" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I120">
         <v>11192167</v>
       </c>
       <c r="J120" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="121" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H121" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I121">
         <v>12673238</v>
       </c>
       <c r="J121" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="122" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H122" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I122">
         <v>15838517</v>
       </c>
       <c r="J122" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="123" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H123" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I123">
         <v>12218847</v>
       </c>
       <c r="J123" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="124" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H124" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I124">
         <v>16171214</v>
       </c>
       <c r="J124" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="125" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H125" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I125">
         <v>11291291</v>
       </c>
       <c r="J125" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="126" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H126" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I126">
         <v>14134779</v>
       </c>
       <c r="J126" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="127" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H127" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I127">
         <v>14134778</v>
       </c>
       <c r="J127" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="128" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H128" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I128">
         <v>37790051</v>
       </c>
       <c r="J128" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="129" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H129" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I129">
         <v>39071990</v>
       </c>
       <c r="J129" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="130" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H130" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I130">
         <v>39006857</v>
       </c>
       <c r="J130" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="131" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H131" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I131">
         <v>39006855</v>
       </c>
       <c r="J131" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="132" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H132" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I132">
         <v>39006854</v>
       </c>
       <c r="J132" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="133" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H133" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I133">
         <v>12434130</v>
       </c>
       <c r="J133" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="134" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H134" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I134">
         <v>11671480</v>
       </c>
       <c r="J134" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="135" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H135" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I135">
         <v>11192166</v>
       </c>
       <c r="J135" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="136" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H136" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I136">
         <v>37594934</v>
       </c>
       <c r="J136" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="137" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H137" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I137">
         <v>32548061</v>
       </c>
       <c r="J137" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="138" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H138" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I138">
         <v>32711387</v>
       </c>
       <c r="J138" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="139" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H139" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I139">
         <v>32710937</v>
       </c>
       <c r="J139" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="140" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H140" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I140">
         <v>35876282</v>
       </c>
       <c r="J140" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="141" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H141" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I141">
         <v>15702671</v>
       </c>
       <c r="J141" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="142" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H142" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I142">
         <v>11229298</v>
       </c>
       <c r="J142" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="143" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H143" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I143">
         <v>50709616</v>
       </c>
       <c r="J143" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="144" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H144" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I144">
         <v>37034524</v>
       </c>
       <c r="J144" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="145" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H145" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I145">
         <v>14299890</v>
       </c>
       <c r="J145" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="146" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H146" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I146">
         <v>13195811</v>
       </c>
       <c r="J146" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="147" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H147" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I147">
         <v>36608029</v>
       </c>
       <c r="J147" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="148" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H148" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I148">
         <v>13195957</v>
@@ -4602,315 +4606,315 @@
     </row>
     <row r="149" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H149" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I149">
         <v>10121189</v>
       </c>
       <c r="J149" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="150" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H150" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I150">
         <v>8122806</v>
       </c>
       <c r="J150" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="151" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H151" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I151">
         <v>48477550</v>
       </c>
       <c r="J151" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="152" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H152" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I152">
         <v>11288089</v>
       </c>
       <c r="J152" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="153" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H153" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I153">
         <v>11104533</v>
       </c>
       <c r="J153" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="154" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H154" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I154">
         <v>10124384</v>
       </c>
       <c r="J154" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="155" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H155" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I155">
         <v>46995055</v>
       </c>
       <c r="J155" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="156" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H156" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I156">
         <v>11744316</v>
       </c>
       <c r="J156" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="157" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H157" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I157">
         <v>13069194</v>
       </c>
       <c r="J157" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="158" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H158" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I158">
         <v>19365568</v>
       </c>
       <c r="J158" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="159" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H159" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I159">
         <v>47861038</v>
       </c>
       <c r="J159" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="160" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H160" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I160">
         <v>43252471</v>
       </c>
       <c r="J160" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="161" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H161" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I161">
         <v>4125381</v>
       </c>
       <c r="J161" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="162" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H162" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I162">
         <v>38183281</v>
       </c>
       <c r="J162" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="163" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H163" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I163">
         <v>14107560</v>
       </c>
       <c r="J163" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="164" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H164" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I164">
         <v>44916947</v>
       </c>
       <c r="J164" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="165" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H165" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I165">
         <v>40640374</v>
       </c>
       <c r="J165" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="166" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H166" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I166">
         <v>13745117</v>
       </c>
       <c r="J166" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="167" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H167" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I167">
         <v>15414324</v>
       </c>
       <c r="J167" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="168" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H168" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I168">
         <v>35192489</v>
       </c>
       <c r="J168" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="169" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H169" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I169">
         <v>40982029</v>
       </c>
       <c r="J169" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="170" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H170" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I170">
         <v>10858043</v>
       </c>
       <c r="J170" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="171" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H171" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I171">
         <v>4125377</v>
       </c>
       <c r="J171" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="172" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H172" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I172">
         <v>26426530</v>
       </c>
       <c r="J172" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="173" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H173" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I173">
         <v>18980681</v>
       </c>
       <c r="J173" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="174" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H174" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I174">
         <v>12439390</v>
       </c>
       <c r="J174" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="175" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H175" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I175">
         <v>12263239</v>
       </c>
       <c r="J175" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="176" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H176" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I176">
         <v>50725354</v>
       </c>
       <c r="J176" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="177" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H177" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I177">
         <v>16179047</v>
@@ -4921,370 +4925,370 @@
     </row>
     <row r="178" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H178" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I178">
         <v>20815743</v>
       </c>
       <c r="J178" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="179" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H179" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I179">
         <v>39651008</v>
       </c>
       <c r="J179" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="180" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H180" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I180">
         <v>42839047</v>
       </c>
       <c r="J180" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="181" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H181" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I181">
         <v>38455497</v>
       </c>
       <c r="J181" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="182" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H182" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I182">
         <v>37173787</v>
       </c>
       <c r="J182" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="183" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H183" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I183">
         <v>42913903</v>
       </c>
       <c r="J183" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="184" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H184" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I184">
         <v>41864123</v>
       </c>
       <c r="J184" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="185" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H185" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I185">
         <v>4152612</v>
       </c>
       <c r="J185" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="186" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H186" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I186">
         <v>4152610</v>
       </c>
       <c r="J186" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="187" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H187" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I187">
         <v>35896315</v>
       </c>
       <c r="J187" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="188" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H188" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I188">
         <v>31743599</v>
       </c>
       <c r="J188" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="189" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H189" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I189">
         <v>4152608</v>
       </c>
       <c r="J189" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="190" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H190" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I190">
         <v>4152606</v>
       </c>
       <c r="J190" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="191" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H191" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I191">
         <v>34098917</v>
       </c>
       <c r="J191" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="192" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H192" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I192">
         <v>34801754</v>
       </c>
       <c r="J192" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="193" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H193" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I193">
         <v>37639889</v>
       </c>
       <c r="J193" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="194" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H194" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I194">
         <v>51533853</v>
       </c>
       <c r="J194" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="195" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H195" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I195">
         <v>49985232</v>
       </c>
       <c r="J195" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="196" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H196" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I196">
         <v>50155408</v>
       </c>
       <c r="J196" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="197" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H197" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I197">
         <v>35401181</v>
       </c>
       <c r="J197" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="198" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H198" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I198">
         <v>38157908</v>
       </c>
       <c r="J198" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="199" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H199" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I199">
         <v>41662266</v>
       </c>
       <c r="J199" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="200" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H200" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I200">
         <v>47936724</v>
       </c>
       <c r="J200" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="201" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H201" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I201">
         <v>38417806</v>
       </c>
       <c r="J201" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="202" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H202" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I202">
         <v>38158208</v>
       </c>
       <c r="J202" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="203" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H203" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I203">
         <v>12263163</v>
       </c>
       <c r="J203" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="204" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H204" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I204">
         <v>15826960</v>
       </c>
       <c r="J204" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="205" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H205" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I205">
         <v>13573385</v>
       </c>
       <c r="J205" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="206" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H206" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I206">
         <v>42871700</v>
       </c>
       <c r="J206" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="207" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H207" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I207">
         <v>39257536</v>
       </c>
       <c r="J207" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="208" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H208" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I208">
         <v>37424126</v>
       </c>
       <c r="J208" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="209" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H209" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I209">
         <v>36802614</v>
       </c>
       <c r="J209" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="210" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H210" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I210">
         <v>36577826</v>
       </c>
       <c r="J210" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="211" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H211" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I211">
         <v>35149611</v>
@@ -5295,128 +5299,128 @@
     </row>
     <row r="212" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I212">
         <v>26196255</v>
       </c>
       <c r="J212" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="213" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H213" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I213">
         <v>11156528</v>
       </c>
       <c r="J213" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="214" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H214" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I214">
         <v>38415503</v>
       </c>
       <c r="J214" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="215" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H215" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I215">
         <v>37244806</v>
       </c>
       <c r="J215" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="216" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H216" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I216">
         <v>27011098</v>
       </c>
       <c r="J216" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="217" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H217" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I217">
         <v>26019234</v>
       </c>
       <c r="J217" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="218" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H218" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I218">
         <v>13959023</v>
       </c>
       <c r="J218" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="219" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H219" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I219">
         <v>12496637</v>
       </c>
       <c r="J219" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="220" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H220" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I220">
         <v>25411238</v>
       </c>
       <c r="J220" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="221" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H221" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I221">
         <v>38312169</v>
       </c>
       <c r="J221" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="222" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H222" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I222">
         <v>31886592</v>
       </c>
       <c r="J222" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="223" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H223" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I223">
         <v>11670520</v>
@@ -5427,348 +5431,348 @@
     </row>
     <row r="224" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H224" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I224">
         <v>26500515</v>
       </c>
       <c r="J224" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="225" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H225" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I225">
         <v>36162739</v>
       </c>
       <c r="J225" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="226" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H226" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I226">
         <v>39893389</v>
       </c>
       <c r="J226" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="227" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H227" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I227">
         <v>39296173</v>
       </c>
       <c r="J227" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="228" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H228" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I228">
         <v>26491140</v>
       </c>
       <c r="J228" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="229" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H229" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I229">
         <v>49473587</v>
       </c>
       <c r="J229" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="230" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H230" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I230">
         <v>50326931</v>
       </c>
       <c r="J230" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="231" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H231" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I231">
         <v>12095120</v>
       </c>
       <c r="J231" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="232" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H232" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I232">
         <v>11765770</v>
       </c>
       <c r="J232" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="233" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H233" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I233">
         <v>15757638</v>
       </c>
       <c r="J233" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="234" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H234" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I234">
         <v>12038103</v>
       </c>
       <c r="J234" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="235" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H235" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I235">
         <v>46801171</v>
       </c>
       <c r="J235" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="236" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H236" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I236">
         <v>10155238</v>
       </c>
       <c r="J236" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="237" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H237" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I237">
         <v>10816066</v>
       </c>
       <c r="J237" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="238" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H238" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I238">
         <v>8668649</v>
       </c>
       <c r="J238" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="239" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H239" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I239">
         <v>36635604</v>
       </c>
       <c r="J239" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="240" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H240" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I240">
         <v>8837870</v>
       </c>
       <c r="J240" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="241" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H241" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I241">
         <v>5359040</v>
       </c>
       <c r="J241" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="242" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H242" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I242">
         <v>42373723</v>
       </c>
       <c r="J242" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="243" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H243" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I243">
         <v>16303007</v>
       </c>
       <c r="J243" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="244" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H244" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I244">
         <v>27303665</v>
       </c>
       <c r="J244" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="245" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H245" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I245">
         <v>5462299</v>
       </c>
       <c r="J245" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="246" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H246" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I246">
         <v>47220150</v>
       </c>
       <c r="J246" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="247" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H247" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I247">
         <v>42265154</v>
       </c>
       <c r="J247" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="248" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H248" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I248">
         <v>48105600</v>
       </c>
       <c r="J248" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="249" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H249" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I249">
         <v>34991467</v>
       </c>
       <c r="J249" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="250" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H250" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I250">
         <v>34348663</v>
       </c>
       <c r="J250" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="251" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H251" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I251">
         <v>34535085</v>
       </c>
       <c r="J251" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="252" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H252" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I252">
         <v>41140508</v>
       </c>
       <c r="J252" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="253" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H253" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I253">
         <v>22441147</v>
       </c>
       <c r="J253" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="254" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H254" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I254">
         <v>36811022</v>
       </c>
       <c r="J254" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="255" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H255" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I255">
         <v>36811023</v>
@@ -5779,414 +5783,414 @@
     </row>
     <row r="256" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H256" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I256">
         <v>42217758</v>
       </c>
       <c r="J256" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="257" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H257" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I257">
         <v>39384055</v>
       </c>
       <c r="J257" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="258" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H258" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I258">
         <v>11681261</v>
       </c>
       <c r="J258" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="259" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H259" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I259">
         <v>37161537</v>
       </c>
       <c r="J259" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="260" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H260" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I260">
         <v>30405071</v>
       </c>
       <c r="J260" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="261" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H261" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I261">
         <v>22403445</v>
       </c>
       <c r="J261" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="262" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H262" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I262">
         <v>26257716</v>
       </c>
       <c r="J262" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="263" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H263" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I263">
         <v>12481760</v>
       </c>
       <c r="J263" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="264" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H264" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I264">
         <v>12481759</v>
       </c>
       <c r="J264" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="265" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H265" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I265">
         <v>36682232</v>
       </c>
       <c r="J265" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="266" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H266" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I266">
         <v>46727700</v>
       </c>
       <c r="J266" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="267" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H267" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I267">
         <v>40771157</v>
       </c>
       <c r="J267" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="268" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H268" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I268">
         <v>19104731</v>
       </c>
       <c r="J268" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="269" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H269" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I269">
         <v>39944753</v>
       </c>
       <c r="J269" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="270" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H270" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I270">
         <v>48449253</v>
       </c>
       <c r="J270" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="271" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H271" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I271">
         <v>42051062</v>
       </c>
       <c r="J271" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="272" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H272" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I272">
         <v>18291047</v>
       </c>
       <c r="J272" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="273" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H273" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I273">
         <v>10727917</v>
       </c>
       <c r="J273" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="274" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H274" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I274">
         <v>46543317</v>
       </c>
       <c r="J274" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="275" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H275" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I275">
         <v>13644995</v>
       </c>
       <c r="J275" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="276" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H276" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I276">
         <v>42486414</v>
       </c>
       <c r="J276" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="277" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H277" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I277">
         <v>44695653</v>
       </c>
       <c r="J277" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="278" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H278" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I278">
         <v>44374810</v>
       </c>
       <c r="J278" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="279" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H279" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I279">
         <v>29258063</v>
       </c>
       <c r="J279" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="280" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H280" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I280">
         <v>13405604</v>
       </c>
       <c r="J280" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="281" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H281" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I281">
         <v>10646862</v>
       </c>
       <c r="J281" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="282" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H282" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I282">
         <v>12362063</v>
       </c>
       <c r="J282" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="283" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H283" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I283">
         <v>40185196</v>
       </c>
       <c r="J283" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="284" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H284" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I284">
         <v>15825326</v>
       </c>
       <c r="J284" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="285" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H285" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I285">
         <v>26375455</v>
       </c>
       <c r="J285" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="286" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H286" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I286">
         <v>42803850</v>
       </c>
       <c r="J286" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="287" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H287" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I287">
         <v>50154913</v>
       </c>
       <c r="J287" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="288" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H288" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I288">
         <v>16806254</v>
       </c>
       <c r="J288" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="289" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H289" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I289">
         <v>40501253</v>
       </c>
       <c r="J289" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="290" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H290" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I290">
         <v>14878740</v>
       </c>
       <c r="J290" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="291" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H291" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I291">
         <v>12673237</v>
       </c>
       <c r="J291" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="292" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H292" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I292">
         <v>17579662</v>
       </c>
       <c r="J292" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="293" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H293" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I293">
         <v>14719737</v>
@@ -6197,1085 +6201,1085 @@
     </row>
     <row r="294" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H294" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I294">
         <v>22119013</v>
       </c>
       <c r="J294" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="295" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H295" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I295">
         <v>15795597</v>
       </c>
       <c r="J295" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="296" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H296" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I296">
         <v>12126317</v>
       </c>
       <c r="J296" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="297" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H297" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I297">
         <v>39239709</v>
       </c>
       <c r="J297" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="298" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H298" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I298">
         <v>14488275</v>
       </c>
       <c r="J298" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="299" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H299" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I299">
         <v>42519088</v>
       </c>
       <c r="J299" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="300" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H300" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I300">
         <v>17579394</v>
       </c>
       <c r="J300" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="301" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H301" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I301">
         <v>27056005</v>
       </c>
       <c r="J301" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="302" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H302" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I302">
         <v>24832169</v>
       </c>
       <c r="J302" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="303" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H303" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I303">
         <v>39147133</v>
       </c>
       <c r="J303" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="304" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H304" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I304">
         <v>39030281</v>
       </c>
       <c r="J304" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="305" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H305" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I305">
         <v>13373616</v>
       </c>
       <c r="J305" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="306" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H306" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I306">
         <v>12757668</v>
       </c>
       <c r="J306" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="307" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H307" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I307">
         <v>38977260</v>
       </c>
       <c r="J307" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="308" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H308" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I308">
         <v>38676914</v>
       </c>
       <c r="J308" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="309" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H309" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I309">
         <v>39911056</v>
       </c>
       <c r="J309" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="310" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H310" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I310">
         <v>40102936</v>
       </c>
       <c r="J310" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="311" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H311" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I311">
         <v>10929274</v>
       </c>
       <c r="J311" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="312" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H312" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I312">
         <v>10929273</v>
       </c>
       <c r="J312" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="313" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H313" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I313">
         <v>38412071</v>
       </c>
       <c r="J313" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="314" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H314" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I314">
         <v>29280326</v>
       </c>
       <c r="J314" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="315" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H315" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I315">
         <v>38412101</v>
       </c>
       <c r="J315" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="316" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H316" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I316">
         <v>5332788</v>
       </c>
       <c r="J316" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="317" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H317" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I317">
         <v>5332789</v>
       </c>
       <c r="J317" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="318" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H318" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I318">
         <v>51016959</v>
       </c>
       <c r="J318" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="319" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H319" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I319">
         <v>40636333</v>
       </c>
       <c r="J319" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="320" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H320" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I320">
         <v>50875168</v>
       </c>
       <c r="J320" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="321" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H321" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I321">
         <v>51623281</v>
       </c>
       <c r="J321" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="322" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H322" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I322">
         <v>51897600</v>
       </c>
       <c r="J322" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="323" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H323" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I323">
         <v>51989601</v>
       </c>
       <c r="J323" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="324" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H324" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I324">
         <v>52390638</v>
       </c>
       <c r="J324" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="325" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H325" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I325">
         <v>52362395</v>
       </c>
       <c r="J325" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="326" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H326" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I326">
         <v>52155415</v>
       </c>
       <c r="J326" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="327" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H327" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I327">
         <v>52162444</v>
       </c>
       <c r="J327" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="328" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H328" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I328">
         <v>52270898</v>
       </c>
       <c r="J328" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="329" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H329" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I329">
         <v>52211558</v>
       </c>
       <c r="J329" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="330" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H330" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I330">
         <v>52217000</v>
       </c>
       <c r="J330" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="331" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H331" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I331">
         <v>51689222</v>
       </c>
       <c r="J331" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="332" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H332" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I332">
         <v>51684787</v>
       </c>
       <c r="J332" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="333" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H333" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I333">
         <v>51883980</v>
       </c>
       <c r="J333" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="334" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H334" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I334">
         <v>51898514</v>
       </c>
       <c r="J334" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="335" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H335" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I335">
         <v>52990015</v>
       </c>
       <c r="J335" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="336" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H336" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I336">
         <v>52581507</v>
       </c>
       <c r="J336" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="337" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H337" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I337">
         <v>52613211</v>
       </c>
       <c r="J337" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="338" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H338" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I338">
         <v>52578670</v>
       </c>
       <c r="J338" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="339" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H339" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I339">
         <v>52874174</v>
       </c>
       <c r="J339" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="340" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H340" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I340">
         <v>52872566</v>
       </c>
       <c r="J340" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="341" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H341" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I341">
         <v>54145830</v>
       </c>
       <c r="J341" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="342" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H342" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I342">
         <v>53052265</v>
       </c>
       <c r="J342" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="343" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H343" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I343">
         <v>53297446</v>
       </c>
       <c r="J343" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="344" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H344" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I344">
         <v>53583387</v>
       </c>
       <c r="J344" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="345" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H345" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I345">
         <v>53564659</v>
       </c>
       <c r="J345" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="346" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H346" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I346">
         <v>53569741</v>
       </c>
       <c r="J346" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="347" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H347" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I347">
         <v>53680118</v>
       </c>
       <c r="J347" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="348" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H348" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I348">
         <v>53776254</v>
       </c>
       <c r="J348" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="349" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H349" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I349">
         <v>53967042</v>
       </c>
       <c r="J349" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="350" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H350" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I350">
         <v>55275736</v>
       </c>
       <c r="J350" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="351" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H351" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I351">
         <v>56663811</v>
       </c>
       <c r="J351" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="352" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H352" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I352">
         <v>59082806</v>
       </c>
       <c r="J352" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="353" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H353" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I353">
         <v>55369678</v>
       </c>
       <c r="J353" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="354" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H354" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I354">
         <v>55354052</v>
       </c>
       <c r="J354" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="355" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H355" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I355">
         <v>55381383</v>
       </c>
       <c r="J355" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="356" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H356" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I356">
         <v>55609278</v>
       </c>
       <c r="J356" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="357" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H357" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I357">
         <v>55356212</v>
       </c>
       <c r="J357" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="358" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H358" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I358">
         <v>55449180</v>
       </c>
       <c r="J358" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="359" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H359" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I359">
         <v>55357095</v>
       </c>
       <c r="J359" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="360" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H360" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I360">
         <v>55384739</v>
       </c>
       <c r="J360" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="361" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H361" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I361">
         <v>55357155</v>
       </c>
       <c r="J361" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="362" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H362" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I362">
         <v>55389336</v>
       </c>
       <c r="J362" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="363" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H363" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I363">
         <v>55356388</v>
       </c>
       <c r="J363" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="364" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H364" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I364">
         <v>55610213</v>
       </c>
       <c r="J364" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="365" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H365" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I365">
         <v>55462718</v>
       </c>
       <c r="J365" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="366" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H366" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I366">
         <v>58084222</v>
       </c>
       <c r="J366" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="367" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H367" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I367">
         <v>56651433</v>
       </c>
       <c r="J367" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="368" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H368" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I368">
         <v>56479851</v>
       </c>
       <c r="J368" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="369" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H369" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I369">
         <v>56667264</v>
       </c>
       <c r="J369" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="370" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H370" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I370">
         <v>56896464</v>
       </c>
       <c r="J370" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="371" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H371" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I371">
         <v>57592449</v>
       </c>
       <c r="J371" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="372" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H372" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I372">
         <v>56183402</v>
       </c>
       <c r="J372" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="373" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H373" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I373">
         <v>56651667</v>
       </c>
       <c r="J373" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="374" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H374" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I374">
         <v>58987730</v>
       </c>
       <c r="J374" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="375" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H375" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I375">
         <v>57422656</v>
       </c>
       <c r="J375" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="376" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H376" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I376">
         <v>58040260</v>
       </c>
       <c r="J376" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="377" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H377" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I377">
         <v>59070986</v>
       </c>
       <c r="J377" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="378" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H378" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I378">
         <v>59058036</v>
       </c>
       <c r="J378" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="379" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H379" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I379">
         <v>58505144</v>
       </c>
       <c r="J379" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="380" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H380" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I380">
         <v>58610450</v>
       </c>
       <c r="J380" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="381" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H381" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I381">
         <v>59056260</v>
       </c>
       <c r="J381" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="382" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H382" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I382">
         <v>58722261</v>
       </c>
       <c r="J382" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="383" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H383" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I383">
         <v>58716097</v>
       </c>
       <c r="J383" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="384" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H384" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I384">
         <v>58730204</v>
       </c>
       <c r="J384" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="385" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H385" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I385">
         <v>59199875</v>
       </c>
       <c r="J385" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="386" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H386" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I386">
         <v>59759466</v>
       </c>
       <c r="J386" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="387" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H387" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I387">
         <v>59332927</v>
       </c>
       <c r="J387" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="388" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H388" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I388">
         <v>59944694</v>
       </c>
       <c r="J388" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="389" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H389" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I389">
         <v>60019261</v>
       </c>
       <c r="J389" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="390" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H390" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I390">
         <v>59932138</v>
       </c>
       <c r="J390" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="391" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H391" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I391">
         <v>59924956</v>
       </c>
       <c r="J391" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="392" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H392" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I392">
         <v>59927382</v>
@@ -7286,18 +7290,18 @@
     </row>
     <row r="393" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H393" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I393">
         <v>59836396</v>
       </c>
       <c r="J393" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="394" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H394" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I394">
         <v>60015061</v>
@@ -7308,942 +7312,942 @@
     </row>
     <row r="395" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H395" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I395">
         <v>60023938</v>
       </c>
       <c r="J395" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="396" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H396" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I396">
         <v>60025950</v>
       </c>
       <c r="J396" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="397" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H397" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I397">
         <v>60024864</v>
       </c>
       <c r="J397" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="398" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H398" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I398">
         <v>60084208</v>
       </c>
       <c r="J398" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="399" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H399" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I399">
         <v>60085614</v>
       </c>
       <c r="J399" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="400" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H400" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I400">
         <v>60133592</v>
       </c>
       <c r="J400" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="401" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H401" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I401">
         <v>60450424</v>
       </c>
       <c r="J401" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="402" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H402" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I402">
         <v>60380162</v>
       </c>
       <c r="J402" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="403" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H403" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I403">
         <v>60541542</v>
       </c>
       <c r="J403" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="404" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H404" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I404">
         <v>60541171</v>
       </c>
       <c r="J404" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="405" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H405" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I405">
         <v>60543356</v>
       </c>
       <c r="J405" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="406" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H406" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I406">
         <v>60530655</v>
       </c>
       <c r="J406" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="407" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H407" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I407">
         <v>60615380</v>
       </c>
       <c r="J407" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="408" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H408" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I408">
         <v>60725132</v>
       </c>
       <c r="J408" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="409" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H409" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I409">
         <v>62575565</v>
       </c>
       <c r="J409" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="410" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H410" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I410">
         <v>61766007</v>
       </c>
       <c r="J410" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="411" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H411" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I411">
         <v>61089339</v>
       </c>
       <c r="J411" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="412" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H412" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I412">
         <v>62377903</v>
       </c>
       <c r="J412" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="413" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H413" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I413">
         <v>60542212</v>
       </c>
       <c r="J413" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="414" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H414" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I414">
         <v>61044622</v>
       </c>
       <c r="J414" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="415" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H415" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I415">
         <v>61199642</v>
       </c>
       <c r="J415" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="416" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H416" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I416">
         <v>61760291</v>
       </c>
       <c r="J416" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="417" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H417" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I417">
         <v>61923953</v>
       </c>
       <c r="J417" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="418" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H418" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I418">
         <v>61760141</v>
       </c>
       <c r="J418" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="419" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H419" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I419">
         <v>61929592</v>
       </c>
       <c r="J419" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="420" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H420" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I420">
         <v>61929727</v>
       </c>
       <c r="J420" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="421" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H421" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I421">
         <v>61929494</v>
       </c>
       <c r="J421" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="422" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H422" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I422">
         <v>61929493</v>
       </c>
       <c r="J422" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="423" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H423" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I423">
         <v>61879892</v>
       </c>
       <c r="J423" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="424" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H424" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I424">
         <v>62378988</v>
       </c>
       <c r="J424" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="425" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H425" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I425">
         <v>62375802</v>
       </c>
       <c r="J425" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="426" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H426" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I426">
         <v>62379668</v>
       </c>
       <c r="J426" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="427" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H427" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I427">
         <v>62221331</v>
       </c>
       <c r="J427" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="428" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H428" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I428">
         <v>62385013</v>
       </c>
       <c r="J428" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="429" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H429" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I429">
         <v>62380995</v>
       </c>
       <c r="J429" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="430" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H430" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I430">
         <v>62421723</v>
       </c>
       <c r="J430" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="431" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H431" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I431">
         <v>62374813</v>
       </c>
       <c r="J431" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="432" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H432" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I432">
         <v>62499786</v>
       </c>
       <c r="J432" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="433" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H433" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I433">
         <v>62498583</v>
       </c>
       <c r="J433" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="434" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H434" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I434">
         <v>63346456</v>
       </c>
       <c r="J434" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="435" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H435" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I435">
         <v>63100963</v>
       </c>
       <c r="J435" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="436" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H436" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I436">
         <v>63396496</v>
       </c>
       <c r="J436" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="437" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H437" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I437">
         <v>64270608</v>
       </c>
       <c r="J437" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="438" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H438" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I438">
         <v>63573761</v>
       </c>
       <c r="J438" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="439" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H439" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I439">
         <v>64330763</v>
       </c>
       <c r="J439" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="440" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H440" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I440">
         <v>64330764</v>
       </c>
       <c r="J440" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="441" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H441" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I441">
         <v>64212552</v>
       </c>
       <c r="J441" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="442" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H442" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I442">
         <v>64212544</v>
       </c>
       <c r="J442" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="443" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H443" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I443">
         <v>64212543</v>
       </c>
       <c r="J443" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="444" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H444" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I444">
         <v>64212381</v>
       </c>
       <c r="J444" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="445" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H445" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I445">
         <v>64114088</v>
       </c>
       <c r="J445" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="446" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H446" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I446">
         <v>64223250</v>
       </c>
       <c r="J446" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="447" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H447" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I447">
         <v>64214259</v>
       </c>
       <c r="J447" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="448" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H448" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I448">
         <v>64214258</v>
       </c>
       <c r="J448" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="449" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H449" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I449">
         <v>63742200</v>
       </c>
       <c r="J449" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="450" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H450" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I450">
         <v>64606094</v>
       </c>
       <c r="J450" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="451" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H451" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I451">
         <v>64287980</v>
       </c>
       <c r="J451" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="452" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H452" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I452">
         <v>64257297</v>
       </c>
       <c r="J452" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="453" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H453" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I453">
         <v>66097436</v>
       </c>
       <c r="J453" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="454" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H454" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I454">
         <v>64330309</v>
       </c>
       <c r="J454" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="455" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H455" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I455">
         <v>64846264</v>
       </c>
       <c r="J455" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="456" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H456" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I456">
         <v>64753996</v>
       </c>
       <c r="J456" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="457" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H457" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I457">
         <v>64778162</v>
       </c>
       <c r="J457" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="458" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H458" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I458">
         <v>64778161</v>
       </c>
       <c r="J458" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="459" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H459" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I459">
         <v>64808932</v>
       </c>
       <c r="J459" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="460" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H460" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I460">
         <v>64789478</v>
       </c>
       <c r="J460" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="461" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H461" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I461">
         <v>64912430</v>
       </c>
       <c r="J461" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="462" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H462" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I462">
         <v>64971361</v>
       </c>
       <c r="J462" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="463" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H463" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I463">
         <v>65145714</v>
       </c>
       <c r="J463" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="464" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H464" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I464">
         <v>65081124</v>
       </c>
       <c r="J464" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="465" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H465" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I465">
         <v>65181042</v>
       </c>
       <c r="J465" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="466" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H466" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I466">
         <v>65179405</v>
       </c>
       <c r="J466" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="467" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H467" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I467">
         <v>65566244</v>
       </c>
       <c r="J467" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="468" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H468" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I468">
         <v>65566541</v>
       </c>
       <c r="J468" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="469" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H469" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I469">
         <v>65656468</v>
       </c>
       <c r="J469" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="470" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H470" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I470">
         <v>65657039</v>
       </c>
       <c r="J470" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="471" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H471" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I471">
         <v>66217025</v>
       </c>
       <c r="J471" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="472" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H472" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I472">
         <v>66214618</v>
       </c>
       <c r="J472" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="473" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H473" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I473">
         <v>65935700</v>
       </c>
       <c r="J473" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="474" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H474" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I474">
         <v>65934564</v>
       </c>
       <c r="J474" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="475" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H475" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I475">
         <v>65933937</v>
       </c>
       <c r="J475" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="476" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H476" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I476">
         <v>66046959</v>
       </c>
       <c r="J476" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="477" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H477" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I477">
         <v>65969750</v>
       </c>
       <c r="J477" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="478" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H478" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I478">
         <v>66358440</v>
       </c>
       <c r="J478" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="479" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H479" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I479">
         <v>66417803</v>
       </c>
       <c r="J479" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="480" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H480" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I480">
         <v>66417801</v>
@@ -8254,695 +8258,695 @@
     </row>
     <row r="481" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H481" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I481">
         <v>66357977</v>
       </c>
       <c r="J481" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="482" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H482" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I482">
         <v>67191572</v>
       </c>
       <c r="J482" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="483" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H483" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I483">
         <v>66546178</v>
       </c>
       <c r="J483" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="484" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H484" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I484">
         <v>67627331</v>
       </c>
       <c r="J484" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="485" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H485" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I485">
         <v>66778787</v>
       </c>
       <c r="J485" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="486" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H486" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I486">
         <v>66778788</v>
       </c>
       <c r="J486" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="487" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H487" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I487">
         <v>66778789</v>
       </c>
       <c r="J487" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="488" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H488" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I488">
         <v>66896364</v>
       </c>
       <c r="J488" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="489" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H489" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I489">
         <v>66607099</v>
       </c>
       <c r="J489" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="490" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H490" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I490">
         <v>66864708</v>
       </c>
       <c r="J490" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="491" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H491" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I491">
         <v>66850322</v>
       </c>
       <c r="J491" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="492" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H492" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I492">
         <v>67268341</v>
       </c>
       <c r="J492" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="493" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H493" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I493">
         <v>67268348</v>
       </c>
       <c r="J493" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="494" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H494" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I494">
         <v>67268349</v>
       </c>
       <c r="J494" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="495" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H495" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I495">
         <v>67268350</v>
       </c>
       <c r="J495" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="496" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H496" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I496">
         <v>67272047</v>
       </c>
       <c r="J496" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="497" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H497" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I497">
         <v>67272046</v>
       </c>
       <c r="J497" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="498" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H498" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I498">
         <v>67438488</v>
       </c>
       <c r="J498" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="499" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H499" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I499">
         <v>67438487</v>
       </c>
       <c r="J499" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="500" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H500" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I500">
         <v>68253037</v>
       </c>
       <c r="J500" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="501" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H501" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I501">
         <v>67891311</v>
       </c>
       <c r="J501" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="502" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H502" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I502">
         <v>67900090</v>
       </c>
       <c r="J502" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="503" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H503" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I503">
         <v>67630646</v>
       </c>
       <c r="J503" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="504" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H504" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I504">
         <v>67974104</v>
       </c>
       <c r="J504" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="505" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H505" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I505">
         <v>67989839</v>
       </c>
       <c r="J505" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="506" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H506" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I506">
         <v>67988468</v>
       </c>
       <c r="J506" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="507" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H507" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I507">
         <v>68466892</v>
       </c>
       <c r="J507" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="508" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H508" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I508">
         <v>69040158</v>
       </c>
       <c r="J508" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="509" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H509" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I509">
         <v>68462854</v>
       </c>
       <c r="J509" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="510" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H510" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I510" t="s">
+        <v>534</v>
+      </c>
+      <c r="J510" t="s">
         <v>535</v>
-      </c>
-      <c r="J510" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="511" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H511" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I511" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="J511" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="512" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H512" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I512">
         <v>68677002</v>
       </c>
       <c r="J512" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="513" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H513" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I513">
         <v>68880617</v>
       </c>
       <c r="J513" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="514" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H514" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I514">
         <v>68934411</v>
       </c>
       <c r="J514" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="515" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H515" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I515">
         <v>68924611</v>
       </c>
       <c r="J515" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="516" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H516" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I516">
         <v>69039437</v>
       </c>
       <c r="J516" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="517" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H517" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I517">
         <v>69039778</v>
       </c>
       <c r="J517" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="518" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H518" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I518">
         <v>69279032</v>
       </c>
       <c r="J518" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="519" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H519" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I519">
         <v>68938743</v>
       </c>
       <c r="J519" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="520" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H520" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I520">
         <v>69772629</v>
       </c>
       <c r="J520" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="521" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H521" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I521">
         <v>69772627</v>
       </c>
       <c r="J521" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="522" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H522" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I522">
         <v>69772625</v>
       </c>
       <c r="J522" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="523" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H523" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I523">
         <v>69292187</v>
       </c>
       <c r="J523" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="524" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H524" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I524">
         <v>69292186</v>
       </c>
       <c r="J524" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="525" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H525" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I525">
         <v>69292185</v>
       </c>
       <c r="J525" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="526" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H526" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I526">
         <v>69096297</v>
       </c>
       <c r="J526" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="527" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H527" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I527">
         <v>69096296</v>
       </c>
       <c r="J527" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="528" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H528" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I528">
         <v>69594684</v>
       </c>
       <c r="J528" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="529" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H529" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I529">
         <v>70204974</v>
       </c>
       <c r="J529" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="530" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H530" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I530">
         <v>70204975</v>
       </c>
       <c r="J530" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="531" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H531" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I531">
         <v>69767288</v>
       </c>
       <c r="J531" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="532" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H532" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I532">
         <v>69766464</v>
       </c>
       <c r="J532" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="533" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H533" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I533">
         <v>69803799</v>
       </c>
       <c r="J533" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="534" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H534" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I534">
         <v>70251147</v>
       </c>
       <c r="J534" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="535" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H535" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I535">
         <v>69770093</v>
       </c>
       <c r="J535" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="536" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H536" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I536">
         <v>70205079</v>
       </c>
       <c r="J536" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="537" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H537" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I537">
         <v>70530577</v>
       </c>
       <c r="J537" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="538" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H538" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I538">
         <v>70530576</v>
       </c>
       <c r="J538" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="539" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H539" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I539">
         <v>71030052</v>
       </c>
       <c r="J539" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="540" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H540" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I540">
         <v>70770186</v>
       </c>
       <c r="J540" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="541" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H541" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I541">
         <v>71173111</v>
       </c>
       <c r="J541" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="542" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H542" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I542">
         <v>71156871</v>
       </c>
       <c r="J542" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="543" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H543" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I543">
         <v>71291488</v>
       </c>
       <c r="J543" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="544" spans="8:10" x14ac:dyDescent="0.3">
@@ -8950,656 +8954,656 @@
         <v>71042279</v>
       </c>
       <c r="J544" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="545" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H545" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I545">
         <v>71947627</v>
       </c>
       <c r="J545" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="546" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H546" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I546">
         <v>72182444</v>
       </c>
       <c r="J546" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="547" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H547" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I547">
         <v>72300747</v>
       </c>
       <c r="J547" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="548" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H548" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I548">
         <v>72417582</v>
       </c>
       <c r="J548" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="549" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H549" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I549">
         <v>72614935</v>
       </c>
       <c r="J549" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="550" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H550" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I550">
         <v>72614936</v>
       </c>
       <c r="J550" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="551" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H551" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I551">
         <v>72614937</v>
       </c>
       <c r="J551" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="552" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H552" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I552">
         <v>73226633</v>
       </c>
       <c r="J552" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="553" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H553" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I553">
         <v>73226632</v>
       </c>
       <c r="J553" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="554" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H554" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I554">
         <v>73316683</v>
       </c>
       <c r="J554" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="555" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H555" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I555">
         <v>73316684</v>
       </c>
       <c r="J555" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="556" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H556" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I556">
         <v>73316685</v>
       </c>
       <c r="J556" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="557" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H557" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I557">
         <v>72699936</v>
       </c>
       <c r="J557" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="558" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H558" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I558">
         <v>72699935</v>
       </c>
       <c r="J558" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="559" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H559" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I559">
         <v>72828733</v>
       </c>
       <c r="J559" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="560" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H560" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I560">
         <v>72828734</v>
       </c>
       <c r="J560" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="561" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H561" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I561">
         <v>72683872</v>
       </c>
       <c r="J561" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="562" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H562" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I562">
         <v>72910681</v>
       </c>
       <c r="J562" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="563" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H563" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I563">
         <v>72910683</v>
       </c>
       <c r="J563" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="564" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H564" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I564">
         <v>73523448</v>
       </c>
       <c r="J564" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="565" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H565" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I565">
         <v>73461995</v>
       </c>
       <c r="J565" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="566" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H566" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I566">
         <v>73956460</v>
       </c>
       <c r="J566" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="567" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H567" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I567">
         <v>73956461</v>
       </c>
       <c r="J567" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="568" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H568" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I568">
         <v>73956459</v>
       </c>
       <c r="J568" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="569" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H569" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I569">
         <v>74685916</v>
       </c>
       <c r="J569" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="570" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H570" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I570">
         <v>73975553</v>
       </c>
       <c r="J570" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="571" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H571" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I571">
         <v>73952843</v>
       </c>
       <c r="J571" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="572" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H572" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I572">
         <v>74550323</v>
       </c>
       <c r="J572" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="573" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H573" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I573">
         <v>75989703</v>
       </c>
       <c r="J573" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="574" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H574" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I574">
         <v>74693807</v>
       </c>
       <c r="J574" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="575" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H575" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I575">
         <v>73893263</v>
       </c>
       <c r="J575" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="576" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H576" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I576">
         <v>74884452</v>
       </c>
       <c r="J576" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="577" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H577" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I577">
         <v>74826973</v>
       </c>
       <c r="J577" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="578" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H578" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I578">
         <v>74826974</v>
       </c>
       <c r="J578" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="579" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H579" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I579">
         <v>75077119</v>
       </c>
       <c r="J579" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="580" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H580" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I580">
         <v>78867502</v>
       </c>
       <c r="J580" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="581" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H581" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I581">
         <v>80192305</v>
       </c>
       <c r="J581" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="582" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H582" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I582">
         <v>75741354</v>
       </c>
       <c r="J582" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="583" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H583" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I583">
         <v>78625461</v>
       </c>
       <c r="J583" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="584" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H584" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I584">
         <v>76375598</v>
       </c>
       <c r="J584" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="585" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H585" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I585">
         <v>76375597</v>
       </c>
       <c r="J585" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="586" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H586" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I586">
         <v>76374400</v>
       </c>
       <c r="J586" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="587" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H587" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I587">
         <v>76374401</v>
       </c>
       <c r="J587" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="588" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H588" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I588">
         <v>76241042</v>
       </c>
       <c r="J588" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="589" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H589" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I589">
         <v>76533940</v>
       </c>
       <c r="J589" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="590" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H590" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I590">
         <v>77463489</v>
       </c>
       <c r="J590" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="591" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H591" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I591">
         <v>77463490</v>
       </c>
       <c r="J591" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="592" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H592" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I592" s="2">
         <v>78907466</v>
       </c>
       <c r="J592" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="593" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H593" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I593" s="2">
         <v>78907465</v>
       </c>
       <c r="J593" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="594" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H594" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I594" s="2">
         <v>78903848</v>
       </c>
       <c r="J594" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="595" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H595" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I595" s="2">
         <v>78903849</v>
       </c>
       <c r="J595" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="596" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H596" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I596" s="2">
         <v>78621004</v>
       </c>
       <c r="J596" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="597" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H597" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I597" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="J597" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="598" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H598" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I598" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="J598" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="599" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H599" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I599" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="J599" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="600" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H600" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I600" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="J600" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="601" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H601" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I601" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="J601" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="602" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H602" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I602" s="2">
         <v>80629877</v>
       </c>
       <c r="J602" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="603" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H603" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I603" s="2">
         <v>80629881</v>
       </c>
       <c r="J603" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
   </sheetData>

--- a/data/이슈제품.xlsx
+++ b/data/이슈제품.xlsx
@@ -8,13 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OA\Desktop\쿠팡업로드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48A0FDCF-8E6E-4B6C-B7E8-42E6F6450ADB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B8D548-1721-40EA-B84A-FB3A85BCD34F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$13:$C$13</definedName>
+  </definedNames>
   <calcPr calcId="179021"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="650">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="657">
   <si>
     <t>오아디머무드등-화이트</t>
   </si>
@@ -1933,10 +1938,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>협의, 10월 중순</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>오아넥스트레쳐S-베이지</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1958,10 +1959,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>입고X, 10월 중순</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>협의, 10월 말</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1970,10 +1967,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>입고X, 10/20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>입고X, 10/16</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1994,7 +1987,47 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>입고X, 10/6 예정</t>
+    <t>입고X, 10/13 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입고X, 10/12 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입고X, 10/14 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>협의, 10/14 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입고X, 10/16 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입고X, 10/20 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입고X, 10/20 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sku id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전산명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입고X, 11월 초</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2002,7 +2035,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2023,6 +2056,15 @@
       <color rgb="FFFF0000"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
@@ -2049,7 +2091,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2062,11 +2104,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2377,13 +2453,13 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>60015061</v>
+        <v>27056005</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>330</v>
       </c>
       <c r="C2" t="s">
-        <v>1</v>
+        <v>629</v>
       </c>
       <c r="H2" t="s">
         <v>30</v>
@@ -2397,13 +2473,13 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>76375597</v>
+        <v>52270898</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>357</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>642</v>
       </c>
       <c r="H3" t="s">
         <v>30</v>
@@ -2417,13 +2493,13 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>58505144</v>
+        <v>4152606</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>223</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>640</v>
       </c>
       <c r="H4" t="s">
         <v>30</v>
@@ -2437,13 +2513,13 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>50725354</v>
+        <v>12263239</v>
       </c>
       <c r="B5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C5" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H5" t="s">
         <v>30</v>
@@ -2457,10 +2533,10 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>12263239</v>
+        <v>68880617</v>
       </c>
       <c r="B6" t="s">
-        <v>207</v>
+        <v>633</v>
       </c>
       <c r="C6" t="s">
         <v>627</v>
@@ -2477,13 +2553,13 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>68880617</v>
+        <v>5332788</v>
       </c>
       <c r="B7" t="s">
-        <v>634</v>
+        <v>345</v>
       </c>
       <c r="C7" t="s">
-        <v>627</v>
+        <v>639</v>
       </c>
       <c r="H7" t="s">
         <v>30</v>
@@ -2497,13 +2573,13 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>42519088</v>
+        <v>11229298</v>
       </c>
       <c r="B8" t="s">
-        <v>328</v>
+        <v>175</v>
       </c>
       <c r="C8" t="s">
-        <v>640</v>
+        <v>649</v>
       </c>
       <c r="H8" t="s">
         <v>30</v>
@@ -2517,13 +2593,13 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>4152606</v>
+        <v>58505144</v>
       </c>
       <c r="B9" t="s">
-        <v>223</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>642</v>
+        <v>17</v>
       </c>
       <c r="H9" t="s">
         <v>30</v>
@@ -2537,13 +2613,13 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>4125377</v>
+        <v>65933937</v>
       </c>
       <c r="B10" t="s">
-        <v>203</v>
+        <v>500</v>
       </c>
       <c r="C10" t="s">
-        <v>628</v>
+        <v>644</v>
       </c>
       <c r="H10" t="s">
         <v>30</v>
@@ -2557,13 +2633,13 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>26426530</v>
+        <v>76375597</v>
       </c>
       <c r="B11" t="s">
-        <v>204</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>628</v>
+        <v>23</v>
       </c>
       <c r="H11" t="s">
         <v>30</v>
@@ -2577,13 +2653,13 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>12439390</v>
+        <v>60015061</v>
       </c>
       <c r="B12" t="s">
-        <v>206</v>
+        <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>633</v>
+        <v>1</v>
       </c>
       <c r="H12" t="s">
         <v>30</v>
@@ -2597,13 +2673,13 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>5332788</v>
+        <v>50725354</v>
       </c>
       <c r="B13" t="s">
-        <v>345</v>
+        <v>208</v>
       </c>
       <c r="C13" t="s">
-        <v>641</v>
+        <v>626</v>
       </c>
       <c r="H13" t="s">
         <v>30</v>
@@ -2617,13 +2693,13 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>11229298</v>
+        <v>50153946</v>
       </c>
       <c r="B14" t="s">
-        <v>175</v>
+        <v>115</v>
       </c>
       <c r="C14" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H14" t="s">
         <v>30</v>
@@ -2637,13 +2713,13 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>27056005</v>
+        <v>75741354</v>
       </c>
       <c r="B15" t="s">
-        <v>330</v>
+        <v>605</v>
       </c>
       <c r="C15" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H15" t="s">
         <v>30</v>
@@ -2657,13 +2733,13 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>50153946</v>
+        <v>60542212</v>
       </c>
       <c r="B16" t="s">
-        <v>115</v>
+        <v>438</v>
       </c>
       <c r="C16" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H16" t="s">
         <v>30</v>
@@ -2677,13 +2753,13 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>75741354</v>
+        <v>15414324</v>
       </c>
       <c r="B17" t="s">
-        <v>605</v>
+        <v>199</v>
       </c>
       <c r="C17" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="H17" t="s">
         <v>30</v>
@@ -2697,13 +2773,13 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>60542212</v>
+        <v>12439390</v>
       </c>
       <c r="B18" t="s">
-        <v>438</v>
+        <v>206</v>
       </c>
       <c r="C18" t="s">
-        <v>631</v>
+        <v>652</v>
       </c>
       <c r="H18" t="s">
         <v>30</v>
@@ -2716,14 +2792,14 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="3">
-        <v>13101217</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>649</v>
+      <c r="A19">
+        <v>14107560</v>
+      </c>
+      <c r="B19" t="s">
+        <v>195</v>
+      </c>
+      <c r="C19" t="s">
+        <v>651</v>
       </c>
       <c r="H19" t="s">
         <v>30</v>
@@ -2737,13 +2813,13 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>15414324</v>
+        <v>17579394</v>
       </c>
       <c r="B20" t="s">
-        <v>199</v>
+        <v>329</v>
       </c>
       <c r="C20" t="s">
-        <v>632</v>
+        <v>650</v>
       </c>
       <c r="H20" t="s">
         <v>30</v>
@@ -2757,13 +2833,13 @@
     </row>
     <row r="21" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>51623281</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>636</v>
+        <v>53569741</v>
+      </c>
+      <c r="B21" t="s">
+        <v>375</v>
       </c>
       <c r="C21" t="s">
-        <v>638</v>
+        <v>650</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>30</v>
@@ -2777,13 +2853,13 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>51989601</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>637</v>
+        <v>75077119</v>
+      </c>
+      <c r="B22" t="s">
+        <v>602</v>
       </c>
       <c r="C22" t="s">
-        <v>638</v>
+        <v>656</v>
       </c>
       <c r="H22" t="s">
         <v>30</v>
@@ -2797,13 +2873,13 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>11192166</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>167</v>
+        <v>42519088</v>
+      </c>
+      <c r="B23" t="s">
+        <v>328</v>
       </c>
       <c r="C23" t="s">
-        <v>638</v>
+        <v>648</v>
       </c>
       <c r="H23" t="s">
         <v>30</v>
@@ -2817,13 +2893,13 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>15812678</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>146</v>
+        <v>4125377</v>
+      </c>
+      <c r="B24" t="s">
+        <v>203</v>
       </c>
       <c r="C24" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="H24" t="s">
         <v>30</v>
@@ -2837,13 +2913,13 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>12091621</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>143</v>
+        <v>26426530</v>
+      </c>
+      <c r="B25" t="s">
+        <v>204</v>
       </c>
       <c r="C25" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="H25" t="s">
         <v>30</v>
@@ -2857,13 +2933,13 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>12143584</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>150</v>
+        <v>43252471</v>
+      </c>
+      <c r="B26" t="s">
+        <v>192</v>
       </c>
       <c r="C26" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="H26" t="s">
         <v>30</v>
@@ -2877,13 +2953,13 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>11192167</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>151</v>
+        <v>64789478</v>
+      </c>
+      <c r="B27" t="s">
+        <v>485</v>
       </c>
       <c r="C27" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="H27" t="s">
         <v>30</v>
@@ -2897,13 +2973,13 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>12143581</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>147</v>
+        <v>71030052</v>
+      </c>
+      <c r="B28" t="s">
+        <v>564</v>
       </c>
       <c r="C28" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="H28" t="s">
         <v>30</v>
@@ -2916,14 +2992,14 @@
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29">
-        <v>11192165</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C29" t="s">
-        <v>638</v>
+      <c r="A29" s="3">
+        <v>13101217</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>647</v>
       </c>
       <c r="H29" t="s">
         <v>57</v>
@@ -2937,13 +3013,13 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>11192163</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>149</v>
+        <v>53583387</v>
+      </c>
+      <c r="B30" t="s">
+        <v>373</v>
       </c>
       <c r="C30" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="H30" t="s">
         <v>59</v>
@@ -2957,13 +3033,13 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>11291291</v>
+        <v>51623281</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>157</v>
+        <v>635</v>
       </c>
       <c r="C31" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H31" t="s">
         <v>59</v>
@@ -2977,13 +3053,13 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>16171214</v>
+        <v>51989601</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>156</v>
+        <v>636</v>
       </c>
       <c r="C32" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H32" t="s">
         <v>59</v>
@@ -2997,13 +3073,13 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>12218847</v>
+        <v>11192166</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="C33" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H33" t="s">
         <v>59</v>
@@ -3017,13 +3093,13 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>15838517</v>
+        <v>15812678</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="C34" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H34" t="s">
         <v>59</v>
@@ -3037,13 +3113,13 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>12673238</v>
+        <v>12091621</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="C35" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H35" t="s">
         <v>59</v>
@@ -3057,13 +3133,13 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>37790051</v>
+        <v>12143584</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="C36" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H36" t="s">
         <v>59</v>
@@ -3077,13 +3153,13 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>37594934</v>
+        <v>11192167</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="C37" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H37" t="s">
         <v>59</v>
@@ -3097,13 +3173,13 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>15702671</v>
+        <v>12143581</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>174</v>
+        <v>147</v>
       </c>
       <c r="C38" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H38" t="s">
         <v>59</v>
@@ -3117,13 +3193,13 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>39071990</v>
+        <v>11192165</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="C39" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H39" t="s">
         <v>59</v>
@@ -3137,13 +3213,13 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>52204284</v>
+        <v>11192163</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>92</v>
+        <v>149</v>
       </c>
       <c r="C40" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H40" t="s">
         <v>59</v>
@@ -3157,13 +3233,13 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>39006854</v>
+        <v>11291291</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="C41" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H41" t="s">
         <v>59</v>
@@ -3177,13 +3253,13 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>39006857</v>
+        <v>16171214</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="C42" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H42" t="s">
         <v>59</v>
@@ -3197,13 +3273,13 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>39006855</v>
+        <v>12218847</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C43" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H43" t="s">
         <v>59</v>
@@ -3217,13 +3293,13 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>51883980</v>
+        <v>15838517</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>362</v>
+        <v>154</v>
       </c>
       <c r="C44" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H44" t="s">
         <v>59</v>
@@ -3237,13 +3313,13 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>52578670</v>
+        <v>12673238</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>367</v>
+        <v>152</v>
       </c>
       <c r="C45" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H45" t="s">
         <v>59</v>
@@ -3257,13 +3333,13 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>52155531</v>
+        <v>37790051</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>94</v>
+        <v>160</v>
       </c>
       <c r="C46" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H46" t="s">
         <v>59</v>
@@ -3277,13 +3353,13 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>15831347</v>
+        <v>37594934</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="C47" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H47" t="s">
         <v>59</v>
@@ -3297,13 +3373,13 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>32548061</v>
+        <v>15702671</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="C48" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H48" t="s">
         <v>59</v>
@@ -3317,13 +3393,13 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>35876282</v>
+        <v>39071990</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="C49" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H49" t="s">
         <v>59</v>
@@ -3337,13 +3413,13 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>16805855</v>
+        <v>52204284</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>145</v>
+        <v>92</v>
       </c>
       <c r="C50" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H50" t="s">
         <v>59</v>
@@ -3357,13 +3433,13 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>55381383</v>
+        <v>39006854</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>384</v>
+        <v>164</v>
       </c>
       <c r="C51" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H51" t="s">
         <v>59</v>
@@ -3377,13 +3453,13 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>55449180</v>
+        <v>39006857</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>386</v>
+        <v>162</v>
       </c>
       <c r="C52" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H52" t="s">
         <v>59</v>
@@ -3397,13 +3473,13 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>55384739</v>
+        <v>39006855</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>388</v>
+        <v>163</v>
       </c>
       <c r="C53" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H53" t="s">
         <v>59</v>
@@ -3417,13 +3493,13 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>55389336</v>
+        <v>51883980</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>635</v>
+        <v>362</v>
       </c>
       <c r="C54" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H54" t="s">
         <v>59</v>
@@ -3437,13 +3513,13 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>55609278</v>
+        <v>52578670</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="C55" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H55" t="s">
         <v>59</v>
@@ -3457,13 +3533,13 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>71042279</v>
+        <v>52155531</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>569</v>
+        <v>94</v>
       </c>
       <c r="C56" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="H56" t="s">
         <v>59</v>
@@ -3477,13 +3553,13 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>67630646</v>
-      </c>
-      <c r="B57" t="s">
-        <v>527</v>
+        <v>15831347</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>142</v>
       </c>
       <c r="C57" t="s">
-        <v>646</v>
+        <v>637</v>
       </c>
       <c r="H57" t="s">
         <v>59</v>
@@ -3497,13 +3573,13 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>64971361</v>
-      </c>
-      <c r="B58" t="s">
-        <v>487</v>
+        <v>32548061</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="C58" t="s">
-        <v>646</v>
+        <v>637</v>
       </c>
       <c r="H58" t="s">
         <v>59</v>
@@ -3517,13 +3593,13 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>62421723</v>
-      </c>
-      <c r="B59" t="s">
-        <v>455</v>
+        <v>35876282</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>173</v>
       </c>
       <c r="C59" t="s">
-        <v>646</v>
+        <v>637</v>
       </c>
       <c r="H59" t="s">
         <v>59</v>
@@ -3537,13 +3613,13 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>62374813</v>
-      </c>
-      <c r="B60" t="s">
-        <v>456</v>
+        <v>16805855</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>145</v>
       </c>
       <c r="C60" t="s">
-        <v>646</v>
+        <v>637</v>
       </c>
       <c r="H60" t="s">
         <v>59</v>
@@ -3557,13 +3633,13 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>68462854</v>
-      </c>
-      <c r="B61" t="s">
-        <v>533</v>
+        <v>55381383</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>384</v>
       </c>
       <c r="C61" t="s">
-        <v>646</v>
+        <v>637</v>
       </c>
       <c r="H61" t="s">
         <v>59</v>
@@ -3577,13 +3653,13 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>64114088</v>
-      </c>
-      <c r="B62" t="s">
-        <v>470</v>
+        <v>55449180</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>386</v>
       </c>
       <c r="C62" t="s">
-        <v>646</v>
+        <v>637</v>
       </c>
       <c r="H62" t="s">
         <v>91</v>
@@ -3597,13 +3673,13 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>19213859</v>
-      </c>
-      <c r="B63" t="s">
-        <v>35</v>
+        <v>55384739</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>388</v>
       </c>
       <c r="C63" t="s">
-        <v>646</v>
+        <v>637</v>
       </c>
       <c r="H63" t="s">
         <v>93</v>
@@ -3617,13 +3693,13 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>13004238</v>
-      </c>
-      <c r="B64" t="s">
-        <v>37</v>
+        <v>55389336</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>634</v>
       </c>
       <c r="C64" t="s">
-        <v>646</v>
+        <v>637</v>
       </c>
       <c r="H64" t="s">
         <v>95</v>
@@ -3637,13 +3713,13 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>43252471</v>
-      </c>
-      <c r="B65" t="s">
-        <v>192</v>
+        <v>55609278</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>385</v>
       </c>
       <c r="C65" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="H65" t="s">
         <v>95</v>
@@ -3657,13 +3733,13 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>75077119</v>
-      </c>
-      <c r="B66" t="s">
-        <v>602</v>
+        <v>71042279</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>569</v>
       </c>
       <c r="C66" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="H66" t="s">
         <v>95</v>
@@ -3677,13 +3753,13 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>52270898</v>
+        <v>67630646</v>
       </c>
       <c r="B67" t="s">
-        <v>357</v>
+        <v>527</v>
       </c>
       <c r="C67" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="H67" t="s">
         <v>99</v>
@@ -3697,13 +3773,13 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>65933937</v>
+        <v>64971361</v>
       </c>
       <c r="B68" t="s">
-        <v>500</v>
+        <v>487</v>
       </c>
       <c r="C68" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="H68" t="s">
         <v>99</v>
@@ -3717,13 +3793,13 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>53583387</v>
+        <v>62421723</v>
       </c>
       <c r="B69" t="s">
-        <v>373</v>
+        <v>455</v>
       </c>
       <c r="C69" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="H69" t="s">
         <v>99</v>
@@ -3736,6 +3812,15 @@
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>62374813</v>
+      </c>
+      <c r="B70" t="s">
+        <v>456</v>
+      </c>
+      <c r="C70" t="s">
+        <v>643</v>
+      </c>
       <c r="H70" t="s">
         <v>99</v>
       </c>
@@ -3747,6 +3832,15 @@
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <v>68462854</v>
+      </c>
+      <c r="B71" t="s">
+        <v>533</v>
+      </c>
+      <c r="C71" t="s">
+        <v>643</v>
+      </c>
       <c r="H71" t="s">
         <v>99</v>
       </c>
@@ -3758,6 +3852,15 @@
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <v>64114088</v>
+      </c>
+      <c r="B72" t="s">
+        <v>470</v>
+      </c>
+      <c r="C72" t="s">
+        <v>643</v>
+      </c>
       <c r="H72" t="s">
         <v>99</v>
       </c>
@@ -3769,6 +3872,15 @@
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <v>19213859</v>
+      </c>
+      <c r="B73" t="s">
+        <v>35</v>
+      </c>
+      <c r="C73" t="s">
+        <v>643</v>
+      </c>
       <c r="H73" t="s">
         <v>99</v>
       </c>
@@ -3780,6 +3892,15 @@
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>13004238</v>
+      </c>
+      <c r="B74" t="s">
+        <v>37</v>
+      </c>
+      <c r="C74" t="s">
+        <v>643</v>
+      </c>
       <c r="H74" t="s">
         <v>99</v>
       </c>
@@ -9607,8 +9728,208 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C1" xr:uid="{A6FE7512-3857-453D-8560-A4BD3D2FAE16}">
+    <sortState ref="A2:C74">
+      <sortCondition descending="1" ref="C1"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="A1:A73 A78:A1048576">
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADA1740B-2D70-4413-85EC-C8ECA18DA9CB}">
+  <dimension ref="A13:C27"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="13" spans="1:3" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <v>13101217</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>4125377</v>
+      </c>
+      <c r="B15" t="s">
+        <v>203</v>
+      </c>
+      <c r="C15" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>26426530</v>
+      </c>
+      <c r="B16" t="s">
+        <v>204</v>
+      </c>
+      <c r="C16" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>43252471</v>
+      </c>
+      <c r="B17" t="s">
+        <v>192</v>
+      </c>
+      <c r="C17" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>64789478</v>
+      </c>
+      <c r="B18" t="s">
+        <v>485</v>
+      </c>
+      <c r="C18" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>71030052</v>
+      </c>
+      <c r="B19" t="s">
+        <v>564</v>
+      </c>
+      <c r="C19" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>11229298</v>
+      </c>
+      <c r="B20" t="s">
+        <v>175</v>
+      </c>
+      <c r="C20" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>75077119</v>
+      </c>
+      <c r="B21" t="s">
+        <v>602</v>
+      </c>
+      <c r="C21" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>42519088</v>
+      </c>
+      <c r="B22" t="s">
+        <v>328</v>
+      </c>
+      <c r="C22" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>17579394</v>
+      </c>
+      <c r="B23" t="s">
+        <v>329</v>
+      </c>
+      <c r="C23" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>53569741</v>
+      </c>
+      <c r="B24" t="s">
+        <v>375</v>
+      </c>
+      <c r="C24" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>53583387</v>
+      </c>
+      <c r="B25" t="s">
+        <v>373</v>
+      </c>
+      <c r="C25" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>12439390</v>
+      </c>
+      <c r="B26" t="s">
+        <v>206</v>
+      </c>
+      <c r="C26" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>14107560</v>
+      </c>
+      <c r="B27" t="s">
+        <v>195</v>
+      </c>
+      <c r="C27" t="s">
+        <v>651</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A13:C13" xr:uid="{117D3307-ACCB-47D2-B6C5-649AA920507F}">
+    <sortState ref="A14:C25">
+      <sortCondition descending="1" ref="C13"/>
+    </sortState>
+  </autoFilter>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="A26:A27 A14:A24">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A25">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/이슈제품.xlsx
+++ b/data/이슈제품.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OA\Desktop\쿠팡업로드\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B8D548-1721-40EA-B84A-FB3A85BCD34F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$13:$C$13</definedName>
   </definedNames>
-  <calcPr calcId="179021"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -30,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1377" uniqueCount="656">
   <si>
     <t>오아디머무드등-화이트</t>
   </si>
@@ -1927,10 +1926,6 @@
   </si>
   <si>
     <t>입고X, 11/17 생산완료</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>입고X, 10월 초 예정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2034,7 +2029,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2417,7 +2412,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J603"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2479,7 +2474,7 @@
         <v>357</v>
       </c>
       <c r="C3" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H3" t="s">
         <v>30</v>
@@ -2499,7 +2494,7 @@
         <v>223</v>
       </c>
       <c r="C4" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H4" t="s">
         <v>30</v>
@@ -2536,7 +2531,7 @@
         <v>68880617</v>
       </c>
       <c r="B6" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C6" t="s">
         <v>627</v>
@@ -2559,7 +2554,7 @@
         <v>345</v>
       </c>
       <c r="C7" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H7" t="s">
         <v>30</v>
@@ -2579,7 +2574,7 @@
         <v>175</v>
       </c>
       <c r="C8" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H8" t="s">
         <v>30</v>
@@ -2619,7 +2614,7 @@
         <v>500</v>
       </c>
       <c r="C10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H10" t="s">
         <v>30</v>
@@ -2733,10 +2728,10 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>60542212</v>
+        <v>15414324</v>
       </c>
       <c r="B16" t="s">
-        <v>438</v>
+        <v>199</v>
       </c>
       <c r="C16" t="s">
         <v>631</v>
@@ -2753,13 +2748,13 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>15414324</v>
+        <v>12439390</v>
       </c>
       <c r="B17" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C17" t="s">
-        <v>632</v>
+        <v>651</v>
       </c>
       <c r="H17" t="s">
         <v>30</v>
@@ -2773,13 +2768,13 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>12439390</v>
+        <v>14107560</v>
       </c>
       <c r="B18" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="C18" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="H18" t="s">
         <v>30</v>
@@ -2793,13 +2788,13 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>14107560</v>
+        <v>17579394</v>
       </c>
       <c r="B19" t="s">
-        <v>195</v>
+        <v>329</v>
       </c>
       <c r="C19" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="H19" t="s">
         <v>30</v>
@@ -2813,13 +2808,13 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>17579394</v>
+        <v>53569741</v>
       </c>
       <c r="B20" t="s">
-        <v>329</v>
+        <v>375</v>
       </c>
       <c r="C20" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H20" t="s">
         <v>30</v>
@@ -2833,13 +2828,13 @@
     </row>
     <row r="21" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>53569741</v>
+        <v>75077119</v>
       </c>
       <c r="B21" t="s">
-        <v>375</v>
+        <v>602</v>
       </c>
       <c r="C21" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>30</v>
@@ -2853,13 +2848,13 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>75077119</v>
+        <v>53583387</v>
       </c>
       <c r="B22" t="s">
-        <v>602</v>
+        <v>373</v>
       </c>
       <c r="C22" t="s">
-        <v>656</v>
+        <v>644</v>
       </c>
       <c r="H22" t="s">
         <v>30</v>
@@ -2873,13 +2868,13 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>42519088</v>
-      </c>
-      <c r="B23" t="s">
-        <v>328</v>
+        <v>51623281</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>634</v>
       </c>
       <c r="C23" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="H23" t="s">
         <v>30</v>
@@ -2893,13 +2888,13 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>4125377</v>
-      </c>
-      <c r="B24" t="s">
-        <v>203</v>
+        <v>51989601</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>635</v>
       </c>
       <c r="C24" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
       <c r="H24" t="s">
         <v>30</v>
@@ -2913,13 +2908,13 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>26426530</v>
-      </c>
-      <c r="B25" t="s">
-        <v>204</v>
+        <v>11192166</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>167</v>
       </c>
       <c r="C25" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
       <c r="H25" t="s">
         <v>30</v>
@@ -2933,13 +2928,13 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>43252471</v>
-      </c>
-      <c r="B26" t="s">
-        <v>192</v>
+        <v>15812678</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>146</v>
       </c>
       <c r="C26" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
       <c r="H26" t="s">
         <v>30</v>
@@ -2953,13 +2948,13 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>64789478</v>
-      </c>
-      <c r="B27" t="s">
-        <v>485</v>
+        <v>12091621</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>143</v>
       </c>
       <c r="C27" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
       <c r="H27" t="s">
         <v>30</v>
@@ -2973,13 +2968,13 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>71030052</v>
-      </c>
-      <c r="B28" t="s">
-        <v>564</v>
+        <v>12143584</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="C28" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
       <c r="H28" t="s">
         <v>30</v>
@@ -2992,14 +2987,14 @@
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" s="3">
-        <v>13101217</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>647</v>
+      <c r="A29">
+        <v>11192167</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C29" t="s">
+        <v>636</v>
       </c>
       <c r="H29" t="s">
         <v>57</v>
@@ -3013,13 +3008,13 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>53583387</v>
-      </c>
-      <c r="B30" t="s">
-        <v>373</v>
+        <v>12143581</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>147</v>
       </c>
       <c r="C30" t="s">
-        <v>645</v>
+        <v>636</v>
       </c>
       <c r="H30" t="s">
         <v>59</v>
@@ -3033,13 +3028,13 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>51623281</v>
+        <v>11192165</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>635</v>
+        <v>148</v>
       </c>
       <c r="C31" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H31" t="s">
         <v>59</v>
@@ -3053,13 +3048,13 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>51989601</v>
+        <v>11192163</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C32" t="s">
         <v>636</v>
-      </c>
-      <c r="C32" t="s">
-        <v>637</v>
       </c>
       <c r="H32" t="s">
         <v>59</v>
@@ -3073,13 +3068,13 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>11192166</v>
+        <v>11291291</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="C33" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H33" t="s">
         <v>59</v>
@@ -3093,13 +3088,13 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>15812678</v>
+        <v>16171214</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="C34" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H34" t="s">
         <v>59</v>
@@ -3113,13 +3108,13 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>12091621</v>
+        <v>12218847</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="C35" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H35" t="s">
         <v>59</v>
@@ -3133,13 +3128,13 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>12143584</v>
+        <v>15838517</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C36" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H36" t="s">
         <v>59</v>
@@ -3153,13 +3148,13 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>11192167</v>
+        <v>12673238</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C37" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H37" t="s">
         <v>59</v>
@@ -3173,13 +3168,13 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>12143581</v>
+        <v>37790051</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="C38" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H38" t="s">
         <v>59</v>
@@ -3193,13 +3188,13 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>11192165</v>
+        <v>37594934</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="C39" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H39" t="s">
         <v>59</v>
@@ -3213,13 +3208,13 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>11192163</v>
+        <v>15702671</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>149</v>
+        <v>174</v>
       </c>
       <c r="C40" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H40" t="s">
         <v>59</v>
@@ -3233,13 +3228,13 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>11291291</v>
+        <v>39071990</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C41" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H41" t="s">
         <v>59</v>
@@ -3253,13 +3248,13 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>16171214</v>
+        <v>52204284</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>156</v>
+        <v>92</v>
       </c>
       <c r="C42" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H42" t="s">
         <v>59</v>
@@ -3273,13 +3268,13 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>12218847</v>
+        <v>39006854</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="C43" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H43" t="s">
         <v>59</v>
@@ -3293,13 +3288,13 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>15838517</v>
+        <v>39006857</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="C44" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H44" t="s">
         <v>59</v>
@@ -3313,13 +3308,13 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>12673238</v>
+        <v>39006855</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="C45" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H45" t="s">
         <v>59</v>
@@ -3333,13 +3328,13 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>37790051</v>
+        <v>51883980</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>160</v>
+        <v>362</v>
       </c>
       <c r="C46" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H46" t="s">
         <v>59</v>
@@ -3353,13 +3348,13 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>37594934</v>
+        <v>52578670</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>168</v>
+        <v>367</v>
       </c>
       <c r="C47" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H47" t="s">
         <v>59</v>
@@ -3373,13 +3368,13 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>15702671</v>
+        <v>52155531</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>174</v>
+        <v>94</v>
       </c>
       <c r="C48" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H48" t="s">
         <v>59</v>
@@ -3393,13 +3388,13 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>39071990</v>
+        <v>15831347</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="C49" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H49" t="s">
         <v>59</v>
@@ -3413,13 +3408,13 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>52204284</v>
+        <v>32548061</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>92</v>
+        <v>169</v>
       </c>
       <c r="C50" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H50" t="s">
         <v>59</v>
@@ -3433,13 +3428,13 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>39006854</v>
+        <v>35876282</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="C51" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H51" t="s">
         <v>59</v>
@@ -3453,13 +3448,13 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>39006857</v>
+        <v>16805855</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="C52" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H52" t="s">
         <v>59</v>
@@ -3473,13 +3468,13 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>39006855</v>
+        <v>55381383</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>163</v>
+        <v>384</v>
       </c>
       <c r="C53" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H53" t="s">
         <v>59</v>
@@ -3493,13 +3488,13 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>51883980</v>
+        <v>55449180</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>362</v>
+        <v>386</v>
       </c>
       <c r="C54" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H54" t="s">
         <v>59</v>
@@ -3513,13 +3508,13 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>52578670</v>
+        <v>55384739</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>367</v>
+        <v>388</v>
       </c>
       <c r="C55" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H55" t="s">
         <v>59</v>
@@ -3533,13 +3528,13 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>52155531</v>
+        <v>55389336</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>94</v>
+        <v>633</v>
       </c>
       <c r="C56" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H56" t="s">
         <v>59</v>
@@ -3553,13 +3548,13 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>15831347</v>
+        <v>55609278</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>142</v>
+        <v>385</v>
       </c>
       <c r="C57" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H57" t="s">
         <v>59</v>
@@ -3573,10 +3568,10 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>32548061</v>
+        <v>71042279</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>169</v>
+        <v>569</v>
       </c>
       <c r="C58" t="s">
         <v>637</v>
@@ -3593,13 +3588,13 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>35876282</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>173</v>
+        <v>67630646</v>
+      </c>
+      <c r="B59" t="s">
+        <v>527</v>
       </c>
       <c r="C59" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="H59" t="s">
         <v>59</v>
@@ -3613,13 +3608,13 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>16805855</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>145</v>
+        <v>64971361</v>
+      </c>
+      <c r="B60" t="s">
+        <v>487</v>
       </c>
       <c r="C60" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="H60" t="s">
         <v>59</v>
@@ -3633,13 +3628,13 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>55381383</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>384</v>
+        <v>62421723</v>
+      </c>
+      <c r="B61" t="s">
+        <v>455</v>
       </c>
       <c r="C61" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="H61" t="s">
         <v>59</v>
@@ -3653,13 +3648,13 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>55449180</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>386</v>
+        <v>62374813</v>
+      </c>
+      <c r="B62" t="s">
+        <v>456</v>
       </c>
       <c r="C62" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="H62" t="s">
         <v>91</v>
@@ -3673,13 +3668,13 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>55384739</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>388</v>
+        <v>68462854</v>
+      </c>
+      <c r="B63" t="s">
+        <v>533</v>
       </c>
       <c r="C63" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="H63" t="s">
         <v>93</v>
@@ -3693,13 +3688,13 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>55389336</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>634</v>
+        <v>64114088</v>
+      </c>
+      <c r="B64" t="s">
+        <v>470</v>
       </c>
       <c r="C64" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="H64" t="s">
         <v>95</v>
@@ -3713,13 +3708,13 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>55609278</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>385</v>
+        <v>19213859</v>
+      </c>
+      <c r="B65" t="s">
+        <v>35</v>
       </c>
       <c r="C65" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="H65" t="s">
         <v>95</v>
@@ -3733,13 +3728,13 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>71042279</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>569</v>
+        <v>13004238</v>
+      </c>
+      <c r="B66" t="s">
+        <v>37</v>
       </c>
       <c r="C66" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="H66" t="s">
         <v>95</v>
@@ -3752,15 +3747,6 @@
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A67">
-        <v>67630646</v>
-      </c>
-      <c r="B67" t="s">
-        <v>527</v>
-      </c>
-      <c r="C67" t="s">
-        <v>643</v>
-      </c>
       <c r="H67" t="s">
         <v>99</v>
       </c>
@@ -3772,15 +3758,6 @@
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A68">
-        <v>64971361</v>
-      </c>
-      <c r="B68" t="s">
-        <v>487</v>
-      </c>
-      <c r="C68" t="s">
-        <v>643</v>
-      </c>
       <c r="H68" t="s">
         <v>99</v>
       </c>
@@ -3792,15 +3769,6 @@
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A69">
-        <v>62421723</v>
-      </c>
-      <c r="B69" t="s">
-        <v>455</v>
-      </c>
-      <c r="C69" t="s">
-        <v>643</v>
-      </c>
       <c r="H69" t="s">
         <v>99</v>
       </c>
@@ -3812,15 +3780,6 @@
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A70">
-        <v>62374813</v>
-      </c>
-      <c r="B70" t="s">
-        <v>456</v>
-      </c>
-      <c r="C70" t="s">
-        <v>643</v>
-      </c>
       <c r="H70" t="s">
         <v>99</v>
       </c>
@@ -3832,15 +3791,6 @@
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A71">
-        <v>68462854</v>
-      </c>
-      <c r="B71" t="s">
-        <v>533</v>
-      </c>
-      <c r="C71" t="s">
-        <v>643</v>
-      </c>
       <c r="H71" t="s">
         <v>99</v>
       </c>
@@ -3852,15 +3802,6 @@
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A72">
-        <v>64114088</v>
-      </c>
-      <c r="B72" t="s">
-        <v>470</v>
-      </c>
-      <c r="C72" t="s">
-        <v>643</v>
-      </c>
       <c r="H72" t="s">
         <v>99</v>
       </c>
@@ -3872,15 +3813,6 @@
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A73">
-        <v>19213859</v>
-      </c>
-      <c r="B73" t="s">
-        <v>35</v>
-      </c>
-      <c r="C73" t="s">
-        <v>643</v>
-      </c>
       <c r="H73" t="s">
         <v>99</v>
       </c>
@@ -3892,15 +3824,6 @@
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A74">
-        <v>13004238</v>
-      </c>
-      <c r="B74" t="s">
-        <v>37</v>
-      </c>
-      <c r="C74" t="s">
-        <v>643</v>
-      </c>
       <c r="H74" t="s">
         <v>99</v>
       </c>
@@ -9728,13 +9651,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C1" xr:uid="{A6FE7512-3857-453D-8560-A4BD3D2FAE16}">
+  <autoFilter ref="A1:C1">
     <sortState ref="A2:C74">
       <sortCondition descending="1" ref="C1"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:A73 A78:A1048576">
+  <conditionalFormatting sqref="A70:A1048576 A1:A65">
     <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9743,7 +9666,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADA1740B-2D70-4413-85EC-C8ECA18DA9CB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A13:C27"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -9754,13 +9677,13 @@
   <sheetData>
     <row r="13" spans="1:3" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>653</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="C13" s="4" t="s">
         <v>654</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -9771,7 +9694,7 @@
         <v>71</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -9782,7 +9705,7 @@
         <v>203</v>
       </c>
       <c r="C15" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -9793,7 +9716,7 @@
         <v>204</v>
       </c>
       <c r="C16" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -9804,7 +9727,7 @@
         <v>192</v>
       </c>
       <c r="C17" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -9815,7 +9738,7 @@
         <v>485</v>
       </c>
       <c r="C18" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -9826,7 +9749,7 @@
         <v>564</v>
       </c>
       <c r="C19" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -9837,7 +9760,7 @@
         <v>175</v>
       </c>
       <c r="C20" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
@@ -9848,7 +9771,7 @@
         <v>602</v>
       </c>
       <c r="C21" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -9859,7 +9782,7 @@
         <v>328</v>
       </c>
       <c r="C22" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -9870,7 +9793,7 @@
         <v>329</v>
       </c>
       <c r="C23" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -9881,7 +9804,7 @@
         <v>375</v>
       </c>
       <c r="C24" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -9892,7 +9815,7 @@
         <v>373</v>
       </c>
       <c r="C25" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -9903,7 +9826,7 @@
         <v>206</v>
       </c>
       <c r="C26" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -9914,11 +9837,11 @@
         <v>195</v>
       </c>
       <c r="C27" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A13:C13" xr:uid="{117D3307-ACCB-47D2-B6C5-649AA920507F}">
+  <autoFilter ref="A13:C13">
     <sortState ref="A14:C25">
       <sortCondition descending="1" ref="C13"/>
     </sortState>

--- a/data/이슈제품.xlsx
+++ b/data/이슈제품.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1377" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1375" uniqueCount="656">
   <si>
     <t>오아디머무드등-화이트</t>
   </si>
@@ -2568,13 +2568,13 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>11229298</v>
+        <v>58505144</v>
       </c>
       <c r="B8" t="s">
-        <v>175</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>648</v>
+        <v>17</v>
       </c>
       <c r="H8" t="s">
         <v>30</v>
@@ -2588,13 +2588,13 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>58505144</v>
+        <v>65933937</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>500</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>643</v>
       </c>
       <c r="H9" t="s">
         <v>30</v>
@@ -2608,13 +2608,13 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>65933937</v>
+        <v>76375597</v>
       </c>
       <c r="B10" t="s">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>643</v>
+        <v>23</v>
       </c>
       <c r="H10" t="s">
         <v>30</v>
@@ -2628,13 +2628,13 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>76375597</v>
+        <v>60015061</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="H11" t="s">
         <v>30</v>
@@ -2648,13 +2648,13 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>60015061</v>
+        <v>50725354</v>
       </c>
       <c r="B12" t="s">
-        <v>5</v>
+        <v>208</v>
       </c>
       <c r="C12" t="s">
-        <v>1</v>
+        <v>626</v>
       </c>
       <c r="H12" t="s">
         <v>30</v>
@@ -2668,13 +2668,13 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>50725354</v>
+        <v>50153946</v>
       </c>
       <c r="B13" t="s">
-        <v>208</v>
+        <v>115</v>
       </c>
       <c r="C13" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="H13" t="s">
         <v>30</v>
@@ -2688,13 +2688,13 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>50153946</v>
+        <v>75741354</v>
       </c>
       <c r="B14" t="s">
-        <v>115</v>
+        <v>605</v>
       </c>
       <c r="C14" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="H14" t="s">
         <v>30</v>
@@ -2708,13 +2708,13 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>75741354</v>
+        <v>15414324</v>
       </c>
       <c r="B15" t="s">
-        <v>605</v>
+        <v>199</v>
       </c>
       <c r="C15" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="H15" t="s">
         <v>30</v>
@@ -2728,13 +2728,13 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>15414324</v>
+        <v>12439390</v>
       </c>
       <c r="B16" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C16" t="s">
-        <v>631</v>
+        <v>651</v>
       </c>
       <c r="H16" t="s">
         <v>30</v>
@@ -2748,13 +2748,13 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>12439390</v>
+        <v>14107560</v>
       </c>
       <c r="B17" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="C17" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H17" t="s">
         <v>30</v>
@@ -2768,13 +2768,13 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>14107560</v>
+        <v>17579394</v>
       </c>
       <c r="B18" t="s">
-        <v>195</v>
+        <v>329</v>
       </c>
       <c r="C18" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H18" t="s">
         <v>30</v>
@@ -2788,10 +2788,10 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>17579394</v>
+        <v>53569741</v>
       </c>
       <c r="B19" t="s">
-        <v>329</v>
+        <v>375</v>
       </c>
       <c r="C19" t="s">
         <v>649</v>
@@ -2808,13 +2808,13 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>53569741</v>
+        <v>75077119</v>
       </c>
       <c r="B20" t="s">
-        <v>375</v>
+        <v>602</v>
       </c>
       <c r="C20" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="H20" t="s">
         <v>30</v>
@@ -2828,13 +2828,13 @@
     </row>
     <row r="21" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>75077119</v>
+        <v>53583387</v>
       </c>
       <c r="B21" t="s">
-        <v>602</v>
+        <v>373</v>
       </c>
       <c r="C21" t="s">
-        <v>655</v>
+        <v>644</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>30</v>
@@ -2848,13 +2848,13 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>53583387</v>
-      </c>
-      <c r="B22" t="s">
-        <v>373</v>
+        <v>51623281</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>634</v>
       </c>
       <c r="C22" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="H22" t="s">
         <v>30</v>
@@ -2868,10 +2868,10 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>51623281</v>
+        <v>51989601</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C23" t="s">
         <v>636</v>
@@ -2888,10 +2888,10 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>51989601</v>
+        <v>11192166</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>635</v>
+        <v>167</v>
       </c>
       <c r="C24" t="s">
         <v>636</v>
@@ -2908,10 +2908,10 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>11192166</v>
+        <v>15812678</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="C25" t="s">
         <v>636</v>
@@ -2928,10 +2928,10 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>15812678</v>
+        <v>12091621</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C26" t="s">
         <v>636</v>
@@ -2948,10 +2948,10 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>12091621</v>
+        <v>12143584</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C27" t="s">
         <v>636</v>
@@ -2968,10 +2968,10 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>12143584</v>
+        <v>11192167</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C28" t="s">
         <v>636</v>
@@ -2988,10 +2988,10 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>11192167</v>
+        <v>12143581</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C29" t="s">
         <v>636</v>
@@ -3008,10 +3008,10 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>12143581</v>
+        <v>11192165</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C30" t="s">
         <v>636</v>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>11192165</v>
+        <v>11192163</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C31" t="s">
         <v>636</v>
@@ -3048,10 +3048,10 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>11192163</v>
+        <v>11291291</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="C32" t="s">
         <v>636</v>
@@ -3068,10 +3068,10 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>11291291</v>
+        <v>16171214</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C33" t="s">
         <v>636</v>
@@ -3088,10 +3088,10 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>16171214</v>
+        <v>12218847</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C34" t="s">
         <v>636</v>
@@ -3108,10 +3108,10 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>12218847</v>
+        <v>15838517</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C35" t="s">
         <v>636</v>
@@ -3128,10 +3128,10 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>15838517</v>
+        <v>12673238</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C36" t="s">
         <v>636</v>
@@ -3148,10 +3148,10 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>12673238</v>
+        <v>37790051</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="C37" t="s">
         <v>636</v>
@@ -3168,10 +3168,10 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>37790051</v>
+        <v>37594934</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="C38" t="s">
         <v>636</v>
@@ -3188,10 +3188,10 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>37594934</v>
+        <v>15702671</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C39" t="s">
         <v>636</v>
@@ -3208,10 +3208,10 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>15702671</v>
+        <v>39071990</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="C40" t="s">
         <v>636</v>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>39071990</v>
+        <v>52204284</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>161</v>
+        <v>92</v>
       </c>
       <c r="C41" t="s">
         <v>636</v>
@@ -3248,10 +3248,10 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>52204284</v>
+        <v>39006854</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>92</v>
+        <v>164</v>
       </c>
       <c r="C42" t="s">
         <v>636</v>
@@ -3268,10 +3268,10 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>39006854</v>
+        <v>39006857</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C43" t="s">
         <v>636</v>
@@ -3288,10 +3288,10 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>39006857</v>
+        <v>39006855</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C44" t="s">
         <v>636</v>
@@ -3308,10 +3308,10 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>39006855</v>
+        <v>51883980</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>163</v>
+        <v>362</v>
       </c>
       <c r="C45" t="s">
         <v>636</v>
@@ -3328,10 +3328,10 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>51883980</v>
+        <v>52578670</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="C46" t="s">
         <v>636</v>
@@ -3348,10 +3348,10 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>52578670</v>
+        <v>52155531</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>367</v>
+        <v>94</v>
       </c>
       <c r="C47" t="s">
         <v>636</v>
@@ -3368,10 +3368,10 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>52155531</v>
+        <v>15831347</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>94</v>
+        <v>142</v>
       </c>
       <c r="C48" t="s">
         <v>636</v>
@@ -3388,10 +3388,10 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>15831347</v>
+        <v>32548061</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>142</v>
+        <v>169</v>
       </c>
       <c r="C49" t="s">
         <v>636</v>
@@ -3408,10 +3408,10 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>32548061</v>
+        <v>35876282</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C50" t="s">
         <v>636</v>
@@ -3428,10 +3428,10 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>35876282</v>
+        <v>16805855</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>173</v>
+        <v>145</v>
       </c>
       <c r="C51" t="s">
         <v>636</v>
@@ -3448,10 +3448,10 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>16805855</v>
+        <v>55381383</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>145</v>
+        <v>384</v>
       </c>
       <c r="C52" t="s">
         <v>636</v>
@@ -3468,10 +3468,10 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>55381383</v>
+        <v>55449180</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C53" t="s">
         <v>636</v>
@@ -3488,10 +3488,10 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>55449180</v>
+        <v>55384739</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C54" t="s">
         <v>636</v>
@@ -3508,10 +3508,10 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>55384739</v>
+        <v>55389336</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>388</v>
+        <v>633</v>
       </c>
       <c r="C55" t="s">
         <v>636</v>
@@ -3528,10 +3528,10 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>55389336</v>
+        <v>55609278</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>633</v>
+        <v>385</v>
       </c>
       <c r="C56" t="s">
         <v>636</v>
@@ -3548,13 +3548,13 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>55609278</v>
+        <v>71042279</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>385</v>
+        <v>569</v>
       </c>
       <c r="C57" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H57" t="s">
         <v>59</v>
@@ -3568,13 +3568,13 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>71042279</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>569</v>
+        <v>67630646</v>
+      </c>
+      <c r="B58" t="s">
+        <v>527</v>
       </c>
       <c r="C58" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="H58" t="s">
         <v>59</v>
@@ -3588,10 +3588,10 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>67630646</v>
+        <v>64971361</v>
       </c>
       <c r="B59" t="s">
-        <v>527</v>
+        <v>487</v>
       </c>
       <c r="C59" t="s">
         <v>642</v>
@@ -3608,10 +3608,10 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>64971361</v>
+        <v>62421723</v>
       </c>
       <c r="B60" t="s">
-        <v>487</v>
+        <v>455</v>
       </c>
       <c r="C60" t="s">
         <v>642</v>
@@ -3628,10 +3628,10 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>62421723</v>
+        <v>62374813</v>
       </c>
       <c r="B61" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C61" t="s">
         <v>642</v>
@@ -3648,10 +3648,10 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>62374813</v>
+        <v>68462854</v>
       </c>
       <c r="B62" t="s">
-        <v>456</v>
+        <v>533</v>
       </c>
       <c r="C62" t="s">
         <v>642</v>
@@ -3668,10 +3668,10 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>68462854</v>
+        <v>64114088</v>
       </c>
       <c r="B63" t="s">
-        <v>533</v>
+        <v>470</v>
       </c>
       <c r="C63" t="s">
         <v>642</v>
@@ -3688,10 +3688,10 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>64114088</v>
+        <v>19213859</v>
       </c>
       <c r="B64" t="s">
-        <v>470</v>
+        <v>35</v>
       </c>
       <c r="C64" t="s">
         <v>642</v>
@@ -3708,10 +3708,10 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>19213859</v>
+        <v>13004238</v>
       </c>
       <c r="B65" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C65" t="s">
         <v>642</v>
@@ -3727,15 +3727,6 @@
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A66">
-        <v>13004238</v>
-      </c>
-      <c r="B66" t="s">
-        <v>37</v>
-      </c>
-      <c r="C66" t="s">
-        <v>642</v>
-      </c>
       <c r="H66" t="s">
         <v>95</v>
       </c>
@@ -9657,7 +9648,7 @@
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A70:A1048576 A1:A65">
+  <conditionalFormatting sqref="A69:A1048576 A1:A64">
     <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/이슈제품.xlsx
+++ b/data/이슈제품.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OA\Desktop\쿠팡업로드\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BEE33D4B-2830-49AB-8324-35097E9ED2E7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1375" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1375" uniqueCount="657">
   <si>
     <t>오아디머무드등-화이트</t>
   </si>
@@ -1921,18 +1922,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>협의, 9/30 생산완료</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>입고X, 11/17 생산완료</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>입고X, 10월 중순 예정</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>오아넥스트레쳐S-베이지</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1966,10 +1959,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>협의, 11월초</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>광고OFF</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2023,13 +2012,29 @@
   </si>
   <si>
     <t>입고X, 11월 초</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입고X, 10/15 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>협의, 10/15 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>협의, 10/23 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입고X, 10/27 예정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2412,7 +2417,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J603"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2454,7 +2459,7 @@
         <v>330</v>
       </c>
       <c r="C2" t="s">
-        <v>629</v>
+        <v>655</v>
       </c>
       <c r="H2" t="s">
         <v>30</v>
@@ -2474,7 +2479,7 @@
         <v>357</v>
       </c>
       <c r="C3" t="s">
-        <v>641</v>
+        <v>654</v>
       </c>
       <c r="H3" t="s">
         <v>30</v>
@@ -2494,7 +2499,7 @@
         <v>223</v>
       </c>
       <c r="C4" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="H4" t="s">
         <v>30</v>
@@ -2531,7 +2536,7 @@
         <v>68880617</v>
       </c>
       <c r="B6" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C6" t="s">
         <v>627</v>
@@ -2554,7 +2559,7 @@
         <v>345</v>
       </c>
       <c r="C7" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="H7" t="s">
         <v>30</v>
@@ -2594,7 +2599,7 @@
         <v>500</v>
       </c>
       <c r="C9" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H9" t="s">
         <v>30</v>
@@ -2674,7 +2679,7 @@
         <v>115</v>
       </c>
       <c r="C13" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H13" t="s">
         <v>30</v>
@@ -2714,7 +2719,7 @@
         <v>199</v>
       </c>
       <c r="C15" t="s">
-        <v>631</v>
+        <v>656</v>
       </c>
       <c r="H15" t="s">
         <v>30</v>
@@ -2734,7 +2739,7 @@
         <v>206</v>
       </c>
       <c r="C16" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="H16" t="s">
         <v>30</v>
@@ -2754,7 +2759,7 @@
         <v>195</v>
       </c>
       <c r="C17" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="H17" t="s">
         <v>30</v>
@@ -2768,13 +2773,13 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>17579394</v>
+        <v>53569741</v>
       </c>
       <c r="B18" t="s">
-        <v>329</v>
+        <v>375</v>
       </c>
       <c r="C18" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="H18" t="s">
         <v>30</v>
@@ -2788,13 +2793,13 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>53569741</v>
+        <v>75077119</v>
       </c>
       <c r="B19" t="s">
-        <v>375</v>
+        <v>602</v>
       </c>
       <c r="C19" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="H19" t="s">
         <v>30</v>
@@ -2808,13 +2813,13 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>75077119</v>
+        <v>53583387</v>
       </c>
       <c r="B20" t="s">
-        <v>602</v>
+        <v>373</v>
       </c>
       <c r="C20" t="s">
-        <v>655</v>
+        <v>641</v>
       </c>
       <c r="H20" t="s">
         <v>30</v>
@@ -2828,13 +2833,13 @@
     </row>
     <row r="21" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>53583387</v>
-      </c>
-      <c r="B21" t="s">
-        <v>373</v>
+        <v>51623281</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>632</v>
       </c>
       <c r="C21" t="s">
-        <v>644</v>
+        <v>634</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>30</v>
@@ -2848,13 +2853,13 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>51623281</v>
+        <v>51989601</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="C22" t="s">
         <v>634</v>
-      </c>
-      <c r="C22" t="s">
-        <v>636</v>
       </c>
       <c r="H22" t="s">
         <v>30</v>
@@ -2868,13 +2873,13 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>51989601</v>
+        <v>11192166</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>635</v>
+        <v>167</v>
       </c>
       <c r="C23" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H23" t="s">
         <v>30</v>
@@ -2888,13 +2893,13 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>11192166</v>
+        <v>15812678</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="C24" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H24" t="s">
         <v>30</v>
@@ -2908,13 +2913,13 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>15812678</v>
+        <v>12091621</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C25" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H25" t="s">
         <v>30</v>
@@ -2928,13 +2933,13 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>12091621</v>
+        <v>12143584</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C26" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H26" t="s">
         <v>30</v>
@@ -2948,13 +2953,13 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>12143584</v>
+        <v>11192167</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C27" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H27" t="s">
         <v>30</v>
@@ -2968,13 +2973,13 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>11192167</v>
+        <v>12143581</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C28" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H28" t="s">
         <v>30</v>
@@ -2988,13 +2993,13 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>12143581</v>
+        <v>11192165</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C29" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H29" t="s">
         <v>57</v>
@@ -3008,13 +3013,13 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>11192165</v>
+        <v>11192163</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C30" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H30" t="s">
         <v>59</v>
@@ -3028,13 +3033,13 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>11192163</v>
+        <v>11291291</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="C31" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H31" t="s">
         <v>59</v>
@@ -3048,13 +3053,13 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>11291291</v>
+        <v>16171214</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C32" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H32" t="s">
         <v>59</v>
@@ -3068,13 +3073,13 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>16171214</v>
+        <v>12218847</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C33" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H33" t="s">
         <v>59</v>
@@ -3088,13 +3093,13 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>12218847</v>
+        <v>15838517</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C34" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H34" t="s">
         <v>59</v>
@@ -3108,13 +3113,13 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>15838517</v>
+        <v>12673238</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C35" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H35" t="s">
         <v>59</v>
@@ -3128,13 +3133,13 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>12673238</v>
+        <v>37790051</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="C36" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H36" t="s">
         <v>59</v>
@@ -3148,13 +3153,13 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>37790051</v>
+        <v>37594934</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="C37" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H37" t="s">
         <v>59</v>
@@ -3168,13 +3173,13 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>37594934</v>
+        <v>15702671</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C38" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H38" t="s">
         <v>59</v>
@@ -3188,13 +3193,13 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>15702671</v>
+        <v>39071990</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="C39" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H39" t="s">
         <v>59</v>
@@ -3208,13 +3213,13 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>39071990</v>
+        <v>52204284</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>161</v>
+        <v>92</v>
       </c>
       <c r="C40" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H40" t="s">
         <v>59</v>
@@ -3228,13 +3233,13 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>52204284</v>
+        <v>39006854</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>92</v>
+        <v>164</v>
       </c>
       <c r="C41" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H41" t="s">
         <v>59</v>
@@ -3248,13 +3253,13 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>39006854</v>
+        <v>39006857</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C42" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H42" t="s">
         <v>59</v>
@@ -3268,13 +3273,13 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>39006857</v>
+        <v>39006855</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C43" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H43" t="s">
         <v>59</v>
@@ -3288,13 +3293,13 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>39006855</v>
+        <v>51883980</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>163</v>
+        <v>362</v>
       </c>
       <c r="C44" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H44" t="s">
         <v>59</v>
@@ -3308,13 +3313,13 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>51883980</v>
+        <v>52578670</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="C45" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H45" t="s">
         <v>59</v>
@@ -3328,13 +3333,13 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>52578670</v>
+        <v>52155531</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>367</v>
+        <v>94</v>
       </c>
       <c r="C46" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H46" t="s">
         <v>59</v>
@@ -3348,13 +3353,13 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>52155531</v>
+        <v>15831347</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>94</v>
+        <v>142</v>
       </c>
       <c r="C47" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H47" t="s">
         <v>59</v>
@@ -3368,13 +3373,13 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>15831347</v>
+        <v>32548061</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>142</v>
+        <v>169</v>
       </c>
       <c r="C48" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H48" t="s">
         <v>59</v>
@@ -3388,13 +3393,13 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>32548061</v>
+        <v>35876282</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C49" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H49" t="s">
         <v>59</v>
@@ -3408,13 +3413,13 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>35876282</v>
+        <v>16805855</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>173</v>
+        <v>145</v>
       </c>
       <c r="C50" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H50" t="s">
         <v>59</v>
@@ -3428,13 +3433,13 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>16805855</v>
+        <v>55381383</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>145</v>
+        <v>384</v>
       </c>
       <c r="C51" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H51" t="s">
         <v>59</v>
@@ -3448,13 +3453,13 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>55381383</v>
+        <v>55449180</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C52" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H52" t="s">
         <v>59</v>
@@ -3468,13 +3473,13 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>55449180</v>
+        <v>55384739</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C53" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H53" t="s">
         <v>59</v>
@@ -3488,13 +3493,13 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>55384739</v>
+        <v>55389336</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>388</v>
+        <v>631</v>
       </c>
       <c r="C54" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H54" t="s">
         <v>59</v>
@@ -3508,13 +3513,13 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>55389336</v>
+        <v>55609278</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>633</v>
+        <v>385</v>
       </c>
       <c r="C55" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H55" t="s">
         <v>59</v>
@@ -3528,13 +3533,13 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>55609278</v>
+        <v>71042279</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>385</v>
+        <v>569</v>
       </c>
       <c r="C56" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H56" t="s">
         <v>59</v>
@@ -3548,13 +3553,13 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>71042279</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>569</v>
+        <v>67630646</v>
+      </c>
+      <c r="B57" t="s">
+        <v>527</v>
       </c>
       <c r="C57" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H57" t="s">
         <v>59</v>
@@ -3568,13 +3573,13 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>67630646</v>
+        <v>64971361</v>
       </c>
       <c r="B58" t="s">
-        <v>527</v>
+        <v>487</v>
       </c>
       <c r="C58" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="H58" t="s">
         <v>59</v>
@@ -3588,13 +3593,13 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>64971361</v>
+        <v>62421723</v>
       </c>
       <c r="B59" t="s">
-        <v>487</v>
+        <v>455</v>
       </c>
       <c r="C59" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="H59" t="s">
         <v>59</v>
@@ -3608,13 +3613,13 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>62421723</v>
+        <v>62374813</v>
       </c>
       <c r="B60" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C60" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="H60" t="s">
         <v>59</v>
@@ -3628,13 +3633,13 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>62374813</v>
+        <v>68462854</v>
       </c>
       <c r="B61" t="s">
-        <v>456</v>
+        <v>533</v>
       </c>
       <c r="C61" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="H61" t="s">
         <v>59</v>
@@ -3648,13 +3653,13 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>68462854</v>
+        <v>64114088</v>
       </c>
       <c r="B62" t="s">
-        <v>533</v>
+        <v>470</v>
       </c>
       <c r="C62" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="H62" t="s">
         <v>91</v>
@@ -3668,13 +3673,13 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>64114088</v>
+        <v>19213859</v>
       </c>
       <c r="B63" t="s">
-        <v>470</v>
+        <v>35</v>
       </c>
       <c r="C63" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="H63" t="s">
         <v>93</v>
@@ -3688,13 +3693,13 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>19213859</v>
+        <v>13004238</v>
       </c>
       <c r="B64" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C64" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="H64" t="s">
         <v>95</v>
@@ -3708,13 +3713,13 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>13004238</v>
+        <v>11229298</v>
       </c>
       <c r="B65" t="s">
-        <v>37</v>
+        <v>175</v>
       </c>
       <c r="C65" t="s">
-        <v>642</v>
+        <v>656</v>
       </c>
       <c r="H65" t="s">
         <v>95</v>
@@ -9642,14 +9647,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C1">
+  <autoFilter ref="A1:C1" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <sortState ref="A2:C74">
       <sortCondition descending="1" ref="C1"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A69:A1048576 A1:A64">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+  <conditionalFormatting sqref="A69:A1048576 A1:A63">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -9657,7 +9662,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A13:C27"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -9668,13 +9673,13 @@
   <sheetData>
     <row r="13" spans="1:3" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -9685,7 +9690,7 @@
         <v>71</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -9696,7 +9701,7 @@
         <v>203</v>
       </c>
       <c r="C15" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -9707,7 +9712,7 @@
         <v>204</v>
       </c>
       <c r="C16" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -9718,7 +9723,7 @@
         <v>192</v>
       </c>
       <c r="C17" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -9729,7 +9734,7 @@
         <v>485</v>
       </c>
       <c r="C18" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -9740,7 +9745,7 @@
         <v>564</v>
       </c>
       <c r="C19" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -9751,7 +9756,7 @@
         <v>175</v>
       </c>
       <c r="C20" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
     </row>
     <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
@@ -9762,7 +9767,7 @@
         <v>602</v>
       </c>
       <c r="C21" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -9773,7 +9778,7 @@
         <v>328</v>
       </c>
       <c r="C22" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -9784,7 +9789,7 @@
         <v>329</v>
       </c>
       <c r="C23" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -9795,7 +9800,7 @@
         <v>375</v>
       </c>
       <c r="C24" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -9806,7 +9811,7 @@
         <v>373</v>
       </c>
       <c r="C25" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -9817,7 +9822,7 @@
         <v>206</v>
       </c>
       <c r="C26" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -9828,21 +9833,21 @@
         <v>195</v>
       </c>
       <c r="C27" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A13:C13">
+  <autoFilter ref="A13:C13" xr:uid="{00000000-0009-0000-0000-000001000000}">
     <sortState ref="A14:C25">
       <sortCondition descending="1" ref="C13"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A26:A27 A14:A24">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A25">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/이슈제품.xlsx
+++ b/data/이슈제품.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OA\Desktop\쿠팡업로드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BEE33D4B-2830-49AB-8324-35097E9ED2E7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2723A068-3266-43C1-B5B7-A04256B16213}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -83,9 +83,6 @@
     <t>보아르터보스티머-아이보리</t>
   </si>
   <si>
-    <t>입고X, 특판출고</t>
-  </si>
-  <si>
     <t>오아턴에어탁상팬</t>
   </si>
   <si>
@@ -2028,6 +2025,11 @@
   </si>
   <si>
     <t>입고X, 10/27 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기존 전지 내 다른모델 리콜실시중으로 260922007 발주건부터 신규전지로 인증변경
+기존재고 약 5500개 소진후 변경</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2091,7 +2093,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2106,6 +2108,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2433,22 +2438,22 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" t="s">
         <v>24</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>25</v>
       </c>
-      <c r="C1" t="s">
+      <c r="H1" t="s">
         <v>26</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>27</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>28</v>
-      </c>
-      <c r="J1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -2456,19 +2461,19 @@
         <v>27056005</v>
       </c>
       <c r="B2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C2" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I2">
         <v>3636925</v>
       </c>
       <c r="J2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -2476,19 +2481,19 @@
         <v>52270898</v>
       </c>
       <c r="B3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C3" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I3">
         <v>3636926</v>
       </c>
       <c r="J3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -2496,19 +2501,19 @@
         <v>4152606</v>
       </c>
       <c r="B4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C4" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I4">
         <v>3636927</v>
       </c>
       <c r="J4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -2516,19 +2521,19 @@
         <v>12263239</v>
       </c>
       <c r="B5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C5" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I5">
         <v>39415252</v>
       </c>
       <c r="J5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -2536,19 +2541,19 @@
         <v>68880617</v>
       </c>
       <c r="B6" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I6">
         <v>19213859</v>
       </c>
       <c r="J6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -2556,213 +2561,213 @@
         <v>5332788</v>
       </c>
       <c r="B7" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C7" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I7">
         <v>20342327</v>
       </c>
       <c r="J7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>58505144</v>
+        <v>65933937</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>499</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>639</v>
       </c>
       <c r="H8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I8">
         <v>13004238</v>
       </c>
       <c r="J8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>65933937</v>
+        <v>76375597</v>
       </c>
       <c r="B9" t="s">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>640</v>
+        <v>22</v>
       </c>
       <c r="H9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I9">
         <v>20341619</v>
       </c>
       <c r="J9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>76375597</v>
+        <v>60015061</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I10">
         <v>11092035</v>
       </c>
       <c r="J10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>60015061</v>
+        <v>50725354</v>
       </c>
       <c r="B11" t="s">
-        <v>5</v>
+        <v>207</v>
       </c>
       <c r="C11" t="s">
-        <v>1</v>
+        <v>625</v>
       </c>
       <c r="H11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I11">
         <v>40852278</v>
       </c>
       <c r="J11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>50725354</v>
+        <v>50153946</v>
       </c>
       <c r="B12" t="s">
-        <v>208</v>
+        <v>114</v>
       </c>
       <c r="C12" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="H12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I12">
         <v>29266932</v>
       </c>
       <c r="J12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>50153946</v>
+        <v>75741354</v>
       </c>
       <c r="B13" t="s">
-        <v>115</v>
+        <v>604</v>
       </c>
       <c r="C13" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="H13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I13">
         <v>12586373</v>
       </c>
       <c r="J13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>75741354</v>
+        <v>15414324</v>
       </c>
       <c r="B14" t="s">
-        <v>605</v>
+        <v>198</v>
       </c>
       <c r="C14" t="s">
-        <v>628</v>
+        <v>655</v>
       </c>
       <c r="H14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I14">
         <v>11055651</v>
       </c>
       <c r="J14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>15414324</v>
+        <v>12439390</v>
       </c>
       <c r="B15" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="C15" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="H15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I15">
         <v>38659485</v>
       </c>
       <c r="J15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>12439390</v>
+        <v>14107560</v>
       </c>
       <c r="B16" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="C16" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="H16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I16">
         <v>9567647</v>
       </c>
       <c r="J16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>14107560</v>
+        <v>53569741</v>
       </c>
       <c r="B17" t="s">
-        <v>195</v>
+        <v>374</v>
       </c>
       <c r="C17" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="H17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I17">
         <v>40180424</v>
@@ -2773,1143 +2778,1143 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>53569741</v>
+        <v>75077119</v>
       </c>
       <c r="B18" t="s">
-        <v>375</v>
+        <v>601</v>
       </c>
       <c r="C18" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="H18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I18">
         <v>39228155</v>
       </c>
       <c r="J18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>75077119</v>
+        <v>53583387</v>
       </c>
       <c r="B19" t="s">
-        <v>602</v>
+        <v>372</v>
       </c>
       <c r="C19" t="s">
-        <v>652</v>
+        <v>640</v>
       </c>
       <c r="H19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I19">
         <v>38407975</v>
       </c>
       <c r="J19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>53583387</v>
-      </c>
-      <c r="B20" t="s">
-        <v>373</v>
+        <v>51623281</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>631</v>
       </c>
       <c r="C20" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="H20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I20">
         <v>38545387</v>
       </c>
       <c r="J20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>51623281</v>
+        <v>51989601</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>632</v>
       </c>
       <c r="C21" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I21" s="3">
         <v>18816827</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>51989601</v>
+        <v>11192166</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C22" t="s">
         <v>633</v>
       </c>
-      <c r="C22" t="s">
-        <v>634</v>
-      </c>
       <c r="H22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I22">
         <v>39278162</v>
       </c>
       <c r="J22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>11192166</v>
+        <v>15812678</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="C23" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I23">
         <v>13100374</v>
       </c>
       <c r="J23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>15812678</v>
+        <v>12091621</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C24" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I24">
         <v>10855225</v>
       </c>
       <c r="J24" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>12091621</v>
+        <v>12143584</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C25" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I25">
         <v>38490171</v>
       </c>
       <c r="J25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>12143584</v>
+        <v>11192167</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>150</v>
       </c>
       <c r="C26" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I26">
         <v>38490170</v>
       </c>
       <c r="J26" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>11192167</v>
+        <v>12143581</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C27" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I27">
         <v>38417027</v>
       </c>
       <c r="J27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>12143581</v>
+        <v>11192165</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>147</v>
       </c>
       <c r="C28" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I28">
         <v>13099542</v>
       </c>
       <c r="J28" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>11192165</v>
+        <v>11192163</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>148</v>
       </c>
       <c r="C29" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I29">
         <v>10324264</v>
       </c>
       <c r="J29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>11192163</v>
+        <v>11291291</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="C30" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H30" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I30">
         <v>39229235</v>
       </c>
       <c r="J30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>11291291</v>
+        <v>16171214</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C31" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I31">
         <v>12775098</v>
       </c>
       <c r="J31" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>16171214</v>
+        <v>12218847</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C32" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H32" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I32">
         <v>12775097</v>
       </c>
       <c r="J32" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>12218847</v>
+        <v>15838517</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C33" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H33" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I33">
         <v>12775096</v>
       </c>
       <c r="J33" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>15838517</v>
+        <v>12673238</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C34" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H34" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I34">
         <v>13151160</v>
       </c>
       <c r="J34" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>12673238</v>
+        <v>37790051</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="C35" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I35">
         <v>13151158</v>
       </c>
       <c r="J35" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>37790051</v>
+        <v>37594934</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="C36" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H36" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I36">
         <v>35403063</v>
       </c>
       <c r="J36" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>37594934</v>
+        <v>15702671</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C37" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H37" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I37">
         <v>13473750</v>
       </c>
       <c r="J37" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>15702671</v>
+        <v>39071990</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="C38" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I38">
         <v>17014694</v>
       </c>
       <c r="J38" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>39071990</v>
+        <v>52204284</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>161</v>
+        <v>91</v>
       </c>
       <c r="C39" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H39" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I39">
         <v>17014693</v>
       </c>
       <c r="J39" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>52204284</v>
+        <v>39006854</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>92</v>
+        <v>163</v>
       </c>
       <c r="C40" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H40" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I40">
         <v>13101218</v>
       </c>
       <c r="J40" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>39006854</v>
+        <v>39006857</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C41" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H41" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I41">
         <v>13101217</v>
       </c>
       <c r="J41" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>39006857</v>
+        <v>39006855</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>162</v>
       </c>
       <c r="C42" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H42" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I42">
         <v>16981939</v>
       </c>
       <c r="J42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>39006855</v>
+        <v>51883980</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>163</v>
+        <v>361</v>
       </c>
       <c r="C43" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I43">
         <v>12846219</v>
       </c>
       <c r="J43" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>51883980</v>
+        <v>52578670</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C44" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H44" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I44">
         <v>17398556</v>
       </c>
       <c r="J44" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>52578670</v>
+        <v>52155531</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>367</v>
+        <v>93</v>
       </c>
       <c r="C45" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H45" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I45">
         <v>16972627</v>
       </c>
       <c r="J45" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>52155531</v>
+        <v>15831347</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>94</v>
+        <v>141</v>
       </c>
       <c r="C46" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H46" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I46">
         <v>12846215</v>
       </c>
       <c r="J46" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>15831347</v>
+        <v>32548061</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="C47" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H47" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I47">
         <v>39663616</v>
       </c>
       <c r="J47" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>32548061</v>
+        <v>35876282</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C48" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H48" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I48">
         <v>37843037</v>
       </c>
       <c r="J48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>35876282</v>
+        <v>16805855</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>173</v>
+        <v>144</v>
       </c>
       <c r="C49" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I49">
         <v>12465755</v>
       </c>
       <c r="J49" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>16805855</v>
+        <v>55381383</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>145</v>
+        <v>383</v>
       </c>
       <c r="C50" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H50" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I50">
         <v>11671481</v>
       </c>
       <c r="J50" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>55381383</v>
+        <v>55449180</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C51" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H51" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I51">
         <v>12685386</v>
       </c>
       <c r="J51" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>55449180</v>
+        <v>55384739</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C52" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H52" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I52">
         <v>12674974</v>
       </c>
       <c r="J52" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>55384739</v>
+        <v>55389336</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>388</v>
+        <v>630</v>
       </c>
       <c r="C53" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H53" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I53">
         <v>12674973</v>
       </c>
       <c r="J53" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>55389336</v>
+        <v>55609278</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>631</v>
+        <v>384</v>
       </c>
       <c r="C54" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H54" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I54">
         <v>27515992</v>
       </c>
       <c r="J54" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>55609278</v>
+        <v>71042279</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>385</v>
+        <v>568</v>
       </c>
       <c r="C55" t="s">
         <v>634</v>
       </c>
       <c r="H55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I55">
         <v>18928667</v>
       </c>
       <c r="J55" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>71042279</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>569</v>
+        <v>67630646</v>
+      </c>
+      <c r="B56" t="s">
+        <v>526</v>
       </c>
       <c r="C56" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="H56" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I56">
         <v>14218803</v>
       </c>
       <c r="J56" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>67630646</v>
+        <v>64971361</v>
       </c>
       <c r="B57" t="s">
-        <v>527</v>
+        <v>486</v>
       </c>
       <c r="C57" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H57" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I57">
         <v>14218802</v>
       </c>
       <c r="J57" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>64971361</v>
+        <v>62421723</v>
       </c>
       <c r="B58" t="s">
-        <v>487</v>
+        <v>454</v>
       </c>
       <c r="C58" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H58" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I58">
         <v>14473529</v>
       </c>
       <c r="J58" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>62421723</v>
+        <v>62374813</v>
       </c>
       <c r="B59" t="s">
         <v>455</v>
       </c>
       <c r="C59" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H59" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I59">
         <v>25512595</v>
       </c>
       <c r="J59" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>62374813</v>
+        <v>68462854</v>
       </c>
       <c r="B60" t="s">
-        <v>456</v>
+        <v>532</v>
       </c>
       <c r="C60" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H60" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I60">
         <v>25433097</v>
       </c>
       <c r="J60" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>68462854</v>
+        <v>64114088</v>
       </c>
       <c r="B61" t="s">
-        <v>533</v>
+        <v>469</v>
       </c>
       <c r="C61" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H61" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I61">
         <v>50012601</v>
       </c>
       <c r="J61" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>64114088</v>
+        <v>19213859</v>
       </c>
       <c r="B62" t="s">
-        <v>470</v>
+        <v>34</v>
       </c>
       <c r="C62" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H62" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I62">
         <v>52204284</v>
       </c>
       <c r="J62" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>19213859</v>
+        <v>13004238</v>
       </c>
       <c r="B63" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C63" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H63" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I63">
         <v>52155531</v>
       </c>
       <c r="J63" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>13004238</v>
+        <v>11229298</v>
       </c>
       <c r="B64" t="s">
-        <v>37</v>
+        <v>174</v>
       </c>
       <c r="C64" t="s">
-        <v>639</v>
+        <v>655</v>
       </c>
       <c r="H64" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I64">
         <v>10814871</v>
       </c>
       <c r="J64" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>11229298</v>
+        <v>37161537</v>
       </c>
       <c r="B65" t="s">
-        <v>175</v>
-      </c>
-      <c r="C65" t="s">
+        <v>288</v>
+      </c>
+      <c r="C65" s="5" t="s">
         <v>656</v>
       </c>
       <c r="H65" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I65">
         <v>31792560</v>
       </c>
       <c r="J65" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H66" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I66">
         <v>10694343</v>
       </c>
       <c r="J66" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H67" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I67">
         <v>43431417</v>
       </c>
       <c r="J67" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H68" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I68">
         <v>10978754</v>
       </c>
       <c r="J68" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H69" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I69">
         <v>10974363</v>
       </c>
       <c r="J69" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H70" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I70">
         <v>39376011</v>
       </c>
       <c r="J70" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H71" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I71">
         <v>38310913</v>
       </c>
       <c r="J71" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H72" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I72">
         <v>40639939</v>
       </c>
       <c r="J72" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H73" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I73">
         <v>44581094</v>
       </c>
       <c r="J73" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H74" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I74">
         <v>39270777</v>
       </c>
       <c r="J74" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H75" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I75">
         <v>45342904</v>
       </c>
       <c r="J75" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H76" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I76">
         <v>19619417</v>
       </c>
       <c r="J76" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H77" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I77">
         <v>36606823</v>
       </c>
       <c r="J77" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H78" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I78">
         <v>12585217</v>
       </c>
       <c r="J78" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H79" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I79">
         <v>11511332</v>
       </c>
       <c r="J79" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H80" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I80">
         <v>12579597</v>
       </c>
       <c r="J80" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="81" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H81" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I81">
         <v>50153946</v>
       </c>
       <c r="J81" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="82" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H82" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I82">
         <v>50723598</v>
@@ -3920,40 +3925,40 @@
     </row>
     <row r="83" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H83" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I83">
         <v>34464589</v>
       </c>
       <c r="J83" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="84" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H84" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I84">
         <v>12029130</v>
       </c>
       <c r="J84" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="85" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H85" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I85">
         <v>46962408</v>
       </c>
       <c r="J85" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="86" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H86" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I86">
         <v>11874445</v>
@@ -3964,106 +3969,106 @@
     </row>
     <row r="87" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H87" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I87">
         <v>25665354</v>
       </c>
       <c r="J87" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="88" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H88" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I88">
         <v>46550390</v>
       </c>
       <c r="J88" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="89" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H89" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I89">
         <v>45573288</v>
       </c>
       <c r="J89" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="90" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H90" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I90">
         <v>34318450</v>
       </c>
       <c r="J90" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="91" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H91" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I91">
         <v>45701215</v>
       </c>
       <c r="J91" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="92" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H92" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I92">
         <v>15004955</v>
       </c>
       <c r="J92" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="93" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H93" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I93">
         <v>25321998</v>
       </c>
       <c r="J93" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="94" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H94" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I94">
         <v>25321996</v>
       </c>
       <c r="J94" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="95" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H95" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I95">
         <v>46191377</v>
       </c>
       <c r="J95" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="96" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H96" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I96">
         <v>45349063</v>
@@ -4074,568 +4079,568 @@
     </row>
     <row r="97" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H97" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I97">
         <v>44996967</v>
       </c>
       <c r="J97" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="98" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H98" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I98">
         <v>15462869</v>
       </c>
       <c r="J98" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="99" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H99" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I99">
         <v>15462868</v>
       </c>
       <c r="J99" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="100" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H100" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I100">
         <v>46671749</v>
       </c>
       <c r="J100" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="101" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H101" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I101">
         <v>35137369</v>
       </c>
       <c r="J101" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="102" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H102" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I102">
         <v>34320929</v>
       </c>
       <c r="J102" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="103" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H103" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I103">
         <v>34320928</v>
       </c>
       <c r="J103" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="104" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H104" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I104">
         <v>23200605</v>
       </c>
       <c r="J104" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="105" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H105" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I105">
         <v>23200603</v>
       </c>
       <c r="J105" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="106" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H106" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I106">
         <v>43571361</v>
       </c>
       <c r="J106" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="107" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H107" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I107">
         <v>43571360</v>
       </c>
       <c r="J107" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="108" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H108" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I108">
         <v>34330469</v>
       </c>
       <c r="J108" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="109" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H109" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I109">
         <v>34331612</v>
       </c>
       <c r="J109" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="110" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H110" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I110">
         <v>34352694</v>
       </c>
       <c r="J110" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="111" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H111" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I111">
         <v>39063227</v>
       </c>
       <c r="J111" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="112" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H112" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I112">
         <v>15831347</v>
       </c>
       <c r="J112" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="113" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H113" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I113">
         <v>12091621</v>
       </c>
       <c r="J113" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="114" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H114" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I114">
         <v>16805855</v>
       </c>
       <c r="J114" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="115" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H115" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I115">
         <v>15812678</v>
       </c>
       <c r="J115" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="116" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H116" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I116">
         <v>12143581</v>
       </c>
       <c r="J116" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="117" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H117" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I117">
         <v>11192165</v>
       </c>
       <c r="J117" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="118" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H118" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I118">
         <v>11192163</v>
       </c>
       <c r="J118" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="119" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H119" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I119">
         <v>12143584</v>
       </c>
       <c r="J119" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="120" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H120" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I120">
         <v>11192167</v>
       </c>
       <c r="J120" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="121" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H121" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I121">
         <v>12673238</v>
       </c>
       <c r="J121" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="122" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H122" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I122">
         <v>15838517</v>
       </c>
       <c r="J122" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="123" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H123" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I123">
         <v>12218847</v>
       </c>
       <c r="J123" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="124" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H124" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I124">
         <v>16171214</v>
       </c>
       <c r="J124" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="125" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H125" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I125">
         <v>11291291</v>
       </c>
       <c r="J125" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="126" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H126" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I126">
         <v>14134779</v>
       </c>
       <c r="J126" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="127" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H127" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I127">
         <v>14134778</v>
       </c>
       <c r="J127" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="128" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H128" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I128">
         <v>37790051</v>
       </c>
       <c r="J128" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="129" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H129" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I129">
         <v>39071990</v>
       </c>
       <c r="J129" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="130" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H130" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I130">
         <v>39006857</v>
       </c>
       <c r="J130" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="131" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H131" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I131">
         <v>39006855</v>
       </c>
       <c r="J131" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="132" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H132" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I132">
         <v>39006854</v>
       </c>
       <c r="J132" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="133" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H133" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I133">
         <v>12434130</v>
       </c>
       <c r="J133" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="134" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H134" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I134">
         <v>11671480</v>
       </c>
       <c r="J134" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="135" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H135" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I135">
         <v>11192166</v>
       </c>
       <c r="J135" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="136" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H136" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I136">
         <v>37594934</v>
       </c>
       <c r="J136" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="137" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H137" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I137">
         <v>32548061</v>
       </c>
       <c r="J137" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="138" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H138" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I138">
         <v>32711387</v>
       </c>
       <c r="J138" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="139" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H139" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I139">
         <v>32710937</v>
       </c>
       <c r="J139" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="140" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H140" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I140">
         <v>35876282</v>
       </c>
       <c r="J140" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="141" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H141" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I141">
         <v>15702671</v>
       </c>
       <c r="J141" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="142" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H142" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I142">
         <v>11229298</v>
       </c>
       <c r="J142" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="143" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H143" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I143">
         <v>50709616</v>
       </c>
       <c r="J143" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="144" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H144" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I144">
         <v>37034524</v>
       </c>
       <c r="J144" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="145" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H145" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I145">
         <v>14299890</v>
       </c>
       <c r="J145" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="146" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H146" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I146">
         <v>13195811</v>
       </c>
       <c r="J146" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="147" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H147" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I147">
         <v>36608029</v>
       </c>
       <c r="J147" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="148" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H148" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I148">
         <v>13195957</v>
@@ -4646,315 +4651,315 @@
     </row>
     <row r="149" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H149" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I149">
         <v>10121189</v>
       </c>
       <c r="J149" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="150" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H150" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I150">
         <v>8122806</v>
       </c>
       <c r="J150" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="151" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H151" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I151">
         <v>48477550</v>
       </c>
       <c r="J151" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="152" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H152" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I152">
         <v>11288089</v>
       </c>
       <c r="J152" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="153" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H153" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I153">
         <v>11104533</v>
       </c>
       <c r="J153" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="154" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H154" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I154">
         <v>10124384</v>
       </c>
       <c r="J154" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="155" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H155" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I155">
         <v>46995055</v>
       </c>
       <c r="J155" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="156" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H156" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I156">
         <v>11744316</v>
       </c>
       <c r="J156" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="157" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H157" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I157">
         <v>13069194</v>
       </c>
       <c r="J157" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="158" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H158" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I158">
         <v>19365568</v>
       </c>
       <c r="J158" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="159" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H159" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I159">
         <v>47861038</v>
       </c>
       <c r="J159" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="160" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H160" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I160">
         <v>43252471</v>
       </c>
       <c r="J160" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="161" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H161" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I161">
         <v>4125381</v>
       </c>
       <c r="J161" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="162" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H162" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I162">
         <v>38183281</v>
       </c>
       <c r="J162" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="163" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H163" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I163">
         <v>14107560</v>
       </c>
       <c r="J163" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="164" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H164" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I164">
         <v>44916947</v>
       </c>
       <c r="J164" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="165" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H165" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I165">
         <v>40640374</v>
       </c>
       <c r="J165" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="166" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H166" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I166">
         <v>13745117</v>
       </c>
       <c r="J166" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="167" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H167" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I167">
         <v>15414324</v>
       </c>
       <c r="J167" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="168" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H168" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I168">
         <v>35192489</v>
       </c>
       <c r="J168" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="169" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H169" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I169">
         <v>40982029</v>
       </c>
       <c r="J169" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="170" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H170" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I170">
         <v>10858043</v>
       </c>
       <c r="J170" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="171" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H171" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I171">
         <v>4125377</v>
       </c>
       <c r="J171" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="172" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H172" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I172">
         <v>26426530</v>
       </c>
       <c r="J172" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="173" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H173" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I173">
         <v>18980681</v>
       </c>
       <c r="J173" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="174" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H174" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I174">
         <v>12439390</v>
       </c>
       <c r="J174" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="175" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H175" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I175">
         <v>12263239</v>
       </c>
       <c r="J175" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="176" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H176" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I176">
         <v>50725354</v>
       </c>
       <c r="J176" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="177" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H177" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I177">
         <v>16179047</v>
@@ -4965,370 +4970,370 @@
     </row>
     <row r="178" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H178" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I178">
         <v>20815743</v>
       </c>
       <c r="J178" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="179" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H179" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I179">
         <v>39651008</v>
       </c>
       <c r="J179" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="180" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H180" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I180">
         <v>42839047</v>
       </c>
       <c r="J180" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="181" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H181" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I181">
         <v>38455497</v>
       </c>
       <c r="J181" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="182" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H182" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I182">
         <v>37173787</v>
       </c>
       <c r="J182" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="183" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H183" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I183">
         <v>42913903</v>
       </c>
       <c r="J183" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="184" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H184" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I184">
         <v>41864123</v>
       </c>
       <c r="J184" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="185" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H185" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I185">
         <v>4152612</v>
       </c>
       <c r="J185" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="186" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H186" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I186">
         <v>4152610</v>
       </c>
       <c r="J186" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="187" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H187" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I187">
         <v>35896315</v>
       </c>
       <c r="J187" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="188" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H188" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I188">
         <v>31743599</v>
       </c>
       <c r="J188" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="189" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H189" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I189">
         <v>4152608</v>
       </c>
       <c r="J189" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="190" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H190" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I190">
         <v>4152606</v>
       </c>
       <c r="J190" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="191" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H191" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I191">
         <v>34098917</v>
       </c>
       <c r="J191" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="192" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H192" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I192">
         <v>34801754</v>
       </c>
       <c r="J192" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="193" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H193" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I193">
         <v>37639889</v>
       </c>
       <c r="J193" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="194" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H194" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I194">
         <v>51533853</v>
       </c>
       <c r="J194" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="195" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H195" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I195">
         <v>49985232</v>
       </c>
       <c r="J195" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="196" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H196" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I196">
         <v>50155408</v>
       </c>
       <c r="J196" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="197" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H197" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I197">
         <v>35401181</v>
       </c>
       <c r="J197" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="198" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H198" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I198">
         <v>38157908</v>
       </c>
       <c r="J198" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="199" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H199" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I199">
         <v>41662266</v>
       </c>
       <c r="J199" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="200" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H200" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I200">
         <v>47936724</v>
       </c>
       <c r="J200" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="201" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H201" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I201">
         <v>38417806</v>
       </c>
       <c r="J201" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="202" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H202" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I202">
         <v>38158208</v>
       </c>
       <c r="J202" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="203" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H203" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I203">
         <v>12263163</v>
       </c>
       <c r="J203" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="204" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H204" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I204">
         <v>15826960</v>
       </c>
       <c r="J204" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="205" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H205" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I205">
         <v>13573385</v>
       </c>
       <c r="J205" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="206" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H206" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I206">
         <v>42871700</v>
       </c>
       <c r="J206" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="207" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H207" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I207">
         <v>39257536</v>
       </c>
       <c r="J207" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="208" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H208" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I208">
         <v>37424126</v>
       </c>
       <c r="J208" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="209" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H209" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I209">
         <v>36802614</v>
       </c>
       <c r="J209" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="210" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H210" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I210">
         <v>36577826</v>
       </c>
       <c r="J210" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="211" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H211" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I211">
         <v>35149611</v>
@@ -5339,128 +5344,128 @@
     </row>
     <row r="212" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H212" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I212">
         <v>26196255</v>
       </c>
       <c r="J212" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="213" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H213" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I213">
         <v>11156528</v>
       </c>
       <c r="J213" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="214" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H214" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I214">
         <v>38415503</v>
       </c>
       <c r="J214" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="215" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H215" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I215">
         <v>37244806</v>
       </c>
       <c r="J215" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="216" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H216" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I216">
         <v>27011098</v>
       </c>
       <c r="J216" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="217" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H217" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I217">
         <v>26019234</v>
       </c>
       <c r="J217" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="218" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H218" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I218">
         <v>13959023</v>
       </c>
       <c r="J218" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="219" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H219" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I219">
         <v>12496637</v>
       </c>
       <c r="J219" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="220" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H220" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I220">
         <v>25411238</v>
       </c>
       <c r="J220" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="221" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H221" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I221">
         <v>38312169</v>
       </c>
       <c r="J221" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="222" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H222" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I222">
         <v>31886592</v>
       </c>
       <c r="J222" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="223" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H223" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I223">
         <v>11670520</v>
@@ -5471,348 +5476,348 @@
     </row>
     <row r="224" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H224" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I224">
         <v>26500515</v>
       </c>
       <c r="J224" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="225" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H225" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I225">
         <v>36162739</v>
       </c>
       <c r="J225" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="226" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H226" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I226">
         <v>39893389</v>
       </c>
       <c r="J226" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="227" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H227" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I227">
         <v>39296173</v>
       </c>
       <c r="J227" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="228" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H228" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I228">
         <v>26491140</v>
       </c>
       <c r="J228" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="229" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H229" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I229">
         <v>49473587</v>
       </c>
       <c r="J229" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="230" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H230" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I230">
         <v>50326931</v>
       </c>
       <c r="J230" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="231" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H231" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I231">
         <v>12095120</v>
       </c>
       <c r="J231" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="232" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H232" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I232">
         <v>11765770</v>
       </c>
       <c r="J232" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="233" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H233" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I233">
         <v>15757638</v>
       </c>
       <c r="J233" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="234" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H234" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I234">
         <v>12038103</v>
       </c>
       <c r="J234" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="235" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H235" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I235">
         <v>46801171</v>
       </c>
       <c r="J235" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="236" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H236" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I236">
         <v>10155238</v>
       </c>
       <c r="J236" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="237" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H237" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I237">
         <v>10816066</v>
       </c>
       <c r="J237" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="238" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H238" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I238">
         <v>8668649</v>
       </c>
       <c r="J238" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="239" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H239" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I239">
         <v>36635604</v>
       </c>
       <c r="J239" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="240" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H240" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I240">
         <v>8837870</v>
       </c>
       <c r="J240" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="241" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H241" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I241">
         <v>5359040</v>
       </c>
       <c r="J241" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="242" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H242" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I242">
         <v>42373723</v>
       </c>
       <c r="J242" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="243" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H243" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I243">
         <v>16303007</v>
       </c>
       <c r="J243" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="244" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H244" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I244">
         <v>27303665</v>
       </c>
       <c r="J244" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="245" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H245" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I245">
         <v>5462299</v>
       </c>
       <c r="J245" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="246" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H246" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I246">
         <v>47220150</v>
       </c>
       <c r="J246" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="247" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H247" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I247">
         <v>42265154</v>
       </c>
       <c r="J247" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="248" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H248" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I248">
         <v>48105600</v>
       </c>
       <c r="J248" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="249" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H249" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I249">
         <v>34991467</v>
       </c>
       <c r="J249" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="250" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H250" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I250">
         <v>34348663</v>
       </c>
       <c r="J250" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="251" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H251" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I251">
         <v>34535085</v>
       </c>
       <c r="J251" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="252" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H252" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I252">
         <v>41140508</v>
       </c>
       <c r="J252" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="253" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H253" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I253">
         <v>22441147</v>
       </c>
       <c r="J253" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="254" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H254" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I254">
         <v>36811022</v>
       </c>
       <c r="J254" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="255" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H255" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I255">
         <v>36811023</v>
@@ -5823,414 +5828,414 @@
     </row>
     <row r="256" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H256" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I256">
         <v>42217758</v>
       </c>
       <c r="J256" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="257" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H257" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I257">
         <v>39384055</v>
       </c>
       <c r="J257" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="258" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H258" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I258">
         <v>11681261</v>
       </c>
       <c r="J258" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="259" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H259" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I259">
         <v>37161537</v>
       </c>
       <c r="J259" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="260" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H260" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I260">
         <v>30405071</v>
       </c>
       <c r="J260" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="261" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H261" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I261">
         <v>22403445</v>
       </c>
       <c r="J261" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="262" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H262" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I262">
         <v>26257716</v>
       </c>
       <c r="J262" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="263" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H263" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I263">
         <v>12481760</v>
       </c>
       <c r="J263" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="264" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H264" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I264">
         <v>12481759</v>
       </c>
       <c r="J264" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="265" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H265" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I265">
         <v>36682232</v>
       </c>
       <c r="J265" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="266" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H266" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I266">
         <v>46727700</v>
       </c>
       <c r="J266" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="267" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H267" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I267">
         <v>40771157</v>
       </c>
       <c r="J267" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="268" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H268" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I268">
         <v>19104731</v>
       </c>
       <c r="J268" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="269" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H269" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I269">
         <v>39944753</v>
       </c>
       <c r="J269" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="270" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H270" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I270">
         <v>48449253</v>
       </c>
       <c r="J270" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="271" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H271" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I271">
         <v>42051062</v>
       </c>
       <c r="J271" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="272" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H272" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I272">
         <v>18291047</v>
       </c>
       <c r="J272" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="273" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H273" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I273">
         <v>10727917</v>
       </c>
       <c r="J273" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="274" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H274" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I274">
         <v>46543317</v>
       </c>
       <c r="J274" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="275" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H275" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I275">
         <v>13644995</v>
       </c>
       <c r="J275" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="276" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H276" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I276">
         <v>42486414</v>
       </c>
       <c r="J276" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="277" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H277" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I277">
         <v>44695653</v>
       </c>
       <c r="J277" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="278" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H278" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I278">
         <v>44374810</v>
       </c>
       <c r="J278" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="279" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H279" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I279">
         <v>29258063</v>
       </c>
       <c r="J279" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="280" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H280" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I280">
         <v>13405604</v>
       </c>
       <c r="J280" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="281" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H281" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I281">
         <v>10646862</v>
       </c>
       <c r="J281" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="282" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H282" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I282">
         <v>12362063</v>
       </c>
       <c r="J282" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="283" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H283" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I283">
         <v>40185196</v>
       </c>
       <c r="J283" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="284" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H284" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I284">
         <v>15825326</v>
       </c>
       <c r="J284" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="285" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H285" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I285">
         <v>26375455</v>
       </c>
       <c r="J285" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="286" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H286" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I286">
         <v>42803850</v>
       </c>
       <c r="J286" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="287" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H287" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I287">
         <v>50154913</v>
       </c>
       <c r="J287" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="288" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H288" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I288">
         <v>16806254</v>
       </c>
       <c r="J288" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="289" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H289" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I289">
         <v>40501253</v>
       </c>
       <c r="J289" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="290" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H290" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I290">
         <v>14878740</v>
       </c>
       <c r="J290" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="291" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H291" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I291">
         <v>12673237</v>
       </c>
       <c r="J291" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="292" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H292" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I292">
         <v>17579662</v>
       </c>
       <c r="J292" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="293" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H293" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I293">
         <v>14719737</v>
@@ -6241,942 +6246,942 @@
     </row>
     <row r="294" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H294" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I294">
         <v>22119013</v>
       </c>
       <c r="J294" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="295" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H295" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I295">
         <v>15795597</v>
       </c>
       <c r="J295" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="296" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H296" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I296">
         <v>12126317</v>
       </c>
       <c r="J296" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="297" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H297" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I297">
         <v>39239709</v>
       </c>
       <c r="J297" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="298" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H298" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I298">
         <v>14488275</v>
       </c>
       <c r="J298" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="299" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H299" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I299">
         <v>42519088</v>
       </c>
       <c r="J299" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="300" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H300" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I300">
         <v>17579394</v>
       </c>
       <c r="J300" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="301" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H301" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I301">
         <v>27056005</v>
       </c>
       <c r="J301" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="302" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H302" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I302">
         <v>24832169</v>
       </c>
       <c r="J302" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="303" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H303" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I303">
         <v>39147133</v>
       </c>
       <c r="J303" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="304" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H304" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I304">
         <v>39030281</v>
       </c>
       <c r="J304" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="305" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H305" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I305">
         <v>13373616</v>
       </c>
       <c r="J305" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="306" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H306" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I306">
         <v>12757668</v>
       </c>
       <c r="J306" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="307" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H307" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I307">
         <v>38977260</v>
       </c>
       <c r="J307" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="308" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H308" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I308">
         <v>38676914</v>
       </c>
       <c r="J308" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="309" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H309" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I309">
         <v>39911056</v>
       </c>
       <c r="J309" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="310" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H310" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I310">
         <v>40102936</v>
       </c>
       <c r="J310" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="311" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H311" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I311">
         <v>10929274</v>
       </c>
       <c r="J311" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="312" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H312" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I312">
         <v>10929273</v>
       </c>
       <c r="J312" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="313" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H313" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I313">
         <v>38412071</v>
       </c>
       <c r="J313" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="314" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H314" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I314">
         <v>29280326</v>
       </c>
       <c r="J314" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="315" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H315" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I315">
         <v>38412101</v>
       </c>
       <c r="J315" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="316" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H316" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I316">
         <v>5332788</v>
       </c>
       <c r="J316" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="317" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H317" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I317">
         <v>5332789</v>
       </c>
       <c r="J317" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="318" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H318" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I318">
         <v>51016959</v>
       </c>
       <c r="J318" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="319" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H319" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I319">
         <v>40636333</v>
       </c>
       <c r="J319" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="320" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H320" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I320">
         <v>50875168</v>
       </c>
       <c r="J320" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="321" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H321" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I321">
         <v>51623281</v>
       </c>
       <c r="J321" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="322" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H322" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I322">
         <v>51897600</v>
       </c>
       <c r="J322" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="323" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H323" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I323">
         <v>51989601</v>
       </c>
       <c r="J323" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="324" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H324" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I324">
         <v>52390638</v>
       </c>
       <c r="J324" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="325" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H325" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I325">
         <v>52362395</v>
       </c>
       <c r="J325" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="326" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H326" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I326">
         <v>52155415</v>
       </c>
       <c r="J326" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="327" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H327" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I327">
         <v>52162444</v>
       </c>
       <c r="J327" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="328" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H328" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I328">
         <v>52270898</v>
       </c>
       <c r="J328" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="329" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H329" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I329">
         <v>52211558</v>
       </c>
       <c r="J329" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="330" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H330" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I330">
         <v>52217000</v>
       </c>
       <c r="J330" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="331" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H331" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I331">
         <v>51689222</v>
       </c>
       <c r="J331" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="332" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H332" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I332">
         <v>51684787</v>
       </c>
       <c r="J332" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="333" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H333" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I333">
         <v>51883980</v>
       </c>
       <c r="J333" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="334" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H334" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I334">
         <v>51898514</v>
       </c>
       <c r="J334" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="335" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H335" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I335">
         <v>52990015</v>
       </c>
       <c r="J335" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="336" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H336" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I336">
         <v>52581507</v>
       </c>
       <c r="J336" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="337" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H337" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I337">
         <v>52613211</v>
       </c>
       <c r="J337" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="338" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H338" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I338">
         <v>52578670</v>
       </c>
       <c r="J338" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="339" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H339" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I339">
         <v>52874174</v>
       </c>
       <c r="J339" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="340" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H340" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I340">
         <v>52872566</v>
       </c>
       <c r="J340" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="341" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H341" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I341">
         <v>54145830</v>
       </c>
       <c r="J341" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="342" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H342" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I342">
         <v>53052265</v>
       </c>
       <c r="J342" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="343" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H343" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I343">
         <v>53297446</v>
       </c>
       <c r="J343" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="344" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H344" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I344">
         <v>53583387</v>
       </c>
       <c r="J344" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="345" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H345" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I345">
         <v>53564659</v>
       </c>
       <c r="J345" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="346" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H346" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I346">
         <v>53569741</v>
       </c>
       <c r="J346" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="347" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H347" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I347">
         <v>53680118</v>
       </c>
       <c r="J347" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="348" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H348" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I348">
         <v>53776254</v>
       </c>
       <c r="J348" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="349" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H349" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I349">
         <v>53967042</v>
       </c>
       <c r="J349" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="350" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H350" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I350">
         <v>55275736</v>
       </c>
       <c r="J350" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="351" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H351" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I351">
         <v>56663811</v>
       </c>
       <c r="J351" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="352" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H352" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I352">
         <v>59082806</v>
       </c>
       <c r="J352" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="353" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H353" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I353">
         <v>55369678</v>
       </c>
       <c r="J353" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="354" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H354" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I354">
         <v>55354052</v>
       </c>
       <c r="J354" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="355" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H355" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I355">
         <v>55381383</v>
       </c>
       <c r="J355" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="356" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H356" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I356">
         <v>55609278</v>
       </c>
       <c r="J356" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="357" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H357" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I357">
         <v>55356212</v>
       </c>
       <c r="J357" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="358" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H358" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I358">
         <v>55449180</v>
       </c>
       <c r="J358" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="359" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H359" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I359">
         <v>55357095</v>
       </c>
       <c r="J359" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="360" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H360" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I360">
         <v>55384739</v>
       </c>
       <c r="J360" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="361" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H361" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I361">
         <v>55357155</v>
       </c>
       <c r="J361" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="362" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H362" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I362">
         <v>55389336</v>
       </c>
       <c r="J362" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="363" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H363" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I363">
         <v>55356388</v>
       </c>
       <c r="J363" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="364" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H364" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I364">
         <v>55610213</v>
       </c>
       <c r="J364" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="365" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H365" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I365">
         <v>55462718</v>
       </c>
       <c r="J365" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="366" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H366" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I366">
         <v>58084222</v>
       </c>
       <c r="J366" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="367" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H367" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I367">
         <v>56651433</v>
       </c>
       <c r="J367" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="368" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H368" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I368">
         <v>56479851</v>
       </c>
       <c r="J368" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="369" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H369" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I369">
         <v>56667264</v>
       </c>
       <c r="J369" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="370" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H370" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I370">
         <v>56896464</v>
       </c>
       <c r="J370" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="371" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H371" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I371">
         <v>57592449</v>
       </c>
       <c r="J371" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="372" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H372" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I372">
         <v>56183402</v>
       </c>
       <c r="J372" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="373" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H373" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I373">
         <v>56651667</v>
       </c>
       <c r="J373" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="374" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H374" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I374">
         <v>58987730</v>
       </c>
       <c r="J374" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="375" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H375" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I375">
         <v>57422656</v>
       </c>
       <c r="J375" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="376" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H376" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I376">
         <v>58040260</v>
       </c>
       <c r="J376" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="377" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H377" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I377">
         <v>59070986</v>
       </c>
       <c r="J377" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="378" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H378" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I378">
         <v>59058036</v>
       </c>
       <c r="J378" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="379" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H379" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I379">
         <v>58505144</v>
@@ -7187,139 +7192,139 @@
     </row>
     <row r="380" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H380" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I380">
         <v>58610450</v>
       </c>
       <c r="J380" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="381" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H381" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I381">
         <v>59056260</v>
       </c>
       <c r="J381" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="382" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H382" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I382">
         <v>58722261</v>
       </c>
       <c r="J382" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="383" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H383" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I383">
         <v>58716097</v>
       </c>
       <c r="J383" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="384" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H384" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I384">
         <v>58730204</v>
       </c>
       <c r="J384" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="385" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H385" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I385">
         <v>59199875</v>
       </c>
       <c r="J385" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="386" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H386" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I386">
         <v>59759466</v>
       </c>
       <c r="J386" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="387" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H387" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I387">
         <v>59332927</v>
       </c>
       <c r="J387" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="388" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H388" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I388">
         <v>59944694</v>
       </c>
       <c r="J388" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="389" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H389" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I389">
         <v>60019261</v>
       </c>
       <c r="J389" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="390" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H390" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I390">
         <v>59932138</v>
       </c>
       <c r="J390" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="391" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H391" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I391">
         <v>59924956</v>
       </c>
       <c r="J391" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="392" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H392" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I392">
         <v>59927382</v>
@@ -7330,18 +7335,18 @@
     </row>
     <row r="393" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H393" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I393">
         <v>59836396</v>
       </c>
       <c r="J393" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="394" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H394" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I394">
         <v>60015061</v>
@@ -7352,942 +7357,942 @@
     </row>
     <row r="395" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H395" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I395">
         <v>60023938</v>
       </c>
       <c r="J395" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="396" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H396" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I396">
         <v>60025950</v>
       </c>
       <c r="J396" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="397" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H397" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I397">
         <v>60024864</v>
       </c>
       <c r="J397" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="398" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H398" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I398">
         <v>60084208</v>
       </c>
       <c r="J398" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="399" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H399" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I399">
         <v>60085614</v>
       </c>
       <c r="J399" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="400" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H400" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I400">
         <v>60133592</v>
       </c>
       <c r="J400" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="401" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H401" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I401">
         <v>60450424</v>
       </c>
       <c r="J401" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="402" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H402" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I402">
         <v>60380162</v>
       </c>
       <c r="J402" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="403" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H403" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I403">
         <v>60541542</v>
       </c>
       <c r="J403" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="404" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H404" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I404">
         <v>60541171</v>
       </c>
       <c r="J404" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="405" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H405" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I405">
         <v>60543356</v>
       </c>
       <c r="J405" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="406" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H406" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I406">
         <v>60530655</v>
       </c>
       <c r="J406" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="407" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H407" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I407">
         <v>60615380</v>
       </c>
       <c r="J407" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="408" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H408" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I408">
         <v>60725132</v>
       </c>
       <c r="J408" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="409" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H409" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I409">
         <v>62575565</v>
       </c>
       <c r="J409" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="410" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H410" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I410">
         <v>61766007</v>
       </c>
       <c r="J410" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="411" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H411" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I411">
         <v>61089339</v>
       </c>
       <c r="J411" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="412" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H412" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I412">
         <v>62377903</v>
       </c>
       <c r="J412" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="413" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H413" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I413">
         <v>60542212</v>
       </c>
       <c r="J413" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="414" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H414" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I414">
         <v>61044622</v>
       </c>
       <c r="J414" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="415" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H415" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I415">
         <v>61199642</v>
       </c>
       <c r="J415" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="416" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H416" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I416">
         <v>61760291</v>
       </c>
       <c r="J416" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="417" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H417" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I417">
         <v>61923953</v>
       </c>
       <c r="J417" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="418" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H418" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I418">
         <v>61760141</v>
       </c>
       <c r="J418" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="419" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H419" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I419">
         <v>61929592</v>
       </c>
       <c r="J419" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="420" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H420" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I420">
         <v>61929727</v>
       </c>
       <c r="J420" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="421" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H421" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I421">
         <v>61929494</v>
       </c>
       <c r="J421" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="422" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H422" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I422">
         <v>61929493</v>
       </c>
       <c r="J422" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="423" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H423" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I423">
         <v>61879892</v>
       </c>
       <c r="J423" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="424" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H424" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I424">
         <v>62378988</v>
       </c>
       <c r="J424" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="425" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H425" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I425">
         <v>62375802</v>
       </c>
       <c r="J425" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="426" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H426" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I426">
         <v>62379668</v>
       </c>
       <c r="J426" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="427" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H427" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I427">
         <v>62221331</v>
       </c>
       <c r="J427" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="428" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H428" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I428">
         <v>62385013</v>
       </c>
       <c r="J428" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="429" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H429" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I429">
         <v>62380995</v>
       </c>
       <c r="J429" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="430" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H430" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I430">
         <v>62421723</v>
       </c>
       <c r="J430" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="431" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H431" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I431">
         <v>62374813</v>
       </c>
       <c r="J431" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="432" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H432" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I432">
         <v>62499786</v>
       </c>
       <c r="J432" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="433" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H433" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I433">
         <v>62498583</v>
       </c>
       <c r="J433" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="434" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H434" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I434">
         <v>63346456</v>
       </c>
       <c r="J434" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="435" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H435" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I435">
         <v>63100963</v>
       </c>
       <c r="J435" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="436" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H436" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I436">
         <v>63396496</v>
       </c>
       <c r="J436" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="437" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H437" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I437">
         <v>64270608</v>
       </c>
       <c r="J437" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="438" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H438" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I438">
         <v>63573761</v>
       </c>
       <c r="J438" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="439" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H439" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I439">
         <v>64330763</v>
       </c>
       <c r="J439" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="440" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H440" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I440">
         <v>64330764</v>
       </c>
       <c r="J440" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="441" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H441" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I441">
         <v>64212552</v>
       </c>
       <c r="J441" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="442" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H442" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I442">
         <v>64212544</v>
       </c>
       <c r="J442" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="443" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H443" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I443">
         <v>64212543</v>
       </c>
       <c r="J443" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="444" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H444" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I444">
         <v>64212381</v>
       </c>
       <c r="J444" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="445" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H445" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I445">
         <v>64114088</v>
       </c>
       <c r="J445" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="446" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H446" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I446">
         <v>64223250</v>
       </c>
       <c r="J446" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="447" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H447" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I447">
         <v>64214259</v>
       </c>
       <c r="J447" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="448" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H448" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I448">
         <v>64214258</v>
       </c>
       <c r="J448" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="449" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H449" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I449">
         <v>63742200</v>
       </c>
       <c r="J449" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="450" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H450" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I450">
         <v>64606094</v>
       </c>
       <c r="J450" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="451" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H451" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I451">
         <v>64287980</v>
       </c>
       <c r="J451" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="452" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H452" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I452">
         <v>64257297</v>
       </c>
       <c r="J452" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="453" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H453" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I453">
         <v>66097436</v>
       </c>
       <c r="J453" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="454" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H454" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I454">
         <v>64330309</v>
       </c>
       <c r="J454" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="455" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H455" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I455">
         <v>64846264</v>
       </c>
       <c r="J455" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="456" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H456" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I456">
         <v>64753996</v>
       </c>
       <c r="J456" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="457" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H457" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I457">
         <v>64778162</v>
       </c>
       <c r="J457" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="458" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H458" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I458">
         <v>64778161</v>
       </c>
       <c r="J458" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="459" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H459" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I459">
         <v>64808932</v>
       </c>
       <c r="J459" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="460" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H460" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I460">
         <v>64789478</v>
       </c>
       <c r="J460" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="461" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H461" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I461">
         <v>64912430</v>
       </c>
       <c r="J461" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="462" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H462" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I462">
         <v>64971361</v>
       </c>
       <c r="J462" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="463" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H463" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I463">
         <v>65145714</v>
       </c>
       <c r="J463" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="464" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H464" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I464">
         <v>65081124</v>
       </c>
       <c r="J464" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="465" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H465" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I465">
         <v>65181042</v>
       </c>
       <c r="J465" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="466" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H466" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I466">
         <v>65179405</v>
       </c>
       <c r="J466" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="467" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H467" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I467">
         <v>65566244</v>
       </c>
       <c r="J467" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="468" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H468" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I468">
         <v>65566541</v>
       </c>
       <c r="J468" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="469" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H469" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I469">
         <v>65656468</v>
       </c>
       <c r="J469" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="470" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H470" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I470">
         <v>65657039</v>
       </c>
       <c r="J470" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="471" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H471" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I471">
         <v>66217025</v>
       </c>
       <c r="J471" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="472" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H472" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I472">
         <v>66214618</v>
       </c>
       <c r="J472" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="473" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H473" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I473">
         <v>65935700</v>
       </c>
       <c r="J473" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="474" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H474" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I474">
         <v>65934564</v>
       </c>
       <c r="J474" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="475" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H475" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I475">
         <v>65933937</v>
       </c>
       <c r="J475" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="476" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H476" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I476">
         <v>66046959</v>
       </c>
       <c r="J476" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="477" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H477" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I477">
         <v>65969750</v>
       </c>
       <c r="J477" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="478" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H478" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I478">
         <v>66358440</v>
       </c>
       <c r="J478" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="479" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H479" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I479">
         <v>66417803</v>
       </c>
       <c r="J479" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="480" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H480" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I480">
         <v>66417801</v>
@@ -8298,695 +8303,695 @@
     </row>
     <row r="481" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H481" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I481">
         <v>66357977</v>
       </c>
       <c r="J481" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="482" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H482" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I482">
         <v>67191572</v>
       </c>
       <c r="J482" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="483" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H483" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I483">
         <v>66546178</v>
       </c>
       <c r="J483" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="484" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H484" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I484">
         <v>67627331</v>
       </c>
       <c r="J484" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="485" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H485" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I485">
         <v>66778787</v>
       </c>
       <c r="J485" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="486" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H486" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I486">
         <v>66778788</v>
       </c>
       <c r="J486" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="487" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H487" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I487">
         <v>66778789</v>
       </c>
       <c r="J487" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="488" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H488" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I488">
         <v>66896364</v>
       </c>
       <c r="J488" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="489" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H489" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I489">
         <v>66607099</v>
       </c>
       <c r="J489" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="490" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H490" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I490">
         <v>66864708</v>
       </c>
       <c r="J490" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="491" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H491" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I491">
         <v>66850322</v>
       </c>
       <c r="J491" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="492" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H492" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I492">
         <v>67268341</v>
       </c>
       <c r="J492" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="493" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H493" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I493">
         <v>67268348</v>
       </c>
       <c r="J493" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="494" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H494" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I494">
         <v>67268349</v>
       </c>
       <c r="J494" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="495" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H495" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I495">
         <v>67268350</v>
       </c>
       <c r="J495" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="496" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H496" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I496">
         <v>67272047</v>
       </c>
       <c r="J496" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="497" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H497" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I497">
         <v>67272046</v>
       </c>
       <c r="J497" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="498" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H498" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I498">
         <v>67438488</v>
       </c>
       <c r="J498" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="499" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H499" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I499">
         <v>67438487</v>
       </c>
       <c r="J499" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="500" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H500" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I500">
         <v>68253037</v>
       </c>
       <c r="J500" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="501" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H501" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I501">
         <v>67891311</v>
       </c>
       <c r="J501" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="502" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H502" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I502">
         <v>67900090</v>
       </c>
       <c r="J502" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="503" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H503" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I503">
         <v>67630646</v>
       </c>
       <c r="J503" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="504" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H504" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I504">
         <v>67974104</v>
       </c>
       <c r="J504" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="505" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H505" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I505">
         <v>67989839</v>
       </c>
       <c r="J505" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="506" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H506" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I506">
         <v>67988468</v>
       </c>
       <c r="J506" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="507" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H507" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I507">
         <v>68466892</v>
       </c>
       <c r="J507" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="508" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H508" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I508">
         <v>69040158</v>
       </c>
       <c r="J508" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="509" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H509" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I509">
         <v>68462854</v>
       </c>
       <c r="J509" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="510" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H510" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I510" t="s">
+        <v>533</v>
+      </c>
+      <c r="J510" t="s">
         <v>534</v>
-      </c>
-      <c r="J510" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="511" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H511" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I511" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="J511" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="512" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H512" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I512">
         <v>68677002</v>
       </c>
       <c r="J512" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="513" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H513" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I513">
         <v>68880617</v>
       </c>
       <c r="J513" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="514" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H514" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I514">
         <v>68934411</v>
       </c>
       <c r="J514" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="515" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H515" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I515">
         <v>68924611</v>
       </c>
       <c r="J515" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="516" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H516" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I516">
         <v>69039437</v>
       </c>
       <c r="J516" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="517" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H517" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I517">
         <v>69039778</v>
       </c>
       <c r="J517" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="518" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H518" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I518">
         <v>69279032</v>
       </c>
       <c r="J518" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="519" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H519" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I519">
         <v>68938743</v>
       </c>
       <c r="J519" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="520" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H520" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I520">
         <v>69772629</v>
       </c>
       <c r="J520" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="521" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H521" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I521">
         <v>69772627</v>
       </c>
       <c r="J521" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="522" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H522" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I522">
         <v>69772625</v>
       </c>
       <c r="J522" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="523" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H523" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I523">
         <v>69292187</v>
       </c>
       <c r="J523" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="524" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H524" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I524">
         <v>69292186</v>
       </c>
       <c r="J524" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="525" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H525" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I525">
         <v>69292185</v>
       </c>
       <c r="J525" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="526" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H526" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I526">
         <v>69096297</v>
       </c>
       <c r="J526" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="527" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H527" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I527">
         <v>69096296</v>
       </c>
       <c r="J527" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="528" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H528" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I528">
         <v>69594684</v>
       </c>
       <c r="J528" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="529" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H529" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I529">
         <v>70204974</v>
       </c>
       <c r="J529" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="530" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H530" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I530">
         <v>70204975</v>
       </c>
       <c r="J530" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="531" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H531" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I531">
         <v>69767288</v>
       </c>
       <c r="J531" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="532" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H532" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I532">
         <v>69766464</v>
       </c>
       <c r="J532" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="533" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H533" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I533">
         <v>69803799</v>
       </c>
       <c r="J533" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="534" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H534" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I534">
         <v>70251147</v>
       </c>
       <c r="J534" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="535" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H535" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I535">
         <v>69770093</v>
       </c>
       <c r="J535" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="536" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H536" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I536">
         <v>70205079</v>
       </c>
       <c r="J536" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="537" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H537" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I537">
         <v>70530577</v>
       </c>
       <c r="J537" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="538" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H538" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I538">
         <v>70530576</v>
       </c>
       <c r="J538" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="539" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H539" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I539">
         <v>71030052</v>
       </c>
       <c r="J539" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="540" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H540" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I540">
         <v>70770186</v>
       </c>
       <c r="J540" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="541" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H541" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I541">
         <v>71173111</v>
       </c>
       <c r="J541" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="542" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H542" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I542">
         <v>71156871</v>
       </c>
       <c r="J542" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="543" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H543" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I543">
         <v>71291488</v>
       </c>
       <c r="J543" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="544" spans="8:10" x14ac:dyDescent="0.3">
@@ -8994,331 +8999,331 @@
         <v>71042279</v>
       </c>
       <c r="J544" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="545" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H545" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I545">
         <v>71947627</v>
       </c>
       <c r="J545" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="546" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H546" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I546">
         <v>72182444</v>
       </c>
       <c r="J546" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="547" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H547" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I547">
         <v>72300747</v>
       </c>
       <c r="J547" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="548" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H548" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I548">
         <v>72417582</v>
       </c>
       <c r="J548" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="549" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H549" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I549">
         <v>72614935</v>
       </c>
       <c r="J549" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="550" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H550" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I550">
         <v>72614936</v>
       </c>
       <c r="J550" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="551" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H551" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I551">
         <v>72614937</v>
       </c>
       <c r="J551" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="552" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H552" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I552">
         <v>73226633</v>
       </c>
       <c r="J552" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="553" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H553" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I553">
         <v>73226632</v>
       </c>
       <c r="J553" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="554" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H554" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I554">
         <v>73316683</v>
       </c>
       <c r="J554" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="555" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H555" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I555">
         <v>73316684</v>
       </c>
       <c r="J555" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="556" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H556" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I556">
         <v>73316685</v>
       </c>
       <c r="J556" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="557" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H557" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I557">
         <v>72699936</v>
       </c>
       <c r="J557" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="558" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H558" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I558">
         <v>72699935</v>
       </c>
       <c r="J558" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="559" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H559" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I559">
         <v>72828733</v>
       </c>
       <c r="J559" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="560" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H560" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I560">
         <v>72828734</v>
       </c>
       <c r="J560" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="561" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H561" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I561">
         <v>72683872</v>
       </c>
       <c r="J561" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="562" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H562" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I562">
         <v>72910681</v>
       </c>
       <c r="J562" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="563" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H563" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I563">
         <v>72910683</v>
       </c>
       <c r="J563" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="564" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H564" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I564">
         <v>73523448</v>
       </c>
       <c r="J564" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="565" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H565" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I565">
         <v>73461995</v>
       </c>
       <c r="J565" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="566" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H566" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I566">
         <v>73956460</v>
       </c>
       <c r="J566" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="567" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H567" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I567">
         <v>73956461</v>
       </c>
       <c r="J567" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="568" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H568" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I568">
         <v>73956459</v>
       </c>
       <c r="J568" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="569" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H569" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I569">
         <v>74685916</v>
       </c>
       <c r="J569" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="570" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H570" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I570">
         <v>73975553</v>
       </c>
       <c r="J570" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="571" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H571" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I571">
         <v>73952843</v>
       </c>
       <c r="J571" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="572" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H572" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I572">
         <v>74550323</v>
       </c>
       <c r="J572" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="573" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H573" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I573">
         <v>75989703</v>
       </c>
       <c r="J573" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="574" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H574" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I574">
         <v>74693807</v>
@@ -9329,7 +9334,7 @@
     </row>
     <row r="575" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H575" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I575">
         <v>73893263</v>
@@ -9340,310 +9345,310 @@
     </row>
     <row r="576" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H576" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I576">
         <v>74884452</v>
       </c>
       <c r="J576" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="577" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H577" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I577">
         <v>74826973</v>
       </c>
       <c r="J577" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="578" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H578" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I578">
         <v>74826974</v>
       </c>
       <c r="J578" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="579" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H579" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I579">
         <v>75077119</v>
       </c>
       <c r="J579" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="580" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H580" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I580">
         <v>78867502</v>
       </c>
       <c r="J580" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="581" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H581" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I581">
         <v>80192305</v>
       </c>
       <c r="J581" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="582" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H582" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I582">
         <v>75741354</v>
       </c>
       <c r="J582" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="583" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H583" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I583">
         <v>78625461</v>
       </c>
       <c r="J583" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="584" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H584" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I584">
         <v>76375598</v>
       </c>
       <c r="J584" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="585" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H585" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I585">
         <v>76375597</v>
       </c>
       <c r="J585" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="586" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H586" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I586">
         <v>76374400</v>
       </c>
       <c r="J586" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="587" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H587" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I587">
         <v>76374401</v>
       </c>
       <c r="J587" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="588" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H588" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I588">
         <v>76241042</v>
       </c>
       <c r="J588" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="589" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H589" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I589">
         <v>76533940</v>
       </c>
       <c r="J589" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="590" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H590" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I590">
         <v>77463489</v>
       </c>
       <c r="J590" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="591" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H591" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I591">
         <v>77463490</v>
       </c>
       <c r="J591" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="592" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H592" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I592" s="2">
         <v>78907466</v>
       </c>
       <c r="J592" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="593" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H593" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I593" s="2">
         <v>78907465</v>
       </c>
       <c r="J593" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="594" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H594" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I594" s="2">
         <v>78903848</v>
       </c>
       <c r="J594" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="595" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H595" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I595" s="2">
         <v>78903849</v>
       </c>
       <c r="J595" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="596" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H596" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I596" s="2">
         <v>78621004</v>
       </c>
       <c r="J596" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="597" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H597" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I597" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="J597" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="598" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H598" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I598" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="J598" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="599" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H599" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I599" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="J599" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="600" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H600" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I600" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="J600" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="601" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H601" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I601" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="J601" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="602" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H602" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I602" s="2">
         <v>80629877</v>
       </c>
       <c r="J602" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="603" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H603" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I603" s="2">
         <v>80629881</v>
       </c>
       <c r="J603" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
   </sheetData>
@@ -9653,8 +9658,8 @@
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A69:A1048576 A1:A63">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  <conditionalFormatting sqref="A69:A1048576 A1:A62">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -9673,13 +9678,13 @@
   <sheetData>
     <row r="13" spans="1:3" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>649</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="C13" s="4" t="s">
         <v>650</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -9687,10 +9692,10 @@
         <v>13101217</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -9698,10 +9703,10 @@
         <v>4125377</v>
       </c>
       <c r="B15" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C15" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -9709,10 +9714,10 @@
         <v>26426530</v>
       </c>
       <c r="B16" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C16" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -9720,10 +9725,10 @@
         <v>43252471</v>
       </c>
       <c r="B17" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C17" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -9731,10 +9736,10 @@
         <v>64789478</v>
       </c>
       <c r="B18" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C18" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -9742,10 +9747,10 @@
         <v>71030052</v>
       </c>
       <c r="B19" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C19" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -9753,10 +9758,10 @@
         <v>11229298</v>
       </c>
       <c r="B20" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C20" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
@@ -9764,10 +9769,10 @@
         <v>75077119</v>
       </c>
       <c r="B21" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C21" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -9775,10 +9780,10 @@
         <v>42519088</v>
       </c>
       <c r="B22" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C22" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -9786,10 +9791,10 @@
         <v>17579394</v>
       </c>
       <c r="B23" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C23" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -9797,10 +9802,10 @@
         <v>53569741</v>
       </c>
       <c r="B24" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C24" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -9808,10 +9813,10 @@
         <v>53583387</v>
       </c>
       <c r="B25" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C25" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -9819,10 +9824,10 @@
         <v>12439390</v>
       </c>
       <c r="B26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C26" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -9830,10 +9835,10 @@
         <v>14107560</v>
       </c>
       <c r="B27" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C27" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
   </sheetData>

--- a/data/이슈제품.xlsx
+++ b/data/이슈제품.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OA\Desktop\쿠팡업로드\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2723A068-3266-43C1-B5B7-A04256B16213}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1375" uniqueCount="657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="686">
   <si>
     <t>오아디머무드등-화이트</t>
   </si>
@@ -308,15 +307,9 @@
     <t>보아르스위프클링전용필터</t>
   </si>
   <si>
-    <t>이미용</t>
-  </si>
-  <si>
     <t>오아에어셋거치대</t>
   </si>
   <si>
-    <t>차량</t>
-  </si>
-  <si>
     <t>오아와이더F3</t>
   </si>
   <si>
@@ -564,9 +557,6 @@
   </si>
   <si>
     <t>오아다리360</t>
-  </si>
-  <si>
-    <t>오아듀얼무릎마사지기V2</t>
   </si>
   <si>
     <t>오아아이템플</t>
@@ -2031,12 +2021,108 @@
     <t>기존 전지 내 다른모델 리콜실시중으로 260922007 발주건부터 신규전지로 인증변경
 기존재고 약 5500개 소진후 변경</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오아터치무선접이식키보드-포그밀크</t>
+  </si>
+  <si>
+    <t>오아터치무선접이식키보드-메탈그레이</t>
+  </si>
+  <si>
+    <t>뷰티</t>
+  </si>
+  <si>
+    <t>오아듀얼글로우-샌드크림</t>
+  </si>
+  <si>
+    <t>오아듀얼글로우-포그밀크</t>
+  </si>
+  <si>
+    <t>오아롤링넥마사지기-샌드크림</t>
+  </si>
+  <si>
+    <t>오아소닉제트드라이기-메탈그레이</t>
+  </si>
+  <si>
+    <t>보아르플라밍1500W컨벡션히터-그레이</t>
+  </si>
+  <si>
+    <t>보아르플라밍1000W컨벡션히터-그레이</t>
+  </si>
+  <si>
+    <t>보아르더글라스PRO가열식가습기-화이트</t>
+  </si>
+  <si>
+    <t>오아듀얼무릎마사지기V2-베이지</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>오아포핸드손마사지기-샌드크림</t>
+  </si>
+  <si>
+    <t>보아르아가미니휴대용젖병소독기-화이트</t>
+  </si>
+  <si>
+    <t>보아르스마트락텀블러-아이보리</t>
+  </si>
+  <si>
+    <t>보아르아가담이유식포트워머-화이트</t>
+  </si>
+  <si>
+    <t>보아르아가듀스테인리스빨대컵-아이보리</t>
+  </si>
+  <si>
+    <t>오아에어스트레처-샌드크림</t>
+  </si>
+  <si>
+    <t>오아클린이퓨어M-포그밀크</t>
+  </si>
+  <si>
+    <t>오아포켓나노-샌드크림</t>
+  </si>
+  <si>
+    <t>오아3in1커브마사지건-샌드크림</t>
+  </si>
+  <si>
+    <t>오아폴드에어드라이기-옐로우</t>
+  </si>
+  <si>
+    <t>오아클린이포켓-포그밀크</t>
+  </si>
+  <si>
+    <t>보아르플로업가열식가습기13L-화이트</t>
+  </si>
+  <si>
+    <t>보아르이지업텀블렌더1+1기획세트-아이보리</t>
+  </si>
+  <si>
+    <t>오아3in1올케어히팅EMS마사지기-어비스블랙</t>
+  </si>
+  <si>
+    <t>오아포켓랩-샌드크림</t>
+  </si>
+  <si>
+    <t>오아오플로우드라이기-화이트</t>
+  </si>
+  <si>
+    <t>오아베이직풋스파-샌드크림</t>
+  </si>
+  <si>
+    <t>오아코어스트레처-샌드크림</t>
+  </si>
+  <si>
+    <t>보아르포스S-화이트</t>
+  </si>
+  <si>
+    <t>오아포그팟가습기-포그밀크</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2422,8 +2508,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J603"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J632"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
@@ -2461,19 +2547,19 @@
         <v>27056005</v>
       </c>
       <c r="B2" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C2" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="H2" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="I2">
-        <v>3636925</v>
+        <v>16972627</v>
       </c>
       <c r="J2" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -2481,19 +2567,19 @@
         <v>52270898</v>
       </c>
       <c r="B3" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C3" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="H3" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="I3">
-        <v>3636926</v>
+        <v>17398556</v>
       </c>
       <c r="J3" t="s">
-        <v>31</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -2501,19 +2587,19 @@
         <v>4152606</v>
       </c>
       <c r="B4" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C4" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="H4" t="s">
-        <v>29</v>
+        <v>107</v>
       </c>
       <c r="I4">
-        <v>3636927</v>
+        <v>36811022</v>
       </c>
       <c r="J4" t="s">
-        <v>32</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -2521,19 +2607,19 @@
         <v>12263239</v>
       </c>
       <c r="B5" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C5" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="H5" t="s">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="I5">
-        <v>39415252</v>
+        <v>80915325</v>
       </c>
       <c r="J5" t="s">
-        <v>33</v>
+        <v>654</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -2541,19 +2627,19 @@
         <v>68880617</v>
       </c>
       <c r="B6" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="C6" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="H6" t="s">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="I6">
-        <v>19213859</v>
+        <v>80915326</v>
       </c>
       <c r="J6" t="s">
-        <v>34</v>
+        <v>655</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -2561,19 +2647,19 @@
         <v>5332788</v>
       </c>
       <c r="B7" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C7" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="H7" t="s">
-        <v>29</v>
+        <v>656</v>
       </c>
       <c r="I7">
-        <v>20342327</v>
+        <v>80953015</v>
       </c>
       <c r="J7" t="s">
-        <v>35</v>
+        <v>657</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -2581,19 +2667,19 @@
         <v>65933937</v>
       </c>
       <c r="B8" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C8" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="H8" t="s">
-        <v>29</v>
+        <v>656</v>
       </c>
       <c r="I8">
-        <v>13004238</v>
+        <v>80953016</v>
       </c>
       <c r="J8" t="s">
-        <v>36</v>
+        <v>658</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -2610,10 +2696,10 @@
         <v>29</v>
       </c>
       <c r="I9">
-        <v>20341619</v>
+        <v>20342327</v>
       </c>
       <c r="J9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -2630,10 +2716,10 @@
         <v>29</v>
       </c>
       <c r="I10">
-        <v>11092035</v>
+        <v>12586373</v>
       </c>
       <c r="J10" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -2641,19 +2727,19 @@
         <v>50725354</v>
       </c>
       <c r="B11" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C11" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="H11" t="s">
         <v>29</v>
       </c>
       <c r="I11">
-        <v>40852278</v>
+        <v>11055651</v>
       </c>
       <c r="J11" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -2661,19 +2747,19 @@
         <v>50153946</v>
       </c>
       <c r="B12" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C12" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="H12" t="s">
         <v>29</v>
       </c>
       <c r="I12">
-        <v>29266932</v>
+        <v>18816827</v>
       </c>
       <c r="J12" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -2681,19 +2767,19 @@
         <v>75741354</v>
       </c>
       <c r="B13" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="C13" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="H13" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="I13">
-        <v>12586373</v>
+        <v>39229235</v>
       </c>
       <c r="J13" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -2701,19 +2787,19 @@
         <v>15414324</v>
       </c>
       <c r="B14" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C14" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="H14" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="I14">
-        <v>11055651</v>
+        <v>13151160</v>
       </c>
       <c r="J14" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -2721,19 +2807,19 @@
         <v>12439390</v>
       </c>
       <c r="B15" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C15" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="H15" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="I15">
-        <v>38659485</v>
+        <v>13151158</v>
       </c>
       <c r="J15" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -2741,19 +2827,19 @@
         <v>14107560</v>
       </c>
       <c r="B16" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C16" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="H16" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="I16">
-        <v>9567647</v>
+        <v>17014694</v>
       </c>
       <c r="J16" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
@@ -2761,19 +2847,19 @@
         <v>53569741</v>
       </c>
       <c r="B17" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C17" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="H17" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="I17">
-        <v>40180424</v>
+        <v>17014693</v>
       </c>
       <c r="J17" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
@@ -2781,19 +2867,19 @@
         <v>75077119</v>
       </c>
       <c r="B18" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="C18" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="H18" t="s">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="I18">
-        <v>39228155</v>
+        <v>10978754</v>
       </c>
       <c r="J18" t="s">
-        <v>45</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
@@ -2801,19 +2887,19 @@
         <v>53583387</v>
       </c>
       <c r="B19" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C19" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="H19" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I19">
-        <v>38407975</v>
+        <v>19619417</v>
       </c>
       <c r="J19" t="s">
-        <v>46</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
@@ -2821,19 +2907,19 @@
         <v>51623281</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="C20" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H20" t="s">
         <v>29</v>
       </c>
       <c r="I20">
-        <v>38545387</v>
+        <v>39063227</v>
       </c>
       <c r="J20" t="s">
-        <v>47</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -2841,19 +2927,19 @@
         <v>51989601</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="C21" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>29</v>
+        <v>169</v>
       </c>
       <c r="I21" s="3">
-        <v>18816827</v>
+        <v>46995055</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>48</v>
+        <v>183</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
@@ -2861,19 +2947,19 @@
         <v>11192166</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C22" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H22" t="s">
-        <v>29</v>
+        <v>169</v>
       </c>
       <c r="I22">
-        <v>39278162</v>
+        <v>11744316</v>
       </c>
       <c r="J22" t="s">
-        <v>49</v>
+        <v>184</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
@@ -2881,19 +2967,19 @@
         <v>15812678</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C23" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H23" t="s">
-        <v>29</v>
+        <v>169</v>
       </c>
       <c r="I23">
-        <v>13100374</v>
+        <v>13069194</v>
       </c>
       <c r="J23" t="s">
-        <v>50</v>
+        <v>185</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
@@ -2901,19 +2987,19 @@
         <v>12091621</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C24" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H24" t="s">
-        <v>29</v>
+        <v>169</v>
       </c>
       <c r="I24">
-        <v>10855225</v>
+        <v>4125381</v>
       </c>
       <c r="J24" t="s">
-        <v>51</v>
+        <v>189</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
@@ -2921,19 +3007,19 @@
         <v>12143584</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C25" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H25" t="s">
-        <v>29</v>
+        <v>208</v>
       </c>
       <c r="I25">
-        <v>38490171</v>
+        <v>42839047</v>
       </c>
       <c r="J25" t="s">
-        <v>52</v>
+        <v>209</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
@@ -2941,19 +3027,19 @@
         <v>11192167</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C26" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H26" t="s">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="I26">
-        <v>38490170</v>
+        <v>4152612</v>
       </c>
       <c r="J26" t="s">
-        <v>53</v>
+        <v>214</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
@@ -2961,19 +3047,19 @@
         <v>12143581</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C27" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H27" t="s">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="I27">
-        <v>38417027</v>
+        <v>4152610</v>
       </c>
       <c r="J27" t="s">
-        <v>54</v>
+        <v>215</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
@@ -2981,19 +3067,19 @@
         <v>11192165</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C28" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H28" t="s">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="I28">
-        <v>13099542</v>
+        <v>34098917</v>
       </c>
       <c r="J28" t="s">
-        <v>55</v>
+        <v>220</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
@@ -3001,19 +3087,19 @@
         <v>11192163</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C29" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H29" t="s">
-        <v>56</v>
+        <v>656</v>
       </c>
       <c r="I29">
-        <v>10324264</v>
+        <v>49985232</v>
       </c>
       <c r="J29" t="s">
-        <v>57</v>
+        <v>224</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
@@ -3021,19 +3107,19 @@
         <v>11291291</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C30" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H30" t="s">
-        <v>58</v>
+        <v>656</v>
       </c>
       <c r="I30">
-        <v>39229235</v>
+        <v>50155408</v>
       </c>
       <c r="J30" t="s">
-        <v>59</v>
+        <v>225</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
@@ -3041,19 +3127,19 @@
         <v>16171214</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C31" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H31" t="s">
-        <v>58</v>
+        <v>656</v>
       </c>
       <c r="I31">
-        <v>12775098</v>
+        <v>41662266</v>
       </c>
       <c r="J31" t="s">
-        <v>60</v>
+        <v>228</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
@@ -3061,19 +3147,19 @@
         <v>12218847</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C32" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H32" t="s">
-        <v>58</v>
+        <v>656</v>
       </c>
       <c r="I32">
-        <v>12775097</v>
+        <v>13573385</v>
       </c>
       <c r="J32" t="s">
-        <v>61</v>
+        <v>234</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
@@ -3081,19 +3167,19 @@
         <v>15838517</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C33" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H33" t="s">
-        <v>58</v>
+        <v>656</v>
       </c>
       <c r="I33">
-        <v>12775096</v>
+        <v>42871700</v>
       </c>
       <c r="J33" t="s">
-        <v>62</v>
+        <v>235</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
@@ -3101,19 +3187,19 @@
         <v>12673238</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C34" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H34" t="s">
-        <v>58</v>
+        <v>656</v>
       </c>
       <c r="I34">
-        <v>13151160</v>
+        <v>39257536</v>
       </c>
       <c r="J34" t="s">
-        <v>63</v>
+        <v>236</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
@@ -3121,19 +3207,19 @@
         <v>37790051</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C35" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H35" t="s">
-        <v>58</v>
+        <v>656</v>
       </c>
       <c r="I35">
-        <v>13151158</v>
+        <v>37424126</v>
       </c>
       <c r="J35" t="s">
-        <v>64</v>
+        <v>237</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
@@ -3141,19 +3227,19 @@
         <v>37594934</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C36" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H36" t="s">
-        <v>58</v>
+        <v>656</v>
       </c>
       <c r="I36">
-        <v>35403063</v>
+        <v>36802614</v>
       </c>
       <c r="J36" t="s">
-        <v>65</v>
+        <v>238</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
@@ -3161,19 +3247,19 @@
         <v>15702671</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C37" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H37" t="s">
-        <v>58</v>
+        <v>656</v>
       </c>
       <c r="I37">
-        <v>13473750</v>
+        <v>36577826</v>
       </c>
       <c r="J37" t="s">
-        <v>66</v>
+        <v>239</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
@@ -3181,19 +3267,19 @@
         <v>39071990</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C38" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H38" t="s">
-        <v>58</v>
+        <v>656</v>
       </c>
       <c r="I38">
-        <v>17014694</v>
+        <v>26196255</v>
       </c>
       <c r="J38" t="s">
-        <v>67</v>
+        <v>240</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
@@ -3204,16 +3290,16 @@
         <v>91</v>
       </c>
       <c r="C39" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H39" t="s">
-        <v>58</v>
+        <v>656</v>
       </c>
       <c r="I39">
-        <v>17014693</v>
+        <v>26019234</v>
       </c>
       <c r="J39" t="s">
-        <v>68</v>
+        <v>245</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
@@ -3221,19 +3307,19 @@
         <v>39006854</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C40" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H40" t="s">
-        <v>58</v>
+        <v>656</v>
       </c>
       <c r="I40">
-        <v>13101218</v>
+        <v>25411238</v>
       </c>
       <c r="J40" t="s">
-        <v>69</v>
+        <v>248</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
@@ -3241,19 +3327,19 @@
         <v>39006857</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C41" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H41" t="s">
-        <v>58</v>
+        <v>656</v>
       </c>
       <c r="I41">
-        <v>13101217</v>
+        <v>26500515</v>
       </c>
       <c r="J41" t="s">
-        <v>70</v>
+        <v>251</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
@@ -3261,19 +3347,19 @@
         <v>39006855</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C42" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H42" t="s">
-        <v>58</v>
+        <v>656</v>
       </c>
       <c r="I42">
-        <v>16981939</v>
+        <v>36162739</v>
       </c>
       <c r="J42" t="s">
-        <v>71</v>
+        <v>252</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
@@ -3281,19 +3367,19 @@
         <v>51883980</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C43" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H43" t="s">
-        <v>58</v>
+        <v>656</v>
       </c>
       <c r="I43">
-        <v>12846219</v>
+        <v>39893389</v>
       </c>
       <c r="J43" t="s">
-        <v>72</v>
+        <v>253</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
@@ -3301,19 +3387,19 @@
         <v>52578670</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C44" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H44" t="s">
-        <v>58</v>
+        <v>656</v>
       </c>
       <c r="I44">
-        <v>17398556</v>
+        <v>39296173</v>
       </c>
       <c r="J44" t="s">
-        <v>73</v>
+        <v>254</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
@@ -3321,19 +3407,19 @@
         <v>52155531</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C45" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H45" t="s">
-        <v>58</v>
+        <v>141</v>
       </c>
       <c r="I45">
-        <v>16972627</v>
+        <v>42217758</v>
       </c>
       <c r="J45" t="s">
-        <v>74</v>
+        <v>282</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
@@ -3341,19 +3427,19 @@
         <v>15831347</v>
       </c>
       <c r="B46" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C46" t="s">
+        <v>630</v>
+      </c>
+      <c r="H46" t="s">
         <v>141</v>
       </c>
-      <c r="C46" t="s">
-        <v>633</v>
-      </c>
-      <c r="H46" t="s">
-        <v>58</v>
-      </c>
       <c r="I46">
-        <v>12846215</v>
+        <v>22403445</v>
       </c>
       <c r="J46" t="s">
-        <v>75</v>
+        <v>287</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
@@ -3361,19 +3447,19 @@
         <v>32548061</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C47" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H47" t="s">
-        <v>58</v>
+        <v>141</v>
       </c>
       <c r="I47">
-        <v>39663616</v>
+        <v>26257716</v>
       </c>
       <c r="J47" t="s">
-        <v>76</v>
+        <v>288</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
@@ -3381,19 +3467,19 @@
         <v>35876282</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C48" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H48" t="s">
-        <v>58</v>
+        <v>141</v>
       </c>
       <c r="I48">
-        <v>37843037</v>
+        <v>42486414</v>
       </c>
       <c r="J48" t="s">
-        <v>77</v>
+        <v>302</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
@@ -3401,19 +3487,19 @@
         <v>16805855</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C49" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H49" t="s">
-        <v>58</v>
+        <v>141</v>
       </c>
       <c r="I49">
-        <v>12465755</v>
+        <v>44695653</v>
       </c>
       <c r="J49" t="s">
-        <v>78</v>
+        <v>303</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
@@ -3421,19 +3507,19 @@
         <v>55381383</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C50" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H50" t="s">
-        <v>58</v>
+        <v>141</v>
       </c>
       <c r="I50">
-        <v>11671481</v>
+        <v>13405604</v>
       </c>
       <c r="J50" t="s">
-        <v>79</v>
+        <v>306</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
@@ -3441,19 +3527,19 @@
         <v>55449180</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C51" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H51" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="I51">
-        <v>12685386</v>
+        <v>39911056</v>
       </c>
       <c r="J51" t="s">
-        <v>80</v>
+        <v>334</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
@@ -3461,19 +3547,19 @@
         <v>55384739</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C52" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H52" t="s">
-        <v>58</v>
+        <v>656</v>
       </c>
       <c r="I52">
-        <v>12674974</v>
+        <v>51897600</v>
       </c>
       <c r="J52" t="s">
-        <v>81</v>
+        <v>347</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
@@ -3481,19 +3567,19 @@
         <v>55389336</v>
       </c>
       <c r="B53" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="C53" t="s">
         <v>630</v>
       </c>
-      <c r="C53" t="s">
-        <v>633</v>
-      </c>
       <c r="H53" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="I53">
-        <v>12674973</v>
+        <v>52990015</v>
       </c>
       <c r="J53" t="s">
-        <v>82</v>
+        <v>360</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
@@ -3501,19 +3587,19 @@
         <v>55609278</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C54" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H54" t="s">
         <v>58</v>
       </c>
       <c r="I54">
-        <v>27515992</v>
+        <v>55354052</v>
       </c>
       <c r="J54" t="s">
-        <v>83</v>
+        <v>379</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
@@ -3521,19 +3607,19 @@
         <v>71042279</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="C55" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="H55" t="s">
-        <v>58</v>
+        <v>169</v>
       </c>
       <c r="I55">
-        <v>18928667</v>
+        <v>55356388</v>
       </c>
       <c r="J55" t="s">
-        <v>84</v>
+        <v>387</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
@@ -3541,19 +3627,19 @@
         <v>67630646</v>
       </c>
       <c r="B56" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="C56" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="H56" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="I56">
-        <v>14218803</v>
+        <v>62377903</v>
       </c>
       <c r="J56" t="s">
-        <v>85</v>
+        <v>433</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
@@ -3561,19 +3647,19 @@
         <v>64971361</v>
       </c>
       <c r="B57" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C57" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="H57" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="I57">
-        <v>14218802</v>
+        <v>66097436</v>
       </c>
       <c r="J57" t="s">
-        <v>86</v>
+        <v>474</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
@@ -3581,19 +3667,19 @@
         <v>62421723</v>
       </c>
       <c r="B58" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C58" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="H58" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="I58">
-        <v>14473529</v>
+        <v>81675750</v>
       </c>
       <c r="J58" t="s">
-        <v>87</v>
+        <v>615</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
@@ -3601,19 +3687,19 @@
         <v>62374813</v>
       </c>
       <c r="B59" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C59" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="H59" t="s">
-        <v>58</v>
+        <v>169</v>
       </c>
       <c r="I59">
-        <v>25512595</v>
+        <v>81638306</v>
       </c>
       <c r="J59" t="s">
-        <v>20</v>
+        <v>659</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
@@ -3621,19 +3707,19 @@
         <v>68462854</v>
       </c>
       <c r="B60" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="C60" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="H60" t="s">
-        <v>58</v>
+        <v>656</v>
       </c>
       <c r="I60">
-        <v>25433097</v>
+        <v>81918457</v>
       </c>
       <c r="J60" t="s">
-        <v>88</v>
+        <v>660</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
@@ -3641,19 +3727,19 @@
         <v>64114088</v>
       </c>
       <c r="B61" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="C61" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="H61" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="I61">
-        <v>50012601</v>
+        <v>81988924</v>
       </c>
       <c r="J61" t="s">
-        <v>89</v>
+        <v>661</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
@@ -3664,16 +3750,16 @@
         <v>34</v>
       </c>
       <c r="C62" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="H62" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I62">
-        <v>52204284</v>
+        <v>82014131</v>
       </c>
       <c r="J62" t="s">
-        <v>91</v>
+        <v>662</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
@@ -3684,16 +3770,16 @@
         <v>36</v>
       </c>
       <c r="C63" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="H63" t="s">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c r="I63">
-        <v>52155531</v>
+        <v>81538523</v>
       </c>
       <c r="J63" t="s">
-        <v>93</v>
+        <v>663</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
@@ -3701,19 +3787,19 @@
         <v>11229298</v>
       </c>
       <c r="B64" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C64" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="H64" t="s">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c r="I64">
-        <v>10814871</v>
+        <v>3636926</v>
       </c>
       <c r="J64" t="s">
-        <v>95</v>
+        <v>31</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="82.5" x14ac:dyDescent="0.3">
@@ -3721,522 +3807,522 @@
         <v>37161537</v>
       </c>
       <c r="B65" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="H65" t="s">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c r="I65">
-        <v>31792560</v>
+        <v>3636927</v>
       </c>
       <c r="J65" t="s">
-        <v>96</v>
+        <v>32</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H66" t="s">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c r="I66">
-        <v>10694343</v>
+        <v>3636925</v>
       </c>
       <c r="J66" t="s">
-        <v>97</v>
+        <v>30</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H67" t="s">
-        <v>98</v>
+        <v>169</v>
       </c>
       <c r="I67">
-        <v>43431417</v>
+        <v>4125377</v>
       </c>
       <c r="J67" t="s">
-        <v>99</v>
+        <v>199</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H68" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I68">
-        <v>10978754</v>
+        <v>4152608</v>
       </c>
       <c r="J68" t="s">
-        <v>100</v>
+        <v>218</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H69" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I69">
-        <v>10974363</v>
+        <v>4152606</v>
       </c>
       <c r="J69" t="s">
-        <v>101</v>
+        <v>219</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H70" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I70">
-        <v>39376011</v>
+        <v>5332788</v>
       </c>
       <c r="J70" t="s">
-        <v>102</v>
+        <v>341</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H71" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I71">
-        <v>38310913</v>
+        <v>5332789</v>
       </c>
       <c r="J71" t="s">
-        <v>103</v>
+        <v>342</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H72" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="I72">
-        <v>40639939</v>
+        <v>5359040</v>
       </c>
       <c r="J72" t="s">
-        <v>104</v>
+        <v>268</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H73" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="I73">
-        <v>44581094</v>
+        <v>5462299</v>
       </c>
       <c r="J73" t="s">
-        <v>105</v>
+        <v>272</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H74" t="s">
-        <v>98</v>
+        <v>169</v>
       </c>
       <c r="I74">
-        <v>39270777</v>
+        <v>8122806</v>
       </c>
       <c r="J74" t="s">
-        <v>106</v>
+        <v>178</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H75" t="s">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="I75">
-        <v>45342904</v>
+        <v>8668649</v>
       </c>
       <c r="J75" t="s">
-        <v>107</v>
+        <v>265</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H76" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="I76">
-        <v>19619417</v>
+        <v>8837870</v>
       </c>
       <c r="J76" t="s">
-        <v>108</v>
+        <v>267</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H77" t="s">
-        <v>109</v>
+        <v>29</v>
       </c>
       <c r="I77">
-        <v>36606823</v>
+        <v>9567647</v>
       </c>
       <c r="J77" t="s">
-        <v>110</v>
+        <v>44</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H78" t="s">
-        <v>90</v>
+        <v>169</v>
       </c>
       <c r="I78">
-        <v>12585217</v>
+        <v>10121189</v>
       </c>
       <c r="J78" t="s">
-        <v>111</v>
+        <v>177</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H79" t="s">
-        <v>90</v>
+        <v>169</v>
       </c>
       <c r="I79">
-        <v>11511332</v>
+        <v>10124384</v>
       </c>
       <c r="J79" t="s">
-        <v>112</v>
+        <v>182</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H80" t="s">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="I80">
-        <v>12579597</v>
+        <v>10155238</v>
       </c>
       <c r="J80" t="s">
-        <v>113</v>
+        <v>263</v>
       </c>
     </row>
     <row r="81" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H81" t="s">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="I81">
-        <v>50153946</v>
+        <v>10324264</v>
       </c>
       <c r="J81" t="s">
-        <v>114</v>
+        <v>57</v>
       </c>
     </row>
     <row r="82" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H82" t="s">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="I82">
-        <v>50723598</v>
+        <v>10646862</v>
       </c>
       <c r="J82" t="s">
-        <v>13</v>
+        <v>307</v>
       </c>
     </row>
     <row r="83" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H83" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="I83">
-        <v>34464589</v>
+        <v>10694343</v>
       </c>
       <c r="J83" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
     </row>
     <row r="84" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H84" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="I84">
-        <v>12029130</v>
+        <v>10727917</v>
       </c>
       <c r="J84" t="s">
-        <v>117</v>
+        <v>299</v>
       </c>
     </row>
     <row r="85" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H85" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="I85">
-        <v>46962408</v>
+        <v>10814871</v>
       </c>
       <c r="J85" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
     </row>
     <row r="86" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H86" t="s">
-        <v>115</v>
+        <v>150</v>
       </c>
       <c r="I86">
-        <v>11874445</v>
+        <v>10816066</v>
       </c>
       <c r="J86" t="s">
-        <v>6</v>
+        <v>264</v>
       </c>
     </row>
     <row r="87" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H87" t="s">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="I87">
-        <v>25665354</v>
+        <v>10855225</v>
       </c>
       <c r="J87" t="s">
-        <v>119</v>
+        <v>51</v>
       </c>
     </row>
     <row r="88" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H88" t="s">
-        <v>115</v>
+        <v>169</v>
       </c>
       <c r="I88">
-        <v>46550390</v>
+        <v>10858043</v>
       </c>
       <c r="J88" t="s">
-        <v>120</v>
+        <v>198</v>
       </c>
     </row>
     <row r="89" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H89" t="s">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="I89">
-        <v>45573288</v>
+        <v>10929273</v>
       </c>
       <c r="J89" t="s">
-        <v>121</v>
+        <v>337</v>
       </c>
     </row>
     <row r="90" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H90" t="s">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="I90">
-        <v>34318450</v>
+        <v>10929274</v>
       </c>
       <c r="J90" t="s">
-        <v>122</v>
+        <v>336</v>
       </c>
     </row>
     <row r="91" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H91" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="I91">
-        <v>45701215</v>
+        <v>10974363</v>
       </c>
       <c r="J91" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
     </row>
     <row r="92" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H92" t="s">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="I92">
-        <v>15004955</v>
+        <v>11092035</v>
       </c>
       <c r="J92" t="s">
-        <v>123</v>
+        <v>38</v>
       </c>
     </row>
     <row r="93" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H93" t="s">
-        <v>115</v>
+        <v>169</v>
       </c>
       <c r="I93">
-        <v>25321998</v>
+        <v>11104533</v>
       </c>
       <c r="J93" t="s">
-        <v>124</v>
+        <v>181</v>
       </c>
     </row>
     <row r="94" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H94" t="s">
-        <v>115</v>
+        <v>656</v>
       </c>
       <c r="I94">
-        <v>25321996</v>
+        <v>11156528</v>
       </c>
       <c r="J94" t="s">
-        <v>125</v>
+        <v>241</v>
       </c>
     </row>
     <row r="95" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H95" t="s">
-        <v>115</v>
+        <v>56</v>
       </c>
       <c r="I95">
-        <v>46191377</v>
+        <v>11192163</v>
       </c>
       <c r="J95" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
     </row>
     <row r="96" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H96" t="s">
-        <v>115</v>
+        <v>56</v>
       </c>
       <c r="I96">
-        <v>45349063</v>
+        <v>11192165</v>
       </c>
       <c r="J96" t="s">
-        <v>7</v>
+        <v>145</v>
       </c>
     </row>
     <row r="97" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H97" t="s">
-        <v>115</v>
+        <v>56</v>
       </c>
       <c r="I97">
-        <v>44996967</v>
+        <v>11192166</v>
       </c>
       <c r="J97" t="s">
-        <v>18</v>
+        <v>164</v>
       </c>
     </row>
     <row r="98" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H98" t="s">
-        <v>115</v>
+        <v>56</v>
       </c>
       <c r="I98">
-        <v>15462869</v>
+        <v>11192167</v>
       </c>
       <c r="J98" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
     </row>
     <row r="99" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H99" t="s">
-        <v>115</v>
+        <v>169</v>
       </c>
       <c r="I99">
-        <v>15462868</v>
+        <v>11229298</v>
       </c>
       <c r="J99" t="s">
-        <v>128</v>
+        <v>172</v>
       </c>
     </row>
     <row r="100" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H100" t="s">
-        <v>115</v>
+        <v>169</v>
       </c>
       <c r="I100">
-        <v>46671749</v>
+        <v>11288089</v>
       </c>
       <c r="J100" t="s">
-        <v>129</v>
+        <v>180</v>
       </c>
     </row>
     <row r="101" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H101" t="s">
-        <v>115</v>
+        <v>150</v>
       </c>
       <c r="I101">
-        <v>35137369</v>
+        <v>11291291</v>
       </c>
       <c r="J101" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
     </row>
     <row r="102" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H102" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="I102">
-        <v>34320929</v>
+        <v>11511332</v>
       </c>
       <c r="J102" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
     </row>
     <row r="103" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H103" t="s">
-        <v>115</v>
+        <v>656</v>
       </c>
       <c r="I103">
-        <v>34320928</v>
+        <v>11670520</v>
       </c>
       <c r="J103" t="s">
-        <v>132</v>
+        <v>10</v>
       </c>
     </row>
     <row r="104" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H104" t="s">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="I104">
-        <v>23200605</v>
+        <v>11671480</v>
       </c>
       <c r="J104" t="s">
-        <v>133</v>
+        <v>163</v>
       </c>
     </row>
     <row r="105" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H105" t="s">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="I105">
-        <v>23200603</v>
+        <v>11671481</v>
       </c>
       <c r="J105" t="s">
-        <v>134</v>
+        <v>79</v>
       </c>
     </row>
     <row r="106" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H106" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="I106">
-        <v>43571361</v>
+        <v>11681261</v>
       </c>
       <c r="J106" t="s">
-        <v>135</v>
+        <v>284</v>
       </c>
     </row>
     <row r="107" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H107" t="s">
-        <v>115</v>
+        <v>150</v>
       </c>
       <c r="I107">
-        <v>43571360</v>
+        <v>11765770</v>
       </c>
       <c r="J107" t="s">
-        <v>136</v>
+        <v>259</v>
       </c>
     </row>
     <row r="108" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H108" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I108">
-        <v>34330469</v>
+        <v>11874445</v>
       </c>
       <c r="J108" t="s">
-        <v>137</v>
+        <v>6</v>
       </c>
     </row>
     <row r="109" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H109" t="s">
+        <v>113</v>
+      </c>
+      <c r="I109">
+        <v>12029130</v>
+      </c>
+      <c r="J109" t="s">
         <v>115</v>
-      </c>
-      <c r="I109">
-        <v>34331612</v>
-      </c>
-      <c r="J109" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="110" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H110" t="s">
-        <v>115</v>
+        <v>150</v>
       </c>
       <c r="I110">
-        <v>34352694</v>
+        <v>12038103</v>
       </c>
       <c r="J110" t="s">
-        <v>139</v>
+        <v>261</v>
       </c>
     </row>
     <row r="111" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H111" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="I111">
-        <v>39063227</v>
+        <v>12091621</v>
       </c>
       <c r="J111" t="s">
         <v>140</v>
@@ -4244,32 +4330,32 @@
     </row>
     <row r="112" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H112" t="s">
-        <v>56</v>
+        <v>150</v>
       </c>
       <c r="I112">
-        <v>15831347</v>
+        <v>12095120</v>
       </c>
       <c r="J112" t="s">
-        <v>141</v>
+        <v>258</v>
       </c>
     </row>
     <row r="113" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H113" t="s">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="I113">
-        <v>12091621</v>
+        <v>12126317</v>
       </c>
       <c r="J113" t="s">
-        <v>142</v>
+        <v>321</v>
       </c>
     </row>
     <row r="114" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H114" t="s">
-        <v>143</v>
+        <v>56</v>
       </c>
       <c r="I114">
-        <v>16805855</v>
+        <v>12143581</v>
       </c>
       <c r="J114" t="s">
         <v>144</v>
@@ -4280,142 +4366,142 @@
         <v>56</v>
       </c>
       <c r="I115">
-        <v>15812678</v>
+        <v>12143584</v>
       </c>
       <c r="J115" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="116" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H116" t="s">
-        <v>56</v>
+        <v>150</v>
       </c>
       <c r="I116">
-        <v>12143581</v>
+        <v>12218847</v>
       </c>
       <c r="J116" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="117" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H117" t="s">
-        <v>56</v>
+        <v>656</v>
       </c>
       <c r="I117">
-        <v>11192165</v>
+        <v>12263163</v>
       </c>
       <c r="J117" t="s">
-        <v>147</v>
+        <v>232</v>
       </c>
     </row>
     <row r="118" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H118" t="s">
-        <v>56</v>
+        <v>169</v>
       </c>
       <c r="I118">
-        <v>11192163</v>
+        <v>12263239</v>
       </c>
       <c r="J118" t="s">
-        <v>148</v>
+        <v>203</v>
       </c>
     </row>
     <row r="119" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H119" t="s">
-        <v>56</v>
+        <v>141</v>
       </c>
       <c r="I119">
-        <v>12143584</v>
+        <v>12362063</v>
       </c>
       <c r="J119" t="s">
-        <v>149</v>
+        <v>308</v>
       </c>
     </row>
     <row r="120" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H120" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I120">
-        <v>11192167</v>
+        <v>12434130</v>
       </c>
       <c r="J120" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
     </row>
     <row r="121" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H121" t="s">
-        <v>90</v>
+        <v>169</v>
       </c>
       <c r="I121">
-        <v>12673238</v>
+        <v>12439390</v>
       </c>
       <c r="J121" t="s">
-        <v>151</v>
+        <v>202</v>
       </c>
     </row>
     <row r="122" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H122" t="s">
-        <v>152</v>
+        <v>58</v>
       </c>
       <c r="I122">
-        <v>15838517</v>
+        <v>12465755</v>
       </c>
       <c r="J122" t="s">
-        <v>153</v>
+        <v>78</v>
       </c>
     </row>
     <row r="123" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H123" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="I123">
-        <v>12218847</v>
+        <v>12481759</v>
       </c>
       <c r="J123" t="s">
-        <v>154</v>
+        <v>290</v>
       </c>
     </row>
     <row r="124" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H124" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="I124">
-        <v>16171214</v>
+        <v>12481760</v>
       </c>
       <c r="J124" t="s">
-        <v>155</v>
+        <v>289</v>
       </c>
     </row>
     <row r="125" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H125" t="s">
-        <v>152</v>
+        <v>656</v>
       </c>
       <c r="I125">
-        <v>11291291</v>
+        <v>12496637</v>
       </c>
       <c r="J125" t="s">
-        <v>156</v>
+        <v>247</v>
       </c>
     </row>
     <row r="126" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H126" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="I126">
-        <v>14134779</v>
+        <v>12579597</v>
       </c>
       <c r="J126" t="s">
-        <v>157</v>
+        <v>111</v>
       </c>
     </row>
     <row r="127" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H127" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="I127">
-        <v>14134778</v>
+        <v>12585217</v>
       </c>
       <c r="J127" t="s">
-        <v>158</v>
+        <v>109</v>
       </c>
     </row>
     <row r="128" spans="8:10" x14ac:dyDescent="0.3">
@@ -4423,10 +4509,10 @@
         <v>90</v>
       </c>
       <c r="I128">
-        <v>37790051</v>
+        <v>12673237</v>
       </c>
       <c r="J128" t="s">
-        <v>159</v>
+        <v>317</v>
       </c>
     </row>
     <row r="129" spans="8:10" x14ac:dyDescent="0.3">
@@ -4434,54 +4520,54 @@
         <v>90</v>
       </c>
       <c r="I129">
-        <v>39071990</v>
+        <v>12673238</v>
       </c>
       <c r="J129" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
     </row>
     <row r="130" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H130" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="I130">
-        <v>39006857</v>
+        <v>12674973</v>
       </c>
       <c r="J130" t="s">
-        <v>161</v>
+        <v>82</v>
       </c>
     </row>
     <row r="131" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H131" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="I131">
-        <v>39006855</v>
+        <v>12674974</v>
       </c>
       <c r="J131" t="s">
-        <v>162</v>
+        <v>81</v>
       </c>
     </row>
     <row r="132" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H132" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="I132">
-        <v>39006854</v>
+        <v>12685386</v>
       </c>
       <c r="J132" t="s">
-        <v>163</v>
+        <v>80</v>
       </c>
     </row>
     <row r="133" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H133" t="s">
-        <v>58</v>
+        <v>169</v>
       </c>
       <c r="I133">
-        <v>12434130</v>
+        <v>12757668</v>
       </c>
       <c r="J133" t="s">
-        <v>164</v>
+        <v>331</v>
       </c>
     </row>
     <row r="134" spans="8:10" x14ac:dyDescent="0.3">
@@ -4489,43 +4575,43 @@
         <v>58</v>
       </c>
       <c r="I134">
-        <v>11671480</v>
+        <v>12775096</v>
       </c>
       <c r="J134" t="s">
-        <v>165</v>
+        <v>62</v>
       </c>
     </row>
     <row r="135" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H135" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I135">
-        <v>11192166</v>
+        <v>12775097</v>
       </c>
       <c r="J135" t="s">
-        <v>166</v>
+        <v>61</v>
       </c>
     </row>
     <row r="136" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H136" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="I136">
-        <v>37594934</v>
+        <v>12775098</v>
       </c>
       <c r="J136" t="s">
-        <v>167</v>
+        <v>60</v>
       </c>
     </row>
     <row r="137" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H137" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="I137">
-        <v>32548061</v>
+        <v>12846215</v>
       </c>
       <c r="J137" t="s">
-        <v>168</v>
+        <v>75</v>
       </c>
     </row>
     <row r="138" spans="8:10" x14ac:dyDescent="0.3">
@@ -4533,1085 +4619,1085 @@
         <v>58</v>
       </c>
       <c r="I138">
-        <v>32711387</v>
+        <v>12846219</v>
       </c>
       <c r="J138" t="s">
-        <v>169</v>
+        <v>72</v>
       </c>
     </row>
     <row r="139" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H139" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="I139">
-        <v>32710937</v>
+        <v>13004238</v>
       </c>
       <c r="J139" t="s">
-        <v>170</v>
+        <v>36</v>
       </c>
     </row>
     <row r="140" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H140" t="s">
-        <v>171</v>
+        <v>29</v>
       </c>
       <c r="I140">
-        <v>35876282</v>
+        <v>13099542</v>
       </c>
       <c r="J140" t="s">
-        <v>172</v>
+        <v>55</v>
       </c>
     </row>
     <row r="141" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H141" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I141">
-        <v>15702671</v>
+        <v>13100374</v>
       </c>
       <c r="J141" t="s">
-        <v>173</v>
+        <v>50</v>
       </c>
     </row>
     <row r="142" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H142" t="s">
-        <v>171</v>
+        <v>58</v>
       </c>
       <c r="I142">
-        <v>11229298</v>
+        <v>13101217</v>
       </c>
       <c r="J142" t="s">
-        <v>174</v>
+        <v>70</v>
       </c>
     </row>
     <row r="143" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H143" t="s">
-        <v>171</v>
+        <v>58</v>
       </c>
       <c r="I143">
-        <v>50709616</v>
+        <v>13101218</v>
       </c>
       <c r="J143" t="s">
-        <v>175</v>
+        <v>69</v>
       </c>
     </row>
     <row r="144" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H144" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I144">
-        <v>37034524</v>
+        <v>13195811</v>
       </c>
       <c r="J144" t="s">
-        <v>176</v>
+        <v>664</v>
       </c>
     </row>
     <row r="145" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H145" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I145">
-        <v>14299890</v>
+        <v>13195957</v>
       </c>
       <c r="J145" t="s">
-        <v>177</v>
+        <v>8</v>
       </c>
     </row>
     <row r="146" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H146" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I146">
-        <v>13195811</v>
+        <v>13373616</v>
       </c>
       <c r="J146" t="s">
-        <v>178</v>
+        <v>330</v>
       </c>
     </row>
     <row r="147" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H147" t="s">
-        <v>171</v>
+        <v>58</v>
       </c>
       <c r="I147">
-        <v>36608029</v>
+        <v>13473750</v>
       </c>
       <c r="J147" t="s">
-        <v>179</v>
+        <v>66</v>
       </c>
     </row>
     <row r="148" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H148" t="s">
-        <v>171</v>
+        <v>141</v>
       </c>
       <c r="I148">
-        <v>13195957</v>
+        <v>13644995</v>
       </c>
       <c r="J148" t="s">
-        <v>8</v>
+        <v>301</v>
       </c>
     </row>
     <row r="149" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H149" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I149">
-        <v>10121189</v>
+        <v>13745117</v>
       </c>
       <c r="J149" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
     </row>
     <row r="150" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H150" t="s">
-        <v>171</v>
+        <v>656</v>
       </c>
       <c r="I150">
-        <v>8122806</v>
+        <v>13959023</v>
       </c>
       <c r="J150" t="s">
-        <v>181</v>
+        <v>246</v>
       </c>
     </row>
     <row r="151" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H151" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I151">
-        <v>48477550</v>
+        <v>14107560</v>
       </c>
       <c r="J151" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
     </row>
     <row r="152" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H152" t="s">
-        <v>171</v>
+        <v>58</v>
       </c>
       <c r="I152">
-        <v>11288089</v>
+        <v>14134778</v>
       </c>
       <c r="J152" t="s">
-        <v>183</v>
+        <v>156</v>
       </c>
     </row>
     <row r="153" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H153" t="s">
-        <v>171</v>
+        <v>58</v>
       </c>
       <c r="I153">
-        <v>11104533</v>
+        <v>14134779</v>
       </c>
       <c r="J153" t="s">
-        <v>184</v>
+        <v>155</v>
       </c>
     </row>
     <row r="154" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H154" t="s">
-        <v>171</v>
+        <v>58</v>
       </c>
       <c r="I154">
-        <v>10124384</v>
+        <v>14218802</v>
       </c>
       <c r="J154" t="s">
-        <v>185</v>
+        <v>86</v>
       </c>
     </row>
     <row r="155" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H155" t="s">
-        <v>171</v>
+        <v>58</v>
       </c>
       <c r="I155">
-        <v>46995055</v>
+        <v>14218803</v>
       </c>
       <c r="J155" t="s">
-        <v>186</v>
+        <v>85</v>
       </c>
     </row>
     <row r="156" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H156" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I156">
-        <v>11744316</v>
+        <v>14299890</v>
       </c>
       <c r="J156" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
     </row>
     <row r="157" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H157" t="s">
-        <v>171</v>
+        <v>58</v>
       </c>
       <c r="I157">
-        <v>13069194</v>
+        <v>14473529</v>
       </c>
       <c r="J157" t="s">
-        <v>188</v>
+        <v>87</v>
       </c>
     </row>
     <row r="158" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H158" t="s">
-        <v>171</v>
+        <v>90</v>
       </c>
       <c r="I158">
-        <v>19365568</v>
+        <v>14488275</v>
       </c>
       <c r="J158" t="s">
-        <v>189</v>
+        <v>323</v>
       </c>
     </row>
     <row r="159" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H159" t="s">
-        <v>171</v>
+        <v>90</v>
       </c>
       <c r="I159">
-        <v>47861038</v>
+        <v>14719737</v>
       </c>
       <c r="J159" t="s">
-        <v>190</v>
+        <v>4</v>
       </c>
     </row>
     <row r="160" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H160" t="s">
-        <v>171</v>
+        <v>90</v>
       </c>
       <c r="I160">
-        <v>43252471</v>
+        <v>14878740</v>
       </c>
       <c r="J160" t="s">
-        <v>191</v>
+        <v>316</v>
       </c>
     </row>
     <row r="161" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H161" t="s">
-        <v>171</v>
+        <v>113</v>
       </c>
       <c r="I161">
-        <v>4125381</v>
+        <v>15004955</v>
       </c>
       <c r="J161" t="s">
-        <v>192</v>
+        <v>121</v>
       </c>
     </row>
     <row r="162" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H162" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I162">
-        <v>38183281</v>
+        <v>15414324</v>
       </c>
       <c r="J162" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="163" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H163" t="s">
-        <v>171</v>
+        <v>113</v>
       </c>
       <c r="I163">
-        <v>14107560</v>
+        <v>15462868</v>
       </c>
       <c r="J163" t="s">
-        <v>194</v>
+        <v>126</v>
       </c>
     </row>
     <row r="164" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H164" t="s">
-        <v>171</v>
+        <v>113</v>
       </c>
       <c r="I164">
-        <v>44916947</v>
+        <v>15462869</v>
       </c>
       <c r="J164" t="s">
-        <v>195</v>
+        <v>125</v>
       </c>
     </row>
     <row r="165" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H165" t="s">
+        <v>90</v>
+      </c>
+      <c r="I165">
+        <v>15702671</v>
+      </c>
+      <c r="J165" t="s">
         <v>171</v>
-      </c>
-      <c r="I165">
-        <v>40640374</v>
-      </c>
-      <c r="J165" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="166" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H166" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="I166">
-        <v>13745117</v>
+        <v>15757638</v>
       </c>
       <c r="J166" t="s">
-        <v>197</v>
+        <v>260</v>
       </c>
     </row>
     <row r="167" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H167" t="s">
-        <v>171</v>
+        <v>90</v>
       </c>
       <c r="I167">
-        <v>15414324</v>
+        <v>15795597</v>
       </c>
       <c r="J167" t="s">
-        <v>198</v>
+        <v>320</v>
       </c>
     </row>
     <row r="168" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H168" t="s">
-        <v>171</v>
+        <v>56</v>
       </c>
       <c r="I168">
-        <v>35192489</v>
+        <v>15812678</v>
       </c>
       <c r="J168" t="s">
-        <v>199</v>
+        <v>143</v>
       </c>
     </row>
     <row r="169" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H169" t="s">
-        <v>171</v>
+        <v>90</v>
       </c>
       <c r="I169">
-        <v>40982029</v>
+        <v>15825326</v>
       </c>
       <c r="J169" t="s">
-        <v>200</v>
+        <v>310</v>
       </c>
     </row>
     <row r="170" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H170" t="s">
-        <v>171</v>
+        <v>656</v>
       </c>
       <c r="I170">
-        <v>10858043</v>
+        <v>15826960</v>
       </c>
       <c r="J170" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
     </row>
     <row r="171" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H171" t="s">
-        <v>171</v>
+        <v>56</v>
       </c>
       <c r="I171">
-        <v>4125377</v>
+        <v>15831347</v>
       </c>
       <c r="J171" t="s">
-        <v>202</v>
+        <v>139</v>
       </c>
     </row>
     <row r="172" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H172" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="I172">
-        <v>26426530</v>
+        <v>15838517</v>
       </c>
       <c r="J172" t="s">
-        <v>203</v>
+        <v>151</v>
       </c>
     </row>
     <row r="173" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H173" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="I173">
-        <v>18980681</v>
+        <v>16171214</v>
       </c>
       <c r="J173" t="s">
-        <v>204</v>
+        <v>153</v>
       </c>
     </row>
     <row r="174" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H174" t="s">
-        <v>171</v>
+        <v>205</v>
       </c>
       <c r="I174">
-        <v>12439390</v>
+        <v>16179047</v>
       </c>
       <c r="J174" t="s">
-        <v>205</v>
+        <v>12</v>
       </c>
     </row>
     <row r="175" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H175" t="s">
-        <v>171</v>
+        <v>107</v>
       </c>
       <c r="I175">
-        <v>12263239</v>
+        <v>16303007</v>
       </c>
       <c r="J175" t="s">
-        <v>206</v>
+        <v>270</v>
       </c>
     </row>
     <row r="176" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H176" t="s">
-        <v>171</v>
+        <v>141</v>
       </c>
       <c r="I176">
-        <v>50725354</v>
+        <v>16805855</v>
       </c>
       <c r="J176" t="s">
-        <v>207</v>
+        <v>142</v>
       </c>
     </row>
     <row r="177" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H177" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="I177">
-        <v>16179047</v>
+        <v>16806254</v>
       </c>
       <c r="J177" t="s">
-        <v>12</v>
+        <v>314</v>
       </c>
     </row>
     <row r="178" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H178" t="s">
-        <v>208</v>
+        <v>58</v>
       </c>
       <c r="I178">
-        <v>20815743</v>
+        <v>16981939</v>
       </c>
       <c r="J178" t="s">
-        <v>209</v>
+        <v>71</v>
       </c>
     </row>
     <row r="179" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H179" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="I179">
-        <v>39651008</v>
+        <v>17579394</v>
       </c>
       <c r="J179" t="s">
-        <v>210</v>
+        <v>325</v>
       </c>
     </row>
     <row r="180" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H180" t="s">
-        <v>211</v>
+        <v>90</v>
       </c>
       <c r="I180">
-        <v>42839047</v>
+        <v>17579662</v>
       </c>
       <c r="J180" t="s">
-        <v>212</v>
+        <v>318</v>
       </c>
     </row>
     <row r="181" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H181" t="s">
-        <v>211</v>
+        <v>141</v>
       </c>
       <c r="I181">
-        <v>38455497</v>
+        <v>18291047</v>
       </c>
       <c r="J181" t="s">
-        <v>213</v>
+        <v>298</v>
       </c>
     </row>
     <row r="182" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H182" t="s">
-        <v>211</v>
+        <v>58</v>
       </c>
       <c r="I182">
-        <v>37173787</v>
+        <v>18928667</v>
       </c>
       <c r="J182" t="s">
-        <v>214</v>
+        <v>84</v>
       </c>
     </row>
     <row r="183" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H183" t="s">
-        <v>98</v>
+        <v>169</v>
       </c>
       <c r="I183">
-        <v>42913903</v>
+        <v>18980681</v>
       </c>
       <c r="J183" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
     </row>
     <row r="184" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H184" t="s">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="I184">
-        <v>41864123</v>
+        <v>19104731</v>
       </c>
       <c r="J184" t="s">
-        <v>216</v>
+        <v>294</v>
       </c>
     </row>
     <row r="185" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H185" t="s">
-        <v>98</v>
+        <v>29</v>
       </c>
       <c r="I185">
-        <v>4152612</v>
+        <v>19213859</v>
       </c>
       <c r="J185" t="s">
-        <v>217</v>
+        <v>34</v>
       </c>
     </row>
     <row r="186" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H186" t="s">
-        <v>98</v>
+        <v>169</v>
       </c>
       <c r="I186">
-        <v>4152610</v>
+        <v>19365568</v>
       </c>
       <c r="J186" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
     </row>
     <row r="187" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H187" t="s">
-        <v>98</v>
+        <v>29</v>
       </c>
       <c r="I187">
-        <v>35896315</v>
+        <v>20341619</v>
       </c>
       <c r="J187" t="s">
-        <v>219</v>
+        <v>37</v>
       </c>
     </row>
     <row r="188" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H188" t="s">
-        <v>98</v>
+        <v>205</v>
       </c>
       <c r="I188">
-        <v>31743599</v>
+        <v>20815743</v>
       </c>
       <c r="J188" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
     </row>
     <row r="189" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H189" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="I189">
-        <v>4152608</v>
+        <v>22119013</v>
       </c>
       <c r="J189" t="s">
-        <v>221</v>
+        <v>319</v>
       </c>
     </row>
     <row r="190" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H190" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="I190">
-        <v>4152606</v>
+        <v>22441147</v>
       </c>
       <c r="J190" t="s">
-        <v>222</v>
+        <v>280</v>
       </c>
     </row>
     <row r="191" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H191" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="I191">
-        <v>34098917</v>
+        <v>23200603</v>
       </c>
       <c r="J191" t="s">
-        <v>223</v>
+        <v>132</v>
       </c>
     </row>
     <row r="192" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H192" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="I192">
-        <v>34801754</v>
+        <v>23200605</v>
       </c>
       <c r="J192" t="s">
-        <v>224</v>
+        <v>131</v>
       </c>
     </row>
     <row r="193" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H193" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I193">
-        <v>37639889</v>
+        <v>24832169</v>
       </c>
       <c r="J193" t="s">
-        <v>225</v>
+        <v>327</v>
       </c>
     </row>
     <row r="194" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H194" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="I194">
-        <v>51533853</v>
+        <v>25321996</v>
       </c>
       <c r="J194" t="s">
-        <v>226</v>
+        <v>123</v>
       </c>
     </row>
     <row r="195" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H195" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="I195">
-        <v>49985232</v>
+        <v>25321998</v>
       </c>
       <c r="J195" t="s">
-        <v>227</v>
+        <v>122</v>
       </c>
     </row>
     <row r="196" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H196" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="I196">
-        <v>50155408</v>
+        <v>25433097</v>
       </c>
       <c r="J196" t="s">
-        <v>228</v>
+        <v>88</v>
       </c>
     </row>
     <row r="197" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H197" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="I197">
-        <v>35401181</v>
+        <v>25512595</v>
       </c>
       <c r="J197" t="s">
-        <v>229</v>
+        <v>20</v>
       </c>
     </row>
     <row r="198" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H198" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="I198">
-        <v>38157908</v>
+        <v>25665354</v>
       </c>
       <c r="J198" t="s">
-        <v>230</v>
+        <v>117</v>
       </c>
     </row>
     <row r="199" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H199" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I199">
-        <v>41662266</v>
+        <v>26375455</v>
       </c>
       <c r="J199" t="s">
-        <v>231</v>
+        <v>311</v>
       </c>
     </row>
     <row r="200" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H200" t="s">
-        <v>92</v>
+        <v>169</v>
       </c>
       <c r="I200">
-        <v>47936724</v>
+        <v>26426530</v>
       </c>
       <c r="J200" t="s">
-        <v>232</v>
+        <v>200</v>
       </c>
     </row>
     <row r="201" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H201" t="s">
-        <v>92</v>
+        <v>656</v>
       </c>
       <c r="I201">
-        <v>38417806</v>
+        <v>26491140</v>
       </c>
       <c r="J201" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
     </row>
     <row r="202" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H202" t="s">
-        <v>92</v>
+        <v>656</v>
       </c>
       <c r="I202">
-        <v>38158208</v>
+        <v>27011098</v>
       </c>
       <c r="J202" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
     </row>
     <row r="203" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H203" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I203">
-        <v>12263163</v>
+        <v>27056005</v>
       </c>
       <c r="J203" t="s">
-        <v>235</v>
+        <v>326</v>
       </c>
     </row>
     <row r="204" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H204" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="I204">
-        <v>15826960</v>
+        <v>27303665</v>
       </c>
       <c r="J204" t="s">
-        <v>236</v>
+        <v>271</v>
       </c>
     </row>
     <row r="205" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H205" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="I205">
-        <v>13573385</v>
+        <v>27515992</v>
       </c>
       <c r="J205" t="s">
-        <v>237</v>
+        <v>83</v>
       </c>
     </row>
     <row r="206" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H206" t="s">
-        <v>92</v>
+        <v>141</v>
       </c>
       <c r="I206">
-        <v>42871700</v>
+        <v>29258063</v>
       </c>
       <c r="J206" t="s">
-        <v>238</v>
+        <v>305</v>
       </c>
     </row>
     <row r="207" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H207" t="s">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c r="I207">
-        <v>39257536</v>
+        <v>29266932</v>
       </c>
       <c r="J207" t="s">
-        <v>239</v>
+        <v>40</v>
       </c>
     </row>
     <row r="208" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H208" t="s">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c r="I208">
-        <v>37424126</v>
+        <v>29280326</v>
       </c>
       <c r="J208" t="s">
-        <v>240</v>
+        <v>339</v>
       </c>
     </row>
     <row r="209" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H209" t="s">
-        <v>92</v>
+        <v>141</v>
       </c>
       <c r="I209">
-        <v>36802614</v>
+        <v>30405071</v>
       </c>
       <c r="J209" t="s">
-        <v>241</v>
+        <v>286</v>
       </c>
     </row>
     <row r="210" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H210" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I210">
-        <v>36577826</v>
+        <v>31743599</v>
       </c>
       <c r="J210" t="s">
-        <v>242</v>
+        <v>217</v>
       </c>
     </row>
     <row r="211" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H211" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I211">
-        <v>35149611</v>
+        <v>31792560</v>
       </c>
       <c r="J211" t="s">
-        <v>2</v>
+        <v>94</v>
       </c>
     </row>
     <row r="212" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H212" t="s">
-        <v>92</v>
+        <v>656</v>
       </c>
       <c r="I212">
-        <v>26196255</v>
+        <v>31886592</v>
       </c>
       <c r="J212" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
     </row>
     <row r="213" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H213" t="s">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c r="I213">
-        <v>11156528</v>
+        <v>32548061</v>
       </c>
       <c r="J213" t="s">
-        <v>244</v>
+        <v>166</v>
       </c>
     </row>
     <row r="214" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H214" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="I214">
-        <v>38415503</v>
+        <v>32710937</v>
       </c>
       <c r="J214" t="s">
-        <v>245</v>
+        <v>168</v>
       </c>
     </row>
     <row r="215" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H215" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="I215">
-        <v>37244806</v>
+        <v>32711387</v>
       </c>
       <c r="J215" t="s">
-        <v>246</v>
+        <v>167</v>
       </c>
     </row>
     <row r="216" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H216" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="I216">
-        <v>27011098</v>
+        <v>34318450</v>
       </c>
       <c r="J216" t="s">
-        <v>247</v>
+        <v>120</v>
       </c>
     </row>
     <row r="217" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H217" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="I217">
-        <v>26019234</v>
+        <v>34320928</v>
       </c>
       <c r="J217" t="s">
-        <v>248</v>
+        <v>130</v>
       </c>
     </row>
     <row r="218" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H218" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="I218">
-        <v>13959023</v>
+        <v>34320929</v>
       </c>
       <c r="J218" t="s">
-        <v>249</v>
+        <v>129</v>
       </c>
     </row>
     <row r="219" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H219" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="I219">
-        <v>12496637</v>
+        <v>34330469</v>
       </c>
       <c r="J219" t="s">
-        <v>250</v>
+        <v>135</v>
       </c>
     </row>
     <row r="220" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H220" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="I220">
-        <v>25411238</v>
+        <v>34331612</v>
       </c>
       <c r="J220" t="s">
-        <v>251</v>
+        <v>136</v>
       </c>
     </row>
     <row r="221" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H221" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="I221">
-        <v>38312169</v>
+        <v>34348663</v>
       </c>
       <c r="J221" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
     </row>
     <row r="222" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H222" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="I222">
-        <v>31886592</v>
+        <v>34352694</v>
       </c>
       <c r="J222" t="s">
-        <v>253</v>
+        <v>137</v>
       </c>
     </row>
     <row r="223" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H223" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="I223">
-        <v>11670520</v>
+        <v>34464589</v>
       </c>
       <c r="J223" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
     </row>
     <row r="224" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H224" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="I224">
-        <v>26500515</v>
+        <v>34535085</v>
       </c>
       <c r="J224" t="s">
-        <v>254</v>
+        <v>278</v>
       </c>
     </row>
     <row r="225" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H225" t="s">
-        <v>92</v>
+        <v>656</v>
       </c>
       <c r="I225">
-        <v>36162739</v>
+        <v>34801754</v>
       </c>
       <c r="J225" t="s">
-        <v>255</v>
+        <v>221</v>
       </c>
     </row>
     <row r="226" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H226" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="I226">
-        <v>39893389</v>
+        <v>34991467</v>
       </c>
       <c r="J226" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
     </row>
     <row r="227" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H227" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="I227">
-        <v>39296173</v>
+        <v>35137369</v>
       </c>
       <c r="J227" t="s">
-        <v>257</v>
+        <v>128</v>
       </c>
     </row>
     <row r="228" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H228" t="s">
-        <v>92</v>
+        <v>656</v>
       </c>
       <c r="I228">
-        <v>26491140</v>
+        <v>35149611</v>
       </c>
       <c r="J228" t="s">
-        <v>258</v>
+        <v>2</v>
       </c>
     </row>
     <row r="229" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H229" t="s">
-        <v>56</v>
+        <v>169</v>
       </c>
       <c r="I229">
-        <v>49473587</v>
+        <v>35192489</v>
       </c>
       <c r="J229" t="s">
-        <v>259</v>
+        <v>196</v>
       </c>
     </row>
     <row r="230" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H230" t="s">
-        <v>92</v>
+        <v>656</v>
       </c>
       <c r="I230">
-        <v>50326931</v>
+        <v>35401181</v>
       </c>
       <c r="J230" t="s">
-        <v>260</v>
+        <v>226</v>
       </c>
     </row>
     <row r="231" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H231" t="s">
-        <v>152</v>
+        <v>58</v>
       </c>
       <c r="I231">
-        <v>12095120</v>
+        <v>35403063</v>
       </c>
       <c r="J231" t="s">
-        <v>261</v>
+        <v>65</v>
       </c>
     </row>
     <row r="232" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H232" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="I232">
-        <v>11765770</v>
+        <v>35876282</v>
       </c>
       <c r="J232" t="s">
-        <v>262</v>
+        <v>170</v>
       </c>
     </row>
     <row r="233" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H233" t="s">
-        <v>152</v>
+        <v>96</v>
       </c>
       <c r="I233">
-        <v>15757638</v>
+        <v>35896315</v>
       </c>
       <c r="J233" t="s">
-        <v>263</v>
+        <v>216</v>
       </c>
     </row>
     <row r="234" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H234" t="s">
-        <v>152</v>
+        <v>107</v>
       </c>
       <c r="I234">
-        <v>12038103</v>
+        <v>36606823</v>
       </c>
       <c r="J234" t="s">
-        <v>264</v>
+        <v>108</v>
       </c>
     </row>
     <row r="235" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H235" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="I235">
-        <v>46801171</v>
+        <v>36608029</v>
       </c>
       <c r="J235" t="s">
-        <v>265</v>
+        <v>176</v>
       </c>
     </row>
     <row r="236" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H236" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I236">
-        <v>10155238</v>
+        <v>36635604</v>
       </c>
       <c r="J236" t="s">
         <v>266</v>
@@ -5619,508 +5705,508 @@
     </row>
     <row r="237" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H237" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="I237">
-        <v>10816066</v>
+        <v>36682232</v>
       </c>
       <c r="J237" t="s">
-        <v>267</v>
+        <v>291</v>
       </c>
     </row>
     <row r="238" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H238" t="s">
-        <v>152</v>
+        <v>107</v>
       </c>
       <c r="I238">
-        <v>8668649</v>
+        <v>36811023</v>
       </c>
       <c r="J238" t="s">
-        <v>268</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H239" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="I239">
-        <v>36635604</v>
+        <v>37034524</v>
       </c>
       <c r="J239" t="s">
-        <v>269</v>
+        <v>174</v>
       </c>
     </row>
     <row r="240" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H240" t="s">
-        <v>109</v>
+        <v>208</v>
       </c>
       <c r="I240">
-        <v>8837870</v>
+        <v>37161537</v>
       </c>
       <c r="J240" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
     </row>
     <row r="241" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H241" t="s">
-        <v>109</v>
+        <v>208</v>
       </c>
       <c r="I241">
-        <v>5359040</v>
+        <v>37173787</v>
       </c>
       <c r="J241" t="s">
-        <v>271</v>
+        <v>211</v>
       </c>
     </row>
     <row r="242" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H242" t="s">
-        <v>109</v>
+        <v>656</v>
       </c>
       <c r="I242">
-        <v>42373723</v>
+        <v>37244806</v>
       </c>
       <c r="J242" t="s">
-        <v>272</v>
+        <v>243</v>
       </c>
     </row>
     <row r="243" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H243" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="I243">
-        <v>16303007</v>
+        <v>37594934</v>
       </c>
       <c r="J243" t="s">
-        <v>273</v>
+        <v>165</v>
       </c>
     </row>
     <row r="244" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H244" t="s">
-        <v>109</v>
+        <v>656</v>
       </c>
       <c r="I244">
-        <v>27303665</v>
+        <v>37639889</v>
       </c>
       <c r="J244" t="s">
-        <v>274</v>
+        <v>222</v>
       </c>
     </row>
     <row r="245" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H245" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="I245">
-        <v>5462299</v>
+        <v>37790051</v>
       </c>
       <c r="J245" t="s">
-        <v>275</v>
+        <v>157</v>
       </c>
     </row>
     <row r="246" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H246" t="s">
-        <v>109</v>
+        <v>58</v>
       </c>
       <c r="I246">
-        <v>47220150</v>
+        <v>37843037</v>
       </c>
       <c r="J246" t="s">
-        <v>276</v>
+        <v>77</v>
       </c>
     </row>
     <row r="247" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H247" t="s">
-        <v>109</v>
+        <v>656</v>
       </c>
       <c r="I247">
-        <v>42265154</v>
+        <v>38157908</v>
       </c>
       <c r="J247" t="s">
-        <v>277</v>
+        <v>227</v>
       </c>
     </row>
     <row r="248" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H248" t="s">
-        <v>109</v>
+        <v>656</v>
       </c>
       <c r="I248">
-        <v>48105600</v>
+        <v>38158208</v>
       </c>
       <c r="J248" t="s">
-        <v>278</v>
+        <v>231</v>
       </c>
     </row>
     <row r="249" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H249" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
       <c r="I249">
-        <v>34991467</v>
+        <v>38183281</v>
       </c>
       <c r="J249" t="s">
-        <v>279</v>
+        <v>190</v>
       </c>
     </row>
     <row r="250" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H250" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="I250">
-        <v>34348663</v>
+        <v>38310913</v>
       </c>
       <c r="J250" t="s">
-        <v>280</v>
+        <v>101</v>
       </c>
     </row>
     <row r="251" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H251" t="s">
-        <v>109</v>
+        <v>656</v>
       </c>
       <c r="I251">
-        <v>34535085</v>
+        <v>38312169</v>
       </c>
       <c r="J251" t="s">
-        <v>281</v>
+        <v>249</v>
       </c>
     </row>
     <row r="252" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H252" t="s">
-        <v>109</v>
+        <v>29</v>
       </c>
       <c r="I252">
-        <v>41140508</v>
+        <v>38407975</v>
       </c>
       <c r="J252" t="s">
-        <v>282</v>
+        <v>46</v>
       </c>
     </row>
     <row r="253" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H253" t="s">
-        <v>109</v>
+        <v>29</v>
       </c>
       <c r="I253">
-        <v>22441147</v>
+        <v>38412071</v>
       </c>
       <c r="J253" t="s">
-        <v>283</v>
+        <v>338</v>
       </c>
     </row>
     <row r="254" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H254" t="s">
-        <v>109</v>
+        <v>29</v>
       </c>
       <c r="I254">
-        <v>36811022</v>
+        <v>38412101</v>
       </c>
       <c r="J254" t="s">
-        <v>284</v>
+        <v>340</v>
       </c>
     </row>
     <row r="255" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H255" t="s">
-        <v>109</v>
+        <v>656</v>
       </c>
       <c r="I255">
-        <v>36811023</v>
+        <v>38415503</v>
       </c>
       <c r="J255" t="s">
-        <v>0</v>
+        <v>242</v>
       </c>
     </row>
     <row r="256" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H256" t="s">
-        <v>143</v>
+        <v>29</v>
       </c>
       <c r="I256">
-        <v>42217758</v>
+        <v>38417027</v>
       </c>
       <c r="J256" t="s">
-        <v>285</v>
+        <v>54</v>
       </c>
     </row>
     <row r="257" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H257" t="s">
-        <v>143</v>
+        <v>656</v>
       </c>
       <c r="I257">
-        <v>39384055</v>
+        <v>38417806</v>
       </c>
       <c r="J257" t="s">
-        <v>286</v>
+        <v>230</v>
       </c>
     </row>
     <row r="258" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H258" t="s">
-        <v>143</v>
+        <v>208</v>
       </c>
       <c r="I258">
-        <v>11681261</v>
+        <v>38455497</v>
       </c>
       <c r="J258" t="s">
-        <v>287</v>
+        <v>210</v>
       </c>
     </row>
     <row r="259" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H259" t="s">
-        <v>211</v>
+        <v>29</v>
       </c>
       <c r="I259">
-        <v>37161537</v>
+        <v>38490170</v>
       </c>
       <c r="J259" t="s">
-        <v>288</v>
+        <v>53</v>
       </c>
     </row>
     <row r="260" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H260" t="s">
-        <v>143</v>
+        <v>29</v>
       </c>
       <c r="I260">
-        <v>30405071</v>
+        <v>38490171</v>
       </c>
       <c r="J260" t="s">
-        <v>289</v>
+        <v>52</v>
       </c>
     </row>
     <row r="261" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H261" t="s">
-        <v>143</v>
+        <v>29</v>
       </c>
       <c r="I261">
-        <v>22403445</v>
+        <v>38545387</v>
       </c>
       <c r="J261" t="s">
-        <v>290</v>
+        <v>47</v>
       </c>
     </row>
     <row r="262" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H262" t="s">
-        <v>143</v>
+        <v>29</v>
       </c>
       <c r="I262">
-        <v>26257716</v>
+        <v>38659485</v>
       </c>
       <c r="J262" t="s">
-        <v>291</v>
+        <v>43</v>
       </c>
     </row>
     <row r="263" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H263" t="s">
-        <v>143</v>
+        <v>29</v>
       </c>
       <c r="I263">
-        <v>12481760</v>
+        <v>38676914</v>
       </c>
       <c r="J263" t="s">
-        <v>292</v>
+        <v>333</v>
       </c>
     </row>
     <row r="264" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H264" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="I264">
-        <v>12481759</v>
+        <v>38977260</v>
       </c>
       <c r="J264" t="s">
-        <v>293</v>
+        <v>332</v>
       </c>
     </row>
     <row r="265" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H265" t="s">
-        <v>143</v>
+        <v>29</v>
       </c>
       <c r="I265">
-        <v>36682232</v>
+        <v>39006855</v>
       </c>
       <c r="J265" t="s">
-        <v>294</v>
+        <v>160</v>
       </c>
     </row>
     <row r="266" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H266" t="s">
-        <v>143</v>
+        <v>29</v>
       </c>
       <c r="I266">
-        <v>46727700</v>
+        <v>39006854</v>
       </c>
       <c r="J266" t="s">
-        <v>295</v>
+        <v>161</v>
       </c>
     </row>
     <row r="267" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H267" t="s">
-        <v>143</v>
+        <v>29</v>
       </c>
       <c r="I267">
-        <v>40771157</v>
+        <v>39006857</v>
       </c>
       <c r="J267" t="s">
-        <v>296</v>
+        <v>159</v>
       </c>
     </row>
     <row r="268" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H268" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="I268">
-        <v>19104731</v>
+        <v>39030281</v>
       </c>
       <c r="J268" t="s">
-        <v>297</v>
+        <v>329</v>
       </c>
     </row>
     <row r="269" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H269" t="s">
-        <v>143</v>
+        <v>90</v>
       </c>
       <c r="I269">
-        <v>39944753</v>
+        <v>39071990</v>
       </c>
       <c r="J269" t="s">
-        <v>298</v>
+        <v>158</v>
       </c>
     </row>
     <row r="270" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H270" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="I270">
-        <v>48449253</v>
+        <v>39147133</v>
       </c>
       <c r="J270" t="s">
-        <v>299</v>
+        <v>328</v>
       </c>
     </row>
     <row r="271" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H271" t="s">
-        <v>143</v>
+        <v>29</v>
       </c>
       <c r="I271">
-        <v>42051062</v>
+        <v>39228155</v>
       </c>
       <c r="J271" t="s">
-        <v>300</v>
+        <v>45</v>
       </c>
     </row>
     <row r="272" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H272" t="s">
-        <v>143</v>
+        <v>90</v>
       </c>
       <c r="I272">
-        <v>18291047</v>
+        <v>39239709</v>
       </c>
       <c r="J272" t="s">
-        <v>301</v>
+        <v>322</v>
       </c>
     </row>
     <row r="273" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H273" t="s">
-        <v>143</v>
+        <v>96</v>
       </c>
       <c r="I273">
-        <v>10727917</v>
+        <v>39270777</v>
       </c>
       <c r="J273" t="s">
-        <v>302</v>
+        <v>104</v>
       </c>
     </row>
     <row r="274" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H274" t="s">
-        <v>143</v>
+        <v>29</v>
       </c>
       <c r="I274">
-        <v>46543317</v>
+        <v>39278162</v>
       </c>
       <c r="J274" t="s">
-        <v>303</v>
+        <v>49</v>
       </c>
     </row>
     <row r="275" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H275" t="s">
-        <v>143</v>
+        <v>96</v>
       </c>
       <c r="I275">
-        <v>13644995</v>
+        <v>39376011</v>
       </c>
       <c r="J275" t="s">
-        <v>304</v>
+        <v>100</v>
       </c>
     </row>
     <row r="276" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H276" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I276">
-        <v>42486414</v>
+        <v>39384055</v>
       </c>
       <c r="J276" t="s">
-        <v>305</v>
+        <v>283</v>
       </c>
     </row>
     <row r="277" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H277" t="s">
-        <v>143</v>
+        <v>29</v>
       </c>
       <c r="I277">
-        <v>44695653</v>
+        <v>39415252</v>
       </c>
       <c r="J277" t="s">
-        <v>306</v>
+        <v>33</v>
       </c>
     </row>
     <row r="278" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H278" t="s">
-        <v>143</v>
+        <v>205</v>
       </c>
       <c r="I278">
-        <v>44374810</v>
+        <v>39651008</v>
       </c>
       <c r="J278" t="s">
-        <v>307</v>
+        <v>207</v>
       </c>
     </row>
     <row r="279" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H279" t="s">
-        <v>143</v>
+        <v>58</v>
       </c>
       <c r="I279">
-        <v>29258063</v>
+        <v>39663616</v>
       </c>
       <c r="J279" t="s">
-        <v>308</v>
+        <v>76</v>
       </c>
     </row>
     <row r="280" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H280" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I280">
-        <v>13405604</v>
+        <v>39944753</v>
       </c>
       <c r="J280" t="s">
-        <v>309</v>
+        <v>295</v>
       </c>
     </row>
     <row r="281" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H281" t="s">
-        <v>143</v>
+        <v>29</v>
       </c>
       <c r="I281">
-        <v>10646862</v>
+        <v>40102936</v>
       </c>
       <c r="J281" t="s">
-        <v>310</v>
+        <v>335</v>
       </c>
     </row>
     <row r="282" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H282" t="s">
-        <v>143</v>
+        <v>29</v>
       </c>
       <c r="I282">
-        <v>12362063</v>
+        <v>40180424</v>
       </c>
       <c r="J282" t="s">
-        <v>311</v>
+        <v>9</v>
       </c>
     </row>
     <row r="283" spans="8:10" x14ac:dyDescent="0.3">
@@ -6131,7 +6217,7 @@
         <v>40185196</v>
       </c>
       <c r="J283" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="284" spans="8:10" x14ac:dyDescent="0.3">
@@ -6139,10 +6225,10 @@
         <v>90</v>
       </c>
       <c r="I284">
-        <v>15825326</v>
+        <v>40501253</v>
       </c>
       <c r="J284" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="285" spans="8:10" x14ac:dyDescent="0.3">
@@ -6150,120 +6236,120 @@
         <v>90</v>
       </c>
       <c r="I285">
-        <v>26375455</v>
+        <v>40636333</v>
       </c>
       <c r="J285" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="286" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H286" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="I286">
-        <v>42803850</v>
+        <v>40639939</v>
       </c>
       <c r="J286" t="s">
-        <v>315</v>
+        <v>102</v>
       </c>
     </row>
     <row r="287" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H287" t="s">
-        <v>90</v>
+        <v>169</v>
       </c>
       <c r="I287">
-        <v>50154913</v>
+        <v>40640374</v>
       </c>
       <c r="J287" t="s">
-        <v>316</v>
+        <v>193</v>
       </c>
     </row>
     <row r="288" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H288" t="s">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="I288">
-        <v>16806254</v>
+        <v>40771157</v>
       </c>
       <c r="J288" t="s">
-        <v>317</v>
+        <v>293</v>
       </c>
     </row>
     <row r="289" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H289" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I289">
-        <v>40501253</v>
+        <v>40852278</v>
       </c>
       <c r="J289" t="s">
-        <v>318</v>
+        <v>39</v>
       </c>
     </row>
     <row r="290" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H290" t="s">
-        <v>90</v>
+        <v>169</v>
       </c>
       <c r="I290">
-        <v>14878740</v>
+        <v>40982029</v>
       </c>
       <c r="J290" t="s">
-        <v>319</v>
+        <v>197</v>
       </c>
     </row>
     <row r="291" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H291" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="I291">
-        <v>12673237</v>
+        <v>41140508</v>
       </c>
       <c r="J291" t="s">
-        <v>320</v>
+        <v>279</v>
       </c>
     </row>
     <row r="292" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H292" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="I292">
-        <v>17579662</v>
+        <v>41864123</v>
       </c>
       <c r="J292" t="s">
-        <v>321</v>
+        <v>213</v>
       </c>
     </row>
     <row r="293" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H293" t="s">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="I293">
-        <v>14719737</v>
+        <v>42051062</v>
       </c>
       <c r="J293" t="s">
-        <v>4</v>
+        <v>297</v>
       </c>
     </row>
     <row r="294" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H294" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="I294">
-        <v>22119013</v>
+        <v>42265154</v>
       </c>
       <c r="J294" t="s">
-        <v>322</v>
+        <v>274</v>
       </c>
     </row>
     <row r="295" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H295" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="I295">
-        <v>15795597</v>
+        <v>42373723</v>
       </c>
       <c r="J295" t="s">
-        <v>323</v>
+        <v>269</v>
       </c>
     </row>
     <row r="296" spans="8:10" x14ac:dyDescent="0.3">
@@ -6271,7 +6357,7 @@
         <v>90</v>
       </c>
       <c r="I296">
-        <v>12126317</v>
+        <v>42519088</v>
       </c>
       <c r="J296" t="s">
         <v>324</v>
@@ -6282,318 +6368,318 @@
         <v>90</v>
       </c>
       <c r="I297">
-        <v>39239709</v>
+        <v>42803850</v>
       </c>
       <c r="J297" t="s">
-        <v>325</v>
+        <v>312</v>
       </c>
     </row>
     <row r="298" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H298" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="I298">
-        <v>14488275</v>
+        <v>42913903</v>
       </c>
       <c r="J298" t="s">
-        <v>326</v>
+        <v>212</v>
       </c>
     </row>
     <row r="299" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H299" t="s">
-        <v>90</v>
+        <v>169</v>
       </c>
       <c r="I299">
-        <v>42519088</v>
+        <v>43252471</v>
       </c>
       <c r="J299" t="s">
-        <v>327</v>
+        <v>188</v>
       </c>
     </row>
     <row r="300" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H300" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="I300">
-        <v>17579394</v>
+        <v>43431417</v>
       </c>
       <c r="J300" t="s">
-        <v>328</v>
+        <v>97</v>
       </c>
     </row>
     <row r="301" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H301" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="I301">
-        <v>27056005</v>
+        <v>43571360</v>
       </c>
       <c r="J301" t="s">
-        <v>329</v>
+        <v>134</v>
       </c>
     </row>
     <row r="302" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H302" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="I302">
-        <v>24832169</v>
+        <v>43571361</v>
       </c>
       <c r="J302" t="s">
-        <v>330</v>
+        <v>133</v>
       </c>
     </row>
     <row r="303" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H303" t="s">
-        <v>171</v>
+        <v>141</v>
       </c>
       <c r="I303">
-        <v>39147133</v>
+        <v>44374810</v>
       </c>
       <c r="J303" t="s">
-        <v>331</v>
+        <v>304</v>
       </c>
     </row>
     <row r="304" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H304" t="s">
-        <v>171</v>
+        <v>96</v>
       </c>
       <c r="I304">
-        <v>39030281</v>
+        <v>44581094</v>
       </c>
       <c r="J304" t="s">
-        <v>332</v>
+        <v>103</v>
       </c>
     </row>
     <row r="305" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H305" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I305">
-        <v>13373616</v>
+        <v>44916947</v>
       </c>
       <c r="J305" t="s">
-        <v>333</v>
+        <v>192</v>
       </c>
     </row>
     <row r="306" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H306" t="s">
-        <v>171</v>
+        <v>113</v>
       </c>
       <c r="I306">
-        <v>12757668</v>
+        <v>44996967</v>
       </c>
       <c r="J306" t="s">
-        <v>334</v>
+        <v>18</v>
       </c>
     </row>
     <row r="307" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H307" t="s">
-        <v>171</v>
+        <v>90</v>
       </c>
       <c r="I307">
-        <v>38977260</v>
+        <v>45342904</v>
       </c>
       <c r="J307" t="s">
-        <v>335</v>
+        <v>105</v>
       </c>
     </row>
     <row r="308" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H308" t="s">
-        <v>29</v>
+        <v>113</v>
       </c>
       <c r="I308">
-        <v>38676914</v>
+        <v>45349063</v>
       </c>
       <c r="J308" t="s">
-        <v>336</v>
+        <v>7</v>
       </c>
     </row>
     <row r="309" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H309" t="s">
-        <v>29</v>
+        <v>113</v>
       </c>
       <c r="I309">
-        <v>39911056</v>
+        <v>45573288</v>
       </c>
       <c r="J309" t="s">
-        <v>337</v>
+        <v>119</v>
       </c>
     </row>
     <row r="310" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H310" t="s">
-        <v>29</v>
+        <v>113</v>
       </c>
       <c r="I310">
-        <v>40102936</v>
+        <v>45701215</v>
       </c>
       <c r="J310" t="s">
-        <v>338</v>
+        <v>17</v>
       </c>
     </row>
     <row r="311" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H311" t="s">
-        <v>29</v>
+        <v>113</v>
       </c>
       <c r="I311">
-        <v>10929274</v>
+        <v>46191377</v>
       </c>
       <c r="J311" t="s">
-        <v>339</v>
+        <v>124</v>
       </c>
     </row>
     <row r="312" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H312" t="s">
-        <v>29</v>
+        <v>141</v>
       </c>
       <c r="I312">
-        <v>10929273</v>
+        <v>46543317</v>
       </c>
       <c r="J312" t="s">
-        <v>340</v>
+        <v>300</v>
       </c>
     </row>
     <row r="313" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H313" t="s">
-        <v>29</v>
+        <v>113</v>
       </c>
       <c r="I313">
-        <v>38412071</v>
+        <v>46550390</v>
       </c>
       <c r="J313" t="s">
-        <v>341</v>
+        <v>118</v>
       </c>
     </row>
     <row r="314" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H314" t="s">
-        <v>29</v>
+        <v>113</v>
       </c>
       <c r="I314">
-        <v>29280326</v>
+        <v>46671749</v>
       </c>
       <c r="J314" t="s">
-        <v>342</v>
+        <v>127</v>
       </c>
     </row>
     <row r="315" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H315" t="s">
-        <v>29</v>
+        <v>141</v>
       </c>
       <c r="I315">
-        <v>38412101</v>
+        <v>46727700</v>
       </c>
       <c r="J315" t="s">
-        <v>343</v>
+        <v>292</v>
       </c>
     </row>
     <row r="316" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H316" t="s">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="I316">
-        <v>5332788</v>
+        <v>46801171</v>
       </c>
       <c r="J316" t="s">
-        <v>344</v>
+        <v>262</v>
       </c>
     </row>
     <row r="317" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H317" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="I317">
-        <v>5332789</v>
+        <v>46962408</v>
       </c>
       <c r="J317" t="s">
-        <v>345</v>
+        <v>116</v>
       </c>
     </row>
     <row r="318" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H318" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="I318">
-        <v>51016959</v>
+        <v>47220150</v>
       </c>
       <c r="J318" t="s">
-        <v>346</v>
+        <v>273</v>
       </c>
     </row>
     <row r="319" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H319" t="s">
-        <v>90</v>
+        <v>169</v>
       </c>
       <c r="I319">
-        <v>40636333</v>
+        <v>47861038</v>
       </c>
       <c r="J319" t="s">
-        <v>347</v>
+        <v>187</v>
       </c>
     </row>
     <row r="320" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H320" t="s">
-        <v>171</v>
+        <v>656</v>
       </c>
       <c r="I320">
-        <v>50875168</v>
+        <v>47936724</v>
       </c>
       <c r="J320" t="s">
-        <v>348</v>
+        <v>229</v>
       </c>
     </row>
     <row r="321" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H321" t="s">
-        <v>58</v>
+        <v>107</v>
       </c>
       <c r="I321">
-        <v>51623281</v>
+        <v>48105600</v>
       </c>
       <c r="J321" t="s">
-        <v>349</v>
+        <v>275</v>
       </c>
     </row>
     <row r="322" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H322" t="s">
-        <v>92</v>
+        <v>141</v>
       </c>
       <c r="I322">
-        <v>51897600</v>
+        <v>48449253</v>
       </c>
       <c r="J322" t="s">
-        <v>350</v>
+        <v>296</v>
       </c>
     </row>
     <row r="323" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H323" t="s">
-        <v>58</v>
+        <v>169</v>
       </c>
       <c r="I323">
-        <v>51989601</v>
+        <v>48477550</v>
       </c>
       <c r="J323" t="s">
-        <v>351</v>
+        <v>179</v>
       </c>
     </row>
     <row r="324" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H324" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
       <c r="I324">
-        <v>52390638</v>
+        <v>49473587</v>
       </c>
       <c r="J324" t="s">
-        <v>352</v>
+        <v>256</v>
       </c>
     </row>
     <row r="325" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H325" t="s">
-        <v>109</v>
+        <v>58</v>
       </c>
       <c r="I325">
-        <v>52362395</v>
+        <v>50012601</v>
       </c>
       <c r="J325" t="s">
-        <v>353</v>
+        <v>89</v>
       </c>
     </row>
     <row r="326" spans="8:10" x14ac:dyDescent="0.3">
@@ -6601,109 +6687,109 @@
         <v>90</v>
       </c>
       <c r="I326">
-        <v>52155415</v>
+        <v>50153946</v>
       </c>
       <c r="J326" t="s">
-        <v>354</v>
+        <v>112</v>
       </c>
     </row>
     <row r="327" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H327" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I327">
-        <v>52162444</v>
+        <v>50154913</v>
       </c>
       <c r="J327" t="s">
-        <v>355</v>
+        <v>313</v>
       </c>
     </row>
     <row r="328" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H328" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I328">
-        <v>52270898</v>
+        <v>50709616</v>
       </c>
       <c r="J328" t="s">
-        <v>356</v>
+        <v>173</v>
       </c>
     </row>
     <row r="329" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H329" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="I329">
-        <v>52211558</v>
+        <v>50723598</v>
       </c>
       <c r="J329" t="s">
-        <v>357</v>
+        <v>13</v>
       </c>
     </row>
     <row r="330" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H330" t="s">
-        <v>98</v>
+        <v>169</v>
       </c>
       <c r="I330">
-        <v>52217000</v>
+        <v>50725354</v>
       </c>
       <c r="J330" t="s">
-        <v>358</v>
+        <v>204</v>
       </c>
     </row>
     <row r="331" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H331" t="s">
-        <v>29</v>
+        <v>656</v>
       </c>
       <c r="I331">
-        <v>51689222</v>
+        <v>50326931</v>
       </c>
       <c r="J331" t="s">
-        <v>359</v>
+        <v>257</v>
       </c>
     </row>
     <row r="332" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H332" t="s">
-        <v>29</v>
+        <v>169</v>
       </c>
       <c r="I332">
-        <v>51684787</v>
+        <v>50875168</v>
       </c>
       <c r="J332" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
     </row>
     <row r="333" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H333" t="s">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="I333">
-        <v>51883980</v>
+        <v>51016959</v>
       </c>
       <c r="J333" t="s">
-        <v>361</v>
+        <v>343</v>
       </c>
     </row>
     <row r="334" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H334" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="I334">
-        <v>51898514</v>
+        <v>51623281</v>
       </c>
       <c r="J334" t="s">
-        <v>362</v>
+        <v>346</v>
       </c>
     </row>
     <row r="335" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H335" t="s">
-        <v>98</v>
+        <v>29</v>
       </c>
       <c r="I335">
-        <v>52990015</v>
+        <v>51684787</v>
       </c>
       <c r="J335" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
     </row>
     <row r="336" spans="8:10" x14ac:dyDescent="0.3">
@@ -6711,10 +6797,10 @@
         <v>29</v>
       </c>
       <c r="I336">
-        <v>52581507</v>
+        <v>51689222</v>
       </c>
       <c r="J336" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="337" spans="8:10" x14ac:dyDescent="0.3">
@@ -6722,10 +6808,10 @@
         <v>29</v>
       </c>
       <c r="I337">
-        <v>52613211</v>
+        <v>51883980</v>
       </c>
       <c r="J337" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
     </row>
     <row r="338" spans="8:10" x14ac:dyDescent="0.3">
@@ -6733,54 +6819,54 @@
         <v>29</v>
       </c>
       <c r="I338">
-        <v>52578670</v>
+        <v>51898514</v>
       </c>
       <c r="J338" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
     </row>
     <row r="339" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H339" t="s">
-        <v>171</v>
+        <v>58</v>
       </c>
       <c r="I339">
-        <v>52874174</v>
+        <v>51989601</v>
       </c>
       <c r="J339" t="s">
-        <v>367</v>
+        <v>348</v>
       </c>
     </row>
     <row r="340" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H340" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I340">
-        <v>52872566</v>
+        <v>52155415</v>
       </c>
       <c r="J340" t="s">
-        <v>368</v>
+        <v>351</v>
       </c>
     </row>
     <row r="341" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H341" t="s">
-        <v>171</v>
+        <v>656</v>
       </c>
       <c r="I341">
-        <v>54145830</v>
+        <v>52155531</v>
       </c>
       <c r="J341" t="s">
-        <v>369</v>
+        <v>92</v>
       </c>
     </row>
     <row r="342" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H342" t="s">
-        <v>29</v>
+        <v>656</v>
       </c>
       <c r="I342">
-        <v>53052265</v>
+        <v>52162444</v>
       </c>
       <c r="J342" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
     </row>
     <row r="343" spans="8:10" x14ac:dyDescent="0.3">
@@ -6788,109 +6874,109 @@
         <v>90</v>
       </c>
       <c r="I343">
-        <v>53297446</v>
+        <v>52204284</v>
       </c>
       <c r="J343" t="s">
-        <v>371</v>
+        <v>91</v>
       </c>
     </row>
     <row r="344" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H344" t="s">
-        <v>143</v>
+        <v>96</v>
       </c>
       <c r="I344">
-        <v>53583387</v>
+        <v>52211558</v>
       </c>
       <c r="J344" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
     </row>
     <row r="345" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H345" t="s">
-        <v>143</v>
+        <v>96</v>
       </c>
       <c r="I345">
-        <v>53564659</v>
+        <v>52217000</v>
       </c>
       <c r="J345" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
     </row>
     <row r="346" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H346" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="I346">
-        <v>53569741</v>
+        <v>52270898</v>
       </c>
       <c r="J346" t="s">
-        <v>374</v>
+        <v>353</v>
       </c>
     </row>
     <row r="347" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H347" t="s">
-        <v>58</v>
+        <v>656</v>
       </c>
       <c r="I347">
-        <v>53680118</v>
+        <v>51533853</v>
       </c>
       <c r="J347" t="s">
-        <v>375</v>
+        <v>223</v>
       </c>
     </row>
     <row r="348" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H348" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="I348">
-        <v>53776254</v>
+        <v>52390638</v>
       </c>
       <c r="J348" t="s">
-        <v>376</v>
+        <v>349</v>
       </c>
     </row>
     <row r="349" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H349" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="I349">
-        <v>53967042</v>
+        <v>52362395</v>
       </c>
       <c r="J349" t="s">
-        <v>377</v>
+        <v>350</v>
       </c>
     </row>
     <row r="350" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H350" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I350">
-        <v>55275736</v>
+        <v>52578670</v>
       </c>
       <c r="J350" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
     </row>
     <row r="351" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H351" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I351">
-        <v>56663811</v>
+        <v>52581507</v>
       </c>
       <c r="J351" t="s">
-        <v>379</v>
+        <v>361</v>
       </c>
     </row>
     <row r="352" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H352" t="s">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c r="I352">
-        <v>59082806</v>
+        <v>52613211</v>
       </c>
       <c r="J352" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
     </row>
     <row r="353" spans="8:10" x14ac:dyDescent="0.3">
@@ -6898,76 +6984,76 @@
         <v>29</v>
       </c>
       <c r="I353">
-        <v>55369678</v>
+        <v>52872566</v>
       </c>
       <c r="J353" t="s">
-        <v>381</v>
+        <v>365</v>
       </c>
     </row>
     <row r="354" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H354" t="s">
-        <v>58</v>
+        <v>169</v>
       </c>
       <c r="I354">
-        <v>55354052</v>
+        <v>52874174</v>
       </c>
       <c r="J354" t="s">
-        <v>382</v>
+        <v>364</v>
       </c>
     </row>
     <row r="355" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H355" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="I355">
-        <v>55381383</v>
+        <v>53052265</v>
       </c>
       <c r="J355" t="s">
-        <v>383</v>
+        <v>367</v>
       </c>
     </row>
     <row r="356" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H356" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="I356">
-        <v>55609278</v>
+        <v>53297446</v>
       </c>
       <c r="J356" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
     </row>
     <row r="357" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H357" t="s">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="I357">
-        <v>55356212</v>
+        <v>53564659</v>
       </c>
       <c r="J357" t="s">
-        <v>19</v>
+        <v>370</v>
       </c>
     </row>
     <row r="358" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H358" t="s">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="I358">
-        <v>55449180</v>
+        <v>53569741</v>
       </c>
       <c r="J358" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
     </row>
     <row r="359" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H359" t="s">
-        <v>58</v>
+        <v>141</v>
       </c>
       <c r="I359">
-        <v>55357095</v>
+        <v>53583387</v>
       </c>
       <c r="J359" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
     </row>
     <row r="360" spans="8:10" x14ac:dyDescent="0.3">
@@ -6975,65 +7061,65 @@
         <v>58</v>
       </c>
       <c r="I360">
-        <v>55384739</v>
+        <v>53680118</v>
       </c>
       <c r="J360" t="s">
-        <v>387</v>
+        <v>372</v>
       </c>
     </row>
     <row r="361" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H361" t="s">
-        <v>58</v>
+        <v>656</v>
       </c>
       <c r="I361">
-        <v>55357155</v>
+        <v>53776254</v>
       </c>
       <c r="J361" t="s">
-        <v>388</v>
+        <v>373</v>
       </c>
     </row>
     <row r="362" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H362" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="I362">
-        <v>55389336</v>
+        <v>53967042</v>
       </c>
       <c r="J362" t="s">
-        <v>389</v>
+        <v>374</v>
       </c>
     </row>
     <row r="363" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H363" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I363">
-        <v>55356388</v>
+        <v>54145830</v>
       </c>
       <c r="J363" t="s">
-        <v>390</v>
+        <v>366</v>
       </c>
     </row>
     <row r="364" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H364" t="s">
-        <v>171</v>
+        <v>90</v>
       </c>
       <c r="I364">
-        <v>55610213</v>
+        <v>55275736</v>
       </c>
       <c r="J364" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="365" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H365" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="I365">
-        <v>55462718</v>
+        <v>55357095</v>
       </c>
       <c r="J365" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
     </row>
     <row r="366" spans="8:10" x14ac:dyDescent="0.3">
@@ -7041,780 +7127,780 @@
         <v>58</v>
       </c>
       <c r="I366">
-        <v>58084222</v>
+        <v>55357155</v>
       </c>
       <c r="J366" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
     </row>
     <row r="367" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H367" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="I367">
-        <v>56651433</v>
+        <v>55356212</v>
       </c>
       <c r="J367" t="s">
-        <v>394</v>
+        <v>19</v>
       </c>
     </row>
     <row r="368" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H368" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="I368">
-        <v>56479851</v>
+        <v>55381383</v>
       </c>
       <c r="J368" t="s">
-        <v>395</v>
+        <v>380</v>
       </c>
     </row>
     <row r="369" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H369" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="I369">
-        <v>56667264</v>
+        <v>55384739</v>
       </c>
       <c r="J369" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
     </row>
     <row r="370" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H370" t="s">
-        <v>143</v>
+        <v>29</v>
       </c>
       <c r="I370">
-        <v>56896464</v>
+        <v>55369678</v>
       </c>
       <c r="J370" t="s">
-        <v>397</v>
+        <v>378</v>
       </c>
     </row>
     <row r="371" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H371" t="s">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="I371">
-        <v>57592449</v>
+        <v>55389336</v>
       </c>
       <c r="J371" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
     </row>
     <row r="372" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H372" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I372">
-        <v>56183402</v>
+        <v>55449180</v>
       </c>
       <c r="J372" t="s">
-        <v>399</v>
+        <v>382</v>
       </c>
     </row>
     <row r="373" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H373" t="s">
-        <v>92</v>
+        <v>656</v>
       </c>
       <c r="I373">
-        <v>56651667</v>
+        <v>55462718</v>
       </c>
       <c r="J373" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
     </row>
     <row r="374" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H374" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="I374">
-        <v>58987730</v>
+        <v>55609278</v>
       </c>
       <c r="J374" t="s">
-        <v>401</v>
+        <v>381</v>
       </c>
     </row>
     <row r="375" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H375" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I375">
-        <v>57422656</v>
+        <v>55610213</v>
       </c>
       <c r="J375" t="s">
-        <v>402</v>
+        <v>388</v>
       </c>
     </row>
     <row r="376" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H376" t="s">
-        <v>92</v>
+        <v>656</v>
       </c>
       <c r="I376">
-        <v>58040260</v>
+        <v>56183402</v>
       </c>
       <c r="J376" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
     </row>
     <row r="377" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H377" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="I377">
-        <v>59070986</v>
+        <v>56479851</v>
       </c>
       <c r="J377" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
     </row>
     <row r="378" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H378" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="I378">
-        <v>59058036</v>
+        <v>56663811</v>
       </c>
       <c r="J378" t="s">
-        <v>405</v>
+        <v>376</v>
       </c>
     </row>
     <row r="379" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H379" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="I379">
-        <v>58505144</v>
+        <v>56651433</v>
       </c>
       <c r="J379" t="s">
-        <v>16</v>
+        <v>391</v>
       </c>
     </row>
     <row r="380" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H380" t="s">
-        <v>115</v>
+        <v>656</v>
       </c>
       <c r="I380">
-        <v>58610450</v>
+        <v>56651667</v>
       </c>
       <c r="J380" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
     </row>
     <row r="381" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H381" t="s">
-        <v>143</v>
+        <v>90</v>
       </c>
       <c r="I381">
-        <v>59056260</v>
+        <v>56667264</v>
       </c>
       <c r="J381" t="s">
-        <v>407</v>
+        <v>393</v>
       </c>
     </row>
     <row r="382" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H382" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="I382">
-        <v>58722261</v>
+        <v>56896464</v>
       </c>
       <c r="J382" t="s">
-        <v>408</v>
+        <v>394</v>
       </c>
     </row>
     <row r="383" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H383" t="s">
-        <v>115</v>
+        <v>169</v>
       </c>
       <c r="I383">
-        <v>58716097</v>
+        <v>57422656</v>
       </c>
       <c r="J383" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
     </row>
     <row r="384" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H384" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="I384">
-        <v>58730204</v>
+        <v>57592449</v>
       </c>
       <c r="J384" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
     </row>
     <row r="385" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H385" t="s">
-        <v>115</v>
+        <v>656</v>
       </c>
       <c r="I385">
-        <v>59199875</v>
+        <v>58040260</v>
       </c>
       <c r="J385" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
     </row>
     <row r="386" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H386" t="s">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="I386">
-        <v>59759466</v>
+        <v>58084222</v>
       </c>
       <c r="J386" t="s">
-        <v>412</v>
+        <v>390</v>
       </c>
     </row>
     <row r="387" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H387" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I387">
-        <v>59332927</v>
+        <v>58505144</v>
       </c>
       <c r="J387" t="s">
-        <v>413</v>
+        <v>16</v>
       </c>
     </row>
     <row r="388" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H388" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="I388">
-        <v>59944694</v>
+        <v>58610450</v>
       </c>
       <c r="J388" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
     </row>
     <row r="389" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H389" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I389">
-        <v>60019261</v>
+        <v>58716097</v>
       </c>
       <c r="J389" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
     </row>
     <row r="390" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H390" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="I390">
-        <v>59932138</v>
+        <v>58722261</v>
       </c>
       <c r="J390" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
     </row>
     <row r="391" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H391" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I391">
-        <v>59924956</v>
+        <v>58730204</v>
       </c>
       <c r="J391" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
     </row>
     <row r="392" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H392" t="s">
-        <v>115</v>
+        <v>656</v>
       </c>
       <c r="I392">
-        <v>59927382</v>
+        <v>58987730</v>
       </c>
       <c r="J392" t="s">
-        <v>11</v>
+        <v>398</v>
       </c>
     </row>
     <row r="393" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H393" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="I393">
-        <v>59836396</v>
+        <v>59058036</v>
       </c>
       <c r="J393" t="s">
-        <v>418</v>
+        <v>402</v>
       </c>
     </row>
     <row r="394" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H394" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="I394">
-        <v>60015061</v>
+        <v>59056260</v>
       </c>
       <c r="J394" t="s">
-        <v>5</v>
+        <v>404</v>
       </c>
     </row>
     <row r="395" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H395" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="I395">
-        <v>60023938</v>
+        <v>59070986</v>
       </c>
       <c r="J395" t="s">
-        <v>419</v>
+        <v>401</v>
       </c>
     </row>
     <row r="396" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H396" t="s">
-        <v>115</v>
+        <v>656</v>
       </c>
       <c r="I396">
-        <v>60025950</v>
+        <v>59082806</v>
       </c>
       <c r="J396" t="s">
-        <v>420</v>
+        <v>377</v>
       </c>
     </row>
     <row r="397" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H397" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I397">
-        <v>60024864</v>
+        <v>59199875</v>
       </c>
       <c r="J397" t="s">
-        <v>421</v>
+        <v>408</v>
       </c>
     </row>
     <row r="398" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H398" t="s">
-        <v>115</v>
+        <v>656</v>
       </c>
       <c r="I398">
-        <v>60084208</v>
+        <v>59332927</v>
       </c>
       <c r="J398" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
     </row>
     <row r="399" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H399" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="I399">
-        <v>60085614</v>
+        <v>59759466</v>
       </c>
       <c r="J399" t="s">
-        <v>423</v>
+        <v>409</v>
       </c>
     </row>
     <row r="400" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H400" t="s">
-        <v>171</v>
+        <v>113</v>
       </c>
       <c r="I400">
-        <v>60133592</v>
+        <v>59836396</v>
       </c>
       <c r="J400" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
     </row>
     <row r="401" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H401" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="I401">
-        <v>60450424</v>
+        <v>59927382</v>
       </c>
       <c r="J401" t="s">
-        <v>425</v>
+        <v>11</v>
       </c>
     </row>
     <row r="402" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H402" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="I402">
-        <v>60380162</v>
+        <v>59924956</v>
       </c>
       <c r="J402" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
     </row>
     <row r="403" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H403" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="I403">
-        <v>60541542</v>
+        <v>59932138</v>
       </c>
       <c r="J403" t="s">
-        <v>427</v>
+        <v>413</v>
       </c>
     </row>
     <row r="404" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H404" t="s">
-        <v>152</v>
+        <v>656</v>
       </c>
       <c r="I404">
-        <v>60541171</v>
+        <v>59944694</v>
       </c>
       <c r="J404" t="s">
-        <v>428</v>
+        <v>411</v>
       </c>
     </row>
     <row r="405" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H405" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="I405">
-        <v>60543356</v>
+        <v>60015061</v>
       </c>
       <c r="J405" t="s">
-        <v>429</v>
+        <v>5</v>
       </c>
     </row>
     <row r="406" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H406" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I406">
-        <v>60530655</v>
+        <v>60019261</v>
       </c>
       <c r="J406" t="s">
-        <v>430</v>
+        <v>412</v>
       </c>
     </row>
     <row r="407" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H407" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="I407">
-        <v>60615380</v>
+        <v>60023938</v>
       </c>
       <c r="J407" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
     </row>
     <row r="408" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H408" t="s">
-        <v>58</v>
+        <v>113</v>
       </c>
       <c r="I408">
-        <v>60725132</v>
+        <v>60024864</v>
       </c>
       <c r="J408" t="s">
-        <v>432</v>
+        <v>418</v>
       </c>
     </row>
     <row r="409" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H409" t="s">
-        <v>58</v>
+        <v>113</v>
       </c>
       <c r="I409">
-        <v>62575565</v>
+        <v>60025950</v>
       </c>
       <c r="J409" t="s">
-        <v>433</v>
+        <v>417</v>
       </c>
     </row>
     <row r="410" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H410" t="s">
-        <v>171</v>
+        <v>113</v>
       </c>
       <c r="I410">
-        <v>61766007</v>
+        <v>60084208</v>
       </c>
       <c r="J410" t="s">
-        <v>434</v>
+        <v>419</v>
       </c>
     </row>
     <row r="411" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H411" t="s">
-        <v>98</v>
+        <v>656</v>
       </c>
       <c r="I411">
-        <v>61089339</v>
+        <v>60085614</v>
       </c>
       <c r="J411" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
     </row>
     <row r="412" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H412" t="s">
-        <v>98</v>
+        <v>169</v>
       </c>
       <c r="I412">
-        <v>62377903</v>
+        <v>60133592</v>
       </c>
       <c r="J412" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
     </row>
     <row r="413" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H413" t="s">
-        <v>92</v>
+        <v>141</v>
       </c>
       <c r="I413">
-        <v>60542212</v>
+        <v>60380162</v>
       </c>
       <c r="J413" t="s">
-        <v>437</v>
+        <v>423</v>
       </c>
     </row>
     <row r="414" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H414" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="I414">
-        <v>61044622</v>
+        <v>60450424</v>
       </c>
       <c r="J414" t="s">
-        <v>438</v>
+        <v>422</v>
       </c>
     </row>
     <row r="415" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H415" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="I415">
-        <v>61199642</v>
+        <v>60530655</v>
       </c>
       <c r="J415" t="s">
-        <v>439</v>
+        <v>427</v>
       </c>
     </row>
     <row r="416" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H416" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="I416">
-        <v>61760291</v>
+        <v>60541171</v>
       </c>
       <c r="J416" t="s">
-        <v>440</v>
+        <v>425</v>
       </c>
     </row>
     <row r="417" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H417" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="I417">
-        <v>61923953</v>
+        <v>60541542</v>
       </c>
       <c r="J417" t="s">
-        <v>441</v>
+        <v>424</v>
       </c>
     </row>
     <row r="418" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H418" t="s">
-        <v>143</v>
+        <v>656</v>
       </c>
       <c r="I418">
-        <v>61760141</v>
+        <v>60542212</v>
       </c>
       <c r="J418" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
     </row>
     <row r="419" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H419" t="s">
-        <v>143</v>
+        <v>90</v>
       </c>
       <c r="I419">
-        <v>61929592</v>
+        <v>60543356</v>
       </c>
       <c r="J419" t="s">
-        <v>443</v>
+        <v>426</v>
       </c>
     </row>
     <row r="420" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H420" t="s">
-        <v>143</v>
+        <v>90</v>
       </c>
       <c r="I420">
-        <v>61929727</v>
+        <v>60615380</v>
       </c>
       <c r="J420" t="s">
-        <v>444</v>
+        <v>428</v>
       </c>
     </row>
     <row r="421" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H421" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="I421">
-        <v>61929494</v>
+        <v>60725132</v>
       </c>
       <c r="J421" t="s">
-        <v>445</v>
+        <v>429</v>
       </c>
     </row>
     <row r="422" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H422" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="I422">
-        <v>61929493</v>
+        <v>61044622</v>
       </c>
       <c r="J422" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
     </row>
     <row r="423" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H423" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I423">
-        <v>61879892</v>
+        <v>61089339</v>
       </c>
       <c r="J423" t="s">
-        <v>447</v>
+        <v>432</v>
       </c>
     </row>
     <row r="424" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H424" t="s">
-        <v>58</v>
+        <v>656</v>
       </c>
       <c r="I424">
-        <v>62378988</v>
+        <v>61199642</v>
       </c>
       <c r="J424" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
     </row>
     <row r="425" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H425" t="s">
-        <v>58</v>
+        <v>141</v>
       </c>
       <c r="I425">
-        <v>62375802</v>
+        <v>61760141</v>
       </c>
       <c r="J425" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
     </row>
     <row r="426" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H426" t="s">
-        <v>58</v>
+        <v>141</v>
       </c>
       <c r="I426">
-        <v>62379668</v>
+        <v>61760291</v>
       </c>
       <c r="J426" t="s">
-        <v>450</v>
+        <v>437</v>
       </c>
     </row>
     <row r="427" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H427" t="s">
-        <v>211</v>
+        <v>169</v>
       </c>
       <c r="I427">
-        <v>62221331</v>
+        <v>61766007</v>
       </c>
       <c r="J427" t="s">
-        <v>451</v>
+        <v>431</v>
       </c>
     </row>
     <row r="428" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H428" t="s">
-        <v>143</v>
+        <v>96</v>
       </c>
       <c r="I428">
-        <v>62385013</v>
+        <v>61879892</v>
       </c>
       <c r="J428" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
     </row>
     <row r="429" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H429" t="s">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="I429">
-        <v>62380995</v>
+        <v>61923953</v>
       </c>
       <c r="J429" t="s">
-        <v>453</v>
+        <v>438</v>
       </c>
     </row>
     <row r="430" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H430" t="s">
-        <v>98</v>
+        <v>656</v>
       </c>
       <c r="I430">
-        <v>62421723</v>
+        <v>61929493</v>
       </c>
       <c r="J430" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
     </row>
     <row r="431" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H431" t="s">
-        <v>98</v>
+        <v>656</v>
       </c>
       <c r="I431">
-        <v>62374813</v>
+        <v>61929494</v>
       </c>
       <c r="J431" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
     </row>
     <row r="432" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H432" t="s">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="I432">
-        <v>62499786</v>
+        <v>61929592</v>
       </c>
       <c r="J432" t="s">
-        <v>456</v>
+        <v>440</v>
       </c>
     </row>
     <row r="433" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H433" t="s">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="I433">
-        <v>62498583</v>
+        <v>61929727</v>
       </c>
       <c r="J433" t="s">
-        <v>457</v>
+        <v>441</v>
       </c>
     </row>
     <row r="434" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H434" t="s">
-        <v>143</v>
+        <v>208</v>
       </c>
       <c r="I434">
-        <v>63346456</v>
+        <v>62221331</v>
       </c>
       <c r="J434" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
     </row>
     <row r="435" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H435" t="s">
-        <v>143</v>
+        <v>96</v>
       </c>
       <c r="I435">
-        <v>63100963</v>
+        <v>62374813</v>
       </c>
       <c r="J435" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
     </row>
     <row r="436" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H436" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="I436">
-        <v>63396496</v>
+        <v>62375802</v>
       </c>
       <c r="J436" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
     </row>
     <row r="437" spans="8:10" x14ac:dyDescent="0.3">
@@ -7822,417 +7908,417 @@
         <v>58</v>
       </c>
       <c r="I437">
-        <v>64270608</v>
+        <v>62378988</v>
       </c>
       <c r="J437" t="s">
-        <v>461</v>
+        <v>445</v>
       </c>
     </row>
     <row r="438" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H438" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="I438">
-        <v>63573761</v>
+        <v>62379668</v>
       </c>
       <c r="J438" t="s">
-        <v>462</v>
+        <v>447</v>
       </c>
     </row>
     <row r="439" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H439" t="s">
-        <v>92</v>
+        <v>141</v>
       </c>
       <c r="I439">
-        <v>64330763</v>
+        <v>62380995</v>
       </c>
       <c r="J439" t="s">
-        <v>463</v>
+        <v>450</v>
       </c>
     </row>
     <row r="440" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H440" t="s">
-        <v>92</v>
+        <v>141</v>
       </c>
       <c r="I440">
-        <v>64330764</v>
+        <v>62385013</v>
       </c>
       <c r="J440" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
     </row>
     <row r="441" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H441" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I441">
-        <v>64212552</v>
+        <v>62421723</v>
       </c>
       <c r="J441" t="s">
-        <v>465</v>
+        <v>451</v>
       </c>
     </row>
     <row r="442" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H442" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I442">
-        <v>64212544</v>
+        <v>62498583</v>
       </c>
       <c r="J442" t="s">
-        <v>466</v>
+        <v>454</v>
       </c>
     </row>
     <row r="443" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H443" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I443">
-        <v>64212543</v>
+        <v>62499786</v>
       </c>
       <c r="J443" t="s">
-        <v>467</v>
+        <v>453</v>
       </c>
     </row>
     <row r="444" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H444" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="I444">
-        <v>64212381</v>
+        <v>62575565</v>
       </c>
       <c r="J444" t="s">
-        <v>468</v>
+        <v>430</v>
       </c>
     </row>
     <row r="445" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H445" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="I445">
-        <v>64114088</v>
+        <v>63100963</v>
       </c>
       <c r="J445" t="s">
-        <v>469</v>
+        <v>456</v>
       </c>
     </row>
     <row r="446" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H446" t="s">
-        <v>171</v>
+        <v>141</v>
       </c>
       <c r="I446">
-        <v>64223250</v>
+        <v>63346456</v>
       </c>
       <c r="J446" t="s">
-        <v>470</v>
+        <v>455</v>
       </c>
     </row>
     <row r="447" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H447" t="s">
-        <v>171</v>
+        <v>90</v>
       </c>
       <c r="I447">
-        <v>64214259</v>
+        <v>63396496</v>
       </c>
       <c r="J447" t="s">
-        <v>471</v>
+        <v>457</v>
       </c>
     </row>
     <row r="448" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H448" t="s">
-        <v>171</v>
+        <v>656</v>
       </c>
       <c r="I448">
-        <v>64214258</v>
+        <v>63573761</v>
       </c>
       <c r="J448" t="s">
-        <v>472</v>
+        <v>459</v>
       </c>
     </row>
     <row r="449" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H449" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I449">
         <v>63742200</v>
       </c>
       <c r="J449" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="450" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H450" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="I450">
-        <v>64606094</v>
+        <v>64114088</v>
       </c>
       <c r="J450" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
     </row>
     <row r="451" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H451" t="s">
-        <v>98</v>
+        <v>656</v>
       </c>
       <c r="I451">
-        <v>64287980</v>
+        <v>64212381</v>
       </c>
       <c r="J451" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
     </row>
     <row r="452" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H452" t="s">
-        <v>98</v>
+        <v>656</v>
       </c>
       <c r="I452">
-        <v>64257297</v>
+        <v>64212544</v>
       </c>
       <c r="J452" t="s">
-        <v>476</v>
+        <v>463</v>
       </c>
     </row>
     <row r="453" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H453" t="s">
-        <v>98</v>
+        <v>656</v>
       </c>
       <c r="I453">
-        <v>66097436</v>
+        <v>64212543</v>
       </c>
       <c r="J453" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
     </row>
     <row r="454" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H454" t="s">
-        <v>143</v>
+        <v>656</v>
       </c>
       <c r="I454">
-        <v>64330309</v>
+        <v>64212552</v>
       </c>
       <c r="J454" t="s">
-        <v>478</v>
+        <v>462</v>
       </c>
     </row>
     <row r="455" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H455" t="s">
-        <v>211</v>
+        <v>169</v>
       </c>
       <c r="I455">
-        <v>64846264</v>
+        <v>64214259</v>
       </c>
       <c r="J455" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
     </row>
     <row r="456" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H456" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
       <c r="I456">
-        <v>64753996</v>
+        <v>64214258</v>
       </c>
       <c r="J456" t="s">
-        <v>480</v>
+        <v>469</v>
       </c>
     </row>
     <row r="457" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H457" t="s">
-        <v>92</v>
+        <v>169</v>
       </c>
       <c r="I457">
-        <v>64778162</v>
+        <v>64223250</v>
       </c>
       <c r="J457" t="s">
-        <v>481</v>
+        <v>467</v>
       </c>
     </row>
     <row r="458" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H458" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I458">
-        <v>64778161</v>
+        <v>64257297</v>
       </c>
       <c r="J458" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
     </row>
     <row r="459" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H459" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="I459">
-        <v>64808932</v>
+        <v>64270608</v>
       </c>
       <c r="J459" t="s">
-        <v>483</v>
+        <v>458</v>
       </c>
     </row>
     <row r="460" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H460" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="I460">
-        <v>64789478</v>
+        <v>64287980</v>
       </c>
       <c r="J460" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
     </row>
     <row r="461" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H461" t="s">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="I461">
-        <v>64912430</v>
+        <v>64330309</v>
       </c>
       <c r="J461" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
     </row>
     <row r="462" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H462" t="s">
-        <v>98</v>
+        <v>656</v>
       </c>
       <c r="I462">
-        <v>64971361</v>
+        <v>64330763</v>
       </c>
       <c r="J462" t="s">
-        <v>486</v>
+        <v>460</v>
       </c>
     </row>
     <row r="463" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H463" t="s">
-        <v>143</v>
+        <v>656</v>
       </c>
       <c r="I463">
-        <v>65145714</v>
+        <v>64330764</v>
       </c>
       <c r="J463" t="s">
-        <v>487</v>
+        <v>461</v>
       </c>
     </row>
     <row r="464" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H464" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I464">
-        <v>65081124</v>
+        <v>64606094</v>
       </c>
       <c r="J464" t="s">
-        <v>488</v>
+        <v>471</v>
       </c>
     </row>
     <row r="465" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H465" t="s">
-        <v>29</v>
+        <v>107</v>
       </c>
       <c r="I465">
-        <v>65181042</v>
+        <v>64753996</v>
       </c>
       <c r="J465" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
     </row>
     <row r="466" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H466" t="s">
-        <v>29</v>
+        <v>656</v>
       </c>
       <c r="I466">
-        <v>65179405</v>
+        <v>64778161</v>
       </c>
       <c r="J466" t="s">
-        <v>490</v>
+        <v>479</v>
       </c>
     </row>
     <row r="467" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H467" t="s">
-        <v>29</v>
+        <v>656</v>
       </c>
       <c r="I467">
-        <v>65566244</v>
+        <v>64778162</v>
       </c>
       <c r="J467" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
     </row>
     <row r="468" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H468" t="s">
-        <v>29</v>
+        <v>107</v>
       </c>
       <c r="I468">
-        <v>65566541</v>
+        <v>64789478</v>
       </c>
       <c r="J468" t="s">
-        <v>492</v>
+        <v>481</v>
       </c>
     </row>
     <row r="469" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H469" t="s">
-        <v>29</v>
+        <v>656</v>
       </c>
       <c r="I469">
-        <v>65656468</v>
+        <v>64808932</v>
       </c>
       <c r="J469" t="s">
-        <v>493</v>
+        <v>480</v>
       </c>
     </row>
     <row r="470" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H470" t="s">
-        <v>29</v>
+        <v>208</v>
       </c>
       <c r="I470">
-        <v>65657039</v>
+        <v>64846264</v>
       </c>
       <c r="J470" t="s">
-        <v>494</v>
+        <v>476</v>
       </c>
     </row>
     <row r="471" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H471" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I471">
-        <v>66217025</v>
+        <v>64912430</v>
       </c>
       <c r="J471" t="s">
-        <v>495</v>
+        <v>482</v>
       </c>
     </row>
     <row r="472" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H472" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I472">
-        <v>66214618</v>
+        <v>64971361</v>
       </c>
       <c r="J472" t="s">
-        <v>496</v>
+        <v>483</v>
       </c>
     </row>
     <row r="473" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H473" t="s">
-        <v>29</v>
+        <v>656</v>
       </c>
       <c r="I473">
-        <v>65935700</v>
+        <v>65081124</v>
       </c>
       <c r="J473" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
     </row>
     <row r="474" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H474" t="s">
-        <v>29</v>
+        <v>141</v>
       </c>
       <c r="I474">
-        <v>65934564</v>
+        <v>65145714</v>
       </c>
       <c r="J474" t="s">
-        <v>498</v>
+        <v>484</v>
       </c>
     </row>
     <row r="475" spans="8:10" x14ac:dyDescent="0.3">
@@ -8240,10 +8326,10 @@
         <v>29</v>
       </c>
       <c r="I475">
-        <v>65933937</v>
+        <v>65179405</v>
       </c>
       <c r="J475" t="s">
-        <v>499</v>
+        <v>487</v>
       </c>
     </row>
     <row r="476" spans="8:10" x14ac:dyDescent="0.3">
@@ -8251,560 +8337,560 @@
         <v>29</v>
       </c>
       <c r="I476">
-        <v>66046959</v>
+        <v>65181042</v>
       </c>
       <c r="J476" t="s">
-        <v>500</v>
+        <v>486</v>
       </c>
     </row>
     <row r="477" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H477" t="s">
-        <v>98</v>
+        <v>29</v>
       </c>
       <c r="I477">
-        <v>65969750</v>
+        <v>65566244</v>
       </c>
       <c r="J477" t="s">
-        <v>501</v>
+        <v>488</v>
       </c>
     </row>
     <row r="478" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H478" t="s">
-        <v>171</v>
+        <v>29</v>
       </c>
       <c r="I478">
-        <v>66358440</v>
+        <v>65566541</v>
       </c>
       <c r="J478" t="s">
-        <v>502</v>
+        <v>489</v>
       </c>
     </row>
     <row r="479" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H479" t="s">
-        <v>143</v>
+        <v>29</v>
       </c>
       <c r="I479">
-        <v>66417803</v>
+        <v>65656468</v>
       </c>
       <c r="J479" t="s">
-        <v>503</v>
+        <v>490</v>
       </c>
     </row>
     <row r="480" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H480" t="s">
-        <v>143</v>
+        <v>29</v>
       </c>
       <c r="I480">
-        <v>66417801</v>
+        <v>65657039</v>
       </c>
       <c r="J480" t="s">
-        <v>3</v>
+        <v>491</v>
       </c>
     </row>
     <row r="481" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H481" t="s">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c r="I481">
-        <v>66357977</v>
+        <v>65933937</v>
       </c>
       <c r="J481" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
     </row>
     <row r="482" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H482" t="s">
-        <v>171</v>
+        <v>29</v>
       </c>
       <c r="I482">
-        <v>67191572</v>
+        <v>65934564</v>
       </c>
       <c r="J482" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
     </row>
     <row r="483" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H483" t="s">
-        <v>171</v>
+        <v>29</v>
       </c>
       <c r="I483">
-        <v>66546178</v>
+        <v>65935700</v>
       </c>
       <c r="J483" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
     </row>
     <row r="484" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H484" t="s">
-        <v>171</v>
+        <v>96</v>
       </c>
       <c r="I484">
-        <v>67627331</v>
+        <v>65969750</v>
       </c>
       <c r="J484" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
     </row>
     <row r="485" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H485" t="s">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c r="I485">
-        <v>66778787</v>
+        <v>66046959</v>
       </c>
       <c r="J485" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="486" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H486" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I486">
-        <v>66778788</v>
+        <v>66214618</v>
       </c>
       <c r="J486" t="s">
-        <v>509</v>
+        <v>493</v>
       </c>
     </row>
     <row r="487" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H487" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I487">
-        <v>66778789</v>
+        <v>66217025</v>
       </c>
       <c r="J487" t="s">
-        <v>510</v>
+        <v>492</v>
       </c>
     </row>
     <row r="488" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H488" t="s">
-        <v>90</v>
+        <v>656</v>
       </c>
       <c r="I488">
-        <v>66896364</v>
+        <v>66357977</v>
       </c>
       <c r="J488" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
     </row>
     <row r="489" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H489" t="s">
-        <v>29</v>
+        <v>169</v>
       </c>
       <c r="I489">
-        <v>66607099</v>
+        <v>66358440</v>
       </c>
       <c r="J489" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
     </row>
     <row r="490" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H490" t="s">
-        <v>29</v>
+        <v>141</v>
       </c>
       <c r="I490">
-        <v>66864708</v>
+        <v>66417803</v>
       </c>
       <c r="J490" t="s">
-        <v>513</v>
+        <v>500</v>
       </c>
     </row>
     <row r="491" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H491" t="s">
-        <v>29</v>
+        <v>141</v>
       </c>
       <c r="I491">
-        <v>66850322</v>
+        <v>66417801</v>
       </c>
       <c r="J491" t="s">
-        <v>514</v>
+        <v>3</v>
       </c>
     </row>
     <row r="492" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H492" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
       <c r="I492">
-        <v>67268341</v>
+        <v>66546178</v>
       </c>
       <c r="J492" t="s">
-        <v>515</v>
+        <v>503</v>
       </c>
     </row>
     <row r="493" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H493" t="s">
-        <v>109</v>
+        <v>29</v>
       </c>
       <c r="I493">
-        <v>67268348</v>
+        <v>66607099</v>
       </c>
       <c r="J493" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
     </row>
     <row r="494" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H494" t="s">
-        <v>109</v>
+        <v>656</v>
       </c>
       <c r="I494">
-        <v>67268349</v>
+        <v>66778787</v>
       </c>
       <c r="J494" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
     </row>
     <row r="495" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H495" t="s">
-        <v>109</v>
+        <v>656</v>
       </c>
       <c r="I495">
-        <v>67268350</v>
+        <v>66778788</v>
       </c>
       <c r="J495" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
     </row>
     <row r="496" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H496" t="s">
-        <v>109</v>
+        <v>656</v>
       </c>
       <c r="I496">
-        <v>67272047</v>
+        <v>66778789</v>
       </c>
       <c r="J496" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
     </row>
     <row r="497" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H497" t="s">
-        <v>109</v>
+        <v>29</v>
       </c>
       <c r="I497">
-        <v>67272046</v>
+        <v>66850322</v>
       </c>
       <c r="J497" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
     </row>
     <row r="498" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H498" t="s">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c r="I498">
-        <v>67438488</v>
+        <v>66864708</v>
       </c>
       <c r="J498" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="499" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H499" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I499">
-        <v>67438487</v>
+        <v>66896364</v>
       </c>
       <c r="J499" t="s">
-        <v>522</v>
+        <v>508</v>
       </c>
     </row>
     <row r="500" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H500" t="s">
-        <v>92</v>
+        <v>169</v>
       </c>
       <c r="I500">
-        <v>68253037</v>
+        <v>67191572</v>
       </c>
       <c r="J500" t="s">
-        <v>523</v>
+        <v>502</v>
       </c>
     </row>
     <row r="501" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H501" t="s">
-        <v>171</v>
+        <v>107</v>
       </c>
       <c r="I501">
-        <v>67891311</v>
+        <v>67268348</v>
       </c>
       <c r="J501" t="s">
-        <v>524</v>
+        <v>513</v>
       </c>
     </row>
     <row r="502" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H502" t="s">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="I502">
-        <v>67900090</v>
+        <v>67268349</v>
       </c>
       <c r="J502" t="s">
-        <v>525</v>
+        <v>514</v>
       </c>
     </row>
     <row r="503" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H503" t="s">
-        <v>29</v>
+        <v>107</v>
       </c>
       <c r="I503">
-        <v>67630646</v>
+        <v>67268341</v>
       </c>
       <c r="J503" t="s">
-        <v>526</v>
+        <v>512</v>
       </c>
     </row>
     <row r="504" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H504" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="I504">
-        <v>67974104</v>
+        <v>67268350</v>
       </c>
       <c r="J504" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
     </row>
     <row r="505" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H505" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I505">
-        <v>67989839</v>
+        <v>67272047</v>
       </c>
       <c r="J505" t="s">
-        <v>528</v>
+        <v>516</v>
       </c>
     </row>
     <row r="506" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H506" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I506">
-        <v>67988468</v>
+        <v>67272046</v>
       </c>
       <c r="J506" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
     </row>
     <row r="507" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H507" t="s">
-        <v>98</v>
+        <v>656</v>
       </c>
       <c r="I507">
-        <v>68466892</v>
+        <v>67438487</v>
       </c>
       <c r="J507" t="s">
-        <v>530</v>
+        <v>519</v>
       </c>
     </row>
     <row r="508" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H508" t="s">
-        <v>98</v>
+        <v>656</v>
       </c>
       <c r="I508">
-        <v>69040158</v>
+        <v>67438488</v>
       </c>
       <c r="J508" t="s">
-        <v>531</v>
+        <v>518</v>
       </c>
     </row>
     <row r="509" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H509" t="s">
-        <v>98</v>
+        <v>169</v>
       </c>
       <c r="I509">
-        <v>68462854</v>
+        <v>67627331</v>
       </c>
       <c r="J509" t="s">
-        <v>532</v>
+        <v>504</v>
       </c>
     </row>
     <row r="510" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H510" t="s">
-        <v>94</v>
-      </c>
-      <c r="I510" t="s">
-        <v>533</v>
+        <v>29</v>
+      </c>
+      <c r="I510">
+        <v>67630646</v>
       </c>
       <c r="J510" t="s">
-        <v>534</v>
+        <v>523</v>
       </c>
     </row>
     <row r="511" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H511" t="s">
-        <v>94</v>
-      </c>
-      <c r="I511" t="s">
-        <v>533</v>
+        <v>169</v>
+      </c>
+      <c r="I511">
+        <v>67891311</v>
       </c>
       <c r="J511" t="s">
-        <v>535</v>
+        <v>521</v>
       </c>
     </row>
     <row r="512" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H512" t="s">
-        <v>92</v>
+        <v>141</v>
       </c>
       <c r="I512">
-        <v>68677002</v>
+        <v>67900090</v>
       </c>
       <c r="J512" t="s">
-        <v>536</v>
+        <v>522</v>
       </c>
     </row>
     <row r="513" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H513" t="s">
-        <v>171</v>
+        <v>96</v>
       </c>
       <c r="I513">
-        <v>68880617</v>
+        <v>67974104</v>
       </c>
       <c r="J513" t="s">
-        <v>537</v>
+        <v>524</v>
       </c>
     </row>
     <row r="514" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H514" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="I514">
-        <v>68934411</v>
+        <v>67988468</v>
       </c>
       <c r="J514" t="s">
-        <v>538</v>
+        <v>526</v>
       </c>
     </row>
     <row r="515" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H515" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="I515">
-        <v>68924611</v>
+        <v>67989839</v>
       </c>
       <c r="J515" t="s">
-        <v>539</v>
+        <v>525</v>
       </c>
     </row>
     <row r="516" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H516" t="s">
-        <v>92</v>
+        <v>656</v>
       </c>
       <c r="I516">
-        <v>69039437</v>
+        <v>68253037</v>
       </c>
       <c r="J516" t="s">
-        <v>540</v>
+        <v>520</v>
       </c>
     </row>
     <row r="517" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H517" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I517">
-        <v>69039778</v>
+        <v>68462854</v>
       </c>
       <c r="J517" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
     </row>
     <row r="518" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H518" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="I518">
-        <v>69279032</v>
+        <v>68466892</v>
       </c>
       <c r="J518" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
     </row>
     <row r="519" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H519" t="s">
-        <v>92</v>
+        <v>656</v>
       </c>
       <c r="I519">
-        <v>68938743</v>
+        <v>68677002</v>
       </c>
       <c r="J519" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
     </row>
     <row r="520" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H520" t="s">
-        <v>58</v>
+        <v>169</v>
       </c>
       <c r="I520">
-        <v>69772629</v>
+        <v>68880617</v>
       </c>
       <c r="J520" t="s">
-        <v>544</v>
+        <v>534</v>
       </c>
     </row>
     <row r="521" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H521" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="I521">
-        <v>69772627</v>
+        <v>68924611</v>
       </c>
       <c r="J521" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
     </row>
     <row r="522" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H522" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="I522">
-        <v>69772625</v>
+        <v>68934411</v>
       </c>
       <c r="J522" t="s">
-        <v>546</v>
+        <v>535</v>
       </c>
     </row>
     <row r="523" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H523" t="s">
-        <v>98</v>
+        <v>656</v>
       </c>
       <c r="I523">
-        <v>69292187</v>
+        <v>68938743</v>
       </c>
       <c r="J523" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
     </row>
     <row r="524" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H524" t="s">
-        <v>98</v>
+        <v>656</v>
       </c>
       <c r="I524">
-        <v>69292186</v>
+        <v>69039437</v>
       </c>
       <c r="J524" t="s">
-        <v>548</v>
+        <v>537</v>
       </c>
     </row>
     <row r="525" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H525" t="s">
-        <v>98</v>
+        <v>656</v>
       </c>
       <c r="I525">
-        <v>69292185</v>
+        <v>69039778</v>
       </c>
       <c r="J525" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
     </row>
     <row r="526" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H526" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="I526">
-        <v>69096297</v>
+        <v>69040158</v>
       </c>
       <c r="J526" t="s">
-        <v>550</v>
+        <v>528</v>
       </c>
     </row>
     <row r="527" spans="8:10" x14ac:dyDescent="0.3">
@@ -8815,411 +8901,414 @@
         <v>69096296</v>
       </c>
       <c r="J527" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="528" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H528" t="s">
-        <v>143</v>
+        <v>58</v>
       </c>
       <c r="I528">
-        <v>69594684</v>
+        <v>69096297</v>
       </c>
       <c r="J528" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
     </row>
     <row r="529" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H529" t="s">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="I529">
-        <v>70204974</v>
+        <v>69279032</v>
       </c>
       <c r="J529" t="s">
-        <v>553</v>
+        <v>539</v>
       </c>
     </row>
     <row r="530" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H530" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I530">
-        <v>70204975</v>
+        <v>69292186</v>
       </c>
       <c r="J530" t="s">
-        <v>554</v>
+        <v>545</v>
       </c>
     </row>
     <row r="531" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H531" t="s">
-        <v>143</v>
+        <v>96</v>
       </c>
       <c r="I531">
-        <v>69767288</v>
+        <v>69292185</v>
       </c>
       <c r="J531" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
     </row>
     <row r="532" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H532" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I532">
-        <v>69766464</v>
+        <v>69292187</v>
       </c>
       <c r="J532" t="s">
-        <v>556</v>
+        <v>544</v>
       </c>
     </row>
     <row r="533" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H533" t="s">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="I533">
-        <v>69803799</v>
+        <v>69594684</v>
       </c>
       <c r="J533" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
     </row>
     <row r="534" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H534" t="s">
-        <v>143</v>
+        <v>96</v>
       </c>
       <c r="I534">
-        <v>70251147</v>
+        <v>69766464</v>
       </c>
       <c r="J534" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
     </row>
     <row r="535" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H535" t="s">
-        <v>171</v>
+        <v>141</v>
       </c>
       <c r="I535">
-        <v>69770093</v>
+        <v>69767288</v>
       </c>
       <c r="J535" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
     </row>
     <row r="536" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H536" t="s">
-        <v>92</v>
+        <v>169</v>
       </c>
       <c r="I536">
-        <v>70205079</v>
+        <v>69770093</v>
       </c>
       <c r="J536" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
     </row>
     <row r="537" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H537" t="s">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="I537">
-        <v>70530577</v>
+        <v>69772627</v>
       </c>
       <c r="J537" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
     </row>
     <row r="538" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H538" t="s">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="I538">
-        <v>70530576</v>
+        <v>69772625</v>
       </c>
       <c r="J538" t="s">
-        <v>562</v>
+        <v>543</v>
       </c>
     </row>
     <row r="539" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H539" t="s">
-        <v>109</v>
+        <v>58</v>
       </c>
       <c r="I539">
-        <v>71030052</v>
+        <v>69772629</v>
       </c>
       <c r="J539" t="s">
-        <v>563</v>
+        <v>541</v>
       </c>
     </row>
     <row r="540" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H540" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="I540">
-        <v>70770186</v>
+        <v>69803799</v>
       </c>
       <c r="J540" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
     </row>
     <row r="541" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H541" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="I541">
-        <v>71173111</v>
+        <v>70204974</v>
       </c>
       <c r="J541" t="s">
-        <v>565</v>
+        <v>550</v>
       </c>
     </row>
     <row r="542" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H542" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="I542">
-        <v>71156871</v>
+        <v>70204975</v>
       </c>
       <c r="J542" t="s">
-        <v>566</v>
+        <v>551</v>
       </c>
     </row>
     <row r="543" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H543" t="s">
-        <v>115</v>
+        <v>656</v>
       </c>
       <c r="I543">
-        <v>71291488</v>
+        <v>70205079</v>
       </c>
       <c r="J543" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
     </row>
     <row r="544" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H544" t="s">
+        <v>141</v>
+      </c>
       <c r="I544">
-        <v>71042279</v>
+        <v>70251147</v>
       </c>
       <c r="J544" t="s">
-        <v>568</v>
+        <v>555</v>
       </c>
     </row>
     <row r="545" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H545" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="I545">
-        <v>71947627</v>
+        <v>70530577</v>
       </c>
       <c r="J545" t="s">
-        <v>569</v>
+        <v>558</v>
       </c>
     </row>
     <row r="546" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H546" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="I546">
-        <v>72182444</v>
+        <v>70530576</v>
       </c>
       <c r="J546" t="s">
-        <v>570</v>
+        <v>559</v>
       </c>
     </row>
     <row r="547" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H547" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I547">
-        <v>72300747</v>
+        <v>70770186</v>
       </c>
       <c r="J547" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
     </row>
     <row r="548" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H548" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="I548">
-        <v>72417582</v>
+        <v>71030052</v>
       </c>
       <c r="J548" t="s">
-        <v>572</v>
+        <v>560</v>
       </c>
     </row>
     <row r="549" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H549" t="s">
-        <v>115</v>
+        <v>665</v>
       </c>
       <c r="I549">
-        <v>72614935</v>
+        <v>71042279</v>
       </c>
       <c r="J549" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
     </row>
     <row r="550" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H550" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I550">
-        <v>72614936</v>
+        <v>71156871</v>
       </c>
       <c r="J550" t="s">
-        <v>574</v>
+        <v>563</v>
       </c>
     </row>
     <row r="551" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H551" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I551">
-        <v>72614937</v>
+        <v>71173111</v>
       </c>
       <c r="J551" t="s">
-        <v>575</v>
+        <v>562</v>
       </c>
     </row>
     <row r="552" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H552" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="I552">
-        <v>73226633</v>
+        <v>71291488</v>
       </c>
       <c r="J552" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
     </row>
     <row r="553" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H553" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="I553">
-        <v>73226632</v>
+        <v>71947627</v>
       </c>
       <c r="J553" t="s">
-        <v>577</v>
+        <v>566</v>
       </c>
     </row>
     <row r="554" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H554" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="I554">
-        <v>73316683</v>
+        <v>72182444</v>
       </c>
       <c r="J554" t="s">
-        <v>578</v>
+        <v>567</v>
       </c>
     </row>
     <row r="555" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H555" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="I555">
-        <v>73316684</v>
+        <v>72300747</v>
       </c>
       <c r="J555" t="s">
-        <v>579</v>
+        <v>568</v>
       </c>
     </row>
     <row r="556" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H556" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="I556">
-        <v>73316685</v>
+        <v>72417582</v>
       </c>
       <c r="J556" t="s">
-        <v>580</v>
+        <v>569</v>
       </c>
     </row>
     <row r="557" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H557" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I557">
-        <v>72699936</v>
+        <v>72614935</v>
       </c>
       <c r="J557" t="s">
-        <v>581</v>
+        <v>570</v>
       </c>
     </row>
     <row r="558" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H558" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I558">
-        <v>72699935</v>
+        <v>72614937</v>
       </c>
       <c r="J558" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
     </row>
     <row r="559" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H559" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I559">
-        <v>72828733</v>
+        <v>72614936</v>
       </c>
       <c r="J559" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
     </row>
     <row r="560" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H560" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="I560">
-        <v>72828734</v>
+        <v>72683872</v>
       </c>
       <c r="J560" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="561" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H561" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="I561">
-        <v>72683872</v>
+        <v>72699935</v>
       </c>
       <c r="J561" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
     </row>
     <row r="562" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H562" t="s">
-        <v>58</v>
+        <v>113</v>
       </c>
       <c r="I562">
-        <v>72910681</v>
+        <v>72699936</v>
       </c>
       <c r="J562" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
     </row>
     <row r="563" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H563" t="s">
-        <v>58</v>
+        <v>113</v>
       </c>
       <c r="I563">
-        <v>72910683</v>
+        <v>72828734</v>
       </c>
       <c r="J563" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
     </row>
     <row r="564" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H564" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="I564">
-        <v>73523448</v>
+        <v>72828733</v>
       </c>
       <c r="J564" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
     </row>
     <row r="565" spans="8:10" x14ac:dyDescent="0.3">
@@ -9227,439 +9316,758 @@
         <v>58</v>
       </c>
       <c r="I565">
-        <v>73461995</v>
+        <v>72910681</v>
       </c>
       <c r="J565" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
     </row>
     <row r="566" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H566" t="s">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="I566">
-        <v>73956460</v>
+        <v>72910683</v>
       </c>
       <c r="J566" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
     </row>
     <row r="567" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H567" t="s">
-        <v>98</v>
+        <v>656</v>
       </c>
       <c r="I567">
-        <v>73956461</v>
+        <v>73226632</v>
       </c>
       <c r="J567" t="s">
-        <v>591</v>
+        <v>574</v>
       </c>
     </row>
     <row r="568" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H568" t="s">
-        <v>98</v>
+        <v>656</v>
       </c>
       <c r="I568">
-        <v>73956459</v>
+        <v>73226633</v>
       </c>
       <c r="J568" t="s">
-        <v>592</v>
+        <v>573</v>
       </c>
     </row>
     <row r="569" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H569" t="s">
-        <v>58</v>
+        <v>141</v>
       </c>
       <c r="I569">
-        <v>74685916</v>
+        <v>73316684</v>
       </c>
       <c r="J569" t="s">
-        <v>593</v>
+        <v>576</v>
       </c>
     </row>
     <row r="570" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H570" t="s">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="I570">
-        <v>73975553</v>
+        <v>73316683</v>
       </c>
       <c r="J570" t="s">
-        <v>594</v>
+        <v>575</v>
       </c>
     </row>
     <row r="571" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H571" t="s">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="I571">
-        <v>73952843</v>
+        <v>73316685</v>
       </c>
       <c r="J571" t="s">
-        <v>595</v>
+        <v>577</v>
       </c>
     </row>
     <row r="572" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H572" t="s">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="I572">
-        <v>74550323</v>
+        <v>73461995</v>
       </c>
       <c r="J572" t="s">
-        <v>596</v>
+        <v>586</v>
       </c>
     </row>
     <row r="573" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H573" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I573">
-        <v>75989703</v>
+        <v>73523448</v>
       </c>
       <c r="J573" t="s">
-        <v>597</v>
+        <v>585</v>
       </c>
     </row>
     <row r="574" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H574" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I574">
-        <v>74693807</v>
+        <v>73893263</v>
       </c>
       <c r="J574" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="575" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H575" t="s">
-        <v>143</v>
+        <v>96</v>
       </c>
       <c r="I575">
-        <v>73893263</v>
+        <v>73952843</v>
       </c>
       <c r="J575" t="s">
-        <v>15</v>
+        <v>592</v>
       </c>
     </row>
     <row r="576" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H576" t="s">
-        <v>143</v>
+        <v>96</v>
       </c>
       <c r="I576">
-        <v>74884452</v>
+        <v>73956460</v>
       </c>
       <c r="J576" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
     </row>
     <row r="577" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H577" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I577">
-        <v>74826973</v>
+        <v>73956461</v>
       </c>
       <c r="J577" t="s">
-        <v>599</v>
+        <v>588</v>
       </c>
     </row>
     <row r="578" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H578" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I578">
-        <v>74826974</v>
+        <v>73956459</v>
       </c>
       <c r="J578" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
     </row>
     <row r="579" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H579" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="I579">
-        <v>75077119</v>
+        <v>73975553</v>
       </c>
       <c r="J579" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
     </row>
     <row r="580" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H580" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="I580">
-        <v>78867502</v>
+        <v>74550323</v>
       </c>
       <c r="J580" t="s">
-        <v>602</v>
+        <v>593</v>
       </c>
     </row>
     <row r="581" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H581" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="I581">
-        <v>80192305</v>
+        <v>74685916</v>
       </c>
       <c r="J581" t="s">
-        <v>603</v>
+        <v>590</v>
       </c>
     </row>
     <row r="582" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H582" t="s">
-        <v>92</v>
+        <v>141</v>
       </c>
       <c r="I582">
-        <v>75741354</v>
+        <v>74693807</v>
       </c>
       <c r="J582" t="s">
-        <v>604</v>
+        <v>14</v>
       </c>
     </row>
     <row r="583" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H583" t="s">
-        <v>143</v>
+        <v>96</v>
       </c>
       <c r="I583">
-        <v>78625461</v>
+        <v>74826973</v>
       </c>
       <c r="J583" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
     </row>
     <row r="584" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H584" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I584">
-        <v>76375598</v>
+        <v>74826974</v>
       </c>
       <c r="J584" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
     </row>
     <row r="585" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H585" t="s">
-        <v>92</v>
+        <v>141</v>
       </c>
       <c r="I585">
-        <v>76375597</v>
+        <v>74884452</v>
       </c>
       <c r="J585" t="s">
-        <v>21</v>
+        <v>595</v>
       </c>
     </row>
     <row r="586" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H586" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I586">
-        <v>76374400</v>
+        <v>75077119</v>
       </c>
       <c r="J586" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
     </row>
     <row r="587" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H587" t="s">
-        <v>92</v>
+        <v>656</v>
       </c>
       <c r="I587">
-        <v>76374401</v>
+        <v>75741354</v>
       </c>
       <c r="J587" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
     </row>
     <row r="588" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H588" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I588">
-        <v>76241042</v>
+        <v>75989703</v>
       </c>
       <c r="J588" t="s">
-        <v>609</v>
+        <v>594</v>
       </c>
     </row>
     <row r="589" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H589" t="s">
-        <v>90</v>
+        <v>656</v>
       </c>
       <c r="I589">
-        <v>76533940</v>
+        <v>76241042</v>
       </c>
       <c r="J589" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
     </row>
     <row r="590" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H590" t="s">
-        <v>92</v>
+        <v>656</v>
       </c>
       <c r="I590">
-        <v>77463489</v>
+        <v>76374401</v>
       </c>
       <c r="J590" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
     </row>
     <row r="591" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H591" t="s">
-        <v>92</v>
+        <v>656</v>
       </c>
       <c r="I591">
-        <v>77463490</v>
+        <v>76374400</v>
       </c>
       <c r="J591" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
     </row>
     <row r="592" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H592" t="s">
-        <v>58</v>
+        <v>656</v>
       </c>
       <c r="I592" s="2">
-        <v>78907466</v>
+        <v>76375598</v>
       </c>
       <c r="J592" t="s">
-        <v>613</v>
+        <v>603</v>
       </c>
     </row>
     <row r="593" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H593" t="s">
-        <v>58</v>
+        <v>656</v>
       </c>
       <c r="I593" s="2">
-        <v>78907465</v>
+        <v>76375597</v>
       </c>
       <c r="J593" t="s">
-        <v>614</v>
+        <v>21</v>
       </c>
     </row>
     <row r="594" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H594" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="I594" s="2">
-        <v>78903848</v>
+        <v>76533940</v>
       </c>
       <c r="J594" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
     </row>
     <row r="595" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H595" t="s">
-        <v>58</v>
+        <v>656</v>
       </c>
       <c r="I595" s="2">
-        <v>78903849</v>
+        <v>77463489</v>
       </c>
       <c r="J595" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
     </row>
     <row r="596" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H596" t="s">
-        <v>58</v>
+        <v>656</v>
       </c>
       <c r="I596" s="2">
-        <v>78621004</v>
+        <v>77463490</v>
       </c>
       <c r="J596" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
     </row>
     <row r="597" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H597" t="s">
-        <v>29</v>
-      </c>
-      <c r="I597" t="s">
-        <v>533</v>
+        <v>58</v>
+      </c>
+      <c r="I597">
+        <v>78621004</v>
       </c>
       <c r="J597" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="598" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H598" t="s">
-        <v>90</v>
-      </c>
-      <c r="I598" t="s">
-        <v>533</v>
+        <v>141</v>
+      </c>
+      <c r="I598">
+        <v>78625461</v>
       </c>
       <c r="J598" t="s">
-        <v>619</v>
+        <v>602</v>
       </c>
     </row>
     <row r="599" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H599" t="s">
-        <v>98</v>
-      </c>
-      <c r="I599" t="s">
-        <v>533</v>
+        <v>656</v>
+      </c>
+      <c r="I599">
+        <v>78867502</v>
       </c>
       <c r="J599" t="s">
-        <v>620</v>
+        <v>599</v>
       </c>
     </row>
     <row r="600" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H600" t="s">
-        <v>98</v>
-      </c>
-      <c r="I600" t="s">
-        <v>533</v>
+        <v>58</v>
+      </c>
+      <c r="I600">
+        <v>78903849</v>
       </c>
       <c r="J600" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
     </row>
     <row r="601" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H601" t="s">
-        <v>152</v>
-      </c>
-      <c r="I601" t="s">
-        <v>533</v>
+        <v>58</v>
+      </c>
+      <c r="I601">
+        <v>78903848</v>
       </c>
       <c r="J601" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="602" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H602" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="I602" s="2">
-        <v>80629877</v>
+        <v>78907465</v>
       </c>
       <c r="J602" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
     </row>
     <row r="603" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H603" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="I603" s="2">
+        <v>78907466</v>
+      </c>
+      <c r="J603" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="604" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H604" t="s">
+        <v>169</v>
+      </c>
+      <c r="I604">
+        <v>79040263</v>
+      </c>
+      <c r="J604" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="605" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H605" t="s">
+        <v>208</v>
+      </c>
+      <c r="I605">
+        <v>79475749</v>
+      </c>
+      <c r="J605" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="606" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H606" t="s">
+        <v>141</v>
+      </c>
+      <c r="I606">
+        <v>79944232</v>
+      </c>
+      <c r="J606" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="607" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H607" t="s">
+        <v>656</v>
+      </c>
+      <c r="I607">
+        <v>80192305</v>
+      </c>
+      <c r="J607" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="608" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H608" t="s">
+        <v>208</v>
+      </c>
+      <c r="I608">
+        <v>80460979</v>
+      </c>
+      <c r="J608" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="609" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H609" t="s">
+        <v>656</v>
+      </c>
+      <c r="I609">
         <v>80629881</v>
       </c>
-      <c r="J603" t="s">
-        <v>624</v>
+      <c r="J609" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="610" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H610" t="s">
+        <v>656</v>
+      </c>
+      <c r="I610">
+        <v>80629877</v>
+      </c>
+      <c r="J610" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="611" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H611" t="s">
+        <v>141</v>
+      </c>
+      <c r="I611">
+        <v>81340922</v>
+      </c>
+      <c r="J611" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="612" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H612" t="s">
+        <v>169</v>
+      </c>
+      <c r="I612" t="s">
+        <v>530</v>
+      </c>
+      <c r="J612" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="613" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H613" t="s">
+        <v>96</v>
+      </c>
+      <c r="I613" t="s">
+        <v>530</v>
+      </c>
+      <c r="J613" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="614" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H614" t="s">
+        <v>96</v>
+      </c>
+      <c r="I614" t="s">
+        <v>530</v>
+      </c>
+      <c r="J614" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="615" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H615" t="s">
+        <v>90</v>
+      </c>
+      <c r="I615" t="s">
+        <v>530</v>
+      </c>
+      <c r="J615" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="616" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H616" t="s">
+        <v>96</v>
+      </c>
+      <c r="I616" t="s">
+        <v>530</v>
+      </c>
+      <c r="J616" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="617" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H617" t="s">
+        <v>96</v>
+      </c>
+      <c r="I617" t="s">
+        <v>530</v>
+      </c>
+      <c r="J617" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="618" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H618" t="s">
+        <v>150</v>
+      </c>
+      <c r="I618" t="s">
+        <v>530</v>
+      </c>
+      <c r="J618" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="619" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H619" t="s">
+        <v>58</v>
+      </c>
+      <c r="I619" t="s">
+        <v>530</v>
+      </c>
+      <c r="J619" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="620" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H620" t="s">
+        <v>96</v>
+      </c>
+      <c r="I620" t="s">
+        <v>530</v>
+      </c>
+      <c r="J620" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="621" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H621" t="s">
+        <v>169</v>
+      </c>
+      <c r="I621" t="s">
+        <v>530</v>
+      </c>
+      <c r="J621" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="622" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H622" t="s">
+        <v>656</v>
+      </c>
+      <c r="I622" t="s">
+        <v>530</v>
+      </c>
+      <c r="J622" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="623" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H623" t="s">
+        <v>58</v>
+      </c>
+      <c r="I623" t="s">
+        <v>530</v>
+      </c>
+      <c r="J623" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="624" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H624" t="s">
+        <v>29</v>
+      </c>
+      <c r="I624" t="s">
+        <v>530</v>
+      </c>
+      <c r="J624" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="625" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H625" t="s">
+        <v>141</v>
+      </c>
+      <c r="I625" t="s">
+        <v>530</v>
+      </c>
+      <c r="J625" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="626" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H626" t="s">
+        <v>169</v>
+      </c>
+      <c r="I626" t="s">
+        <v>530</v>
+      </c>
+      <c r="J626" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="627" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H627" t="s">
+        <v>96</v>
+      </c>
+      <c r="I627" t="s">
+        <v>530</v>
+      </c>
+      <c r="J627" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="628" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H628" t="s">
+        <v>656</v>
+      </c>
+      <c r="I628" t="s">
+        <v>530</v>
+      </c>
+      <c r="J628" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="629" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H629" t="s">
+        <v>169</v>
+      </c>
+      <c r="I629" t="s">
+        <v>530</v>
+      </c>
+      <c r="J629" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="630" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H630" t="s">
+        <v>169</v>
+      </c>
+      <c r="I630" t="s">
+        <v>530</v>
+      </c>
+      <c r="J630" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="631" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H631" t="s">
+        <v>90</v>
+      </c>
+      <c r="I631" t="s">
+        <v>530</v>
+      </c>
+      <c r="J631" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="632" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H632" t="s">
+        <v>29</v>
+      </c>
+      <c r="I632" t="s">
+        <v>530</v>
+      </c>
+      <c r="J632" t="s">
+        <v>685</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C1" xr:uid="{00000000-0009-0000-0000-000000000000}">
+  <autoFilter ref="A1:C1">
     <sortState ref="A2:C74">
       <sortCondition descending="1" ref="C1"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A69:A1048576 A1:A62">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -9667,7 +10075,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A13:C27"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -9678,13 +10086,13 @@
   <sheetData>
     <row r="13" spans="1:3" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -9695,7 +10103,7 @@
         <v>70</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -9703,10 +10111,10 @@
         <v>4125377</v>
       </c>
       <c r="B15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C15" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -9714,10 +10122,10 @@
         <v>26426530</v>
       </c>
       <c r="B16" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C16" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -9725,10 +10133,10 @@
         <v>43252471</v>
       </c>
       <c r="B17" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C17" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -9736,10 +10144,10 @@
         <v>64789478</v>
       </c>
       <c r="B18" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C18" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -9747,10 +10155,10 @@
         <v>71030052</v>
       </c>
       <c r="B19" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="C19" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -9758,10 +10166,10 @@
         <v>11229298</v>
       </c>
       <c r="B20" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C20" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
     </row>
     <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
@@ -9769,10 +10177,10 @@
         <v>75077119</v>
       </c>
       <c r="B21" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="C21" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -9780,10 +10188,10 @@
         <v>42519088</v>
       </c>
       <c r="B22" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C22" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -9791,10 +10199,10 @@
         <v>17579394</v>
       </c>
       <c r="B23" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C23" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -9802,10 +10210,10 @@
         <v>53569741</v>
       </c>
       <c r="B24" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C24" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -9813,10 +10221,10 @@
         <v>53583387</v>
       </c>
       <c r="B25" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C25" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -9824,10 +10232,10 @@
         <v>12439390</v>
       </c>
       <c r="B26" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C26" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -9835,24 +10243,24 @@
         <v>14107560</v>
       </c>
       <c r="B27" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C27" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A13:C13" xr:uid="{00000000-0009-0000-0000-000001000000}">
+  <autoFilter ref="A13:C13">
     <sortState ref="A14:C25">
       <sortCondition descending="1" ref="C13"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A26:A27 A14:A24">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A25">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/이슈제품.xlsx
+++ b/data/이슈제품.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OA\Desktop\쿠팡업로드\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{522AF6C3-1DDE-46ED-8856-E183636DA996}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$13:$C$13</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -30,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1648" uniqueCount="680">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1626" uniqueCount="669">
   <si>
     <t>오아디머무드등-화이트</t>
   </si>
@@ -2015,58 +2014,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>오아넥스트레쳐</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>보아르아이워시</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>오아클린건</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>오아이지네일드릴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>오아듀얼히팅뷰러-핑크</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>오아듀얼히팅뷰러-화이트</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>오아퀵롤차저65W-어비스블랙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>오아에어셋2-아이보리</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>오아퓨어필워터</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>오아UV렌즈세척기-아이보리</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>협의, 10/21 예정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10/20 &gt; 10/16 입고확정</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10/16 입고확정</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>입고확정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2114,12 +2065,16 @@
   </si>
   <si>
     <t>뷰티</t>
+  </si>
+  <si>
+    <t>10/20 생산완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="7">
     <font>
       <sz val="11"/>
@@ -2239,67 +2194,7 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="7">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2645,7 +2540,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K611"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -2782,7 +2677,7 @@
         <v>344</v>
       </c>
       <c r="C6" t="s">
-        <v>661</v>
+        <v>651</v>
       </c>
       <c r="H6" t="s">
         <v>29</v>
@@ -2960,13 +2855,13 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14">
-        <v>12439390</v>
+        <v>75077119</v>
       </c>
       <c r="B14" t="s">
-        <v>205</v>
+        <v>598</v>
       </c>
       <c r="C14" t="s">
-        <v>662</v>
+        <v>643</v>
       </c>
       <c r="H14" t="s">
         <v>29</v>
@@ -2983,13 +2878,13 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15">
-        <v>14107560</v>
+        <v>53583387</v>
       </c>
       <c r="B15" t="s">
-        <v>194</v>
+        <v>372</v>
       </c>
       <c r="C15" t="s">
-        <v>662</v>
+        <v>632</v>
       </c>
       <c r="H15" t="s">
         <v>29</v>
@@ -3006,13 +2901,13 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16">
-        <v>75077119</v>
-      </c>
-      <c r="B16" t="s">
-        <v>598</v>
+        <v>51623281</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>624</v>
       </c>
       <c r="C16" t="s">
-        <v>643</v>
+        <v>626</v>
       </c>
       <c r="H16" t="s">
         <v>29</v>
@@ -3029,13 +2924,13 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17">
-        <v>53583387</v>
-      </c>
-      <c r="B17" t="s">
-        <v>372</v>
+        <v>51989601</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>625</v>
       </c>
       <c r="C17" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="H17" t="s">
         <v>29</v>
@@ -3052,10 +2947,10 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18">
-        <v>51623281</v>
+        <v>11192166</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>624</v>
+        <v>166</v>
       </c>
       <c r="C18" t="s">
         <v>626</v>
@@ -3075,10 +2970,10 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19">
-        <v>51989601</v>
+        <v>15812678</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>625</v>
+        <v>145</v>
       </c>
       <c r="C19" t="s">
         <v>626</v>
@@ -3098,10 +2993,10 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20">
-        <v>11192166</v>
+        <v>12091621</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="C20" t="s">
         <v>626</v>
@@ -3121,10 +3016,10 @@
     </row>
     <row r="21" spans="1:11" s="3" customFormat="1">
       <c r="A21">
-        <v>15812678</v>
+        <v>12143584</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C21" t="s">
         <v>626</v>
@@ -3144,10 +3039,10 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22">
-        <v>12091621</v>
+        <v>11192167</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="C22" t="s">
         <v>626</v>
@@ -3167,10 +3062,10 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23">
-        <v>12143584</v>
+        <v>12143581</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C23" t="s">
         <v>626</v>
@@ -3190,10 +3085,10 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24">
-        <v>11192167</v>
+        <v>11192165</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C24" t="s">
         <v>626</v>
@@ -3213,10 +3108,10 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25">
-        <v>12143581</v>
+        <v>11192163</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C25" t="s">
         <v>626</v>
@@ -3236,10 +3131,10 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26">
-        <v>11192165</v>
+        <v>11291291</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="C26" t="s">
         <v>626</v>
@@ -3259,10 +3154,10 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27">
-        <v>11192163</v>
+        <v>16171214</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C27" t="s">
         <v>626</v>
@@ -3282,10 +3177,10 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28">
-        <v>11291291</v>
+        <v>12218847</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C28" t="s">
         <v>626</v>
@@ -3305,10 +3200,10 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29">
-        <v>16171214</v>
+        <v>15838517</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C29" t="s">
         <v>626</v>
@@ -3328,10 +3223,10 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30">
-        <v>12218847</v>
+        <v>12673238</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C30" t="s">
         <v>626</v>
@@ -3351,10 +3246,10 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31">
-        <v>15838517</v>
+        <v>37790051</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C31" t="s">
         <v>626</v>
@@ -3374,10 +3269,10 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32">
-        <v>12673238</v>
+        <v>37594934</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="C32" t="s">
         <v>626</v>
@@ -3397,10 +3292,10 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33">
-        <v>37790051</v>
+        <v>15702671</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="C33" t="s">
         <v>626</v>
@@ -3420,10 +3315,10 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34">
-        <v>37594934</v>
+        <v>39071990</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C34" t="s">
         <v>626</v>
@@ -3443,10 +3338,10 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35">
-        <v>15702671</v>
+        <v>52204284</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>173</v>
+        <v>91</v>
       </c>
       <c r="C35" t="s">
         <v>626</v>
@@ -3466,10 +3361,10 @@
     </row>
     <row r="36" spans="1:11">
       <c r="A36">
-        <v>39071990</v>
+        <v>39006854</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C36" t="s">
         <v>626</v>
@@ -3489,10 +3384,10 @@
     </row>
     <row r="37" spans="1:11">
       <c r="A37">
-        <v>52204284</v>
+        <v>39006857</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>91</v>
+        <v>161</v>
       </c>
       <c r="C37" t="s">
         <v>626</v>
@@ -3512,10 +3407,10 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38">
-        <v>39006854</v>
+        <v>39006855</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C38" t="s">
         <v>626</v>
@@ -3535,10 +3430,10 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39">
-        <v>39006857</v>
+        <v>51883980</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>161</v>
+        <v>361</v>
       </c>
       <c r="C39" t="s">
         <v>626</v>
@@ -3558,10 +3453,10 @@
     </row>
     <row r="40" spans="1:11">
       <c r="A40">
-        <v>39006855</v>
+        <v>52578670</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>162</v>
+        <v>366</v>
       </c>
       <c r="C40" t="s">
         <v>626</v>
@@ -3581,10 +3476,10 @@
     </row>
     <row r="41" spans="1:11">
       <c r="A41">
-        <v>51883980</v>
+        <v>52155531</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>361</v>
+        <v>93</v>
       </c>
       <c r="C41" t="s">
         <v>626</v>
@@ -3604,10 +3499,10 @@
     </row>
     <row r="42" spans="1:11">
       <c r="A42">
-        <v>52578670</v>
+        <v>15831347</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>366</v>
+        <v>141</v>
       </c>
       <c r="C42" t="s">
         <v>626</v>
@@ -3627,10 +3522,10 @@
     </row>
     <row r="43" spans="1:11">
       <c r="A43">
-        <v>52155531</v>
+        <v>32548061</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>93</v>
+        <v>168</v>
       </c>
       <c r="C43" t="s">
         <v>626</v>
@@ -3650,10 +3545,10 @@
     </row>
     <row r="44" spans="1:11">
       <c r="A44">
-        <v>15831347</v>
+        <v>35876282</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="C44" t="s">
         <v>626</v>
@@ -3673,10 +3568,10 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45">
-        <v>32548061</v>
+        <v>16805855</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="C45" t="s">
         <v>626</v>
@@ -3696,10 +3591,10 @@
     </row>
     <row r="46" spans="1:11">
       <c r="A46">
-        <v>35876282</v>
+        <v>55381383</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>172</v>
+        <v>383</v>
       </c>
       <c r="C46" t="s">
         <v>626</v>
@@ -3719,10 +3614,10 @@
     </row>
     <row r="47" spans="1:11">
       <c r="A47">
-        <v>16805855</v>
+        <v>55449180</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>144</v>
+        <v>385</v>
       </c>
       <c r="C47" t="s">
         <v>626</v>
@@ -3742,10 +3637,10 @@
     </row>
     <row r="48" spans="1:11">
       <c r="A48">
-        <v>55381383</v>
+        <v>55384739</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C48" t="s">
         <v>626</v>
@@ -3765,10 +3660,10 @@
     </row>
     <row r="49" spans="1:11">
       <c r="A49">
-        <v>55449180</v>
+        <v>55389336</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>385</v>
+        <v>623</v>
       </c>
       <c r="C49" t="s">
         <v>626</v>
@@ -3788,10 +3683,10 @@
     </row>
     <row r="50" spans="1:11">
       <c r="A50">
-        <v>55384739</v>
+        <v>55609278</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C50" t="s">
         <v>626</v>
@@ -3811,13 +3706,13 @@
     </row>
     <row r="51" spans="1:11">
       <c r="A51">
-        <v>55389336</v>
+        <v>71042279</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>623</v>
+        <v>565</v>
       </c>
       <c r="C51" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H51" t="s">
         <v>58</v>
@@ -3834,13 +3729,13 @@
     </row>
     <row r="52" spans="1:11">
       <c r="A52">
-        <v>55609278</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>384</v>
+        <v>67630646</v>
+      </c>
+      <c r="B52" t="s">
+        <v>526</v>
       </c>
       <c r="C52" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="H52" t="s">
         <v>58</v>
@@ -3857,13 +3752,13 @@
     </row>
     <row r="53" spans="1:11">
       <c r="A53">
-        <v>71042279</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>565</v>
+        <v>64971361</v>
+      </c>
+      <c r="B53" t="s">
+        <v>486</v>
       </c>
       <c r="C53" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="H53" t="s">
         <v>58</v>
@@ -3880,10 +3775,10 @@
     </row>
     <row r="54" spans="1:11">
       <c r="A54">
-        <v>67630646</v>
+        <v>62421723</v>
       </c>
       <c r="B54" t="s">
-        <v>526</v>
+        <v>454</v>
       </c>
       <c r="C54" t="s">
         <v>630</v>
@@ -3903,10 +3798,10 @@
     </row>
     <row r="55" spans="1:11">
       <c r="A55">
-        <v>64971361</v>
+        <v>62374813</v>
       </c>
       <c r="B55" t="s">
-        <v>486</v>
+        <v>455</v>
       </c>
       <c r="C55" t="s">
         <v>630</v>
@@ -3926,10 +3821,10 @@
     </row>
     <row r="56" spans="1:11">
       <c r="A56">
-        <v>62421723</v>
+        <v>68462854</v>
       </c>
       <c r="B56" t="s">
-        <v>454</v>
+        <v>532</v>
       </c>
       <c r="C56" t="s">
         <v>630</v>
@@ -3949,10 +3844,10 @@
     </row>
     <row r="57" spans="1:11">
       <c r="A57">
-        <v>62374813</v>
+        <v>64114088</v>
       </c>
       <c r="B57" t="s">
-        <v>455</v>
+        <v>469</v>
       </c>
       <c r="C57" t="s">
         <v>630</v>
@@ -3972,10 +3867,10 @@
     </row>
     <row r="58" spans="1:11">
       <c r="A58">
-        <v>68462854</v>
+        <v>19213859</v>
       </c>
       <c r="B58" t="s">
-        <v>532</v>
+        <v>34</v>
       </c>
       <c r="C58" t="s">
         <v>630</v>
@@ -3995,10 +3890,10 @@
     </row>
     <row r="59" spans="1:11">
       <c r="A59">
-        <v>64114088</v>
+        <v>13004238</v>
       </c>
       <c r="B59" t="s">
-        <v>469</v>
+        <v>36</v>
       </c>
       <c r="C59" t="s">
         <v>630</v>
@@ -4018,13 +3913,13 @@
     </row>
     <row r="60" spans="1:11">
       <c r="A60">
-        <v>19213859</v>
+        <v>11229298</v>
       </c>
       <c r="B60" t="s">
-        <v>34</v>
+        <v>174</v>
       </c>
       <c r="C60" t="s">
-        <v>630</v>
+        <v>645</v>
       </c>
       <c r="H60" t="s">
         <v>58</v>
@@ -4039,15 +3934,15 @@
         <v>25433097</v>
       </c>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61" spans="1:11" ht="82.5">
       <c r="A61">
-        <v>13004238</v>
+        <v>37161537</v>
       </c>
       <c r="B61" t="s">
-        <v>36</v>
-      </c>
-      <c r="C61" t="s">
-        <v>630</v>
+        <v>288</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>646</v>
       </c>
       <c r="H61" t="s">
         <v>58</v>
@@ -4064,13 +3959,13 @@
     </row>
     <row r="62" spans="1:11">
       <c r="A62">
-        <v>11229298</v>
+        <v>13745117</v>
       </c>
       <c r="B62" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="C62" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="H62" t="s">
         <v>90</v>
@@ -4085,15 +3980,15 @@
         <v>52204284</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="82.5">
+    <row r="63" spans="1:11">
       <c r="A63">
-        <v>37161537</v>
+        <v>73226633</v>
       </c>
       <c r="B63" t="s">
-        <v>288</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>646</v>
+        <v>573</v>
+      </c>
+      <c r="C63" t="s">
+        <v>668</v>
       </c>
       <c r="H63" t="s">
         <v>92</v>
@@ -4109,15 +4004,6 @@
       </c>
     </row>
     <row r="64" spans="1:11">
-      <c r="A64">
-        <v>13745117</v>
-      </c>
-      <c r="B64" t="s">
-        <v>197</v>
-      </c>
-      <c r="C64" t="s">
-        <v>647</v>
-      </c>
       <c r="H64" t="s">
         <v>94</v>
       </c>
@@ -4132,15 +4018,6 @@
       </c>
     </row>
     <row r="65" spans="1:11">
-      <c r="A65" s="8">
-        <v>15826960</v>
-      </c>
-      <c r="B65" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="C65" s="10" t="s">
-        <v>648</v>
-      </c>
       <c r="H65" t="s">
         <v>94</v>
       </c>
@@ -4155,15 +4032,6 @@
       </c>
     </row>
     <row r="66" spans="1:11">
-      <c r="A66" s="8">
-        <v>58505144</v>
-      </c>
-      <c r="B66" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" s="10" t="s">
-        <v>648</v>
-      </c>
       <c r="H66" t="s">
         <v>94</v>
       </c>
@@ -4178,15 +4046,6 @@
       </c>
     </row>
     <row r="67" spans="1:11">
-      <c r="A67" s="8">
-        <v>61199642</v>
-      </c>
-      <c r="B67" s="9" t="s">
-        <v>439</v>
-      </c>
-      <c r="C67" s="10" t="s">
-        <v>648</v>
-      </c>
       <c r="H67" t="s">
         <v>98</v>
       </c>
@@ -4201,15 +4060,6 @@
       </c>
     </row>
     <row r="68" spans="1:11">
-      <c r="A68" s="8">
-        <v>64912430</v>
-      </c>
-      <c r="B68" s="9" t="s">
-        <v>485</v>
-      </c>
-      <c r="C68" s="10" t="s">
-        <v>648</v>
-      </c>
       <c r="H68" t="s">
         <v>98</v>
       </c>
@@ -4224,15 +4074,6 @@
       </c>
     </row>
     <row r="69" spans="1:11">
-      <c r="A69" s="8">
-        <v>10124384</v>
-      </c>
-      <c r="B69" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="C69" s="10" t="s">
-        <v>648</v>
-      </c>
       <c r="H69" t="s">
         <v>98</v>
       </c>
@@ -4247,15 +4088,6 @@
       </c>
     </row>
     <row r="70" spans="1:11">
-      <c r="A70" s="8">
-        <v>10929273</v>
-      </c>
-      <c r="B70" s="9" t="s">
-        <v>340</v>
-      </c>
-      <c r="C70" s="10" t="s">
-        <v>648</v>
-      </c>
       <c r="H70" t="s">
         <v>98</v>
       </c>
@@ -4270,15 +4102,6 @@
       </c>
     </row>
     <row r="71" spans="1:11">
-      <c r="A71" s="8">
-        <v>10929274</v>
-      </c>
-      <c r="B71" s="9" t="s">
-        <v>339</v>
-      </c>
-      <c r="C71" s="10" t="s">
-        <v>648</v>
-      </c>
       <c r="H71" t="s">
         <v>98</v>
       </c>
@@ -4293,15 +4116,6 @@
       </c>
     </row>
     <row r="72" spans="1:11">
-      <c r="A72" s="8">
-        <v>11670520</v>
-      </c>
-      <c r="B72" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C72" s="10" t="s">
-        <v>648</v>
-      </c>
       <c r="H72" t="s">
         <v>98</v>
       </c>
@@ -4316,15 +4130,6 @@
       </c>
     </row>
     <row r="73" spans="1:11">
-      <c r="A73" s="8">
-        <v>12029130</v>
-      </c>
-      <c r="B73" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="C73" s="10" t="s">
-        <v>648</v>
-      </c>
       <c r="H73" t="s">
         <v>98</v>
       </c>
@@ -4339,15 +4144,6 @@
       </c>
     </row>
     <row r="74" spans="1:11">
-      <c r="A74" s="8">
-        <v>12038103</v>
-      </c>
-      <c r="B74" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="C74" s="10" t="s">
-        <v>648</v>
-      </c>
       <c r="H74" t="s">
         <v>98</v>
       </c>
@@ -4362,15 +4158,6 @@
       </c>
     </row>
     <row r="75" spans="1:11">
-      <c r="A75" s="8">
-        <v>12095120</v>
-      </c>
-      <c r="B75" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="C75" s="10" t="s">
-        <v>648</v>
-      </c>
       <c r="H75" t="s">
         <v>90</v>
       </c>
@@ -4385,15 +4172,6 @@
       </c>
     </row>
     <row r="76" spans="1:11">
-      <c r="A76" s="8">
-        <v>12481760</v>
-      </c>
-      <c r="B76" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="C76" s="10" t="s">
-        <v>648</v>
-      </c>
       <c r="H76" t="s">
         <v>90</v>
       </c>
@@ -4408,15 +4186,6 @@
       </c>
     </row>
     <row r="77" spans="1:11">
-      <c r="A77" s="8">
-        <v>13195957</v>
-      </c>
-      <c r="B77" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C77" s="10" t="s">
-        <v>648</v>
-      </c>
       <c r="H77" t="s">
         <v>109</v>
       </c>
@@ -4431,15 +4200,6 @@
       </c>
     </row>
     <row r="78" spans="1:11">
-      <c r="A78" s="8">
-        <v>14299890</v>
-      </c>
-      <c r="B78" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="C78" s="10" t="s">
-        <v>648</v>
-      </c>
       <c r="H78" t="s">
         <v>90</v>
       </c>
@@ -4455,10 +4215,10 @@
     </row>
     <row r="79" spans="1:11">
       <c r="A79" s="8">
-        <v>14473529</v>
+        <v>15826960</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>87</v>
+        <v>236</v>
       </c>
       <c r="C79" s="10" t="s">
         <v>648</v>
@@ -4478,10 +4238,10 @@
     </row>
     <row r="80" spans="1:11">
       <c r="A80" s="8">
-        <v>15757638</v>
+        <v>58505144</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>263</v>
+        <v>16</v>
       </c>
       <c r="C80" s="10" t="s">
         <v>648</v>
@@ -4501,10 +4261,10 @@
     </row>
     <row r="81" spans="1:11">
       <c r="A81" s="8">
-        <v>16806254</v>
+        <v>61199642</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>317</v>
+        <v>439</v>
       </c>
       <c r="C81" s="10" t="s">
         <v>648</v>
@@ -4524,10 +4284,10 @@
     </row>
     <row r="82" spans="1:11">
       <c r="A82" s="8">
-        <v>20341619</v>
+        <v>64912430</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>37</v>
+        <v>485</v>
       </c>
       <c r="C82" s="10" t="s">
         <v>648</v>
@@ -4547,10 +4307,10 @@
     </row>
     <row r="83" spans="1:11">
       <c r="A83" s="8">
-        <v>22119013</v>
+        <v>10124384</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>322</v>
+        <v>185</v>
       </c>
       <c r="C83" s="10" t="s">
         <v>648</v>
@@ -4570,10 +4330,10 @@
     </row>
     <row r="84" spans="1:11">
       <c r="A84" s="8">
-        <v>25433097</v>
+        <v>10929273</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>88</v>
+        <v>340</v>
       </c>
       <c r="C84" s="10" t="s">
         <v>648</v>
@@ -4593,10 +4353,10 @@
     </row>
     <row r="85" spans="1:11">
       <c r="A85" s="8">
-        <v>25512595</v>
+        <v>10929274</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>20</v>
+        <v>339</v>
       </c>
       <c r="C85" s="10" t="s">
         <v>648</v>
@@ -4616,10 +4376,10 @@
     </row>
     <row r="86" spans="1:11">
       <c r="A86" s="8">
-        <v>25665354</v>
+        <v>11670520</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>119</v>
+        <v>10</v>
       </c>
       <c r="C86" s="10" t="s">
         <v>648</v>
@@ -4639,10 +4399,10 @@
     </row>
     <row r="87" spans="1:11">
       <c r="A87" s="8">
-        <v>29258063</v>
+        <v>12029130</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>308</v>
+        <v>117</v>
       </c>
       <c r="C87" s="10" t="s">
         <v>648</v>
@@ -4662,10 +4422,10 @@
     </row>
     <row r="88" spans="1:11">
       <c r="A88" s="8">
-        <v>29266932</v>
+        <v>12038103</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>40</v>
+        <v>264</v>
       </c>
       <c r="C88" s="10" t="s">
         <v>648</v>
@@ -4685,10 +4445,10 @@
     </row>
     <row r="89" spans="1:11">
       <c r="A89" s="8">
-        <v>34991467</v>
+        <v>12095120</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="C89" s="10" t="s">
         <v>648</v>
@@ -4708,10 +4468,10 @@
     </row>
     <row r="90" spans="1:11">
       <c r="A90" s="8">
-        <v>35401181</v>
+        <v>12481760</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>229</v>
+        <v>292</v>
       </c>
       <c r="C90" s="10" t="s">
         <v>648</v>
@@ -4731,10 +4491,10 @@
     </row>
     <row r="91" spans="1:11">
       <c r="A91" s="8">
-        <v>36606823</v>
+        <v>13195957</v>
       </c>
       <c r="B91" s="9" t="s">
-        <v>110</v>
+        <v>8</v>
       </c>
       <c r="C91" s="10" t="s">
         <v>648</v>
@@ -4754,10 +4514,10 @@
     </row>
     <row r="92" spans="1:11">
       <c r="A92" s="8">
-        <v>38157908</v>
+        <v>14299890</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>230</v>
+        <v>177</v>
       </c>
       <c r="C92" s="10" t="s">
         <v>648</v>
@@ -4777,10 +4537,10 @@
     </row>
     <row r="93" spans="1:11">
       <c r="A93" s="8">
-        <v>38407975</v>
+        <v>14473529</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="C93" s="10" t="s">
         <v>648</v>
@@ -4800,10 +4560,10 @@
     </row>
     <row r="94" spans="1:11">
       <c r="A94" s="8">
-        <v>38659485</v>
+        <v>15757638</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>43</v>
+        <v>263</v>
       </c>
       <c r="C94" s="10" t="s">
         <v>648</v>
@@ -4823,10 +4583,10 @@
     </row>
     <row r="95" spans="1:11">
       <c r="A95" s="8">
-        <v>39239709</v>
+        <v>16806254</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="C95" s="10" t="s">
         <v>648</v>
@@ -4846,10 +4606,10 @@
     </row>
     <row r="96" spans="1:11">
       <c r="A96" s="8">
-        <v>39944753</v>
+        <v>20341619</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>298</v>
+        <v>37</v>
       </c>
       <c r="C96" s="10" t="s">
         <v>648</v>
@@ -4869,10 +4629,10 @@
     </row>
     <row r="97" spans="1:11">
       <c r="A97" s="8">
-        <v>40180424</v>
+        <v>22119013</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>9</v>
+        <v>322</v>
       </c>
       <c r="C97" s="10" t="s">
         <v>648</v>
@@ -4892,10 +4652,10 @@
     </row>
     <row r="98" spans="1:11">
       <c r="A98" s="8">
-        <v>43571361</v>
+        <v>25433097</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>135</v>
+        <v>88</v>
       </c>
       <c r="C98" s="10" t="s">
         <v>648</v>
@@ -4915,10 +4675,10 @@
     </row>
     <row r="99" spans="1:11">
       <c r="A99" s="8">
-        <v>46801171</v>
+        <v>25512595</v>
       </c>
       <c r="B99" s="9" t="s">
-        <v>265</v>
+        <v>20</v>
       </c>
       <c r="C99" s="10" t="s">
         <v>648</v>
@@ -4938,10 +4698,10 @@
     </row>
     <row r="100" spans="1:11">
       <c r="A100" s="8">
-        <v>48449253</v>
+        <v>25665354</v>
       </c>
       <c r="B100" s="9" t="s">
-        <v>299</v>
+        <v>119</v>
       </c>
       <c r="C100" s="10" t="s">
         <v>648</v>
@@ -4961,10 +4721,10 @@
     </row>
     <row r="101" spans="1:11">
       <c r="A101" s="8">
-        <v>53967042</v>
+        <v>29258063</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>377</v>
+        <v>308</v>
       </c>
       <c r="C101" s="10" t="s">
         <v>648</v>
@@ -4984,10 +4744,10 @@
     </row>
     <row r="102" spans="1:11">
       <c r="A102" s="8">
-        <v>55275736</v>
+        <v>29266932</v>
       </c>
       <c r="B102" s="9" t="s">
-        <v>378</v>
+        <v>40</v>
       </c>
       <c r="C102" s="10" t="s">
         <v>648</v>
@@ -5007,10 +4767,10 @@
     </row>
     <row r="103" spans="1:11">
       <c r="A103" s="8">
-        <v>59759466</v>
+        <v>34991467</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>412</v>
+        <v>279</v>
       </c>
       <c r="C103" s="10" t="s">
         <v>648</v>
@@ -5030,10 +4790,10 @@
     </row>
     <row r="104" spans="1:11">
       <c r="A104" s="8">
-        <v>60024864</v>
+        <v>35401181</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>421</v>
+        <v>229</v>
       </c>
       <c r="C104" s="10" t="s">
         <v>648</v>
@@ -5053,10 +4813,10 @@
     </row>
     <row r="105" spans="1:11">
       <c r="A105" s="8">
-        <v>60025950</v>
+        <v>36606823</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>420</v>
+        <v>110</v>
       </c>
       <c r="C105" s="10" t="s">
         <v>648</v>
@@ -5076,10 +4836,10 @@
     </row>
     <row r="106" spans="1:11">
       <c r="A106" s="8">
-        <v>60541171</v>
+        <v>38157908</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>428</v>
+        <v>230</v>
       </c>
       <c r="C106" s="10" t="s">
         <v>648</v>
@@ -5099,10 +4859,10 @@
     </row>
     <row r="107" spans="1:11">
       <c r="A107" s="8">
-        <v>60543356</v>
+        <v>38407975</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>429</v>
+        <v>46</v>
       </c>
       <c r="C107" s="10" t="s">
         <v>648</v>
@@ -5122,10 +4882,10 @@
     </row>
     <row r="108" spans="1:11">
       <c r="A108" s="8">
-        <v>60615380</v>
+        <v>38659485</v>
       </c>
       <c r="B108" s="9" t="s">
-        <v>431</v>
+        <v>43</v>
       </c>
       <c r="C108" s="10" t="s">
         <v>648</v>
@@ -5145,10 +4905,10 @@
     </row>
     <row r="109" spans="1:11">
       <c r="A109" s="8">
-        <v>61760291</v>
+        <v>39239709</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>440</v>
+        <v>325</v>
       </c>
       <c r="C109" s="10" t="s">
         <v>648</v>
@@ -5168,10 +4928,10 @@
     </row>
     <row r="110" spans="1:11">
       <c r="A110" s="8">
-        <v>62385013</v>
+        <v>39944753</v>
       </c>
       <c r="B110" s="9" t="s">
-        <v>452</v>
+        <v>298</v>
       </c>
       <c r="C110" s="10" t="s">
         <v>648</v>
@@ -5191,10 +4951,10 @@
     </row>
     <row r="111" spans="1:11">
       <c r="A111" s="8">
-        <v>64606094</v>
+        <v>40180424</v>
       </c>
       <c r="B111" s="9" t="s">
-        <v>474</v>
+        <v>9</v>
       </c>
       <c r="C111" s="10" t="s">
         <v>648</v>
@@ -5214,10 +4974,10 @@
     </row>
     <row r="112" spans="1:11">
       <c r="A112" s="8">
-        <v>64846264</v>
+        <v>43571361</v>
       </c>
       <c r="B112" s="9" t="s">
-        <v>479</v>
+        <v>135</v>
       </c>
       <c r="C112" s="10" t="s">
         <v>648</v>
@@ -5237,10 +4997,10 @@
     </row>
     <row r="113" spans="1:11">
       <c r="A113" s="8">
-        <v>65566541</v>
+        <v>46801171</v>
       </c>
       <c r="B113" s="9" t="s">
-        <v>492</v>
+        <v>265</v>
       </c>
       <c r="C113" s="10" t="s">
         <v>648</v>
@@ -5260,10 +5020,10 @@
     </row>
     <row r="114" spans="1:11">
       <c r="A114" s="8">
-        <v>66607099</v>
+        <v>48449253</v>
       </c>
       <c r="B114" s="9" t="s">
-        <v>512</v>
+        <v>299</v>
       </c>
       <c r="C114" s="10" t="s">
         <v>648</v>
@@ -5283,10 +5043,10 @@
     </row>
     <row r="115" spans="1:11">
       <c r="A115" s="8">
-        <v>59924956</v>
+        <v>53967042</v>
       </c>
       <c r="B115" s="9" t="s">
-        <v>417</v>
+        <v>377</v>
       </c>
       <c r="C115" s="10" t="s">
         <v>648</v>
@@ -5306,13 +5066,13 @@
     </row>
     <row r="116" spans="1:11">
       <c r="A116" s="8">
-        <v>17014694</v>
+        <v>55275736</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C116" s="9" t="s">
-        <v>649</v>
+        <v>378</v>
+      </c>
+      <c r="C116" s="10" t="s">
+        <v>648</v>
       </c>
       <c r="H116" t="s">
         <v>56</v>
@@ -5329,13 +5089,13 @@
     </row>
     <row r="117" spans="1:11">
       <c r="A117" s="8">
-        <v>17014693</v>
+        <v>59759466</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C117" s="9" t="s">
-        <v>649</v>
+        <v>412</v>
+      </c>
+      <c r="C117" s="10" t="s">
+        <v>648</v>
       </c>
       <c r="H117" t="s">
         <v>56</v>
@@ -5352,13 +5112,13 @@
     </row>
     <row r="118" spans="1:11">
       <c r="A118" s="8">
-        <v>36811022</v>
+        <v>60024864</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>284</v>
+        <v>421</v>
       </c>
       <c r="C118" s="10" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="H118" t="s">
         <v>56</v>
@@ -5375,13 +5135,13 @@
     </row>
     <row r="119" spans="1:11">
       <c r="A119" s="8">
-        <v>36811023</v>
+        <v>60025950</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="H119" t="s">
         <v>56</v>
@@ -5398,13 +5158,13 @@
     </row>
     <row r="120" spans="1:11">
       <c r="A120" s="8">
-        <v>60023938</v>
+        <v>60541171</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="H120" t="s">
         <v>56</v>
@@ -5421,13 +5181,13 @@
     </row>
     <row r="121" spans="1:11">
       <c r="A121" s="8">
-        <v>61929494</v>
+        <v>60543356</v>
       </c>
       <c r="B121" s="9" t="s">
-        <v>445</v>
+        <v>429</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="H121" t="s">
         <v>90</v>
@@ -5444,13 +5204,13 @@
     </row>
     <row r="122" spans="1:11">
       <c r="A122" s="8">
-        <v>66417803</v>
+        <v>60615380</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>503</v>
+        <v>431</v>
       </c>
       <c r="C122" s="10" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="H122" t="s">
         <v>152</v>
@@ -5467,13 +5227,13 @@
     </row>
     <row r="123" spans="1:11">
       <c r="A123" s="8">
-        <v>20342327</v>
+        <v>61760291</v>
       </c>
       <c r="B123" s="9" t="s">
-        <v>35</v>
+        <v>440</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="H123" t="s">
         <v>152</v>
@@ -5490,13 +5250,13 @@
     </row>
     <row r="124" spans="1:11">
       <c r="A124" s="8">
-        <v>12586373</v>
+        <v>62385013</v>
       </c>
       <c r="B124" s="9" t="s">
-        <v>41</v>
+        <v>452</v>
       </c>
       <c r="C124" s="10" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="H124" t="s">
         <v>152</v>
@@ -5513,13 +5273,13 @@
     </row>
     <row r="125" spans="1:11">
       <c r="A125" s="8">
-        <v>11055651</v>
+        <v>64606094</v>
       </c>
       <c r="B125" s="9" t="s">
-        <v>42</v>
+        <v>474</v>
       </c>
       <c r="C125" s="10" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="H125" t="s">
         <v>152</v>
@@ -5536,13 +5296,13 @@
     </row>
     <row r="126" spans="1:11">
       <c r="A126" s="8">
-        <v>18816827</v>
+        <v>64846264</v>
       </c>
       <c r="B126" s="9" t="s">
-        <v>48</v>
+        <v>479</v>
       </c>
       <c r="C126" s="10" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="H126" t="s">
         <v>58</v>
@@ -5559,13 +5319,13 @@
     </row>
     <row r="127" spans="1:11">
       <c r="A127" s="8">
-        <v>39229235</v>
+        <v>65566541</v>
       </c>
       <c r="B127" s="9" t="s">
-        <v>59</v>
+        <v>492</v>
       </c>
       <c r="C127" s="10" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="H127" t="s">
         <v>58</v>
@@ -5582,13 +5342,13 @@
     </row>
     <row r="128" spans="1:11">
       <c r="A128" s="8">
-        <v>13151160</v>
+        <v>66607099</v>
       </c>
       <c r="B128" s="9" t="s">
-        <v>63</v>
+        <v>512</v>
       </c>
       <c r="C128" s="10" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="H128" t="s">
         <v>90</v>
@@ -5605,13 +5365,13 @@
     </row>
     <row r="129" spans="1:11">
       <c r="A129" s="8">
-        <v>13151158</v>
+        <v>59924956</v>
       </c>
       <c r="B129" s="9" t="s">
-        <v>64</v>
+        <v>417</v>
       </c>
       <c r="C129" s="10" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="H129" t="s">
         <v>90</v>
@@ -5628,13 +5388,13 @@
     </row>
     <row r="130" spans="1:11">
       <c r="A130" s="8">
-        <v>10978754</v>
+        <v>17014694</v>
       </c>
       <c r="B130" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="C130" s="10" t="s">
-        <v>650</v>
+        <v>67</v>
+      </c>
+      <c r="C130" s="9" t="s">
+        <v>649</v>
       </c>
       <c r="H130" t="s">
         <v>29</v>
@@ -5651,13 +5411,13 @@
     </row>
     <row r="131" spans="1:11">
       <c r="A131" s="8">
-        <v>19619417</v>
+        <v>17014693</v>
       </c>
       <c r="B131" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="C131" s="10" t="s">
-        <v>650</v>
+        <v>68</v>
+      </c>
+      <c r="C131" s="9" t="s">
+        <v>649</v>
       </c>
       <c r="H131" t="s">
         <v>29</v>
@@ -5674,10 +5434,10 @@
     </row>
     <row r="132" spans="1:11">
       <c r="A132" s="8">
-        <v>39063227</v>
+        <v>36811022</v>
       </c>
       <c r="B132" s="9" t="s">
-        <v>140</v>
+        <v>284</v>
       </c>
       <c r="C132" s="10" t="s">
         <v>650</v>
@@ -5697,10 +5457,10 @@
     </row>
     <row r="133" spans="1:11">
       <c r="A133" s="8">
-        <v>46995055</v>
+        <v>36811023</v>
       </c>
       <c r="B133" s="9" t="s">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="C133" s="10" t="s">
         <v>650</v>
@@ -5720,10 +5480,10 @@
     </row>
     <row r="134" spans="1:11">
       <c r="A134" s="8">
-        <v>11744316</v>
+        <v>60023938</v>
       </c>
       <c r="B134" s="9" t="s">
-        <v>187</v>
+        <v>419</v>
       </c>
       <c r="C134" s="10" t="s">
         <v>650</v>
@@ -5743,10 +5503,10 @@
     </row>
     <row r="135" spans="1:11">
       <c r="A135" s="8">
-        <v>13069194</v>
+        <v>61929494</v>
       </c>
       <c r="B135" s="9" t="s">
-        <v>188</v>
+        <v>445</v>
       </c>
       <c r="C135" s="10" t="s">
         <v>650</v>
@@ -5766,10 +5526,10 @@
     </row>
     <row r="136" spans="1:11">
       <c r="A136" s="8">
-        <v>4125381</v>
+        <v>66417803</v>
       </c>
       <c r="B136" s="9" t="s">
-        <v>192</v>
+        <v>503</v>
       </c>
       <c r="C136" s="10" t="s">
         <v>650</v>
@@ -5789,10 +5549,10 @@
     </row>
     <row r="137" spans="1:11">
       <c r="A137" s="8">
-        <v>42839047</v>
+        <v>20342327</v>
       </c>
       <c r="B137" s="9" t="s">
-        <v>212</v>
+        <v>35</v>
       </c>
       <c r="C137" s="10" t="s">
         <v>650</v>
@@ -5812,10 +5572,10 @@
     </row>
     <row r="138" spans="1:11">
       <c r="A138" s="8">
-        <v>4152612</v>
+        <v>12586373</v>
       </c>
       <c r="B138" s="9" t="s">
-        <v>217</v>
+        <v>41</v>
       </c>
       <c r="C138" s="10" t="s">
         <v>650</v>
@@ -5835,10 +5595,10 @@
     </row>
     <row r="139" spans="1:11">
       <c r="A139" s="8">
-        <v>4152610</v>
+        <v>11055651</v>
       </c>
       <c r="B139" s="9" t="s">
-        <v>218</v>
+        <v>42</v>
       </c>
       <c r="C139" s="10" t="s">
         <v>650</v>
@@ -5858,10 +5618,10 @@
     </row>
     <row r="140" spans="1:11">
       <c r="A140" s="8">
-        <v>34098917</v>
+        <v>18816827</v>
       </c>
       <c r="B140" s="9" t="s">
-        <v>223</v>
+        <v>48</v>
       </c>
       <c r="C140" s="10" t="s">
         <v>650</v>
@@ -5881,10 +5641,10 @@
     </row>
     <row r="141" spans="1:11">
       <c r="A141" s="8">
-        <v>49985232</v>
+        <v>39229235</v>
       </c>
       <c r="B141" s="9" t="s">
-        <v>227</v>
+        <v>59</v>
       </c>
       <c r="C141" s="10" t="s">
         <v>650</v>
@@ -5904,10 +5664,10 @@
     </row>
     <row r="142" spans="1:11">
       <c r="A142" s="8">
-        <v>50155408</v>
+        <v>13151160</v>
       </c>
       <c r="B142" s="9" t="s">
-        <v>228</v>
+        <v>63</v>
       </c>
       <c r="C142" s="10" t="s">
         <v>650</v>
@@ -5927,10 +5687,10 @@
     </row>
     <row r="143" spans="1:11">
       <c r="A143" s="8">
-        <v>41662266</v>
+        <v>13151158</v>
       </c>
       <c r="B143" s="9" t="s">
-        <v>231</v>
+        <v>64</v>
       </c>
       <c r="C143" s="10" t="s">
         <v>650</v>
@@ -5950,10 +5710,10 @@
     </row>
     <row r="144" spans="1:11">
       <c r="A144" s="8">
-        <v>13573385</v>
+        <v>10978754</v>
       </c>
       <c r="B144" s="9" t="s">
-        <v>237</v>
+        <v>100</v>
       </c>
       <c r="C144" s="10" t="s">
         <v>650</v>
@@ -5973,10 +5733,10 @@
     </row>
     <row r="145" spans="1:11">
       <c r="A145" s="8">
-        <v>42871700</v>
+        <v>19619417</v>
       </c>
       <c r="B145" s="9" t="s">
-        <v>238</v>
+        <v>108</v>
       </c>
       <c r="C145" s="10" t="s">
         <v>650</v>
@@ -5996,10 +5756,10 @@
     </row>
     <row r="146" spans="1:11">
       <c r="A146" s="8">
-        <v>39257536</v>
+        <v>39063227</v>
       </c>
       <c r="B146" s="9" t="s">
-        <v>239</v>
+        <v>140</v>
       </c>
       <c r="C146" s="10" t="s">
         <v>650</v>
@@ -6019,10 +5779,10 @@
     </row>
     <row r="147" spans="1:11">
       <c r="A147" s="8">
-        <v>37424126</v>
+        <v>46995055</v>
       </c>
       <c r="B147" s="9" t="s">
-        <v>240</v>
+        <v>186</v>
       </c>
       <c r="C147" s="10" t="s">
         <v>650</v>
@@ -6042,10 +5802,10 @@
     </row>
     <row r="148" spans="1:11">
       <c r="A148" s="8">
-        <v>36802614</v>
+        <v>11744316</v>
       </c>
       <c r="B148" s="9" t="s">
-        <v>241</v>
+        <v>187</v>
       </c>
       <c r="C148" s="10" t="s">
         <v>650</v>
@@ -6065,10 +5825,10 @@
     </row>
     <row r="149" spans="1:11">
       <c r="A149" s="8">
-        <v>36577826</v>
+        <v>13069194</v>
       </c>
       <c r="B149" s="9" t="s">
-        <v>242</v>
+        <v>188</v>
       </c>
       <c r="C149" s="10" t="s">
         <v>650</v>
@@ -6088,10 +5848,10 @@
     </row>
     <row r="150" spans="1:11">
       <c r="A150" s="8">
-        <v>26196255</v>
+        <v>4125381</v>
       </c>
       <c r="B150" s="9" t="s">
-        <v>243</v>
+        <v>192</v>
       </c>
       <c r="C150" s="10" t="s">
         <v>650</v>
@@ -6111,10 +5871,10 @@
     </row>
     <row r="151" spans="1:11">
       <c r="A151" s="8">
-        <v>26019234</v>
+        <v>42839047</v>
       </c>
       <c r="B151" s="9" t="s">
-        <v>248</v>
+        <v>212</v>
       </c>
       <c r="C151" s="10" t="s">
         <v>650</v>
@@ -6134,10 +5894,10 @@
     </row>
     <row r="152" spans="1:11">
       <c r="A152" s="8">
-        <v>25411238</v>
+        <v>4152612</v>
       </c>
       <c r="B152" s="9" t="s">
-        <v>251</v>
+        <v>217</v>
       </c>
       <c r="C152" s="10" t="s">
         <v>650</v>
@@ -6157,10 +5917,10 @@
     </row>
     <row r="153" spans="1:11">
       <c r="A153" s="8">
-        <v>26500515</v>
+        <v>4152610</v>
       </c>
       <c r="B153" s="9" t="s">
-        <v>254</v>
+        <v>218</v>
       </c>
       <c r="C153" s="10" t="s">
         <v>650</v>
@@ -6180,10 +5940,10 @@
     </row>
     <row r="154" spans="1:11">
       <c r="A154" s="8">
-        <v>36162739</v>
+        <v>34098917</v>
       </c>
       <c r="B154" s="9" t="s">
-        <v>255</v>
+        <v>223</v>
       </c>
       <c r="C154" s="10" t="s">
         <v>650</v>
@@ -6203,10 +5963,10 @@
     </row>
     <row r="155" spans="1:11">
       <c r="A155" s="8">
-        <v>39893389</v>
+        <v>49985232</v>
       </c>
       <c r="B155" s="9" t="s">
-        <v>256</v>
+        <v>227</v>
       </c>
       <c r="C155" s="10" t="s">
         <v>650</v>
@@ -6226,10 +5986,10 @@
     </row>
     <row r="156" spans="1:11">
       <c r="A156" s="8">
-        <v>39296173</v>
+        <v>50155408</v>
       </c>
       <c r="B156" s="9" t="s">
-        <v>257</v>
+        <v>228</v>
       </c>
       <c r="C156" s="10" t="s">
         <v>650</v>
@@ -6249,10 +6009,10 @@
     </row>
     <row r="157" spans="1:11">
       <c r="A157" s="8">
-        <v>42217758</v>
+        <v>41662266</v>
       </c>
       <c r="B157" s="9" t="s">
-        <v>285</v>
+        <v>231</v>
       </c>
       <c r="C157" s="10" t="s">
         <v>650</v>
@@ -6272,10 +6032,10 @@
     </row>
     <row r="158" spans="1:11">
       <c r="A158" s="8">
-        <v>22403445</v>
+        <v>13573385</v>
       </c>
       <c r="B158" s="9" t="s">
-        <v>290</v>
+        <v>237</v>
       </c>
       <c r="C158" s="10" t="s">
         <v>650</v>
@@ -6295,10 +6055,10 @@
     </row>
     <row r="159" spans="1:11">
       <c r="A159" s="8">
-        <v>26257716</v>
+        <v>42871700</v>
       </c>
       <c r="B159" s="9" t="s">
-        <v>291</v>
+        <v>238</v>
       </c>
       <c r="C159" s="10" t="s">
         <v>650</v>
@@ -6318,10 +6078,10 @@
     </row>
     <row r="160" spans="1:11">
       <c r="A160" s="8">
-        <v>42486414</v>
+        <v>39257536</v>
       </c>
       <c r="B160" s="9" t="s">
-        <v>305</v>
+        <v>239</v>
       </c>
       <c r="C160" s="10" t="s">
         <v>650</v>
@@ -6341,10 +6101,10 @@
     </row>
     <row r="161" spans="1:11">
       <c r="A161" s="8">
-        <v>44695653</v>
+        <v>37424126</v>
       </c>
       <c r="B161" s="9" t="s">
-        <v>306</v>
+        <v>240</v>
       </c>
       <c r="C161" s="10" t="s">
         <v>650</v>
@@ -6364,10 +6124,10 @@
     </row>
     <row r="162" spans="1:11">
       <c r="A162" s="8">
-        <v>13405604</v>
+        <v>36802614</v>
       </c>
       <c r="B162" s="9" t="s">
-        <v>309</v>
+        <v>241</v>
       </c>
       <c r="C162" s="10" t="s">
         <v>650</v>
@@ -6387,10 +6147,10 @@
     </row>
     <row r="163" spans="1:11">
       <c r="A163" s="8">
-        <v>39911056</v>
+        <v>36577826</v>
       </c>
       <c r="B163" s="9" t="s">
-        <v>337</v>
+        <v>242</v>
       </c>
       <c r="C163" s="10" t="s">
         <v>650</v>
@@ -6410,10 +6170,10 @@
     </row>
     <row r="164" spans="1:11">
       <c r="A164" s="8">
-        <v>51897600</v>
+        <v>26196255</v>
       </c>
       <c r="B164" s="9" t="s">
-        <v>350</v>
+        <v>243</v>
       </c>
       <c r="C164" s="10" t="s">
         <v>650</v>
@@ -6433,10 +6193,10 @@
     </row>
     <row r="165" spans="1:11">
       <c r="A165" s="8">
-        <v>52990015</v>
+        <v>26019234</v>
       </c>
       <c r="B165" s="9" t="s">
-        <v>363</v>
+        <v>248</v>
       </c>
       <c r="C165" s="10" t="s">
         <v>650</v>
@@ -6456,10 +6216,10 @@
     </row>
     <row r="166" spans="1:11">
       <c r="A166" s="8">
-        <v>55354052</v>
+        <v>25411238</v>
       </c>
       <c r="B166" s="9" t="s">
-        <v>382</v>
+        <v>251</v>
       </c>
       <c r="C166" s="10" t="s">
         <v>650</v>
@@ -6479,10 +6239,10 @@
     </row>
     <row r="167" spans="1:11">
       <c r="A167" s="8">
-        <v>55356388</v>
+        <v>26500515</v>
       </c>
       <c r="B167" s="9" t="s">
-        <v>390</v>
+        <v>254</v>
       </c>
       <c r="C167" s="10" t="s">
         <v>650</v>
@@ -6502,10 +6262,10 @@
     </row>
     <row r="168" spans="1:11">
       <c r="A168" s="8">
-        <v>62377903</v>
+        <v>36162739</v>
       </c>
       <c r="B168" s="9" t="s">
-        <v>436</v>
+        <v>255</v>
       </c>
       <c r="C168" s="10" t="s">
         <v>650</v>
@@ -6525,10 +6285,10 @@
     </row>
     <row r="169" spans="1:11">
       <c r="A169" s="8">
-        <v>66097436</v>
+        <v>39893389</v>
       </c>
       <c r="B169" s="9" t="s">
-        <v>477</v>
+        <v>256</v>
       </c>
       <c r="C169" s="10" t="s">
         <v>650</v>
@@ -6548,10 +6308,10 @@
     </row>
     <row r="170" spans="1:11">
       <c r="A170" s="8">
-        <v>11681261</v>
+        <v>39296173</v>
       </c>
       <c r="B170" s="9" t="s">
-        <v>287</v>
+        <v>257</v>
       </c>
       <c r="C170" s="10" t="s">
         <v>650</v>
@@ -6571,10 +6331,10 @@
     </row>
     <row r="171" spans="1:11">
       <c r="A171" s="8">
-        <v>11874445</v>
+        <v>42217758</v>
       </c>
       <c r="B171" s="9" t="s">
-        <v>6</v>
+        <v>285</v>
       </c>
       <c r="C171" s="10" t="s">
         <v>650</v>
@@ -6594,10 +6354,10 @@
     </row>
     <row r="172" spans="1:11">
       <c r="A172" s="8">
-        <v>14719737</v>
+        <v>22403445</v>
       </c>
       <c r="B172" s="9" t="s">
-        <v>4</v>
+        <v>290</v>
       </c>
       <c r="C172" s="10" t="s">
         <v>650</v>
@@ -6617,10 +6377,10 @@
     </row>
     <row r="173" spans="1:11">
       <c r="A173" s="8">
-        <v>16179047</v>
+        <v>26257716</v>
       </c>
       <c r="B173" s="9" t="s">
-        <v>12</v>
+        <v>291</v>
       </c>
       <c r="C173" s="10" t="s">
         <v>650</v>
@@ -6640,10 +6400,10 @@
     </row>
     <row r="174" spans="1:11">
       <c r="A174" s="8">
-        <v>20815743</v>
+        <v>42486414</v>
       </c>
       <c r="B174" s="9" t="s">
-        <v>209</v>
+        <v>305</v>
       </c>
       <c r="C174" s="10" t="s">
         <v>650</v>
@@ -6663,10 +6423,10 @@
     </row>
     <row r="175" spans="1:11">
       <c r="A175" s="8">
-        <v>30405071</v>
+        <v>44695653</v>
       </c>
       <c r="B175" s="9" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="C175" s="10" t="s">
         <v>650</v>
@@ -6686,10 +6446,10 @@
     </row>
     <row r="176" spans="1:11">
       <c r="A176" s="8">
-        <v>34352694</v>
+        <v>13405604</v>
       </c>
       <c r="B176" s="9" t="s">
-        <v>139</v>
+        <v>309</v>
       </c>
       <c r="C176" s="10" t="s">
         <v>650</v>
@@ -6709,10 +6469,10 @@
     </row>
     <row r="177" spans="1:11">
       <c r="A177" s="8">
-        <v>35149611</v>
+        <v>39911056</v>
       </c>
       <c r="B177" s="9" t="s">
-        <v>2</v>
+        <v>337</v>
       </c>
       <c r="C177" s="10" t="s">
         <v>650</v>
@@ -6732,10 +6492,10 @@
     </row>
     <row r="178" spans="1:11">
       <c r="A178" s="8">
-        <v>35896315</v>
+        <v>51897600</v>
       </c>
       <c r="B178" s="9" t="s">
-        <v>219</v>
+        <v>350</v>
       </c>
       <c r="C178" s="10" t="s">
         <v>650</v>
@@ -6755,10 +6515,10 @@
     </row>
     <row r="179" spans="1:11">
       <c r="A179" s="8">
-        <v>36682232</v>
+        <v>52990015</v>
       </c>
       <c r="B179" s="9" t="s">
-        <v>294</v>
+        <v>363</v>
       </c>
       <c r="C179" s="10" t="s">
         <v>650</v>
@@ -6778,10 +6538,10 @@
     </row>
     <row r="180" spans="1:11">
       <c r="A180" s="8">
-        <v>43571360</v>
+        <v>55354052</v>
       </c>
       <c r="B180" s="9" t="s">
-        <v>136</v>
+        <v>382</v>
       </c>
       <c r="C180" s="10" t="s">
         <v>650</v>
@@ -6801,10 +6561,10 @@
     </row>
     <row r="181" spans="1:11">
       <c r="A181" s="8">
-        <v>44374810</v>
+        <v>55356388</v>
       </c>
       <c r="B181" s="9" t="s">
-        <v>307</v>
+        <v>390</v>
       </c>
       <c r="C181" s="10" t="s">
         <v>650</v>
@@ -6824,10 +6584,10 @@
     </row>
     <row r="182" spans="1:11">
       <c r="A182" s="8">
-        <v>45349063</v>
+        <v>62377903</v>
       </c>
       <c r="B182" s="9" t="s">
-        <v>7</v>
+        <v>436</v>
       </c>
       <c r="C182" s="10" t="s">
         <v>650</v>
@@ -6847,10 +6607,10 @@
     </row>
     <row r="183" spans="1:11">
       <c r="A183" s="8">
-        <v>59836396</v>
+        <v>66097436</v>
       </c>
       <c r="B183" s="9" t="s">
-        <v>418</v>
+        <v>477</v>
       </c>
       <c r="C183" s="10" t="s">
         <v>650</v>
@@ -6870,10 +6630,10 @@
     </row>
     <row r="184" spans="1:11">
       <c r="A184" s="8">
-        <v>59927382</v>
+        <v>11681261</v>
       </c>
       <c r="B184" s="9" t="s">
-        <v>11</v>
+        <v>287</v>
       </c>
       <c r="C184" s="10" t="s">
         <v>650</v>
@@ -6893,10 +6653,10 @@
     </row>
     <row r="185" spans="1:11">
       <c r="A185" s="8">
-        <v>60541542</v>
+        <v>11874445</v>
       </c>
       <c r="B185" s="9" t="s">
-        <v>427</v>
+        <v>6</v>
       </c>
       <c r="C185" s="10" t="s">
         <v>650</v>
@@ -6916,10 +6676,10 @@
     </row>
     <row r="186" spans="1:11">
       <c r="A186" s="8">
-        <v>66417801</v>
+        <v>14719737</v>
       </c>
       <c r="B186" s="9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C186" s="10" t="s">
         <v>650</v>
@@ -6938,6 +6698,15 @@
       </c>
     </row>
     <row r="187" spans="1:11">
+      <c r="A187" s="8">
+        <v>16179047</v>
+      </c>
+      <c r="B187" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C187" s="10" t="s">
+        <v>650</v>
+      </c>
       <c r="H187" t="s">
         <v>98</v>
       </c>
@@ -6952,6 +6721,15 @@
       </c>
     </row>
     <row r="188" spans="1:11">
+      <c r="A188" s="8">
+        <v>20815743</v>
+      </c>
+      <c r="B188" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="C188" s="10" t="s">
+        <v>650</v>
+      </c>
       <c r="H188" t="s">
         <v>98</v>
       </c>
@@ -6966,11 +6744,15 @@
       </c>
     </row>
     <row r="189" spans="1:11">
-      <c r="A189" s="13" t="s">
-        <v>664</v>
-      </c>
-      <c r="B189" s="13"/>
-      <c r="C189" s="13"/>
+      <c r="A189" s="8">
+        <v>30405071</v>
+      </c>
+      <c r="B189" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="C189" s="10" t="s">
+        <v>650</v>
+      </c>
       <c r="H189" t="s">
         <v>98</v>
       </c>
@@ -6985,14 +6767,14 @@
       </c>
     </row>
     <row r="190" spans="1:11">
-      <c r="A190">
-        <v>38183281</v>
-      </c>
-      <c r="B190" s="11" t="s">
-        <v>651</v>
-      </c>
-      <c r="C190" t="s">
-        <v>663</v>
+      <c r="A190" s="8">
+        <v>34352694</v>
+      </c>
+      <c r="B190" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="C190" s="10" t="s">
+        <v>650</v>
       </c>
       <c r="H190" t="s">
         <v>98</v>
@@ -7008,14 +6790,14 @@
       </c>
     </row>
     <row r="191" spans="1:11">
-      <c r="A191">
-        <v>12585217</v>
-      </c>
-      <c r="B191" s="12" t="s">
-        <v>652</v>
-      </c>
-      <c r="C191" t="s">
-        <v>663</v>
+      <c r="A191" s="8">
+        <v>35149611</v>
+      </c>
+      <c r="B191" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C191" s="10" t="s">
+        <v>650</v>
       </c>
       <c r="H191" t="s">
         <v>98</v>
@@ -7031,14 +6813,14 @@
       </c>
     </row>
     <row r="192" spans="1:11">
-      <c r="A192">
-        <v>42803850</v>
-      </c>
-      <c r="B192" s="12" t="s">
-        <v>653</v>
-      </c>
-      <c r="C192" t="s">
-        <v>663</v>
+      <c r="A192" s="8">
+        <v>35896315</v>
+      </c>
+      <c r="B192" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="C192" s="10" t="s">
+        <v>650</v>
       </c>
       <c r="H192" t="s">
         <v>92</v>
@@ -7054,14 +6836,14 @@
       </c>
     </row>
     <row r="193" spans="1:11">
-      <c r="A193">
-        <v>34801754</v>
-      </c>
-      <c r="B193" s="12" t="s">
-        <v>654</v>
-      </c>
-      <c r="C193" t="s">
-        <v>663</v>
+      <c r="A193" s="8">
+        <v>36682232</v>
+      </c>
+      <c r="B193" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="C193" s="10" t="s">
+        <v>650</v>
       </c>
       <c r="H193" t="s">
         <v>92</v>
@@ -7077,14 +6859,14 @@
       </c>
     </row>
     <row r="194" spans="1:11">
-      <c r="A194">
-        <v>65081124</v>
-      </c>
-      <c r="B194" s="12" t="s">
-        <v>655</v>
-      </c>
-      <c r="C194" t="s">
-        <v>663</v>
+      <c r="A194" s="8">
+        <v>43571360</v>
+      </c>
+      <c r="B194" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="C194" s="10" t="s">
+        <v>650</v>
       </c>
       <c r="H194" t="s">
         <v>92</v>
@@ -7100,14 +6882,14 @@
       </c>
     </row>
     <row r="195" spans="1:11">
-      <c r="A195">
-        <v>56183402</v>
-      </c>
-      <c r="B195" s="12" t="s">
-        <v>656</v>
-      </c>
-      <c r="C195" t="s">
-        <v>663</v>
+      <c r="A195" s="8">
+        <v>44374810</v>
+      </c>
+      <c r="B195" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="C195" s="10" t="s">
+        <v>650</v>
       </c>
       <c r="H195" t="s">
         <v>92</v>
@@ -7123,14 +6905,14 @@
       </c>
     </row>
     <row r="196" spans="1:11">
-      <c r="A196">
-        <v>69040158</v>
-      </c>
-      <c r="B196" s="12" t="s">
-        <v>657</v>
-      </c>
-      <c r="C196" t="s">
-        <v>663</v>
+      <c r="A196" s="8">
+        <v>45349063</v>
+      </c>
+      <c r="B196" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C196" s="10" t="s">
+        <v>650</v>
       </c>
       <c r="H196" t="s">
         <v>92</v>
@@ -7146,14 +6928,14 @@
       </c>
     </row>
     <row r="197" spans="1:11">
-      <c r="A197">
-        <v>61929493</v>
-      </c>
-      <c r="B197" s="12" t="s">
-        <v>658</v>
-      </c>
-      <c r="C197" t="s">
-        <v>663</v>
+      <c r="A197" s="8">
+        <v>59836396</v>
+      </c>
+      <c r="B197" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="C197" s="10" t="s">
+        <v>650</v>
       </c>
       <c r="H197" t="s">
         <v>92</v>
@@ -7169,14 +6951,14 @@
       </c>
     </row>
     <row r="198" spans="1:11">
-      <c r="A198">
-        <v>50012601</v>
-      </c>
-      <c r="B198" s="12" t="s">
-        <v>659</v>
-      </c>
-      <c r="C198" t="s">
-        <v>663</v>
+      <c r="A198" s="8">
+        <v>59927382</v>
+      </c>
+      <c r="B198" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C198" s="10" t="s">
+        <v>650</v>
       </c>
       <c r="H198" t="s">
         <v>92</v>
@@ -7192,14 +6974,14 @@
       </c>
     </row>
     <row r="199" spans="1:11">
-      <c r="A199">
-        <v>58987730</v>
-      </c>
-      <c r="B199" s="12" t="s">
-        <v>660</v>
-      </c>
-      <c r="C199" t="s">
-        <v>663</v>
+      <c r="A199" s="8">
+        <v>60541542</v>
+      </c>
+      <c r="B199" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="C199" s="10" t="s">
+        <v>650</v>
       </c>
       <c r="H199" t="s">
         <v>92</v>
@@ -7215,7 +6997,15 @@
       </c>
     </row>
     <row r="200" spans="1:11">
-      <c r="B200" s="12"/>
+      <c r="A200" s="8">
+        <v>66417801</v>
+      </c>
+      <c r="B200" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C200" s="10" t="s">
+        <v>650</v>
+      </c>
       <c r="H200" t="s">
         <v>92</v>
       </c>
@@ -7258,6 +7048,11 @@
       </c>
     </row>
     <row r="203" spans="1:11">
+      <c r="A203" s="13" t="s">
+        <v>652</v>
+      </c>
+      <c r="B203" s="13"/>
+      <c r="C203" s="13"/>
       <c r="H203" t="s">
         <v>92</v>
       </c>
@@ -7272,6 +7067,7 @@
       </c>
     </row>
     <row r="204" spans="1:11">
+      <c r="B204" s="11"/>
       <c r="H204" t="s">
         <v>92</v>
       </c>
@@ -7286,6 +7082,7 @@
       </c>
     </row>
     <row r="205" spans="1:11">
+      <c r="B205" s="12"/>
       <c r="H205" t="s">
         <v>92</v>
       </c>
@@ -7300,6 +7097,7 @@
       </c>
     </row>
     <row r="206" spans="1:11">
+      <c r="B206" s="12"/>
       <c r="H206" t="s">
         <v>92</v>
       </c>
@@ -7314,6 +7112,7 @@
       </c>
     </row>
     <row r="207" spans="1:11">
+      <c r="B207" s="12"/>
       <c r="H207" t="s">
         <v>92</v>
       </c>
@@ -7328,6 +7127,7 @@
       </c>
     </row>
     <row r="208" spans="1:11">
+      <c r="B208" s="12"/>
       <c r="H208" t="s">
         <v>92</v>
       </c>
@@ -7341,7 +7141,8 @@
         <v>36577826</v>
       </c>
     </row>
-    <row r="209" spans="8:11">
+    <row r="209" spans="2:11">
+      <c r="B209" s="12"/>
       <c r="H209" t="s">
         <v>92</v>
       </c>
@@ -7355,7 +7156,8 @@
         <v>35149611</v>
       </c>
     </row>
-    <row r="210" spans="8:11">
+    <row r="210" spans="2:11">
+      <c r="B210" s="12"/>
       <c r="H210" t="s">
         <v>92</v>
       </c>
@@ -7369,7 +7171,8 @@
         <v>26196255</v>
       </c>
     </row>
-    <row r="211" spans="8:11">
+    <row r="211" spans="2:11">
+      <c r="B211" s="12"/>
       <c r="H211" t="s">
         <v>92</v>
       </c>
@@ -7383,7 +7186,8 @@
         <v>11156528</v>
       </c>
     </row>
-    <row r="212" spans="8:11">
+    <row r="212" spans="2:11">
+      <c r="B212" s="12"/>
       <c r="H212" t="s">
         <v>92</v>
       </c>
@@ -7397,7 +7201,8 @@
         <v>38415503</v>
       </c>
     </row>
-    <row r="213" spans="8:11">
+    <row r="213" spans="2:11">
+      <c r="B213" s="12"/>
       <c r="H213" t="s">
         <v>92</v>
       </c>
@@ -7411,7 +7216,8 @@
         <v>37244806</v>
       </c>
     </row>
-    <row r="214" spans="8:11">
+    <row r="214" spans="2:11">
+      <c r="B214" s="12"/>
       <c r="H214" t="s">
         <v>92</v>
       </c>
@@ -7425,7 +7231,7 @@
         <v>27011098</v>
       </c>
     </row>
-    <row r="215" spans="8:11">
+    <row r="215" spans="2:11">
       <c r="H215" t="s">
         <v>92</v>
       </c>
@@ -7439,7 +7245,7 @@
         <v>26019234</v>
       </c>
     </row>
-    <row r="216" spans="8:11">
+    <row r="216" spans="2:11">
       <c r="H216" t="s">
         <v>92</v>
       </c>
@@ -7453,7 +7259,7 @@
         <v>13959023</v>
       </c>
     </row>
-    <row r="217" spans="8:11">
+    <row r="217" spans="2:11">
       <c r="H217" t="s">
         <v>92</v>
       </c>
@@ -7467,7 +7273,7 @@
         <v>12496637</v>
       </c>
     </row>
-    <row r="218" spans="8:11">
+    <row r="218" spans="2:11">
       <c r="H218" t="s">
         <v>92</v>
       </c>
@@ -7481,7 +7287,7 @@
         <v>25411238</v>
       </c>
     </row>
-    <row r="219" spans="8:11">
+    <row r="219" spans="2:11">
       <c r="H219" t="s">
         <v>92</v>
       </c>
@@ -7495,7 +7301,7 @@
         <v>38312169</v>
       </c>
     </row>
-    <row r="220" spans="8:11">
+    <row r="220" spans="2:11">
       <c r="H220" t="s">
         <v>92</v>
       </c>
@@ -7509,7 +7315,7 @@
         <v>31886592</v>
       </c>
     </row>
-    <row r="221" spans="8:11">
+    <row r="221" spans="2:11">
       <c r="H221" t="s">
         <v>92</v>
       </c>
@@ -7523,7 +7329,7 @@
         <v>11670520</v>
       </c>
     </row>
-    <row r="222" spans="8:11">
+    <row r="222" spans="2:11">
       <c r="H222" t="s">
         <v>92</v>
       </c>
@@ -7537,7 +7343,7 @@
         <v>26500515</v>
       </c>
     </row>
-    <row r="223" spans="8:11">
+    <row r="223" spans="2:11">
       <c r="H223" t="s">
         <v>92</v>
       </c>
@@ -7551,7 +7357,7 @@
         <v>36162739</v>
       </c>
     </row>
-    <row r="224" spans="8:11">
+    <row r="224" spans="2:11">
       <c r="H224" t="s">
         <v>92</v>
       </c>
@@ -12750,7 +12556,7 @@
         <v>80915325</v>
       </c>
       <c r="J595" t="s">
-        <v>665</v>
+        <v>653</v>
       </c>
       <c r="K595" s="6">
         <v>80915325</v>
@@ -12764,7 +12570,7 @@
         <v>80915326</v>
       </c>
       <c r="J596" t="s">
-        <v>666</v>
+        <v>654</v>
       </c>
       <c r="K596" s="6">
         <v>80915326</v>
@@ -12772,13 +12578,13 @@
     </row>
     <row r="597" spans="8:11">
       <c r="H597" s="7" t="s">
-        <v>679</v>
+        <v>667</v>
       </c>
       <c r="I597" s="6">
         <v>80953015</v>
       </c>
       <c r="J597" t="s">
-        <v>667</v>
+        <v>655</v>
       </c>
       <c r="K597" s="6">
         <v>80953015</v>
@@ -12786,13 +12592,13 @@
     </row>
     <row r="598" spans="8:11">
       <c r="H598" s="7" t="s">
-        <v>679</v>
+        <v>667</v>
       </c>
       <c r="I598" s="6">
         <v>80953016</v>
       </c>
       <c r="J598" t="s">
-        <v>668</v>
+        <v>656</v>
       </c>
       <c r="K598" s="6">
         <v>80953016</v>
@@ -12820,7 +12626,7 @@
         <v>81638306</v>
       </c>
       <c r="J600" t="s">
-        <v>669</v>
+        <v>657</v>
       </c>
       <c r="K600" s="6">
         <v>81638306</v>
@@ -12828,13 +12634,13 @@
     </row>
     <row r="601" spans="8:11">
       <c r="H601" s="7" t="s">
-        <v>679</v>
+        <v>667</v>
       </c>
       <c r="I601" s="6">
         <v>81918457</v>
       </c>
       <c r="J601" t="s">
-        <v>670</v>
+        <v>658</v>
       </c>
       <c r="K601" s="6">
         <v>81918457</v>
@@ -12848,7 +12654,7 @@
         <v>81538523</v>
       </c>
       <c r="J602" t="s">
-        <v>671</v>
+        <v>659</v>
       </c>
       <c r="K602" s="6">
         <v>81538523</v>
@@ -12862,7 +12668,7 @@
         <v>79040263</v>
       </c>
       <c r="J603" t="s">
-        <v>672</v>
+        <v>660</v>
       </c>
       <c r="K603" s="6">
         <v>79040263</v>
@@ -12876,7 +12682,7 @@
         <v>79475749</v>
       </c>
       <c r="J604" t="s">
-        <v>673</v>
+        <v>661</v>
       </c>
       <c r="K604" s="6">
         <v>79475749</v>
@@ -12890,7 +12696,7 @@
         <v>79944232</v>
       </c>
       <c r="J605" t="s">
-        <v>674</v>
+        <v>662</v>
       </c>
       <c r="K605" s="6">
         <v>79944232</v>
@@ -12904,7 +12710,7 @@
         <v>80460979</v>
       </c>
       <c r="J606" t="s">
-        <v>675</v>
+        <v>663</v>
       </c>
       <c r="K606" s="6">
         <v>80460979</v>
@@ -12918,7 +12724,7 @@
         <v>81340922</v>
       </c>
       <c r="J607" t="s">
-        <v>676</v>
+        <v>664</v>
       </c>
       <c r="K607" s="6">
         <v>81340922</v>
@@ -12926,7 +12732,7 @@
     </row>
     <row r="608" spans="8:11">
       <c r="H608" s="7" t="s">
-        <v>679</v>
+        <v>667</v>
       </c>
       <c r="I608" s="6">
         <v>38157908</v>
@@ -12940,7 +12746,7 @@
     </row>
     <row r="609" spans="8:11">
       <c r="H609" s="7" t="s">
-        <v>679</v>
+        <v>667</v>
       </c>
       <c r="I609" s="6">
         <v>41662266</v>
@@ -12960,7 +12766,7 @@
         <v>81988924</v>
       </c>
       <c r="J610" t="s">
-        <v>677</v>
+        <v>665</v>
       </c>
       <c r="K610" s="6">
         <v>81988924</v>
@@ -12974,29 +12780,29 @@
         <v>82014131</v>
       </c>
       <c r="J611" t="s">
-        <v>678</v>
+        <v>666</v>
       </c>
       <c r="K611" s="6">
         <v>82014131</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C1" xr:uid="{00000000-0009-0000-0000-000000000000}">
+  <autoFilter ref="A1:C1">
     <sortState ref="A2:C74">
       <sortCondition descending="1" ref="C1"/>
     </sortState>
   </autoFilter>
   <mergeCells count="1">
-    <mergeCell ref="A189:C189"/>
+    <mergeCell ref="A203:C203"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A66:A186 A191:A1048576 A1:A60">
+  <conditionalFormatting sqref="A80:A200 A205:A1048576 A1:A58">
     <cfRule type="duplicateValues" dxfId="6" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A188:A1048576 A1:A186">
+  <conditionalFormatting sqref="A202:A1048576 A1:A200">
     <cfRule type="duplicateValues" dxfId="5" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A191:A1048576 A1:A186">
+  <conditionalFormatting sqref="A205:A1048576 A1:A200">
     <cfRule type="duplicateValues" dxfId="4" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
@@ -13011,7 +12817,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A13:C27"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -13186,7 +12992,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A13:C13" xr:uid="{00000000-0009-0000-0000-000001000000}">
+  <autoFilter ref="A13:C13">
     <sortState ref="A14:C25">
       <sortCondition descending="1" ref="C13"/>
     </sortState>

--- a/data/이슈제품.xlsx
+++ b/data/이슈제품.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1626" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1630" uniqueCount="670">
   <si>
     <t>오아디머무드등-화이트</t>
   </si>
@@ -2068,6 +2068,10 @@
   </si>
   <si>
     <t>10/20 생산완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입고X, 인증번호 오류로 다음 발주건부터 입고 가능</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2194,7 +2198,17 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -4004,6 +4018,15 @@
       </c>
     </row>
     <row r="64" spans="1:11">
+      <c r="A64" s="6">
+        <v>80915325</v>
+      </c>
+      <c r="B64" t="s">
+        <v>653</v>
+      </c>
+      <c r="C64" t="s">
+        <v>669</v>
+      </c>
       <c r="H64" t="s">
         <v>94</v>
       </c>
@@ -4018,6 +4041,15 @@
       </c>
     </row>
     <row r="65" spans="1:11">
+      <c r="A65" s="6">
+        <v>80915326</v>
+      </c>
+      <c r="B65" t="s">
+        <v>654</v>
+      </c>
+      <c r="C65" t="s">
+        <v>669</v>
+      </c>
       <c r="H65" t="s">
         <v>94</v>
       </c>
@@ -12797,18 +12829,21 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A80:A200 A205:A1048576 A1:A58">
-    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A202:A1048576 A1:A200">
-    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+  <conditionalFormatting sqref="A202:A1048576 A1:A63 A66:A200">
+    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A205:A1048576 A1:A200">
-    <cfRule type="duplicateValues" dxfId="4" priority="19"/>
+  <conditionalFormatting sqref="A205:A1048576 A1:A63 A66:A200">
+    <cfRule type="duplicateValues" dxfId="5" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
+    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K595:K611">
     <cfRule type="duplicateValues" dxfId="3" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K595:K611">
+  <conditionalFormatting sqref="A64:A65">
     <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/이슈제품.xlsx
+++ b/data/이슈제품.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Music\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1630" uniqueCount="670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="671">
   <si>
     <t>오아디머무드등-화이트</t>
   </si>
@@ -2072,6 +2072,10 @@
   </si>
   <si>
     <t>입고X, 인증번호 오류로 다음 발주건부터 입고 가능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>협의, 재고 부족</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2198,7 +2202,17 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -4064,6 +4078,15 @@
       </c>
     </row>
     <row r="66" spans="1:11">
+      <c r="A66">
+        <v>73893263</v>
+      </c>
+      <c r="B66" t="s">
+        <v>15</v>
+      </c>
+      <c r="C66" t="s">
+        <v>670</v>
+      </c>
       <c r="H66" t="s">
         <v>94</v>
       </c>
@@ -12829,22 +12852,25 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A80:A200 A205:A1048576 A1:A58">
-    <cfRule type="duplicateValues" dxfId="7" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A202:A1048576 A1:A63 A66:A200">
-    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
+  <conditionalFormatting sqref="A202:A1048576 A1:A63 A67:A200">
+    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A205:A1048576 A1:A63 A66:A200">
-    <cfRule type="duplicateValues" dxfId="5" priority="20"/>
+  <conditionalFormatting sqref="A205:A1048576 A1:A63 A67:A200">
+    <cfRule type="duplicateValues" dxfId="6" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K595:K611">
     <cfRule type="duplicateValues" dxfId="4" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K595:K611">
+  <conditionalFormatting sqref="A64:A65">
     <cfRule type="duplicateValues" dxfId="3" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A64:A65">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+  <conditionalFormatting sqref="A66">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -13034,10 +13060,10 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A26:A27 A14:A24">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A25">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/이슈제품.xlsx
+++ b/data/이슈제품.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1628" uniqueCount="670">
   <si>
     <t>오아디머무드등-화이트</t>
   </si>
@@ -2011,10 +2011,6 @@
   </si>
   <si>
     <t>단종</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>협의, 10/21 예정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2699,13 +2695,13 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6">
-        <v>5332788</v>
+        <v>65933937</v>
       </c>
       <c r="B6" t="s">
-        <v>344</v>
+        <v>499</v>
       </c>
       <c r="C6" t="s">
-        <v>651</v>
+        <v>631</v>
       </c>
       <c r="H6" t="s">
         <v>29</v>
@@ -2722,13 +2718,13 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7">
-        <v>65933937</v>
+        <v>76375597</v>
       </c>
       <c r="B7" t="s">
-        <v>499</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>631</v>
+        <v>22</v>
       </c>
       <c r="H7" t="s">
         <v>29</v>
@@ -2745,13 +2741,13 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8">
-        <v>76375597</v>
+        <v>60015061</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="H8" t="s">
         <v>29</v>
@@ -2768,13 +2764,13 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9">
-        <v>60015061</v>
+        <v>50725354</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>207</v>
       </c>
       <c r="C9" t="s">
-        <v>1</v>
+        <v>618</v>
       </c>
       <c r="H9" t="s">
         <v>29</v>
@@ -2791,13 +2787,13 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10">
-        <v>50725354</v>
+        <v>50153946</v>
       </c>
       <c r="B10" t="s">
-        <v>207</v>
+        <v>114</v>
       </c>
       <c r="C10" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="H10" t="s">
         <v>29</v>
@@ -2814,13 +2810,13 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11">
-        <v>50153946</v>
+        <v>75741354</v>
       </c>
       <c r="B11" t="s">
-        <v>114</v>
+        <v>601</v>
       </c>
       <c r="C11" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H11" t="s">
         <v>29</v>
@@ -2837,13 +2833,13 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12">
-        <v>75741354</v>
+        <v>15414324</v>
       </c>
       <c r="B12" t="s">
-        <v>601</v>
+        <v>198</v>
       </c>
       <c r="C12" t="s">
-        <v>620</v>
+        <v>645</v>
       </c>
       <c r="H12" t="s">
         <v>29</v>
@@ -2860,13 +2856,13 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13">
-        <v>15414324</v>
+        <v>75077119</v>
       </c>
       <c r="B13" t="s">
-        <v>198</v>
+        <v>598</v>
       </c>
       <c r="C13" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="H13" t="s">
         <v>29</v>
@@ -2883,13 +2879,13 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14">
-        <v>75077119</v>
-      </c>
-      <c r="B14" t="s">
-        <v>598</v>
+        <v>51623281</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>624</v>
       </c>
       <c r="C14" t="s">
-        <v>643</v>
+        <v>626</v>
       </c>
       <c r="H14" t="s">
         <v>29</v>
@@ -2906,13 +2902,13 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15">
-        <v>53583387</v>
-      </c>
-      <c r="B15" t="s">
-        <v>372</v>
+        <v>51989601</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>625</v>
       </c>
       <c r="C15" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="H15" t="s">
         <v>29</v>
@@ -2929,10 +2925,10 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16">
-        <v>51623281</v>
+        <v>11192166</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>624</v>
+        <v>166</v>
       </c>
       <c r="C16" t="s">
         <v>626</v>
@@ -2952,10 +2948,10 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17">
-        <v>51989601</v>
+        <v>15812678</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>625</v>
+        <v>145</v>
       </c>
       <c r="C17" t="s">
         <v>626</v>
@@ -2975,10 +2971,10 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18">
-        <v>11192166</v>
+        <v>12091621</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="C18" t="s">
         <v>626</v>
@@ -2998,10 +2994,10 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19">
-        <v>15812678</v>
+        <v>12143584</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C19" t="s">
         <v>626</v>
@@ -3021,10 +3017,10 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20">
-        <v>12091621</v>
+        <v>11192167</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="C20" t="s">
         <v>626</v>
@@ -3044,10 +3040,10 @@
     </row>
     <row r="21" spans="1:11" s="3" customFormat="1">
       <c r="A21">
-        <v>12143584</v>
+        <v>12143581</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C21" t="s">
         <v>626</v>
@@ -3067,10 +3063,10 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22">
-        <v>11192167</v>
+        <v>11192165</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C22" t="s">
         <v>626</v>
@@ -3090,10 +3086,10 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23">
-        <v>12143581</v>
+        <v>11192163</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C23" t="s">
         <v>626</v>
@@ -3113,10 +3109,10 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24">
-        <v>11192165</v>
+        <v>11291291</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="C24" t="s">
         <v>626</v>
@@ -3136,10 +3132,10 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25">
-        <v>11192163</v>
+        <v>16171214</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C25" t="s">
         <v>626</v>
@@ -3159,10 +3155,10 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26">
-        <v>11291291</v>
+        <v>12218847</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C26" t="s">
         <v>626</v>
@@ -3182,10 +3178,10 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27">
-        <v>16171214</v>
+        <v>15838517</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C27" t="s">
         <v>626</v>
@@ -3205,10 +3201,10 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28">
-        <v>12218847</v>
+        <v>12673238</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C28" t="s">
         <v>626</v>
@@ -3228,10 +3224,10 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29">
-        <v>15838517</v>
+        <v>37790051</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C29" t="s">
         <v>626</v>
@@ -3251,10 +3247,10 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30">
-        <v>12673238</v>
+        <v>37594934</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="C30" t="s">
         <v>626</v>
@@ -3274,10 +3270,10 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31">
-        <v>37790051</v>
+        <v>15702671</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="C31" t="s">
         <v>626</v>
@@ -3297,10 +3293,10 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32">
-        <v>37594934</v>
+        <v>39071990</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C32" t="s">
         <v>626</v>
@@ -3320,10 +3316,10 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33">
-        <v>15702671</v>
+        <v>52204284</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>173</v>
+        <v>91</v>
       </c>
       <c r="C33" t="s">
         <v>626</v>
@@ -3343,10 +3339,10 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34">
-        <v>39071990</v>
+        <v>39006854</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C34" t="s">
         <v>626</v>
@@ -3366,10 +3362,10 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35">
-        <v>52204284</v>
+        <v>39006857</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>91</v>
+        <v>161</v>
       </c>
       <c r="C35" t="s">
         <v>626</v>
@@ -3389,10 +3385,10 @@
     </row>
     <row r="36" spans="1:11">
       <c r="A36">
-        <v>39006854</v>
+        <v>39006855</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C36" t="s">
         <v>626</v>
@@ -3412,10 +3408,10 @@
     </row>
     <row r="37" spans="1:11">
       <c r="A37">
-        <v>39006857</v>
+        <v>51883980</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>161</v>
+        <v>361</v>
       </c>
       <c r="C37" t="s">
         <v>626</v>
@@ -3435,10 +3431,10 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38">
-        <v>39006855</v>
+        <v>52578670</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>162</v>
+        <v>366</v>
       </c>
       <c r="C38" t="s">
         <v>626</v>
@@ -3458,10 +3454,10 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39">
-        <v>51883980</v>
+        <v>52155531</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>361</v>
+        <v>93</v>
       </c>
       <c r="C39" t="s">
         <v>626</v>
@@ -3481,10 +3477,10 @@
     </row>
     <row r="40" spans="1:11">
       <c r="A40">
-        <v>52578670</v>
+        <v>15831347</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>366</v>
+        <v>141</v>
       </c>
       <c r="C40" t="s">
         <v>626</v>
@@ -3504,10 +3500,10 @@
     </row>
     <row r="41" spans="1:11">
       <c r="A41">
-        <v>52155531</v>
+        <v>32548061</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>93</v>
+        <v>168</v>
       </c>
       <c r="C41" t="s">
         <v>626</v>
@@ -3527,10 +3523,10 @@
     </row>
     <row r="42" spans="1:11">
       <c r="A42">
-        <v>15831347</v>
+        <v>35876282</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="C42" t="s">
         <v>626</v>
@@ -3550,10 +3546,10 @@
     </row>
     <row r="43" spans="1:11">
       <c r="A43">
-        <v>32548061</v>
+        <v>16805855</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="C43" t="s">
         <v>626</v>
@@ -3573,10 +3569,10 @@
     </row>
     <row r="44" spans="1:11">
       <c r="A44">
-        <v>35876282</v>
+        <v>55381383</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>172</v>
+        <v>383</v>
       </c>
       <c r="C44" t="s">
         <v>626</v>
@@ -3596,10 +3592,10 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45">
-        <v>16805855</v>
+        <v>55449180</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>144</v>
+        <v>385</v>
       </c>
       <c r="C45" t="s">
         <v>626</v>
@@ -3619,10 +3615,10 @@
     </row>
     <row r="46" spans="1:11">
       <c r="A46">
-        <v>55381383</v>
+        <v>55384739</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C46" t="s">
         <v>626</v>
@@ -3642,10 +3638,10 @@
     </row>
     <row r="47" spans="1:11">
       <c r="A47">
-        <v>55449180</v>
+        <v>55389336</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>385</v>
+        <v>623</v>
       </c>
       <c r="C47" t="s">
         <v>626</v>
@@ -3665,10 +3661,10 @@
     </row>
     <row r="48" spans="1:11">
       <c r="A48">
-        <v>55384739</v>
+        <v>55609278</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C48" t="s">
         <v>626</v>
@@ -3688,13 +3684,13 @@
     </row>
     <row r="49" spans="1:11">
       <c r="A49">
-        <v>55389336</v>
+        <v>71042279</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>623</v>
+        <v>565</v>
       </c>
       <c r="C49" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H49" t="s">
         <v>58</v>
@@ -3711,13 +3707,13 @@
     </row>
     <row r="50" spans="1:11">
       <c r="A50">
-        <v>55609278</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>384</v>
+        <v>67630646</v>
+      </c>
+      <c r="B50" t="s">
+        <v>526</v>
       </c>
       <c r="C50" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="H50" t="s">
         <v>58</v>
@@ -3734,13 +3730,13 @@
     </row>
     <row r="51" spans="1:11">
       <c r="A51">
-        <v>71042279</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>565</v>
+        <v>64971361</v>
+      </c>
+      <c r="B51" t="s">
+        <v>486</v>
       </c>
       <c r="C51" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="H51" t="s">
         <v>58</v>
@@ -3757,10 +3753,10 @@
     </row>
     <row r="52" spans="1:11">
       <c r="A52">
-        <v>67630646</v>
+        <v>62421723</v>
       </c>
       <c r="B52" t="s">
-        <v>526</v>
+        <v>454</v>
       </c>
       <c r="C52" t="s">
         <v>630</v>
@@ -3780,10 +3776,10 @@
     </row>
     <row r="53" spans="1:11">
       <c r="A53">
-        <v>64971361</v>
+        <v>62374813</v>
       </c>
       <c r="B53" t="s">
-        <v>486</v>
+        <v>455</v>
       </c>
       <c r="C53" t="s">
         <v>630</v>
@@ -3803,10 +3799,10 @@
     </row>
     <row r="54" spans="1:11">
       <c r="A54">
-        <v>62421723</v>
+        <v>68462854</v>
       </c>
       <c r="B54" t="s">
-        <v>454</v>
+        <v>532</v>
       </c>
       <c r="C54" t="s">
         <v>630</v>
@@ -3826,10 +3822,10 @@
     </row>
     <row r="55" spans="1:11">
       <c r="A55">
-        <v>62374813</v>
+        <v>64114088</v>
       </c>
       <c r="B55" t="s">
-        <v>455</v>
+        <v>469</v>
       </c>
       <c r="C55" t="s">
         <v>630</v>
@@ -3849,10 +3845,10 @@
     </row>
     <row r="56" spans="1:11">
       <c r="A56">
-        <v>68462854</v>
+        <v>19213859</v>
       </c>
       <c r="B56" t="s">
-        <v>532</v>
+        <v>34</v>
       </c>
       <c r="C56" t="s">
         <v>630</v>
@@ -3872,10 +3868,10 @@
     </row>
     <row r="57" spans="1:11">
       <c r="A57">
-        <v>64114088</v>
+        <v>13004238</v>
       </c>
       <c r="B57" t="s">
-        <v>469</v>
+        <v>36</v>
       </c>
       <c r="C57" t="s">
         <v>630</v>
@@ -3895,13 +3891,13 @@
     </row>
     <row r="58" spans="1:11">
       <c r="A58">
-        <v>19213859</v>
+        <v>11229298</v>
       </c>
       <c r="B58" t="s">
-        <v>34</v>
+        <v>174</v>
       </c>
       <c r="C58" t="s">
-        <v>630</v>
+        <v>645</v>
       </c>
       <c r="H58" t="s">
         <v>58</v>
@@ -3916,15 +3912,15 @@
         <v>14473529</v>
       </c>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:11" ht="82.5">
       <c r="A59">
-        <v>13004238</v>
+        <v>37161537</v>
       </c>
       <c r="B59" t="s">
-        <v>36</v>
-      </c>
-      <c r="C59" t="s">
-        <v>630</v>
+        <v>288</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>646</v>
       </c>
       <c r="H59" t="s">
         <v>58</v>
@@ -3941,13 +3937,13 @@
     </row>
     <row r="60" spans="1:11">
       <c r="A60">
-        <v>11229298</v>
+        <v>13745117</v>
       </c>
       <c r="B60" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="C60" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="H60" t="s">
         <v>58</v>
@@ -3962,15 +3958,15 @@
         <v>25433097</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="82.5">
+    <row r="61" spans="1:11">
       <c r="A61">
-        <v>37161537</v>
+        <v>73226633</v>
       </c>
       <c r="B61" t="s">
-        <v>288</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>646</v>
+        <v>573</v>
+      </c>
+      <c r="C61" t="s">
+        <v>667</v>
       </c>
       <c r="H61" t="s">
         <v>58</v>
@@ -3986,14 +3982,14 @@
       </c>
     </row>
     <row r="62" spans="1:11">
-      <c r="A62">
-        <v>13745117</v>
+      <c r="A62" s="6">
+        <v>80915325</v>
       </c>
       <c r="B62" t="s">
-        <v>197</v>
+        <v>652</v>
       </c>
       <c r="C62" t="s">
-        <v>647</v>
+        <v>668</v>
       </c>
       <c r="H62" t="s">
         <v>90</v>
@@ -4009,11 +4005,11 @@
       </c>
     </row>
     <row r="63" spans="1:11">
-      <c r="A63">
-        <v>73226633</v>
+      <c r="A63" s="6">
+        <v>80915326</v>
       </c>
       <c r="B63" t="s">
-        <v>573</v>
+        <v>653</v>
       </c>
       <c r="C63" t="s">
         <v>668</v>
@@ -4032,11 +4028,11 @@
       </c>
     </row>
     <row r="64" spans="1:11">
-      <c r="A64" s="6">
-        <v>80915325</v>
+      <c r="A64">
+        <v>73893263</v>
       </c>
       <c r="B64" t="s">
-        <v>653</v>
+        <v>15</v>
       </c>
       <c r="C64" t="s">
         <v>669</v>
@@ -4055,15 +4051,6 @@
       </c>
     </row>
     <row r="65" spans="1:11">
-      <c r="A65" s="6">
-        <v>80915326</v>
-      </c>
-      <c r="B65" t="s">
-        <v>654</v>
-      </c>
-      <c r="C65" t="s">
-        <v>669</v>
-      </c>
       <c r="H65" t="s">
         <v>94</v>
       </c>
@@ -4078,15 +4065,6 @@
       </c>
     </row>
     <row r="66" spans="1:11">
-      <c r="A66">
-        <v>73893263</v>
-      </c>
-      <c r="B66" t="s">
-        <v>15</v>
-      </c>
-      <c r="C66" t="s">
-        <v>670</v>
-      </c>
       <c r="H66" t="s">
         <v>94</v>
       </c>
@@ -4241,6 +4219,15 @@
       </c>
     </row>
     <row r="77" spans="1:11">
+      <c r="A77" s="8">
+        <v>15826960</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="C77" s="10" t="s">
+        <v>648</v>
+      </c>
       <c r="H77" t="s">
         <v>109</v>
       </c>
@@ -4255,6 +4242,15 @@
       </c>
     </row>
     <row r="78" spans="1:11">
+      <c r="A78" s="8">
+        <v>58505144</v>
+      </c>
+      <c r="B78" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" s="10" t="s">
+        <v>648</v>
+      </c>
       <c r="H78" t="s">
         <v>90</v>
       </c>
@@ -4270,10 +4266,10 @@
     </row>
     <row r="79" spans="1:11">
       <c r="A79" s="8">
-        <v>15826960</v>
+        <v>61199642</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>236</v>
+        <v>439</v>
       </c>
       <c r="C79" s="10" t="s">
         <v>648</v>
@@ -4293,10 +4289,10 @@
     </row>
     <row r="80" spans="1:11">
       <c r="A80" s="8">
-        <v>58505144</v>
+        <v>64912430</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>16</v>
+        <v>485</v>
       </c>
       <c r="C80" s="10" t="s">
         <v>648</v>
@@ -4316,10 +4312,10 @@
     </row>
     <row r="81" spans="1:11">
       <c r="A81" s="8">
-        <v>61199642</v>
+        <v>10124384</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>439</v>
+        <v>185</v>
       </c>
       <c r="C81" s="10" t="s">
         <v>648</v>
@@ -4339,10 +4335,10 @@
     </row>
     <row r="82" spans="1:11">
       <c r="A82" s="8">
-        <v>64912430</v>
+        <v>10929273</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>485</v>
+        <v>340</v>
       </c>
       <c r="C82" s="10" t="s">
         <v>648</v>
@@ -4362,10 +4358,10 @@
     </row>
     <row r="83" spans="1:11">
       <c r="A83" s="8">
-        <v>10124384</v>
+        <v>10929274</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>185</v>
+        <v>339</v>
       </c>
       <c r="C83" s="10" t="s">
         <v>648</v>
@@ -4385,10 +4381,10 @@
     </row>
     <row r="84" spans="1:11">
       <c r="A84" s="8">
-        <v>10929273</v>
+        <v>11670520</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>340</v>
+        <v>10</v>
       </c>
       <c r="C84" s="10" t="s">
         <v>648</v>
@@ -4408,10 +4404,10 @@
     </row>
     <row r="85" spans="1:11">
       <c r="A85" s="8">
-        <v>10929274</v>
+        <v>12029130</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>339</v>
+        <v>117</v>
       </c>
       <c r="C85" s="10" t="s">
         <v>648</v>
@@ -4431,10 +4427,10 @@
     </row>
     <row r="86" spans="1:11">
       <c r="A86" s="8">
-        <v>11670520</v>
+        <v>12038103</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>10</v>
+        <v>264</v>
       </c>
       <c r="C86" s="10" t="s">
         <v>648</v>
@@ -4454,10 +4450,10 @@
     </row>
     <row r="87" spans="1:11">
       <c r="A87" s="8">
-        <v>12029130</v>
+        <v>12095120</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>117</v>
+        <v>261</v>
       </c>
       <c r="C87" s="10" t="s">
         <v>648</v>
@@ -4477,10 +4473,10 @@
     </row>
     <row r="88" spans="1:11">
       <c r="A88" s="8">
-        <v>12038103</v>
+        <v>12481760</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>264</v>
+        <v>292</v>
       </c>
       <c r="C88" s="10" t="s">
         <v>648</v>
@@ -4500,10 +4496,10 @@
     </row>
     <row r="89" spans="1:11">
       <c r="A89" s="8">
-        <v>12095120</v>
+        <v>13195957</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>261</v>
+        <v>8</v>
       </c>
       <c r="C89" s="10" t="s">
         <v>648</v>
@@ -4523,10 +4519,10 @@
     </row>
     <row r="90" spans="1:11">
       <c r="A90" s="8">
-        <v>12481760</v>
+        <v>14299890</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>292</v>
+        <v>177</v>
       </c>
       <c r="C90" s="10" t="s">
         <v>648</v>
@@ -4546,10 +4542,10 @@
     </row>
     <row r="91" spans="1:11">
       <c r="A91" s="8">
-        <v>13195957</v>
+        <v>14473529</v>
       </c>
       <c r="B91" s="9" t="s">
-        <v>8</v>
+        <v>87</v>
       </c>
       <c r="C91" s="10" t="s">
         <v>648</v>
@@ -4569,10 +4565,10 @@
     </row>
     <row r="92" spans="1:11">
       <c r="A92" s="8">
-        <v>14299890</v>
+        <v>15757638</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>177</v>
+        <v>263</v>
       </c>
       <c r="C92" s="10" t="s">
         <v>648</v>
@@ -4592,10 +4588,10 @@
     </row>
     <row r="93" spans="1:11">
       <c r="A93" s="8">
-        <v>14473529</v>
+        <v>16806254</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>87</v>
+        <v>317</v>
       </c>
       <c r="C93" s="10" t="s">
         <v>648</v>
@@ -4615,10 +4611,10 @@
     </row>
     <row r="94" spans="1:11">
       <c r="A94" s="8">
-        <v>15757638</v>
+        <v>20341619</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>263</v>
+        <v>37</v>
       </c>
       <c r="C94" s="10" t="s">
         <v>648</v>
@@ -4638,10 +4634,10 @@
     </row>
     <row r="95" spans="1:11">
       <c r="A95" s="8">
-        <v>16806254</v>
+        <v>22119013</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C95" s="10" t="s">
         <v>648</v>
@@ -4661,10 +4657,10 @@
     </row>
     <row r="96" spans="1:11">
       <c r="A96" s="8">
-        <v>20341619</v>
+        <v>25433097</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="C96" s="10" t="s">
         <v>648</v>
@@ -4684,10 +4680,10 @@
     </row>
     <row r="97" spans="1:11">
       <c r="A97" s="8">
-        <v>22119013</v>
+        <v>25512595</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>322</v>
+        <v>20</v>
       </c>
       <c r="C97" s="10" t="s">
         <v>648</v>
@@ -4707,10 +4703,10 @@
     </row>
     <row r="98" spans="1:11">
       <c r="A98" s="8">
-        <v>25433097</v>
+        <v>25665354</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="C98" s="10" t="s">
         <v>648</v>
@@ -4730,10 +4726,10 @@
     </row>
     <row r="99" spans="1:11">
       <c r="A99" s="8">
-        <v>25512595</v>
+        <v>29258063</v>
       </c>
       <c r="B99" s="9" t="s">
-        <v>20</v>
+        <v>308</v>
       </c>
       <c r="C99" s="10" t="s">
         <v>648</v>
@@ -4753,10 +4749,10 @@
     </row>
     <row r="100" spans="1:11">
       <c r="A100" s="8">
-        <v>25665354</v>
+        <v>29266932</v>
       </c>
       <c r="B100" s="9" t="s">
-        <v>119</v>
+        <v>40</v>
       </c>
       <c r="C100" s="10" t="s">
         <v>648</v>
@@ -4776,10 +4772,10 @@
     </row>
     <row r="101" spans="1:11">
       <c r="A101" s="8">
-        <v>29258063</v>
+        <v>34991467</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>308</v>
+        <v>279</v>
       </c>
       <c r="C101" s="10" t="s">
         <v>648</v>
@@ -4799,10 +4795,10 @@
     </row>
     <row r="102" spans="1:11">
       <c r="A102" s="8">
-        <v>29266932</v>
+        <v>35401181</v>
       </c>
       <c r="B102" s="9" t="s">
-        <v>40</v>
+        <v>229</v>
       </c>
       <c r="C102" s="10" t="s">
         <v>648</v>
@@ -4822,10 +4818,10 @@
     </row>
     <row r="103" spans="1:11">
       <c r="A103" s="8">
-        <v>34991467</v>
+        <v>36606823</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>279</v>
+        <v>110</v>
       </c>
       <c r="C103" s="10" t="s">
         <v>648</v>
@@ -4845,10 +4841,10 @@
     </row>
     <row r="104" spans="1:11">
       <c r="A104" s="8">
-        <v>35401181</v>
+        <v>38157908</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C104" s="10" t="s">
         <v>648</v>
@@ -4868,10 +4864,10 @@
     </row>
     <row r="105" spans="1:11">
       <c r="A105" s="8">
-        <v>36606823</v>
+        <v>38407975</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="C105" s="10" t="s">
         <v>648</v>
@@ -4891,10 +4887,10 @@
     </row>
     <row r="106" spans="1:11">
       <c r="A106" s="8">
-        <v>38157908</v>
+        <v>38659485</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>230</v>
+        <v>43</v>
       </c>
       <c r="C106" s="10" t="s">
         <v>648</v>
@@ -4914,10 +4910,10 @@
     </row>
     <row r="107" spans="1:11">
       <c r="A107" s="8">
-        <v>38407975</v>
+        <v>39239709</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>46</v>
+        <v>325</v>
       </c>
       <c r="C107" s="10" t="s">
         <v>648</v>
@@ -4937,10 +4933,10 @@
     </row>
     <row r="108" spans="1:11">
       <c r="A108" s="8">
-        <v>38659485</v>
+        <v>39944753</v>
       </c>
       <c r="B108" s="9" t="s">
-        <v>43</v>
+        <v>298</v>
       </c>
       <c r="C108" s="10" t="s">
         <v>648</v>
@@ -4960,10 +4956,10 @@
     </row>
     <row r="109" spans="1:11">
       <c r="A109" s="8">
-        <v>39239709</v>
+        <v>40180424</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>325</v>
+        <v>9</v>
       </c>
       <c r="C109" s="10" t="s">
         <v>648</v>
@@ -4983,10 +4979,10 @@
     </row>
     <row r="110" spans="1:11">
       <c r="A110" s="8">
-        <v>39944753</v>
+        <v>43571361</v>
       </c>
       <c r="B110" s="9" t="s">
-        <v>298</v>
+        <v>135</v>
       </c>
       <c r="C110" s="10" t="s">
         <v>648</v>
@@ -5006,10 +5002,10 @@
     </row>
     <row r="111" spans="1:11">
       <c r="A111" s="8">
-        <v>40180424</v>
+        <v>46801171</v>
       </c>
       <c r="B111" s="9" t="s">
-        <v>9</v>
+        <v>265</v>
       </c>
       <c r="C111" s="10" t="s">
         <v>648</v>
@@ -5029,10 +5025,10 @@
     </row>
     <row r="112" spans="1:11">
       <c r="A112" s="8">
-        <v>43571361</v>
+        <v>48449253</v>
       </c>
       <c r="B112" s="9" t="s">
-        <v>135</v>
+        <v>299</v>
       </c>
       <c r="C112" s="10" t="s">
         <v>648</v>
@@ -5052,10 +5048,10 @@
     </row>
     <row r="113" spans="1:11">
       <c r="A113" s="8">
-        <v>46801171</v>
+        <v>53967042</v>
       </c>
       <c r="B113" s="9" t="s">
-        <v>265</v>
+        <v>377</v>
       </c>
       <c r="C113" s="10" t="s">
         <v>648</v>
@@ -5075,10 +5071,10 @@
     </row>
     <row r="114" spans="1:11">
       <c r="A114" s="8">
-        <v>48449253</v>
+        <v>55275736</v>
       </c>
       <c r="B114" s="9" t="s">
-        <v>299</v>
+        <v>378</v>
       </c>
       <c r="C114" s="10" t="s">
         <v>648</v>
@@ -5098,10 +5094,10 @@
     </row>
     <row r="115" spans="1:11">
       <c r="A115" s="8">
-        <v>53967042</v>
+        <v>59759466</v>
       </c>
       <c r="B115" s="9" t="s">
-        <v>377</v>
+        <v>412</v>
       </c>
       <c r="C115" s="10" t="s">
         <v>648</v>
@@ -5121,10 +5117,10 @@
     </row>
     <row r="116" spans="1:11">
       <c r="A116" s="8">
-        <v>55275736</v>
+        <v>60024864</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>378</v>
+        <v>421</v>
       </c>
       <c r="C116" s="10" t="s">
         <v>648</v>
@@ -5144,10 +5140,10 @@
     </row>
     <row r="117" spans="1:11">
       <c r="A117" s="8">
-        <v>59759466</v>
+        <v>60025950</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="C117" s="10" t="s">
         <v>648</v>
@@ -5167,10 +5163,10 @@
     </row>
     <row r="118" spans="1:11">
       <c r="A118" s="8">
-        <v>60024864</v>
+        <v>60541171</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="C118" s="10" t="s">
         <v>648</v>
@@ -5190,10 +5186,10 @@
     </row>
     <row r="119" spans="1:11">
       <c r="A119" s="8">
-        <v>60025950</v>
+        <v>60543356</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="C119" s="10" t="s">
         <v>648</v>
@@ -5213,10 +5209,10 @@
     </row>
     <row r="120" spans="1:11">
       <c r="A120" s="8">
-        <v>60541171</v>
+        <v>60615380</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C120" s="10" t="s">
         <v>648</v>
@@ -5236,10 +5232,10 @@
     </row>
     <row r="121" spans="1:11">
       <c r="A121" s="8">
-        <v>60543356</v>
+        <v>61760291</v>
       </c>
       <c r="B121" s="9" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C121" s="10" t="s">
         <v>648</v>
@@ -5259,10 +5255,10 @@
     </row>
     <row r="122" spans="1:11">
       <c r="A122" s="8">
-        <v>60615380</v>
+        <v>62385013</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="C122" s="10" t="s">
         <v>648</v>
@@ -5282,10 +5278,10 @@
     </row>
     <row r="123" spans="1:11">
       <c r="A123" s="8">
-        <v>61760291</v>
+        <v>64606094</v>
       </c>
       <c r="B123" s="9" t="s">
-        <v>440</v>
+        <v>474</v>
       </c>
       <c r="C123" s="10" t="s">
         <v>648</v>
@@ -5305,10 +5301,10 @@
     </row>
     <row r="124" spans="1:11">
       <c r="A124" s="8">
-        <v>62385013</v>
+        <v>64846264</v>
       </c>
       <c r="B124" s="9" t="s">
-        <v>452</v>
+        <v>479</v>
       </c>
       <c r="C124" s="10" t="s">
         <v>648</v>
@@ -5328,10 +5324,10 @@
     </row>
     <row r="125" spans="1:11">
       <c r="A125" s="8">
-        <v>64606094</v>
+        <v>65566541</v>
       </c>
       <c r="B125" s="9" t="s">
-        <v>474</v>
+        <v>492</v>
       </c>
       <c r="C125" s="10" t="s">
         <v>648</v>
@@ -5351,10 +5347,10 @@
     </row>
     <row r="126" spans="1:11">
       <c r="A126" s="8">
-        <v>64846264</v>
+        <v>66607099</v>
       </c>
       <c r="B126" s="9" t="s">
-        <v>479</v>
+        <v>512</v>
       </c>
       <c r="C126" s="10" t="s">
         <v>648</v>
@@ -5374,10 +5370,10 @@
     </row>
     <row r="127" spans="1:11">
       <c r="A127" s="8">
-        <v>65566541</v>
+        <v>59924956</v>
       </c>
       <c r="B127" s="9" t="s">
-        <v>492</v>
+        <v>417</v>
       </c>
       <c r="C127" s="10" t="s">
         <v>648</v>
@@ -5397,13 +5393,13 @@
     </row>
     <row r="128" spans="1:11">
       <c r="A128" s="8">
-        <v>66607099</v>
+        <v>17014694</v>
       </c>
       <c r="B128" s="9" t="s">
-        <v>512</v>
-      </c>
-      <c r="C128" s="10" t="s">
-        <v>648</v>
+        <v>67</v>
+      </c>
+      <c r="C128" s="9" t="s">
+        <v>649</v>
       </c>
       <c r="H128" t="s">
         <v>90</v>
@@ -5420,13 +5416,13 @@
     </row>
     <row r="129" spans="1:11">
       <c r="A129" s="8">
-        <v>59924956</v>
+        <v>17014693</v>
       </c>
       <c r="B129" s="9" t="s">
-        <v>417</v>
-      </c>
-      <c r="C129" s="10" t="s">
-        <v>648</v>
+        <v>68</v>
+      </c>
+      <c r="C129" s="9" t="s">
+        <v>649</v>
       </c>
       <c r="H129" t="s">
         <v>90</v>
@@ -5443,13 +5439,13 @@
     </row>
     <row r="130" spans="1:11">
       <c r="A130" s="8">
-        <v>17014694</v>
+        <v>36811022</v>
       </c>
       <c r="B130" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C130" s="9" t="s">
-        <v>649</v>
+        <v>284</v>
+      </c>
+      <c r="C130" s="10" t="s">
+        <v>650</v>
       </c>
       <c r="H130" t="s">
         <v>29</v>
@@ -5466,13 +5462,13 @@
     </row>
     <row r="131" spans="1:11">
       <c r="A131" s="8">
-        <v>17014693</v>
+        <v>36811023</v>
       </c>
       <c r="B131" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C131" s="9" t="s">
-        <v>649</v>
+        <v>0</v>
+      </c>
+      <c r="C131" s="10" t="s">
+        <v>650</v>
       </c>
       <c r="H131" t="s">
         <v>29</v>
@@ -5489,10 +5485,10 @@
     </row>
     <row r="132" spans="1:11">
       <c r="A132" s="8">
-        <v>36811022</v>
+        <v>60023938</v>
       </c>
       <c r="B132" s="9" t="s">
-        <v>284</v>
+        <v>419</v>
       </c>
       <c r="C132" s="10" t="s">
         <v>650</v>
@@ -5512,10 +5508,10 @@
     </row>
     <row r="133" spans="1:11">
       <c r="A133" s="8">
-        <v>36811023</v>
+        <v>61929494</v>
       </c>
       <c r="B133" s="9" t="s">
-        <v>0</v>
+        <v>445</v>
       </c>
       <c r="C133" s="10" t="s">
         <v>650</v>
@@ -5535,10 +5531,10 @@
     </row>
     <row r="134" spans="1:11">
       <c r="A134" s="8">
-        <v>60023938</v>
+        <v>66417803</v>
       </c>
       <c r="B134" s="9" t="s">
-        <v>419</v>
+        <v>503</v>
       </c>
       <c r="C134" s="10" t="s">
         <v>650</v>
@@ -5558,10 +5554,10 @@
     </row>
     <row r="135" spans="1:11">
       <c r="A135" s="8">
-        <v>61929494</v>
+        <v>20342327</v>
       </c>
       <c r="B135" s="9" t="s">
-        <v>445</v>
+        <v>35</v>
       </c>
       <c r="C135" s="10" t="s">
         <v>650</v>
@@ -5581,10 +5577,10 @@
     </row>
     <row r="136" spans="1:11">
       <c r="A136" s="8">
-        <v>66417803</v>
+        <v>12586373</v>
       </c>
       <c r="B136" s="9" t="s">
-        <v>503</v>
+        <v>41</v>
       </c>
       <c r="C136" s="10" t="s">
         <v>650</v>
@@ -5604,10 +5600,10 @@
     </row>
     <row r="137" spans="1:11">
       <c r="A137" s="8">
-        <v>20342327</v>
+        <v>11055651</v>
       </c>
       <c r="B137" s="9" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C137" s="10" t="s">
         <v>650</v>
@@ -5627,10 +5623,10 @@
     </row>
     <row r="138" spans="1:11">
       <c r="A138" s="8">
-        <v>12586373</v>
+        <v>18816827</v>
       </c>
       <c r="B138" s="9" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C138" s="10" t="s">
         <v>650</v>
@@ -5650,10 +5646,10 @@
     </row>
     <row r="139" spans="1:11">
       <c r="A139" s="8">
-        <v>11055651</v>
+        <v>39229235</v>
       </c>
       <c r="B139" s="9" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="C139" s="10" t="s">
         <v>650</v>
@@ -5673,10 +5669,10 @@
     </row>
     <row r="140" spans="1:11">
       <c r="A140" s="8">
-        <v>18816827</v>
+        <v>13151160</v>
       </c>
       <c r="B140" s="9" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="C140" s="10" t="s">
         <v>650</v>
@@ -5696,10 +5692,10 @@
     </row>
     <row r="141" spans="1:11">
       <c r="A141" s="8">
-        <v>39229235</v>
+        <v>13151158</v>
       </c>
       <c r="B141" s="9" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C141" s="10" t="s">
         <v>650</v>
@@ -5719,10 +5715,10 @@
     </row>
     <row r="142" spans="1:11">
       <c r="A142" s="8">
-        <v>13151160</v>
+        <v>10978754</v>
       </c>
       <c r="B142" s="9" t="s">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="C142" s="10" t="s">
         <v>650</v>
@@ -5742,10 +5738,10 @@
     </row>
     <row r="143" spans="1:11">
       <c r="A143" s="8">
-        <v>13151158</v>
+        <v>19619417</v>
       </c>
       <c r="B143" s="9" t="s">
-        <v>64</v>
+        <v>108</v>
       </c>
       <c r="C143" s="10" t="s">
         <v>650</v>
@@ -5765,10 +5761,10 @@
     </row>
     <row r="144" spans="1:11">
       <c r="A144" s="8">
-        <v>10978754</v>
+        <v>39063227</v>
       </c>
       <c r="B144" s="9" t="s">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="C144" s="10" t="s">
         <v>650</v>
@@ -5788,10 +5784,10 @@
     </row>
     <row r="145" spans="1:11">
       <c r="A145" s="8">
-        <v>19619417</v>
+        <v>46995055</v>
       </c>
       <c r="B145" s="9" t="s">
-        <v>108</v>
+        <v>186</v>
       </c>
       <c r="C145" s="10" t="s">
         <v>650</v>
@@ -5811,10 +5807,10 @@
     </row>
     <row r="146" spans="1:11">
       <c r="A146" s="8">
-        <v>39063227</v>
+        <v>11744316</v>
       </c>
       <c r="B146" s="9" t="s">
-        <v>140</v>
+        <v>187</v>
       </c>
       <c r="C146" s="10" t="s">
         <v>650</v>
@@ -5834,10 +5830,10 @@
     </row>
     <row r="147" spans="1:11">
       <c r="A147" s="8">
-        <v>46995055</v>
+        <v>13069194</v>
       </c>
       <c r="B147" s="9" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C147" s="10" t="s">
         <v>650</v>
@@ -5857,10 +5853,10 @@
     </row>
     <row r="148" spans="1:11">
       <c r="A148" s="8">
-        <v>11744316</v>
+        <v>4125381</v>
       </c>
       <c r="B148" s="9" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C148" s="10" t="s">
         <v>650</v>
@@ -5880,10 +5876,10 @@
     </row>
     <row r="149" spans="1:11">
       <c r="A149" s="8">
-        <v>13069194</v>
+        <v>42839047</v>
       </c>
       <c r="B149" s="9" t="s">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="C149" s="10" t="s">
         <v>650</v>
@@ -5903,10 +5899,10 @@
     </row>
     <row r="150" spans="1:11">
       <c r="A150" s="8">
-        <v>4125381</v>
+        <v>4152612</v>
       </c>
       <c r="B150" s="9" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="C150" s="10" t="s">
         <v>650</v>
@@ -5926,10 +5922,10 @@
     </row>
     <row r="151" spans="1:11">
       <c r="A151" s="8">
-        <v>42839047</v>
+        <v>4152610</v>
       </c>
       <c r="B151" s="9" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="C151" s="10" t="s">
         <v>650</v>
@@ -5949,10 +5945,10 @@
     </row>
     <row r="152" spans="1:11">
       <c r="A152" s="8">
-        <v>4152612</v>
+        <v>34098917</v>
       </c>
       <c r="B152" s="9" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="C152" s="10" t="s">
         <v>650</v>
@@ -5972,10 +5968,10 @@
     </row>
     <row r="153" spans="1:11">
       <c r="A153" s="8">
-        <v>4152610</v>
+        <v>49985232</v>
       </c>
       <c r="B153" s="9" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="C153" s="10" t="s">
         <v>650</v>
@@ -5995,10 +5991,10 @@
     </row>
     <row r="154" spans="1:11">
       <c r="A154" s="8">
-        <v>34098917</v>
+        <v>50155408</v>
       </c>
       <c r="B154" s="9" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="C154" s="10" t="s">
         <v>650</v>
@@ -6018,10 +6014,10 @@
     </row>
     <row r="155" spans="1:11">
       <c r="A155" s="8">
-        <v>49985232</v>
+        <v>41662266</v>
       </c>
       <c r="B155" s="9" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C155" s="10" t="s">
         <v>650</v>
@@ -6041,10 +6037,10 @@
     </row>
     <row r="156" spans="1:11">
       <c r="A156" s="8">
-        <v>50155408</v>
+        <v>13573385</v>
       </c>
       <c r="B156" s="9" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="C156" s="10" t="s">
         <v>650</v>
@@ -6064,10 +6060,10 @@
     </row>
     <row r="157" spans="1:11">
       <c r="A157" s="8">
-        <v>41662266</v>
+        <v>42871700</v>
       </c>
       <c r="B157" s="9" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="C157" s="10" t="s">
         <v>650</v>
@@ -6087,10 +6083,10 @@
     </row>
     <row r="158" spans="1:11">
       <c r="A158" s="8">
-        <v>13573385</v>
+        <v>39257536</v>
       </c>
       <c r="B158" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C158" s="10" t="s">
         <v>650</v>
@@ -6110,10 +6106,10 @@
     </row>
     <row r="159" spans="1:11">
       <c r="A159" s="8">
-        <v>42871700</v>
+        <v>37424126</v>
       </c>
       <c r="B159" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C159" s="10" t="s">
         <v>650</v>
@@ -6133,10 +6129,10 @@
     </row>
     <row r="160" spans="1:11">
       <c r="A160" s="8">
-        <v>39257536</v>
+        <v>36802614</v>
       </c>
       <c r="B160" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C160" s="10" t="s">
         <v>650</v>
@@ -6156,10 +6152,10 @@
     </row>
     <row r="161" spans="1:11">
       <c r="A161" s="8">
-        <v>37424126</v>
+        <v>36577826</v>
       </c>
       <c r="B161" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C161" s="10" t="s">
         <v>650</v>
@@ -6179,10 +6175,10 @@
     </row>
     <row r="162" spans="1:11">
       <c r="A162" s="8">
-        <v>36802614</v>
+        <v>26196255</v>
       </c>
       <c r="B162" s="9" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C162" s="10" t="s">
         <v>650</v>
@@ -6202,10 +6198,10 @@
     </row>
     <row r="163" spans="1:11">
       <c r="A163" s="8">
-        <v>36577826</v>
+        <v>26019234</v>
       </c>
       <c r="B163" s="9" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="C163" s="10" t="s">
         <v>650</v>
@@ -6225,10 +6221,10 @@
     </row>
     <row r="164" spans="1:11">
       <c r="A164" s="8">
-        <v>26196255</v>
+        <v>25411238</v>
       </c>
       <c r="B164" s="9" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="C164" s="10" t="s">
         <v>650</v>
@@ -6248,10 +6244,10 @@
     </row>
     <row r="165" spans="1:11">
       <c r="A165" s="8">
-        <v>26019234</v>
+        <v>26500515</v>
       </c>
       <c r="B165" s="9" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="C165" s="10" t="s">
         <v>650</v>
@@ -6271,10 +6267,10 @@
     </row>
     <row r="166" spans="1:11">
       <c r="A166" s="8">
-        <v>25411238</v>
+        <v>36162739</v>
       </c>
       <c r="B166" s="9" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C166" s="10" t="s">
         <v>650</v>
@@ -6294,10 +6290,10 @@
     </row>
     <row r="167" spans="1:11">
       <c r="A167" s="8">
-        <v>26500515</v>
+        <v>39893389</v>
       </c>
       <c r="B167" s="9" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C167" s="10" t="s">
         <v>650</v>
@@ -6317,10 +6313,10 @@
     </row>
     <row r="168" spans="1:11">
       <c r="A168" s="8">
-        <v>36162739</v>
+        <v>39296173</v>
       </c>
       <c r="B168" s="9" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C168" s="10" t="s">
         <v>650</v>
@@ -6340,10 +6336,10 @@
     </row>
     <row r="169" spans="1:11">
       <c r="A169" s="8">
-        <v>39893389</v>
+        <v>42217758</v>
       </c>
       <c r="B169" s="9" t="s">
-        <v>256</v>
+        <v>285</v>
       </c>
       <c r="C169" s="10" t="s">
         <v>650</v>
@@ -6363,10 +6359,10 @@
     </row>
     <row r="170" spans="1:11">
       <c r="A170" s="8">
-        <v>39296173</v>
+        <v>22403445</v>
       </c>
       <c r="B170" s="9" t="s">
-        <v>257</v>
+        <v>290</v>
       </c>
       <c r="C170" s="10" t="s">
         <v>650</v>
@@ -6386,10 +6382,10 @@
     </row>
     <row r="171" spans="1:11">
       <c r="A171" s="8">
-        <v>42217758</v>
+        <v>26257716</v>
       </c>
       <c r="B171" s="9" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="C171" s="10" t="s">
         <v>650</v>
@@ -6409,10 +6405,10 @@
     </row>
     <row r="172" spans="1:11">
       <c r="A172" s="8">
-        <v>22403445</v>
+        <v>42486414</v>
       </c>
       <c r="B172" s="9" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="C172" s="10" t="s">
         <v>650</v>
@@ -6432,10 +6428,10 @@
     </row>
     <row r="173" spans="1:11">
       <c r="A173" s="8">
-        <v>26257716</v>
+        <v>44695653</v>
       </c>
       <c r="B173" s="9" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="C173" s="10" t="s">
         <v>650</v>
@@ -6455,10 +6451,10 @@
     </row>
     <row r="174" spans="1:11">
       <c r="A174" s="8">
-        <v>42486414</v>
+        <v>13405604</v>
       </c>
       <c r="B174" s="9" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C174" s="10" t="s">
         <v>650</v>
@@ -6478,10 +6474,10 @@
     </row>
     <row r="175" spans="1:11">
       <c r="A175" s="8">
-        <v>44695653</v>
+        <v>39911056</v>
       </c>
       <c r="B175" s="9" t="s">
-        <v>306</v>
+        <v>337</v>
       </c>
       <c r="C175" s="10" t="s">
         <v>650</v>
@@ -6501,10 +6497,10 @@
     </row>
     <row r="176" spans="1:11">
       <c r="A176" s="8">
-        <v>13405604</v>
+        <v>51897600</v>
       </c>
       <c r="B176" s="9" t="s">
-        <v>309</v>
+        <v>350</v>
       </c>
       <c r="C176" s="10" t="s">
         <v>650</v>
@@ -6524,10 +6520,10 @@
     </row>
     <row r="177" spans="1:11">
       <c r="A177" s="8">
-        <v>39911056</v>
+        <v>52990015</v>
       </c>
       <c r="B177" s="9" t="s">
-        <v>337</v>
+        <v>363</v>
       </c>
       <c r="C177" s="10" t="s">
         <v>650</v>
@@ -6547,10 +6543,10 @@
     </row>
     <row r="178" spans="1:11">
       <c r="A178" s="8">
-        <v>51897600</v>
+        <v>55354052</v>
       </c>
       <c r="B178" s="9" t="s">
-        <v>350</v>
+        <v>382</v>
       </c>
       <c r="C178" s="10" t="s">
         <v>650</v>
@@ -6570,10 +6566,10 @@
     </row>
     <row r="179" spans="1:11">
       <c r="A179" s="8">
-        <v>52990015</v>
+        <v>55356388</v>
       </c>
       <c r="B179" s="9" t="s">
-        <v>363</v>
+        <v>390</v>
       </c>
       <c r="C179" s="10" t="s">
         <v>650</v>
@@ -6593,10 +6589,10 @@
     </row>
     <row r="180" spans="1:11">
       <c r="A180" s="8">
-        <v>55354052</v>
+        <v>62377903</v>
       </c>
       <c r="B180" s="9" t="s">
-        <v>382</v>
+        <v>436</v>
       </c>
       <c r="C180" s="10" t="s">
         <v>650</v>
@@ -6616,10 +6612,10 @@
     </row>
     <row r="181" spans="1:11">
       <c r="A181" s="8">
-        <v>55356388</v>
+        <v>66097436</v>
       </c>
       <c r="B181" s="9" t="s">
-        <v>390</v>
+        <v>477</v>
       </c>
       <c r="C181" s="10" t="s">
         <v>650</v>
@@ -6639,10 +6635,10 @@
     </row>
     <row r="182" spans="1:11">
       <c r="A182" s="8">
-        <v>62377903</v>
+        <v>11681261</v>
       </c>
       <c r="B182" s="9" t="s">
-        <v>436</v>
+        <v>287</v>
       </c>
       <c r="C182" s="10" t="s">
         <v>650</v>
@@ -6662,10 +6658,10 @@
     </row>
     <row r="183" spans="1:11">
       <c r="A183" s="8">
-        <v>66097436</v>
+        <v>11874445</v>
       </c>
       <c r="B183" s="9" t="s">
-        <v>477</v>
+        <v>6</v>
       </c>
       <c r="C183" s="10" t="s">
         <v>650</v>
@@ -6685,10 +6681,10 @@
     </row>
     <row r="184" spans="1:11">
       <c r="A184" s="8">
-        <v>11681261</v>
+        <v>14719737</v>
       </c>
       <c r="B184" s="9" t="s">
-        <v>287</v>
+        <v>4</v>
       </c>
       <c r="C184" s="10" t="s">
         <v>650</v>
@@ -6708,10 +6704,10 @@
     </row>
     <row r="185" spans="1:11">
       <c r="A185" s="8">
-        <v>11874445</v>
+        <v>16179047</v>
       </c>
       <c r="B185" s="9" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C185" s="10" t="s">
         <v>650</v>
@@ -6731,10 +6727,10 @@
     </row>
     <row r="186" spans="1:11">
       <c r="A186" s="8">
-        <v>14719737</v>
+        <v>20815743</v>
       </c>
       <c r="B186" s="9" t="s">
-        <v>4</v>
+        <v>209</v>
       </c>
       <c r="C186" s="10" t="s">
         <v>650</v>
@@ -6754,10 +6750,10 @@
     </row>
     <row r="187" spans="1:11">
       <c r="A187" s="8">
-        <v>16179047</v>
+        <v>30405071</v>
       </c>
       <c r="B187" s="9" t="s">
-        <v>12</v>
+        <v>289</v>
       </c>
       <c r="C187" s="10" t="s">
         <v>650</v>
@@ -6777,10 +6773,10 @@
     </row>
     <row r="188" spans="1:11">
       <c r="A188" s="8">
-        <v>20815743</v>
+        <v>34352694</v>
       </c>
       <c r="B188" s="9" t="s">
-        <v>209</v>
+        <v>139</v>
       </c>
       <c r="C188" s="10" t="s">
         <v>650</v>
@@ -6800,10 +6796,10 @@
     </row>
     <row r="189" spans="1:11">
       <c r="A189" s="8">
-        <v>30405071</v>
+        <v>35149611</v>
       </c>
       <c r="B189" s="9" t="s">
-        <v>289</v>
+        <v>2</v>
       </c>
       <c r="C189" s="10" t="s">
         <v>650</v>
@@ -6823,10 +6819,10 @@
     </row>
     <row r="190" spans="1:11">
       <c r="A190" s="8">
-        <v>34352694</v>
+        <v>35896315</v>
       </c>
       <c r="B190" s="9" t="s">
-        <v>139</v>
+        <v>219</v>
       </c>
       <c r="C190" s="10" t="s">
         <v>650</v>
@@ -6846,10 +6842,10 @@
     </row>
     <row r="191" spans="1:11">
       <c r="A191" s="8">
-        <v>35149611</v>
+        <v>36682232</v>
       </c>
       <c r="B191" s="9" t="s">
-        <v>2</v>
+        <v>294</v>
       </c>
       <c r="C191" s="10" t="s">
         <v>650</v>
@@ -6869,10 +6865,10 @@
     </row>
     <row r="192" spans="1:11">
       <c r="A192" s="8">
-        <v>35896315</v>
+        <v>43571360</v>
       </c>
       <c r="B192" s="9" t="s">
-        <v>219</v>
+        <v>136</v>
       </c>
       <c r="C192" s="10" t="s">
         <v>650</v>
@@ -6892,10 +6888,10 @@
     </row>
     <row r="193" spans="1:11">
       <c r="A193" s="8">
-        <v>36682232</v>
+        <v>44374810</v>
       </c>
       <c r="B193" s="9" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="C193" s="10" t="s">
         <v>650</v>
@@ -6915,10 +6911,10 @@
     </row>
     <row r="194" spans="1:11">
       <c r="A194" s="8">
-        <v>43571360</v>
+        <v>45349063</v>
       </c>
       <c r="B194" s="9" t="s">
-        <v>136</v>
+        <v>7</v>
       </c>
       <c r="C194" s="10" t="s">
         <v>650</v>
@@ -6938,10 +6934,10 @@
     </row>
     <row r="195" spans="1:11">
       <c r="A195" s="8">
-        <v>44374810</v>
+        <v>59836396</v>
       </c>
       <c r="B195" s="9" t="s">
-        <v>307</v>
+        <v>418</v>
       </c>
       <c r="C195" s="10" t="s">
         <v>650</v>
@@ -6961,10 +6957,10 @@
     </row>
     <row r="196" spans="1:11">
       <c r="A196" s="8">
-        <v>45349063</v>
+        <v>59927382</v>
       </c>
       <c r="B196" s="9" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C196" s="10" t="s">
         <v>650</v>
@@ -6984,10 +6980,10 @@
     </row>
     <row r="197" spans="1:11">
       <c r="A197" s="8">
-        <v>59836396</v>
+        <v>60541542</v>
       </c>
       <c r="B197" s="9" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="C197" s="10" t="s">
         <v>650</v>
@@ -7007,10 +7003,10 @@
     </row>
     <row r="198" spans="1:11">
       <c r="A198" s="8">
-        <v>59927382</v>
+        <v>66417801</v>
       </c>
       <c r="B198" s="9" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C198" s="10" t="s">
         <v>650</v>
@@ -7029,15 +7025,6 @@
       </c>
     </row>
     <row r="199" spans="1:11">
-      <c r="A199" s="8">
-        <v>60541542</v>
-      </c>
-      <c r="B199" s="9" t="s">
-        <v>427</v>
-      </c>
-      <c r="C199" s="10" t="s">
-        <v>650</v>
-      </c>
       <c r="H199" t="s">
         <v>92</v>
       </c>
@@ -7052,15 +7039,6 @@
       </c>
     </row>
     <row r="200" spans="1:11">
-      <c r="A200" s="8">
-        <v>66417801</v>
-      </c>
-      <c r="B200" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="C200" s="10" t="s">
-        <v>650</v>
-      </c>
       <c r="H200" t="s">
         <v>92</v>
       </c>
@@ -7075,6 +7053,11 @@
       </c>
     </row>
     <row r="201" spans="1:11">
+      <c r="A201" s="13" t="s">
+        <v>651</v>
+      </c>
+      <c r="B201" s="13"/>
+      <c r="C201" s="13"/>
       <c r="H201" t="s">
         <v>92</v>
       </c>
@@ -7089,6 +7072,7 @@
       </c>
     </row>
     <row r="202" spans="1:11">
+      <c r="B202" s="11"/>
       <c r="H202" t="s">
         <v>92</v>
       </c>
@@ -7103,11 +7087,7 @@
       </c>
     </row>
     <row r="203" spans="1:11">
-      <c r="A203" s="13" t="s">
-        <v>652</v>
-      </c>
-      <c r="B203" s="13"/>
-      <c r="C203" s="13"/>
+      <c r="B203" s="12"/>
       <c r="H203" t="s">
         <v>92</v>
       </c>
@@ -7122,7 +7102,7 @@
       </c>
     </row>
     <row r="204" spans="1:11">
-      <c r="B204" s="11"/>
+      <c r="B204" s="12"/>
       <c r="H204" t="s">
         <v>92</v>
       </c>
@@ -7257,7 +7237,6 @@
       </c>
     </row>
     <row r="213" spans="2:11">
-      <c r="B213" s="12"/>
       <c r="H213" t="s">
         <v>92</v>
       </c>
@@ -7272,7 +7251,6 @@
       </c>
     </row>
     <row r="214" spans="2:11">
-      <c r="B214" s="12"/>
       <c r="H214" t="s">
         <v>92</v>
       </c>
@@ -12611,7 +12589,7 @@
         <v>80915325</v>
       </c>
       <c r="J595" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K595" s="6">
         <v>80915325</v>
@@ -12625,7 +12603,7 @@
         <v>80915326</v>
       </c>
       <c r="J596" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="K596" s="6">
         <v>80915326</v>
@@ -12633,13 +12611,13 @@
     </row>
     <row r="597" spans="8:11">
       <c r="H597" s="7" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="I597" s="6">
         <v>80953015</v>
       </c>
       <c r="J597" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="K597" s="6">
         <v>80953015</v>
@@ -12647,13 +12625,13 @@
     </row>
     <row r="598" spans="8:11">
       <c r="H598" s="7" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="I598" s="6">
         <v>80953016</v>
       </c>
       <c r="J598" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="K598" s="6">
         <v>80953016</v>
@@ -12681,7 +12659,7 @@
         <v>81638306</v>
       </c>
       <c r="J600" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K600" s="6">
         <v>81638306</v>
@@ -12689,13 +12667,13 @@
     </row>
     <row r="601" spans="8:11">
       <c r="H601" s="7" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="I601" s="6">
         <v>81918457</v>
       </c>
       <c r="J601" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="K601" s="6">
         <v>81918457</v>
@@ -12709,7 +12687,7 @@
         <v>81538523</v>
       </c>
       <c r="J602" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K602" s="6">
         <v>81538523</v>
@@ -12723,7 +12701,7 @@
         <v>79040263</v>
       </c>
       <c r="J603" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="K603" s="6">
         <v>79040263</v>
@@ -12737,7 +12715,7 @@
         <v>79475749</v>
       </c>
       <c r="J604" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="K604" s="6">
         <v>79475749</v>
@@ -12751,7 +12729,7 @@
         <v>79944232</v>
       </c>
       <c r="J605" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="K605" s="6">
         <v>79944232</v>
@@ -12765,7 +12743,7 @@
         <v>80460979</v>
       </c>
       <c r="J606" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="K606" s="6">
         <v>80460979</v>
@@ -12779,7 +12757,7 @@
         <v>81340922</v>
       </c>
       <c r="J607" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="K607" s="6">
         <v>81340922</v>
@@ -12787,7 +12765,7 @@
     </row>
     <row r="608" spans="8:11">
       <c r="H608" s="7" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="I608" s="6">
         <v>38157908</v>
@@ -12801,7 +12779,7 @@
     </row>
     <row r="609" spans="8:11">
       <c r="H609" s="7" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="I609" s="6">
         <v>41662266</v>
@@ -12821,7 +12799,7 @@
         <v>81988924</v>
       </c>
       <c r="J610" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="K610" s="6">
         <v>81988924</v>
@@ -12835,7 +12813,7 @@
         <v>82014131</v>
       </c>
       <c r="J611" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="K611" s="6">
         <v>82014131</v>
@@ -12848,16 +12826,16 @@
     </sortState>
   </autoFilter>
   <mergeCells count="1">
-    <mergeCell ref="A203:C203"/>
+    <mergeCell ref="A201:C201"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A80:A200 A205:A1048576 A1:A58">
+  <conditionalFormatting sqref="A78:A198 A203:A1048576 A1:A56">
     <cfRule type="duplicateValues" dxfId="8" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A202:A1048576 A1:A63 A67:A200">
+  <conditionalFormatting sqref="A200:A1048576 A1:A61 A65:A198">
     <cfRule type="duplicateValues" dxfId="7" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A205:A1048576 A1:A63 A67:A200">
+  <conditionalFormatting sqref="A203:A1048576 A1:A61 A65:A198">
     <cfRule type="duplicateValues" dxfId="6" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
@@ -12866,11 +12844,11 @@
   <conditionalFormatting sqref="K595:K611">
     <cfRule type="duplicateValues" dxfId="4" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A64:A65">
+  <conditionalFormatting sqref="A62:A63">
     <cfRule type="duplicateValues" dxfId="3" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A66">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="A64">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -13060,10 +13038,10 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A26:A27 A14:A24">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A25">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/이슈제품.xlsx
+++ b/data/이슈제품.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1628" uniqueCount="670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="671">
   <si>
     <t>오아디머무드등-화이트</t>
   </si>
@@ -2072,6 +2072,10 @@
   </si>
   <si>
     <t>협의, 재고 부족</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>협의, 11/4 입고예정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2198,7 +2202,227 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="31">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -4051,6 +4275,15 @@
       </c>
     </row>
     <row r="65" spans="1:11">
+      <c r="A65">
+        <v>5332789</v>
+      </c>
+      <c r="B65" t="s">
+        <v>345</v>
+      </c>
+      <c r="C65" t="s">
+        <v>670</v>
+      </c>
       <c r="H65" t="s">
         <v>94</v>
       </c>
@@ -4065,6 +4298,15 @@
       </c>
     </row>
     <row r="66" spans="1:11">
+      <c r="A66">
+        <v>51016959</v>
+      </c>
+      <c r="B66" t="s">
+        <v>346</v>
+      </c>
+      <c r="C66" t="s">
+        <v>670</v>
+      </c>
       <c r="H66" t="s">
         <v>94</v>
       </c>
@@ -12830,25 +13072,28 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A78:A198 A203:A1048576 A1:A56">
-    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A200:A1048576 A1:A61 A65:A198">
-    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A203:A1048576 A1:A61 A65:A198">
-    <cfRule type="duplicateValues" dxfId="6" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K595:K611">
-    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A62:A63">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -13038,10 +13283,10 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A26:A27 A14:A24">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A25">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/이슈제품.xlsx
+++ b/data/이슈제품.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1630" uniqueCount="670">
   <si>
     <t>오아디머무드등-화이트</t>
   </si>
@@ -1983,10 +1983,6 @@
   </si>
   <si>
     <t>입고X, 11월 초</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>협의, 10/23 예정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2083,7 +2079,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2202,217 +2198,7 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="31">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="10">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2790,7 +2576,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K611"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37.875" bestFit="1" customWidth="1"/>
@@ -2802,7 +2588,7 @@
     <col min="11" max="12" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>23</v>
       </c>
@@ -2825,15 +2611,15 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>27056005</v>
+        <v>4152606</v>
       </c>
       <c r="B2" t="s">
-        <v>329</v>
+        <v>222</v>
       </c>
       <c r="C2" t="s">
-        <v>644</v>
+        <v>628</v>
       </c>
       <c r="H2" t="s">
         <v>29</v>
@@ -2848,15 +2634,15 @@
         <v>3636925</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>4152606</v>
+        <v>12263239</v>
       </c>
       <c r="B3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C3" t="s">
-        <v>628</v>
+        <v>619</v>
       </c>
       <c r="H3" t="s">
         <v>29</v>
@@ -2871,12 +2657,12 @@
         <v>3636926</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>12263239</v>
+        <v>68880617</v>
       </c>
       <c r="B4" t="s">
-        <v>206</v>
+        <v>622</v>
       </c>
       <c r="C4" t="s">
         <v>619</v>
@@ -2894,15 +2680,15 @@
         <v>3636927</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>68880617</v>
+        <v>65933937</v>
       </c>
       <c r="B5" t="s">
-        <v>622</v>
+        <v>499</v>
       </c>
       <c r="C5" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="H5" t="s">
         <v>29</v>
@@ -2917,15 +2703,15 @@
         <v>39415252</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>65933937</v>
+        <v>76375597</v>
       </c>
       <c r="B6" t="s">
-        <v>499</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>631</v>
+        <v>22</v>
       </c>
       <c r="H6" t="s">
         <v>29</v>
@@ -2940,15 +2726,15 @@
         <v>19213859</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>76375597</v>
+        <v>60015061</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="H7" t="s">
         <v>29</v>
@@ -2963,15 +2749,15 @@
         <v>20342327</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>60015061</v>
+        <v>50725354</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>207</v>
       </c>
       <c r="C8" t="s">
-        <v>1</v>
+        <v>618</v>
       </c>
       <c r="H8" t="s">
         <v>29</v>
@@ -2986,15 +2772,15 @@
         <v>13004238</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>50725354</v>
+        <v>50153946</v>
       </c>
       <c r="B9" t="s">
-        <v>207</v>
+        <v>114</v>
       </c>
       <c r="C9" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="H9" t="s">
         <v>29</v>
@@ -3009,15 +2795,15 @@
         <v>20341619</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>50153946</v>
+        <v>75741354</v>
       </c>
       <c r="B10" t="s">
-        <v>114</v>
+        <v>601</v>
       </c>
       <c r="C10" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H10" t="s">
         <v>29</v>
@@ -3032,15 +2818,15 @@
         <v>11092035</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>75741354</v>
+        <v>15414324</v>
       </c>
       <c r="B11" t="s">
-        <v>601</v>
+        <v>198</v>
       </c>
       <c r="C11" t="s">
-        <v>620</v>
+        <v>644</v>
       </c>
       <c r="H11" t="s">
         <v>29</v>
@@ -3055,15 +2841,15 @@
         <v>40852278</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>15414324</v>
+        <v>75077119</v>
       </c>
       <c r="B12" t="s">
-        <v>198</v>
+        <v>598</v>
       </c>
       <c r="C12" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="H12" t="s">
         <v>29</v>
@@ -3078,15 +2864,15 @@
         <v>29266932</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>75077119</v>
-      </c>
-      <c r="B13" t="s">
-        <v>598</v>
+        <v>51623281</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>624</v>
       </c>
       <c r="C13" t="s">
-        <v>643</v>
+        <v>626</v>
       </c>
       <c r="H13" t="s">
         <v>29</v>
@@ -3101,12 +2887,12 @@
         <v>12586373</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>51623281</v>
+        <v>51989601</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C14" t="s">
         <v>626</v>
@@ -3124,12 +2910,12 @@
         <v>11055651</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>51989601</v>
+        <v>11192166</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>625</v>
+        <v>166</v>
       </c>
       <c r="C15" t="s">
         <v>626</v>
@@ -3147,12 +2933,12 @@
         <v>38659485</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>11192166</v>
+        <v>15812678</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="C16" t="s">
         <v>626</v>
@@ -3170,12 +2956,12 @@
         <v>9567647</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>15812678</v>
+        <v>12091621</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C17" t="s">
         <v>626</v>
@@ -3193,12 +2979,12 @@
         <v>40180424</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>12091621</v>
+        <v>12143584</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="C18" t="s">
         <v>626</v>
@@ -3216,12 +3002,12 @@
         <v>39228155</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>12143584</v>
+        <v>11192167</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C19" t="s">
         <v>626</v>
@@ -3239,12 +3025,12 @@
         <v>38407975</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>11192167</v>
+        <v>12143581</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C20" t="s">
         <v>626</v>
@@ -3262,12 +3048,12 @@
         <v>38545387</v>
       </c>
     </row>
-    <row r="21" spans="1:11" s="3" customFormat="1">
+    <row r="21" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>12143581</v>
+        <v>11192165</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C21" t="s">
         <v>626</v>
@@ -3285,12 +3071,12 @@
         <v>18816827</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>11192165</v>
+        <v>11192163</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C22" t="s">
         <v>626</v>
@@ -3308,12 +3094,12 @@
         <v>39278162</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>11192163</v>
+        <v>11291291</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="C23" t="s">
         <v>626</v>
@@ -3331,12 +3117,12 @@
         <v>13100374</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>11291291</v>
+        <v>16171214</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C24" t="s">
         <v>626</v>
@@ -3354,12 +3140,12 @@
         <v>10855225</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>16171214</v>
+        <v>12218847</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C25" t="s">
         <v>626</v>
@@ -3377,12 +3163,12 @@
         <v>38490171</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>12218847</v>
+        <v>15838517</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C26" t="s">
         <v>626</v>
@@ -3400,12 +3186,12 @@
         <v>38490170</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>15838517</v>
+        <v>12673238</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C27" t="s">
         <v>626</v>
@@ -3423,12 +3209,12 @@
         <v>38417027</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>12673238</v>
+        <v>37790051</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="C28" t="s">
         <v>626</v>
@@ -3446,12 +3232,12 @@
         <v>13099542</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>37790051</v>
+        <v>37594934</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="C29" t="s">
         <v>626</v>
@@ -3469,12 +3255,12 @@
         <v>10324264</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>37594934</v>
+        <v>15702671</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="C30" t="s">
         <v>626</v>
@@ -3492,12 +3278,12 @@
         <v>39229235</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>15702671</v>
+        <v>39071990</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="C31" t="s">
         <v>626</v>
@@ -3515,12 +3301,12 @@
         <v>12775098</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>39071990</v>
+        <v>52204284</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>160</v>
+        <v>91</v>
       </c>
       <c r="C32" t="s">
         <v>626</v>
@@ -3538,12 +3324,12 @@
         <v>12775097</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>52204284</v>
+        <v>39006854</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>91</v>
+        <v>163</v>
       </c>
       <c r="C33" t="s">
         <v>626</v>
@@ -3561,12 +3347,12 @@
         <v>12775096</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>39006854</v>
+        <v>39006857</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C34" t="s">
         <v>626</v>
@@ -3584,12 +3370,12 @@
         <v>13151160</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>39006857</v>
+        <v>39006855</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C35" t="s">
         <v>626</v>
@@ -3607,12 +3393,12 @@
         <v>13151158</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>39006855</v>
+        <v>51883980</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>162</v>
+        <v>361</v>
       </c>
       <c r="C36" t="s">
         <v>626</v>
@@ -3630,12 +3416,12 @@
         <v>35403063</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>51883980</v>
+        <v>52578670</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="C37" t="s">
         <v>626</v>
@@ -3653,12 +3439,12 @@
         <v>13473750</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>52578670</v>
+        <v>52155531</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>366</v>
+        <v>93</v>
       </c>
       <c r="C38" t="s">
         <v>626</v>
@@ -3676,12 +3462,12 @@
         <v>17014694</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>52155531</v>
+        <v>15831347</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>93</v>
+        <v>141</v>
       </c>
       <c r="C39" t="s">
         <v>626</v>
@@ -3699,12 +3485,12 @@
         <v>17014693</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>15831347</v>
+        <v>32548061</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="C40" t="s">
         <v>626</v>
@@ -3722,12 +3508,12 @@
         <v>13101218</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>32548061</v>
+        <v>35876282</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C41" t="s">
         <v>626</v>
@@ -3745,12 +3531,12 @@
         <v>13101217</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>35876282</v>
+        <v>16805855</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="C42" t="s">
         <v>626</v>
@@ -3768,12 +3554,12 @@
         <v>16981939</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>16805855</v>
+        <v>55381383</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>144</v>
+        <v>383</v>
       </c>
       <c r="C43" t="s">
         <v>626</v>
@@ -3791,12 +3577,12 @@
         <v>12846219</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>55381383</v>
+        <v>55449180</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C44" t="s">
         <v>626</v>
@@ -3814,12 +3600,12 @@
         <v>17398556</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>55449180</v>
+        <v>55384739</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C45" t="s">
         <v>626</v>
@@ -3837,12 +3623,12 @@
         <v>16972627</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>55384739</v>
+        <v>55389336</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>387</v>
+        <v>623</v>
       </c>
       <c r="C46" t="s">
         <v>626</v>
@@ -3860,12 +3646,12 @@
         <v>12846215</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>55389336</v>
+        <v>55609278</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>623</v>
+        <v>384</v>
       </c>
       <c r="C47" t="s">
         <v>626</v>
@@ -3883,15 +3669,15 @@
         <v>39663616</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>55609278</v>
+        <v>71042279</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>384</v>
+        <v>565</v>
       </c>
       <c r="C48" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H48" t="s">
         <v>58</v>
@@ -3906,15 +3692,15 @@
         <v>37843037</v>
       </c>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>71042279</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>565</v>
+        <v>67630646</v>
+      </c>
+      <c r="B49" t="s">
+        <v>526</v>
       </c>
       <c r="C49" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="H49" t="s">
         <v>58</v>
@@ -3929,12 +3715,12 @@
         <v>12465755</v>
       </c>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>67630646</v>
+        <v>64971361</v>
       </c>
       <c r="B50" t="s">
-        <v>526</v>
+        <v>486</v>
       </c>
       <c r="C50" t="s">
         <v>630</v>
@@ -3952,12 +3738,12 @@
         <v>11671481</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>64971361</v>
+        <v>62421723</v>
       </c>
       <c r="B51" t="s">
-        <v>486</v>
+        <v>454</v>
       </c>
       <c r="C51" t="s">
         <v>630</v>
@@ -3975,12 +3761,12 @@
         <v>12685386</v>
       </c>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>62421723</v>
+        <v>62374813</v>
       </c>
       <c r="B52" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C52" t="s">
         <v>630</v>
@@ -3998,12 +3784,12 @@
         <v>12674974</v>
       </c>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>62374813</v>
+        <v>68462854</v>
       </c>
       <c r="B53" t="s">
-        <v>455</v>
+        <v>532</v>
       </c>
       <c r="C53" t="s">
         <v>630</v>
@@ -4021,12 +3807,12 @@
         <v>12674973</v>
       </c>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>68462854</v>
+        <v>64114088</v>
       </c>
       <c r="B54" t="s">
-        <v>532</v>
+        <v>469</v>
       </c>
       <c r="C54" t="s">
         <v>630</v>
@@ -4044,12 +3830,12 @@
         <v>27515992</v>
       </c>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>64114088</v>
+        <v>19213859</v>
       </c>
       <c r="B55" t="s">
-        <v>469</v>
+        <v>34</v>
       </c>
       <c r="C55" t="s">
         <v>630</v>
@@ -4067,12 +3853,12 @@
         <v>18928667</v>
       </c>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>19213859</v>
+        <v>13004238</v>
       </c>
       <c r="B56" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C56" t="s">
         <v>630</v>
@@ -4090,15 +3876,15 @@
         <v>14218803</v>
       </c>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>13004238</v>
+        <v>11229298</v>
       </c>
       <c r="B57" t="s">
-        <v>36</v>
+        <v>174</v>
       </c>
       <c r="C57" t="s">
-        <v>630</v>
+        <v>644</v>
       </c>
       <c r="H57" t="s">
         <v>58</v>
@@ -4113,14 +3899,14 @@
         <v>14218802</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:11" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>11229298</v>
+        <v>37161537</v>
       </c>
       <c r="B58" t="s">
-        <v>174</v>
-      </c>
-      <c r="C58" t="s">
+        <v>288</v>
+      </c>
+      <c r="C58" s="5" t="s">
         <v>645</v>
       </c>
       <c r="H58" t="s">
@@ -4136,14 +3922,14 @@
         <v>14473529</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="82.5">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>37161537</v>
+        <v>13745117</v>
       </c>
       <c r="B59" t="s">
-        <v>288</v>
-      </c>
-      <c r="C59" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="C59" t="s">
         <v>646</v>
       </c>
       <c r="H59" t="s">
@@ -4159,15 +3945,15 @@
         <v>25512595</v>
       </c>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>13745117</v>
+        <v>73226633</v>
       </c>
       <c r="B60" t="s">
-        <v>197</v>
+        <v>573</v>
       </c>
       <c r="C60" t="s">
-        <v>647</v>
+        <v>666</v>
       </c>
       <c r="H60" t="s">
         <v>58</v>
@@ -4182,12 +3968,12 @@
         <v>25433097</v>
       </c>
     </row>
-    <row r="61" spans="1:11">
-      <c r="A61">
-        <v>73226633</v>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A61" s="6">
+        <v>80915325</v>
       </c>
       <c r="B61" t="s">
-        <v>573</v>
+        <v>651</v>
       </c>
       <c r="C61" t="s">
         <v>667</v>
@@ -4205,15 +3991,15 @@
         <v>50012601</v>
       </c>
     </row>
-    <row r="62" spans="1:11">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="6">
-        <v>80915325</v>
+        <v>80915326</v>
       </c>
       <c r="B62" t="s">
         <v>652</v>
       </c>
       <c r="C62" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H62" t="s">
         <v>90</v>
@@ -4228,12 +4014,12 @@
         <v>52204284</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
-      <c r="A63" s="6">
-        <v>80915326</v>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>73893263</v>
       </c>
       <c r="B63" t="s">
-        <v>653</v>
+        <v>15</v>
       </c>
       <c r="C63" t="s">
         <v>668</v>
@@ -4251,12 +4037,12 @@
         <v>52155531</v>
       </c>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>73893263</v>
+        <v>5332789</v>
       </c>
       <c r="B64" t="s">
-        <v>15</v>
+        <v>345</v>
       </c>
       <c r="C64" t="s">
         <v>669</v>
@@ -4274,15 +4060,15 @@
         <v>10814871</v>
       </c>
     </row>
-    <row r="65" spans="1:11">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>5332789</v>
+        <v>51016959</v>
       </c>
       <c r="B65" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C65" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H65" t="s">
         <v>94</v>
@@ -4297,16 +4083,7 @@
         <v>31792560</v>
       </c>
     </row>
-    <row r="66" spans="1:11">
-      <c r="A66">
-        <v>51016959</v>
-      </c>
-      <c r="B66" t="s">
-        <v>346</v>
-      </c>
-      <c r="C66" t="s">
-        <v>670</v>
-      </c>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H66" t="s">
         <v>94</v>
       </c>
@@ -4320,7 +4097,7 @@
         <v>10694343</v>
       </c>
     </row>
-    <row r="67" spans="1:11">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H67" t="s">
         <v>98</v>
       </c>
@@ -4334,7 +4111,7 @@
         <v>43431417</v>
       </c>
     </row>
-    <row r="68" spans="1:11">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H68" t="s">
         <v>98</v>
       </c>
@@ -4348,7 +4125,7 @@
         <v>10978754</v>
       </c>
     </row>
-    <row r="69" spans="1:11">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H69" t="s">
         <v>98</v>
       </c>
@@ -4362,7 +4139,7 @@
         <v>10974363</v>
       </c>
     </row>
-    <row r="70" spans="1:11">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H70" t="s">
         <v>98</v>
       </c>
@@ -4376,7 +4153,7 @@
         <v>39376011</v>
       </c>
     </row>
-    <row r="71" spans="1:11">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H71" t="s">
         <v>98</v>
       </c>
@@ -4390,7 +4167,7 @@
         <v>38310913</v>
       </c>
     </row>
-    <row r="72" spans="1:11">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H72" t="s">
         <v>98</v>
       </c>
@@ -4404,7 +4181,7 @@
         <v>40639939</v>
       </c>
     </row>
-    <row r="73" spans="1:11">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H73" t="s">
         <v>98</v>
       </c>
@@ -4418,7 +4195,7 @@
         <v>44581094</v>
       </c>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H74" t="s">
         <v>98</v>
       </c>
@@ -4432,7 +4209,7 @@
         <v>39270777</v>
       </c>
     </row>
-    <row r="75" spans="1:11">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H75" t="s">
         <v>90</v>
       </c>
@@ -4446,7 +4223,16 @@
         <v>45342904</v>
       </c>
     </row>
-    <row r="76" spans="1:11">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A76" s="8">
+        <v>15826960</v>
+      </c>
+      <c r="B76" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="C76" s="10" t="s">
+        <v>647</v>
+      </c>
       <c r="H76" t="s">
         <v>90</v>
       </c>
@@ -4460,15 +4246,15 @@
         <v>19619417</v>
       </c>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" s="8">
-        <v>15826960</v>
+        <v>58505144</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>236</v>
+        <v>16</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H77" t="s">
         <v>109</v>
@@ -4483,15 +4269,15 @@
         <v>36606823</v>
       </c>
     </row>
-    <row r="78" spans="1:11">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" s="8">
-        <v>58505144</v>
+        <v>61199642</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>16</v>
+        <v>439</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H78" t="s">
         <v>90</v>
@@ -4506,15 +4292,15 @@
         <v>12585217</v>
       </c>
     </row>
-    <row r="79" spans="1:11">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" s="8">
-        <v>61199642</v>
+        <v>64912430</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>439</v>
+        <v>485</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H79" t="s">
         <v>90</v>
@@ -4529,15 +4315,15 @@
         <v>11511332</v>
       </c>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" s="8">
-        <v>64912430</v>
+        <v>10124384</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>485</v>
+        <v>185</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H80" t="s">
         <v>90</v>
@@ -4552,15 +4338,15 @@
         <v>12579597</v>
       </c>
     </row>
-    <row r="81" spans="1:11">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" s="8">
-        <v>10124384</v>
+        <v>10929273</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>185</v>
+        <v>340</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H81" t="s">
         <v>90</v>
@@ -4575,15 +4361,15 @@
         <v>50153946</v>
       </c>
     </row>
-    <row r="82" spans="1:11">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" s="8">
-        <v>10929273</v>
+        <v>10929274</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H82" t="s">
         <v>90</v>
@@ -4598,15 +4384,15 @@
         <v>50723598</v>
       </c>
     </row>
-    <row r="83" spans="1:11">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" s="8">
-        <v>10929274</v>
+        <v>11670520</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>339</v>
+        <v>10</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H83" t="s">
         <v>115</v>
@@ -4621,15 +4407,15 @@
         <v>34464589</v>
       </c>
     </row>
-    <row r="84" spans="1:11">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" s="8">
-        <v>11670520</v>
+        <v>12029130</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>10</v>
+        <v>117</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H84" t="s">
         <v>115</v>
@@ -4644,15 +4430,15 @@
         <v>12029130</v>
       </c>
     </row>
-    <row r="85" spans="1:11">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" s="8">
-        <v>12029130</v>
+        <v>12038103</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>117</v>
+        <v>264</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H85" t="s">
         <v>115</v>
@@ -4667,15 +4453,15 @@
         <v>46962408</v>
       </c>
     </row>
-    <row r="86" spans="1:11">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" s="8">
-        <v>12038103</v>
+        <v>12095120</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H86" t="s">
         <v>115</v>
@@ -4690,15 +4476,15 @@
         <v>11874445</v>
       </c>
     </row>
-    <row r="87" spans="1:11">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" s="8">
-        <v>12095120</v>
+        <v>12481760</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H87" t="s">
         <v>115</v>
@@ -4713,15 +4499,15 @@
         <v>25665354</v>
       </c>
     </row>
-    <row r="88" spans="1:11">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88" s="8">
-        <v>12481760</v>
+        <v>13195957</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>292</v>
+        <v>8</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H88" t="s">
         <v>115</v>
@@ -4736,15 +4522,15 @@
         <v>46550390</v>
       </c>
     </row>
-    <row r="89" spans="1:11">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89" s="8">
-        <v>13195957</v>
+        <v>14299890</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>8</v>
+        <v>177</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H89" t="s">
         <v>115</v>
@@ -4759,15 +4545,15 @@
         <v>45573288</v>
       </c>
     </row>
-    <row r="90" spans="1:11">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90" s="8">
-        <v>14299890</v>
+        <v>14473529</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>177</v>
+        <v>87</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H90" t="s">
         <v>115</v>
@@ -4782,15 +4568,15 @@
         <v>34318450</v>
       </c>
     </row>
-    <row r="91" spans="1:11">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" s="8">
-        <v>14473529</v>
+        <v>15757638</v>
       </c>
       <c r="B91" s="9" t="s">
-        <v>87</v>
+        <v>263</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H91" t="s">
         <v>115</v>
@@ -4805,15 +4591,15 @@
         <v>45701215</v>
       </c>
     </row>
-    <row r="92" spans="1:11">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92" s="8">
-        <v>15757638</v>
+        <v>16806254</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>263</v>
+        <v>317</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H92" t="s">
         <v>115</v>
@@ -4828,15 +4614,15 @@
         <v>15004955</v>
       </c>
     </row>
-    <row r="93" spans="1:11">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" s="8">
-        <v>16806254</v>
+        <v>20341619</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>317</v>
+        <v>37</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H93" t="s">
         <v>115</v>
@@ -4851,15 +4637,15 @@
         <v>25321998</v>
       </c>
     </row>
-    <row r="94" spans="1:11">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94" s="8">
-        <v>20341619</v>
+        <v>22119013</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>37</v>
+        <v>322</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H94" t="s">
         <v>115</v>
@@ -4874,15 +4660,15 @@
         <v>25321996</v>
       </c>
     </row>
-    <row r="95" spans="1:11">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95" s="8">
-        <v>22119013</v>
+        <v>25433097</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>322</v>
+        <v>88</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H95" t="s">
         <v>115</v>
@@ -4897,15 +4683,15 @@
         <v>46191377</v>
       </c>
     </row>
-    <row r="96" spans="1:11">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" s="8">
-        <v>25433097</v>
+        <v>25512595</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H96" t="s">
         <v>115</v>
@@ -4920,15 +4706,15 @@
         <v>45349063</v>
       </c>
     </row>
-    <row r="97" spans="1:11">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" s="8">
-        <v>25512595</v>
+        <v>25665354</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H97" t="s">
         <v>115</v>
@@ -4943,15 +4729,15 @@
         <v>44996967</v>
       </c>
     </row>
-    <row r="98" spans="1:11">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" s="8">
-        <v>25665354</v>
+        <v>29258063</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>119</v>
+        <v>308</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H98" t="s">
         <v>115</v>
@@ -4966,15 +4752,15 @@
         <v>15462869</v>
       </c>
     </row>
-    <row r="99" spans="1:11">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" s="8">
-        <v>29258063</v>
+        <v>29266932</v>
       </c>
       <c r="B99" s="9" t="s">
-        <v>308</v>
+        <v>40</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H99" t="s">
         <v>115</v>
@@ -4989,15 +4775,15 @@
         <v>15462868</v>
       </c>
     </row>
-    <row r="100" spans="1:11">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" s="8">
-        <v>29266932</v>
+        <v>34991467</v>
       </c>
       <c r="B100" s="9" t="s">
-        <v>40</v>
+        <v>279</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H100" t="s">
         <v>115</v>
@@ -5012,15 +4798,15 @@
         <v>46671749</v>
       </c>
     </row>
-    <row r="101" spans="1:11">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="8">
-        <v>34991467</v>
+        <v>35401181</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>279</v>
+        <v>229</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H101" t="s">
         <v>115</v>
@@ -5035,15 +4821,15 @@
         <v>35137369</v>
       </c>
     </row>
-    <row r="102" spans="1:11">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" s="8">
-        <v>35401181</v>
+        <v>36606823</v>
       </c>
       <c r="B102" s="9" t="s">
-        <v>229</v>
+        <v>110</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H102" t="s">
         <v>115</v>
@@ -5058,15 +4844,15 @@
         <v>34320929</v>
       </c>
     </row>
-    <row r="103" spans="1:11">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" s="8">
-        <v>36606823</v>
+        <v>38157908</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>110</v>
+        <v>230</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H103" t="s">
         <v>115</v>
@@ -5081,15 +4867,15 @@
         <v>34320928</v>
       </c>
     </row>
-    <row r="104" spans="1:11">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" s="8">
-        <v>38157908</v>
+        <v>38407975</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>230</v>
+        <v>46</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H104" t="s">
         <v>115</v>
@@ -5104,15 +4890,15 @@
         <v>23200605</v>
       </c>
     </row>
-    <row r="105" spans="1:11">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" s="8">
-        <v>38407975</v>
+        <v>38659485</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C105" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H105" t="s">
         <v>115</v>
@@ -5127,15 +4913,15 @@
         <v>23200603</v>
       </c>
     </row>
-    <row r="106" spans="1:11">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" s="8">
-        <v>38659485</v>
+        <v>39239709</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>43</v>
+        <v>325</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H106" t="s">
         <v>115</v>
@@ -5150,15 +4936,15 @@
         <v>43571361</v>
       </c>
     </row>
-    <row r="107" spans="1:11">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" s="8">
-        <v>39239709</v>
+        <v>39944753</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>325</v>
+        <v>298</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H107" t="s">
         <v>115</v>
@@ -5173,15 +4959,15 @@
         <v>43571360</v>
       </c>
     </row>
-    <row r="108" spans="1:11">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" s="8">
-        <v>39944753</v>
+        <v>40180424</v>
       </c>
       <c r="B108" s="9" t="s">
-        <v>298</v>
+        <v>9</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H108" t="s">
         <v>115</v>
@@ -5196,15 +4982,15 @@
         <v>34330469</v>
       </c>
     </row>
-    <row r="109" spans="1:11">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" s="8">
-        <v>40180424</v>
+        <v>43571361</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>9</v>
+        <v>135</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H109" t="s">
         <v>115</v>
@@ -5219,15 +5005,15 @@
         <v>34331612</v>
       </c>
     </row>
-    <row r="110" spans="1:11">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110" s="8">
-        <v>43571361</v>
+        <v>46801171</v>
       </c>
       <c r="B110" s="9" t="s">
-        <v>135</v>
+        <v>265</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H110" t="s">
         <v>115</v>
@@ -5242,15 +5028,15 @@
         <v>34352694</v>
       </c>
     </row>
-    <row r="111" spans="1:11">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111" s="8">
-        <v>46801171</v>
+        <v>48449253</v>
       </c>
       <c r="B111" s="9" t="s">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H111" t="s">
         <v>29</v>
@@ -5265,15 +5051,15 @@
         <v>39063227</v>
       </c>
     </row>
-    <row r="112" spans="1:11">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" s="8">
-        <v>48449253</v>
+        <v>53967042</v>
       </c>
       <c r="B112" s="9" t="s">
-        <v>299</v>
+        <v>377</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H112" t="s">
         <v>56</v>
@@ -5288,15 +5074,15 @@
         <v>15831347</v>
       </c>
     </row>
-    <row r="113" spans="1:11">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113" s="8">
-        <v>53967042</v>
+        <v>55275736</v>
       </c>
       <c r="B113" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H113" t="s">
         <v>56</v>
@@ -5311,15 +5097,15 @@
         <v>12091621</v>
       </c>
     </row>
-    <row r="114" spans="1:11">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114" s="8">
-        <v>55275736</v>
+        <v>59759466</v>
       </c>
       <c r="B114" s="9" t="s">
-        <v>378</v>
+        <v>412</v>
       </c>
       <c r="C114" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H114" t="s">
         <v>143</v>
@@ -5334,15 +5120,15 @@
         <v>16805855</v>
       </c>
     </row>
-    <row r="115" spans="1:11">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115" s="8">
-        <v>59759466</v>
+        <v>60024864</v>
       </c>
       <c r="B115" s="9" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="C115" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H115" t="s">
         <v>56</v>
@@ -5357,15 +5143,15 @@
         <v>15812678</v>
       </c>
     </row>
-    <row r="116" spans="1:11">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116" s="8">
-        <v>60024864</v>
+        <v>60025950</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C116" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H116" t="s">
         <v>56</v>
@@ -5380,15 +5166,15 @@
         <v>12143581</v>
       </c>
     </row>
-    <row r="117" spans="1:11">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117" s="8">
-        <v>60025950</v>
+        <v>60541171</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="C117" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H117" t="s">
         <v>56</v>
@@ -5403,15 +5189,15 @@
         <v>11192165</v>
       </c>
     </row>
-    <row r="118" spans="1:11">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A118" s="8">
-        <v>60541171</v>
+        <v>60543356</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C118" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H118" t="s">
         <v>56</v>
@@ -5426,15 +5212,15 @@
         <v>11192163</v>
       </c>
     </row>
-    <row r="119" spans="1:11">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119" s="8">
-        <v>60543356</v>
+        <v>60615380</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H119" t="s">
         <v>56</v>
@@ -5449,15 +5235,15 @@
         <v>12143584</v>
       </c>
     </row>
-    <row r="120" spans="1:11">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A120" s="8">
-        <v>60615380</v>
+        <v>61760291</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H120" t="s">
         <v>56</v>
@@ -5472,15 +5258,15 @@
         <v>11192167</v>
       </c>
     </row>
-    <row r="121" spans="1:11">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A121" s="8">
-        <v>61760291</v>
+        <v>62385013</v>
       </c>
       <c r="B121" s="9" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H121" t="s">
         <v>90</v>
@@ -5495,15 +5281,15 @@
         <v>12673238</v>
       </c>
     </row>
-    <row r="122" spans="1:11">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A122" s="8">
-        <v>62385013</v>
+        <v>64606094</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>452</v>
+        <v>474</v>
       </c>
       <c r="C122" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H122" t="s">
         <v>152</v>
@@ -5518,15 +5304,15 @@
         <v>15838517</v>
       </c>
     </row>
-    <row r="123" spans="1:11">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A123" s="8">
-        <v>64606094</v>
+        <v>64846264</v>
       </c>
       <c r="B123" s="9" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H123" t="s">
         <v>152</v>
@@ -5541,15 +5327,15 @@
         <v>12218847</v>
       </c>
     </row>
-    <row r="124" spans="1:11">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A124" s="8">
-        <v>64846264</v>
+        <v>65566541</v>
       </c>
       <c r="B124" s="9" t="s">
-        <v>479</v>
+        <v>492</v>
       </c>
       <c r="C124" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H124" t="s">
         <v>152</v>
@@ -5564,15 +5350,15 @@
         <v>16171214</v>
       </c>
     </row>
-    <row r="125" spans="1:11">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A125" s="8">
-        <v>65566541</v>
+        <v>66607099</v>
       </c>
       <c r="B125" s="9" t="s">
-        <v>492</v>
+        <v>512</v>
       </c>
       <c r="C125" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H125" t="s">
         <v>152</v>
@@ -5587,15 +5373,15 @@
         <v>11291291</v>
       </c>
     </row>
-    <row r="126" spans="1:11">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A126" s="8">
-        <v>66607099</v>
+        <v>59924956</v>
       </c>
       <c r="B126" s="9" t="s">
-        <v>512</v>
+        <v>417</v>
       </c>
       <c r="C126" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H126" t="s">
         <v>58</v>
@@ -5610,14 +5396,14 @@
         <v>14134779</v>
       </c>
     </row>
-    <row r="127" spans="1:11">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A127" s="8">
-        <v>59924956</v>
+        <v>17014694</v>
       </c>
       <c r="B127" s="9" t="s">
-        <v>417</v>
-      </c>
-      <c r="C127" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C127" s="9" t="s">
         <v>648</v>
       </c>
       <c r="H127" t="s">
@@ -5633,15 +5419,15 @@
         <v>14134778</v>
       </c>
     </row>
-    <row r="128" spans="1:11">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A128" s="8">
-        <v>17014694</v>
+        <v>17014693</v>
       </c>
       <c r="B128" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C128" s="9" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H128" t="s">
         <v>90</v>
@@ -5656,14 +5442,14 @@
         <v>37790051</v>
       </c>
     </row>
-    <row r="129" spans="1:11">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A129" s="8">
-        <v>17014693</v>
+        <v>36811022</v>
       </c>
       <c r="B129" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C129" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="C129" s="10" t="s">
         <v>649</v>
       </c>
       <c r="H129" t="s">
@@ -5679,15 +5465,15 @@
         <v>39071990</v>
       </c>
     </row>
-    <row r="130" spans="1:11">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A130" s="8">
-        <v>36811022</v>
+        <v>36811023</v>
       </c>
       <c r="B130" s="9" t="s">
-        <v>284</v>
+        <v>0</v>
       </c>
       <c r="C130" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H130" t="s">
         <v>29</v>
@@ -5702,15 +5488,15 @@
         <v>39006857</v>
       </c>
     </row>
-    <row r="131" spans="1:11">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131" s="8">
-        <v>36811023</v>
+        <v>60023938</v>
       </c>
       <c r="B131" s="9" t="s">
-        <v>0</v>
+        <v>419</v>
       </c>
       <c r="C131" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H131" t="s">
         <v>29</v>
@@ -5725,15 +5511,15 @@
         <v>39006855</v>
       </c>
     </row>
-    <row r="132" spans="1:11">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A132" s="8">
-        <v>60023938</v>
+        <v>61929494</v>
       </c>
       <c r="B132" s="9" t="s">
-        <v>419</v>
+        <v>445</v>
       </c>
       <c r="C132" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H132" t="s">
         <v>29</v>
@@ -5748,15 +5534,15 @@
         <v>39006854</v>
       </c>
     </row>
-    <row r="133" spans="1:11">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133" s="8">
-        <v>61929494</v>
+        <v>66417803</v>
       </c>
       <c r="B133" s="9" t="s">
-        <v>445</v>
+        <v>503</v>
       </c>
       <c r="C133" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H133" t="s">
         <v>58</v>
@@ -5771,15 +5557,15 @@
         <v>12434130</v>
       </c>
     </row>
-    <row r="134" spans="1:11">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A134" s="8">
-        <v>66417803</v>
+        <v>20342327</v>
       </c>
       <c r="B134" s="9" t="s">
-        <v>503</v>
+        <v>35</v>
       </c>
       <c r="C134" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H134" t="s">
         <v>58</v>
@@ -5794,15 +5580,15 @@
         <v>11671480</v>
       </c>
     </row>
-    <row r="135" spans="1:11">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135" s="8">
-        <v>20342327</v>
+        <v>12586373</v>
       </c>
       <c r="B135" s="9" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C135" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H135" t="s">
         <v>56</v>
@@ -5817,15 +5603,15 @@
         <v>11192166</v>
       </c>
     </row>
-    <row r="136" spans="1:11">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136" s="8">
-        <v>12586373</v>
+        <v>11055651</v>
       </c>
       <c r="B136" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C136" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H136" t="s">
         <v>90</v>
@@ -5840,15 +5626,15 @@
         <v>37594934</v>
       </c>
     </row>
-    <row r="137" spans="1:11">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137" s="8">
-        <v>11055651</v>
+        <v>18816827</v>
       </c>
       <c r="B137" s="9" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C137" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H137" t="s">
         <v>29</v>
@@ -5863,15 +5649,15 @@
         <v>32548061</v>
       </c>
     </row>
-    <row r="138" spans="1:11">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138" s="8">
-        <v>18816827</v>
+        <v>39229235</v>
       </c>
       <c r="B138" s="9" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="C138" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H138" t="s">
         <v>58</v>
@@ -5886,15 +5672,15 @@
         <v>32711387</v>
       </c>
     </row>
-    <row r="139" spans="1:11">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139" s="8">
-        <v>39229235</v>
+        <v>13151160</v>
       </c>
       <c r="B139" s="9" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C139" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H139" t="s">
         <v>58</v>
@@ -5909,15 +5695,15 @@
         <v>32710937</v>
       </c>
     </row>
-    <row r="140" spans="1:11">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A140" s="8">
-        <v>13151160</v>
+        <v>13151158</v>
       </c>
       <c r="B140" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C140" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H140" t="s">
         <v>171</v>
@@ -5932,15 +5718,15 @@
         <v>35876282</v>
       </c>
     </row>
-    <row r="141" spans="1:11">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A141" s="8">
-        <v>13151158</v>
+        <v>10978754</v>
       </c>
       <c r="B141" s="9" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="C141" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H141" t="s">
         <v>90</v>
@@ -5955,15 +5741,15 @@
         <v>15702671</v>
       </c>
     </row>
-    <row r="142" spans="1:11">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A142" s="8">
-        <v>10978754</v>
+        <v>19619417</v>
       </c>
       <c r="B142" s="9" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="C142" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H142" t="s">
         <v>171</v>
@@ -5978,15 +5764,15 @@
         <v>11229298</v>
       </c>
     </row>
-    <row r="143" spans="1:11">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A143" s="8">
-        <v>19619417</v>
+        <v>39063227</v>
       </c>
       <c r="B143" s="9" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="C143" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H143" t="s">
         <v>171</v>
@@ -6001,15 +5787,15 @@
         <v>50709616</v>
       </c>
     </row>
-    <row r="144" spans="1:11">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A144" s="8">
-        <v>39063227</v>
+        <v>46995055</v>
       </c>
       <c r="B144" s="9" t="s">
-        <v>140</v>
+        <v>186</v>
       </c>
       <c r="C144" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H144" t="s">
         <v>171</v>
@@ -6024,15 +5810,15 @@
         <v>37034524</v>
       </c>
     </row>
-    <row r="145" spans="1:11">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A145" s="8">
-        <v>46995055</v>
+        <v>11744316</v>
       </c>
       <c r="B145" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C145" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H145" t="s">
         <v>171</v>
@@ -6047,15 +5833,15 @@
         <v>14299890</v>
       </c>
     </row>
-    <row r="146" spans="1:11">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A146" s="8">
-        <v>11744316</v>
+        <v>13069194</v>
       </c>
       <c r="B146" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C146" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H146" t="s">
         <v>171</v>
@@ -6070,15 +5856,15 @@
         <v>13195811</v>
       </c>
     </row>
-    <row r="147" spans="1:11">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A147" s="8">
-        <v>13069194</v>
+        <v>4125381</v>
       </c>
       <c r="B147" s="9" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C147" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H147" t="s">
         <v>171</v>
@@ -6093,15 +5879,15 @@
         <v>36608029</v>
       </c>
     </row>
-    <row r="148" spans="1:11">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A148" s="8">
-        <v>4125381</v>
+        <v>42839047</v>
       </c>
       <c r="B148" s="9" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="C148" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H148" t="s">
         <v>171</v>
@@ -6116,15 +5902,15 @@
         <v>13195957</v>
       </c>
     </row>
-    <row r="149" spans="1:11">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A149" s="8">
-        <v>42839047</v>
+        <v>4152612</v>
       </c>
       <c r="B149" s="9" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C149" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H149" t="s">
         <v>171</v>
@@ -6139,15 +5925,15 @@
         <v>10121189</v>
       </c>
     </row>
-    <row r="150" spans="1:11">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A150" s="8">
-        <v>4152612</v>
+        <v>4152610</v>
       </c>
       <c r="B150" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C150" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H150" t="s">
         <v>171</v>
@@ -6162,15 +5948,15 @@
         <v>8122806</v>
       </c>
     </row>
-    <row r="151" spans="1:11">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A151" s="8">
-        <v>4152610</v>
+        <v>34098917</v>
       </c>
       <c r="B151" s="9" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C151" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H151" t="s">
         <v>171</v>
@@ -6185,15 +5971,15 @@
         <v>48477550</v>
       </c>
     </row>
-    <row r="152" spans="1:11">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A152" s="8">
-        <v>34098917</v>
+        <v>49985232</v>
       </c>
       <c r="B152" s="9" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C152" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H152" t="s">
         <v>171</v>
@@ -6208,15 +5994,15 @@
         <v>11288089</v>
       </c>
     </row>
-    <row r="153" spans="1:11">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A153" s="8">
-        <v>49985232</v>
+        <v>50155408</v>
       </c>
       <c r="B153" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C153" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H153" t="s">
         <v>171</v>
@@ -6231,15 +6017,15 @@
         <v>11104533</v>
       </c>
     </row>
-    <row r="154" spans="1:11">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A154" s="8">
-        <v>50155408</v>
+        <v>41662266</v>
       </c>
       <c r="B154" s="9" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C154" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H154" t="s">
         <v>171</v>
@@ -6254,15 +6040,15 @@
         <v>10124384</v>
       </c>
     </row>
-    <row r="155" spans="1:11">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A155" s="8">
-        <v>41662266</v>
+        <v>13573385</v>
       </c>
       <c r="B155" s="9" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C155" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H155" t="s">
         <v>171</v>
@@ -6277,15 +6063,15 @@
         <v>46995055</v>
       </c>
     </row>
-    <row r="156" spans="1:11">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A156" s="8">
-        <v>13573385</v>
+        <v>42871700</v>
       </c>
       <c r="B156" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C156" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H156" t="s">
         <v>171</v>
@@ -6300,15 +6086,15 @@
         <v>11744316</v>
       </c>
     </row>
-    <row r="157" spans="1:11">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A157" s="8">
-        <v>42871700</v>
+        <v>39257536</v>
       </c>
       <c r="B157" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C157" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H157" t="s">
         <v>171</v>
@@ -6323,15 +6109,15 @@
         <v>13069194</v>
       </c>
     </row>
-    <row r="158" spans="1:11">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A158" s="8">
-        <v>39257536</v>
+        <v>37424126</v>
       </c>
       <c r="B158" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C158" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H158" t="s">
         <v>171</v>
@@ -6346,15 +6132,15 @@
         <v>19365568</v>
       </c>
     </row>
-    <row r="159" spans="1:11">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A159" s="8">
-        <v>37424126</v>
+        <v>36802614</v>
       </c>
       <c r="B159" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C159" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H159" t="s">
         <v>171</v>
@@ -6369,15 +6155,15 @@
         <v>47861038</v>
       </c>
     </row>
-    <row r="160" spans="1:11">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A160" s="8">
-        <v>36802614</v>
+        <v>36577826</v>
       </c>
       <c r="B160" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C160" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H160" t="s">
         <v>171</v>
@@ -6392,15 +6178,15 @@
         <v>43252471</v>
       </c>
     </row>
-    <row r="161" spans="1:11">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A161" s="8">
-        <v>36577826</v>
+        <v>26196255</v>
       </c>
       <c r="B161" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C161" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H161" t="s">
         <v>171</v>
@@ -6415,15 +6201,15 @@
         <v>4125381</v>
       </c>
     </row>
-    <row r="162" spans="1:11">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A162" s="8">
-        <v>26196255</v>
+        <v>26019234</v>
       </c>
       <c r="B162" s="9" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="C162" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H162" t="s">
         <v>171</v>
@@ -6438,15 +6224,15 @@
         <v>38183281</v>
       </c>
     </row>
-    <row r="163" spans="1:11">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A163" s="8">
-        <v>26019234</v>
+        <v>25411238</v>
       </c>
       <c r="B163" s="9" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C163" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H163" t="s">
         <v>171</v>
@@ -6461,15 +6247,15 @@
         <v>14107560</v>
       </c>
     </row>
-    <row r="164" spans="1:11">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A164" s="8">
-        <v>25411238</v>
+        <v>26500515</v>
       </c>
       <c r="B164" s="9" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C164" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H164" t="s">
         <v>171</v>
@@ -6484,15 +6270,15 @@
         <v>44916947</v>
       </c>
     </row>
-    <row r="165" spans="1:11">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A165" s="8">
-        <v>26500515</v>
+        <v>36162739</v>
       </c>
       <c r="B165" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C165" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H165" t="s">
         <v>171</v>
@@ -6507,15 +6293,15 @@
         <v>40640374</v>
       </c>
     </row>
-    <row r="166" spans="1:11">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A166" s="8">
-        <v>36162739</v>
+        <v>39893389</v>
       </c>
       <c r="B166" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C166" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H166" t="s">
         <v>171</v>
@@ -6530,15 +6316,15 @@
         <v>13745117</v>
       </c>
     </row>
-    <row r="167" spans="1:11">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A167" s="8">
-        <v>39893389</v>
+        <v>39296173</v>
       </c>
       <c r="B167" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C167" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H167" t="s">
         <v>171</v>
@@ -6553,15 +6339,15 @@
         <v>15414324</v>
       </c>
     </row>
-    <row r="168" spans="1:11">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A168" s="8">
-        <v>39296173</v>
+        <v>42217758</v>
       </c>
       <c r="B168" s="9" t="s">
-        <v>257</v>
+        <v>285</v>
       </c>
       <c r="C168" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H168" t="s">
         <v>171</v>
@@ -6576,15 +6362,15 @@
         <v>35192489</v>
       </c>
     </row>
-    <row r="169" spans="1:11">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A169" s="8">
-        <v>42217758</v>
+        <v>22403445</v>
       </c>
       <c r="B169" s="9" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="C169" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H169" t="s">
         <v>171</v>
@@ -6599,15 +6385,15 @@
         <v>40982029</v>
       </c>
     </row>
-    <row r="170" spans="1:11">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A170" s="8">
-        <v>22403445</v>
+        <v>26257716</v>
       </c>
       <c r="B170" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C170" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H170" t="s">
         <v>171</v>
@@ -6622,15 +6408,15 @@
         <v>10858043</v>
       </c>
     </row>
-    <row r="171" spans="1:11">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A171" s="8">
-        <v>26257716</v>
+        <v>42486414</v>
       </c>
       <c r="B171" s="9" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="C171" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H171" t="s">
         <v>171</v>
@@ -6645,15 +6431,15 @@
         <v>4125377</v>
       </c>
     </row>
-    <row r="172" spans="1:11">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A172" s="8">
-        <v>42486414</v>
+        <v>44695653</v>
       </c>
       <c r="B172" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C172" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H172" t="s">
         <v>171</v>
@@ -6668,15 +6454,15 @@
         <v>26426530</v>
       </c>
     </row>
-    <row r="173" spans="1:11">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A173" s="8">
-        <v>44695653</v>
+        <v>13405604</v>
       </c>
       <c r="B173" s="9" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C173" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H173" t="s">
         <v>171</v>
@@ -6691,15 +6477,15 @@
         <v>18980681</v>
       </c>
     </row>
-    <row r="174" spans="1:11">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A174" s="8">
-        <v>13405604</v>
+        <v>39911056</v>
       </c>
       <c r="B174" s="9" t="s">
-        <v>309</v>
+        <v>337</v>
       </c>
       <c r="C174" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H174" t="s">
         <v>171</v>
@@ -6714,15 +6500,15 @@
         <v>12439390</v>
       </c>
     </row>
-    <row r="175" spans="1:11">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A175" s="8">
-        <v>39911056</v>
+        <v>51897600</v>
       </c>
       <c r="B175" s="9" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="C175" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H175" t="s">
         <v>171</v>
@@ -6737,15 +6523,15 @@
         <v>12263239</v>
       </c>
     </row>
-    <row r="176" spans="1:11">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A176" s="8">
-        <v>51897600</v>
+        <v>52990015</v>
       </c>
       <c r="B176" s="9" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="C176" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H176" t="s">
         <v>171</v>
@@ -6760,15 +6546,15 @@
         <v>50725354</v>
       </c>
     </row>
-    <row r="177" spans="1:11">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A177" s="8">
-        <v>52990015</v>
+        <v>55354052</v>
       </c>
       <c r="B177" s="9" t="s">
-        <v>363</v>
+        <v>382</v>
       </c>
       <c r="C177" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H177" t="s">
         <v>208</v>
@@ -6783,15 +6569,15 @@
         <v>16179047</v>
       </c>
     </row>
-    <row r="178" spans="1:11">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A178" s="8">
-        <v>55354052</v>
+        <v>55356388</v>
       </c>
       <c r="B178" s="9" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="C178" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H178" t="s">
         <v>208</v>
@@ -6806,15 +6592,15 @@
         <v>20815743</v>
       </c>
     </row>
-    <row r="179" spans="1:11">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A179" s="8">
-        <v>55356388</v>
+        <v>62377903</v>
       </c>
       <c r="B179" s="9" t="s">
-        <v>390</v>
+        <v>436</v>
       </c>
       <c r="C179" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H179" t="s">
         <v>208</v>
@@ -6829,15 +6615,15 @@
         <v>39651008</v>
       </c>
     </row>
-    <row r="180" spans="1:11">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A180" s="8">
-        <v>62377903</v>
+        <v>66097436</v>
       </c>
       <c r="B180" s="9" t="s">
-        <v>436</v>
+        <v>477</v>
       </c>
       <c r="C180" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H180" t="s">
         <v>211</v>
@@ -6852,15 +6638,15 @@
         <v>42839047</v>
       </c>
     </row>
-    <row r="181" spans="1:11">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A181" s="8">
-        <v>66097436</v>
+        <v>11681261</v>
       </c>
       <c r="B181" s="9" t="s">
-        <v>477</v>
+        <v>287</v>
       </c>
       <c r="C181" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H181" t="s">
         <v>211</v>
@@ -6875,15 +6661,15 @@
         <v>38455497</v>
       </c>
     </row>
-    <row r="182" spans="1:11">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A182" s="8">
-        <v>11681261</v>
+        <v>11874445</v>
       </c>
       <c r="B182" s="9" t="s">
-        <v>287</v>
+        <v>6</v>
       </c>
       <c r="C182" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H182" t="s">
         <v>211</v>
@@ -6898,15 +6684,15 @@
         <v>37173787</v>
       </c>
     </row>
-    <row r="183" spans="1:11">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A183" s="8">
-        <v>11874445</v>
+        <v>14719737</v>
       </c>
       <c r="B183" s="9" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C183" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H183" t="s">
         <v>98</v>
@@ -6921,15 +6707,15 @@
         <v>42913903</v>
       </c>
     </row>
-    <row r="184" spans="1:11">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A184" s="8">
-        <v>14719737</v>
+        <v>16179047</v>
       </c>
       <c r="B184" s="9" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C184" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H184" t="s">
         <v>98</v>
@@ -6944,15 +6730,15 @@
         <v>41864123</v>
       </c>
     </row>
-    <row r="185" spans="1:11">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A185" s="8">
-        <v>16179047</v>
+        <v>20815743</v>
       </c>
       <c r="B185" s="9" t="s">
-        <v>12</v>
+        <v>209</v>
       </c>
       <c r="C185" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H185" t="s">
         <v>98</v>
@@ -6967,15 +6753,15 @@
         <v>4152612</v>
       </c>
     </row>
-    <row r="186" spans="1:11">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A186" s="8">
-        <v>20815743</v>
+        <v>30405071</v>
       </c>
       <c r="B186" s="9" t="s">
-        <v>209</v>
+        <v>289</v>
       </c>
       <c r="C186" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H186" t="s">
         <v>98</v>
@@ -6990,15 +6776,15 @@
         <v>4152610</v>
       </c>
     </row>
-    <row r="187" spans="1:11">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A187" s="8">
-        <v>30405071</v>
+        <v>34352694</v>
       </c>
       <c r="B187" s="9" t="s">
-        <v>289</v>
+        <v>139</v>
       </c>
       <c r="C187" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H187" t="s">
         <v>98</v>
@@ -7013,15 +6799,15 @@
         <v>35896315</v>
       </c>
     </row>
-    <row r="188" spans="1:11">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A188" s="8">
-        <v>34352694</v>
+        <v>35149611</v>
       </c>
       <c r="B188" s="9" t="s">
-        <v>139</v>
+        <v>2</v>
       </c>
       <c r="C188" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H188" t="s">
         <v>98</v>
@@ -7036,15 +6822,15 @@
         <v>31743599</v>
       </c>
     </row>
-    <row r="189" spans="1:11">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A189" s="8">
-        <v>35149611</v>
+        <v>35896315</v>
       </c>
       <c r="B189" s="9" t="s">
-        <v>2</v>
+        <v>219</v>
       </c>
       <c r="C189" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H189" t="s">
         <v>98</v>
@@ -7059,15 +6845,15 @@
         <v>4152608</v>
       </c>
     </row>
-    <row r="190" spans="1:11">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A190" s="8">
-        <v>35896315</v>
+        <v>36682232</v>
       </c>
       <c r="B190" s="9" t="s">
-        <v>219</v>
+        <v>294</v>
       </c>
       <c r="C190" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H190" t="s">
         <v>98</v>
@@ -7082,15 +6868,15 @@
         <v>4152606</v>
       </c>
     </row>
-    <row r="191" spans="1:11">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A191" s="8">
-        <v>36682232</v>
+        <v>43571360</v>
       </c>
       <c r="B191" s="9" t="s">
-        <v>294</v>
+        <v>136</v>
       </c>
       <c r="C191" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H191" t="s">
         <v>98</v>
@@ -7105,15 +6891,15 @@
         <v>34098917</v>
       </c>
     </row>
-    <row r="192" spans="1:11">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A192" s="8">
-        <v>43571360</v>
+        <v>44374810</v>
       </c>
       <c r="B192" s="9" t="s">
-        <v>136</v>
+        <v>307</v>
       </c>
       <c r="C192" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H192" t="s">
         <v>92</v>
@@ -7128,15 +6914,15 @@
         <v>34801754</v>
       </c>
     </row>
-    <row r="193" spans="1:11">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A193" s="8">
-        <v>44374810</v>
+        <v>45349063</v>
       </c>
       <c r="B193" s="9" t="s">
-        <v>307</v>
+        <v>7</v>
       </c>
       <c r="C193" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H193" t="s">
         <v>92</v>
@@ -7151,15 +6937,15 @@
         <v>37639889</v>
       </c>
     </row>
-    <row r="194" spans="1:11">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A194" s="8">
-        <v>45349063</v>
+        <v>59836396</v>
       </c>
       <c r="B194" s="9" t="s">
-        <v>7</v>
+        <v>418</v>
       </c>
       <c r="C194" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H194" t="s">
         <v>92</v>
@@ -7174,15 +6960,15 @@
         <v>51533853</v>
       </c>
     </row>
-    <row r="195" spans="1:11">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A195" s="8">
-        <v>59836396</v>
+        <v>59927382</v>
       </c>
       <c r="B195" s="9" t="s">
-        <v>418</v>
+        <v>11</v>
       </c>
       <c r="C195" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H195" t="s">
         <v>92</v>
@@ -7197,15 +6983,15 @@
         <v>49985232</v>
       </c>
     </row>
-    <row r="196" spans="1:11">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A196" s="8">
-        <v>59927382</v>
+        <v>60541542</v>
       </c>
       <c r="B196" s="9" t="s">
-        <v>11</v>
+        <v>427</v>
       </c>
       <c r="C196" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H196" t="s">
         <v>92</v>
@@ -7220,15 +7006,15 @@
         <v>50155408</v>
       </c>
     </row>
-    <row r="197" spans="1:11">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A197" s="8">
-        <v>60541542</v>
+        <v>66417801</v>
       </c>
       <c r="B197" s="9" t="s">
-        <v>427</v>
+        <v>3</v>
       </c>
       <c r="C197" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H197" t="s">
         <v>92</v>
@@ -7243,16 +7029,7 @@
         <v>35401181</v>
       </c>
     </row>
-    <row r="198" spans="1:11">
-      <c r="A198" s="8">
-        <v>66417801</v>
-      </c>
-      <c r="B198" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="C198" s="10" t="s">
-        <v>650</v>
-      </c>
+    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H198" t="s">
         <v>92</v>
       </c>
@@ -7266,7 +7043,7 @@
         <v>47936724</v>
       </c>
     </row>
-    <row r="199" spans="1:11">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H199" t="s">
         <v>92</v>
       </c>
@@ -7280,7 +7057,12 @@
         <v>38417806</v>
       </c>
     </row>
-    <row r="200" spans="1:11">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A200" s="13" t="s">
+        <v>650</v>
+      </c>
+      <c r="B200" s="13"/>
+      <c r="C200" s="13"/>
       <c r="H200" t="s">
         <v>92</v>
       </c>
@@ -7294,12 +7076,8 @@
         <v>38158208</v>
       </c>
     </row>
-    <row r="201" spans="1:11">
-      <c r="A201" s="13" t="s">
-        <v>651</v>
-      </c>
-      <c r="B201" s="13"/>
-      <c r="C201" s="13"/>
+    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B201" s="11"/>
       <c r="H201" t="s">
         <v>92</v>
       </c>
@@ -7313,8 +7091,8 @@
         <v>12263163</v>
       </c>
     </row>
-    <row r="202" spans="1:11">
-      <c r="B202" s="11"/>
+    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B202" s="12"/>
       <c r="H202" t="s">
         <v>92</v>
       </c>
@@ -7328,7 +7106,7 @@
         <v>15826960</v>
       </c>
     </row>
-    <row r="203" spans="1:11">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B203" s="12"/>
       <c r="H203" t="s">
         <v>92</v>
@@ -7343,7 +7121,7 @@
         <v>13573385</v>
       </c>
     </row>
-    <row r="204" spans="1:11">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B204" s="12"/>
       <c r="H204" t="s">
         <v>92</v>
@@ -7358,7 +7136,7 @@
         <v>42871700</v>
       </c>
     </row>
-    <row r="205" spans="1:11">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B205" s="12"/>
       <c r="H205" t="s">
         <v>92</v>
@@ -7373,7 +7151,7 @@
         <v>39257536</v>
       </c>
     </row>
-    <row r="206" spans="1:11">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B206" s="12"/>
       <c r="H206" t="s">
         <v>92</v>
@@ -7388,7 +7166,7 @@
         <v>37424126</v>
       </c>
     </row>
-    <row r="207" spans="1:11">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B207" s="12"/>
       <c r="H207" t="s">
         <v>92</v>
@@ -7403,7 +7181,7 @@
         <v>36802614</v>
       </c>
     </row>
-    <row r="208" spans="1:11">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B208" s="12"/>
       <c r="H208" t="s">
         <v>92</v>
@@ -7418,7 +7196,7 @@
         <v>36577826</v>
       </c>
     </row>
-    <row r="209" spans="2:11">
+    <row r="209" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B209" s="12"/>
       <c r="H209" t="s">
         <v>92</v>
@@ -7433,7 +7211,7 @@
         <v>35149611</v>
       </c>
     </row>
-    <row r="210" spans="2:11">
+    <row r="210" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B210" s="12"/>
       <c r="H210" t="s">
         <v>92</v>
@@ -7448,7 +7226,7 @@
         <v>26196255</v>
       </c>
     </row>
-    <row r="211" spans="2:11">
+    <row r="211" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B211" s="12"/>
       <c r="H211" t="s">
         <v>92</v>
@@ -7463,8 +7241,7 @@
         <v>11156528</v>
       </c>
     </row>
-    <row r="212" spans="2:11">
-      <c r="B212" s="12"/>
+    <row r="212" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H212" t="s">
         <v>92</v>
       </c>
@@ -7478,7 +7255,7 @@
         <v>38415503</v>
       </c>
     </row>
-    <row r="213" spans="2:11">
+    <row r="213" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H213" t="s">
         <v>92</v>
       </c>
@@ -7492,7 +7269,7 @@
         <v>37244806</v>
       </c>
     </row>
-    <row r="214" spans="2:11">
+    <row r="214" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H214" t="s">
         <v>92</v>
       </c>
@@ -7506,7 +7283,7 @@
         <v>27011098</v>
       </c>
     </row>
-    <row r="215" spans="2:11">
+    <row r="215" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H215" t="s">
         <v>92</v>
       </c>
@@ -7520,7 +7297,7 @@
         <v>26019234</v>
       </c>
     </row>
-    <row r="216" spans="2:11">
+    <row r="216" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H216" t="s">
         <v>92</v>
       </c>
@@ -7534,7 +7311,7 @@
         <v>13959023</v>
       </c>
     </row>
-    <row r="217" spans="2:11">
+    <row r="217" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H217" t="s">
         <v>92</v>
       </c>
@@ -7548,7 +7325,7 @@
         <v>12496637</v>
       </c>
     </row>
-    <row r="218" spans="2:11">
+    <row r="218" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H218" t="s">
         <v>92</v>
       </c>
@@ -7562,7 +7339,7 @@
         <v>25411238</v>
       </c>
     </row>
-    <row r="219" spans="2:11">
+    <row r="219" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H219" t="s">
         <v>92</v>
       </c>
@@ -7576,7 +7353,7 @@
         <v>38312169</v>
       </c>
     </row>
-    <row r="220" spans="2:11">
+    <row r="220" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H220" t="s">
         <v>92</v>
       </c>
@@ -7590,7 +7367,7 @@
         <v>31886592</v>
       </c>
     </row>
-    <row r="221" spans="2:11">
+    <row r="221" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H221" t="s">
         <v>92</v>
       </c>
@@ -7604,7 +7381,7 @@
         <v>11670520</v>
       </c>
     </row>
-    <row r="222" spans="2:11">
+    <row r="222" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H222" t="s">
         <v>92</v>
       </c>
@@ -7618,7 +7395,7 @@
         <v>26500515</v>
       </c>
     </row>
-    <row r="223" spans="2:11">
+    <row r="223" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H223" t="s">
         <v>92</v>
       </c>
@@ -7632,7 +7409,7 @@
         <v>36162739</v>
       </c>
     </row>
-    <row r="224" spans="2:11">
+    <row r="224" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H224" t="s">
         <v>92</v>
       </c>
@@ -7646,7 +7423,7 @@
         <v>39893389</v>
       </c>
     </row>
-    <row r="225" spans="8:11">
+    <row r="225" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H225" t="s">
         <v>92</v>
       </c>
@@ -7660,7 +7437,7 @@
         <v>39296173</v>
       </c>
     </row>
-    <row r="226" spans="8:11">
+    <row r="226" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H226" t="s">
         <v>92</v>
       </c>
@@ -7674,7 +7451,7 @@
         <v>26491140</v>
       </c>
     </row>
-    <row r="227" spans="8:11">
+    <row r="227" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H227" t="s">
         <v>56</v>
       </c>
@@ -7688,7 +7465,7 @@
         <v>49473587</v>
       </c>
     </row>
-    <row r="228" spans="8:11">
+    <row r="228" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H228" t="s">
         <v>92</v>
       </c>
@@ -7702,7 +7479,7 @@
         <v>50326931</v>
       </c>
     </row>
-    <row r="229" spans="8:11">
+    <row r="229" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H229" t="s">
         <v>152</v>
       </c>
@@ -7716,7 +7493,7 @@
         <v>12095120</v>
       </c>
     </row>
-    <row r="230" spans="8:11">
+    <row r="230" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H230" t="s">
         <v>152</v>
       </c>
@@ -7730,7 +7507,7 @@
         <v>11765770</v>
       </c>
     </row>
-    <row r="231" spans="8:11">
+    <row r="231" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H231" t="s">
         <v>152</v>
       </c>
@@ -7744,7 +7521,7 @@
         <v>15757638</v>
       </c>
     </row>
-    <row r="232" spans="8:11">
+    <row r="232" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H232" t="s">
         <v>152</v>
       </c>
@@ -7758,7 +7535,7 @@
         <v>12038103</v>
       </c>
     </row>
-    <row r="233" spans="8:11">
+    <row r="233" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H233" t="s">
         <v>152</v>
       </c>
@@ -7772,7 +7549,7 @@
         <v>46801171</v>
       </c>
     </row>
-    <row r="234" spans="8:11">
+    <row r="234" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H234" t="s">
         <v>152</v>
       </c>
@@ -7786,7 +7563,7 @@
         <v>10155238</v>
       </c>
     </row>
-    <row r="235" spans="8:11">
+    <row r="235" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H235" t="s">
         <v>152</v>
       </c>
@@ -7800,7 +7577,7 @@
         <v>10816066</v>
       </c>
     </row>
-    <row r="236" spans="8:11">
+    <row r="236" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H236" t="s">
         <v>152</v>
       </c>
@@ -7814,7 +7591,7 @@
         <v>8668649</v>
       </c>
     </row>
-    <row r="237" spans="8:11">
+    <row r="237" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H237" t="s">
         <v>152</v>
       </c>
@@ -7828,7 +7605,7 @@
         <v>36635604</v>
       </c>
     </row>
-    <row r="238" spans="8:11">
+    <row r="238" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H238" t="s">
         <v>109</v>
       </c>
@@ -7842,7 +7619,7 @@
         <v>8837870</v>
       </c>
     </row>
-    <row r="239" spans="8:11">
+    <row r="239" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H239" t="s">
         <v>109</v>
       </c>
@@ -7856,7 +7633,7 @@
         <v>5359040</v>
       </c>
     </row>
-    <row r="240" spans="8:11">
+    <row r="240" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H240" t="s">
         <v>109</v>
       </c>
@@ -7870,7 +7647,7 @@
         <v>42373723</v>
       </c>
     </row>
-    <row r="241" spans="8:11">
+    <row r="241" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H241" t="s">
         <v>109</v>
       </c>
@@ -7884,7 +7661,7 @@
         <v>16303007</v>
       </c>
     </row>
-    <row r="242" spans="8:11">
+    <row r="242" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H242" t="s">
         <v>109</v>
       </c>
@@ -7898,7 +7675,7 @@
         <v>27303665</v>
       </c>
     </row>
-    <row r="243" spans="8:11">
+    <row r="243" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H243" t="s">
         <v>109</v>
       </c>
@@ -7912,7 +7689,7 @@
         <v>5462299</v>
       </c>
     </row>
-    <row r="244" spans="8:11">
+    <row r="244" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H244" t="s">
         <v>109</v>
       </c>
@@ -7926,7 +7703,7 @@
         <v>47220150</v>
       </c>
     </row>
-    <row r="245" spans="8:11">
+    <row r="245" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H245" t="s">
         <v>109</v>
       </c>
@@ -7940,7 +7717,7 @@
         <v>42265154</v>
       </c>
     </row>
-    <row r="246" spans="8:11">
+    <row r="246" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H246" t="s">
         <v>109</v>
       </c>
@@ -7954,7 +7731,7 @@
         <v>48105600</v>
       </c>
     </row>
-    <row r="247" spans="8:11">
+    <row r="247" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H247" t="s">
         <v>109</v>
       </c>
@@ -7968,7 +7745,7 @@
         <v>34991467</v>
       </c>
     </row>
-    <row r="248" spans="8:11">
+    <row r="248" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H248" t="s">
         <v>109</v>
       </c>
@@ -7982,7 +7759,7 @@
         <v>34348663</v>
       </c>
     </row>
-    <row r="249" spans="8:11">
+    <row r="249" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H249" t="s">
         <v>109</v>
       </c>
@@ -7996,7 +7773,7 @@
         <v>34535085</v>
       </c>
     </row>
-    <row r="250" spans="8:11">
+    <row r="250" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H250" t="s">
         <v>109</v>
       </c>
@@ -8010,7 +7787,7 @@
         <v>41140508</v>
       </c>
     </row>
-    <row r="251" spans="8:11">
+    <row r="251" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H251" t="s">
         <v>109</v>
       </c>
@@ -8024,7 +7801,7 @@
         <v>22441147</v>
       </c>
     </row>
-    <row r="252" spans="8:11">
+    <row r="252" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H252" t="s">
         <v>109</v>
       </c>
@@ -8038,7 +7815,7 @@
         <v>36811022</v>
       </c>
     </row>
-    <row r="253" spans="8:11">
+    <row r="253" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H253" t="s">
         <v>109</v>
       </c>
@@ -8052,7 +7829,7 @@
         <v>36811023</v>
       </c>
     </row>
-    <row r="254" spans="8:11">
+    <row r="254" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H254" t="s">
         <v>143</v>
       </c>
@@ -8066,7 +7843,7 @@
         <v>42217758</v>
       </c>
     </row>
-    <row r="255" spans="8:11">
+    <row r="255" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H255" t="s">
         <v>143</v>
       </c>
@@ -8080,7 +7857,7 @@
         <v>39384055</v>
       </c>
     </row>
-    <row r="256" spans="8:11">
+    <row r="256" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H256" t="s">
         <v>143</v>
       </c>
@@ -8094,7 +7871,7 @@
         <v>11681261</v>
       </c>
     </row>
-    <row r="257" spans="8:11">
+    <row r="257" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H257" t="s">
         <v>211</v>
       </c>
@@ -8108,7 +7885,7 @@
         <v>37161537</v>
       </c>
     </row>
-    <row r="258" spans="8:11">
+    <row r="258" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H258" t="s">
         <v>143</v>
       </c>
@@ -8122,7 +7899,7 @@
         <v>30405071</v>
       </c>
     </row>
-    <row r="259" spans="8:11">
+    <row r="259" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H259" t="s">
         <v>143</v>
       </c>
@@ -8136,7 +7913,7 @@
         <v>22403445</v>
       </c>
     </row>
-    <row r="260" spans="8:11">
+    <row r="260" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H260" t="s">
         <v>143</v>
       </c>
@@ -8150,7 +7927,7 @@
         <v>26257716</v>
       </c>
     </row>
-    <row r="261" spans="8:11">
+    <row r="261" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H261" t="s">
         <v>143</v>
       </c>
@@ -8164,7 +7941,7 @@
         <v>12481760</v>
       </c>
     </row>
-    <row r="262" spans="8:11">
+    <row r="262" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H262" t="s">
         <v>143</v>
       </c>
@@ -8178,7 +7955,7 @@
         <v>12481759</v>
       </c>
     </row>
-    <row r="263" spans="8:11">
+    <row r="263" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H263" t="s">
         <v>143</v>
       </c>
@@ -8192,7 +7969,7 @@
         <v>36682232</v>
       </c>
     </row>
-    <row r="264" spans="8:11">
+    <row r="264" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H264" t="s">
         <v>143</v>
       </c>
@@ -8206,7 +7983,7 @@
         <v>46727700</v>
       </c>
     </row>
-    <row r="265" spans="8:11">
+    <row r="265" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H265" t="s">
         <v>143</v>
       </c>
@@ -8220,7 +7997,7 @@
         <v>40771157</v>
       </c>
     </row>
-    <row r="266" spans="8:11">
+    <row r="266" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H266" t="s">
         <v>143</v>
       </c>
@@ -8234,7 +8011,7 @@
         <v>19104731</v>
       </c>
     </row>
-    <row r="267" spans="8:11">
+    <row r="267" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H267" t="s">
         <v>143</v>
       </c>
@@ -8248,7 +8025,7 @@
         <v>39944753</v>
       </c>
     </row>
-    <row r="268" spans="8:11">
+    <row r="268" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H268" t="s">
         <v>143</v>
       </c>
@@ -8262,7 +8039,7 @@
         <v>48449253</v>
       </c>
     </row>
-    <row r="269" spans="8:11">
+    <row r="269" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H269" t="s">
         <v>143</v>
       </c>
@@ -8276,7 +8053,7 @@
         <v>42051062</v>
       </c>
     </row>
-    <row r="270" spans="8:11">
+    <row r="270" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H270" t="s">
         <v>143</v>
       </c>
@@ -8290,7 +8067,7 @@
         <v>18291047</v>
       </c>
     </row>
-    <row r="271" spans="8:11">
+    <row r="271" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H271" t="s">
         <v>143</v>
       </c>
@@ -8304,7 +8081,7 @@
         <v>10727917</v>
       </c>
     </row>
-    <row r="272" spans="8:11">
+    <row r="272" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H272" t="s">
         <v>143</v>
       </c>
@@ -8318,7 +8095,7 @@
         <v>46543317</v>
       </c>
     </row>
-    <row r="273" spans="8:11">
+    <row r="273" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H273" t="s">
         <v>143</v>
       </c>
@@ -8332,7 +8109,7 @@
         <v>13644995</v>
       </c>
     </row>
-    <row r="274" spans="8:11">
+    <row r="274" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H274" t="s">
         <v>143</v>
       </c>
@@ -8346,7 +8123,7 @@
         <v>42486414</v>
       </c>
     </row>
-    <row r="275" spans="8:11">
+    <row r="275" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H275" t="s">
         <v>143</v>
       </c>
@@ -8360,7 +8137,7 @@
         <v>44695653</v>
       </c>
     </row>
-    <row r="276" spans="8:11">
+    <row r="276" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H276" t="s">
         <v>143</v>
       </c>
@@ -8374,7 +8151,7 @@
         <v>44374810</v>
       </c>
     </row>
-    <row r="277" spans="8:11">
+    <row r="277" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H277" t="s">
         <v>143</v>
       </c>
@@ -8388,7 +8165,7 @@
         <v>29258063</v>
       </c>
     </row>
-    <row r="278" spans="8:11">
+    <row r="278" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H278" t="s">
         <v>143</v>
       </c>
@@ -8402,7 +8179,7 @@
         <v>13405604</v>
       </c>
     </row>
-    <row r="279" spans="8:11">
+    <row r="279" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H279" t="s">
         <v>143</v>
       </c>
@@ -8416,7 +8193,7 @@
         <v>10646862</v>
       </c>
     </row>
-    <row r="280" spans="8:11">
+    <row r="280" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H280" t="s">
         <v>143</v>
       </c>
@@ -8430,7 +8207,7 @@
         <v>12362063</v>
       </c>
     </row>
-    <row r="281" spans="8:11">
+    <row r="281" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H281" t="s">
         <v>90</v>
       </c>
@@ -8444,7 +8221,7 @@
         <v>40185196</v>
       </c>
     </row>
-    <row r="282" spans="8:11">
+    <row r="282" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H282" t="s">
         <v>90</v>
       </c>
@@ -8458,7 +8235,7 @@
         <v>15825326</v>
       </c>
     </row>
-    <row r="283" spans="8:11">
+    <row r="283" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H283" t="s">
         <v>90</v>
       </c>
@@ -8472,7 +8249,7 @@
         <v>26375455</v>
       </c>
     </row>
-    <row r="284" spans="8:11">
+    <row r="284" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H284" t="s">
         <v>90</v>
       </c>
@@ -8486,7 +8263,7 @@
         <v>42803850</v>
       </c>
     </row>
-    <row r="285" spans="8:11">
+    <row r="285" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H285" t="s">
         <v>90</v>
       </c>
@@ -8500,7 +8277,7 @@
         <v>50154913</v>
       </c>
     </row>
-    <row r="286" spans="8:11">
+    <row r="286" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H286" t="s">
         <v>90</v>
       </c>
@@ -8514,7 +8291,7 @@
         <v>16806254</v>
       </c>
     </row>
-    <row r="287" spans="8:11">
+    <row r="287" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H287" t="s">
         <v>90</v>
       </c>
@@ -8528,7 +8305,7 @@
         <v>40501253</v>
       </c>
     </row>
-    <row r="288" spans="8:11">
+    <row r="288" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H288" t="s">
         <v>90</v>
       </c>
@@ -8542,7 +8319,7 @@
         <v>14878740</v>
       </c>
     </row>
-    <row r="289" spans="8:11">
+    <row r="289" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H289" t="s">
         <v>90</v>
       </c>
@@ -8556,7 +8333,7 @@
         <v>12673237</v>
       </c>
     </row>
-    <row r="290" spans="8:11">
+    <row r="290" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H290" t="s">
         <v>90</v>
       </c>
@@ -8570,7 +8347,7 @@
         <v>17579662</v>
       </c>
     </row>
-    <row r="291" spans="8:11">
+    <row r="291" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H291" t="s">
         <v>90</v>
       </c>
@@ -8584,7 +8361,7 @@
         <v>14719737</v>
       </c>
     </row>
-    <row r="292" spans="8:11">
+    <row r="292" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H292" t="s">
         <v>90</v>
       </c>
@@ -8598,7 +8375,7 @@
         <v>22119013</v>
       </c>
     </row>
-    <row r="293" spans="8:11">
+    <row r="293" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H293" t="s">
         <v>90</v>
       </c>
@@ -8612,7 +8389,7 @@
         <v>15795597</v>
       </c>
     </row>
-    <row r="294" spans="8:11">
+    <row r="294" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H294" t="s">
         <v>90</v>
       </c>
@@ -8626,7 +8403,7 @@
         <v>12126317</v>
       </c>
     </row>
-    <row r="295" spans="8:11">
+    <row r="295" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H295" t="s">
         <v>90</v>
       </c>
@@ -8640,7 +8417,7 @@
         <v>39239709</v>
       </c>
     </row>
-    <row r="296" spans="8:11">
+    <row r="296" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H296" t="s">
         <v>90</v>
       </c>
@@ -8654,7 +8431,7 @@
         <v>14488275</v>
       </c>
     </row>
-    <row r="297" spans="8:11">
+    <row r="297" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H297" t="s">
         <v>90</v>
       </c>
@@ -8668,7 +8445,7 @@
         <v>42519088</v>
       </c>
     </row>
-    <row r="298" spans="8:11">
+    <row r="298" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H298" t="s">
         <v>90</v>
       </c>
@@ -8682,7 +8459,7 @@
         <v>17579394</v>
       </c>
     </row>
-    <row r="299" spans="8:11">
+    <row r="299" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H299" t="s">
         <v>90</v>
       </c>
@@ -8696,7 +8473,7 @@
         <v>27056005</v>
       </c>
     </row>
-    <row r="300" spans="8:11">
+    <row r="300" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H300" t="s">
         <v>90</v>
       </c>
@@ -8710,7 +8487,7 @@
         <v>24832169</v>
       </c>
     </row>
-    <row r="301" spans="8:11">
+    <row r="301" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H301" t="s">
         <v>171</v>
       </c>
@@ -8724,7 +8501,7 @@
         <v>39147133</v>
       </c>
     </row>
-    <row r="302" spans="8:11">
+    <row r="302" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H302" t="s">
         <v>171</v>
       </c>
@@ -8738,7 +8515,7 @@
         <v>39030281</v>
       </c>
     </row>
-    <row r="303" spans="8:11">
+    <row r="303" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H303" t="s">
         <v>171</v>
       </c>
@@ -8752,7 +8529,7 @@
         <v>13373616</v>
       </c>
     </row>
-    <row r="304" spans="8:11">
+    <row r="304" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H304" t="s">
         <v>171</v>
       </c>
@@ -8766,7 +8543,7 @@
         <v>12757668</v>
       </c>
     </row>
-    <row r="305" spans="8:11">
+    <row r="305" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H305" t="s">
         <v>171</v>
       </c>
@@ -8780,7 +8557,7 @@
         <v>38977260</v>
       </c>
     </row>
-    <row r="306" spans="8:11">
+    <row r="306" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H306" t="s">
         <v>29</v>
       </c>
@@ -8794,7 +8571,7 @@
         <v>38676914</v>
       </c>
     </row>
-    <row r="307" spans="8:11">
+    <row r="307" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H307" t="s">
         <v>29</v>
       </c>
@@ -8808,7 +8585,7 @@
         <v>39911056</v>
       </c>
     </row>
-    <row r="308" spans="8:11">
+    <row r="308" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H308" t="s">
         <v>29</v>
       </c>
@@ -8822,7 +8599,7 @@
         <v>40102936</v>
       </c>
     </row>
-    <row r="309" spans="8:11">
+    <row r="309" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H309" t="s">
         <v>29</v>
       </c>
@@ -8836,7 +8613,7 @@
         <v>10929274</v>
       </c>
     </row>
-    <row r="310" spans="8:11">
+    <row r="310" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H310" t="s">
         <v>29</v>
       </c>
@@ -8850,7 +8627,7 @@
         <v>10929273</v>
       </c>
     </row>
-    <row r="311" spans="8:11">
+    <row r="311" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H311" t="s">
         <v>29</v>
       </c>
@@ -8864,7 +8641,7 @@
         <v>38412071</v>
       </c>
     </row>
-    <row r="312" spans="8:11">
+    <row r="312" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H312" t="s">
         <v>29</v>
       </c>
@@ -8878,7 +8655,7 @@
         <v>29280326</v>
       </c>
     </row>
-    <row r="313" spans="8:11">
+    <row r="313" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H313" t="s">
         <v>29</v>
       </c>
@@ -8892,7 +8669,7 @@
         <v>38412101</v>
       </c>
     </row>
-    <row r="314" spans="8:11">
+    <row r="314" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H314" t="s">
         <v>98</v>
       </c>
@@ -8906,7 +8683,7 @@
         <v>5332788</v>
       </c>
     </row>
-    <row r="315" spans="8:11">
+    <row r="315" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H315" t="s">
         <v>98</v>
       </c>
@@ -8920,7 +8697,7 @@
         <v>5332789</v>
       </c>
     </row>
-    <row r="316" spans="8:11">
+    <row r="316" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H316" t="s">
         <v>98</v>
       </c>
@@ -8934,7 +8711,7 @@
         <v>51016959</v>
       </c>
     </row>
-    <row r="317" spans="8:11">
+    <row r="317" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H317" t="s">
         <v>90</v>
       </c>
@@ -8948,7 +8725,7 @@
         <v>40636333</v>
       </c>
     </row>
-    <row r="318" spans="8:11">
+    <row r="318" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H318" t="s">
         <v>171</v>
       </c>
@@ -8962,7 +8739,7 @@
         <v>50875168</v>
       </c>
     </row>
-    <row r="319" spans="8:11">
+    <row r="319" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H319" t="s">
         <v>58</v>
       </c>
@@ -8976,7 +8753,7 @@
         <v>51623281</v>
       </c>
     </row>
-    <row r="320" spans="8:11">
+    <row r="320" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H320" t="s">
         <v>92</v>
       </c>
@@ -8990,7 +8767,7 @@
         <v>51897600</v>
       </c>
     </row>
-    <row r="321" spans="8:11">
+    <row r="321" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H321" t="s">
         <v>58</v>
       </c>
@@ -9004,7 +8781,7 @@
         <v>51989601</v>
       </c>
     </row>
-    <row r="322" spans="8:11">
+    <row r="322" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H322" t="s">
         <v>109</v>
       </c>
@@ -9018,7 +8795,7 @@
         <v>52390638</v>
       </c>
     </row>
-    <row r="323" spans="8:11">
+    <row r="323" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H323" t="s">
         <v>109</v>
       </c>
@@ -9032,7 +8809,7 @@
         <v>52362395</v>
       </c>
     </row>
-    <row r="324" spans="8:11">
+    <row r="324" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H324" t="s">
         <v>90</v>
       </c>
@@ -9046,7 +8823,7 @@
         <v>52155415</v>
       </c>
     </row>
-    <row r="325" spans="8:11">
+    <row r="325" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H325" t="s">
         <v>92</v>
       </c>
@@ -9060,7 +8837,7 @@
         <v>52162444</v>
       </c>
     </row>
-    <row r="326" spans="8:11">
+    <row r="326" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H326" t="s">
         <v>171</v>
       </c>
@@ -9074,7 +8851,7 @@
         <v>52270898</v>
       </c>
     </row>
-    <row r="327" spans="8:11">
+    <row r="327" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H327" t="s">
         <v>98</v>
       </c>
@@ -9088,7 +8865,7 @@
         <v>52211558</v>
       </c>
     </row>
-    <row r="328" spans="8:11">
+    <row r="328" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H328" t="s">
         <v>98</v>
       </c>
@@ -9102,7 +8879,7 @@
         <v>52217000</v>
       </c>
     </row>
-    <row r="329" spans="8:11">
+    <row r="329" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H329" t="s">
         <v>29</v>
       </c>
@@ -9116,7 +8893,7 @@
         <v>51689222</v>
       </c>
     </row>
-    <row r="330" spans="8:11">
+    <row r="330" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H330" t="s">
         <v>29</v>
       </c>
@@ -9130,7 +8907,7 @@
         <v>51684787</v>
       </c>
     </row>
-    <row r="331" spans="8:11">
+    <row r="331" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H331" t="s">
         <v>29</v>
       </c>
@@ -9144,7 +8921,7 @@
         <v>51883980</v>
       </c>
     </row>
-    <row r="332" spans="8:11">
+    <row r="332" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H332" t="s">
         <v>29</v>
       </c>
@@ -9158,7 +8935,7 @@
         <v>51898514</v>
       </c>
     </row>
-    <row r="333" spans="8:11">
+    <row r="333" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H333" t="s">
         <v>98</v>
       </c>
@@ -9172,7 +8949,7 @@
         <v>52990015</v>
       </c>
     </row>
-    <row r="334" spans="8:11">
+    <row r="334" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H334" t="s">
         <v>29</v>
       </c>
@@ -9186,7 +8963,7 @@
         <v>52581507</v>
       </c>
     </row>
-    <row r="335" spans="8:11">
+    <row r="335" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H335" t="s">
         <v>29</v>
       </c>
@@ -9200,7 +8977,7 @@
         <v>52613211</v>
       </c>
     </row>
-    <row r="336" spans="8:11">
+    <row r="336" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H336" t="s">
         <v>29</v>
       </c>
@@ -9214,7 +8991,7 @@
         <v>52578670</v>
       </c>
     </row>
-    <row r="337" spans="8:11">
+    <row r="337" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H337" t="s">
         <v>171</v>
       </c>
@@ -9228,7 +9005,7 @@
         <v>52874174</v>
       </c>
     </row>
-    <row r="338" spans="8:11">
+    <row r="338" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H338" t="s">
         <v>29</v>
       </c>
@@ -9242,7 +9019,7 @@
         <v>52872566</v>
       </c>
     </row>
-    <row r="339" spans="8:11">
+    <row r="339" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H339" t="s">
         <v>171</v>
       </c>
@@ -9256,7 +9033,7 @@
         <v>54145830</v>
       </c>
     </row>
-    <row r="340" spans="8:11">
+    <row r="340" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H340" t="s">
         <v>29</v>
       </c>
@@ -9270,7 +9047,7 @@
         <v>53052265</v>
       </c>
     </row>
-    <row r="341" spans="8:11">
+    <row r="341" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H341" t="s">
         <v>90</v>
       </c>
@@ -9284,7 +9061,7 @@
         <v>53297446</v>
       </c>
     </row>
-    <row r="342" spans="8:11">
+    <row r="342" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H342" t="s">
         <v>143</v>
       </c>
@@ -9298,7 +9075,7 @@
         <v>53583387</v>
       </c>
     </row>
-    <row r="343" spans="8:11">
+    <row r="343" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H343" t="s">
         <v>143</v>
       </c>
@@ -9312,7 +9089,7 @@
         <v>53564659</v>
       </c>
     </row>
-    <row r="344" spans="8:11">
+    <row r="344" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H344" t="s">
         <v>143</v>
       </c>
@@ -9326,7 +9103,7 @@
         <v>53569741</v>
       </c>
     </row>
-    <row r="345" spans="8:11">
+    <row r="345" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H345" t="s">
         <v>58</v>
       </c>
@@ -9340,7 +9117,7 @@
         <v>53680118</v>
       </c>
     </row>
-    <row r="346" spans="8:11">
+    <row r="346" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H346" t="s">
         <v>92</v>
       </c>
@@ -9354,7 +9131,7 @@
         <v>53776254</v>
       </c>
     </row>
-    <row r="347" spans="8:11">
+    <row r="347" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H347" t="s">
         <v>90</v>
       </c>
@@ -9368,7 +9145,7 @@
         <v>53967042</v>
       </c>
     </row>
-    <row r="348" spans="8:11">
+    <row r="348" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H348" t="s">
         <v>90</v>
       </c>
@@ -9382,7 +9159,7 @@
         <v>55275736</v>
       </c>
     </row>
-    <row r="349" spans="8:11">
+    <row r="349" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H349" t="s">
         <v>90</v>
       </c>
@@ -9396,7 +9173,7 @@
         <v>56663811</v>
       </c>
     </row>
-    <row r="350" spans="8:11">
+    <row r="350" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H350" t="s">
         <v>92</v>
       </c>
@@ -9410,7 +9187,7 @@
         <v>59082806</v>
       </c>
     </row>
-    <row r="351" spans="8:11">
+    <row r="351" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H351" t="s">
         <v>29</v>
       </c>
@@ -9424,7 +9201,7 @@
         <v>55369678</v>
       </c>
     </row>
-    <row r="352" spans="8:11">
+    <row r="352" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H352" t="s">
         <v>58</v>
       </c>
@@ -9438,7 +9215,7 @@
         <v>55354052</v>
       </c>
     </row>
-    <row r="353" spans="8:11">
+    <row r="353" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H353" t="s">
         <v>58</v>
       </c>
@@ -9452,7 +9229,7 @@
         <v>55381383</v>
       </c>
     </row>
-    <row r="354" spans="8:11">
+    <row r="354" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H354" t="s">
         <v>58</v>
       </c>
@@ -9466,7 +9243,7 @@
         <v>55609278</v>
       </c>
     </row>
-    <row r="355" spans="8:11">
+    <row r="355" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H355" t="s">
         <v>90</v>
       </c>
@@ -9480,7 +9257,7 @@
         <v>55356212</v>
       </c>
     </row>
-    <row r="356" spans="8:11">
+    <row r="356" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H356" t="s">
         <v>90</v>
       </c>
@@ -9494,7 +9271,7 @@
         <v>55449180</v>
       </c>
     </row>
-    <row r="357" spans="8:11">
+    <row r="357" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H357" t="s">
         <v>58</v>
       </c>
@@ -9508,7 +9285,7 @@
         <v>55357095</v>
       </c>
     </row>
-    <row r="358" spans="8:11">
+    <row r="358" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H358" t="s">
         <v>58</v>
       </c>
@@ -9522,7 +9299,7 @@
         <v>55384739</v>
       </c>
     </row>
-    <row r="359" spans="8:11">
+    <row r="359" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H359" t="s">
         <v>58</v>
       </c>
@@ -9536,7 +9313,7 @@
         <v>55357155</v>
       </c>
     </row>
-    <row r="360" spans="8:11">
+    <row r="360" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H360" t="s">
         <v>58</v>
       </c>
@@ -9550,7 +9327,7 @@
         <v>55389336</v>
       </c>
     </row>
-    <row r="361" spans="8:11">
+    <row r="361" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H361" t="s">
         <v>171</v>
       </c>
@@ -9564,7 +9341,7 @@
         <v>55356388</v>
       </c>
     </row>
-    <row r="362" spans="8:11">
+    <row r="362" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H362" t="s">
         <v>171</v>
       </c>
@@ -9578,7 +9355,7 @@
         <v>55610213</v>
       </c>
     </row>
-    <row r="363" spans="8:11">
+    <row r="363" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H363" t="s">
         <v>92</v>
       </c>
@@ -9592,7 +9369,7 @@
         <v>55462718</v>
       </c>
     </row>
-    <row r="364" spans="8:11">
+    <row r="364" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H364" t="s">
         <v>58</v>
       </c>
@@ -9606,7 +9383,7 @@
         <v>58084222</v>
       </c>
     </row>
-    <row r="365" spans="8:11">
+    <row r="365" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H365" t="s">
         <v>58</v>
       </c>
@@ -9620,7 +9397,7 @@
         <v>56651433</v>
       </c>
     </row>
-    <row r="366" spans="8:11">
+    <row r="366" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H366" t="s">
         <v>94</v>
       </c>
@@ -9634,7 +9411,7 @@
         <v>56479851</v>
       </c>
     </row>
-    <row r="367" spans="8:11">
+    <row r="367" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H367" t="s">
         <v>90</v>
       </c>
@@ -9648,7 +9425,7 @@
         <v>56667264</v>
       </c>
     </row>
-    <row r="368" spans="8:11">
+    <row r="368" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H368" t="s">
         <v>143</v>
       </c>
@@ -9662,7 +9439,7 @@
         <v>56896464</v>
       </c>
     </row>
-    <row r="369" spans="8:11">
+    <row r="369" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H369" t="s">
         <v>98</v>
       </c>
@@ -9676,7 +9453,7 @@
         <v>57592449</v>
       </c>
     </row>
-    <row r="370" spans="8:11">
+    <row r="370" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H370" t="s">
         <v>92</v>
       </c>
@@ -9690,7 +9467,7 @@
         <v>56183402</v>
       </c>
     </row>
-    <row r="371" spans="8:11">
+    <row r="371" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H371" t="s">
         <v>92</v>
       </c>
@@ -9704,7 +9481,7 @@
         <v>56651667</v>
       </c>
     </row>
-    <row r="372" spans="8:11">
+    <row r="372" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H372" t="s">
         <v>92</v>
       </c>
@@ -9718,7 +9495,7 @@
         <v>58987730</v>
       </c>
     </row>
-    <row r="373" spans="8:11">
+    <row r="373" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H373" t="s">
         <v>171</v>
       </c>
@@ -9732,7 +9509,7 @@
         <v>57422656</v>
       </c>
     </row>
-    <row r="374" spans="8:11">
+    <row r="374" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H374" t="s">
         <v>92</v>
       </c>
@@ -9746,7 +9523,7 @@
         <v>58040260</v>
       </c>
     </row>
-    <row r="375" spans="8:11">
+    <row r="375" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H375" t="s">
         <v>90</v>
       </c>
@@ -9760,7 +9537,7 @@
         <v>59070986</v>
       </c>
     </row>
-    <row r="376" spans="8:11">
+    <row r="376" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H376" t="s">
         <v>98</v>
       </c>
@@ -9774,7 +9551,7 @@
         <v>59058036</v>
       </c>
     </row>
-    <row r="377" spans="8:11">
+    <row r="377" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H377" t="s">
         <v>90</v>
       </c>
@@ -9788,7 +9565,7 @@
         <v>58505144</v>
       </c>
     </row>
-    <row r="378" spans="8:11">
+    <row r="378" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H378" t="s">
         <v>115</v>
       </c>
@@ -9802,7 +9579,7 @@
         <v>58610450</v>
       </c>
     </row>
-    <row r="379" spans="8:11">
+    <row r="379" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H379" t="s">
         <v>143</v>
       </c>
@@ -9816,7 +9593,7 @@
         <v>59056260</v>
       </c>
     </row>
-    <row r="380" spans="8:11">
+    <row r="380" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H380" t="s">
         <v>115</v>
       </c>
@@ -9830,7 +9607,7 @@
         <v>58722261</v>
       </c>
     </row>
-    <row r="381" spans="8:11">
+    <row r="381" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H381" t="s">
         <v>115</v>
       </c>
@@ -9844,7 +9621,7 @@
         <v>58716097</v>
       </c>
     </row>
-    <row r="382" spans="8:11">
+    <row r="382" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H382" t="s">
         <v>115</v>
       </c>
@@ -9858,7 +9635,7 @@
         <v>58730204</v>
       </c>
     </row>
-    <row r="383" spans="8:11">
+    <row r="383" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H383" t="s">
         <v>115</v>
       </c>
@@ -9872,7 +9649,7 @@
         <v>59199875</v>
       </c>
     </row>
-    <row r="384" spans="8:11">
+    <row r="384" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H384" t="s">
         <v>115</v>
       </c>
@@ -9886,7 +9663,7 @@
         <v>59759466</v>
       </c>
     </row>
-    <row r="385" spans="8:11">
+    <row r="385" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H385" t="s">
         <v>92</v>
       </c>
@@ -9900,7 +9677,7 @@
         <v>59332927</v>
       </c>
     </row>
-    <row r="386" spans="8:11">
+    <row r="386" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H386" t="s">
         <v>92</v>
       </c>
@@ -9914,7 +9691,7 @@
         <v>59944694</v>
       </c>
     </row>
-    <row r="387" spans="8:11">
+    <row r="387" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H387" t="s">
         <v>115</v>
       </c>
@@ -9928,7 +9705,7 @@
         <v>60019261</v>
       </c>
     </row>
-    <row r="388" spans="8:11">
+    <row r="388" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H388" t="s">
         <v>143</v>
       </c>
@@ -9942,7 +9719,7 @@
         <v>59932138</v>
       </c>
     </row>
-    <row r="389" spans="8:11">
+    <row r="389" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H389" t="s">
         <v>115</v>
       </c>
@@ -9956,7 +9733,7 @@
         <v>59924956</v>
       </c>
     </row>
-    <row r="390" spans="8:11">
+    <row r="390" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H390" t="s">
         <v>115</v>
       </c>
@@ -9970,7 +9747,7 @@
         <v>59927382</v>
       </c>
     </row>
-    <row r="391" spans="8:11">
+    <row r="391" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H391" t="s">
         <v>115</v>
       </c>
@@ -9984,7 +9761,7 @@
         <v>59836396</v>
       </c>
     </row>
-    <row r="392" spans="8:11">
+    <row r="392" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H392" t="s">
         <v>115</v>
       </c>
@@ -9998,7 +9775,7 @@
         <v>60015061</v>
       </c>
     </row>
-    <row r="393" spans="8:11">
+    <row r="393" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H393" t="s">
         <v>115</v>
       </c>
@@ -10012,7 +9789,7 @@
         <v>60023938</v>
       </c>
     </row>
-    <row r="394" spans="8:11">
+    <row r="394" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H394" t="s">
         <v>115</v>
       </c>
@@ -10026,7 +9803,7 @@
         <v>60025950</v>
       </c>
     </row>
-    <row r="395" spans="8:11">
+    <row r="395" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H395" t="s">
         <v>115</v>
       </c>
@@ -10040,7 +9817,7 @@
         <v>60024864</v>
       </c>
     </row>
-    <row r="396" spans="8:11">
+    <row r="396" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H396" t="s">
         <v>115</v>
       </c>
@@ -10054,7 +9831,7 @@
         <v>60084208</v>
       </c>
     </row>
-    <row r="397" spans="8:11">
+    <row r="397" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H397" t="s">
         <v>92</v>
       </c>
@@ -10068,7 +9845,7 @@
         <v>60085614</v>
       </c>
     </row>
-    <row r="398" spans="8:11">
+    <row r="398" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H398" t="s">
         <v>171</v>
       </c>
@@ -10082,7 +9859,7 @@
         <v>60133592</v>
       </c>
     </row>
-    <row r="399" spans="8:11">
+    <row r="399" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H399" t="s">
         <v>143</v>
       </c>
@@ -10096,7 +9873,7 @@
         <v>60450424</v>
       </c>
     </row>
-    <row r="400" spans="8:11">
+    <row r="400" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H400" t="s">
         <v>143</v>
       </c>
@@ -10110,7 +9887,7 @@
         <v>60380162</v>
       </c>
     </row>
-    <row r="401" spans="8:11">
+    <row r="401" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H401" t="s">
         <v>152</v>
       </c>
@@ -10124,7 +9901,7 @@
         <v>60541542</v>
       </c>
     </row>
-    <row r="402" spans="8:11">
+    <row r="402" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H402" t="s">
         <v>152</v>
       </c>
@@ -10138,7 +9915,7 @@
         <v>60541171</v>
       </c>
     </row>
-    <row r="403" spans="8:11">
+    <row r="403" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H403" t="s">
         <v>90</v>
       </c>
@@ -10152,7 +9929,7 @@
         <v>60543356</v>
       </c>
     </row>
-    <row r="404" spans="8:11">
+    <row r="404" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H404" t="s">
         <v>115</v>
       </c>
@@ -10166,7 +9943,7 @@
         <v>60530655</v>
       </c>
     </row>
-    <row r="405" spans="8:11">
+    <row r="405" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H405" t="s">
         <v>90</v>
       </c>
@@ -10180,7 +9957,7 @@
         <v>60615380</v>
       </c>
     </row>
-    <row r="406" spans="8:11">
+    <row r="406" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H406" t="s">
         <v>58</v>
       </c>
@@ -10194,7 +9971,7 @@
         <v>60725132</v>
       </c>
     </row>
-    <row r="407" spans="8:11">
+    <row r="407" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H407" t="s">
         <v>58</v>
       </c>
@@ -10208,7 +9985,7 @@
         <v>62575565</v>
       </c>
     </row>
-    <row r="408" spans="8:11">
+    <row r="408" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H408" t="s">
         <v>171</v>
       </c>
@@ -10222,7 +9999,7 @@
         <v>61766007</v>
       </c>
     </row>
-    <row r="409" spans="8:11">
+    <row r="409" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H409" t="s">
         <v>98</v>
       </c>
@@ -10236,7 +10013,7 @@
         <v>61089339</v>
       </c>
     </row>
-    <row r="410" spans="8:11">
+    <row r="410" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H410" t="s">
         <v>98</v>
       </c>
@@ -10250,7 +10027,7 @@
         <v>62377903</v>
       </c>
     </row>
-    <row r="411" spans="8:11">
+    <row r="411" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H411" t="s">
         <v>92</v>
       </c>
@@ -10264,7 +10041,7 @@
         <v>60542212</v>
       </c>
     </row>
-    <row r="412" spans="8:11">
+    <row r="412" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H412" t="s">
         <v>109</v>
       </c>
@@ -10278,7 +10055,7 @@
         <v>61044622</v>
       </c>
     </row>
-    <row r="413" spans="8:11">
+    <row r="413" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H413" t="s">
         <v>92</v>
       </c>
@@ -10292,7 +10069,7 @@
         <v>61199642</v>
       </c>
     </row>
-    <row r="414" spans="8:11">
+    <row r="414" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H414" t="s">
         <v>143</v>
       </c>
@@ -10306,7 +10083,7 @@
         <v>61760291</v>
       </c>
     </row>
-    <row r="415" spans="8:11">
+    <row r="415" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H415" t="s">
         <v>109</v>
       </c>
@@ -10320,7 +10097,7 @@
         <v>61923953</v>
       </c>
     </row>
-    <row r="416" spans="8:11">
+    <row r="416" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H416" t="s">
         <v>143</v>
       </c>
@@ -10334,7 +10111,7 @@
         <v>61760141</v>
       </c>
     </row>
-    <row r="417" spans="8:11">
+    <row r="417" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H417" t="s">
         <v>143</v>
       </c>
@@ -10348,7 +10125,7 @@
         <v>61929592</v>
       </c>
     </row>
-    <row r="418" spans="8:11">
+    <row r="418" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H418" t="s">
         <v>143</v>
       </c>
@@ -10362,7 +10139,7 @@
         <v>61929727</v>
       </c>
     </row>
-    <row r="419" spans="8:11">
+    <row r="419" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H419" t="s">
         <v>92</v>
       </c>
@@ -10376,7 +10153,7 @@
         <v>61929494</v>
       </c>
     </row>
-    <row r="420" spans="8:11">
+    <row r="420" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H420" t="s">
         <v>92</v>
       </c>
@@ -10390,7 +10167,7 @@
         <v>61929493</v>
       </c>
     </row>
-    <row r="421" spans="8:11">
+    <row r="421" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H421" t="s">
         <v>98</v>
       </c>
@@ -10404,7 +10181,7 @@
         <v>61879892</v>
       </c>
     </row>
-    <row r="422" spans="8:11">
+    <row r="422" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H422" t="s">
         <v>58</v>
       </c>
@@ -10418,7 +10195,7 @@
         <v>62378988</v>
       </c>
     </row>
-    <row r="423" spans="8:11">
+    <row r="423" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H423" t="s">
         <v>58</v>
       </c>
@@ -10432,7 +10209,7 @@
         <v>62375802</v>
       </c>
     </row>
-    <row r="424" spans="8:11">
+    <row r="424" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H424" t="s">
         <v>58</v>
       </c>
@@ -10446,7 +10223,7 @@
         <v>62379668</v>
       </c>
     </row>
-    <row r="425" spans="8:11">
+    <row r="425" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H425" t="s">
         <v>211</v>
       </c>
@@ -10460,7 +10237,7 @@
         <v>62221331</v>
       </c>
     </row>
-    <row r="426" spans="8:11">
+    <row r="426" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H426" t="s">
         <v>143</v>
       </c>
@@ -10474,7 +10251,7 @@
         <v>62385013</v>
       </c>
     </row>
-    <row r="427" spans="8:11">
+    <row r="427" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H427" t="s">
         <v>143</v>
       </c>
@@ -10488,7 +10265,7 @@
         <v>62380995</v>
       </c>
     </row>
-    <row r="428" spans="8:11">
+    <row r="428" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H428" t="s">
         <v>98</v>
       </c>
@@ -10502,7 +10279,7 @@
         <v>62421723</v>
       </c>
     </row>
-    <row r="429" spans="8:11">
+    <row r="429" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H429" t="s">
         <v>98</v>
       </c>
@@ -10516,7 +10293,7 @@
         <v>62374813</v>
       </c>
     </row>
-    <row r="430" spans="8:11">
+    <row r="430" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H430" t="s">
         <v>98</v>
       </c>
@@ -10530,7 +10307,7 @@
         <v>62499786</v>
       </c>
     </row>
-    <row r="431" spans="8:11">
+    <row r="431" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H431" t="s">
         <v>98</v>
       </c>
@@ -10544,7 +10321,7 @@
         <v>62498583</v>
       </c>
     </row>
-    <row r="432" spans="8:11">
+    <row r="432" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H432" t="s">
         <v>143</v>
       </c>
@@ -10558,7 +10335,7 @@
         <v>63346456</v>
       </c>
     </row>
-    <row r="433" spans="8:11">
+    <row r="433" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H433" t="s">
         <v>143</v>
       </c>
@@ -10572,7 +10349,7 @@
         <v>63100963</v>
       </c>
     </row>
-    <row r="434" spans="8:11">
+    <row r="434" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H434" t="s">
         <v>90</v>
       </c>
@@ -10586,7 +10363,7 @@
         <v>63396496</v>
       </c>
     </row>
-    <row r="435" spans="8:11">
+    <row r="435" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H435" t="s">
         <v>58</v>
       </c>
@@ -10600,7 +10377,7 @@
         <v>64270608</v>
       </c>
     </row>
-    <row r="436" spans="8:11">
+    <row r="436" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H436" t="s">
         <v>92</v>
       </c>
@@ -10614,7 +10391,7 @@
         <v>63573761</v>
       </c>
     </row>
-    <row r="437" spans="8:11">
+    <row r="437" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H437" t="s">
         <v>92</v>
       </c>
@@ -10628,7 +10405,7 @@
         <v>64330763</v>
       </c>
     </row>
-    <row r="438" spans="8:11">
+    <row r="438" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H438" t="s">
         <v>92</v>
       </c>
@@ -10642,7 +10419,7 @@
         <v>64330764</v>
       </c>
     </row>
-    <row r="439" spans="8:11">
+    <row r="439" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H439" t="s">
         <v>92</v>
       </c>
@@ -10656,7 +10433,7 @@
         <v>64212552</v>
       </c>
     </row>
-    <row r="440" spans="8:11">
+    <row r="440" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H440" t="s">
         <v>92</v>
       </c>
@@ -10670,7 +10447,7 @@
         <v>64212544</v>
       </c>
     </row>
-    <row r="441" spans="8:11">
+    <row r="441" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H441" t="s">
         <v>92</v>
       </c>
@@ -10684,7 +10461,7 @@
         <v>64212543</v>
       </c>
     </row>
-    <row r="442" spans="8:11">
+    <row r="442" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H442" t="s">
         <v>92</v>
       </c>
@@ -10698,7 +10475,7 @@
         <v>64212381</v>
       </c>
     </row>
-    <row r="443" spans="8:11">
+    <row r="443" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H443" t="s">
         <v>109</v>
       </c>
@@ -10712,7 +10489,7 @@
         <v>64114088</v>
       </c>
     </row>
-    <row r="444" spans="8:11">
+    <row r="444" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H444" t="s">
         <v>171</v>
       </c>
@@ -10726,7 +10503,7 @@
         <v>64223250</v>
       </c>
     </row>
-    <row r="445" spans="8:11">
+    <row r="445" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H445" t="s">
         <v>171</v>
       </c>
@@ -10740,7 +10517,7 @@
         <v>64214259</v>
       </c>
     </row>
-    <row r="446" spans="8:11">
+    <row r="446" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H446" t="s">
         <v>171</v>
       </c>
@@ -10754,7 +10531,7 @@
         <v>64214258</v>
       </c>
     </row>
-    <row r="447" spans="8:11">
+    <row r="447" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H447" t="s">
         <v>143</v>
       </c>
@@ -10768,7 +10545,7 @@
         <v>63742200</v>
       </c>
     </row>
-    <row r="448" spans="8:11">
+    <row r="448" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H448" t="s">
         <v>90</v>
       </c>
@@ -10782,7 +10559,7 @@
         <v>64606094</v>
       </c>
     </row>
-    <row r="449" spans="8:11">
+    <row r="449" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H449" t="s">
         <v>98</v>
       </c>
@@ -10796,7 +10573,7 @@
         <v>64287980</v>
       </c>
     </row>
-    <row r="450" spans="8:11">
+    <row r="450" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H450" t="s">
         <v>98</v>
       </c>
@@ -10810,7 +10587,7 @@
         <v>64257297</v>
       </c>
     </row>
-    <row r="451" spans="8:11">
+    <row r="451" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H451" t="s">
         <v>98</v>
       </c>
@@ -10824,7 +10601,7 @@
         <v>66097436</v>
       </c>
     </row>
-    <row r="452" spans="8:11">
+    <row r="452" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H452" t="s">
         <v>143</v>
       </c>
@@ -10838,7 +10615,7 @@
         <v>64330309</v>
       </c>
     </row>
-    <row r="453" spans="8:11">
+    <row r="453" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H453" t="s">
         <v>211</v>
       </c>
@@ -10852,7 +10629,7 @@
         <v>64846264</v>
       </c>
     </row>
-    <row r="454" spans="8:11">
+    <row r="454" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H454" t="s">
         <v>109</v>
       </c>
@@ -10866,7 +10643,7 @@
         <v>64753996</v>
       </c>
     </row>
-    <row r="455" spans="8:11">
+    <row r="455" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H455" t="s">
         <v>92</v>
       </c>
@@ -10880,7 +10657,7 @@
         <v>64778162</v>
       </c>
     </row>
-    <row r="456" spans="8:11">
+    <row r="456" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H456" t="s">
         <v>92</v>
       </c>
@@ -10894,7 +10671,7 @@
         <v>64778161</v>
       </c>
     </row>
-    <row r="457" spans="8:11">
+    <row r="457" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H457" t="s">
         <v>92</v>
       </c>
@@ -10908,7 +10685,7 @@
         <v>64808932</v>
       </c>
     </row>
-    <row r="458" spans="8:11">
+    <row r="458" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H458" t="s">
         <v>109</v>
       </c>
@@ -10922,7 +10699,7 @@
         <v>64789478</v>
       </c>
     </row>
-    <row r="459" spans="8:11">
+    <row r="459" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H459" t="s">
         <v>98</v>
       </c>
@@ -10936,7 +10713,7 @@
         <v>64912430</v>
       </c>
     </row>
-    <row r="460" spans="8:11">
+    <row r="460" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H460" t="s">
         <v>98</v>
       </c>
@@ -10950,7 +10727,7 @@
         <v>64971361</v>
       </c>
     </row>
-    <row r="461" spans="8:11">
+    <row r="461" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H461" t="s">
         <v>143</v>
       </c>
@@ -10964,7 +10741,7 @@
         <v>65145714</v>
       </c>
     </row>
-    <row r="462" spans="8:11">
+    <row r="462" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H462" t="s">
         <v>92</v>
       </c>
@@ -10978,7 +10755,7 @@
         <v>65081124</v>
       </c>
     </row>
-    <row r="463" spans="8:11">
+    <row r="463" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H463" t="s">
         <v>29</v>
       </c>
@@ -10992,7 +10769,7 @@
         <v>65181042</v>
       </c>
     </row>
-    <row r="464" spans="8:11">
+    <row r="464" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H464" t="s">
         <v>29</v>
       </c>
@@ -11006,7 +10783,7 @@
         <v>65179405</v>
       </c>
     </row>
-    <row r="465" spans="8:11">
+    <row r="465" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H465" t="s">
         <v>29</v>
       </c>
@@ -11020,7 +10797,7 @@
         <v>65566244</v>
       </c>
     </row>
-    <row r="466" spans="8:11">
+    <row r="466" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H466" t="s">
         <v>29</v>
       </c>
@@ -11034,7 +10811,7 @@
         <v>65566541</v>
       </c>
     </row>
-    <row r="467" spans="8:11">
+    <row r="467" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H467" t="s">
         <v>29</v>
       </c>
@@ -11048,7 +10825,7 @@
         <v>65656468</v>
       </c>
     </row>
-    <row r="468" spans="8:11">
+    <row r="468" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H468" t="s">
         <v>29</v>
       </c>
@@ -11062,7 +10839,7 @@
         <v>65657039</v>
       </c>
     </row>
-    <row r="469" spans="8:11">
+    <row r="469" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H469" t="s">
         <v>98</v>
       </c>
@@ -11076,7 +10853,7 @@
         <v>66217025</v>
       </c>
     </row>
-    <row r="470" spans="8:11">
+    <row r="470" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H470" t="s">
         <v>98</v>
       </c>
@@ -11090,7 +10867,7 @@
         <v>66214618</v>
       </c>
     </row>
-    <row r="471" spans="8:11">
+    <row r="471" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H471" t="s">
         <v>29</v>
       </c>
@@ -11104,7 +10881,7 @@
         <v>65935700</v>
       </c>
     </row>
-    <row r="472" spans="8:11">
+    <row r="472" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H472" t="s">
         <v>29</v>
       </c>
@@ -11118,7 +10895,7 @@
         <v>65934564</v>
       </c>
     </row>
-    <row r="473" spans="8:11">
+    <row r="473" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H473" t="s">
         <v>29</v>
       </c>
@@ -11132,7 +10909,7 @@
         <v>65933937</v>
       </c>
     </row>
-    <row r="474" spans="8:11">
+    <row r="474" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H474" t="s">
         <v>29</v>
       </c>
@@ -11146,7 +10923,7 @@
         <v>66046959</v>
       </c>
     </row>
-    <row r="475" spans="8:11">
+    <row r="475" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H475" t="s">
         <v>98</v>
       </c>
@@ -11160,7 +10937,7 @@
         <v>65969750</v>
       </c>
     </row>
-    <row r="476" spans="8:11">
+    <row r="476" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H476" t="s">
         <v>171</v>
       </c>
@@ -11174,7 +10951,7 @@
         <v>66358440</v>
       </c>
     </row>
-    <row r="477" spans="8:11">
+    <row r="477" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H477" t="s">
         <v>143</v>
       </c>
@@ -11188,7 +10965,7 @@
         <v>66417803</v>
       </c>
     </row>
-    <row r="478" spans="8:11">
+    <row r="478" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H478" t="s">
         <v>143</v>
       </c>
@@ -11202,7 +10979,7 @@
         <v>66417801</v>
       </c>
     </row>
-    <row r="479" spans="8:11">
+    <row r="479" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H479" t="s">
         <v>92</v>
       </c>
@@ -11216,7 +10993,7 @@
         <v>66357977</v>
       </c>
     </row>
-    <row r="480" spans="8:11">
+    <row r="480" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H480" t="s">
         <v>171</v>
       </c>
@@ -11230,7 +11007,7 @@
         <v>67191572</v>
       </c>
     </row>
-    <row r="481" spans="8:11">
+    <row r="481" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H481" t="s">
         <v>171</v>
       </c>
@@ -11244,7 +11021,7 @@
         <v>66546178</v>
       </c>
     </row>
-    <row r="482" spans="8:11">
+    <row r="482" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H482" t="s">
         <v>171</v>
       </c>
@@ -11258,7 +11035,7 @@
         <v>67627331</v>
       </c>
     </row>
-    <row r="483" spans="8:11">
+    <row r="483" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H483" t="s">
         <v>92</v>
       </c>
@@ -11272,7 +11049,7 @@
         <v>66778787</v>
       </c>
     </row>
-    <row r="484" spans="8:11">
+    <row r="484" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H484" t="s">
         <v>92</v>
       </c>
@@ -11286,7 +11063,7 @@
         <v>66778788</v>
       </c>
     </row>
-    <row r="485" spans="8:11">
+    <row r="485" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H485" t="s">
         <v>92</v>
       </c>
@@ -11300,7 +11077,7 @@
         <v>66778789</v>
       </c>
     </row>
-    <row r="486" spans="8:11">
+    <row r="486" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H486" t="s">
         <v>90</v>
       </c>
@@ -11314,7 +11091,7 @@
         <v>66896364</v>
       </c>
     </row>
-    <row r="487" spans="8:11">
+    <row r="487" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H487" t="s">
         <v>29</v>
       </c>
@@ -11328,7 +11105,7 @@
         <v>66607099</v>
       </c>
     </row>
-    <row r="488" spans="8:11">
+    <row r="488" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H488" t="s">
         <v>29</v>
       </c>
@@ -11342,7 +11119,7 @@
         <v>66864708</v>
       </c>
     </row>
-    <row r="489" spans="8:11">
+    <row r="489" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H489" t="s">
         <v>29</v>
       </c>
@@ -11356,7 +11133,7 @@
         <v>66850322</v>
       </c>
     </row>
-    <row r="490" spans="8:11">
+    <row r="490" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H490" t="s">
         <v>109</v>
       </c>
@@ -11370,7 +11147,7 @@
         <v>67268341</v>
       </c>
     </row>
-    <row r="491" spans="8:11">
+    <row r="491" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H491" t="s">
         <v>109</v>
       </c>
@@ -11384,7 +11161,7 @@
         <v>67268348</v>
       </c>
     </row>
-    <row r="492" spans="8:11">
+    <row r="492" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H492" t="s">
         <v>109</v>
       </c>
@@ -11398,7 +11175,7 @@
         <v>67268349</v>
       </c>
     </row>
-    <row r="493" spans="8:11">
+    <row r="493" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H493" t="s">
         <v>109</v>
       </c>
@@ -11412,7 +11189,7 @@
         <v>67268350</v>
       </c>
     </row>
-    <row r="494" spans="8:11">
+    <row r="494" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H494" t="s">
         <v>109</v>
       </c>
@@ -11426,7 +11203,7 @@
         <v>67272047</v>
       </c>
     </row>
-    <row r="495" spans="8:11">
+    <row r="495" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H495" t="s">
         <v>109</v>
       </c>
@@ -11440,7 +11217,7 @@
         <v>67272046</v>
       </c>
     </row>
-    <row r="496" spans="8:11">
+    <row r="496" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H496" t="s">
         <v>92</v>
       </c>
@@ -11454,7 +11231,7 @@
         <v>67438488</v>
       </c>
     </row>
-    <row r="497" spans="8:11">
+    <row r="497" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H497" t="s">
         <v>92</v>
       </c>
@@ -11468,7 +11245,7 @@
         <v>67438487</v>
       </c>
     </row>
-    <row r="498" spans="8:11">
+    <row r="498" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H498" t="s">
         <v>92</v>
       </c>
@@ -11482,7 +11259,7 @@
         <v>68253037</v>
       </c>
     </row>
-    <row r="499" spans="8:11">
+    <row r="499" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H499" t="s">
         <v>171</v>
       </c>
@@ -11496,7 +11273,7 @@
         <v>67891311</v>
       </c>
     </row>
-    <row r="500" spans="8:11">
+    <row r="500" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H500" t="s">
         <v>143</v>
       </c>
@@ -11510,7 +11287,7 @@
         <v>67900090</v>
       </c>
     </row>
-    <row r="501" spans="8:11">
+    <row r="501" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H501" t="s">
         <v>29</v>
       </c>
@@ -11524,7 +11301,7 @@
         <v>67630646</v>
       </c>
     </row>
-    <row r="502" spans="8:11">
+    <row r="502" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H502" t="s">
         <v>98</v>
       </c>
@@ -11538,7 +11315,7 @@
         <v>67974104</v>
       </c>
     </row>
-    <row r="503" spans="8:11">
+    <row r="503" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H503" t="s">
         <v>109</v>
       </c>
@@ -11552,7 +11329,7 @@
         <v>67989839</v>
       </c>
     </row>
-    <row r="504" spans="8:11">
+    <row r="504" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H504" t="s">
         <v>109</v>
       </c>
@@ -11566,7 +11343,7 @@
         <v>67988468</v>
       </c>
     </row>
-    <row r="505" spans="8:11">
+    <row r="505" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H505" t="s">
         <v>98</v>
       </c>
@@ -11580,7 +11357,7 @@
         <v>68466892</v>
       </c>
     </row>
-    <row r="506" spans="8:11">
+    <row r="506" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H506" t="s">
         <v>98</v>
       </c>
@@ -11594,7 +11371,7 @@
         <v>69040158</v>
       </c>
     </row>
-    <row r="507" spans="8:11">
+    <row r="507" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H507" t="s">
         <v>98</v>
       </c>
@@ -11608,7 +11385,7 @@
         <v>68462854</v>
       </c>
     </row>
-    <row r="508" spans="8:11">
+    <row r="508" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H508" t="s">
         <v>92</v>
       </c>
@@ -11622,7 +11399,7 @@
         <v>68677002</v>
       </c>
     </row>
-    <row r="509" spans="8:11">
+    <row r="509" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H509" t="s">
         <v>171</v>
       </c>
@@ -11636,7 +11413,7 @@
         <v>68880617</v>
       </c>
     </row>
-    <row r="510" spans="8:11">
+    <row r="510" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H510" t="s">
         <v>98</v>
       </c>
@@ -11650,7 +11427,7 @@
         <v>68934411</v>
       </c>
     </row>
-    <row r="511" spans="8:11">
+    <row r="511" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H511" t="s">
         <v>98</v>
       </c>
@@ -11664,7 +11441,7 @@
         <v>68924611</v>
       </c>
     </row>
-    <row r="512" spans="8:11">
+    <row r="512" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H512" t="s">
         <v>92</v>
       </c>
@@ -11678,7 +11455,7 @@
         <v>69039437</v>
       </c>
     </row>
-    <row r="513" spans="8:11">
+    <row r="513" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H513" t="s">
         <v>92</v>
       </c>
@@ -11692,7 +11469,7 @@
         <v>69039778</v>
       </c>
     </row>
-    <row r="514" spans="8:11">
+    <row r="514" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H514" t="s">
         <v>58</v>
       </c>
@@ -11706,7 +11483,7 @@
         <v>69279032</v>
       </c>
     </row>
-    <row r="515" spans="8:11">
+    <row r="515" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H515" t="s">
         <v>92</v>
       </c>
@@ -11720,7 +11497,7 @@
         <v>68938743</v>
       </c>
     </row>
-    <row r="516" spans="8:11">
+    <row r="516" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H516" t="s">
         <v>58</v>
       </c>
@@ -11734,7 +11511,7 @@
         <v>69772629</v>
       </c>
     </row>
-    <row r="517" spans="8:11">
+    <row r="517" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H517" t="s">
         <v>58</v>
       </c>
@@ -11748,7 +11525,7 @@
         <v>69772627</v>
       </c>
     </row>
-    <row r="518" spans="8:11">
+    <row r="518" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H518" t="s">
         <v>58</v>
       </c>
@@ -11762,7 +11539,7 @@
         <v>69772625</v>
       </c>
     </row>
-    <row r="519" spans="8:11">
+    <row r="519" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H519" t="s">
         <v>98</v>
       </c>
@@ -11776,7 +11553,7 @@
         <v>69292187</v>
       </c>
     </row>
-    <row r="520" spans="8:11">
+    <row r="520" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H520" t="s">
         <v>98</v>
       </c>
@@ -11790,7 +11567,7 @@
         <v>69292186</v>
       </c>
     </row>
-    <row r="521" spans="8:11">
+    <row r="521" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H521" t="s">
         <v>98</v>
       </c>
@@ -11804,7 +11581,7 @@
         <v>69292185</v>
       </c>
     </row>
-    <row r="522" spans="8:11">
+    <row r="522" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H522" t="s">
         <v>58</v>
       </c>
@@ -11818,7 +11595,7 @@
         <v>69096297</v>
       </c>
     </row>
-    <row r="523" spans="8:11">
+    <row r="523" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H523" t="s">
         <v>58</v>
       </c>
@@ -11832,7 +11609,7 @@
         <v>69096296</v>
       </c>
     </row>
-    <row r="524" spans="8:11">
+    <row r="524" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H524" t="s">
         <v>143</v>
       </c>
@@ -11846,7 +11623,7 @@
         <v>69594684</v>
       </c>
     </row>
-    <row r="525" spans="8:11">
+    <row r="525" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H525" t="s">
         <v>98</v>
       </c>
@@ -11860,7 +11637,7 @@
         <v>70204974</v>
       </c>
     </row>
-    <row r="526" spans="8:11">
+    <row r="526" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H526" t="s">
         <v>98</v>
       </c>
@@ -11874,7 +11651,7 @@
         <v>70204975</v>
       </c>
     </row>
-    <row r="527" spans="8:11">
+    <row r="527" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H527" t="s">
         <v>143</v>
       </c>
@@ -11888,7 +11665,7 @@
         <v>69767288</v>
       </c>
     </row>
-    <row r="528" spans="8:11">
+    <row r="528" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H528" t="s">
         <v>98</v>
       </c>
@@ -11902,7 +11679,7 @@
         <v>69766464</v>
       </c>
     </row>
-    <row r="529" spans="8:11">
+    <row r="529" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H529" t="s">
         <v>98</v>
       </c>
@@ -11916,7 +11693,7 @@
         <v>69803799</v>
       </c>
     </row>
-    <row r="530" spans="8:11">
+    <row r="530" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H530" t="s">
         <v>143</v>
       </c>
@@ -11930,7 +11707,7 @@
         <v>70251147</v>
       </c>
     </row>
-    <row r="531" spans="8:11">
+    <row r="531" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H531" t="s">
         <v>171</v>
       </c>
@@ -11944,7 +11721,7 @@
         <v>69770093</v>
       </c>
     </row>
-    <row r="532" spans="8:11">
+    <row r="532" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H532" t="s">
         <v>92</v>
       </c>
@@ -11958,7 +11735,7 @@
         <v>70205079</v>
       </c>
     </row>
-    <row r="533" spans="8:11">
+    <row r="533" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H533" t="s">
         <v>98</v>
       </c>
@@ -11972,7 +11749,7 @@
         <v>70530577</v>
       </c>
     </row>
-    <row r="534" spans="8:11">
+    <row r="534" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H534" t="s">
         <v>98</v>
       </c>
@@ -11986,7 +11763,7 @@
         <v>70530576</v>
       </c>
     </row>
-    <row r="535" spans="8:11">
+    <row r="535" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H535" t="s">
         <v>109</v>
       </c>
@@ -12000,7 +11777,7 @@
         <v>71030052</v>
       </c>
     </row>
-    <row r="536" spans="8:11">
+    <row r="536" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H536" t="s">
         <v>115</v>
       </c>
@@ -12014,7 +11791,7 @@
         <v>70770186</v>
       </c>
     </row>
-    <row r="537" spans="8:11">
+    <row r="537" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H537" t="s">
         <v>115</v>
       </c>
@@ -12028,7 +11805,7 @@
         <v>71173111</v>
       </c>
     </row>
-    <row r="538" spans="8:11">
+    <row r="538" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H538" t="s">
         <v>115</v>
       </c>
@@ -12042,7 +11819,7 @@
         <v>71156871</v>
       </c>
     </row>
-    <row r="539" spans="8:11">
+    <row r="539" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H539" t="s">
         <v>115</v>
       </c>
@@ -12056,7 +11833,7 @@
         <v>71291488</v>
       </c>
     </row>
-    <row r="540" spans="8:11">
+    <row r="540" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I540">
         <v>71042279</v>
       </c>
@@ -12067,7 +11844,7 @@
         <v>71042279</v>
       </c>
     </row>
-    <row r="541" spans="8:11">
+    <row r="541" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H541" t="s">
         <v>115</v>
       </c>
@@ -12081,7 +11858,7 @@
         <v>71947627</v>
       </c>
     </row>
-    <row r="542" spans="8:11">
+    <row r="542" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H542" t="s">
         <v>115</v>
       </c>
@@ -12095,7 +11872,7 @@
         <v>72182444</v>
       </c>
     </row>
-    <row r="543" spans="8:11">
+    <row r="543" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H543" t="s">
         <v>115</v>
       </c>
@@ -12109,7 +11886,7 @@
         <v>72300747</v>
       </c>
     </row>
-    <row r="544" spans="8:11">
+    <row r="544" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H544" t="s">
         <v>115</v>
       </c>
@@ -12123,7 +11900,7 @@
         <v>72417582</v>
       </c>
     </row>
-    <row r="545" spans="8:11">
+    <row r="545" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H545" t="s">
         <v>115</v>
       </c>
@@ -12137,7 +11914,7 @@
         <v>72614935</v>
       </c>
     </row>
-    <row r="546" spans="8:11">
+    <row r="546" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H546" t="s">
         <v>115</v>
       </c>
@@ -12151,7 +11928,7 @@
         <v>72614936</v>
       </c>
     </row>
-    <row r="547" spans="8:11">
+    <row r="547" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H547" t="s">
         <v>115</v>
       </c>
@@ -12165,7 +11942,7 @@
         <v>72614937</v>
       </c>
     </row>
-    <row r="548" spans="8:11">
+    <row r="548" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H548" t="s">
         <v>92</v>
       </c>
@@ -12179,7 +11956,7 @@
         <v>73226633</v>
       </c>
     </row>
-    <row r="549" spans="8:11">
+    <row r="549" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H549" t="s">
         <v>92</v>
       </c>
@@ -12193,7 +11970,7 @@
         <v>73226632</v>
       </c>
     </row>
-    <row r="550" spans="8:11">
+    <row r="550" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H550" t="s">
         <v>143</v>
       </c>
@@ -12207,7 +11984,7 @@
         <v>73316683</v>
       </c>
     </row>
-    <row r="551" spans="8:11">
+    <row r="551" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H551" t="s">
         <v>143</v>
       </c>
@@ -12221,7 +11998,7 @@
         <v>73316684</v>
       </c>
     </row>
-    <row r="552" spans="8:11">
+    <row r="552" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H552" t="s">
         <v>143</v>
       </c>
@@ -12235,7 +12012,7 @@
         <v>73316685</v>
       </c>
     </row>
-    <row r="553" spans="8:11">
+    <row r="553" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H553" t="s">
         <v>115</v>
       </c>
@@ -12249,7 +12026,7 @@
         <v>72699936</v>
       </c>
     </row>
-    <row r="554" spans="8:11">
+    <row r="554" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H554" t="s">
         <v>115</v>
       </c>
@@ -12263,7 +12040,7 @@
         <v>72699935</v>
       </c>
     </row>
-    <row r="555" spans="8:11">
+    <row r="555" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H555" t="s">
         <v>115</v>
       </c>
@@ -12277,7 +12054,7 @@
         <v>72828733</v>
       </c>
     </row>
-    <row r="556" spans="8:11">
+    <row r="556" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H556" t="s">
         <v>115</v>
       </c>
@@ -12291,7 +12068,7 @@
         <v>72828734</v>
       </c>
     </row>
-    <row r="557" spans="8:11">
+    <row r="557" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H557" t="s">
         <v>90</v>
       </c>
@@ -12305,7 +12082,7 @@
         <v>72683872</v>
       </c>
     </row>
-    <row r="558" spans="8:11">
+    <row r="558" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H558" t="s">
         <v>58</v>
       </c>
@@ -12319,7 +12096,7 @@
         <v>72910681</v>
       </c>
     </row>
-    <row r="559" spans="8:11">
+    <row r="559" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H559" t="s">
         <v>58</v>
       </c>
@@ -12333,7 +12110,7 @@
         <v>72910683</v>
       </c>
     </row>
-    <row r="560" spans="8:11">
+    <row r="560" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H560" t="s">
         <v>98</v>
       </c>
@@ -12347,7 +12124,7 @@
         <v>73523448</v>
       </c>
     </row>
-    <row r="561" spans="8:11">
+    <row r="561" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H561" t="s">
         <v>58</v>
       </c>
@@ -12361,7 +12138,7 @@
         <v>73461995</v>
       </c>
     </row>
-    <row r="562" spans="8:11">
+    <row r="562" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H562" t="s">
         <v>98</v>
       </c>
@@ -12375,7 +12152,7 @@
         <v>73956460</v>
       </c>
     </row>
-    <row r="563" spans="8:11">
+    <row r="563" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H563" t="s">
         <v>98</v>
       </c>
@@ -12389,7 +12166,7 @@
         <v>73956461</v>
       </c>
     </row>
-    <row r="564" spans="8:11">
+    <row r="564" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H564" t="s">
         <v>98</v>
       </c>
@@ -12403,7 +12180,7 @@
         <v>73956459</v>
       </c>
     </row>
-    <row r="565" spans="8:11">
+    <row r="565" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H565" t="s">
         <v>58</v>
       </c>
@@ -12417,7 +12194,7 @@
         <v>74685916</v>
       </c>
     </row>
-    <row r="566" spans="8:11">
+    <row r="566" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H566" t="s">
         <v>98</v>
       </c>
@@ -12431,7 +12208,7 @@
         <v>73975553</v>
       </c>
     </row>
-    <row r="567" spans="8:11">
+    <row r="567" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H567" t="s">
         <v>98</v>
       </c>
@@ -12445,7 +12222,7 @@
         <v>73952843</v>
       </c>
     </row>
-    <row r="568" spans="8:11">
+    <row r="568" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H568" t="s">
         <v>115</v>
       </c>
@@ -12459,7 +12236,7 @@
         <v>74550323</v>
       </c>
     </row>
-    <row r="569" spans="8:11">
+    <row r="569" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H569" t="s">
         <v>98</v>
       </c>
@@ -12473,7 +12250,7 @@
         <v>75989703</v>
       </c>
     </row>
-    <row r="570" spans="8:11">
+    <row r="570" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H570" t="s">
         <v>143</v>
       </c>
@@ -12487,7 +12264,7 @@
         <v>74693807</v>
       </c>
     </row>
-    <row r="571" spans="8:11">
+    <row r="571" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H571" t="s">
         <v>143</v>
       </c>
@@ -12501,7 +12278,7 @@
         <v>73893263</v>
       </c>
     </row>
-    <row r="572" spans="8:11">
+    <row r="572" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H572" t="s">
         <v>143</v>
       </c>
@@ -12515,7 +12292,7 @@
         <v>74884452</v>
       </c>
     </row>
-    <row r="573" spans="8:11">
+    <row r="573" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H573" t="s">
         <v>98</v>
       </c>
@@ -12529,7 +12306,7 @@
         <v>74826973</v>
       </c>
     </row>
-    <row r="574" spans="8:11">
+    <row r="574" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H574" t="s">
         <v>98</v>
       </c>
@@ -12543,7 +12320,7 @@
         <v>74826974</v>
       </c>
     </row>
-    <row r="575" spans="8:11">
+    <row r="575" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H575" t="s">
         <v>90</v>
       </c>
@@ -12557,7 +12334,7 @@
         <v>75077119</v>
       </c>
     </row>
-    <row r="576" spans="8:11">
+    <row r="576" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H576" t="s">
         <v>92</v>
       </c>
@@ -12571,7 +12348,7 @@
         <v>78867502</v>
       </c>
     </row>
-    <row r="577" spans="8:11">
+    <row r="577" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H577" t="s">
         <v>92</v>
       </c>
@@ -12585,7 +12362,7 @@
         <v>80192305</v>
       </c>
     </row>
-    <row r="578" spans="8:11">
+    <row r="578" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H578" t="s">
         <v>92</v>
       </c>
@@ -12599,7 +12376,7 @@
         <v>75741354</v>
       </c>
     </row>
-    <row r="579" spans="8:11">
+    <row r="579" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H579" t="s">
         <v>143</v>
       </c>
@@ -12613,7 +12390,7 @@
         <v>78625461</v>
       </c>
     </row>
-    <row r="580" spans="8:11">
+    <row r="580" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H580" t="s">
         <v>92</v>
       </c>
@@ -12627,7 +12404,7 @@
         <v>76375598</v>
       </c>
     </row>
-    <row r="581" spans="8:11">
+    <row r="581" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H581" t="s">
         <v>92</v>
       </c>
@@ -12641,7 +12418,7 @@
         <v>76375597</v>
       </c>
     </row>
-    <row r="582" spans="8:11">
+    <row r="582" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H582" t="s">
         <v>92</v>
       </c>
@@ -12655,7 +12432,7 @@
         <v>76374400</v>
       </c>
     </row>
-    <row r="583" spans="8:11">
+    <row r="583" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H583" t="s">
         <v>92</v>
       </c>
@@ -12669,7 +12446,7 @@
         <v>76374401</v>
       </c>
     </row>
-    <row r="584" spans="8:11">
+    <row r="584" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H584" t="s">
         <v>92</v>
       </c>
@@ -12683,7 +12460,7 @@
         <v>76241042</v>
       </c>
     </row>
-    <row r="585" spans="8:11">
+    <row r="585" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H585" t="s">
         <v>90</v>
       </c>
@@ -12697,7 +12474,7 @@
         <v>76533940</v>
       </c>
     </row>
-    <row r="586" spans="8:11">
+    <row r="586" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H586" t="s">
         <v>92</v>
       </c>
@@ -12711,7 +12488,7 @@
         <v>77463489</v>
       </c>
     </row>
-    <row r="587" spans="8:11">
+    <row r="587" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H587" t="s">
         <v>92</v>
       </c>
@@ -12725,7 +12502,7 @@
         <v>77463490</v>
       </c>
     </row>
-    <row r="588" spans="8:11">
+    <row r="588" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H588" t="s">
         <v>58</v>
       </c>
@@ -12739,7 +12516,7 @@
         <v>78907466</v>
       </c>
     </row>
-    <row r="589" spans="8:11">
+    <row r="589" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H589" t="s">
         <v>58</v>
       </c>
@@ -12753,7 +12530,7 @@
         <v>78907465</v>
       </c>
     </row>
-    <row r="590" spans="8:11">
+    <row r="590" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H590" t="s">
         <v>58</v>
       </c>
@@ -12767,7 +12544,7 @@
         <v>78903848</v>
       </c>
     </row>
-    <row r="591" spans="8:11">
+    <row r="591" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H591" t="s">
         <v>58</v>
       </c>
@@ -12781,7 +12558,7 @@
         <v>78903849</v>
       </c>
     </row>
-    <row r="592" spans="8:11">
+    <row r="592" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H592" t="s">
         <v>58</v>
       </c>
@@ -12795,7 +12572,7 @@
         <v>78621004</v>
       </c>
     </row>
-    <row r="593" spans="8:11">
+    <row r="593" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H593" t="s">
         <v>92</v>
       </c>
@@ -12809,7 +12586,7 @@
         <v>80629877</v>
       </c>
     </row>
-    <row r="594" spans="8:11">
+    <row r="594" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H594" t="s">
         <v>92</v>
       </c>
@@ -12823,7 +12600,7 @@
         <v>80629881</v>
       </c>
     </row>
-    <row r="595" spans="8:11">
+    <row r="595" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H595" s="7" t="s">
         <v>98</v>
       </c>
@@ -12831,13 +12608,13 @@
         <v>80915325</v>
       </c>
       <c r="J595" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="K595" s="6">
         <v>80915325</v>
       </c>
     </row>
-    <row r="596" spans="8:11">
+    <row r="596" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H596" s="7" t="s">
         <v>98</v>
       </c>
@@ -12845,41 +12622,41 @@
         <v>80915326</v>
       </c>
       <c r="J596" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K596" s="6">
         <v>80915326</v>
       </c>
     </row>
-    <row r="597" spans="8:11">
+    <row r="597" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H597" s="7" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="I597" s="6">
         <v>80953015</v>
       </c>
       <c r="J597" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="K597" s="6">
         <v>80953015</v>
       </c>
     </row>
-    <row r="598" spans="8:11">
+    <row r="598" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H598" s="7" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="I598" s="6">
         <v>80953016</v>
       </c>
       <c r="J598" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="K598" s="6">
         <v>80953016</v>
       </c>
     </row>
-    <row r="599" spans="8:11">
+    <row r="599" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H599" s="7" t="s">
         <v>29</v>
       </c>
@@ -12893,7 +12670,7 @@
         <v>81675750</v>
       </c>
     </row>
-    <row r="600" spans="8:11">
+    <row r="600" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H600" s="7" t="s">
         <v>171</v>
       </c>
@@ -12901,27 +12678,27 @@
         <v>81638306</v>
       </c>
       <c r="J600" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="K600" s="6">
         <v>81638306</v>
       </c>
     </row>
-    <row r="601" spans="8:11">
+    <row r="601" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H601" s="7" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="I601" s="6">
         <v>81918457</v>
       </c>
       <c r="J601" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K601" s="6">
         <v>81918457</v>
       </c>
     </row>
-    <row r="602" spans="8:11">
+    <row r="602" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H602" s="7" t="s">
         <v>29</v>
       </c>
@@ -12929,13 +12706,13 @@
         <v>81538523</v>
       </c>
       <c r="J602" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="K602" s="6">
         <v>81538523</v>
       </c>
     </row>
-    <row r="603" spans="8:11">
+    <row r="603" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H603" s="7" t="s">
         <v>171</v>
       </c>
@@ -12943,13 +12720,13 @@
         <v>79040263</v>
       </c>
       <c r="J603" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K603" s="6">
         <v>79040263</v>
       </c>
     </row>
-    <row r="604" spans="8:11">
+    <row r="604" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H604" s="7" t="s">
         <v>211</v>
       </c>
@@ -12957,13 +12734,13 @@
         <v>79475749</v>
       </c>
       <c r="J604" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="K604" s="6">
         <v>79475749</v>
       </c>
     </row>
-    <row r="605" spans="8:11">
+    <row r="605" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H605" s="7" t="s">
         <v>143</v>
       </c>
@@ -12971,13 +12748,13 @@
         <v>79944232</v>
       </c>
       <c r="J605" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="K605" s="6">
         <v>79944232</v>
       </c>
     </row>
-    <row r="606" spans="8:11">
+    <row r="606" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H606" s="7" t="s">
         <v>211</v>
       </c>
@@ -12985,13 +12762,13 @@
         <v>80460979</v>
       </c>
       <c r="J606" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="K606" s="6">
         <v>80460979</v>
       </c>
     </row>
-    <row r="607" spans="8:11">
+    <row r="607" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H607" s="7" t="s">
         <v>143</v>
       </c>
@@ -12999,15 +12776,15 @@
         <v>81340922</v>
       </c>
       <c r="J607" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="K607" s="6">
         <v>81340922</v>
       </c>
     </row>
-    <row r="608" spans="8:11">
+    <row r="608" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H608" s="7" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="I608" s="6">
         <v>38157908</v>
@@ -13019,9 +12796,9 @@
         <v>38157908</v>
       </c>
     </row>
-    <row r="609" spans="8:11">
+    <row r="609" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H609" s="7" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="I609" s="6">
         <v>41662266</v>
@@ -13033,7 +12810,7 @@
         <v>41662266</v>
       </c>
     </row>
-    <row r="610" spans="8:11">
+    <row r="610" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H610" s="7" t="s">
         <v>29</v>
       </c>
@@ -13041,13 +12818,13 @@
         <v>81988924</v>
       </c>
       <c r="J610" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="K610" s="6">
         <v>81988924</v>
       </c>
     </row>
-    <row r="611" spans="8:11">
+    <row r="611" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H611" s="7" t="s">
         <v>29</v>
       </c>
@@ -13055,7 +12832,7 @@
         <v>82014131</v>
       </c>
       <c r="J611" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="K611" s="6">
         <v>82014131</v>
@@ -13068,32 +12845,32 @@
     </sortState>
   </autoFilter>
   <mergeCells count="1">
-    <mergeCell ref="A201:C201"/>
+    <mergeCell ref="A200:C200"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A78:A198 A203:A1048576 A1:A56">
-    <cfRule type="duplicateValues" dxfId="28" priority="11"/>
+  <conditionalFormatting sqref="A77:A197 A202:A1048576 A1:A55">
+    <cfRule type="duplicateValues" dxfId="9" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A200:A1048576 A1:A61 A65:A198">
-    <cfRule type="duplicateValues" dxfId="27" priority="6"/>
+  <conditionalFormatting sqref="A199:A1048576 A1:A60 A64:A197">
+    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A203:A1048576 A1:A61 A65:A198">
-    <cfRule type="duplicateValues" dxfId="26" priority="22"/>
+  <conditionalFormatting sqref="A202:A1048576 A1:A60 A64:A197">
+    <cfRule type="duplicateValues" dxfId="7" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="duplicateValues" dxfId="25" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K595:K611">
-    <cfRule type="duplicateValues" dxfId="24" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A62:A63">
-    <cfRule type="duplicateValues" dxfId="23" priority="3"/>
+  <conditionalFormatting sqref="A61:A62">
+    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A64">
-    <cfRule type="duplicateValues" dxfId="22" priority="2"/>
+  <conditionalFormatting sqref="A63">
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -13103,14 +12880,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A13:C27"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="1:3" ht="20.25">
+    <row r="13" spans="1:3" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>640</v>
       </c>
@@ -13121,7 +12898,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>13101217</v>
       </c>
@@ -13132,7 +12909,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>4125377</v>
       </c>
@@ -13143,7 +12920,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>26426530</v>
       </c>
@@ -13154,7 +12931,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>43252471</v>
       </c>
@@ -13165,7 +12942,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>64789478</v>
       </c>
@@ -13176,7 +12953,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>71030052</v>
       </c>
@@ -13187,7 +12964,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>11229298</v>
       </c>
@@ -13198,7 +12975,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="21" spans="1:3" hidden="1">
+    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>75077119</v>
       </c>
@@ -13209,7 +12986,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>42519088</v>
       </c>
@@ -13220,7 +12997,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>17579394</v>
       </c>
@@ -13231,7 +13008,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>53569741</v>
       </c>
@@ -13242,7 +13019,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>53583387</v>
       </c>
@@ -13253,7 +13030,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>12439390</v>
       </c>
@@ -13264,7 +13041,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>14107560</v>
       </c>
@@ -13283,10 +13060,10 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A26:A27 A14:A24">
-    <cfRule type="duplicateValues" dxfId="30" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A25">
-    <cfRule type="duplicateValues" dxfId="29" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/이슈제품.xlsx
+++ b/data/이슈제품.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Music\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OA\Desktop\쿠팡업로드\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7814E907-B26F-48F9-8228-1841FDB2D218}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$13:$C$13</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1630" uniqueCount="670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1640" uniqueCount="673">
   <si>
     <t>오아디머무드등-화이트</t>
   </si>
@@ -2072,14 +2073,26 @@
   </si>
   <si>
     <t>협의, 11/4 입고예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>협의, 11/12 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>단종</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조절, 11월 3째주 예정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2198,7 +2211,77 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="17">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2574,9 +2657,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K611"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37.875" bestFit="1" customWidth="1"/>
@@ -2588,7 +2671,7 @@
     <col min="11" max="12" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>23</v>
       </c>
@@ -2611,7 +2694,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>4152606</v>
       </c>
@@ -2634,7 +2717,7 @@
         <v>3636925</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>12263239</v>
       </c>
@@ -2657,7 +2740,7 @@
         <v>3636926</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>68880617</v>
       </c>
@@ -2680,7 +2763,7 @@
         <v>3636927</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>65933937</v>
       </c>
@@ -2703,7 +2786,7 @@
         <v>39415252</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>76375597</v>
       </c>
@@ -2726,7 +2809,7 @@
         <v>19213859</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11">
       <c r="A7">
         <v>60015061</v>
       </c>
@@ -2749,7 +2832,7 @@
         <v>20342327</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11">
       <c r="A8">
         <v>50725354</v>
       </c>
@@ -2772,7 +2855,7 @@
         <v>13004238</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11">
       <c r="A9">
         <v>50153946</v>
       </c>
@@ -2795,7 +2878,7 @@
         <v>20341619</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11">
       <c r="A10">
         <v>75741354</v>
       </c>
@@ -2818,7 +2901,7 @@
         <v>11092035</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11">
       <c r="A11">
         <v>15414324</v>
       </c>
@@ -2841,7 +2924,7 @@
         <v>40852278</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11">
       <c r="A12">
         <v>75077119</v>
       </c>
@@ -2864,7 +2947,7 @@
         <v>29266932</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11">
       <c r="A13">
         <v>51623281</v>
       </c>
@@ -2887,7 +2970,7 @@
         <v>12586373</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11">
       <c r="A14">
         <v>51989601</v>
       </c>
@@ -2910,7 +2993,7 @@
         <v>11055651</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11">
       <c r="A15">
         <v>11192166</v>
       </c>
@@ -2933,7 +3016,7 @@
         <v>38659485</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11">
       <c r="A16">
         <v>15812678</v>
       </c>
@@ -2956,7 +3039,7 @@
         <v>9567647</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11">
       <c r="A17">
         <v>12091621</v>
       </c>
@@ -2979,7 +3062,7 @@
         <v>40180424</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11">
       <c r="A18">
         <v>12143584</v>
       </c>
@@ -3002,7 +3085,7 @@
         <v>39228155</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11">
       <c r="A19">
         <v>11192167</v>
       </c>
@@ -3025,7 +3108,7 @@
         <v>38407975</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11">
       <c r="A20">
         <v>12143581</v>
       </c>
@@ -3048,7 +3131,7 @@
         <v>38545387</v>
       </c>
     </row>
-    <row r="21" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" s="3" customFormat="1">
       <c r="A21">
         <v>11192165</v>
       </c>
@@ -3071,7 +3154,7 @@
         <v>18816827</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11">
       <c r="A22">
         <v>11192163</v>
       </c>
@@ -3094,7 +3177,7 @@
         <v>39278162</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11">
       <c r="A23">
         <v>11291291</v>
       </c>
@@ -3117,7 +3200,7 @@
         <v>13100374</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11">
       <c r="A24">
         <v>16171214</v>
       </c>
@@ -3140,7 +3223,7 @@
         <v>10855225</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11">
       <c r="A25">
         <v>12218847</v>
       </c>
@@ -3163,7 +3246,7 @@
         <v>38490171</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11">
       <c r="A26">
         <v>15838517</v>
       </c>
@@ -3186,7 +3269,7 @@
         <v>38490170</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11">
       <c r="A27">
         <v>12673238</v>
       </c>
@@ -3209,7 +3292,7 @@
         <v>38417027</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11">
       <c r="A28">
         <v>37790051</v>
       </c>
@@ -3232,7 +3315,7 @@
         <v>13099542</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11">
       <c r="A29">
         <v>37594934</v>
       </c>
@@ -3255,7 +3338,7 @@
         <v>10324264</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11">
       <c r="A30">
         <v>15702671</v>
       </c>
@@ -3278,7 +3361,7 @@
         <v>39229235</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11">
       <c r="A31">
         <v>39071990</v>
       </c>
@@ -3301,7 +3384,7 @@
         <v>12775098</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11">
       <c r="A32">
         <v>52204284</v>
       </c>
@@ -3324,7 +3407,7 @@
         <v>12775097</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11">
       <c r="A33">
         <v>39006854</v>
       </c>
@@ -3347,7 +3430,7 @@
         <v>12775096</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11">
       <c r="A34">
         <v>39006857</v>
       </c>
@@ -3370,7 +3453,7 @@
         <v>13151160</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11">
       <c r="A35">
         <v>39006855</v>
       </c>
@@ -3393,7 +3476,7 @@
         <v>13151158</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11">
       <c r="A36">
         <v>51883980</v>
       </c>
@@ -3416,7 +3499,7 @@
         <v>35403063</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11">
       <c r="A37">
         <v>52578670</v>
       </c>
@@ -3439,7 +3522,7 @@
         <v>13473750</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11">
       <c r="A38">
         <v>52155531</v>
       </c>
@@ -3462,7 +3545,7 @@
         <v>17014694</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11">
       <c r="A39">
         <v>15831347</v>
       </c>
@@ -3485,7 +3568,7 @@
         <v>17014693</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11">
       <c r="A40">
         <v>32548061</v>
       </c>
@@ -3508,7 +3591,7 @@
         <v>13101218</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11">
       <c r="A41">
         <v>35876282</v>
       </c>
@@ -3531,7 +3614,7 @@
         <v>13101217</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11">
       <c r="A42">
         <v>16805855</v>
       </c>
@@ -3554,7 +3637,7 @@
         <v>16981939</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11">
       <c r="A43">
         <v>55381383</v>
       </c>
@@ -3577,7 +3660,7 @@
         <v>12846219</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11">
       <c r="A44">
         <v>55449180</v>
       </c>
@@ -3600,7 +3683,7 @@
         <v>17398556</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11">
       <c r="A45">
         <v>55384739</v>
       </c>
@@ -3623,7 +3706,7 @@
         <v>16972627</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11">
       <c r="A46">
         <v>55389336</v>
       </c>
@@ -3646,7 +3729,7 @@
         <v>12846215</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11">
       <c r="A47">
         <v>55609278</v>
       </c>
@@ -3669,7 +3752,7 @@
         <v>39663616</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11">
       <c r="A48">
         <v>71042279</v>
       </c>
@@ -3692,7 +3775,7 @@
         <v>37843037</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11">
       <c r="A49">
         <v>67630646</v>
       </c>
@@ -3715,7 +3798,7 @@
         <v>12465755</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11">
       <c r="A50">
         <v>64971361</v>
       </c>
@@ -3738,7 +3821,7 @@
         <v>11671481</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11">
       <c r="A51">
         <v>62421723</v>
       </c>
@@ -3761,7 +3844,7 @@
         <v>12685386</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11">
       <c r="A52">
         <v>62374813</v>
       </c>
@@ -3784,7 +3867,7 @@
         <v>12674974</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11">
       <c r="A53">
         <v>68462854</v>
       </c>
@@ -3807,7 +3890,7 @@
         <v>12674973</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11">
       <c r="A54">
         <v>64114088</v>
       </c>
@@ -3830,7 +3913,7 @@
         <v>27515992</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11">
       <c r="A55">
         <v>19213859</v>
       </c>
@@ -3853,7 +3936,7 @@
         <v>18928667</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11">
       <c r="A56">
         <v>13004238</v>
       </c>
@@ -3876,7 +3959,7 @@
         <v>14218803</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11">
       <c r="A57">
         <v>11229298</v>
       </c>
@@ -3899,7 +3982,7 @@
         <v>14218802</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" ht="82.5">
       <c r="A58">
         <v>37161537</v>
       </c>
@@ -3922,7 +4005,7 @@
         <v>14473529</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11">
       <c r="A59">
         <v>13745117</v>
       </c>
@@ -3945,7 +4028,7 @@
         <v>25512595</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11">
       <c r="A60">
         <v>73226633</v>
       </c>
@@ -3968,7 +4051,7 @@
         <v>25433097</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11">
       <c r="A61" s="6">
         <v>80915325</v>
       </c>
@@ -3991,7 +4074,7 @@
         <v>50012601</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11">
       <c r="A62" s="6">
         <v>80915326</v>
       </c>
@@ -4014,7 +4097,7 @@
         <v>52204284</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11">
       <c r="A63">
         <v>73893263</v>
       </c>
@@ -4037,7 +4120,7 @@
         <v>52155531</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11">
       <c r="A64">
         <v>5332789</v>
       </c>
@@ -4060,7 +4143,7 @@
         <v>10814871</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11">
       <c r="A65">
         <v>51016959</v>
       </c>
@@ -4083,7 +4166,16 @@
         <v>31792560</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11">
+      <c r="A66">
+        <v>73226633</v>
+      </c>
+      <c r="B66" t="s">
+        <v>573</v>
+      </c>
+      <c r="C66" t="s">
+        <v>670</v>
+      </c>
       <c r="H66" t="s">
         <v>94</v>
       </c>
@@ -4097,7 +4189,16 @@
         <v>10694343</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11">
+      <c r="A67">
+        <v>62498583</v>
+      </c>
+      <c r="B67" t="s">
+        <v>457</v>
+      </c>
+      <c r="C67" t="s">
+        <v>672</v>
+      </c>
       <c r="H67" t="s">
         <v>98</v>
       </c>
@@ -4111,7 +4212,16 @@
         <v>43431417</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11">
+      <c r="A68">
+        <v>69766464</v>
+      </c>
+      <c r="B68" t="s">
+        <v>553</v>
+      </c>
+      <c r="C68" t="s">
+        <v>672</v>
+      </c>
       <c r="H68" t="s">
         <v>98</v>
       </c>
@@ -4125,7 +4235,7 @@
         <v>10978754</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11">
       <c r="H69" t="s">
         <v>98</v>
       </c>
@@ -4139,7 +4249,7 @@
         <v>10974363</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11">
       <c r="H70" t="s">
         <v>98</v>
       </c>
@@ -4153,7 +4263,7 @@
         <v>39376011</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11">
       <c r="H71" t="s">
         <v>98</v>
       </c>
@@ -4167,7 +4277,7 @@
         <v>38310913</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11">
       <c r="H72" t="s">
         <v>98</v>
       </c>
@@ -4181,7 +4291,7 @@
         <v>40639939</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11">
       <c r="H73" t="s">
         <v>98</v>
       </c>
@@ -4195,7 +4305,7 @@
         <v>44581094</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11">
       <c r="H74" t="s">
         <v>98</v>
       </c>
@@ -4209,7 +4319,16 @@
         <v>39270777</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11">
+      <c r="A75">
+        <v>65566244</v>
+      </c>
+      <c r="B75" t="s">
+        <v>491</v>
+      </c>
+      <c r="C75" s="10" t="s">
+        <v>647</v>
+      </c>
       <c r="H75" t="s">
         <v>90</v>
       </c>
@@ -4223,7 +4342,7 @@
         <v>45342904</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11">
       <c r="A76" s="8">
         <v>15826960</v>
       </c>
@@ -4246,7 +4365,7 @@
         <v>19619417</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11">
       <c r="A77" s="8">
         <v>58505144</v>
       </c>
@@ -4269,7 +4388,7 @@
         <v>36606823</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11">
       <c r="A78" s="8">
         <v>61199642</v>
       </c>
@@ -4292,7 +4411,7 @@
         <v>12585217</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11">
       <c r="A79" s="8">
         <v>64912430</v>
       </c>
@@ -4315,7 +4434,7 @@
         <v>11511332</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11">
       <c r="A80" s="8">
         <v>10124384</v>
       </c>
@@ -4338,7 +4457,7 @@
         <v>12579597</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11">
       <c r="A81" s="8">
         <v>10929273</v>
       </c>
@@ -4361,7 +4480,7 @@
         <v>50153946</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11">
       <c r="A82" s="8">
         <v>10929274</v>
       </c>
@@ -4384,7 +4503,7 @@
         <v>50723598</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11">
       <c r="A83" s="8">
         <v>11670520</v>
       </c>
@@ -4407,7 +4526,7 @@
         <v>34464589</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11">
       <c r="A84" s="8">
         <v>12029130</v>
       </c>
@@ -4430,7 +4549,7 @@
         <v>12029130</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11">
       <c r="A85" s="8">
         <v>12038103</v>
       </c>
@@ -4453,7 +4572,7 @@
         <v>46962408</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11">
       <c r="A86" s="8">
         <v>12095120</v>
       </c>
@@ -4476,7 +4595,7 @@
         <v>11874445</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11">
       <c r="A87" s="8">
         <v>12481760</v>
       </c>
@@ -4499,7 +4618,7 @@
         <v>25665354</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11">
       <c r="A88" s="8">
         <v>13195957</v>
       </c>
@@ -4522,7 +4641,7 @@
         <v>46550390</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11">
       <c r="A89" s="8">
         <v>14299890</v>
       </c>
@@ -4545,7 +4664,7 @@
         <v>45573288</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11">
       <c r="A90" s="8">
         <v>14473529</v>
       </c>
@@ -4568,7 +4687,7 @@
         <v>34318450</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11">
       <c r="A91" s="8">
         <v>15757638</v>
       </c>
@@ -4591,7 +4710,7 @@
         <v>45701215</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:11">
       <c r="A92" s="8">
         <v>16806254</v>
       </c>
@@ -4614,7 +4733,7 @@
         <v>15004955</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:11">
       <c r="A93" s="8">
         <v>20341619</v>
       </c>
@@ -4637,7 +4756,7 @@
         <v>25321998</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:11">
       <c r="A94" s="8">
         <v>22119013</v>
       </c>
@@ -4660,7 +4779,7 @@
         <v>25321996</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11">
       <c r="A95" s="8">
         <v>25433097</v>
       </c>
@@ -4683,7 +4802,7 @@
         <v>46191377</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11">
       <c r="A96" s="8">
         <v>25512595</v>
       </c>
@@ -4706,7 +4825,7 @@
         <v>45349063</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11">
       <c r="A97" s="8">
         <v>25665354</v>
       </c>
@@ -4729,7 +4848,7 @@
         <v>44996967</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11">
       <c r="A98" s="8">
         <v>29258063</v>
       </c>
@@ -4752,7 +4871,7 @@
         <v>15462869</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11">
       <c r="A99" s="8">
         <v>29266932</v>
       </c>
@@ -4775,7 +4894,7 @@
         <v>15462868</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11">
       <c r="A100" s="8">
         <v>34991467</v>
       </c>
@@ -4798,7 +4917,7 @@
         <v>46671749</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11">
       <c r="A101" s="8">
         <v>35401181</v>
       </c>
@@ -4821,7 +4940,7 @@
         <v>35137369</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11">
       <c r="A102" s="8">
         <v>36606823</v>
       </c>
@@ -4844,7 +4963,7 @@
         <v>34320929</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11">
       <c r="A103" s="8">
         <v>38157908</v>
       </c>
@@ -4867,7 +4986,7 @@
         <v>34320928</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11">
       <c r="A104" s="8">
         <v>38407975</v>
       </c>
@@ -4890,7 +5009,7 @@
         <v>23200605</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11">
       <c r="A105" s="8">
         <v>38659485</v>
       </c>
@@ -4913,7 +5032,7 @@
         <v>23200603</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11">
       <c r="A106" s="8">
         <v>39239709</v>
       </c>
@@ -4936,7 +5055,7 @@
         <v>43571361</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11">
       <c r="A107" s="8">
         <v>39944753</v>
       </c>
@@ -4959,7 +5078,7 @@
         <v>43571360</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11">
       <c r="A108" s="8">
         <v>40180424</v>
       </c>
@@ -4982,7 +5101,7 @@
         <v>34330469</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11">
       <c r="A109" s="8">
         <v>43571361</v>
       </c>
@@ -5005,7 +5124,7 @@
         <v>34331612</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11">
       <c r="A110" s="8">
         <v>46801171</v>
       </c>
@@ -5028,7 +5147,7 @@
         <v>34352694</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11">
       <c r="A111" s="8">
         <v>48449253</v>
       </c>
@@ -5051,7 +5170,7 @@
         <v>39063227</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11">
       <c r="A112" s="8">
         <v>53967042</v>
       </c>
@@ -5074,7 +5193,7 @@
         <v>15831347</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11">
       <c r="A113" s="8">
         <v>55275736</v>
       </c>
@@ -5097,7 +5216,7 @@
         <v>12091621</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11">
       <c r="A114" s="8">
         <v>59759466</v>
       </c>
@@ -5120,7 +5239,7 @@
         <v>16805855</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:11">
       <c r="A115" s="8">
         <v>60024864</v>
       </c>
@@ -5143,7 +5262,7 @@
         <v>15812678</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:11">
       <c r="A116" s="8">
         <v>60025950</v>
       </c>
@@ -5166,7 +5285,7 @@
         <v>12143581</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:11">
       <c r="A117" s="8">
         <v>60541171</v>
       </c>
@@ -5189,7 +5308,7 @@
         <v>11192165</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:11">
       <c r="A118" s="8">
         <v>60543356</v>
       </c>
@@ -5212,7 +5331,7 @@
         <v>11192163</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:11">
       <c r="A119" s="8">
         <v>60615380</v>
       </c>
@@ -5235,7 +5354,7 @@
         <v>12143584</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:11">
       <c r="A120" s="8">
         <v>61760291</v>
       </c>
@@ -5258,7 +5377,7 @@
         <v>11192167</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:11">
       <c r="A121" s="8">
         <v>62385013</v>
       </c>
@@ -5281,7 +5400,7 @@
         <v>12673238</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:11">
       <c r="A122" s="8">
         <v>64606094</v>
       </c>
@@ -5304,7 +5423,7 @@
         <v>15838517</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:11">
       <c r="A123" s="8">
         <v>64846264</v>
       </c>
@@ -5327,7 +5446,7 @@
         <v>12218847</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:11">
       <c r="A124" s="8">
         <v>65566541</v>
       </c>
@@ -5350,7 +5469,7 @@
         <v>16171214</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:11">
       <c r="A125" s="8">
         <v>66607099</v>
       </c>
@@ -5373,7 +5492,7 @@
         <v>11291291</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:11">
       <c r="A126" s="8">
         <v>59924956</v>
       </c>
@@ -5396,7 +5515,7 @@
         <v>14134779</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:11">
       <c r="A127" s="8">
         <v>17014694</v>
       </c>
@@ -5419,7 +5538,7 @@
         <v>14134778</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:11">
       <c r="A128" s="8">
         <v>17014693</v>
       </c>
@@ -5442,7 +5561,7 @@
         <v>37790051</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:11">
       <c r="A129" s="8">
         <v>36811022</v>
       </c>
@@ -5465,7 +5584,7 @@
         <v>39071990</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:11">
       <c r="A130" s="8">
         <v>36811023</v>
       </c>
@@ -5488,7 +5607,7 @@
         <v>39006857</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:11">
       <c r="A131" s="8">
         <v>60023938</v>
       </c>
@@ -5511,7 +5630,7 @@
         <v>39006855</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:11">
       <c r="A132" s="8">
         <v>61929494</v>
       </c>
@@ -5534,7 +5653,7 @@
         <v>39006854</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:11">
       <c r="A133" s="8">
         <v>66417803</v>
       </c>
@@ -5557,7 +5676,7 @@
         <v>12434130</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:11">
       <c r="A134" s="8">
         <v>20342327</v>
       </c>
@@ -5580,7 +5699,7 @@
         <v>11671480</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:11">
       <c r="A135" s="8">
         <v>12586373</v>
       </c>
@@ -5603,7 +5722,7 @@
         <v>11192166</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:11">
       <c r="A136" s="8">
         <v>11055651</v>
       </c>
@@ -5626,7 +5745,7 @@
         <v>37594934</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:11">
       <c r="A137" s="8">
         <v>18816827</v>
       </c>
@@ -5649,7 +5768,7 @@
         <v>32548061</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:11">
       <c r="A138" s="8">
         <v>39229235</v>
       </c>
@@ -5672,7 +5791,7 @@
         <v>32711387</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:11">
       <c r="A139" s="8">
         <v>13151160</v>
       </c>
@@ -5695,7 +5814,7 @@
         <v>32710937</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:11">
       <c r="A140" s="8">
         <v>13151158</v>
       </c>
@@ -5718,7 +5837,7 @@
         <v>35876282</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:11">
       <c r="A141" s="8">
         <v>10978754</v>
       </c>
@@ -5741,7 +5860,7 @@
         <v>15702671</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:11">
       <c r="A142" s="8">
         <v>19619417</v>
       </c>
@@ -5764,7 +5883,7 @@
         <v>11229298</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:11">
       <c r="A143" s="8">
         <v>39063227</v>
       </c>
@@ -5787,7 +5906,7 @@
         <v>50709616</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:11">
       <c r="A144" s="8">
         <v>46995055</v>
       </c>
@@ -5810,7 +5929,7 @@
         <v>37034524</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:11">
       <c r="A145" s="8">
         <v>11744316</v>
       </c>
@@ -5833,7 +5952,7 @@
         <v>14299890</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:11">
       <c r="A146" s="8">
         <v>13069194</v>
       </c>
@@ -5856,7 +5975,7 @@
         <v>13195811</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:11">
       <c r="A147" s="8">
         <v>4125381</v>
       </c>
@@ -5879,7 +5998,7 @@
         <v>36608029</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:11">
       <c r="A148" s="8">
         <v>42839047</v>
       </c>
@@ -5902,7 +6021,7 @@
         <v>13195957</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:11">
       <c r="A149" s="8">
         <v>4152612</v>
       </c>
@@ -5925,7 +6044,7 @@
         <v>10121189</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:11">
       <c r="A150" s="8">
         <v>4152610</v>
       </c>
@@ -5948,7 +6067,7 @@
         <v>8122806</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:11">
       <c r="A151" s="8">
         <v>34098917</v>
       </c>
@@ -5971,7 +6090,7 @@
         <v>48477550</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:11">
       <c r="A152" s="8">
         <v>49985232</v>
       </c>
@@ -5994,7 +6113,7 @@
         <v>11288089</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:11">
       <c r="A153" s="8">
         <v>50155408</v>
       </c>
@@ -6017,7 +6136,7 @@
         <v>11104533</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:11">
       <c r="A154" s="8">
         <v>41662266</v>
       </c>
@@ -6040,7 +6159,7 @@
         <v>10124384</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:11">
       <c r="A155" s="8">
         <v>13573385</v>
       </c>
@@ -6063,7 +6182,7 @@
         <v>46995055</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:11">
       <c r="A156" s="8">
         <v>42871700</v>
       </c>
@@ -6086,7 +6205,7 @@
         <v>11744316</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:11">
       <c r="A157" s="8">
         <v>39257536</v>
       </c>
@@ -6109,7 +6228,7 @@
         <v>13069194</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:11">
       <c r="A158" s="8">
         <v>37424126</v>
       </c>
@@ -6132,7 +6251,7 @@
         <v>19365568</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:11">
       <c r="A159" s="8">
         <v>36802614</v>
       </c>
@@ -6155,7 +6274,7 @@
         <v>47861038</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:11">
       <c r="A160" s="8">
         <v>36577826</v>
       </c>
@@ -6178,7 +6297,7 @@
         <v>43252471</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:11">
       <c r="A161" s="8">
         <v>26196255</v>
       </c>
@@ -6201,7 +6320,7 @@
         <v>4125381</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:11">
       <c r="A162" s="8">
         <v>26019234</v>
       </c>
@@ -6224,7 +6343,7 @@
         <v>38183281</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:11">
       <c r="A163" s="8">
         <v>25411238</v>
       </c>
@@ -6247,7 +6366,7 @@
         <v>14107560</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:11">
       <c r="A164" s="8">
         <v>26500515</v>
       </c>
@@ -6270,7 +6389,7 @@
         <v>44916947</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:11">
       <c r="A165" s="8">
         <v>36162739</v>
       </c>
@@ -6293,7 +6412,7 @@
         <v>40640374</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:11">
       <c r="A166" s="8">
         <v>39893389</v>
       </c>
@@ -6316,7 +6435,7 @@
         <v>13745117</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:11">
       <c r="A167" s="8">
         <v>39296173</v>
       </c>
@@ -6339,7 +6458,7 @@
         <v>15414324</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:11">
       <c r="A168" s="8">
         <v>42217758</v>
       </c>
@@ -6362,7 +6481,7 @@
         <v>35192489</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:11">
       <c r="A169" s="8">
         <v>22403445</v>
       </c>
@@ -6385,7 +6504,7 @@
         <v>40982029</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:11">
       <c r="A170" s="8">
         <v>26257716</v>
       </c>
@@ -6408,7 +6527,7 @@
         <v>10858043</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:11">
       <c r="A171" s="8">
         <v>42486414</v>
       </c>
@@ -6431,7 +6550,7 @@
         <v>4125377</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:11">
       <c r="A172" s="8">
         <v>44695653</v>
       </c>
@@ -6454,7 +6573,7 @@
         <v>26426530</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:11">
       <c r="A173" s="8">
         <v>13405604</v>
       </c>
@@ -6477,7 +6596,7 @@
         <v>18980681</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:11">
       <c r="A174" s="8">
         <v>39911056</v>
       </c>
@@ -6500,7 +6619,7 @@
         <v>12439390</v>
       </c>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:11">
       <c r="A175" s="8">
         <v>51897600</v>
       </c>
@@ -6523,7 +6642,7 @@
         <v>12263239</v>
       </c>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:11">
       <c r="A176" s="8">
         <v>52990015</v>
       </c>
@@ -6546,7 +6665,7 @@
         <v>50725354</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:11">
       <c r="A177" s="8">
         <v>55354052</v>
       </c>
@@ -6569,7 +6688,7 @@
         <v>16179047</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:11">
       <c r="A178" s="8">
         <v>55356388</v>
       </c>
@@ -6592,7 +6711,7 @@
         <v>20815743</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:11">
       <c r="A179" s="8">
         <v>62377903</v>
       </c>
@@ -6615,7 +6734,7 @@
         <v>39651008</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:11">
       <c r="A180" s="8">
         <v>66097436</v>
       </c>
@@ -6638,7 +6757,7 @@
         <v>42839047</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:11">
       <c r="A181" s="8">
         <v>11681261</v>
       </c>
@@ -6661,7 +6780,7 @@
         <v>38455497</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:11">
       <c r="A182" s="8">
         <v>11874445</v>
       </c>
@@ -6684,7 +6803,7 @@
         <v>37173787</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:11">
       <c r="A183" s="8">
         <v>14719737</v>
       </c>
@@ -6707,7 +6826,7 @@
         <v>42913903</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:11">
       <c r="A184" s="8">
         <v>16179047</v>
       </c>
@@ -6730,7 +6849,7 @@
         <v>41864123</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:11">
       <c r="A185" s="8">
         <v>20815743</v>
       </c>
@@ -6753,7 +6872,7 @@
         <v>4152612</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:11">
       <c r="A186" s="8">
         <v>30405071</v>
       </c>
@@ -6776,7 +6895,7 @@
         <v>4152610</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:11">
       <c r="A187" s="8">
         <v>34352694</v>
       </c>
@@ -6799,7 +6918,7 @@
         <v>35896315</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:11">
       <c r="A188" s="8">
         <v>35149611</v>
       </c>
@@ -6822,7 +6941,7 @@
         <v>31743599</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:11">
       <c r="A189" s="8">
         <v>35896315</v>
       </c>
@@ -6845,7 +6964,7 @@
         <v>4152608</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:11">
       <c r="A190" s="8">
         <v>36682232</v>
       </c>
@@ -6868,7 +6987,7 @@
         <v>4152606</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:11">
       <c r="A191" s="8">
         <v>43571360</v>
       </c>
@@ -6891,7 +7010,7 @@
         <v>34098917</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:11">
       <c r="A192" s="8">
         <v>44374810</v>
       </c>
@@ -6914,7 +7033,7 @@
         <v>34801754</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:11">
       <c r="A193" s="8">
         <v>45349063</v>
       </c>
@@ -6937,7 +7056,7 @@
         <v>37639889</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:11">
       <c r="A194" s="8">
         <v>59836396</v>
       </c>
@@ -6960,7 +7079,7 @@
         <v>51533853</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:11">
       <c r="A195" s="8">
         <v>59927382</v>
       </c>
@@ -6983,7 +7102,7 @@
         <v>49985232</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:11">
       <c r="A196" s="8">
         <v>60541542</v>
       </c>
@@ -7006,7 +7125,7 @@
         <v>50155408</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:11">
       <c r="A197" s="8">
         <v>66417801</v>
       </c>
@@ -7029,7 +7148,16 @@
         <v>35401181</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:11">
+      <c r="A198">
+        <v>71291488</v>
+      </c>
+      <c r="B198" t="s">
+        <v>564</v>
+      </c>
+      <c r="C198" s="10" t="s">
+        <v>671</v>
+      </c>
       <c r="H198" t="s">
         <v>92</v>
       </c>
@@ -7043,7 +7171,7 @@
         <v>47936724</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:11">
       <c r="H199" t="s">
         <v>92</v>
       </c>
@@ -7057,7 +7185,7 @@
         <v>38417806</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:11">
       <c r="A200" s="13" t="s">
         <v>650</v>
       </c>
@@ -7076,7 +7204,7 @@
         <v>38158208</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:11">
       <c r="B201" s="11"/>
       <c r="H201" t="s">
         <v>92</v>
@@ -7091,7 +7219,7 @@
         <v>12263163</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:11">
       <c r="B202" s="12"/>
       <c r="H202" t="s">
         <v>92</v>
@@ -7106,7 +7234,7 @@
         <v>15826960</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:11">
       <c r="B203" s="12"/>
       <c r="H203" t="s">
         <v>92</v>
@@ -7121,7 +7249,7 @@
         <v>13573385</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:11">
       <c r="B204" s="12"/>
       <c r="H204" t="s">
         <v>92</v>
@@ -7136,7 +7264,7 @@
         <v>42871700</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:11">
       <c r="B205" s="12"/>
       <c r="H205" t="s">
         <v>92</v>
@@ -7151,7 +7279,7 @@
         <v>39257536</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:11">
       <c r="B206" s="12"/>
       <c r="H206" t="s">
         <v>92</v>
@@ -7166,8 +7294,7 @@
         <v>37424126</v>
       </c>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B207" s="12"/>
+    <row r="207" spans="1:11">
       <c r="H207" t="s">
         <v>92</v>
       </c>
@@ -7181,8 +7308,7 @@
         <v>36802614</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B208" s="12"/>
+    <row r="208" spans="1:11">
       <c r="H208" t="s">
         <v>92</v>
       </c>
@@ -7196,7 +7322,7 @@
         <v>36577826</v>
       </c>
     </row>
-    <row r="209" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:11">
       <c r="B209" s="12"/>
       <c r="H209" t="s">
         <v>92</v>
@@ -7211,7 +7337,7 @@
         <v>35149611</v>
       </c>
     </row>
-    <row r="210" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:11">
       <c r="B210" s="12"/>
       <c r="H210" t="s">
         <v>92</v>
@@ -7226,7 +7352,7 @@
         <v>26196255</v>
       </c>
     </row>
-    <row r="211" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:11">
       <c r="B211" s="12"/>
       <c r="H211" t="s">
         <v>92</v>
@@ -7241,7 +7367,7 @@
         <v>11156528</v>
       </c>
     </row>
-    <row r="212" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:11">
       <c r="H212" t="s">
         <v>92</v>
       </c>
@@ -7255,7 +7381,7 @@
         <v>38415503</v>
       </c>
     </row>
-    <row r="213" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:11">
       <c r="H213" t="s">
         <v>92</v>
       </c>
@@ -7269,7 +7395,7 @@
         <v>37244806</v>
       </c>
     </row>
-    <row r="214" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:11">
       <c r="H214" t="s">
         <v>92</v>
       </c>
@@ -7283,7 +7409,7 @@
         <v>27011098</v>
       </c>
     </row>
-    <row r="215" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:11">
       <c r="H215" t="s">
         <v>92</v>
       </c>
@@ -7297,7 +7423,7 @@
         <v>26019234</v>
       </c>
     </row>
-    <row r="216" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:11">
       <c r="H216" t="s">
         <v>92</v>
       </c>
@@ -7311,7 +7437,7 @@
         <v>13959023</v>
       </c>
     </row>
-    <row r="217" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:11">
       <c r="H217" t="s">
         <v>92</v>
       </c>
@@ -7325,7 +7451,7 @@
         <v>12496637</v>
       </c>
     </row>
-    <row r="218" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:11">
       <c r="H218" t="s">
         <v>92</v>
       </c>
@@ -7339,7 +7465,7 @@
         <v>25411238</v>
       </c>
     </row>
-    <row r="219" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="219" spans="2:11">
       <c r="H219" t="s">
         <v>92</v>
       </c>
@@ -7353,7 +7479,7 @@
         <v>38312169</v>
       </c>
     </row>
-    <row r="220" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="220" spans="2:11">
       <c r="H220" t="s">
         <v>92</v>
       </c>
@@ -7367,7 +7493,7 @@
         <v>31886592</v>
       </c>
     </row>
-    <row r="221" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="221" spans="2:11">
       <c r="H221" t="s">
         <v>92</v>
       </c>
@@ -7381,7 +7507,7 @@
         <v>11670520</v>
       </c>
     </row>
-    <row r="222" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:11">
       <c r="H222" t="s">
         <v>92</v>
       </c>
@@ -7395,7 +7521,7 @@
         <v>26500515</v>
       </c>
     </row>
-    <row r="223" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="223" spans="2:11">
       <c r="H223" t="s">
         <v>92</v>
       </c>
@@ -7409,7 +7535,7 @@
         <v>36162739</v>
       </c>
     </row>
-    <row r="224" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="224" spans="2:11">
       <c r="H224" t="s">
         <v>92</v>
       </c>
@@ -7423,7 +7549,7 @@
         <v>39893389</v>
       </c>
     </row>
-    <row r="225" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="225" spans="8:11">
       <c r="H225" t="s">
         <v>92</v>
       </c>
@@ -7437,7 +7563,7 @@
         <v>39296173</v>
       </c>
     </row>
-    <row r="226" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="226" spans="8:11">
       <c r="H226" t="s">
         <v>92</v>
       </c>
@@ -7451,7 +7577,7 @@
         <v>26491140</v>
       </c>
     </row>
-    <row r="227" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="227" spans="8:11">
       <c r="H227" t="s">
         <v>56</v>
       </c>
@@ -7465,7 +7591,7 @@
         <v>49473587</v>
       </c>
     </row>
-    <row r="228" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="228" spans="8:11">
       <c r="H228" t="s">
         <v>92</v>
       </c>
@@ -7479,7 +7605,7 @@
         <v>50326931</v>
       </c>
     </row>
-    <row r="229" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="229" spans="8:11">
       <c r="H229" t="s">
         <v>152</v>
       </c>
@@ -7493,7 +7619,7 @@
         <v>12095120</v>
       </c>
     </row>
-    <row r="230" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="230" spans="8:11">
       <c r="H230" t="s">
         <v>152</v>
       </c>
@@ -7507,7 +7633,7 @@
         <v>11765770</v>
       </c>
     </row>
-    <row r="231" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="231" spans="8:11">
       <c r="H231" t="s">
         <v>152</v>
       </c>
@@ -7521,7 +7647,7 @@
         <v>15757638</v>
       </c>
     </row>
-    <row r="232" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="232" spans="8:11">
       <c r="H232" t="s">
         <v>152</v>
       </c>
@@ -7535,7 +7661,7 @@
         <v>12038103</v>
       </c>
     </row>
-    <row r="233" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="233" spans="8:11">
       <c r="H233" t="s">
         <v>152</v>
       </c>
@@ -7549,7 +7675,7 @@
         <v>46801171</v>
       </c>
     </row>
-    <row r="234" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="234" spans="8:11">
       <c r="H234" t="s">
         <v>152</v>
       </c>
@@ -7563,7 +7689,7 @@
         <v>10155238</v>
       </c>
     </row>
-    <row r="235" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="235" spans="8:11">
       <c r="H235" t="s">
         <v>152</v>
       </c>
@@ -7577,7 +7703,7 @@
         <v>10816066</v>
       </c>
     </row>
-    <row r="236" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="236" spans="8:11">
       <c r="H236" t="s">
         <v>152</v>
       </c>
@@ -7591,7 +7717,7 @@
         <v>8668649</v>
       </c>
     </row>
-    <row r="237" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="237" spans="8:11">
       <c r="H237" t="s">
         <v>152</v>
       </c>
@@ -7605,7 +7731,7 @@
         <v>36635604</v>
       </c>
     </row>
-    <row r="238" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="238" spans="8:11">
       <c r="H238" t="s">
         <v>109</v>
       </c>
@@ -7619,7 +7745,7 @@
         <v>8837870</v>
       </c>
     </row>
-    <row r="239" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="239" spans="8:11">
       <c r="H239" t="s">
         <v>109</v>
       </c>
@@ -7633,7 +7759,7 @@
         <v>5359040</v>
       </c>
     </row>
-    <row r="240" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="240" spans="8:11">
       <c r="H240" t="s">
         <v>109</v>
       </c>
@@ -7647,7 +7773,7 @@
         <v>42373723</v>
       </c>
     </row>
-    <row r="241" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="241" spans="8:11">
       <c r="H241" t="s">
         <v>109</v>
       </c>
@@ -7661,7 +7787,7 @@
         <v>16303007</v>
       </c>
     </row>
-    <row r="242" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="242" spans="8:11">
       <c r="H242" t="s">
         <v>109</v>
       </c>
@@ -7675,7 +7801,7 @@
         <v>27303665</v>
       </c>
     </row>
-    <row r="243" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="243" spans="8:11">
       <c r="H243" t="s">
         <v>109</v>
       </c>
@@ -7689,7 +7815,7 @@
         <v>5462299</v>
       </c>
     </row>
-    <row r="244" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="244" spans="8:11">
       <c r="H244" t="s">
         <v>109</v>
       </c>
@@ -7703,7 +7829,7 @@
         <v>47220150</v>
       </c>
     </row>
-    <row r="245" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="245" spans="8:11">
       <c r="H245" t="s">
         <v>109</v>
       </c>
@@ -7717,7 +7843,7 @@
         <v>42265154</v>
       </c>
     </row>
-    <row r="246" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="246" spans="8:11">
       <c r="H246" t="s">
         <v>109</v>
       </c>
@@ -7731,7 +7857,7 @@
         <v>48105600</v>
       </c>
     </row>
-    <row r="247" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="247" spans="8:11">
       <c r="H247" t="s">
         <v>109</v>
       </c>
@@ -7745,7 +7871,7 @@
         <v>34991467</v>
       </c>
     </row>
-    <row r="248" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="248" spans="8:11">
       <c r="H248" t="s">
         <v>109</v>
       </c>
@@ -7759,7 +7885,7 @@
         <v>34348663</v>
       </c>
     </row>
-    <row r="249" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="249" spans="8:11">
       <c r="H249" t="s">
         <v>109</v>
       </c>
@@ -7773,7 +7899,7 @@
         <v>34535085</v>
       </c>
     </row>
-    <row r="250" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="250" spans="8:11">
       <c r="H250" t="s">
         <v>109</v>
       </c>
@@ -7787,7 +7913,7 @@
         <v>41140508</v>
       </c>
     </row>
-    <row r="251" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="251" spans="8:11">
       <c r="H251" t="s">
         <v>109</v>
       </c>
@@ -7801,7 +7927,7 @@
         <v>22441147</v>
       </c>
     </row>
-    <row r="252" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="252" spans="8:11">
       <c r="H252" t="s">
         <v>109</v>
       </c>
@@ -7815,7 +7941,7 @@
         <v>36811022</v>
       </c>
     </row>
-    <row r="253" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="253" spans="8:11">
       <c r="H253" t="s">
         <v>109</v>
       </c>
@@ -7829,7 +7955,7 @@
         <v>36811023</v>
       </c>
     </row>
-    <row r="254" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="254" spans="8:11">
       <c r="H254" t="s">
         <v>143</v>
       </c>
@@ -7843,7 +7969,7 @@
         <v>42217758</v>
       </c>
     </row>
-    <row r="255" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="255" spans="8:11">
       <c r="H255" t="s">
         <v>143</v>
       </c>
@@ -7857,7 +7983,7 @@
         <v>39384055</v>
       </c>
     </row>
-    <row r="256" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="256" spans="8:11">
       <c r="H256" t="s">
         <v>143</v>
       </c>
@@ -7871,7 +7997,7 @@
         <v>11681261</v>
       </c>
     </row>
-    <row r="257" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="257" spans="8:11">
       <c r="H257" t="s">
         <v>211</v>
       </c>
@@ -7885,7 +8011,7 @@
         <v>37161537</v>
       </c>
     </row>
-    <row r="258" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="258" spans="8:11">
       <c r="H258" t="s">
         <v>143</v>
       </c>
@@ -7899,7 +8025,7 @@
         <v>30405071</v>
       </c>
     </row>
-    <row r="259" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="259" spans="8:11">
       <c r="H259" t="s">
         <v>143</v>
       </c>
@@ -7913,7 +8039,7 @@
         <v>22403445</v>
       </c>
     </row>
-    <row r="260" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="260" spans="8:11">
       <c r="H260" t="s">
         <v>143</v>
       </c>
@@ -7927,7 +8053,7 @@
         <v>26257716</v>
       </c>
     </row>
-    <row r="261" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="261" spans="8:11">
       <c r="H261" t="s">
         <v>143</v>
       </c>
@@ -7941,7 +8067,7 @@
         <v>12481760</v>
       </c>
     </row>
-    <row r="262" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="262" spans="8:11">
       <c r="H262" t="s">
         <v>143</v>
       </c>
@@ -7955,7 +8081,7 @@
         <v>12481759</v>
       </c>
     </row>
-    <row r="263" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="263" spans="8:11">
       <c r="H263" t="s">
         <v>143</v>
       </c>
@@ -7969,7 +8095,7 @@
         <v>36682232</v>
       </c>
     </row>
-    <row r="264" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="264" spans="8:11">
       <c r="H264" t="s">
         <v>143</v>
       </c>
@@ -7983,7 +8109,7 @@
         <v>46727700</v>
       </c>
     </row>
-    <row r="265" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="265" spans="8:11">
       <c r="H265" t="s">
         <v>143</v>
       </c>
@@ -7997,7 +8123,7 @@
         <v>40771157</v>
       </c>
     </row>
-    <row r="266" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="266" spans="8:11">
       <c r="H266" t="s">
         <v>143</v>
       </c>
@@ -8011,7 +8137,7 @@
         <v>19104731</v>
       </c>
     </row>
-    <row r="267" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="267" spans="8:11">
       <c r="H267" t="s">
         <v>143</v>
       </c>
@@ -8025,7 +8151,7 @@
         <v>39944753</v>
       </c>
     </row>
-    <row r="268" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="268" spans="8:11">
       <c r="H268" t="s">
         <v>143</v>
       </c>
@@ -8039,7 +8165,7 @@
         <v>48449253</v>
       </c>
     </row>
-    <row r="269" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="269" spans="8:11">
       <c r="H269" t="s">
         <v>143</v>
       </c>
@@ -8053,7 +8179,7 @@
         <v>42051062</v>
       </c>
     </row>
-    <row r="270" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="270" spans="8:11">
       <c r="H270" t="s">
         <v>143</v>
       </c>
@@ -8067,7 +8193,7 @@
         <v>18291047</v>
       </c>
     </row>
-    <row r="271" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="271" spans="8:11">
       <c r="H271" t="s">
         <v>143</v>
       </c>
@@ -8081,7 +8207,7 @@
         <v>10727917</v>
       </c>
     </row>
-    <row r="272" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="272" spans="8:11">
       <c r="H272" t="s">
         <v>143</v>
       </c>
@@ -8095,7 +8221,7 @@
         <v>46543317</v>
       </c>
     </row>
-    <row r="273" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="273" spans="8:11">
       <c r="H273" t="s">
         <v>143</v>
       </c>
@@ -8109,7 +8235,7 @@
         <v>13644995</v>
       </c>
     </row>
-    <row r="274" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="274" spans="8:11">
       <c r="H274" t="s">
         <v>143</v>
       </c>
@@ -8123,7 +8249,7 @@
         <v>42486414</v>
       </c>
     </row>
-    <row r="275" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="275" spans="8:11">
       <c r="H275" t="s">
         <v>143</v>
       </c>
@@ -8137,7 +8263,7 @@
         <v>44695653</v>
       </c>
     </row>
-    <row r="276" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="276" spans="8:11">
       <c r="H276" t="s">
         <v>143</v>
       </c>
@@ -8151,7 +8277,7 @@
         <v>44374810</v>
       </c>
     </row>
-    <row r="277" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="277" spans="8:11">
       <c r="H277" t="s">
         <v>143</v>
       </c>
@@ -8165,7 +8291,7 @@
         <v>29258063</v>
       </c>
     </row>
-    <row r="278" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="278" spans="8:11">
       <c r="H278" t="s">
         <v>143</v>
       </c>
@@ -8179,7 +8305,7 @@
         <v>13405604</v>
       </c>
     </row>
-    <row r="279" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="279" spans="8:11">
       <c r="H279" t="s">
         <v>143</v>
       </c>
@@ -8193,7 +8319,7 @@
         <v>10646862</v>
       </c>
     </row>
-    <row r="280" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="280" spans="8:11">
       <c r="H280" t="s">
         <v>143</v>
       </c>
@@ -8207,7 +8333,7 @@
         <v>12362063</v>
       </c>
     </row>
-    <row r="281" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="281" spans="8:11">
       <c r="H281" t="s">
         <v>90</v>
       </c>
@@ -8221,7 +8347,7 @@
         <v>40185196</v>
       </c>
     </row>
-    <row r="282" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="282" spans="8:11">
       <c r="H282" t="s">
         <v>90</v>
       </c>
@@ -8235,7 +8361,7 @@
         <v>15825326</v>
       </c>
     </row>
-    <row r="283" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="283" spans="8:11">
       <c r="H283" t="s">
         <v>90</v>
       </c>
@@ -8249,7 +8375,7 @@
         <v>26375455</v>
       </c>
     </row>
-    <row r="284" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="284" spans="8:11">
       <c r="H284" t="s">
         <v>90</v>
       </c>
@@ -8263,7 +8389,7 @@
         <v>42803850</v>
       </c>
     </row>
-    <row r="285" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="285" spans="8:11">
       <c r="H285" t="s">
         <v>90</v>
       </c>
@@ -8277,7 +8403,7 @@
         <v>50154913</v>
       </c>
     </row>
-    <row r="286" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="286" spans="8:11">
       <c r="H286" t="s">
         <v>90</v>
       </c>
@@ -8291,7 +8417,7 @@
         <v>16806254</v>
       </c>
     </row>
-    <row r="287" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="287" spans="8:11">
       <c r="H287" t="s">
         <v>90</v>
       </c>
@@ -8305,7 +8431,7 @@
         <v>40501253</v>
       </c>
     </row>
-    <row r="288" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="288" spans="8:11">
       <c r="H288" t="s">
         <v>90</v>
       </c>
@@ -8319,7 +8445,7 @@
         <v>14878740</v>
       </c>
     </row>
-    <row r="289" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="289" spans="8:11">
       <c r="H289" t="s">
         <v>90</v>
       </c>
@@ -8333,7 +8459,7 @@
         <v>12673237</v>
       </c>
     </row>
-    <row r="290" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="290" spans="8:11">
       <c r="H290" t="s">
         <v>90</v>
       </c>
@@ -8347,7 +8473,7 @@
         <v>17579662</v>
       </c>
     </row>
-    <row r="291" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="291" spans="8:11">
       <c r="H291" t="s">
         <v>90</v>
       </c>
@@ -8361,7 +8487,7 @@
         <v>14719737</v>
       </c>
     </row>
-    <row r="292" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="292" spans="8:11">
       <c r="H292" t="s">
         <v>90</v>
       </c>
@@ -8375,7 +8501,7 @@
         <v>22119013</v>
       </c>
     </row>
-    <row r="293" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="293" spans="8:11">
       <c r="H293" t="s">
         <v>90</v>
       </c>
@@ -8389,7 +8515,7 @@
         <v>15795597</v>
       </c>
     </row>
-    <row r="294" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="294" spans="8:11">
       <c r="H294" t="s">
         <v>90</v>
       </c>
@@ -8403,7 +8529,7 @@
         <v>12126317</v>
       </c>
     </row>
-    <row r="295" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="295" spans="8:11">
       <c r="H295" t="s">
         <v>90</v>
       </c>
@@ -8417,7 +8543,7 @@
         <v>39239709</v>
       </c>
     </row>
-    <row r="296" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="296" spans="8:11">
       <c r="H296" t="s">
         <v>90</v>
       </c>
@@ -8431,7 +8557,7 @@
         <v>14488275</v>
       </c>
     </row>
-    <row r="297" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="297" spans="8:11">
       <c r="H297" t="s">
         <v>90</v>
       </c>
@@ -8445,7 +8571,7 @@
         <v>42519088</v>
       </c>
     </row>
-    <row r="298" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="298" spans="8:11">
       <c r="H298" t="s">
         <v>90</v>
       </c>
@@ -8459,7 +8585,7 @@
         <v>17579394</v>
       </c>
     </row>
-    <row r="299" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="299" spans="8:11">
       <c r="H299" t="s">
         <v>90</v>
       </c>
@@ -8473,7 +8599,7 @@
         <v>27056005</v>
       </c>
     </row>
-    <row r="300" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="300" spans="8:11">
       <c r="H300" t="s">
         <v>90</v>
       </c>
@@ -8487,7 +8613,7 @@
         <v>24832169</v>
       </c>
     </row>
-    <row r="301" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="301" spans="8:11">
       <c r="H301" t="s">
         <v>171</v>
       </c>
@@ -8501,7 +8627,7 @@
         <v>39147133</v>
       </c>
     </row>
-    <row r="302" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="302" spans="8:11">
       <c r="H302" t="s">
         <v>171</v>
       </c>
@@ -8515,7 +8641,7 @@
         <v>39030281</v>
       </c>
     </row>
-    <row r="303" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="303" spans="8:11">
       <c r="H303" t="s">
         <v>171</v>
       </c>
@@ -8529,7 +8655,7 @@
         <v>13373616</v>
       </c>
     </row>
-    <row r="304" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="304" spans="8:11">
       <c r="H304" t="s">
         <v>171</v>
       </c>
@@ -8543,7 +8669,7 @@
         <v>12757668</v>
       </c>
     </row>
-    <row r="305" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="305" spans="8:11">
       <c r="H305" t="s">
         <v>171</v>
       </c>
@@ -8557,7 +8683,7 @@
         <v>38977260</v>
       </c>
     </row>
-    <row r="306" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="306" spans="8:11">
       <c r="H306" t="s">
         <v>29</v>
       </c>
@@ -8571,7 +8697,7 @@
         <v>38676914</v>
       </c>
     </row>
-    <row r="307" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="307" spans="8:11">
       <c r="H307" t="s">
         <v>29</v>
       </c>
@@ -8585,7 +8711,7 @@
         <v>39911056</v>
       </c>
     </row>
-    <row r="308" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="308" spans="8:11">
       <c r="H308" t="s">
         <v>29</v>
       </c>
@@ -8599,7 +8725,7 @@
         <v>40102936</v>
       </c>
     </row>
-    <row r="309" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="309" spans="8:11">
       <c r="H309" t="s">
         <v>29</v>
       </c>
@@ -8613,7 +8739,7 @@
         <v>10929274</v>
       </c>
     </row>
-    <row r="310" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="310" spans="8:11">
       <c r="H310" t="s">
         <v>29</v>
       </c>
@@ -8627,7 +8753,7 @@
         <v>10929273</v>
       </c>
     </row>
-    <row r="311" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="311" spans="8:11">
       <c r="H311" t="s">
         <v>29</v>
       </c>
@@ -8641,7 +8767,7 @@
         <v>38412071</v>
       </c>
     </row>
-    <row r="312" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="312" spans="8:11">
       <c r="H312" t="s">
         <v>29</v>
       </c>
@@ -8655,7 +8781,7 @@
         <v>29280326</v>
       </c>
     </row>
-    <row r="313" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="313" spans="8:11">
       <c r="H313" t="s">
         <v>29</v>
       </c>
@@ -8669,7 +8795,7 @@
         <v>38412101</v>
       </c>
     </row>
-    <row r="314" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="314" spans="8:11">
       <c r="H314" t="s">
         <v>98</v>
       </c>
@@ -8683,7 +8809,7 @@
         <v>5332788</v>
       </c>
     </row>
-    <row r="315" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="315" spans="8:11">
       <c r="H315" t="s">
         <v>98</v>
       </c>
@@ -8697,7 +8823,7 @@
         <v>5332789</v>
       </c>
     </row>
-    <row r="316" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="316" spans="8:11">
       <c r="H316" t="s">
         <v>98</v>
       </c>
@@ -8711,7 +8837,7 @@
         <v>51016959</v>
       </c>
     </row>
-    <row r="317" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="317" spans="8:11">
       <c r="H317" t="s">
         <v>90</v>
       </c>
@@ -8725,7 +8851,7 @@
         <v>40636333</v>
       </c>
     </row>
-    <row r="318" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="318" spans="8:11">
       <c r="H318" t="s">
         <v>171</v>
       </c>
@@ -8739,7 +8865,7 @@
         <v>50875168</v>
       </c>
     </row>
-    <row r="319" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="319" spans="8:11">
       <c r="H319" t="s">
         <v>58</v>
       </c>
@@ -8753,7 +8879,7 @@
         <v>51623281</v>
       </c>
     </row>
-    <row r="320" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="320" spans="8:11">
       <c r="H320" t="s">
         <v>92</v>
       </c>
@@ -8767,7 +8893,7 @@
         <v>51897600</v>
       </c>
     </row>
-    <row r="321" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="321" spans="8:11">
       <c r="H321" t="s">
         <v>58</v>
       </c>
@@ -8781,7 +8907,7 @@
         <v>51989601</v>
       </c>
     </row>
-    <row r="322" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="322" spans="8:11">
       <c r="H322" t="s">
         <v>109</v>
       </c>
@@ -8795,7 +8921,7 @@
         <v>52390638</v>
       </c>
     </row>
-    <row r="323" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="323" spans="8:11">
       <c r="H323" t="s">
         <v>109</v>
       </c>
@@ -8809,7 +8935,7 @@
         <v>52362395</v>
       </c>
     </row>
-    <row r="324" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="324" spans="8:11">
       <c r="H324" t="s">
         <v>90</v>
       </c>
@@ -8823,7 +8949,7 @@
         <v>52155415</v>
       </c>
     </row>
-    <row r="325" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="325" spans="8:11">
       <c r="H325" t="s">
         <v>92</v>
       </c>
@@ -8837,7 +8963,7 @@
         <v>52162444</v>
       </c>
     </row>
-    <row r="326" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="326" spans="8:11">
       <c r="H326" t="s">
         <v>171</v>
       </c>
@@ -8851,7 +8977,7 @@
         <v>52270898</v>
       </c>
     </row>
-    <row r="327" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="327" spans="8:11">
       <c r="H327" t="s">
         <v>98</v>
       </c>
@@ -8865,7 +8991,7 @@
         <v>52211558</v>
       </c>
     </row>
-    <row r="328" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="328" spans="8:11">
       <c r="H328" t="s">
         <v>98</v>
       </c>
@@ -8879,7 +9005,7 @@
         <v>52217000</v>
       </c>
     </row>
-    <row r="329" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="329" spans="8:11">
       <c r="H329" t="s">
         <v>29</v>
       </c>
@@ -8893,7 +9019,7 @@
         <v>51689222</v>
       </c>
     </row>
-    <row r="330" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="330" spans="8:11">
       <c r="H330" t="s">
         <v>29</v>
       </c>
@@ -8907,7 +9033,7 @@
         <v>51684787</v>
       </c>
     </row>
-    <row r="331" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="331" spans="8:11">
       <c r="H331" t="s">
         <v>29</v>
       </c>
@@ -8921,7 +9047,7 @@
         <v>51883980</v>
       </c>
     </row>
-    <row r="332" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="332" spans="8:11">
       <c r="H332" t="s">
         <v>29</v>
       </c>
@@ -8935,7 +9061,7 @@
         <v>51898514</v>
       </c>
     </row>
-    <row r="333" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="333" spans="8:11">
       <c r="H333" t="s">
         <v>98</v>
       </c>
@@ -8949,7 +9075,7 @@
         <v>52990015</v>
       </c>
     </row>
-    <row r="334" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="334" spans="8:11">
       <c r="H334" t="s">
         <v>29</v>
       </c>
@@ -8963,7 +9089,7 @@
         <v>52581507</v>
       </c>
     </row>
-    <row r="335" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="335" spans="8:11">
       <c r="H335" t="s">
         <v>29</v>
       </c>
@@ -8977,7 +9103,7 @@
         <v>52613211</v>
       </c>
     </row>
-    <row r="336" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="336" spans="8:11">
       <c r="H336" t="s">
         <v>29</v>
       </c>
@@ -8991,7 +9117,7 @@
         <v>52578670</v>
       </c>
     </row>
-    <row r="337" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="337" spans="8:11">
       <c r="H337" t="s">
         <v>171</v>
       </c>
@@ -9005,7 +9131,7 @@
         <v>52874174</v>
       </c>
     </row>
-    <row r="338" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="338" spans="8:11">
       <c r="H338" t="s">
         <v>29</v>
       </c>
@@ -9019,7 +9145,7 @@
         <v>52872566</v>
       </c>
     </row>
-    <row r="339" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="339" spans="8:11">
       <c r="H339" t="s">
         <v>171</v>
       </c>
@@ -9033,7 +9159,7 @@
         <v>54145830</v>
       </c>
     </row>
-    <row r="340" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="340" spans="8:11">
       <c r="H340" t="s">
         <v>29</v>
       </c>
@@ -9047,7 +9173,7 @@
         <v>53052265</v>
       </c>
     </row>
-    <row r="341" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="341" spans="8:11">
       <c r="H341" t="s">
         <v>90</v>
       </c>
@@ -9061,7 +9187,7 @@
         <v>53297446</v>
       </c>
     </row>
-    <row r="342" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="342" spans="8:11">
       <c r="H342" t="s">
         <v>143</v>
       </c>
@@ -9075,7 +9201,7 @@
         <v>53583387</v>
       </c>
     </row>
-    <row r="343" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="343" spans="8:11">
       <c r="H343" t="s">
         <v>143</v>
       </c>
@@ -9089,7 +9215,7 @@
         <v>53564659</v>
       </c>
     </row>
-    <row r="344" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="344" spans="8:11">
       <c r="H344" t="s">
         <v>143</v>
       </c>
@@ -9103,7 +9229,7 @@
         <v>53569741</v>
       </c>
     </row>
-    <row r="345" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="345" spans="8:11">
       <c r="H345" t="s">
         <v>58</v>
       </c>
@@ -9117,7 +9243,7 @@
         <v>53680118</v>
       </c>
     </row>
-    <row r="346" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="346" spans="8:11">
       <c r="H346" t="s">
         <v>92</v>
       </c>
@@ -9131,7 +9257,7 @@
         <v>53776254</v>
       </c>
     </row>
-    <row r="347" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="347" spans="8:11">
       <c r="H347" t="s">
         <v>90</v>
       </c>
@@ -9145,7 +9271,7 @@
         <v>53967042</v>
       </c>
     </row>
-    <row r="348" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="348" spans="8:11">
       <c r="H348" t="s">
         <v>90</v>
       </c>
@@ -9159,7 +9285,7 @@
         <v>55275736</v>
       </c>
     </row>
-    <row r="349" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="349" spans="8:11">
       <c r="H349" t="s">
         <v>90</v>
       </c>
@@ -9173,7 +9299,7 @@
         <v>56663811</v>
       </c>
     </row>
-    <row r="350" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="350" spans="8:11">
       <c r="H350" t="s">
         <v>92</v>
       </c>
@@ -9187,7 +9313,7 @@
         <v>59082806</v>
       </c>
     </row>
-    <row r="351" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="351" spans="8:11">
       <c r="H351" t="s">
         <v>29</v>
       </c>
@@ -9201,7 +9327,7 @@
         <v>55369678</v>
       </c>
     </row>
-    <row r="352" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="352" spans="8:11">
       <c r="H352" t="s">
         <v>58</v>
       </c>
@@ -9215,7 +9341,7 @@
         <v>55354052</v>
       </c>
     </row>
-    <row r="353" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="353" spans="8:11">
       <c r="H353" t="s">
         <v>58</v>
       </c>
@@ -9229,7 +9355,7 @@
         <v>55381383</v>
       </c>
     </row>
-    <row r="354" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="354" spans="8:11">
       <c r="H354" t="s">
         <v>58</v>
       </c>
@@ -9243,7 +9369,7 @@
         <v>55609278</v>
       </c>
     </row>
-    <row r="355" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="355" spans="8:11">
       <c r="H355" t="s">
         <v>90</v>
       </c>
@@ -9257,7 +9383,7 @@
         <v>55356212</v>
       </c>
     </row>
-    <row r="356" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="356" spans="8:11">
       <c r="H356" t="s">
         <v>90</v>
       </c>
@@ -9271,7 +9397,7 @@
         <v>55449180</v>
       </c>
     </row>
-    <row r="357" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="357" spans="8:11">
       <c r="H357" t="s">
         <v>58</v>
       </c>
@@ -9285,7 +9411,7 @@
         <v>55357095</v>
       </c>
     </row>
-    <row r="358" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="358" spans="8:11">
       <c r="H358" t="s">
         <v>58</v>
       </c>
@@ -9299,7 +9425,7 @@
         <v>55384739</v>
       </c>
     </row>
-    <row r="359" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="359" spans="8:11">
       <c r="H359" t="s">
         <v>58</v>
       </c>
@@ -9313,7 +9439,7 @@
         <v>55357155</v>
       </c>
     </row>
-    <row r="360" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="360" spans="8:11">
       <c r="H360" t="s">
         <v>58</v>
       </c>
@@ -9327,7 +9453,7 @@
         <v>55389336</v>
       </c>
     </row>
-    <row r="361" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="361" spans="8:11">
       <c r="H361" t="s">
         <v>171</v>
       </c>
@@ -9341,7 +9467,7 @@
         <v>55356388</v>
       </c>
     </row>
-    <row r="362" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="362" spans="8:11">
       <c r="H362" t="s">
         <v>171</v>
       </c>
@@ -9355,7 +9481,7 @@
         <v>55610213</v>
       </c>
     </row>
-    <row r="363" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="363" spans="8:11">
       <c r="H363" t="s">
         <v>92</v>
       </c>
@@ -9369,7 +9495,7 @@
         <v>55462718</v>
       </c>
     </row>
-    <row r="364" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="364" spans="8:11">
       <c r="H364" t="s">
         <v>58</v>
       </c>
@@ -9383,7 +9509,7 @@
         <v>58084222</v>
       </c>
     </row>
-    <row r="365" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="365" spans="8:11">
       <c r="H365" t="s">
         <v>58</v>
       </c>
@@ -9397,7 +9523,7 @@
         <v>56651433</v>
       </c>
     </row>
-    <row r="366" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="366" spans="8:11">
       <c r="H366" t="s">
         <v>94</v>
       </c>
@@ -9411,7 +9537,7 @@
         <v>56479851</v>
       </c>
     </row>
-    <row r="367" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="367" spans="8:11">
       <c r="H367" t="s">
         <v>90</v>
       </c>
@@ -9425,7 +9551,7 @@
         <v>56667264</v>
       </c>
     </row>
-    <row r="368" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="368" spans="8:11">
       <c r="H368" t="s">
         <v>143</v>
       </c>
@@ -9439,7 +9565,7 @@
         <v>56896464</v>
       </c>
     </row>
-    <row r="369" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="369" spans="8:11">
       <c r="H369" t="s">
         <v>98</v>
       </c>
@@ -9453,7 +9579,7 @@
         <v>57592449</v>
       </c>
     </row>
-    <row r="370" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="370" spans="8:11">
       <c r="H370" t="s">
         <v>92</v>
       </c>
@@ -9467,7 +9593,7 @@
         <v>56183402</v>
       </c>
     </row>
-    <row r="371" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="371" spans="8:11">
       <c r="H371" t="s">
         <v>92</v>
       </c>
@@ -9481,7 +9607,7 @@
         <v>56651667</v>
       </c>
     </row>
-    <row r="372" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="372" spans="8:11">
       <c r="H372" t="s">
         <v>92</v>
       </c>
@@ -9495,7 +9621,7 @@
         <v>58987730</v>
       </c>
     </row>
-    <row r="373" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="373" spans="8:11">
       <c r="H373" t="s">
         <v>171</v>
       </c>
@@ -9509,7 +9635,7 @@
         <v>57422656</v>
       </c>
     </row>
-    <row r="374" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="374" spans="8:11">
       <c r="H374" t="s">
         <v>92</v>
       </c>
@@ -9523,7 +9649,7 @@
         <v>58040260</v>
       </c>
     </row>
-    <row r="375" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="375" spans="8:11">
       <c r="H375" t="s">
         <v>90</v>
       </c>
@@ -9537,7 +9663,7 @@
         <v>59070986</v>
       </c>
     </row>
-    <row r="376" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="376" spans="8:11">
       <c r="H376" t="s">
         <v>98</v>
       </c>
@@ -9551,7 +9677,7 @@
         <v>59058036</v>
       </c>
     </row>
-    <row r="377" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="377" spans="8:11">
       <c r="H377" t="s">
         <v>90</v>
       </c>
@@ -9565,7 +9691,7 @@
         <v>58505144</v>
       </c>
     </row>
-    <row r="378" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="378" spans="8:11">
       <c r="H378" t="s">
         <v>115</v>
       </c>
@@ -9579,7 +9705,7 @@
         <v>58610450</v>
       </c>
     </row>
-    <row r="379" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="379" spans="8:11">
       <c r="H379" t="s">
         <v>143</v>
       </c>
@@ -9593,7 +9719,7 @@
         <v>59056260</v>
       </c>
     </row>
-    <row r="380" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="380" spans="8:11">
       <c r="H380" t="s">
         <v>115</v>
       </c>
@@ -9607,7 +9733,7 @@
         <v>58722261</v>
       </c>
     </row>
-    <row r="381" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="381" spans="8:11">
       <c r="H381" t="s">
         <v>115</v>
       </c>
@@ -9621,7 +9747,7 @@
         <v>58716097</v>
       </c>
     </row>
-    <row r="382" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="382" spans="8:11">
       <c r="H382" t="s">
         <v>115</v>
       </c>
@@ -9635,7 +9761,7 @@
         <v>58730204</v>
       </c>
     </row>
-    <row r="383" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="383" spans="8:11">
       <c r="H383" t="s">
         <v>115</v>
       </c>
@@ -9649,7 +9775,7 @@
         <v>59199875</v>
       </c>
     </row>
-    <row r="384" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="384" spans="8:11">
       <c r="H384" t="s">
         <v>115</v>
       </c>
@@ -9663,7 +9789,7 @@
         <v>59759466</v>
       </c>
     </row>
-    <row r="385" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="385" spans="8:11">
       <c r="H385" t="s">
         <v>92</v>
       </c>
@@ -9677,7 +9803,7 @@
         <v>59332927</v>
       </c>
     </row>
-    <row r="386" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="386" spans="8:11">
       <c r="H386" t="s">
         <v>92</v>
       </c>
@@ -9691,7 +9817,7 @@
         <v>59944694</v>
       </c>
     </row>
-    <row r="387" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="387" spans="8:11">
       <c r="H387" t="s">
         <v>115</v>
       </c>
@@ -9705,7 +9831,7 @@
         <v>60019261</v>
       </c>
     </row>
-    <row r="388" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="388" spans="8:11">
       <c r="H388" t="s">
         <v>143</v>
       </c>
@@ -9719,7 +9845,7 @@
         <v>59932138</v>
       </c>
     </row>
-    <row r="389" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="389" spans="8:11">
       <c r="H389" t="s">
         <v>115</v>
       </c>
@@ -9733,7 +9859,7 @@
         <v>59924956</v>
       </c>
     </row>
-    <row r="390" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="390" spans="8:11">
       <c r="H390" t="s">
         <v>115</v>
       </c>
@@ -9747,7 +9873,7 @@
         <v>59927382</v>
       </c>
     </row>
-    <row r="391" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="391" spans="8:11">
       <c r="H391" t="s">
         <v>115</v>
       </c>
@@ -9761,7 +9887,7 @@
         <v>59836396</v>
       </c>
     </row>
-    <row r="392" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="392" spans="8:11">
       <c r="H392" t="s">
         <v>115</v>
       </c>
@@ -9775,7 +9901,7 @@
         <v>60015061</v>
       </c>
     </row>
-    <row r="393" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="393" spans="8:11">
       <c r="H393" t="s">
         <v>115</v>
       </c>
@@ -9789,7 +9915,7 @@
         <v>60023938</v>
       </c>
     </row>
-    <row r="394" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="394" spans="8:11">
       <c r="H394" t="s">
         <v>115</v>
       </c>
@@ -9803,7 +9929,7 @@
         <v>60025950</v>
       </c>
     </row>
-    <row r="395" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="395" spans="8:11">
       <c r="H395" t="s">
         <v>115</v>
       </c>
@@ -9817,7 +9943,7 @@
         <v>60024864</v>
       </c>
     </row>
-    <row r="396" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="396" spans="8:11">
       <c r="H396" t="s">
         <v>115</v>
       </c>
@@ -9831,7 +9957,7 @@
         <v>60084208</v>
       </c>
     </row>
-    <row r="397" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="397" spans="8:11">
       <c r="H397" t="s">
         <v>92</v>
       </c>
@@ -9845,7 +9971,7 @@
         <v>60085614</v>
       </c>
     </row>
-    <row r="398" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="398" spans="8:11">
       <c r="H398" t="s">
         <v>171</v>
       </c>
@@ -9859,7 +9985,7 @@
         <v>60133592</v>
       </c>
     </row>
-    <row r="399" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="399" spans="8:11">
       <c r="H399" t="s">
         <v>143</v>
       </c>
@@ -9873,7 +9999,7 @@
         <v>60450424</v>
       </c>
     </row>
-    <row r="400" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="400" spans="8:11">
       <c r="H400" t="s">
         <v>143</v>
       </c>
@@ -9887,7 +10013,7 @@
         <v>60380162</v>
       </c>
     </row>
-    <row r="401" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="401" spans="8:11">
       <c r="H401" t="s">
         <v>152</v>
       </c>
@@ -9901,7 +10027,7 @@
         <v>60541542</v>
       </c>
     </row>
-    <row r="402" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="402" spans="8:11">
       <c r="H402" t="s">
         <v>152</v>
       </c>
@@ -9915,7 +10041,7 @@
         <v>60541171</v>
       </c>
     </row>
-    <row r="403" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="403" spans="8:11">
       <c r="H403" t="s">
         <v>90</v>
       </c>
@@ -9929,7 +10055,7 @@
         <v>60543356</v>
       </c>
     </row>
-    <row r="404" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="404" spans="8:11">
       <c r="H404" t="s">
         <v>115</v>
       </c>
@@ -9943,7 +10069,7 @@
         <v>60530655</v>
       </c>
     </row>
-    <row r="405" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="405" spans="8:11">
       <c r="H405" t="s">
         <v>90</v>
       </c>
@@ -9957,7 +10083,7 @@
         <v>60615380</v>
       </c>
     </row>
-    <row r="406" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="406" spans="8:11">
       <c r="H406" t="s">
         <v>58</v>
       </c>
@@ -9971,7 +10097,7 @@
         <v>60725132</v>
       </c>
     </row>
-    <row r="407" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="407" spans="8:11">
       <c r="H407" t="s">
         <v>58</v>
       </c>
@@ -9985,7 +10111,7 @@
         <v>62575565</v>
       </c>
     </row>
-    <row r="408" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="408" spans="8:11">
       <c r="H408" t="s">
         <v>171</v>
       </c>
@@ -9999,7 +10125,7 @@
         <v>61766007</v>
       </c>
     </row>
-    <row r="409" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="409" spans="8:11">
       <c r="H409" t="s">
         <v>98</v>
       </c>
@@ -10013,7 +10139,7 @@
         <v>61089339</v>
       </c>
     </row>
-    <row r="410" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="410" spans="8:11">
       <c r="H410" t="s">
         <v>98</v>
       </c>
@@ -10027,7 +10153,7 @@
         <v>62377903</v>
       </c>
     </row>
-    <row r="411" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="411" spans="8:11">
       <c r="H411" t="s">
         <v>92</v>
       </c>
@@ -10041,7 +10167,7 @@
         <v>60542212</v>
       </c>
     </row>
-    <row r="412" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="412" spans="8:11">
       <c r="H412" t="s">
         <v>109</v>
       </c>
@@ -10055,7 +10181,7 @@
         <v>61044622</v>
       </c>
     </row>
-    <row r="413" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="413" spans="8:11">
       <c r="H413" t="s">
         <v>92</v>
       </c>
@@ -10069,7 +10195,7 @@
         <v>61199642</v>
       </c>
     </row>
-    <row r="414" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="414" spans="8:11">
       <c r="H414" t="s">
         <v>143</v>
       </c>
@@ -10083,7 +10209,7 @@
         <v>61760291</v>
       </c>
     </row>
-    <row r="415" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="415" spans="8:11">
       <c r="H415" t="s">
         <v>109</v>
       </c>
@@ -10097,7 +10223,7 @@
         <v>61923953</v>
       </c>
     </row>
-    <row r="416" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="416" spans="8:11">
       <c r="H416" t="s">
         <v>143</v>
       </c>
@@ -10111,7 +10237,7 @@
         <v>61760141</v>
       </c>
     </row>
-    <row r="417" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="417" spans="8:11">
       <c r="H417" t="s">
         <v>143</v>
       </c>
@@ -10125,7 +10251,7 @@
         <v>61929592</v>
       </c>
     </row>
-    <row r="418" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="418" spans="8:11">
       <c r="H418" t="s">
         <v>143</v>
       </c>
@@ -10139,7 +10265,7 @@
         <v>61929727</v>
       </c>
     </row>
-    <row r="419" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="419" spans="8:11">
       <c r="H419" t="s">
         <v>92</v>
       </c>
@@ -10153,7 +10279,7 @@
         <v>61929494</v>
       </c>
     </row>
-    <row r="420" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="420" spans="8:11">
       <c r="H420" t="s">
         <v>92</v>
       </c>
@@ -10167,7 +10293,7 @@
         <v>61929493</v>
       </c>
     </row>
-    <row r="421" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="421" spans="8:11">
       <c r="H421" t="s">
         <v>98</v>
       </c>
@@ -10181,7 +10307,7 @@
         <v>61879892</v>
       </c>
     </row>
-    <row r="422" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="422" spans="8:11">
       <c r="H422" t="s">
         <v>58</v>
       </c>
@@ -10195,7 +10321,7 @@
         <v>62378988</v>
       </c>
     </row>
-    <row r="423" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="423" spans="8:11">
       <c r="H423" t="s">
         <v>58</v>
       </c>
@@ -10209,7 +10335,7 @@
         <v>62375802</v>
       </c>
     </row>
-    <row r="424" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="424" spans="8:11">
       <c r="H424" t="s">
         <v>58</v>
       </c>
@@ -10223,7 +10349,7 @@
         <v>62379668</v>
       </c>
     </row>
-    <row r="425" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="425" spans="8:11">
       <c r="H425" t="s">
         <v>211</v>
       </c>
@@ -10237,7 +10363,7 @@
         <v>62221331</v>
       </c>
     </row>
-    <row r="426" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="426" spans="8:11">
       <c r="H426" t="s">
         <v>143</v>
       </c>
@@ -10251,7 +10377,7 @@
         <v>62385013</v>
       </c>
     </row>
-    <row r="427" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="427" spans="8:11">
       <c r="H427" t="s">
         <v>143</v>
       </c>
@@ -10265,7 +10391,7 @@
         <v>62380995</v>
       </c>
     </row>
-    <row r="428" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="428" spans="8:11">
       <c r="H428" t="s">
         <v>98</v>
       </c>
@@ -10279,7 +10405,7 @@
         <v>62421723</v>
       </c>
     </row>
-    <row r="429" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="429" spans="8:11">
       <c r="H429" t="s">
         <v>98</v>
       </c>
@@ -10293,7 +10419,7 @@
         <v>62374813</v>
       </c>
     </row>
-    <row r="430" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="430" spans="8:11">
       <c r="H430" t="s">
         <v>98</v>
       </c>
@@ -10307,7 +10433,7 @@
         <v>62499786</v>
       </c>
     </row>
-    <row r="431" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="431" spans="8:11">
       <c r="H431" t="s">
         <v>98</v>
       </c>
@@ -10321,7 +10447,7 @@
         <v>62498583</v>
       </c>
     </row>
-    <row r="432" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="432" spans="8:11">
       <c r="H432" t="s">
         <v>143</v>
       </c>
@@ -10335,7 +10461,7 @@
         <v>63346456</v>
       </c>
     </row>
-    <row r="433" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="433" spans="8:11">
       <c r="H433" t="s">
         <v>143</v>
       </c>
@@ -10349,7 +10475,7 @@
         <v>63100963</v>
       </c>
     </row>
-    <row r="434" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="434" spans="8:11">
       <c r="H434" t="s">
         <v>90</v>
       </c>
@@ -10363,7 +10489,7 @@
         <v>63396496</v>
       </c>
     </row>
-    <row r="435" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="435" spans="8:11">
       <c r="H435" t="s">
         <v>58</v>
       </c>
@@ -10377,7 +10503,7 @@
         <v>64270608</v>
       </c>
     </row>
-    <row r="436" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="436" spans="8:11">
       <c r="H436" t="s">
         <v>92</v>
       </c>
@@ -10391,7 +10517,7 @@
         <v>63573761</v>
       </c>
     </row>
-    <row r="437" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="437" spans="8:11">
       <c r="H437" t="s">
         <v>92</v>
       </c>
@@ -10405,7 +10531,7 @@
         <v>64330763</v>
       </c>
     </row>
-    <row r="438" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="438" spans="8:11">
       <c r="H438" t="s">
         <v>92</v>
       </c>
@@ -10419,7 +10545,7 @@
         <v>64330764</v>
       </c>
     </row>
-    <row r="439" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="439" spans="8:11">
       <c r="H439" t="s">
         <v>92</v>
       </c>
@@ -10433,7 +10559,7 @@
         <v>64212552</v>
       </c>
     </row>
-    <row r="440" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="440" spans="8:11">
       <c r="H440" t="s">
         <v>92</v>
       </c>
@@ -10447,7 +10573,7 @@
         <v>64212544</v>
       </c>
     </row>
-    <row r="441" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="441" spans="8:11">
       <c r="H441" t="s">
         <v>92</v>
       </c>
@@ -10461,7 +10587,7 @@
         <v>64212543</v>
       </c>
     </row>
-    <row r="442" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="442" spans="8:11">
       <c r="H442" t="s">
         <v>92</v>
       </c>
@@ -10475,7 +10601,7 @@
         <v>64212381</v>
       </c>
     </row>
-    <row r="443" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="443" spans="8:11">
       <c r="H443" t="s">
         <v>109</v>
       </c>
@@ -10489,7 +10615,7 @@
         <v>64114088</v>
       </c>
     </row>
-    <row r="444" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="444" spans="8:11">
       <c r="H444" t="s">
         <v>171</v>
       </c>
@@ -10503,7 +10629,7 @@
         <v>64223250</v>
       </c>
     </row>
-    <row r="445" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="445" spans="8:11">
       <c r="H445" t="s">
         <v>171</v>
       </c>
@@ -10517,7 +10643,7 @@
         <v>64214259</v>
       </c>
     </row>
-    <row r="446" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="446" spans="8:11">
       <c r="H446" t="s">
         <v>171</v>
       </c>
@@ -10531,7 +10657,7 @@
         <v>64214258</v>
       </c>
     </row>
-    <row r="447" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="447" spans="8:11">
       <c r="H447" t="s">
         <v>143</v>
       </c>
@@ -10545,7 +10671,7 @@
         <v>63742200</v>
       </c>
     </row>
-    <row r="448" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="448" spans="8:11">
       <c r="H448" t="s">
         <v>90</v>
       </c>
@@ -10559,7 +10685,7 @@
         <v>64606094</v>
       </c>
     </row>
-    <row r="449" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="449" spans="8:11">
       <c r="H449" t="s">
         <v>98</v>
       </c>
@@ -10573,7 +10699,7 @@
         <v>64287980</v>
       </c>
     </row>
-    <row r="450" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="450" spans="8:11">
       <c r="H450" t="s">
         <v>98</v>
       </c>
@@ -10587,7 +10713,7 @@
         <v>64257297</v>
       </c>
     </row>
-    <row r="451" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="451" spans="8:11">
       <c r="H451" t="s">
         <v>98</v>
       </c>
@@ -10601,7 +10727,7 @@
         <v>66097436</v>
       </c>
     </row>
-    <row r="452" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="452" spans="8:11">
       <c r="H452" t="s">
         <v>143</v>
       </c>
@@ -10615,7 +10741,7 @@
         <v>64330309</v>
       </c>
     </row>
-    <row r="453" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="453" spans="8:11">
       <c r="H453" t="s">
         <v>211</v>
       </c>
@@ -10629,7 +10755,7 @@
         <v>64846264</v>
       </c>
     </row>
-    <row r="454" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="454" spans="8:11">
       <c r="H454" t="s">
         <v>109</v>
       </c>
@@ -10643,7 +10769,7 @@
         <v>64753996</v>
       </c>
     </row>
-    <row r="455" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="455" spans="8:11">
       <c r="H455" t="s">
         <v>92</v>
       </c>
@@ -10657,7 +10783,7 @@
         <v>64778162</v>
       </c>
     </row>
-    <row r="456" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="456" spans="8:11">
       <c r="H456" t="s">
         <v>92</v>
       </c>
@@ -10671,7 +10797,7 @@
         <v>64778161</v>
       </c>
     </row>
-    <row r="457" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="457" spans="8:11">
       <c r="H457" t="s">
         <v>92</v>
       </c>
@@ -10685,7 +10811,7 @@
         <v>64808932</v>
       </c>
     </row>
-    <row r="458" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="458" spans="8:11">
       <c r="H458" t="s">
         <v>109</v>
       </c>
@@ -10699,7 +10825,7 @@
         <v>64789478</v>
       </c>
     </row>
-    <row r="459" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="459" spans="8:11">
       <c r="H459" t="s">
         <v>98</v>
       </c>
@@ -10713,7 +10839,7 @@
         <v>64912430</v>
       </c>
     </row>
-    <row r="460" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="460" spans="8:11">
       <c r="H460" t="s">
         <v>98</v>
       </c>
@@ -10727,7 +10853,7 @@
         <v>64971361</v>
       </c>
     </row>
-    <row r="461" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="461" spans="8:11">
       <c r="H461" t="s">
         <v>143</v>
       </c>
@@ -10741,7 +10867,7 @@
         <v>65145714</v>
       </c>
     </row>
-    <row r="462" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="462" spans="8:11">
       <c r="H462" t="s">
         <v>92</v>
       </c>
@@ -10755,7 +10881,7 @@
         <v>65081124</v>
       </c>
     </row>
-    <row r="463" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="463" spans="8:11">
       <c r="H463" t="s">
         <v>29</v>
       </c>
@@ -10769,7 +10895,7 @@
         <v>65181042</v>
       </c>
     </row>
-    <row r="464" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="464" spans="8:11">
       <c r="H464" t="s">
         <v>29</v>
       </c>
@@ -10783,7 +10909,7 @@
         <v>65179405</v>
       </c>
     </row>
-    <row r="465" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="465" spans="8:11">
       <c r="H465" t="s">
         <v>29</v>
       </c>
@@ -10797,7 +10923,7 @@
         <v>65566244</v>
       </c>
     </row>
-    <row r="466" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="466" spans="8:11">
       <c r="H466" t="s">
         <v>29</v>
       </c>
@@ -10811,7 +10937,7 @@
         <v>65566541</v>
       </c>
     </row>
-    <row r="467" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="467" spans="8:11">
       <c r="H467" t="s">
         <v>29</v>
       </c>
@@ -10825,7 +10951,7 @@
         <v>65656468</v>
       </c>
     </row>
-    <row r="468" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="468" spans="8:11">
       <c r="H468" t="s">
         <v>29</v>
       </c>
@@ -10839,7 +10965,7 @@
         <v>65657039</v>
       </c>
     </row>
-    <row r="469" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="469" spans="8:11">
       <c r="H469" t="s">
         <v>98</v>
       </c>
@@ -10853,7 +10979,7 @@
         <v>66217025</v>
       </c>
     </row>
-    <row r="470" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="470" spans="8:11">
       <c r="H470" t="s">
         <v>98</v>
       </c>
@@ -10867,7 +10993,7 @@
         <v>66214618</v>
       </c>
     </row>
-    <row r="471" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="471" spans="8:11">
       <c r="H471" t="s">
         <v>29</v>
       </c>
@@ -10881,7 +11007,7 @@
         <v>65935700</v>
       </c>
     </row>
-    <row r="472" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="472" spans="8:11">
       <c r="H472" t="s">
         <v>29</v>
       </c>
@@ -10895,7 +11021,7 @@
         <v>65934564</v>
       </c>
     </row>
-    <row r="473" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="473" spans="8:11">
       <c r="H473" t="s">
         <v>29</v>
       </c>
@@ -10909,7 +11035,7 @@
         <v>65933937</v>
       </c>
     </row>
-    <row r="474" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="474" spans="8:11">
       <c r="H474" t="s">
         <v>29</v>
       </c>
@@ -10923,7 +11049,7 @@
         <v>66046959</v>
       </c>
     </row>
-    <row r="475" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="475" spans="8:11">
       <c r="H475" t="s">
         <v>98</v>
       </c>
@@ -10937,7 +11063,7 @@
         <v>65969750</v>
       </c>
     </row>
-    <row r="476" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="476" spans="8:11">
       <c r="H476" t="s">
         <v>171</v>
       </c>
@@ -10951,7 +11077,7 @@
         <v>66358440</v>
       </c>
     </row>
-    <row r="477" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="477" spans="8:11">
       <c r="H477" t="s">
         <v>143</v>
       </c>
@@ -10965,7 +11091,7 @@
         <v>66417803</v>
       </c>
     </row>
-    <row r="478" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="478" spans="8:11">
       <c r="H478" t="s">
         <v>143</v>
       </c>
@@ -10979,7 +11105,7 @@
         <v>66417801</v>
       </c>
     </row>
-    <row r="479" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="479" spans="8:11">
       <c r="H479" t="s">
         <v>92</v>
       </c>
@@ -10993,7 +11119,7 @@
         <v>66357977</v>
       </c>
     </row>
-    <row r="480" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="480" spans="8:11">
       <c r="H480" t="s">
         <v>171</v>
       </c>
@@ -11007,7 +11133,7 @@
         <v>67191572</v>
       </c>
     </row>
-    <row r="481" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="481" spans="8:11">
       <c r="H481" t="s">
         <v>171</v>
       </c>
@@ -11021,7 +11147,7 @@
         <v>66546178</v>
       </c>
     </row>
-    <row r="482" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="482" spans="8:11">
       <c r="H482" t="s">
         <v>171</v>
       </c>
@@ -11035,7 +11161,7 @@
         <v>67627331</v>
       </c>
     </row>
-    <row r="483" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="483" spans="8:11">
       <c r="H483" t="s">
         <v>92</v>
       </c>
@@ -11049,7 +11175,7 @@
         <v>66778787</v>
       </c>
     </row>
-    <row r="484" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="484" spans="8:11">
       <c r="H484" t="s">
         <v>92</v>
       </c>
@@ -11063,7 +11189,7 @@
         <v>66778788</v>
       </c>
     </row>
-    <row r="485" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="485" spans="8:11">
       <c r="H485" t="s">
         <v>92</v>
       </c>
@@ -11077,7 +11203,7 @@
         <v>66778789</v>
       </c>
     </row>
-    <row r="486" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="486" spans="8:11">
       <c r="H486" t="s">
         <v>90</v>
       </c>
@@ -11091,7 +11217,7 @@
         <v>66896364</v>
       </c>
     </row>
-    <row r="487" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="487" spans="8:11">
       <c r="H487" t="s">
         <v>29</v>
       </c>
@@ -11105,7 +11231,7 @@
         <v>66607099</v>
       </c>
     </row>
-    <row r="488" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="488" spans="8:11">
       <c r="H488" t="s">
         <v>29</v>
       </c>
@@ -11119,7 +11245,7 @@
         <v>66864708</v>
       </c>
     </row>
-    <row r="489" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="489" spans="8:11">
       <c r="H489" t="s">
         <v>29</v>
       </c>
@@ -11133,7 +11259,7 @@
         <v>66850322</v>
       </c>
     </row>
-    <row r="490" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="490" spans="8:11">
       <c r="H490" t="s">
         <v>109</v>
       </c>
@@ -11147,7 +11273,7 @@
         <v>67268341</v>
       </c>
     </row>
-    <row r="491" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="491" spans="8:11">
       <c r="H491" t="s">
         <v>109</v>
       </c>
@@ -11161,7 +11287,7 @@
         <v>67268348</v>
       </c>
     </row>
-    <row r="492" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="492" spans="8:11">
       <c r="H492" t="s">
         <v>109</v>
       </c>
@@ -11175,7 +11301,7 @@
         <v>67268349</v>
       </c>
     </row>
-    <row r="493" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="493" spans="8:11">
       <c r="H493" t="s">
         <v>109</v>
       </c>
@@ -11189,7 +11315,7 @@
         <v>67268350</v>
       </c>
     </row>
-    <row r="494" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="494" spans="8:11">
       <c r="H494" t="s">
         <v>109</v>
       </c>
@@ -11203,7 +11329,7 @@
         <v>67272047</v>
       </c>
     </row>
-    <row r="495" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="495" spans="8:11">
       <c r="H495" t="s">
         <v>109</v>
       </c>
@@ -11217,7 +11343,7 @@
         <v>67272046</v>
       </c>
     </row>
-    <row r="496" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="496" spans="8:11">
       <c r="H496" t="s">
         <v>92</v>
       </c>
@@ -11231,7 +11357,7 @@
         <v>67438488</v>
       </c>
     </row>
-    <row r="497" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="497" spans="8:11">
       <c r="H497" t="s">
         <v>92</v>
       </c>
@@ -11245,7 +11371,7 @@
         <v>67438487</v>
       </c>
     </row>
-    <row r="498" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="498" spans="8:11">
       <c r="H498" t="s">
         <v>92</v>
       </c>
@@ -11259,7 +11385,7 @@
         <v>68253037</v>
       </c>
     </row>
-    <row r="499" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="499" spans="8:11">
       <c r="H499" t="s">
         <v>171</v>
       </c>
@@ -11273,7 +11399,7 @@
         <v>67891311</v>
       </c>
     </row>
-    <row r="500" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="500" spans="8:11">
       <c r="H500" t="s">
         <v>143</v>
       </c>
@@ -11287,7 +11413,7 @@
         <v>67900090</v>
       </c>
     </row>
-    <row r="501" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="501" spans="8:11">
       <c r="H501" t="s">
         <v>29</v>
       </c>
@@ -11301,7 +11427,7 @@
         <v>67630646</v>
       </c>
     </row>
-    <row r="502" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="502" spans="8:11">
       <c r="H502" t="s">
         <v>98</v>
       </c>
@@ -11315,7 +11441,7 @@
         <v>67974104</v>
       </c>
     </row>
-    <row r="503" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="503" spans="8:11">
       <c r="H503" t="s">
         <v>109</v>
       </c>
@@ -11329,7 +11455,7 @@
         <v>67989839</v>
       </c>
     </row>
-    <row r="504" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="504" spans="8:11">
       <c r="H504" t="s">
         <v>109</v>
       </c>
@@ -11343,7 +11469,7 @@
         <v>67988468</v>
       </c>
     </row>
-    <row r="505" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="505" spans="8:11">
       <c r="H505" t="s">
         <v>98</v>
       </c>
@@ -11357,7 +11483,7 @@
         <v>68466892</v>
       </c>
     </row>
-    <row r="506" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="506" spans="8:11">
       <c r="H506" t="s">
         <v>98</v>
       </c>
@@ -11371,7 +11497,7 @@
         <v>69040158</v>
       </c>
     </row>
-    <row r="507" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="507" spans="8:11">
       <c r="H507" t="s">
         <v>98</v>
       </c>
@@ -11385,7 +11511,7 @@
         <v>68462854</v>
       </c>
     </row>
-    <row r="508" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="508" spans="8:11">
       <c r="H508" t="s">
         <v>92</v>
       </c>
@@ -11399,7 +11525,7 @@
         <v>68677002</v>
       </c>
     </row>
-    <row r="509" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="509" spans="8:11">
       <c r="H509" t="s">
         <v>171</v>
       </c>
@@ -11413,7 +11539,7 @@
         <v>68880617</v>
       </c>
     </row>
-    <row r="510" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="510" spans="8:11">
       <c r="H510" t="s">
         <v>98</v>
       </c>
@@ -11427,7 +11553,7 @@
         <v>68934411</v>
       </c>
     </row>
-    <row r="511" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="511" spans="8:11">
       <c r="H511" t="s">
         <v>98</v>
       </c>
@@ -11441,7 +11567,7 @@
         <v>68924611</v>
       </c>
     </row>
-    <row r="512" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="512" spans="8:11">
       <c r="H512" t="s">
         <v>92</v>
       </c>
@@ -11455,7 +11581,7 @@
         <v>69039437</v>
       </c>
     </row>
-    <row r="513" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="513" spans="8:11">
       <c r="H513" t="s">
         <v>92</v>
       </c>
@@ -11469,7 +11595,7 @@
         <v>69039778</v>
       </c>
     </row>
-    <row r="514" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="514" spans="8:11">
       <c r="H514" t="s">
         <v>58</v>
       </c>
@@ -11483,7 +11609,7 @@
         <v>69279032</v>
       </c>
     </row>
-    <row r="515" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="515" spans="8:11">
       <c r="H515" t="s">
         <v>92</v>
       </c>
@@ -11497,7 +11623,7 @@
         <v>68938743</v>
       </c>
     </row>
-    <row r="516" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="516" spans="8:11">
       <c r="H516" t="s">
         <v>58</v>
       </c>
@@ -11511,7 +11637,7 @@
         <v>69772629</v>
       </c>
     </row>
-    <row r="517" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="517" spans="8:11">
       <c r="H517" t="s">
         <v>58</v>
       </c>
@@ -11525,7 +11651,7 @@
         <v>69772627</v>
       </c>
     </row>
-    <row r="518" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="518" spans="8:11">
       <c r="H518" t="s">
         <v>58</v>
       </c>
@@ -11539,7 +11665,7 @@
         <v>69772625</v>
       </c>
     </row>
-    <row r="519" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="519" spans="8:11">
       <c r="H519" t="s">
         <v>98</v>
       </c>
@@ -11553,7 +11679,7 @@
         <v>69292187</v>
       </c>
     </row>
-    <row r="520" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="520" spans="8:11">
       <c r="H520" t="s">
         <v>98</v>
       </c>
@@ -11567,7 +11693,7 @@
         <v>69292186</v>
       </c>
     </row>
-    <row r="521" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="521" spans="8:11">
       <c r="H521" t="s">
         <v>98</v>
       </c>
@@ -11581,7 +11707,7 @@
         <v>69292185</v>
       </c>
     </row>
-    <row r="522" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="522" spans="8:11">
       <c r="H522" t="s">
         <v>58</v>
       </c>
@@ -11595,7 +11721,7 @@
         <v>69096297</v>
       </c>
     </row>
-    <row r="523" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="523" spans="8:11">
       <c r="H523" t="s">
         <v>58</v>
       </c>
@@ -11609,7 +11735,7 @@
         <v>69096296</v>
       </c>
     </row>
-    <row r="524" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="524" spans="8:11">
       <c r="H524" t="s">
         <v>143</v>
       </c>
@@ -11623,7 +11749,7 @@
         <v>69594684</v>
       </c>
     </row>
-    <row r="525" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="525" spans="8:11">
       <c r="H525" t="s">
         <v>98</v>
       </c>
@@ -11637,7 +11763,7 @@
         <v>70204974</v>
       </c>
     </row>
-    <row r="526" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="526" spans="8:11">
       <c r="H526" t="s">
         <v>98</v>
       </c>
@@ -11651,7 +11777,7 @@
         <v>70204975</v>
       </c>
     </row>
-    <row r="527" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="527" spans="8:11">
       <c r="H527" t="s">
         <v>143</v>
       </c>
@@ -11665,7 +11791,7 @@
         <v>69767288</v>
       </c>
     </row>
-    <row r="528" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="528" spans="8:11">
       <c r="H528" t="s">
         <v>98</v>
       </c>
@@ -11679,7 +11805,7 @@
         <v>69766464</v>
       </c>
     </row>
-    <row r="529" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="529" spans="8:11">
       <c r="H529" t="s">
         <v>98</v>
       </c>
@@ -11693,7 +11819,7 @@
         <v>69803799</v>
       </c>
     </row>
-    <row r="530" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="530" spans="8:11">
       <c r="H530" t="s">
         <v>143</v>
       </c>
@@ -11707,7 +11833,7 @@
         <v>70251147</v>
       </c>
     </row>
-    <row r="531" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="531" spans="8:11">
       <c r="H531" t="s">
         <v>171</v>
       </c>
@@ -11721,7 +11847,7 @@
         <v>69770093</v>
       </c>
     </row>
-    <row r="532" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="532" spans="8:11">
       <c r="H532" t="s">
         <v>92</v>
       </c>
@@ -11735,7 +11861,7 @@
         <v>70205079</v>
       </c>
     </row>
-    <row r="533" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="533" spans="8:11">
       <c r="H533" t="s">
         <v>98</v>
       </c>
@@ -11749,7 +11875,7 @@
         <v>70530577</v>
       </c>
     </row>
-    <row r="534" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="534" spans="8:11">
       <c r="H534" t="s">
         <v>98</v>
       </c>
@@ -11763,7 +11889,7 @@
         <v>70530576</v>
       </c>
     </row>
-    <row r="535" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="535" spans="8:11">
       <c r="H535" t="s">
         <v>109</v>
       </c>
@@ -11777,7 +11903,7 @@
         <v>71030052</v>
       </c>
     </row>
-    <row r="536" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="536" spans="8:11">
       <c r="H536" t="s">
         <v>115</v>
       </c>
@@ -11791,7 +11917,7 @@
         <v>70770186</v>
       </c>
     </row>
-    <row r="537" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="537" spans="8:11">
       <c r="H537" t="s">
         <v>115</v>
       </c>
@@ -11805,7 +11931,7 @@
         <v>71173111</v>
       </c>
     </row>
-    <row r="538" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="538" spans="8:11">
       <c r="H538" t="s">
         <v>115</v>
       </c>
@@ -11819,7 +11945,7 @@
         <v>71156871</v>
       </c>
     </row>
-    <row r="539" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="539" spans="8:11">
       <c r="H539" t="s">
         <v>115</v>
       </c>
@@ -11833,7 +11959,7 @@
         <v>71291488</v>
       </c>
     </row>
-    <row r="540" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="540" spans="8:11">
       <c r="I540">
         <v>71042279</v>
       </c>
@@ -11844,7 +11970,7 @@
         <v>71042279</v>
       </c>
     </row>
-    <row r="541" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="541" spans="8:11">
       <c r="H541" t="s">
         <v>115</v>
       </c>
@@ -11858,7 +11984,7 @@
         <v>71947627</v>
       </c>
     </row>
-    <row r="542" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="542" spans="8:11">
       <c r="H542" t="s">
         <v>115</v>
       </c>
@@ -11872,7 +11998,7 @@
         <v>72182444</v>
       </c>
     </row>
-    <row r="543" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="543" spans="8:11">
       <c r="H543" t="s">
         <v>115</v>
       </c>
@@ -11886,7 +12012,7 @@
         <v>72300747</v>
       </c>
     </row>
-    <row r="544" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="544" spans="8:11">
       <c r="H544" t="s">
         <v>115</v>
       </c>
@@ -11900,7 +12026,7 @@
         <v>72417582</v>
       </c>
     </row>
-    <row r="545" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="545" spans="8:11">
       <c r="H545" t="s">
         <v>115</v>
       </c>
@@ -11914,7 +12040,7 @@
         <v>72614935</v>
       </c>
     </row>
-    <row r="546" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="546" spans="8:11">
       <c r="H546" t="s">
         <v>115</v>
       </c>
@@ -11928,7 +12054,7 @@
         <v>72614936</v>
       </c>
     </row>
-    <row r="547" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="547" spans="8:11">
       <c r="H547" t="s">
         <v>115</v>
       </c>
@@ -11942,7 +12068,7 @@
         <v>72614937</v>
       </c>
     </row>
-    <row r="548" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="548" spans="8:11">
       <c r="H548" t="s">
         <v>92</v>
       </c>
@@ -11956,7 +12082,7 @@
         <v>73226633</v>
       </c>
     </row>
-    <row r="549" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="549" spans="8:11">
       <c r="H549" t="s">
         <v>92</v>
       </c>
@@ -11970,7 +12096,7 @@
         <v>73226632</v>
       </c>
     </row>
-    <row r="550" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="550" spans="8:11">
       <c r="H550" t="s">
         <v>143</v>
       </c>
@@ -11984,7 +12110,7 @@
         <v>73316683</v>
       </c>
     </row>
-    <row r="551" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="551" spans="8:11">
       <c r="H551" t="s">
         <v>143</v>
       </c>
@@ -11998,7 +12124,7 @@
         <v>73316684</v>
       </c>
     </row>
-    <row r="552" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="552" spans="8:11">
       <c r="H552" t="s">
         <v>143</v>
       </c>
@@ -12012,7 +12138,7 @@
         <v>73316685</v>
       </c>
     </row>
-    <row r="553" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="553" spans="8:11">
       <c r="H553" t="s">
         <v>115</v>
       </c>
@@ -12026,7 +12152,7 @@
         <v>72699936</v>
       </c>
     </row>
-    <row r="554" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="554" spans="8:11">
       <c r="H554" t="s">
         <v>115</v>
       </c>
@@ -12040,7 +12166,7 @@
         <v>72699935</v>
       </c>
     </row>
-    <row r="555" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="555" spans="8:11">
       <c r="H555" t="s">
         <v>115</v>
       </c>
@@ -12054,7 +12180,7 @@
         <v>72828733</v>
       </c>
     </row>
-    <row r="556" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="556" spans="8:11">
       <c r="H556" t="s">
         <v>115</v>
       </c>
@@ -12068,7 +12194,7 @@
         <v>72828734</v>
       </c>
     </row>
-    <row r="557" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="557" spans="8:11">
       <c r="H557" t="s">
         <v>90</v>
       </c>
@@ -12082,7 +12208,7 @@
         <v>72683872</v>
       </c>
     </row>
-    <row r="558" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="558" spans="8:11">
       <c r="H558" t="s">
         <v>58</v>
       </c>
@@ -12096,7 +12222,7 @@
         <v>72910681</v>
       </c>
     </row>
-    <row r="559" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="559" spans="8:11">
       <c r="H559" t="s">
         <v>58</v>
       </c>
@@ -12110,7 +12236,7 @@
         <v>72910683</v>
       </c>
     </row>
-    <row r="560" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="560" spans="8:11">
       <c r="H560" t="s">
         <v>98</v>
       </c>
@@ -12124,7 +12250,7 @@
         <v>73523448</v>
       </c>
     </row>
-    <row r="561" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="561" spans="8:11">
       <c r="H561" t="s">
         <v>58</v>
       </c>
@@ -12138,7 +12264,7 @@
         <v>73461995</v>
       </c>
     </row>
-    <row r="562" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="562" spans="8:11">
       <c r="H562" t="s">
         <v>98</v>
       </c>
@@ -12152,7 +12278,7 @@
         <v>73956460</v>
       </c>
     </row>
-    <row r="563" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="563" spans="8:11">
       <c r="H563" t="s">
         <v>98</v>
       </c>
@@ -12166,7 +12292,7 @@
         <v>73956461</v>
       </c>
     </row>
-    <row r="564" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="564" spans="8:11">
       <c r="H564" t="s">
         <v>98</v>
       </c>
@@ -12180,7 +12306,7 @@
         <v>73956459</v>
       </c>
     </row>
-    <row r="565" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="565" spans="8:11">
       <c r="H565" t="s">
         <v>58</v>
       </c>
@@ -12194,7 +12320,7 @@
         <v>74685916</v>
       </c>
     </row>
-    <row r="566" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="566" spans="8:11">
       <c r="H566" t="s">
         <v>98</v>
       </c>
@@ -12208,7 +12334,7 @@
         <v>73975553</v>
       </c>
     </row>
-    <row r="567" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="567" spans="8:11">
       <c r="H567" t="s">
         <v>98</v>
       </c>
@@ -12222,7 +12348,7 @@
         <v>73952843</v>
       </c>
     </row>
-    <row r="568" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="568" spans="8:11">
       <c r="H568" t="s">
         <v>115</v>
       </c>
@@ -12236,7 +12362,7 @@
         <v>74550323</v>
       </c>
     </row>
-    <row r="569" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="569" spans="8:11">
       <c r="H569" t="s">
         <v>98</v>
       </c>
@@ -12250,7 +12376,7 @@
         <v>75989703</v>
       </c>
     </row>
-    <row r="570" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="570" spans="8:11">
       <c r="H570" t="s">
         <v>143</v>
       </c>
@@ -12264,7 +12390,7 @@
         <v>74693807</v>
       </c>
     </row>
-    <row r="571" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="571" spans="8:11">
       <c r="H571" t="s">
         <v>143</v>
       </c>
@@ -12278,7 +12404,7 @@
         <v>73893263</v>
       </c>
     </row>
-    <row r="572" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="572" spans="8:11">
       <c r="H572" t="s">
         <v>143</v>
       </c>
@@ -12292,7 +12418,7 @@
         <v>74884452</v>
       </c>
     </row>
-    <row r="573" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="573" spans="8:11">
       <c r="H573" t="s">
         <v>98</v>
       </c>
@@ -12306,7 +12432,7 @@
         <v>74826973</v>
       </c>
     </row>
-    <row r="574" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="574" spans="8:11">
       <c r="H574" t="s">
         <v>98</v>
       </c>
@@ -12320,7 +12446,7 @@
         <v>74826974</v>
       </c>
     </row>
-    <row r="575" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="575" spans="8:11">
       <c r="H575" t="s">
         <v>90</v>
       </c>
@@ -12334,7 +12460,7 @@
         <v>75077119</v>
       </c>
     </row>
-    <row r="576" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="576" spans="8:11">
       <c r="H576" t="s">
         <v>92</v>
       </c>
@@ -12348,7 +12474,7 @@
         <v>78867502</v>
       </c>
     </row>
-    <row r="577" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="577" spans="8:11">
       <c r="H577" t="s">
         <v>92</v>
       </c>
@@ -12362,7 +12488,7 @@
         <v>80192305</v>
       </c>
     </row>
-    <row r="578" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="578" spans="8:11">
       <c r="H578" t="s">
         <v>92</v>
       </c>
@@ -12376,7 +12502,7 @@
         <v>75741354</v>
       </c>
     </row>
-    <row r="579" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="579" spans="8:11">
       <c r="H579" t="s">
         <v>143</v>
       </c>
@@ -12390,7 +12516,7 @@
         <v>78625461</v>
       </c>
     </row>
-    <row r="580" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="580" spans="8:11">
       <c r="H580" t="s">
         <v>92</v>
       </c>
@@ -12404,7 +12530,7 @@
         <v>76375598</v>
       </c>
     </row>
-    <row r="581" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="581" spans="8:11">
       <c r="H581" t="s">
         <v>92</v>
       </c>
@@ -12418,7 +12544,7 @@
         <v>76375597</v>
       </c>
     </row>
-    <row r="582" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="582" spans="8:11">
       <c r="H582" t="s">
         <v>92</v>
       </c>
@@ -12432,7 +12558,7 @@
         <v>76374400</v>
       </c>
     </row>
-    <row r="583" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="583" spans="8:11">
       <c r="H583" t="s">
         <v>92</v>
       </c>
@@ -12446,7 +12572,7 @@
         <v>76374401</v>
       </c>
     </row>
-    <row r="584" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="584" spans="8:11">
       <c r="H584" t="s">
         <v>92</v>
       </c>
@@ -12460,7 +12586,7 @@
         <v>76241042</v>
       </c>
     </row>
-    <row r="585" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="585" spans="8:11">
       <c r="H585" t="s">
         <v>90</v>
       </c>
@@ -12474,7 +12600,7 @@
         <v>76533940</v>
       </c>
     </row>
-    <row r="586" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="586" spans="8:11">
       <c r="H586" t="s">
         <v>92</v>
       </c>
@@ -12488,7 +12614,7 @@
         <v>77463489</v>
       </c>
     </row>
-    <row r="587" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="587" spans="8:11">
       <c r="H587" t="s">
         <v>92</v>
       </c>
@@ -12502,7 +12628,7 @@
         <v>77463490</v>
       </c>
     </row>
-    <row r="588" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="588" spans="8:11">
       <c r="H588" t="s">
         <v>58</v>
       </c>
@@ -12516,7 +12642,7 @@
         <v>78907466</v>
       </c>
     </row>
-    <row r="589" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="589" spans="8:11">
       <c r="H589" t="s">
         <v>58</v>
       </c>
@@ -12530,7 +12656,7 @@
         <v>78907465</v>
       </c>
     </row>
-    <row r="590" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="590" spans="8:11">
       <c r="H590" t="s">
         <v>58</v>
       </c>
@@ -12544,7 +12670,7 @@
         <v>78903848</v>
       </c>
     </row>
-    <row r="591" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="591" spans="8:11">
       <c r="H591" t="s">
         <v>58</v>
       </c>
@@ -12558,7 +12684,7 @@
         <v>78903849</v>
       </c>
     </row>
-    <row r="592" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="592" spans="8:11">
       <c r="H592" t="s">
         <v>58</v>
       </c>
@@ -12572,7 +12698,7 @@
         <v>78621004</v>
       </c>
     </row>
-    <row r="593" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="593" spans="8:11">
       <c r="H593" t="s">
         <v>92</v>
       </c>
@@ -12586,7 +12712,7 @@
         <v>80629877</v>
       </c>
     </row>
-    <row r="594" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="594" spans="8:11">
       <c r="H594" t="s">
         <v>92</v>
       </c>
@@ -12600,7 +12726,7 @@
         <v>80629881</v>
       </c>
     </row>
-    <row r="595" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="595" spans="8:11">
       <c r="H595" s="7" t="s">
         <v>98</v>
       </c>
@@ -12614,7 +12740,7 @@
         <v>80915325</v>
       </c>
     </row>
-    <row r="596" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="596" spans="8:11">
       <c r="H596" s="7" t="s">
         <v>98</v>
       </c>
@@ -12628,7 +12754,7 @@
         <v>80915326</v>
       </c>
     </row>
-    <row r="597" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="597" spans="8:11">
       <c r="H597" s="7" t="s">
         <v>665</v>
       </c>
@@ -12642,7 +12768,7 @@
         <v>80953015</v>
       </c>
     </row>
-    <row r="598" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="598" spans="8:11">
       <c r="H598" s="7" t="s">
         <v>665</v>
       </c>
@@ -12656,7 +12782,7 @@
         <v>80953016</v>
       </c>
     </row>
-    <row r="599" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="599" spans="8:11">
       <c r="H599" s="7" t="s">
         <v>29</v>
       </c>
@@ -12670,7 +12796,7 @@
         <v>81675750</v>
       </c>
     </row>
-    <row r="600" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="600" spans="8:11">
       <c r="H600" s="7" t="s">
         <v>171</v>
       </c>
@@ -12684,7 +12810,7 @@
         <v>81638306</v>
       </c>
     </row>
-    <row r="601" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="601" spans="8:11">
       <c r="H601" s="7" t="s">
         <v>665</v>
       </c>
@@ -12698,7 +12824,7 @@
         <v>81918457</v>
       </c>
     </row>
-    <row r="602" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="602" spans="8:11">
       <c r="H602" s="7" t="s">
         <v>29</v>
       </c>
@@ -12712,7 +12838,7 @@
         <v>81538523</v>
       </c>
     </row>
-    <row r="603" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="603" spans="8:11">
       <c r="H603" s="7" t="s">
         <v>171</v>
       </c>
@@ -12726,7 +12852,7 @@
         <v>79040263</v>
       </c>
     </row>
-    <row r="604" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="604" spans="8:11">
       <c r="H604" s="7" t="s">
         <v>211</v>
       </c>
@@ -12740,7 +12866,7 @@
         <v>79475749</v>
       </c>
     </row>
-    <row r="605" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="605" spans="8:11">
       <c r="H605" s="7" t="s">
         <v>143</v>
       </c>
@@ -12754,7 +12880,7 @@
         <v>79944232</v>
       </c>
     </row>
-    <row r="606" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="606" spans="8:11">
       <c r="H606" s="7" t="s">
         <v>211</v>
       </c>
@@ -12768,7 +12894,7 @@
         <v>80460979</v>
       </c>
     </row>
-    <row r="607" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="607" spans="8:11">
       <c r="H607" s="7" t="s">
         <v>143</v>
       </c>
@@ -12782,7 +12908,7 @@
         <v>81340922</v>
       </c>
     </row>
-    <row r="608" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="608" spans="8:11">
       <c r="H608" s="7" t="s">
         <v>665</v>
       </c>
@@ -12796,7 +12922,7 @@
         <v>38157908</v>
       </c>
     </row>
-    <row r="609" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="609" spans="8:11">
       <c r="H609" s="7" t="s">
         <v>665</v>
       </c>
@@ -12810,7 +12936,7 @@
         <v>41662266</v>
       </c>
     </row>
-    <row r="610" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="610" spans="8:11">
       <c r="H610" s="7" t="s">
         <v>29</v>
       </c>
@@ -12824,7 +12950,7 @@
         <v>81988924</v>
       </c>
     </row>
-    <row r="611" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="611" spans="8:11">
       <c r="H611" s="7" t="s">
         <v>29</v>
       </c>
@@ -12839,7 +12965,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C1">
+  <autoFilter ref="A1:C1" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <sortState ref="A2:C74">
       <sortCondition descending="1" ref="C1"/>
     </sortState>
@@ -12848,29 +12974,50 @@
     <mergeCell ref="A200:C200"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A77:A197 A202:A1048576 A1:A55">
-    <cfRule type="duplicateValues" dxfId="9" priority="11"/>
+  <conditionalFormatting sqref="A77:A197 A202:A206 A1:A55 A209:A1048576">
+    <cfRule type="duplicateValues" dxfId="16" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A199:A1048576 A1:A60 A64:A197">
-    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
+  <conditionalFormatting sqref="A199:A206 A1:A60 A64:A65 A69:A74 A76:A197 A209:A1048576">
+    <cfRule type="duplicateValues" dxfId="15" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A202:A1048576 A1:A60 A64:A197">
-    <cfRule type="duplicateValues" dxfId="7" priority="22"/>
+  <conditionalFormatting sqref="A202:A206 A1:A60 A64:A65 A69:A74 A76:A197 A209:A1048576">
+    <cfRule type="duplicateValues" dxfId="14" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K595:K611">
-    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61:A62">
-    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A63">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+  <conditionalFormatting sqref="A1:A65 A69:A74 A76:A197 A199:A206 A209:A1048576">
+    <cfRule type="duplicateValues" dxfId="9" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A66">
+    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A75">
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A198">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A207">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A208">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A67">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A68">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -12878,16 +13025,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A13:C27"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="1:3" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="20.25">
       <c r="A13" s="4" t="s">
         <v>640</v>
       </c>
@@ -12898,7 +13045,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3">
       <c r="A14" s="3">
         <v>13101217</v>
       </c>
@@ -12909,7 +13056,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3">
       <c r="A15">
         <v>4125377</v>
       </c>
@@ -12920,7 +13067,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="A16">
         <v>26426530</v>
       </c>
@@ -12931,7 +13078,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3">
       <c r="A17">
         <v>43252471</v>
       </c>
@@ -12942,7 +13089,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3">
       <c r="A18">
         <v>64789478</v>
       </c>
@@ -12953,7 +13100,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3">
       <c r="A19">
         <v>71030052</v>
       </c>
@@ -12964,7 +13111,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3">
       <c r="A20">
         <v>11229298</v>
       </c>
@@ -12975,7 +13122,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" hidden="1">
       <c r="A21">
         <v>75077119</v>
       </c>
@@ -12986,7 +13133,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3">
       <c r="A22">
         <v>42519088</v>
       </c>
@@ -12997,7 +13144,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3">
       <c r="A23">
         <v>17579394</v>
       </c>
@@ -13008,7 +13155,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3">
       <c r="A24">
         <v>53569741</v>
       </c>
@@ -13019,7 +13166,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3">
       <c r="A25">
         <v>53583387</v>
       </c>
@@ -13030,7 +13177,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3">
       <c r="A26">
         <v>12439390</v>
       </c>
@@ -13041,7 +13188,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3">
       <c r="A27">
         <v>14107560</v>
       </c>
@@ -13053,17 +13200,17 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A13:C13">
+  <autoFilter ref="A13:C13" xr:uid="{00000000-0009-0000-0000-000001000000}">
     <sortState ref="A14:C25">
       <sortCondition descending="1" ref="C13"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A26:A27 A14:A24">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A25">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/이슈제품.xlsx
+++ b/data/이슈제품.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OA\Desktop\쿠팡업로드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7814E907-B26F-48F9-8228-1841FDB2D218}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{628CD359-F8C9-4524-A5BB-B6157588E5B8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1640" uniqueCount="673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1646" uniqueCount="678">
   <si>
     <t>오아디머무드등-화이트</t>
   </si>
@@ -1984,10 +1984,6 @@
   </si>
   <si>
     <t>입고X, 11월 초</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>입고X, 10/27 예정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2085,6 +2081,28 @@
   </si>
   <si>
     <t>조절, 11월 3째주 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입고X, 11/27 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입고X, 11/23 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>협의, 11/27 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보아르플로업가열식가습기13L-화이트</t>
+  </si>
+  <si>
+    <t>보아르포스S-화이트</t>
+  </si>
+  <si>
+    <t>생활가전</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2211,7 +2229,57 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="22">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2658,7 +2726,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K611"/>
+  <dimension ref="A1:K613"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
@@ -2903,13 +2971,13 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11">
-        <v>15414324</v>
+        <v>75077119</v>
       </c>
       <c r="B11" t="s">
-        <v>198</v>
+        <v>598</v>
       </c>
       <c r="C11" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H11" t="s">
         <v>29</v>
@@ -2926,13 +2994,13 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12">
-        <v>75077119</v>
-      </c>
-      <c r="B12" t="s">
-        <v>598</v>
+        <v>51623281</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>624</v>
       </c>
       <c r="C12" t="s">
-        <v>643</v>
+        <v>626</v>
       </c>
       <c r="H12" t="s">
         <v>29</v>
@@ -2949,10 +3017,10 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13">
-        <v>51623281</v>
+        <v>51989601</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C13" t="s">
         <v>626</v>
@@ -2972,10 +3040,10 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14">
-        <v>51989601</v>
+        <v>11192166</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>625</v>
+        <v>166</v>
       </c>
       <c r="C14" t="s">
         <v>626</v>
@@ -2995,10 +3063,10 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15">
-        <v>11192166</v>
+        <v>15812678</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="C15" t="s">
         <v>626</v>
@@ -3018,10 +3086,10 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16">
-        <v>15812678</v>
+        <v>12091621</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C16" t="s">
         <v>626</v>
@@ -3041,10 +3109,10 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17">
-        <v>12091621</v>
+        <v>12143584</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="C17" t="s">
         <v>626</v>
@@ -3064,10 +3132,10 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18">
-        <v>12143584</v>
+        <v>11192167</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C18" t="s">
         <v>626</v>
@@ -3087,10 +3155,10 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19">
-        <v>11192167</v>
+        <v>12143581</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C19" t="s">
         <v>626</v>
@@ -3110,10 +3178,10 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20">
-        <v>12143581</v>
+        <v>11192165</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C20" t="s">
         <v>626</v>
@@ -3133,10 +3201,10 @@
     </row>
     <row r="21" spans="1:11" s="3" customFormat="1">
       <c r="A21">
-        <v>11192165</v>
+        <v>11192163</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C21" t="s">
         <v>626</v>
@@ -3156,10 +3224,10 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22">
-        <v>11192163</v>
+        <v>11291291</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="C22" t="s">
         <v>626</v>
@@ -3179,10 +3247,10 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23">
-        <v>11291291</v>
+        <v>16171214</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C23" t="s">
         <v>626</v>
@@ -3202,10 +3270,10 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24">
-        <v>16171214</v>
+        <v>12218847</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C24" t="s">
         <v>626</v>
@@ -3225,10 +3293,10 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25">
-        <v>12218847</v>
+        <v>15838517</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C25" t="s">
         <v>626</v>
@@ -3248,10 +3316,10 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26">
-        <v>15838517</v>
+        <v>12673238</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C26" t="s">
         <v>626</v>
@@ -3271,10 +3339,10 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27">
-        <v>12673238</v>
+        <v>37790051</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="C27" t="s">
         <v>626</v>
@@ -3294,10 +3362,10 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28">
-        <v>37790051</v>
+        <v>37594934</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="C28" t="s">
         <v>626</v>
@@ -3317,10 +3385,10 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29">
-        <v>37594934</v>
+        <v>15702671</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="C29" t="s">
         <v>626</v>
@@ -3340,10 +3408,10 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30">
-        <v>15702671</v>
+        <v>39071990</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="C30" t="s">
         <v>626</v>
@@ -3363,10 +3431,10 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31">
-        <v>39071990</v>
+        <v>52204284</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>160</v>
+        <v>91</v>
       </c>
       <c r="C31" t="s">
         <v>626</v>
@@ -3386,10 +3454,10 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32">
-        <v>52204284</v>
+        <v>39006854</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>91</v>
+        <v>163</v>
       </c>
       <c r="C32" t="s">
         <v>626</v>
@@ -3409,10 +3477,10 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33">
-        <v>39006854</v>
+        <v>39006857</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C33" t="s">
         <v>626</v>
@@ -3432,10 +3500,10 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34">
-        <v>39006857</v>
+        <v>39006855</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C34" t="s">
         <v>626</v>
@@ -3455,10 +3523,10 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35">
-        <v>39006855</v>
+        <v>51883980</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>162</v>
+        <v>361</v>
       </c>
       <c r="C35" t="s">
         <v>626</v>
@@ -3478,10 +3546,10 @@
     </row>
     <row r="36" spans="1:11">
       <c r="A36">
-        <v>51883980</v>
+        <v>52578670</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="C36" t="s">
         <v>626</v>
@@ -3501,10 +3569,10 @@
     </row>
     <row r="37" spans="1:11">
       <c r="A37">
-        <v>52578670</v>
+        <v>52155531</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>366</v>
+        <v>93</v>
       </c>
       <c r="C37" t="s">
         <v>626</v>
@@ -3524,10 +3592,10 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38">
-        <v>52155531</v>
+        <v>15831347</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>93</v>
+        <v>141</v>
       </c>
       <c r="C38" t="s">
         <v>626</v>
@@ -3547,10 +3615,10 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39">
-        <v>15831347</v>
+        <v>32548061</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="C39" t="s">
         <v>626</v>
@@ -3570,10 +3638,10 @@
     </row>
     <row r="40" spans="1:11">
       <c r="A40">
-        <v>32548061</v>
+        <v>35876282</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C40" t="s">
         <v>626</v>
@@ -3593,10 +3661,10 @@
     </row>
     <row r="41" spans="1:11">
       <c r="A41">
-        <v>35876282</v>
+        <v>16805855</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="C41" t="s">
         <v>626</v>
@@ -3616,10 +3684,10 @@
     </row>
     <row r="42" spans="1:11">
       <c r="A42">
-        <v>16805855</v>
+        <v>55381383</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>144</v>
+        <v>383</v>
       </c>
       <c r="C42" t="s">
         <v>626</v>
@@ -3639,10 +3707,10 @@
     </row>
     <row r="43" spans="1:11">
       <c r="A43">
-        <v>55381383</v>
+        <v>55449180</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C43" t="s">
         <v>626</v>
@@ -3662,10 +3730,10 @@
     </row>
     <row r="44" spans="1:11">
       <c r="A44">
-        <v>55449180</v>
+        <v>55384739</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C44" t="s">
         <v>626</v>
@@ -3685,10 +3753,10 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45">
-        <v>55384739</v>
+        <v>55389336</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>387</v>
+        <v>623</v>
       </c>
       <c r="C45" t="s">
         <v>626</v>
@@ -3708,10 +3776,10 @@
     </row>
     <row r="46" spans="1:11">
       <c r="A46">
-        <v>55389336</v>
+        <v>55609278</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>623</v>
+        <v>384</v>
       </c>
       <c r="C46" t="s">
         <v>626</v>
@@ -3731,13 +3799,13 @@
     </row>
     <row r="47" spans="1:11">
       <c r="A47">
-        <v>55609278</v>
+        <v>71042279</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>384</v>
+        <v>565</v>
       </c>
       <c r="C47" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H47" t="s">
         <v>58</v>
@@ -3754,13 +3822,13 @@
     </row>
     <row r="48" spans="1:11">
       <c r="A48">
-        <v>71042279</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>565</v>
+        <v>67630646</v>
+      </c>
+      <c r="B48" t="s">
+        <v>526</v>
       </c>
       <c r="C48" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="H48" t="s">
         <v>58</v>
@@ -3777,10 +3845,10 @@
     </row>
     <row r="49" spans="1:11">
       <c r="A49">
-        <v>67630646</v>
+        <v>64971361</v>
       </c>
       <c r="B49" t="s">
-        <v>526</v>
+        <v>486</v>
       </c>
       <c r="C49" t="s">
         <v>630</v>
@@ -3800,10 +3868,10 @@
     </row>
     <row r="50" spans="1:11">
       <c r="A50">
-        <v>64971361</v>
+        <v>62421723</v>
       </c>
       <c r="B50" t="s">
-        <v>486</v>
+        <v>454</v>
       </c>
       <c r="C50" t="s">
         <v>630</v>
@@ -3823,10 +3891,10 @@
     </row>
     <row r="51" spans="1:11">
       <c r="A51">
-        <v>62421723</v>
+        <v>62374813</v>
       </c>
       <c r="B51" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C51" t="s">
         <v>630</v>
@@ -3846,10 +3914,10 @@
     </row>
     <row r="52" spans="1:11">
       <c r="A52">
-        <v>62374813</v>
+        <v>68462854</v>
       </c>
       <c r="B52" t="s">
-        <v>455</v>
+        <v>532</v>
       </c>
       <c r="C52" t="s">
         <v>630</v>
@@ -3869,10 +3937,10 @@
     </row>
     <row r="53" spans="1:11">
       <c r="A53">
-        <v>68462854</v>
+        <v>64114088</v>
       </c>
       <c r="B53" t="s">
-        <v>532</v>
+        <v>469</v>
       </c>
       <c r="C53" t="s">
         <v>630</v>
@@ -3892,10 +3960,10 @@
     </row>
     <row r="54" spans="1:11">
       <c r="A54">
-        <v>64114088</v>
+        <v>19213859</v>
       </c>
       <c r="B54" t="s">
-        <v>469</v>
+        <v>34</v>
       </c>
       <c r="C54" t="s">
         <v>630</v>
@@ -3915,10 +3983,10 @@
     </row>
     <row r="55" spans="1:11">
       <c r="A55">
-        <v>19213859</v>
+        <v>13004238</v>
       </c>
       <c r="B55" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C55" t="s">
         <v>630</v>
@@ -3936,15 +4004,15 @@
         <v>18928667</v>
       </c>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:11" ht="82.5">
       <c r="A56">
-        <v>13004238</v>
+        <v>37161537</v>
       </c>
       <c r="B56" t="s">
-        <v>36</v>
-      </c>
-      <c r="C56" t="s">
-        <v>630</v>
+        <v>288</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>644</v>
       </c>
       <c r="H56" t="s">
         <v>58</v>
@@ -3961,13 +4029,13 @@
     </row>
     <row r="57" spans="1:11">
       <c r="A57">
-        <v>11229298</v>
+        <v>13745117</v>
       </c>
       <c r="B57" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="C57" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H57" t="s">
         <v>58</v>
@@ -3982,15 +4050,15 @@
         <v>14218802</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="82.5">
+    <row r="58" spans="1:11">
       <c r="A58">
-        <v>37161537</v>
+        <v>73226633</v>
       </c>
       <c r="B58" t="s">
-        <v>288</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>645</v>
+        <v>573</v>
+      </c>
+      <c r="C58" t="s">
+        <v>665</v>
       </c>
       <c r="H58" t="s">
         <v>58</v>
@@ -4006,14 +4074,14 @@
       </c>
     </row>
     <row r="59" spans="1:11">
-      <c r="A59">
-        <v>13745117</v>
+      <c r="A59" s="6">
+        <v>80915325</v>
       </c>
       <c r="B59" t="s">
-        <v>197</v>
+        <v>650</v>
       </c>
       <c r="C59" t="s">
-        <v>646</v>
+        <v>666</v>
       </c>
       <c r="H59" t="s">
         <v>58</v>
@@ -4029,11 +4097,11 @@
       </c>
     </row>
     <row r="60" spans="1:11">
-      <c r="A60">
-        <v>73226633</v>
+      <c r="A60" s="6">
+        <v>80915326</v>
       </c>
       <c r="B60" t="s">
-        <v>573</v>
+        <v>651</v>
       </c>
       <c r="C60" t="s">
         <v>666</v>
@@ -4052,11 +4120,11 @@
       </c>
     </row>
     <row r="61" spans="1:11">
-      <c r="A61" s="6">
-        <v>80915325</v>
+      <c r="A61">
+        <v>73893263</v>
       </c>
       <c r="B61" t="s">
-        <v>651</v>
+        <v>15</v>
       </c>
       <c r="C61" t="s">
         <v>667</v>
@@ -4075,14 +4143,14 @@
       </c>
     </row>
     <row r="62" spans="1:11">
-      <c r="A62" s="6">
-        <v>80915326</v>
+      <c r="A62">
+        <v>5332789</v>
       </c>
       <c r="B62" t="s">
-        <v>652</v>
+        <v>345</v>
       </c>
       <c r="C62" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H62" t="s">
         <v>90</v>
@@ -4099,10 +4167,10 @@
     </row>
     <row r="63" spans="1:11">
       <c r="A63">
-        <v>73893263</v>
+        <v>51016959</v>
       </c>
       <c r="B63" t="s">
-        <v>15</v>
+        <v>346</v>
       </c>
       <c r="C63" t="s">
         <v>668</v>
@@ -4122,10 +4190,10 @@
     </row>
     <row r="64" spans="1:11">
       <c r="A64">
-        <v>5332789</v>
+        <v>73226633</v>
       </c>
       <c r="B64" t="s">
-        <v>345</v>
+        <v>573</v>
       </c>
       <c r="C64" t="s">
         <v>669</v>
@@ -4145,13 +4213,13 @@
     </row>
     <row r="65" spans="1:11">
       <c r="A65">
-        <v>51016959</v>
+        <v>62498583</v>
       </c>
       <c r="B65" t="s">
-        <v>346</v>
+        <v>457</v>
       </c>
       <c r="C65" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="H65" t="s">
         <v>94</v>
@@ -4168,13 +4236,13 @@
     </row>
     <row r="66" spans="1:11">
       <c r="A66">
-        <v>73226633</v>
+        <v>69766464</v>
       </c>
       <c r="B66" t="s">
-        <v>573</v>
+        <v>553</v>
       </c>
       <c r="C66" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H66" t="s">
         <v>94</v>
@@ -4191,13 +4259,13 @@
     </row>
     <row r="67" spans="1:11">
       <c r="A67">
-        <v>62498583</v>
+        <v>38676914</v>
       </c>
       <c r="B67" t="s">
-        <v>457</v>
+        <v>336</v>
       </c>
       <c r="C67" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H67" t="s">
         <v>98</v>
@@ -4214,10 +4282,10 @@
     </row>
     <row r="68" spans="1:11">
       <c r="A68">
-        <v>69766464</v>
+        <v>62499786</v>
       </c>
       <c r="B68" t="s">
-        <v>553</v>
+        <v>456</v>
       </c>
       <c r="C68" t="s">
         <v>672</v>
@@ -4236,6 +4304,15 @@
       </c>
     </row>
     <row r="69" spans="1:11">
+      <c r="A69">
+        <v>36608029</v>
+      </c>
+      <c r="B69" t="s">
+        <v>179</v>
+      </c>
+      <c r="C69" t="s">
+        <v>674</v>
+      </c>
       <c r="H69" t="s">
         <v>98</v>
       </c>
@@ -4327,7 +4404,7 @@
         <v>491</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H75" t="s">
         <v>90</v>
@@ -4350,7 +4427,7 @@
         <v>236</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H76" t="s">
         <v>90</v>
@@ -4373,7 +4450,7 @@
         <v>16</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H77" t="s">
         <v>109</v>
@@ -4396,7 +4473,7 @@
         <v>439</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H78" t="s">
         <v>90</v>
@@ -4419,7 +4496,7 @@
         <v>485</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H79" t="s">
         <v>90</v>
@@ -4442,7 +4519,7 @@
         <v>185</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H80" t="s">
         <v>90</v>
@@ -4465,7 +4542,7 @@
         <v>340</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H81" t="s">
         <v>90</v>
@@ -4488,7 +4565,7 @@
         <v>339</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H82" t="s">
         <v>90</v>
@@ -4511,7 +4588,7 @@
         <v>10</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H83" t="s">
         <v>115</v>
@@ -4534,7 +4611,7 @@
         <v>117</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H84" t="s">
         <v>115</v>
@@ -4557,7 +4634,7 @@
         <v>264</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H85" t="s">
         <v>115</v>
@@ -4580,7 +4657,7 @@
         <v>261</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H86" t="s">
         <v>115</v>
@@ -4603,7 +4680,7 @@
         <v>292</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H87" t="s">
         <v>115</v>
@@ -4626,7 +4703,7 @@
         <v>8</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H88" t="s">
         <v>115</v>
@@ -4649,7 +4726,7 @@
         <v>177</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H89" t="s">
         <v>115</v>
@@ -4672,7 +4749,7 @@
         <v>87</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H90" t="s">
         <v>115</v>
@@ -4695,7 +4772,7 @@
         <v>263</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H91" t="s">
         <v>115</v>
@@ -4718,7 +4795,7 @@
         <v>317</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H92" t="s">
         <v>115</v>
@@ -4741,7 +4818,7 @@
         <v>37</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H93" t="s">
         <v>115</v>
@@ -4764,7 +4841,7 @@
         <v>322</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H94" t="s">
         <v>115</v>
@@ -4787,7 +4864,7 @@
         <v>88</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H95" t="s">
         <v>115</v>
@@ -4810,7 +4887,7 @@
         <v>20</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H96" t="s">
         <v>115</v>
@@ -4833,7 +4910,7 @@
         <v>119</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H97" t="s">
         <v>115</v>
@@ -4856,7 +4933,7 @@
         <v>308</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H98" t="s">
         <v>115</v>
@@ -4879,7 +4956,7 @@
         <v>40</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H99" t="s">
         <v>115</v>
@@ -4902,7 +4979,7 @@
         <v>279</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H100" t="s">
         <v>115</v>
@@ -4925,7 +5002,7 @@
         <v>229</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H101" t="s">
         <v>115</v>
@@ -4948,7 +5025,7 @@
         <v>110</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H102" t="s">
         <v>115</v>
@@ -4971,7 +5048,7 @@
         <v>230</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H103" t="s">
         <v>115</v>
@@ -4994,7 +5071,7 @@
         <v>46</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H104" t="s">
         <v>115</v>
@@ -5017,7 +5094,7 @@
         <v>43</v>
       </c>
       <c r="C105" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H105" t="s">
         <v>115</v>
@@ -5040,7 +5117,7 @@
         <v>325</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H106" t="s">
         <v>115</v>
@@ -5063,7 +5140,7 @@
         <v>298</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H107" t="s">
         <v>115</v>
@@ -5086,7 +5163,7 @@
         <v>9</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H108" t="s">
         <v>115</v>
@@ -5109,7 +5186,7 @@
         <v>135</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H109" t="s">
         <v>115</v>
@@ -5132,7 +5209,7 @@
         <v>265</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H110" t="s">
         <v>115</v>
@@ -5155,7 +5232,7 @@
         <v>299</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H111" t="s">
         <v>29</v>
@@ -5178,7 +5255,7 @@
         <v>377</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H112" t="s">
         <v>56</v>
@@ -5201,7 +5278,7 @@
         <v>378</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H113" t="s">
         <v>56</v>
@@ -5224,7 +5301,7 @@
         <v>412</v>
       </c>
       <c r="C114" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H114" t="s">
         <v>143</v>
@@ -5247,7 +5324,7 @@
         <v>421</v>
       </c>
       <c r="C115" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H115" t="s">
         <v>56</v>
@@ -5270,7 +5347,7 @@
         <v>420</v>
       </c>
       <c r="C116" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H116" t="s">
         <v>56</v>
@@ -5293,7 +5370,7 @@
         <v>428</v>
       </c>
       <c r="C117" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H117" t="s">
         <v>56</v>
@@ -5316,7 +5393,7 @@
         <v>429</v>
       </c>
       <c r="C118" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H118" t="s">
         <v>56</v>
@@ -5339,7 +5416,7 @@
         <v>431</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H119" t="s">
         <v>56</v>
@@ -5362,7 +5439,7 @@
         <v>440</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H120" t="s">
         <v>56</v>
@@ -5385,7 +5462,7 @@
         <v>452</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H121" t="s">
         <v>90</v>
@@ -5408,7 +5485,7 @@
         <v>474</v>
       </c>
       <c r="C122" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H122" t="s">
         <v>152</v>
@@ -5431,7 +5508,7 @@
         <v>479</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H123" t="s">
         <v>152</v>
@@ -5454,7 +5531,7 @@
         <v>492</v>
       </c>
       <c r="C124" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H124" t="s">
         <v>152</v>
@@ -5477,7 +5554,7 @@
         <v>512</v>
       </c>
       <c r="C125" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H125" t="s">
         <v>152</v>
@@ -5500,7 +5577,7 @@
         <v>417</v>
       </c>
       <c r="C126" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H126" t="s">
         <v>58</v>
@@ -5523,7 +5600,7 @@
         <v>67</v>
       </c>
       <c r="C127" s="9" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H127" t="s">
         <v>58</v>
@@ -5546,7 +5623,7 @@
         <v>68</v>
       </c>
       <c r="C128" s="9" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H128" t="s">
         <v>90</v>
@@ -5569,7 +5646,7 @@
         <v>284</v>
       </c>
       <c r="C129" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H129" t="s">
         <v>90</v>
@@ -5592,7 +5669,7 @@
         <v>0</v>
       </c>
       <c r="C130" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H130" t="s">
         <v>29</v>
@@ -5615,7 +5692,7 @@
         <v>419</v>
       </c>
       <c r="C131" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H131" t="s">
         <v>29</v>
@@ -5638,7 +5715,7 @@
         <v>445</v>
       </c>
       <c r="C132" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H132" t="s">
         <v>29</v>
@@ -5661,7 +5738,7 @@
         <v>503</v>
       </c>
       <c r="C133" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H133" t="s">
         <v>58</v>
@@ -5684,7 +5761,7 @@
         <v>35</v>
       </c>
       <c r="C134" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H134" t="s">
         <v>58</v>
@@ -5707,7 +5784,7 @@
         <v>41</v>
       </c>
       <c r="C135" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H135" t="s">
         <v>56</v>
@@ -5730,7 +5807,7 @@
         <v>42</v>
       </c>
       <c r="C136" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H136" t="s">
         <v>90</v>
@@ -5753,7 +5830,7 @@
         <v>48</v>
       </c>
       <c r="C137" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H137" t="s">
         <v>29</v>
@@ -5776,7 +5853,7 @@
         <v>59</v>
       </c>
       <c r="C138" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H138" t="s">
         <v>58</v>
@@ -5799,7 +5876,7 @@
         <v>63</v>
       </c>
       <c r="C139" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H139" t="s">
         <v>58</v>
@@ -5822,7 +5899,7 @@
         <v>64</v>
       </c>
       <c r="C140" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H140" t="s">
         <v>171</v>
@@ -5845,7 +5922,7 @@
         <v>100</v>
       </c>
       <c r="C141" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H141" t="s">
         <v>90</v>
@@ -5868,7 +5945,7 @@
         <v>108</v>
       </c>
       <c r="C142" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H142" t="s">
         <v>171</v>
@@ -5891,7 +5968,7 @@
         <v>140</v>
       </c>
       <c r="C143" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H143" t="s">
         <v>171</v>
@@ -5914,7 +5991,7 @@
         <v>186</v>
       </c>
       <c r="C144" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H144" t="s">
         <v>171</v>
@@ -5937,7 +6014,7 @@
         <v>187</v>
       </c>
       <c r="C145" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H145" t="s">
         <v>171</v>
@@ -5960,7 +6037,7 @@
         <v>188</v>
       </c>
       <c r="C146" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H146" t="s">
         <v>171</v>
@@ -5983,7 +6060,7 @@
         <v>192</v>
       </c>
       <c r="C147" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H147" t="s">
         <v>171</v>
@@ -6006,7 +6083,7 @@
         <v>212</v>
       </c>
       <c r="C148" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H148" t="s">
         <v>171</v>
@@ -6029,7 +6106,7 @@
         <v>217</v>
       </c>
       <c r="C149" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H149" t="s">
         <v>171</v>
@@ -6052,7 +6129,7 @@
         <v>218</v>
       </c>
       <c r="C150" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H150" t="s">
         <v>171</v>
@@ -6075,7 +6152,7 @@
         <v>223</v>
       </c>
       <c r="C151" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H151" t="s">
         <v>171</v>
@@ -6098,7 +6175,7 @@
         <v>227</v>
       </c>
       <c r="C152" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H152" t="s">
         <v>171</v>
@@ -6121,7 +6198,7 @@
         <v>228</v>
       </c>
       <c r="C153" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H153" t="s">
         <v>171</v>
@@ -6144,7 +6221,7 @@
         <v>231</v>
       </c>
       <c r="C154" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H154" t="s">
         <v>171</v>
@@ -6167,7 +6244,7 @@
         <v>237</v>
       </c>
       <c r="C155" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H155" t="s">
         <v>171</v>
@@ -6190,7 +6267,7 @@
         <v>238</v>
       </c>
       <c r="C156" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H156" t="s">
         <v>171</v>
@@ -6213,7 +6290,7 @@
         <v>239</v>
       </c>
       <c r="C157" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H157" t="s">
         <v>171</v>
@@ -6236,7 +6313,7 @@
         <v>240</v>
       </c>
       <c r="C158" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H158" t="s">
         <v>171</v>
@@ -6259,7 +6336,7 @@
         <v>241</v>
       </c>
       <c r="C159" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H159" t="s">
         <v>171</v>
@@ -6282,7 +6359,7 @@
         <v>242</v>
       </c>
       <c r="C160" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H160" t="s">
         <v>171</v>
@@ -6305,7 +6382,7 @@
         <v>243</v>
       </c>
       <c r="C161" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H161" t="s">
         <v>171</v>
@@ -6328,7 +6405,7 @@
         <v>248</v>
       </c>
       <c r="C162" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H162" t="s">
         <v>171</v>
@@ -6351,7 +6428,7 @@
         <v>251</v>
       </c>
       <c r="C163" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H163" t="s">
         <v>171</v>
@@ -6374,7 +6451,7 @@
         <v>254</v>
       </c>
       <c r="C164" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H164" t="s">
         <v>171</v>
@@ -6397,7 +6474,7 @@
         <v>255</v>
       </c>
       <c r="C165" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H165" t="s">
         <v>171</v>
@@ -6420,7 +6497,7 @@
         <v>256</v>
       </c>
       <c r="C166" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H166" t="s">
         <v>171</v>
@@ -6443,7 +6520,7 @@
         <v>257</v>
       </c>
       <c r="C167" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H167" t="s">
         <v>171</v>
@@ -6466,7 +6543,7 @@
         <v>285</v>
       </c>
       <c r="C168" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H168" t="s">
         <v>171</v>
@@ -6489,7 +6566,7 @@
         <v>290</v>
       </c>
       <c r="C169" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H169" t="s">
         <v>171</v>
@@ -6512,7 +6589,7 @@
         <v>291</v>
       </c>
       <c r="C170" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H170" t="s">
         <v>171</v>
@@ -6535,7 +6612,7 @@
         <v>305</v>
       </c>
       <c r="C171" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H171" t="s">
         <v>171</v>
@@ -6558,7 +6635,7 @@
         <v>306</v>
       </c>
       <c r="C172" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H172" t="s">
         <v>171</v>
@@ -6581,7 +6658,7 @@
         <v>309</v>
       </c>
       <c r="C173" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H173" t="s">
         <v>171</v>
@@ -6604,7 +6681,7 @@
         <v>337</v>
       </c>
       <c r="C174" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H174" t="s">
         <v>171</v>
@@ -6627,7 +6704,7 @@
         <v>350</v>
       </c>
       <c r="C175" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H175" t="s">
         <v>171</v>
@@ -6650,7 +6727,7 @@
         <v>363</v>
       </c>
       <c r="C176" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H176" t="s">
         <v>171</v>
@@ -6673,7 +6750,7 @@
         <v>382</v>
       </c>
       <c r="C177" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H177" t="s">
         <v>208</v>
@@ -6696,7 +6773,7 @@
         <v>390</v>
       </c>
       <c r="C178" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H178" t="s">
         <v>208</v>
@@ -6719,7 +6796,7 @@
         <v>436</v>
       </c>
       <c r="C179" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H179" t="s">
         <v>208</v>
@@ -6742,7 +6819,7 @@
         <v>477</v>
       </c>
       <c r="C180" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H180" t="s">
         <v>211</v>
@@ -6765,7 +6842,7 @@
         <v>287</v>
       </c>
       <c r="C181" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H181" t="s">
         <v>211</v>
@@ -6788,7 +6865,7 @@
         <v>6</v>
       </c>
       <c r="C182" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H182" t="s">
         <v>211</v>
@@ -6811,7 +6888,7 @@
         <v>4</v>
       </c>
       <c r="C183" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H183" t="s">
         <v>98</v>
@@ -6834,7 +6911,7 @@
         <v>12</v>
       </c>
       <c r="C184" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H184" t="s">
         <v>98</v>
@@ -6857,7 +6934,7 @@
         <v>209</v>
       </c>
       <c r="C185" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H185" t="s">
         <v>98</v>
@@ -6880,7 +6957,7 @@
         <v>289</v>
       </c>
       <c r="C186" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H186" t="s">
         <v>98</v>
@@ -6903,7 +6980,7 @@
         <v>139</v>
       </c>
       <c r="C187" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H187" t="s">
         <v>98</v>
@@ -6926,7 +7003,7 @@
         <v>2</v>
       </c>
       <c r="C188" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H188" t="s">
         <v>98</v>
@@ -6949,7 +7026,7 @@
         <v>219</v>
       </c>
       <c r="C189" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H189" t="s">
         <v>98</v>
@@ -6972,7 +7049,7 @@
         <v>294</v>
       </c>
       <c r="C190" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H190" t="s">
         <v>98</v>
@@ -6995,7 +7072,7 @@
         <v>136</v>
       </c>
       <c r="C191" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H191" t="s">
         <v>98</v>
@@ -7018,7 +7095,7 @@
         <v>307</v>
       </c>
       <c r="C192" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H192" t="s">
         <v>92</v>
@@ -7041,7 +7118,7 @@
         <v>7</v>
       </c>
       <c r="C193" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H193" t="s">
         <v>92</v>
@@ -7064,7 +7141,7 @@
         <v>418</v>
       </c>
       <c r="C194" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H194" t="s">
         <v>92</v>
@@ -7087,7 +7164,7 @@
         <v>11</v>
       </c>
       <c r="C195" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H195" t="s">
         <v>92</v>
@@ -7110,7 +7187,7 @@
         <v>427</v>
       </c>
       <c r="C196" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H196" t="s">
         <v>92</v>
@@ -7133,7 +7210,7 @@
         <v>3</v>
       </c>
       <c r="C197" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H197" t="s">
         <v>92</v>
@@ -7156,7 +7233,7 @@
         <v>564</v>
       </c>
       <c r="C198" s="10" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H198" t="s">
         <v>92</v>
@@ -7187,7 +7264,7 @@
     </row>
     <row r="200" spans="1:11">
       <c r="A200" s="13" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B200" s="13"/>
       <c r="C200" s="13"/>
@@ -12734,7 +12811,7 @@
         <v>80915325</v>
       </c>
       <c r="J595" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="K595" s="6">
         <v>80915325</v>
@@ -12748,7 +12825,7 @@
         <v>80915326</v>
       </c>
       <c r="J596" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="K596" s="6">
         <v>80915326</v>
@@ -12756,13 +12833,13 @@
     </row>
     <row r="597" spans="8:11">
       <c r="H597" s="7" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="I597" s="6">
         <v>80953015</v>
       </c>
       <c r="J597" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K597" s="6">
         <v>80953015</v>
@@ -12770,13 +12847,13 @@
     </row>
     <row r="598" spans="8:11">
       <c r="H598" s="7" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="I598" s="6">
         <v>80953016</v>
       </c>
       <c r="J598" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="K598" s="6">
         <v>80953016</v>
@@ -12804,7 +12881,7 @@
         <v>81638306</v>
       </c>
       <c r="J600" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="K600" s="6">
         <v>81638306</v>
@@ -12812,13 +12889,13 @@
     </row>
     <row r="601" spans="8:11">
       <c r="H601" s="7" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="I601" s="6">
         <v>81918457</v>
       </c>
       <c r="J601" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="K601" s="6">
         <v>81918457</v>
@@ -12832,7 +12909,7 @@
         <v>81538523</v>
       </c>
       <c r="J602" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K602" s="6">
         <v>81538523</v>
@@ -12846,7 +12923,7 @@
         <v>79040263</v>
       </c>
       <c r="J603" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="K603" s="6">
         <v>79040263</v>
@@ -12860,7 +12937,7 @@
         <v>79475749</v>
       </c>
       <c r="J604" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K604" s="6">
         <v>79475749</v>
@@ -12874,7 +12951,7 @@
         <v>79944232</v>
       </c>
       <c r="J605" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="K605" s="6">
         <v>79944232</v>
@@ -12888,7 +12965,7 @@
         <v>80460979</v>
       </c>
       <c r="J606" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="K606" s="6">
         <v>80460979</v>
@@ -12902,7 +12979,7 @@
         <v>81340922</v>
       </c>
       <c r="J607" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="K607" s="6">
         <v>81340922</v>
@@ -12910,7 +12987,7 @@
     </row>
     <row r="608" spans="8:11">
       <c r="H608" s="7" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="I608" s="6">
         <v>38157908</v>
@@ -12924,7 +13001,7 @@
     </row>
     <row r="609" spans="8:11">
       <c r="H609" s="7" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="I609" s="6">
         <v>41662266</v>
@@ -12944,7 +13021,7 @@
         <v>81988924</v>
       </c>
       <c r="J610" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="K610" s="6">
         <v>81988924</v>
@@ -12958,10 +13035,38 @@
         <v>82014131</v>
       </c>
       <c r="J611" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="K611" s="6">
         <v>82014131</v>
+      </c>
+    </row>
+    <row r="612" spans="8:11">
+      <c r="H612" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I612">
+        <v>82118965</v>
+      </c>
+      <c r="J612" t="s">
+        <v>675</v>
+      </c>
+      <c r="K612">
+        <v>82118965</v>
+      </c>
+    </row>
+    <row r="613" spans="8:11">
+      <c r="H613" s="7" t="s">
+        <v>677</v>
+      </c>
+      <c r="I613">
+        <v>82521123</v>
+      </c>
+      <c r="J613" t="s">
+        <v>676</v>
+      </c>
+      <c r="K613">
+        <v>82521123</v>
       </c>
     </row>
   </sheetData>
@@ -12974,49 +13079,64 @@
     <mergeCell ref="A200:C200"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A77:A197 A202:A206 A1:A55 A209:A1048576">
-    <cfRule type="duplicateValues" dxfId="16" priority="18"/>
+  <conditionalFormatting sqref="A62:A63 A199:A206 A1:A58 A72:A74 A76:A197 A209:A1048576">
+    <cfRule type="duplicateValues" dxfId="21" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A199:A206 A1:A60 A64:A65 A69:A74 A76:A197 A209:A1048576">
-    <cfRule type="duplicateValues" dxfId="15" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A202:A206 A1:A60 A64:A65 A69:A74 A76:A197 A209:A1048576">
-    <cfRule type="duplicateValues" dxfId="14" priority="29"/>
+  <conditionalFormatting sqref="A62:A63 A202:A206 A1:A58 A72:A74 A76:A197 A209:A1048576">
+    <cfRule type="duplicateValues" dxfId="20" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="duplicateValues" dxfId="13" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K595:K611">
-    <cfRule type="duplicateValues" dxfId="12" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A61:A62">
-    <cfRule type="duplicateValues" dxfId="11" priority="10"/>
+  <conditionalFormatting sqref="A59:A60">
+    <cfRule type="duplicateValues" dxfId="17" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A63">
-    <cfRule type="duplicateValues" dxfId="10" priority="9"/>
+  <conditionalFormatting sqref="A61">
+    <cfRule type="duplicateValues" dxfId="16" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A65 A69:A74 A76:A197 A199:A206 A209:A1048576">
-    <cfRule type="duplicateValues" dxfId="9" priority="8"/>
+  <conditionalFormatting sqref="A64">
+    <cfRule type="duplicateValues" dxfId="15" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A75">
+    <cfRule type="duplicateValues" dxfId="14" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A198">
+    <cfRule type="duplicateValues" dxfId="13" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A207">
+    <cfRule type="duplicateValues" dxfId="12" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A208">
+    <cfRule type="duplicateValues" dxfId="11" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A65">
+    <cfRule type="duplicateValues" dxfId="10" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A66">
-    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A75">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A198">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A207">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A208">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A67">
+    <cfRule type="duplicateValues" dxfId="8" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A68">
+    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A69">
+    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A77:A197 A202:A206 A1:A54 A209:A1048576">
+    <cfRule type="duplicateValues" dxfId="5" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A63 A72:A74 A76:A197 A199:A206 A209:A1048576">
+    <cfRule type="duplicateValues" dxfId="2" priority="49"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K612">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A68">
+  <conditionalFormatting sqref="K613">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13207,10 +13327,10 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A26:A27 A14:A24">
-    <cfRule type="duplicateValues" dxfId="8" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A25">
-    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/이슈제품.xlsx
+++ b/data/이슈제품.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OA\Desktop\쿠팡업로드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{628CD359-F8C9-4524-A5BB-B6157588E5B8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37BCEC90-8DB6-4BB2-959C-BE0B7E9E2CEB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1646" uniqueCount="678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1640" uniqueCount="675">
   <si>
     <t>오아디머무드등-화이트</t>
   </si>
@@ -1992,10 +1992,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>입고X, 10/28 예정</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>단종예정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2084,15 +2080,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>입고X, 11/27 예정</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>입고X, 11/23 예정</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>협의, 11/27 예정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2110,7 +2098,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2727,7 +2715,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K613"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37.875" bestFit="1" customWidth="1"/>
@@ -2739,7 +2727,7 @@
     <col min="11" max="12" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>23</v>
       </c>
@@ -2762,7 +2750,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>4152606</v>
       </c>
@@ -2785,7 +2773,7 @@
         <v>3636925</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>12263239</v>
       </c>
@@ -2808,7 +2796,7 @@
         <v>3636926</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>68880617</v>
       </c>
@@ -2831,7 +2819,7 @@
         <v>3636927</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>65933937</v>
       </c>
@@ -2854,7 +2842,7 @@
         <v>39415252</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>76375597</v>
       </c>
@@ -2877,7 +2865,7 @@
         <v>19213859</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>60015061</v>
       </c>
@@ -2900,7 +2888,7 @@
         <v>20342327</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>50725354</v>
       </c>
@@ -2923,7 +2911,7 @@
         <v>13004238</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>50153946</v>
       </c>
@@ -2946,7 +2934,7 @@
         <v>20341619</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>75741354</v>
       </c>
@@ -2969,7 +2957,7 @@
         <v>11092035</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>75077119</v>
       </c>
@@ -2992,7 +2980,7 @@
         <v>40852278</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>51623281</v>
       </c>
@@ -3015,7 +3003,7 @@
         <v>29266932</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>51989601</v>
       </c>
@@ -3038,7 +3026,7 @@
         <v>12586373</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>11192166</v>
       </c>
@@ -3061,7 +3049,7 @@
         <v>11055651</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>15812678</v>
       </c>
@@ -3084,7 +3072,7 @@
         <v>38659485</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>12091621</v>
       </c>
@@ -3107,7 +3095,7 @@
         <v>9567647</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>12143584</v>
       </c>
@@ -3130,7 +3118,7 @@
         <v>40180424</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>11192167</v>
       </c>
@@ -3153,7 +3141,7 @@
         <v>39228155</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>12143581</v>
       </c>
@@ -3176,7 +3164,7 @@
         <v>38407975</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>11192165</v>
       </c>
@@ -3199,7 +3187,7 @@
         <v>38545387</v>
       </c>
     </row>
-    <row r="21" spans="1:11" s="3" customFormat="1">
+    <row r="21" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>11192163</v>
       </c>
@@ -3222,7 +3210,7 @@
         <v>18816827</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>11291291</v>
       </c>
@@ -3245,7 +3233,7 @@
         <v>39278162</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>16171214</v>
       </c>
@@ -3268,7 +3256,7 @@
         <v>13100374</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>12218847</v>
       </c>
@@ -3291,7 +3279,7 @@
         <v>10855225</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>15838517</v>
       </c>
@@ -3314,7 +3302,7 @@
         <v>38490171</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>12673238</v>
       </c>
@@ -3337,7 +3325,7 @@
         <v>38490170</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>37790051</v>
       </c>
@@ -3360,7 +3348,7 @@
         <v>38417027</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>37594934</v>
       </c>
@@ -3383,7 +3371,7 @@
         <v>13099542</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>15702671</v>
       </c>
@@ -3406,7 +3394,7 @@
         <v>10324264</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>39071990</v>
       </c>
@@ -3429,7 +3417,7 @@
         <v>39229235</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>52204284</v>
       </c>
@@ -3452,7 +3440,7 @@
         <v>12775098</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>39006854</v>
       </c>
@@ -3475,7 +3463,7 @@
         <v>12775097</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>39006857</v>
       </c>
@@ -3498,7 +3486,7 @@
         <v>12775096</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>39006855</v>
       </c>
@@ -3521,7 +3509,7 @@
         <v>13151160</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>51883980</v>
       </c>
@@ -3544,7 +3532,7 @@
         <v>13151158</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>52578670</v>
       </c>
@@ -3567,7 +3555,7 @@
         <v>35403063</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>52155531</v>
       </c>
@@ -3590,7 +3578,7 @@
         <v>13473750</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>15831347</v>
       </c>
@@ -3613,7 +3601,7 @@
         <v>17014694</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>32548061</v>
       </c>
@@ -3636,7 +3624,7 @@
         <v>17014693</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>35876282</v>
       </c>
@@ -3659,7 +3647,7 @@
         <v>13101218</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>16805855</v>
       </c>
@@ -3682,7 +3670,7 @@
         <v>13101217</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>55381383</v>
       </c>
@@ -3705,7 +3693,7 @@
         <v>16981939</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>55449180</v>
       </c>
@@ -3728,7 +3716,7 @@
         <v>12846219</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>55384739</v>
       </c>
@@ -3751,7 +3739,7 @@
         <v>17398556</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>55389336</v>
       </c>
@@ -3774,7 +3762,7 @@
         <v>16972627</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>55609278</v>
       </c>
@@ -3797,7 +3785,7 @@
         <v>12846215</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>71042279</v>
       </c>
@@ -3820,7 +3808,7 @@
         <v>39663616</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>67630646</v>
       </c>
@@ -3843,7 +3831,7 @@
         <v>37843037</v>
       </c>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>64971361</v>
       </c>
@@ -3866,7 +3854,7 @@
         <v>12465755</v>
       </c>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>62421723</v>
       </c>
@@ -3889,7 +3877,7 @@
         <v>11671481</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>62374813</v>
       </c>
@@ -3912,7 +3900,7 @@
         <v>12685386</v>
       </c>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>68462854</v>
       </c>
@@ -3935,7 +3923,7 @@
         <v>12674974</v>
       </c>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>64114088</v>
       </c>
@@ -3958,7 +3946,7 @@
         <v>12674973</v>
       </c>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>19213859</v>
       </c>
@@ -3981,7 +3969,7 @@
         <v>27515992</v>
       </c>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>13004238</v>
       </c>
@@ -4004,7 +3992,7 @@
         <v>18928667</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="82.5">
+    <row r="56" spans="1:11" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>37161537</v>
       </c>
@@ -4027,16 +4015,7 @@
         <v>14218803</v>
       </c>
     </row>
-    <row r="57" spans="1:11">
-      <c r="A57">
-        <v>13745117</v>
-      </c>
-      <c r="B57" t="s">
-        <v>197</v>
-      </c>
-      <c r="C57" t="s">
-        <v>645</v>
-      </c>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H57" t="s">
         <v>58</v>
       </c>
@@ -4050,7 +4029,7 @@
         <v>14218802</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>73226633</v>
       </c>
@@ -4058,7 +4037,7 @@
         <v>573</v>
       </c>
       <c r="C58" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H58" t="s">
         <v>58</v>
@@ -4073,15 +4052,15 @@
         <v>14473529</v>
       </c>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="6">
         <v>80915325</v>
       </c>
       <c r="B59" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C59" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H59" t="s">
         <v>58</v>
@@ -4096,15 +4075,15 @@
         <v>25512595</v>
       </c>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="6">
         <v>80915326</v>
       </c>
       <c r="B60" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C60" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H60" t="s">
         <v>58</v>
@@ -4119,7 +4098,7 @@
         <v>25433097</v>
       </c>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>73893263</v>
       </c>
@@ -4127,7 +4106,7 @@
         <v>15</v>
       </c>
       <c r="C61" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H61" t="s">
         <v>58</v>
@@ -4142,7 +4121,7 @@
         <v>50012601</v>
       </c>
     </row>
-    <row r="62" spans="1:11">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>5332789</v>
       </c>
@@ -4150,7 +4129,7 @@
         <v>345</v>
       </c>
       <c r="C62" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H62" t="s">
         <v>90</v>
@@ -4165,7 +4144,7 @@
         <v>52204284</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>51016959</v>
       </c>
@@ -4173,7 +4152,7 @@
         <v>346</v>
       </c>
       <c r="C63" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H63" t="s">
         <v>92</v>
@@ -4188,7 +4167,7 @@
         <v>52155531</v>
       </c>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>73226633</v>
       </c>
@@ -4196,7 +4175,7 @@
         <v>573</v>
       </c>
       <c r="C64" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H64" t="s">
         <v>94</v>
@@ -4211,7 +4190,7 @@
         <v>10814871</v>
       </c>
     </row>
-    <row r="65" spans="1:11">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>62498583</v>
       </c>
@@ -4219,7 +4198,7 @@
         <v>457</v>
       </c>
       <c r="C65" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H65" t="s">
         <v>94</v>
@@ -4234,7 +4213,7 @@
         <v>31792560</v>
       </c>
     </row>
-    <row r="66" spans="1:11">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>69766464</v>
       </c>
@@ -4242,7 +4221,7 @@
         <v>553</v>
       </c>
       <c r="C66" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H66" t="s">
         <v>94</v>
@@ -4257,7 +4236,7 @@
         <v>10694343</v>
       </c>
     </row>
-    <row r="67" spans="1:11">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>38676914</v>
       </c>
@@ -4265,7 +4244,7 @@
         <v>336</v>
       </c>
       <c r="C67" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="H67" t="s">
         <v>98</v>
@@ -4280,16 +4259,7 @@
         <v>43431417</v>
       </c>
     </row>
-    <row r="68" spans="1:11">
-      <c r="A68">
-        <v>62499786</v>
-      </c>
-      <c r="B68" t="s">
-        <v>456</v>
-      </c>
-      <c r="C68" t="s">
-        <v>672</v>
-      </c>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H68" t="s">
         <v>98</v>
       </c>
@@ -4303,16 +4273,7 @@
         <v>10978754</v>
       </c>
     </row>
-    <row r="69" spans="1:11">
-      <c r="A69">
-        <v>36608029</v>
-      </c>
-      <c r="B69" t="s">
-        <v>179</v>
-      </c>
-      <c r="C69" t="s">
-        <v>674</v>
-      </c>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H69" t="s">
         <v>98</v>
       </c>
@@ -4326,7 +4287,7 @@
         <v>10974363</v>
       </c>
     </row>
-    <row r="70" spans="1:11">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H70" t="s">
         <v>98</v>
       </c>
@@ -4340,7 +4301,7 @@
         <v>39376011</v>
       </c>
     </row>
-    <row r="71" spans="1:11">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H71" t="s">
         <v>98</v>
       </c>
@@ -4354,7 +4315,7 @@
         <v>38310913</v>
       </c>
     </row>
-    <row r="72" spans="1:11">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H72" t="s">
         <v>98</v>
       </c>
@@ -4368,7 +4329,7 @@
         <v>40639939</v>
       </c>
     </row>
-    <row r="73" spans="1:11">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H73" t="s">
         <v>98</v>
       </c>
@@ -4382,7 +4343,7 @@
         <v>44581094</v>
       </c>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H74" t="s">
         <v>98</v>
       </c>
@@ -4396,7 +4357,7 @@
         <v>39270777</v>
       </c>
     </row>
-    <row r="75" spans="1:11">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>65566244</v>
       </c>
@@ -4404,7 +4365,7 @@
         <v>491</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H75" t="s">
         <v>90</v>
@@ -4419,7 +4380,7 @@
         <v>45342904</v>
       </c>
     </row>
-    <row r="76" spans="1:11">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" s="8">
         <v>15826960</v>
       </c>
@@ -4427,7 +4388,7 @@
         <v>236</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H76" t="s">
         <v>90</v>
@@ -4442,7 +4403,7 @@
         <v>19619417</v>
       </c>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" s="8">
         <v>58505144</v>
       </c>
@@ -4450,7 +4411,7 @@
         <v>16</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H77" t="s">
         <v>109</v>
@@ -4465,7 +4426,7 @@
         <v>36606823</v>
       </c>
     </row>
-    <row r="78" spans="1:11">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" s="8">
         <v>61199642</v>
       </c>
@@ -4473,7 +4434,7 @@
         <v>439</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H78" t="s">
         <v>90</v>
@@ -4488,7 +4449,7 @@
         <v>12585217</v>
       </c>
     </row>
-    <row r="79" spans="1:11">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" s="8">
         <v>64912430</v>
       </c>
@@ -4496,7 +4457,7 @@
         <v>485</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H79" t="s">
         <v>90</v>
@@ -4511,7 +4472,7 @@
         <v>11511332</v>
       </c>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" s="8">
         <v>10124384</v>
       </c>
@@ -4519,7 +4480,7 @@
         <v>185</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H80" t="s">
         <v>90</v>
@@ -4534,7 +4495,7 @@
         <v>12579597</v>
       </c>
     </row>
-    <row r="81" spans="1:11">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" s="8">
         <v>10929273</v>
       </c>
@@ -4542,7 +4503,7 @@
         <v>340</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H81" t="s">
         <v>90</v>
@@ -4557,7 +4518,7 @@
         <v>50153946</v>
       </c>
     </row>
-    <row r="82" spans="1:11">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" s="8">
         <v>10929274</v>
       </c>
@@ -4565,7 +4526,7 @@
         <v>339</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H82" t="s">
         <v>90</v>
@@ -4580,7 +4541,7 @@
         <v>50723598</v>
       </c>
     </row>
-    <row r="83" spans="1:11">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" s="8">
         <v>11670520</v>
       </c>
@@ -4588,7 +4549,7 @@
         <v>10</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H83" t="s">
         <v>115</v>
@@ -4603,7 +4564,7 @@
         <v>34464589</v>
       </c>
     </row>
-    <row r="84" spans="1:11">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" s="8">
         <v>12029130</v>
       </c>
@@ -4611,7 +4572,7 @@
         <v>117</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H84" t="s">
         <v>115</v>
@@ -4626,7 +4587,7 @@
         <v>12029130</v>
       </c>
     </row>
-    <row r="85" spans="1:11">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" s="8">
         <v>12038103</v>
       </c>
@@ -4634,7 +4595,7 @@
         <v>264</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H85" t="s">
         <v>115</v>
@@ -4649,7 +4610,7 @@
         <v>46962408</v>
       </c>
     </row>
-    <row r="86" spans="1:11">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" s="8">
         <v>12095120</v>
       </c>
@@ -4657,7 +4618,7 @@
         <v>261</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H86" t="s">
         <v>115</v>
@@ -4672,7 +4633,7 @@
         <v>11874445</v>
       </c>
     </row>
-    <row r="87" spans="1:11">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" s="8">
         <v>12481760</v>
       </c>
@@ -4680,7 +4641,7 @@
         <v>292</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H87" t="s">
         <v>115</v>
@@ -4695,7 +4656,7 @@
         <v>25665354</v>
       </c>
     </row>
-    <row r="88" spans="1:11">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88" s="8">
         <v>13195957</v>
       </c>
@@ -4703,7 +4664,7 @@
         <v>8</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H88" t="s">
         <v>115</v>
@@ -4718,7 +4679,7 @@
         <v>46550390</v>
       </c>
     </row>
-    <row r="89" spans="1:11">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89" s="8">
         <v>14299890</v>
       </c>
@@ -4726,7 +4687,7 @@
         <v>177</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H89" t="s">
         <v>115</v>
@@ -4741,7 +4702,7 @@
         <v>45573288</v>
       </c>
     </row>
-    <row r="90" spans="1:11">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90" s="8">
         <v>14473529</v>
       </c>
@@ -4749,7 +4710,7 @@
         <v>87</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H90" t="s">
         <v>115</v>
@@ -4764,7 +4725,7 @@
         <v>34318450</v>
       </c>
     </row>
-    <row r="91" spans="1:11">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" s="8">
         <v>15757638</v>
       </c>
@@ -4772,7 +4733,7 @@
         <v>263</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H91" t="s">
         <v>115</v>
@@ -4787,7 +4748,7 @@
         <v>45701215</v>
       </c>
     </row>
-    <row r="92" spans="1:11">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92" s="8">
         <v>16806254</v>
       </c>
@@ -4795,7 +4756,7 @@
         <v>317</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H92" t="s">
         <v>115</v>
@@ -4810,7 +4771,7 @@
         <v>15004955</v>
       </c>
     </row>
-    <row r="93" spans="1:11">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" s="8">
         <v>20341619</v>
       </c>
@@ -4818,7 +4779,7 @@
         <v>37</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H93" t="s">
         <v>115</v>
@@ -4833,7 +4794,7 @@
         <v>25321998</v>
       </c>
     </row>
-    <row r="94" spans="1:11">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94" s="8">
         <v>22119013</v>
       </c>
@@ -4841,7 +4802,7 @@
         <v>322</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H94" t="s">
         <v>115</v>
@@ -4856,7 +4817,7 @@
         <v>25321996</v>
       </c>
     </row>
-    <row r="95" spans="1:11">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95" s="8">
         <v>25433097</v>
       </c>
@@ -4864,7 +4825,7 @@
         <v>88</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H95" t="s">
         <v>115</v>
@@ -4879,7 +4840,7 @@
         <v>46191377</v>
       </c>
     </row>
-    <row r="96" spans="1:11">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" s="8">
         <v>25512595</v>
       </c>
@@ -4887,7 +4848,7 @@
         <v>20</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H96" t="s">
         <v>115</v>
@@ -4902,7 +4863,7 @@
         <v>45349063</v>
       </c>
     </row>
-    <row r="97" spans="1:11">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" s="8">
         <v>25665354</v>
       </c>
@@ -4910,7 +4871,7 @@
         <v>119</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H97" t="s">
         <v>115</v>
@@ -4925,7 +4886,7 @@
         <v>44996967</v>
       </c>
     </row>
-    <row r="98" spans="1:11">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" s="8">
         <v>29258063</v>
       </c>
@@ -4933,7 +4894,7 @@
         <v>308</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H98" t="s">
         <v>115</v>
@@ -4948,7 +4909,7 @@
         <v>15462869</v>
       </c>
     </row>
-    <row r="99" spans="1:11">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" s="8">
         <v>29266932</v>
       </c>
@@ -4956,7 +4917,7 @@
         <v>40</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H99" t="s">
         <v>115</v>
@@ -4971,7 +4932,7 @@
         <v>15462868</v>
       </c>
     </row>
-    <row r="100" spans="1:11">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" s="8">
         <v>34991467</v>
       </c>
@@ -4979,7 +4940,7 @@
         <v>279</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H100" t="s">
         <v>115</v>
@@ -4994,7 +4955,7 @@
         <v>46671749</v>
       </c>
     </row>
-    <row r="101" spans="1:11">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="8">
         <v>35401181</v>
       </c>
@@ -5002,7 +4963,7 @@
         <v>229</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H101" t="s">
         <v>115</v>
@@ -5017,7 +4978,7 @@
         <v>35137369</v>
       </c>
     </row>
-    <row r="102" spans="1:11">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" s="8">
         <v>36606823</v>
       </c>
@@ -5025,7 +4986,7 @@
         <v>110</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H102" t="s">
         <v>115</v>
@@ -5040,7 +5001,7 @@
         <v>34320929</v>
       </c>
     </row>
-    <row r="103" spans="1:11">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" s="8">
         <v>38157908</v>
       </c>
@@ -5048,7 +5009,7 @@
         <v>230</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H103" t="s">
         <v>115</v>
@@ -5063,7 +5024,7 @@
         <v>34320928</v>
       </c>
     </row>
-    <row r="104" spans="1:11">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" s="8">
         <v>38407975</v>
       </c>
@@ -5071,7 +5032,7 @@
         <v>46</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H104" t="s">
         <v>115</v>
@@ -5086,7 +5047,7 @@
         <v>23200605</v>
       </c>
     </row>
-    <row r="105" spans="1:11">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" s="8">
         <v>38659485</v>
       </c>
@@ -5094,7 +5055,7 @@
         <v>43</v>
       </c>
       <c r="C105" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H105" t="s">
         <v>115</v>
@@ -5109,7 +5070,7 @@
         <v>23200603</v>
       </c>
     </row>
-    <row r="106" spans="1:11">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" s="8">
         <v>39239709</v>
       </c>
@@ -5117,7 +5078,7 @@
         <v>325</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H106" t="s">
         <v>115</v>
@@ -5132,7 +5093,7 @@
         <v>43571361</v>
       </c>
     </row>
-    <row r="107" spans="1:11">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" s="8">
         <v>39944753</v>
       </c>
@@ -5140,7 +5101,7 @@
         <v>298</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H107" t="s">
         <v>115</v>
@@ -5155,7 +5116,7 @@
         <v>43571360</v>
       </c>
     </row>
-    <row r="108" spans="1:11">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" s="8">
         <v>40180424</v>
       </c>
@@ -5163,7 +5124,7 @@
         <v>9</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H108" t="s">
         <v>115</v>
@@ -5178,7 +5139,7 @@
         <v>34330469</v>
       </c>
     </row>
-    <row r="109" spans="1:11">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" s="8">
         <v>43571361</v>
       </c>
@@ -5186,7 +5147,7 @@
         <v>135</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H109" t="s">
         <v>115</v>
@@ -5201,7 +5162,7 @@
         <v>34331612</v>
       </c>
     </row>
-    <row r="110" spans="1:11">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110" s="8">
         <v>46801171</v>
       </c>
@@ -5209,7 +5170,7 @@
         <v>265</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H110" t="s">
         <v>115</v>
@@ -5224,7 +5185,7 @@
         <v>34352694</v>
       </c>
     </row>
-    <row r="111" spans="1:11">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111" s="8">
         <v>48449253</v>
       </c>
@@ -5232,7 +5193,7 @@
         <v>299</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H111" t="s">
         <v>29</v>
@@ -5247,7 +5208,7 @@
         <v>39063227</v>
       </c>
     </row>
-    <row r="112" spans="1:11">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" s="8">
         <v>53967042</v>
       </c>
@@ -5255,7 +5216,7 @@
         <v>377</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H112" t="s">
         <v>56</v>
@@ -5270,7 +5231,7 @@
         <v>15831347</v>
       </c>
     </row>
-    <row r="113" spans="1:11">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113" s="8">
         <v>55275736</v>
       </c>
@@ -5278,7 +5239,7 @@
         <v>378</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H113" t="s">
         <v>56</v>
@@ -5293,7 +5254,7 @@
         <v>12091621</v>
       </c>
     </row>
-    <row r="114" spans="1:11">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114" s="8">
         <v>59759466</v>
       </c>
@@ -5301,7 +5262,7 @@
         <v>412</v>
       </c>
       <c r="C114" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H114" t="s">
         <v>143</v>
@@ -5316,7 +5277,7 @@
         <v>16805855</v>
       </c>
     </row>
-    <row r="115" spans="1:11">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115" s="8">
         <v>60024864</v>
       </c>
@@ -5324,7 +5285,7 @@
         <v>421</v>
       </c>
       <c r="C115" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H115" t="s">
         <v>56</v>
@@ -5339,7 +5300,7 @@
         <v>15812678</v>
       </c>
     </row>
-    <row r="116" spans="1:11">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116" s="8">
         <v>60025950</v>
       </c>
@@ -5347,7 +5308,7 @@
         <v>420</v>
       </c>
       <c r="C116" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H116" t="s">
         <v>56</v>
@@ -5362,7 +5323,7 @@
         <v>12143581</v>
       </c>
     </row>
-    <row r="117" spans="1:11">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117" s="8">
         <v>60541171</v>
       </c>
@@ -5370,7 +5331,7 @@
         <v>428</v>
       </c>
       <c r="C117" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H117" t="s">
         <v>56</v>
@@ -5385,7 +5346,7 @@
         <v>11192165</v>
       </c>
     </row>
-    <row r="118" spans="1:11">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A118" s="8">
         <v>60543356</v>
       </c>
@@ -5393,7 +5354,7 @@
         <v>429</v>
       </c>
       <c r="C118" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H118" t="s">
         <v>56</v>
@@ -5408,7 +5369,7 @@
         <v>11192163</v>
       </c>
     </row>
-    <row r="119" spans="1:11">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119" s="8">
         <v>60615380</v>
       </c>
@@ -5416,7 +5377,7 @@
         <v>431</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H119" t="s">
         <v>56</v>
@@ -5431,7 +5392,7 @@
         <v>12143584</v>
       </c>
     </row>
-    <row r="120" spans="1:11">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A120" s="8">
         <v>61760291</v>
       </c>
@@ -5439,7 +5400,7 @@
         <v>440</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H120" t="s">
         <v>56</v>
@@ -5454,7 +5415,7 @@
         <v>11192167</v>
       </c>
     </row>
-    <row r="121" spans="1:11">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A121" s="8">
         <v>62385013</v>
       </c>
@@ -5462,7 +5423,7 @@
         <v>452</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H121" t="s">
         <v>90</v>
@@ -5477,7 +5438,7 @@
         <v>12673238</v>
       </c>
     </row>
-    <row r="122" spans="1:11">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A122" s="8">
         <v>64606094</v>
       </c>
@@ -5485,7 +5446,7 @@
         <v>474</v>
       </c>
       <c r="C122" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H122" t="s">
         <v>152</v>
@@ -5500,7 +5461,7 @@
         <v>15838517</v>
       </c>
     </row>
-    <row r="123" spans="1:11">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A123" s="8">
         <v>64846264</v>
       </c>
@@ -5508,7 +5469,7 @@
         <v>479</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H123" t="s">
         <v>152</v>
@@ -5523,7 +5484,7 @@
         <v>12218847</v>
       </c>
     </row>
-    <row r="124" spans="1:11">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A124" s="8">
         <v>65566541</v>
       </c>
@@ -5531,7 +5492,7 @@
         <v>492</v>
       </c>
       <c r="C124" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H124" t="s">
         <v>152</v>
@@ -5546,7 +5507,7 @@
         <v>16171214</v>
       </c>
     </row>
-    <row r="125" spans="1:11">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A125" s="8">
         <v>66607099</v>
       </c>
@@ -5554,7 +5515,7 @@
         <v>512</v>
       </c>
       <c r="C125" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H125" t="s">
         <v>152</v>
@@ -5569,7 +5530,7 @@
         <v>11291291</v>
       </c>
     </row>
-    <row r="126" spans="1:11">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A126" s="8">
         <v>59924956</v>
       </c>
@@ -5577,7 +5538,7 @@
         <v>417</v>
       </c>
       <c r="C126" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H126" t="s">
         <v>58</v>
@@ -5592,7 +5553,7 @@
         <v>14134779</v>
       </c>
     </row>
-    <row r="127" spans="1:11">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A127" s="8">
         <v>17014694</v>
       </c>
@@ -5600,7 +5561,7 @@
         <v>67</v>
       </c>
       <c r="C127" s="9" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H127" t="s">
         <v>58</v>
@@ -5615,7 +5576,7 @@
         <v>14134778</v>
       </c>
     </row>
-    <row r="128" spans="1:11">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A128" s="8">
         <v>17014693</v>
       </c>
@@ -5623,7 +5584,7 @@
         <v>68</v>
       </c>
       <c r="C128" s="9" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H128" t="s">
         <v>90</v>
@@ -5638,7 +5599,7 @@
         <v>37790051</v>
       </c>
     </row>
-    <row r="129" spans="1:11">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A129" s="8">
         <v>36811022</v>
       </c>
@@ -5646,7 +5607,7 @@
         <v>284</v>
       </c>
       <c r="C129" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H129" t="s">
         <v>90</v>
@@ -5661,7 +5622,7 @@
         <v>39071990</v>
       </c>
     </row>
-    <row r="130" spans="1:11">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A130" s="8">
         <v>36811023</v>
       </c>
@@ -5669,7 +5630,7 @@
         <v>0</v>
       </c>
       <c r="C130" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H130" t="s">
         <v>29</v>
@@ -5684,7 +5645,7 @@
         <v>39006857</v>
       </c>
     </row>
-    <row r="131" spans="1:11">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131" s="8">
         <v>60023938</v>
       </c>
@@ -5692,7 +5653,7 @@
         <v>419</v>
       </c>
       <c r="C131" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H131" t="s">
         <v>29</v>
@@ -5707,7 +5668,7 @@
         <v>39006855</v>
       </c>
     </row>
-    <row r="132" spans="1:11">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A132" s="8">
         <v>61929494</v>
       </c>
@@ -5715,7 +5676,7 @@
         <v>445</v>
       </c>
       <c r="C132" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H132" t="s">
         <v>29</v>
@@ -5730,7 +5691,7 @@
         <v>39006854</v>
       </c>
     </row>
-    <row r="133" spans="1:11">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133" s="8">
         <v>66417803</v>
       </c>
@@ -5738,7 +5699,7 @@
         <v>503</v>
       </c>
       <c r="C133" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H133" t="s">
         <v>58</v>
@@ -5753,7 +5714,7 @@
         <v>12434130</v>
       </c>
     </row>
-    <row r="134" spans="1:11">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A134" s="8">
         <v>20342327</v>
       </c>
@@ -5761,7 +5722,7 @@
         <v>35</v>
       </c>
       <c r="C134" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H134" t="s">
         <v>58</v>
@@ -5776,7 +5737,7 @@
         <v>11671480</v>
       </c>
     </row>
-    <row r="135" spans="1:11">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135" s="8">
         <v>12586373</v>
       </c>
@@ -5784,7 +5745,7 @@
         <v>41</v>
       </c>
       <c r="C135" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H135" t="s">
         <v>56</v>
@@ -5799,7 +5760,7 @@
         <v>11192166</v>
       </c>
     </row>
-    <row r="136" spans="1:11">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136" s="8">
         <v>11055651</v>
       </c>
@@ -5807,7 +5768,7 @@
         <v>42</v>
       </c>
       <c r="C136" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H136" t="s">
         <v>90</v>
@@ -5822,7 +5783,7 @@
         <v>37594934</v>
       </c>
     </row>
-    <row r="137" spans="1:11">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137" s="8">
         <v>18816827</v>
       </c>
@@ -5830,7 +5791,7 @@
         <v>48</v>
       </c>
       <c r="C137" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H137" t="s">
         <v>29</v>
@@ -5845,7 +5806,7 @@
         <v>32548061</v>
       </c>
     </row>
-    <row r="138" spans="1:11">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138" s="8">
         <v>39229235</v>
       </c>
@@ -5853,7 +5814,7 @@
         <v>59</v>
       </c>
       <c r="C138" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H138" t="s">
         <v>58</v>
@@ -5868,7 +5829,7 @@
         <v>32711387</v>
       </c>
     </row>
-    <row r="139" spans="1:11">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139" s="8">
         <v>13151160</v>
       </c>
@@ -5876,7 +5837,7 @@
         <v>63</v>
       </c>
       <c r="C139" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H139" t="s">
         <v>58</v>
@@ -5891,7 +5852,7 @@
         <v>32710937</v>
       </c>
     </row>
-    <row r="140" spans="1:11">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A140" s="8">
         <v>13151158</v>
       </c>
@@ -5899,7 +5860,7 @@
         <v>64</v>
       </c>
       <c r="C140" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H140" t="s">
         <v>171</v>
@@ -5914,7 +5875,7 @@
         <v>35876282</v>
       </c>
     </row>
-    <row r="141" spans="1:11">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A141" s="8">
         <v>10978754</v>
       </c>
@@ -5922,7 +5883,7 @@
         <v>100</v>
       </c>
       <c r="C141" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H141" t="s">
         <v>90</v>
@@ -5937,7 +5898,7 @@
         <v>15702671</v>
       </c>
     </row>
-    <row r="142" spans="1:11">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A142" s="8">
         <v>19619417</v>
       </c>
@@ -5945,7 +5906,7 @@
         <v>108</v>
       </c>
       <c r="C142" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H142" t="s">
         <v>171</v>
@@ -5960,7 +5921,7 @@
         <v>11229298</v>
       </c>
     </row>
-    <row r="143" spans="1:11">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A143" s="8">
         <v>39063227</v>
       </c>
@@ -5968,7 +5929,7 @@
         <v>140</v>
       </c>
       <c r="C143" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H143" t="s">
         <v>171</v>
@@ -5983,7 +5944,7 @@
         <v>50709616</v>
       </c>
     </row>
-    <row r="144" spans="1:11">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A144" s="8">
         <v>46995055</v>
       </c>
@@ -5991,7 +5952,7 @@
         <v>186</v>
       </c>
       <c r="C144" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H144" t="s">
         <v>171</v>
@@ -6006,7 +5967,7 @@
         <v>37034524</v>
       </c>
     </row>
-    <row r="145" spans="1:11">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A145" s="8">
         <v>11744316</v>
       </c>
@@ -6014,7 +5975,7 @@
         <v>187</v>
       </c>
       <c r="C145" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H145" t="s">
         <v>171</v>
@@ -6029,7 +5990,7 @@
         <v>14299890</v>
       </c>
     </row>
-    <row r="146" spans="1:11">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A146" s="8">
         <v>13069194</v>
       </c>
@@ -6037,7 +5998,7 @@
         <v>188</v>
       </c>
       <c r="C146" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H146" t="s">
         <v>171</v>
@@ -6052,7 +6013,7 @@
         <v>13195811</v>
       </c>
     </row>
-    <row r="147" spans="1:11">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A147" s="8">
         <v>4125381</v>
       </c>
@@ -6060,7 +6021,7 @@
         <v>192</v>
       </c>
       <c r="C147" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H147" t="s">
         <v>171</v>
@@ -6075,7 +6036,7 @@
         <v>36608029</v>
       </c>
     </row>
-    <row r="148" spans="1:11">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A148" s="8">
         <v>42839047</v>
       </c>
@@ -6083,7 +6044,7 @@
         <v>212</v>
       </c>
       <c r="C148" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H148" t="s">
         <v>171</v>
@@ -6098,7 +6059,7 @@
         <v>13195957</v>
       </c>
     </row>
-    <row r="149" spans="1:11">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A149" s="8">
         <v>4152612</v>
       </c>
@@ -6106,7 +6067,7 @@
         <v>217</v>
       </c>
       <c r="C149" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H149" t="s">
         <v>171</v>
@@ -6121,7 +6082,7 @@
         <v>10121189</v>
       </c>
     </row>
-    <row r="150" spans="1:11">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A150" s="8">
         <v>4152610</v>
       </c>
@@ -6129,7 +6090,7 @@
         <v>218</v>
       </c>
       <c r="C150" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H150" t="s">
         <v>171</v>
@@ -6144,7 +6105,7 @@
         <v>8122806</v>
       </c>
     </row>
-    <row r="151" spans="1:11">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A151" s="8">
         <v>34098917</v>
       </c>
@@ -6152,7 +6113,7 @@
         <v>223</v>
       </c>
       <c r="C151" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H151" t="s">
         <v>171</v>
@@ -6167,7 +6128,7 @@
         <v>48477550</v>
       </c>
     </row>
-    <row r="152" spans="1:11">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A152" s="8">
         <v>49985232</v>
       </c>
@@ -6175,7 +6136,7 @@
         <v>227</v>
       </c>
       <c r="C152" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H152" t="s">
         <v>171</v>
@@ -6190,7 +6151,7 @@
         <v>11288089</v>
       </c>
     </row>
-    <row r="153" spans="1:11">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A153" s="8">
         <v>50155408</v>
       </c>
@@ -6198,7 +6159,7 @@
         <v>228</v>
       </c>
       <c r="C153" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H153" t="s">
         <v>171</v>
@@ -6213,7 +6174,7 @@
         <v>11104533</v>
       </c>
     </row>
-    <row r="154" spans="1:11">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A154" s="8">
         <v>41662266</v>
       </c>
@@ -6221,7 +6182,7 @@
         <v>231</v>
       </c>
       <c r="C154" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H154" t="s">
         <v>171</v>
@@ -6236,7 +6197,7 @@
         <v>10124384</v>
       </c>
     </row>
-    <row r="155" spans="1:11">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A155" s="8">
         <v>13573385</v>
       </c>
@@ -6244,7 +6205,7 @@
         <v>237</v>
       </c>
       <c r="C155" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H155" t="s">
         <v>171</v>
@@ -6259,7 +6220,7 @@
         <v>46995055</v>
       </c>
     </row>
-    <row r="156" spans="1:11">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A156" s="8">
         <v>42871700</v>
       </c>
@@ -6267,7 +6228,7 @@
         <v>238</v>
       </c>
       <c r="C156" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H156" t="s">
         <v>171</v>
@@ -6282,7 +6243,7 @@
         <v>11744316</v>
       </c>
     </row>
-    <row r="157" spans="1:11">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A157" s="8">
         <v>39257536</v>
       </c>
@@ -6290,7 +6251,7 @@
         <v>239</v>
       </c>
       <c r="C157" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H157" t="s">
         <v>171</v>
@@ -6305,7 +6266,7 @@
         <v>13069194</v>
       </c>
     </row>
-    <row r="158" spans="1:11">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A158" s="8">
         <v>37424126</v>
       </c>
@@ -6313,7 +6274,7 @@
         <v>240</v>
       </c>
       <c r="C158" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H158" t="s">
         <v>171</v>
@@ -6328,7 +6289,7 @@
         <v>19365568</v>
       </c>
     </row>
-    <row r="159" spans="1:11">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A159" s="8">
         <v>36802614</v>
       </c>
@@ -6336,7 +6297,7 @@
         <v>241</v>
       </c>
       <c r="C159" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H159" t="s">
         <v>171</v>
@@ -6351,7 +6312,7 @@
         <v>47861038</v>
       </c>
     </row>
-    <row r="160" spans="1:11">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A160" s="8">
         <v>36577826</v>
       </c>
@@ -6359,7 +6320,7 @@
         <v>242</v>
       </c>
       <c r="C160" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H160" t="s">
         <v>171</v>
@@ -6374,7 +6335,7 @@
         <v>43252471</v>
       </c>
     </row>
-    <row r="161" spans="1:11">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A161" s="8">
         <v>26196255</v>
       </c>
@@ -6382,7 +6343,7 @@
         <v>243</v>
       </c>
       <c r="C161" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H161" t="s">
         <v>171</v>
@@ -6397,7 +6358,7 @@
         <v>4125381</v>
       </c>
     </row>
-    <row r="162" spans="1:11">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A162" s="8">
         <v>26019234</v>
       </c>
@@ -6405,7 +6366,7 @@
         <v>248</v>
       </c>
       <c r="C162" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H162" t="s">
         <v>171</v>
@@ -6420,7 +6381,7 @@
         <v>38183281</v>
       </c>
     </row>
-    <row r="163" spans="1:11">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A163" s="8">
         <v>25411238</v>
       </c>
@@ -6428,7 +6389,7 @@
         <v>251</v>
       </c>
       <c r="C163" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H163" t="s">
         <v>171</v>
@@ -6443,7 +6404,7 @@
         <v>14107560</v>
       </c>
     </row>
-    <row r="164" spans="1:11">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A164" s="8">
         <v>26500515</v>
       </c>
@@ -6451,7 +6412,7 @@
         <v>254</v>
       </c>
       <c r="C164" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H164" t="s">
         <v>171</v>
@@ -6466,7 +6427,7 @@
         <v>44916947</v>
       </c>
     </row>
-    <row r="165" spans="1:11">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A165" s="8">
         <v>36162739</v>
       </c>
@@ -6474,7 +6435,7 @@
         <v>255</v>
       </c>
       <c r="C165" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H165" t="s">
         <v>171</v>
@@ -6489,7 +6450,7 @@
         <v>40640374</v>
       </c>
     </row>
-    <row r="166" spans="1:11">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A166" s="8">
         <v>39893389</v>
       </c>
@@ -6497,7 +6458,7 @@
         <v>256</v>
       </c>
       <c r="C166" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H166" t="s">
         <v>171</v>
@@ -6512,7 +6473,7 @@
         <v>13745117</v>
       </c>
     </row>
-    <row r="167" spans="1:11">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A167" s="8">
         <v>39296173</v>
       </c>
@@ -6520,7 +6481,7 @@
         <v>257</v>
       </c>
       <c r="C167" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H167" t="s">
         <v>171</v>
@@ -6535,7 +6496,7 @@
         <v>15414324</v>
       </c>
     </row>
-    <row r="168" spans="1:11">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A168" s="8">
         <v>42217758</v>
       </c>
@@ -6543,7 +6504,7 @@
         <v>285</v>
       </c>
       <c r="C168" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H168" t="s">
         <v>171</v>
@@ -6558,7 +6519,7 @@
         <v>35192489</v>
       </c>
     </row>
-    <row r="169" spans="1:11">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A169" s="8">
         <v>22403445</v>
       </c>
@@ -6566,7 +6527,7 @@
         <v>290</v>
       </c>
       <c r="C169" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H169" t="s">
         <v>171</v>
@@ -6581,7 +6542,7 @@
         <v>40982029</v>
       </c>
     </row>
-    <row r="170" spans="1:11">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A170" s="8">
         <v>26257716</v>
       </c>
@@ -6589,7 +6550,7 @@
         <v>291</v>
       </c>
       <c r="C170" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H170" t="s">
         <v>171</v>
@@ -6604,7 +6565,7 @@
         <v>10858043</v>
       </c>
     </row>
-    <row r="171" spans="1:11">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A171" s="8">
         <v>42486414</v>
       </c>
@@ -6612,7 +6573,7 @@
         <v>305</v>
       </c>
       <c r="C171" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H171" t="s">
         <v>171</v>
@@ -6627,7 +6588,7 @@
         <v>4125377</v>
       </c>
     </row>
-    <row r="172" spans="1:11">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A172" s="8">
         <v>44695653</v>
       </c>
@@ -6635,7 +6596,7 @@
         <v>306</v>
       </c>
       <c r="C172" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H172" t="s">
         <v>171</v>
@@ -6650,7 +6611,7 @@
         <v>26426530</v>
       </c>
     </row>
-    <row r="173" spans="1:11">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A173" s="8">
         <v>13405604</v>
       </c>
@@ -6658,7 +6619,7 @@
         <v>309</v>
       </c>
       <c r="C173" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H173" t="s">
         <v>171</v>
@@ -6673,7 +6634,7 @@
         <v>18980681</v>
       </c>
     </row>
-    <row r="174" spans="1:11">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A174" s="8">
         <v>39911056</v>
       </c>
@@ -6681,7 +6642,7 @@
         <v>337</v>
       </c>
       <c r="C174" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H174" t="s">
         <v>171</v>
@@ -6696,7 +6657,7 @@
         <v>12439390</v>
       </c>
     </row>
-    <row r="175" spans="1:11">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A175" s="8">
         <v>51897600</v>
       </c>
@@ -6704,7 +6665,7 @@
         <v>350</v>
       </c>
       <c r="C175" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H175" t="s">
         <v>171</v>
@@ -6719,7 +6680,7 @@
         <v>12263239</v>
       </c>
     </row>
-    <row r="176" spans="1:11">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A176" s="8">
         <v>52990015</v>
       </c>
@@ -6727,7 +6688,7 @@
         <v>363</v>
       </c>
       <c r="C176" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H176" t="s">
         <v>171</v>
@@ -6742,7 +6703,7 @@
         <v>50725354</v>
       </c>
     </row>
-    <row r="177" spans="1:11">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A177" s="8">
         <v>55354052</v>
       </c>
@@ -6750,7 +6711,7 @@
         <v>382</v>
       </c>
       <c r="C177" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H177" t="s">
         <v>208</v>
@@ -6765,7 +6726,7 @@
         <v>16179047</v>
       </c>
     </row>
-    <row r="178" spans="1:11">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A178" s="8">
         <v>55356388</v>
       </c>
@@ -6773,7 +6734,7 @@
         <v>390</v>
       </c>
       <c r="C178" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H178" t="s">
         <v>208</v>
@@ -6788,7 +6749,7 @@
         <v>20815743</v>
       </c>
     </row>
-    <row r="179" spans="1:11">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A179" s="8">
         <v>62377903</v>
       </c>
@@ -6796,7 +6757,7 @@
         <v>436</v>
       </c>
       <c r="C179" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H179" t="s">
         <v>208</v>
@@ -6811,7 +6772,7 @@
         <v>39651008</v>
       </c>
     </row>
-    <row r="180" spans="1:11">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A180" s="8">
         <v>66097436</v>
       </c>
@@ -6819,7 +6780,7 @@
         <v>477</v>
       </c>
       <c r="C180" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H180" t="s">
         <v>211</v>
@@ -6834,7 +6795,7 @@
         <v>42839047</v>
       </c>
     </row>
-    <row r="181" spans="1:11">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A181" s="8">
         <v>11681261</v>
       </c>
@@ -6842,7 +6803,7 @@
         <v>287</v>
       </c>
       <c r="C181" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H181" t="s">
         <v>211</v>
@@ -6857,7 +6818,7 @@
         <v>38455497</v>
       </c>
     </row>
-    <row r="182" spans="1:11">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A182" s="8">
         <v>11874445</v>
       </c>
@@ -6865,7 +6826,7 @@
         <v>6</v>
       </c>
       <c r="C182" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H182" t="s">
         <v>211</v>
@@ -6880,7 +6841,7 @@
         <v>37173787</v>
       </c>
     </row>
-    <row r="183" spans="1:11">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A183" s="8">
         <v>14719737</v>
       </c>
@@ -6888,7 +6849,7 @@
         <v>4</v>
       </c>
       <c r="C183" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H183" t="s">
         <v>98</v>
@@ -6903,7 +6864,7 @@
         <v>42913903</v>
       </c>
     </row>
-    <row r="184" spans="1:11">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A184" s="8">
         <v>16179047</v>
       </c>
@@ -6911,7 +6872,7 @@
         <v>12</v>
       </c>
       <c r="C184" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H184" t="s">
         <v>98</v>
@@ -6926,7 +6887,7 @@
         <v>41864123</v>
       </c>
     </row>
-    <row r="185" spans="1:11">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A185" s="8">
         <v>20815743</v>
       </c>
@@ -6934,7 +6895,7 @@
         <v>209</v>
       </c>
       <c r="C185" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H185" t="s">
         <v>98</v>
@@ -6949,7 +6910,7 @@
         <v>4152612</v>
       </c>
     </row>
-    <row r="186" spans="1:11">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A186" s="8">
         <v>30405071</v>
       </c>
@@ -6957,7 +6918,7 @@
         <v>289</v>
       </c>
       <c r="C186" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H186" t="s">
         <v>98</v>
@@ -6972,7 +6933,7 @@
         <v>4152610</v>
       </c>
     </row>
-    <row r="187" spans="1:11">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A187" s="8">
         <v>34352694</v>
       </c>
@@ -6980,7 +6941,7 @@
         <v>139</v>
       </c>
       <c r="C187" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H187" t="s">
         <v>98</v>
@@ -6995,7 +6956,7 @@
         <v>35896315</v>
       </c>
     </row>
-    <row r="188" spans="1:11">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A188" s="8">
         <v>35149611</v>
       </c>
@@ -7003,7 +6964,7 @@
         <v>2</v>
       </c>
       <c r="C188" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H188" t="s">
         <v>98</v>
@@ -7018,7 +6979,7 @@
         <v>31743599</v>
       </c>
     </row>
-    <row r="189" spans="1:11">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A189" s="8">
         <v>35896315</v>
       </c>
@@ -7026,7 +6987,7 @@
         <v>219</v>
       </c>
       <c r="C189" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H189" t="s">
         <v>98</v>
@@ -7041,7 +7002,7 @@
         <v>4152608</v>
       </c>
     </row>
-    <row r="190" spans="1:11">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A190" s="8">
         <v>36682232</v>
       </c>
@@ -7049,7 +7010,7 @@
         <v>294</v>
       </c>
       <c r="C190" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H190" t="s">
         <v>98</v>
@@ -7064,7 +7025,7 @@
         <v>4152606</v>
       </c>
     </row>
-    <row r="191" spans="1:11">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A191" s="8">
         <v>43571360</v>
       </c>
@@ -7072,7 +7033,7 @@
         <v>136</v>
       </c>
       <c r="C191" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H191" t="s">
         <v>98</v>
@@ -7087,7 +7048,7 @@
         <v>34098917</v>
       </c>
     </row>
-    <row r="192" spans="1:11">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A192" s="8">
         <v>44374810</v>
       </c>
@@ -7095,7 +7056,7 @@
         <v>307</v>
       </c>
       <c r="C192" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H192" t="s">
         <v>92</v>
@@ -7110,7 +7071,7 @@
         <v>34801754</v>
       </c>
     </row>
-    <row r="193" spans="1:11">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A193" s="8">
         <v>45349063</v>
       </c>
@@ -7118,7 +7079,7 @@
         <v>7</v>
       </c>
       <c r="C193" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H193" t="s">
         <v>92</v>
@@ -7133,7 +7094,7 @@
         <v>37639889</v>
       </c>
     </row>
-    <row r="194" spans="1:11">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A194" s="8">
         <v>59836396</v>
       </c>
@@ -7141,7 +7102,7 @@
         <v>418</v>
       </c>
       <c r="C194" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H194" t="s">
         <v>92</v>
@@ -7156,7 +7117,7 @@
         <v>51533853</v>
       </c>
     </row>
-    <row r="195" spans="1:11">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A195" s="8">
         <v>59927382</v>
       </c>
@@ -7164,7 +7125,7 @@
         <v>11</v>
       </c>
       <c r="C195" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H195" t="s">
         <v>92</v>
@@ -7179,7 +7140,7 @@
         <v>49985232</v>
       </c>
     </row>
-    <row r="196" spans="1:11">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A196" s="8">
         <v>60541542</v>
       </c>
@@ -7187,7 +7148,7 @@
         <v>427</v>
       </c>
       <c r="C196" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H196" t="s">
         <v>92</v>
@@ -7202,7 +7163,7 @@
         <v>50155408</v>
       </c>
     </row>
-    <row r="197" spans="1:11">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A197" s="8">
         <v>66417801</v>
       </c>
@@ -7210,7 +7171,7 @@
         <v>3</v>
       </c>
       <c r="C197" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H197" t="s">
         <v>92</v>
@@ -7225,7 +7186,7 @@
         <v>35401181</v>
       </c>
     </row>
-    <row r="198" spans="1:11">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>71291488</v>
       </c>
@@ -7233,7 +7194,7 @@
         <v>564</v>
       </c>
       <c r="C198" s="10" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H198" t="s">
         <v>92</v>
@@ -7248,7 +7209,7 @@
         <v>47936724</v>
       </c>
     </row>
-    <row r="199" spans="1:11">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H199" t="s">
         <v>92</v>
       </c>
@@ -7262,9 +7223,9 @@
         <v>38417806</v>
       </c>
     </row>
-    <row r="200" spans="1:11">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A200" s="13" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B200" s="13"/>
       <c r="C200" s="13"/>
@@ -7281,7 +7242,7 @@
         <v>38158208</v>
       </c>
     </row>
-    <row r="201" spans="1:11">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B201" s="11"/>
       <c r="H201" t="s">
         <v>92</v>
@@ -7296,7 +7257,7 @@
         <v>12263163</v>
       </c>
     </row>
-    <row r="202" spans="1:11">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B202" s="12"/>
       <c r="H202" t="s">
         <v>92</v>
@@ -7311,7 +7272,7 @@
         <v>15826960</v>
       </c>
     </row>
-    <row r="203" spans="1:11">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B203" s="12"/>
       <c r="H203" t="s">
         <v>92</v>
@@ -7326,7 +7287,7 @@
         <v>13573385</v>
       </c>
     </row>
-    <row r="204" spans="1:11">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B204" s="12"/>
       <c r="H204" t="s">
         <v>92</v>
@@ -7341,7 +7302,7 @@
         <v>42871700</v>
       </c>
     </row>
-    <row r="205" spans="1:11">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B205" s="12"/>
       <c r="H205" t="s">
         <v>92</v>
@@ -7356,7 +7317,7 @@
         <v>39257536</v>
       </c>
     </row>
-    <row r="206" spans="1:11">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B206" s="12"/>
       <c r="H206" t="s">
         <v>92</v>
@@ -7371,7 +7332,7 @@
         <v>37424126</v>
       </c>
     </row>
-    <row r="207" spans="1:11">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H207" t="s">
         <v>92</v>
       </c>
@@ -7385,7 +7346,7 @@
         <v>36802614</v>
       </c>
     </row>
-    <row r="208" spans="1:11">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H208" t="s">
         <v>92</v>
       </c>
@@ -7399,7 +7360,7 @@
         <v>36577826</v>
       </c>
     </row>
-    <row r="209" spans="2:11">
+    <row r="209" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B209" s="12"/>
       <c r="H209" t="s">
         <v>92</v>
@@ -7414,7 +7375,7 @@
         <v>35149611</v>
       </c>
     </row>
-    <row r="210" spans="2:11">
+    <row r="210" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B210" s="12"/>
       <c r="H210" t="s">
         <v>92</v>
@@ -7429,7 +7390,7 @@
         <v>26196255</v>
       </c>
     </row>
-    <row r="211" spans="2:11">
+    <row r="211" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B211" s="12"/>
       <c r="H211" t="s">
         <v>92</v>
@@ -7444,7 +7405,7 @@
         <v>11156528</v>
       </c>
     </row>
-    <row r="212" spans="2:11">
+    <row r="212" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H212" t="s">
         <v>92</v>
       </c>
@@ -7458,7 +7419,7 @@
         <v>38415503</v>
       </c>
     </row>
-    <row r="213" spans="2:11">
+    <row r="213" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H213" t="s">
         <v>92</v>
       </c>
@@ -7472,7 +7433,7 @@
         <v>37244806</v>
       </c>
     </row>
-    <row r="214" spans="2:11">
+    <row r="214" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H214" t="s">
         <v>92</v>
       </c>
@@ -7486,7 +7447,7 @@
         <v>27011098</v>
       </c>
     </row>
-    <row r="215" spans="2:11">
+    <row r="215" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H215" t="s">
         <v>92</v>
       </c>
@@ -7500,7 +7461,7 @@
         <v>26019234</v>
       </c>
     </row>
-    <row r="216" spans="2:11">
+    <row r="216" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H216" t="s">
         <v>92</v>
       </c>
@@ -7514,7 +7475,7 @@
         <v>13959023</v>
       </c>
     </row>
-    <row r="217" spans="2:11">
+    <row r="217" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H217" t="s">
         <v>92</v>
       </c>
@@ -7528,7 +7489,7 @@
         <v>12496637</v>
       </c>
     </row>
-    <row r="218" spans="2:11">
+    <row r="218" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H218" t="s">
         <v>92</v>
       </c>
@@ -7542,7 +7503,7 @@
         <v>25411238</v>
       </c>
     </row>
-    <row r="219" spans="2:11">
+    <row r="219" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H219" t="s">
         <v>92</v>
       </c>
@@ -7556,7 +7517,7 @@
         <v>38312169</v>
       </c>
     </row>
-    <row r="220" spans="2:11">
+    <row r="220" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H220" t="s">
         <v>92</v>
       </c>
@@ -7570,7 +7531,7 @@
         <v>31886592</v>
       </c>
     </row>
-    <row r="221" spans="2:11">
+    <row r="221" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H221" t="s">
         <v>92</v>
       </c>
@@ -7584,7 +7545,7 @@
         <v>11670520</v>
       </c>
     </row>
-    <row r="222" spans="2:11">
+    <row r="222" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H222" t="s">
         <v>92</v>
       </c>
@@ -7598,7 +7559,7 @@
         <v>26500515</v>
       </c>
     </row>
-    <row r="223" spans="2:11">
+    <row r="223" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H223" t="s">
         <v>92</v>
       </c>
@@ -7612,7 +7573,7 @@
         <v>36162739</v>
       </c>
     </row>
-    <row r="224" spans="2:11">
+    <row r="224" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H224" t="s">
         <v>92</v>
       </c>
@@ -7626,7 +7587,7 @@
         <v>39893389</v>
       </c>
     </row>
-    <row r="225" spans="8:11">
+    <row r="225" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H225" t="s">
         <v>92</v>
       </c>
@@ -7640,7 +7601,7 @@
         <v>39296173</v>
       </c>
     </row>
-    <row r="226" spans="8:11">
+    <row r="226" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H226" t="s">
         <v>92</v>
       </c>
@@ -7654,7 +7615,7 @@
         <v>26491140</v>
       </c>
     </row>
-    <row r="227" spans="8:11">
+    <row r="227" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H227" t="s">
         <v>56</v>
       </c>
@@ -7668,7 +7629,7 @@
         <v>49473587</v>
       </c>
     </row>
-    <row r="228" spans="8:11">
+    <row r="228" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H228" t="s">
         <v>92</v>
       </c>
@@ -7682,7 +7643,7 @@
         <v>50326931</v>
       </c>
     </row>
-    <row r="229" spans="8:11">
+    <row r="229" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H229" t="s">
         <v>152</v>
       </c>
@@ -7696,7 +7657,7 @@
         <v>12095120</v>
       </c>
     </row>
-    <row r="230" spans="8:11">
+    <row r="230" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H230" t="s">
         <v>152</v>
       </c>
@@ -7710,7 +7671,7 @@
         <v>11765770</v>
       </c>
     </row>
-    <row r="231" spans="8:11">
+    <row r="231" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H231" t="s">
         <v>152</v>
       </c>
@@ -7724,7 +7685,7 @@
         <v>15757638</v>
       </c>
     </row>
-    <row r="232" spans="8:11">
+    <row r="232" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H232" t="s">
         <v>152</v>
       </c>
@@ -7738,7 +7699,7 @@
         <v>12038103</v>
       </c>
     </row>
-    <row r="233" spans="8:11">
+    <row r="233" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H233" t="s">
         <v>152</v>
       </c>
@@ -7752,7 +7713,7 @@
         <v>46801171</v>
       </c>
     </row>
-    <row r="234" spans="8:11">
+    <row r="234" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H234" t="s">
         <v>152</v>
       </c>
@@ -7766,7 +7727,7 @@
         <v>10155238</v>
       </c>
     </row>
-    <row r="235" spans="8:11">
+    <row r="235" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H235" t="s">
         <v>152</v>
       </c>
@@ -7780,7 +7741,7 @@
         <v>10816066</v>
       </c>
     </row>
-    <row r="236" spans="8:11">
+    <row r="236" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H236" t="s">
         <v>152</v>
       </c>
@@ -7794,7 +7755,7 @@
         <v>8668649</v>
       </c>
     </row>
-    <row r="237" spans="8:11">
+    <row r="237" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H237" t="s">
         <v>152</v>
       </c>
@@ -7808,7 +7769,7 @@
         <v>36635604</v>
       </c>
     </row>
-    <row r="238" spans="8:11">
+    <row r="238" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H238" t="s">
         <v>109</v>
       </c>
@@ -7822,7 +7783,7 @@
         <v>8837870</v>
       </c>
     </row>
-    <row r="239" spans="8:11">
+    <row r="239" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H239" t="s">
         <v>109</v>
       </c>
@@ -7836,7 +7797,7 @@
         <v>5359040</v>
       </c>
     </row>
-    <row r="240" spans="8:11">
+    <row r="240" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H240" t="s">
         <v>109</v>
       </c>
@@ -7850,7 +7811,7 @@
         <v>42373723</v>
       </c>
     </row>
-    <row r="241" spans="8:11">
+    <row r="241" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H241" t="s">
         <v>109</v>
       </c>
@@ -7864,7 +7825,7 @@
         <v>16303007</v>
       </c>
     </row>
-    <row r="242" spans="8:11">
+    <row r="242" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H242" t="s">
         <v>109</v>
       </c>
@@ -7878,7 +7839,7 @@
         <v>27303665</v>
       </c>
     </row>
-    <row r="243" spans="8:11">
+    <row r="243" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H243" t="s">
         <v>109</v>
       </c>
@@ -7892,7 +7853,7 @@
         <v>5462299</v>
       </c>
     </row>
-    <row r="244" spans="8:11">
+    <row r="244" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H244" t="s">
         <v>109</v>
       </c>
@@ -7906,7 +7867,7 @@
         <v>47220150</v>
       </c>
     </row>
-    <row r="245" spans="8:11">
+    <row r="245" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H245" t="s">
         <v>109</v>
       </c>
@@ -7920,7 +7881,7 @@
         <v>42265154</v>
       </c>
     </row>
-    <row r="246" spans="8:11">
+    <row r="246" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H246" t="s">
         <v>109</v>
       </c>
@@ -7934,7 +7895,7 @@
         <v>48105600</v>
       </c>
     </row>
-    <row r="247" spans="8:11">
+    <row r="247" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H247" t="s">
         <v>109</v>
       </c>
@@ -7948,7 +7909,7 @@
         <v>34991467</v>
       </c>
     </row>
-    <row r="248" spans="8:11">
+    <row r="248" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H248" t="s">
         <v>109</v>
       </c>
@@ -7962,7 +7923,7 @@
         <v>34348663</v>
       </c>
     </row>
-    <row r="249" spans="8:11">
+    <row r="249" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H249" t="s">
         <v>109</v>
       </c>
@@ -7976,7 +7937,7 @@
         <v>34535085</v>
       </c>
     </row>
-    <row r="250" spans="8:11">
+    <row r="250" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H250" t="s">
         <v>109</v>
       </c>
@@ -7990,7 +7951,7 @@
         <v>41140508</v>
       </c>
     </row>
-    <row r="251" spans="8:11">
+    <row r="251" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H251" t="s">
         <v>109</v>
       </c>
@@ -8004,7 +7965,7 @@
         <v>22441147</v>
       </c>
     </row>
-    <row r="252" spans="8:11">
+    <row r="252" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H252" t="s">
         <v>109</v>
       </c>
@@ -8018,7 +7979,7 @@
         <v>36811022</v>
       </c>
     </row>
-    <row r="253" spans="8:11">
+    <row r="253" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H253" t="s">
         <v>109</v>
       </c>
@@ -8032,7 +7993,7 @@
         <v>36811023</v>
       </c>
     </row>
-    <row r="254" spans="8:11">
+    <row r="254" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H254" t="s">
         <v>143</v>
       </c>
@@ -8046,7 +8007,7 @@
         <v>42217758</v>
       </c>
     </row>
-    <row r="255" spans="8:11">
+    <row r="255" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H255" t="s">
         <v>143</v>
       </c>
@@ -8060,7 +8021,7 @@
         <v>39384055</v>
       </c>
     </row>
-    <row r="256" spans="8:11">
+    <row r="256" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H256" t="s">
         <v>143</v>
       </c>
@@ -8074,7 +8035,7 @@
         <v>11681261</v>
       </c>
     </row>
-    <row r="257" spans="8:11">
+    <row r="257" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H257" t="s">
         <v>211</v>
       </c>
@@ -8088,7 +8049,7 @@
         <v>37161537</v>
       </c>
     </row>
-    <row r="258" spans="8:11">
+    <row r="258" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H258" t="s">
         <v>143</v>
       </c>
@@ -8102,7 +8063,7 @@
         <v>30405071</v>
       </c>
     </row>
-    <row r="259" spans="8:11">
+    <row r="259" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H259" t="s">
         <v>143</v>
       </c>
@@ -8116,7 +8077,7 @@
         <v>22403445</v>
       </c>
     </row>
-    <row r="260" spans="8:11">
+    <row r="260" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H260" t="s">
         <v>143</v>
       </c>
@@ -8130,7 +8091,7 @@
         <v>26257716</v>
       </c>
     </row>
-    <row r="261" spans="8:11">
+    <row r="261" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H261" t="s">
         <v>143</v>
       </c>
@@ -8144,7 +8105,7 @@
         <v>12481760</v>
       </c>
     </row>
-    <row r="262" spans="8:11">
+    <row r="262" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H262" t="s">
         <v>143</v>
       </c>
@@ -8158,7 +8119,7 @@
         <v>12481759</v>
       </c>
     </row>
-    <row r="263" spans="8:11">
+    <row r="263" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H263" t="s">
         <v>143</v>
       </c>
@@ -8172,7 +8133,7 @@
         <v>36682232</v>
       </c>
     </row>
-    <row r="264" spans="8:11">
+    <row r="264" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H264" t="s">
         <v>143</v>
       </c>
@@ -8186,7 +8147,7 @@
         <v>46727700</v>
       </c>
     </row>
-    <row r="265" spans="8:11">
+    <row r="265" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H265" t="s">
         <v>143</v>
       </c>
@@ -8200,7 +8161,7 @@
         <v>40771157</v>
       </c>
     </row>
-    <row r="266" spans="8:11">
+    <row r="266" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H266" t="s">
         <v>143</v>
       </c>
@@ -8214,7 +8175,7 @@
         <v>19104731</v>
       </c>
     </row>
-    <row r="267" spans="8:11">
+    <row r="267" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H267" t="s">
         <v>143</v>
       </c>
@@ -8228,7 +8189,7 @@
         <v>39944753</v>
       </c>
     </row>
-    <row r="268" spans="8:11">
+    <row r="268" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H268" t="s">
         <v>143</v>
       </c>
@@ -8242,7 +8203,7 @@
         <v>48449253</v>
       </c>
     </row>
-    <row r="269" spans="8:11">
+    <row r="269" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H269" t="s">
         <v>143</v>
       </c>
@@ -8256,7 +8217,7 @@
         <v>42051062</v>
       </c>
     </row>
-    <row r="270" spans="8:11">
+    <row r="270" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H270" t="s">
         <v>143</v>
       </c>
@@ -8270,7 +8231,7 @@
         <v>18291047</v>
       </c>
     </row>
-    <row r="271" spans="8:11">
+    <row r="271" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H271" t="s">
         <v>143</v>
       </c>
@@ -8284,7 +8245,7 @@
         <v>10727917</v>
       </c>
     </row>
-    <row r="272" spans="8:11">
+    <row r="272" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H272" t="s">
         <v>143</v>
       </c>
@@ -8298,7 +8259,7 @@
         <v>46543317</v>
       </c>
     </row>
-    <row r="273" spans="8:11">
+    <row r="273" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H273" t="s">
         <v>143</v>
       </c>
@@ -8312,7 +8273,7 @@
         <v>13644995</v>
       </c>
     </row>
-    <row r="274" spans="8:11">
+    <row r="274" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H274" t="s">
         <v>143</v>
       </c>
@@ -8326,7 +8287,7 @@
         <v>42486414</v>
       </c>
     </row>
-    <row r="275" spans="8:11">
+    <row r="275" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H275" t="s">
         <v>143</v>
       </c>
@@ -8340,7 +8301,7 @@
         <v>44695653</v>
       </c>
     </row>
-    <row r="276" spans="8:11">
+    <row r="276" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H276" t="s">
         <v>143</v>
       </c>
@@ -8354,7 +8315,7 @@
         <v>44374810</v>
       </c>
     </row>
-    <row r="277" spans="8:11">
+    <row r="277" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H277" t="s">
         <v>143</v>
       </c>
@@ -8368,7 +8329,7 @@
         <v>29258063</v>
       </c>
     </row>
-    <row r="278" spans="8:11">
+    <row r="278" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H278" t="s">
         <v>143</v>
       </c>
@@ -8382,7 +8343,7 @@
         <v>13405604</v>
       </c>
     </row>
-    <row r="279" spans="8:11">
+    <row r="279" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H279" t="s">
         <v>143</v>
       </c>
@@ -8396,7 +8357,7 @@
         <v>10646862</v>
       </c>
     </row>
-    <row r="280" spans="8:11">
+    <row r="280" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H280" t="s">
         <v>143</v>
       </c>
@@ -8410,7 +8371,7 @@
         <v>12362063</v>
       </c>
     </row>
-    <row r="281" spans="8:11">
+    <row r="281" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H281" t="s">
         <v>90</v>
       </c>
@@ -8424,7 +8385,7 @@
         <v>40185196</v>
       </c>
     </row>
-    <row r="282" spans="8:11">
+    <row r="282" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H282" t="s">
         <v>90</v>
       </c>
@@ -8438,7 +8399,7 @@
         <v>15825326</v>
       </c>
     </row>
-    <row r="283" spans="8:11">
+    <row r="283" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H283" t="s">
         <v>90</v>
       </c>
@@ -8452,7 +8413,7 @@
         <v>26375455</v>
       </c>
     </row>
-    <row r="284" spans="8:11">
+    <row r="284" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H284" t="s">
         <v>90</v>
       </c>
@@ -8466,7 +8427,7 @@
         <v>42803850</v>
       </c>
     </row>
-    <row r="285" spans="8:11">
+    <row r="285" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H285" t="s">
         <v>90</v>
       </c>
@@ -8480,7 +8441,7 @@
         <v>50154913</v>
       </c>
     </row>
-    <row r="286" spans="8:11">
+    <row r="286" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H286" t="s">
         <v>90</v>
       </c>
@@ -8494,7 +8455,7 @@
         <v>16806254</v>
       </c>
     </row>
-    <row r="287" spans="8:11">
+    <row r="287" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H287" t="s">
         <v>90</v>
       </c>
@@ -8508,7 +8469,7 @@
         <v>40501253</v>
       </c>
     </row>
-    <row r="288" spans="8:11">
+    <row r="288" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H288" t="s">
         <v>90</v>
       </c>
@@ -8522,7 +8483,7 @@
         <v>14878740</v>
       </c>
     </row>
-    <row r="289" spans="8:11">
+    <row r="289" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H289" t="s">
         <v>90</v>
       </c>
@@ -8536,7 +8497,7 @@
         <v>12673237</v>
       </c>
     </row>
-    <row r="290" spans="8:11">
+    <row r="290" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H290" t="s">
         <v>90</v>
       </c>
@@ -8550,7 +8511,7 @@
         <v>17579662</v>
       </c>
     </row>
-    <row r="291" spans="8:11">
+    <row r="291" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H291" t="s">
         <v>90</v>
       </c>
@@ -8564,7 +8525,7 @@
         <v>14719737</v>
       </c>
     </row>
-    <row r="292" spans="8:11">
+    <row r="292" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H292" t="s">
         <v>90</v>
       </c>
@@ -8578,7 +8539,7 @@
         <v>22119013</v>
       </c>
     </row>
-    <row r="293" spans="8:11">
+    <row r="293" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H293" t="s">
         <v>90</v>
       </c>
@@ -8592,7 +8553,7 @@
         <v>15795597</v>
       </c>
     </row>
-    <row r="294" spans="8:11">
+    <row r="294" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H294" t="s">
         <v>90</v>
       </c>
@@ -8606,7 +8567,7 @@
         <v>12126317</v>
       </c>
     </row>
-    <row r="295" spans="8:11">
+    <row r="295" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H295" t="s">
         <v>90</v>
       </c>
@@ -8620,7 +8581,7 @@
         <v>39239709</v>
       </c>
     </row>
-    <row r="296" spans="8:11">
+    <row r="296" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H296" t="s">
         <v>90</v>
       </c>
@@ -8634,7 +8595,7 @@
         <v>14488275</v>
       </c>
     </row>
-    <row r="297" spans="8:11">
+    <row r="297" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H297" t="s">
         <v>90</v>
       </c>
@@ -8648,7 +8609,7 @@
         <v>42519088</v>
       </c>
     </row>
-    <row r="298" spans="8:11">
+    <row r="298" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H298" t="s">
         <v>90</v>
       </c>
@@ -8662,7 +8623,7 @@
         <v>17579394</v>
       </c>
     </row>
-    <row r="299" spans="8:11">
+    <row r="299" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H299" t="s">
         <v>90</v>
       </c>
@@ -8676,7 +8637,7 @@
         <v>27056005</v>
       </c>
     </row>
-    <row r="300" spans="8:11">
+    <row r="300" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H300" t="s">
         <v>90</v>
       </c>
@@ -8690,7 +8651,7 @@
         <v>24832169</v>
       </c>
     </row>
-    <row r="301" spans="8:11">
+    <row r="301" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H301" t="s">
         <v>171</v>
       </c>
@@ -8704,7 +8665,7 @@
         <v>39147133</v>
       </c>
     </row>
-    <row r="302" spans="8:11">
+    <row r="302" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H302" t="s">
         <v>171</v>
       </c>
@@ -8718,7 +8679,7 @@
         <v>39030281</v>
       </c>
     </row>
-    <row r="303" spans="8:11">
+    <row r="303" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H303" t="s">
         <v>171</v>
       </c>
@@ -8732,7 +8693,7 @@
         <v>13373616</v>
       </c>
     </row>
-    <row r="304" spans="8:11">
+    <row r="304" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H304" t="s">
         <v>171</v>
       </c>
@@ -8746,7 +8707,7 @@
         <v>12757668</v>
       </c>
     </row>
-    <row r="305" spans="8:11">
+    <row r="305" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H305" t="s">
         <v>171</v>
       </c>
@@ -8760,7 +8721,7 @@
         <v>38977260</v>
       </c>
     </row>
-    <row r="306" spans="8:11">
+    <row r="306" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H306" t="s">
         <v>29</v>
       </c>
@@ -8774,7 +8735,7 @@
         <v>38676914</v>
       </c>
     </row>
-    <row r="307" spans="8:11">
+    <row r="307" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H307" t="s">
         <v>29</v>
       </c>
@@ -8788,7 +8749,7 @@
         <v>39911056</v>
       </c>
     </row>
-    <row r="308" spans="8:11">
+    <row r="308" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H308" t="s">
         <v>29</v>
       </c>
@@ -8802,7 +8763,7 @@
         <v>40102936</v>
       </c>
     </row>
-    <row r="309" spans="8:11">
+    <row r="309" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H309" t="s">
         <v>29</v>
       </c>
@@ -8816,7 +8777,7 @@
         <v>10929274</v>
       </c>
     </row>
-    <row r="310" spans="8:11">
+    <row r="310" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H310" t="s">
         <v>29</v>
       </c>
@@ -8830,7 +8791,7 @@
         <v>10929273</v>
       </c>
     </row>
-    <row r="311" spans="8:11">
+    <row r="311" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H311" t="s">
         <v>29</v>
       </c>
@@ -8844,7 +8805,7 @@
         <v>38412071</v>
       </c>
     </row>
-    <row r="312" spans="8:11">
+    <row r="312" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H312" t="s">
         <v>29</v>
       </c>
@@ -8858,7 +8819,7 @@
         <v>29280326</v>
       </c>
     </row>
-    <row r="313" spans="8:11">
+    <row r="313" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H313" t="s">
         <v>29</v>
       </c>
@@ -8872,7 +8833,7 @@
         <v>38412101</v>
       </c>
     </row>
-    <row r="314" spans="8:11">
+    <row r="314" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H314" t="s">
         <v>98</v>
       </c>
@@ -8886,7 +8847,7 @@
         <v>5332788</v>
       </c>
     </row>
-    <row r="315" spans="8:11">
+    <row r="315" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H315" t="s">
         <v>98</v>
       </c>
@@ -8900,7 +8861,7 @@
         <v>5332789</v>
       </c>
     </row>
-    <row r="316" spans="8:11">
+    <row r="316" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H316" t="s">
         <v>98</v>
       </c>
@@ -8914,7 +8875,7 @@
         <v>51016959</v>
       </c>
     </row>
-    <row r="317" spans="8:11">
+    <row r="317" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H317" t="s">
         <v>90</v>
       </c>
@@ -8928,7 +8889,7 @@
         <v>40636333</v>
       </c>
     </row>
-    <row r="318" spans="8:11">
+    <row r="318" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H318" t="s">
         <v>171</v>
       </c>
@@ -8942,7 +8903,7 @@
         <v>50875168</v>
       </c>
     </row>
-    <row r="319" spans="8:11">
+    <row r="319" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H319" t="s">
         <v>58</v>
       </c>
@@ -8956,7 +8917,7 @@
         <v>51623281</v>
       </c>
     </row>
-    <row r="320" spans="8:11">
+    <row r="320" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H320" t="s">
         <v>92</v>
       </c>
@@ -8970,7 +8931,7 @@
         <v>51897600</v>
       </c>
     </row>
-    <row r="321" spans="8:11">
+    <row r="321" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H321" t="s">
         <v>58</v>
       </c>
@@ -8984,7 +8945,7 @@
         <v>51989601</v>
       </c>
     </row>
-    <row r="322" spans="8:11">
+    <row r="322" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H322" t="s">
         <v>109</v>
       </c>
@@ -8998,7 +8959,7 @@
         <v>52390638</v>
       </c>
     </row>
-    <row r="323" spans="8:11">
+    <row r="323" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H323" t="s">
         <v>109</v>
       </c>
@@ -9012,7 +8973,7 @@
         <v>52362395</v>
       </c>
     </row>
-    <row r="324" spans="8:11">
+    <row r="324" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H324" t="s">
         <v>90</v>
       </c>
@@ -9026,7 +8987,7 @@
         <v>52155415</v>
       </c>
     </row>
-    <row r="325" spans="8:11">
+    <row r="325" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H325" t="s">
         <v>92</v>
       </c>
@@ -9040,7 +9001,7 @@
         <v>52162444</v>
       </c>
     </row>
-    <row r="326" spans="8:11">
+    <row r="326" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H326" t="s">
         <v>171</v>
       </c>
@@ -9054,7 +9015,7 @@
         <v>52270898</v>
       </c>
     </row>
-    <row r="327" spans="8:11">
+    <row r="327" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H327" t="s">
         <v>98</v>
       </c>
@@ -9068,7 +9029,7 @@
         <v>52211558</v>
       </c>
     </row>
-    <row r="328" spans="8:11">
+    <row r="328" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H328" t="s">
         <v>98</v>
       </c>
@@ -9082,7 +9043,7 @@
         <v>52217000</v>
       </c>
     </row>
-    <row r="329" spans="8:11">
+    <row r="329" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H329" t="s">
         <v>29</v>
       </c>
@@ -9096,7 +9057,7 @@
         <v>51689222</v>
       </c>
     </row>
-    <row r="330" spans="8:11">
+    <row r="330" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H330" t="s">
         <v>29</v>
       </c>
@@ -9110,7 +9071,7 @@
         <v>51684787</v>
       </c>
     </row>
-    <row r="331" spans="8:11">
+    <row r="331" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H331" t="s">
         <v>29</v>
       </c>
@@ -9124,7 +9085,7 @@
         <v>51883980</v>
       </c>
     </row>
-    <row r="332" spans="8:11">
+    <row r="332" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H332" t="s">
         <v>29</v>
       </c>
@@ -9138,7 +9099,7 @@
         <v>51898514</v>
       </c>
     </row>
-    <row r="333" spans="8:11">
+    <row r="333" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H333" t="s">
         <v>98</v>
       </c>
@@ -9152,7 +9113,7 @@
         <v>52990015</v>
       </c>
     </row>
-    <row r="334" spans="8:11">
+    <row r="334" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H334" t="s">
         <v>29</v>
       </c>
@@ -9166,7 +9127,7 @@
         <v>52581507</v>
       </c>
     </row>
-    <row r="335" spans="8:11">
+    <row r="335" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H335" t="s">
         <v>29</v>
       </c>
@@ -9180,7 +9141,7 @@
         <v>52613211</v>
       </c>
     </row>
-    <row r="336" spans="8:11">
+    <row r="336" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H336" t="s">
         <v>29</v>
       </c>
@@ -9194,7 +9155,7 @@
         <v>52578670</v>
       </c>
     </row>
-    <row r="337" spans="8:11">
+    <row r="337" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H337" t="s">
         <v>171</v>
       </c>
@@ -9208,7 +9169,7 @@
         <v>52874174</v>
       </c>
     </row>
-    <row r="338" spans="8:11">
+    <row r="338" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H338" t="s">
         <v>29</v>
       </c>
@@ -9222,7 +9183,7 @@
         <v>52872566</v>
       </c>
     </row>
-    <row r="339" spans="8:11">
+    <row r="339" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H339" t="s">
         <v>171</v>
       </c>
@@ -9236,7 +9197,7 @@
         <v>54145830</v>
       </c>
     </row>
-    <row r="340" spans="8:11">
+    <row r="340" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H340" t="s">
         <v>29</v>
       </c>
@@ -9250,7 +9211,7 @@
         <v>53052265</v>
       </c>
     </row>
-    <row r="341" spans="8:11">
+    <row r="341" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H341" t="s">
         <v>90</v>
       </c>
@@ -9264,7 +9225,7 @@
         <v>53297446</v>
       </c>
     </row>
-    <row r="342" spans="8:11">
+    <row r="342" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H342" t="s">
         <v>143</v>
       </c>
@@ -9278,7 +9239,7 @@
         <v>53583387</v>
       </c>
     </row>
-    <row r="343" spans="8:11">
+    <row r="343" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H343" t="s">
         <v>143</v>
       </c>
@@ -9292,7 +9253,7 @@
         <v>53564659</v>
       </c>
     </row>
-    <row r="344" spans="8:11">
+    <row r="344" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H344" t="s">
         <v>143</v>
       </c>
@@ -9306,7 +9267,7 @@
         <v>53569741</v>
       </c>
     </row>
-    <row r="345" spans="8:11">
+    <row r="345" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H345" t="s">
         <v>58</v>
       </c>
@@ -9320,7 +9281,7 @@
         <v>53680118</v>
       </c>
     </row>
-    <row r="346" spans="8:11">
+    <row r="346" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H346" t="s">
         <v>92</v>
       </c>
@@ -9334,7 +9295,7 @@
         <v>53776254</v>
       </c>
     </row>
-    <row r="347" spans="8:11">
+    <row r="347" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H347" t="s">
         <v>90</v>
       </c>
@@ -9348,7 +9309,7 @@
         <v>53967042</v>
       </c>
     </row>
-    <row r="348" spans="8:11">
+    <row r="348" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H348" t="s">
         <v>90</v>
       </c>
@@ -9362,7 +9323,7 @@
         <v>55275736</v>
       </c>
     </row>
-    <row r="349" spans="8:11">
+    <row r="349" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H349" t="s">
         <v>90</v>
       </c>
@@ -9376,7 +9337,7 @@
         <v>56663811</v>
       </c>
     </row>
-    <row r="350" spans="8:11">
+    <row r="350" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H350" t="s">
         <v>92</v>
       </c>
@@ -9390,7 +9351,7 @@
         <v>59082806</v>
       </c>
     </row>
-    <row r="351" spans="8:11">
+    <row r="351" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H351" t="s">
         <v>29</v>
       </c>
@@ -9404,7 +9365,7 @@
         <v>55369678</v>
       </c>
     </row>
-    <row r="352" spans="8:11">
+    <row r="352" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H352" t="s">
         <v>58</v>
       </c>
@@ -9418,7 +9379,7 @@
         <v>55354052</v>
       </c>
     </row>
-    <row r="353" spans="8:11">
+    <row r="353" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H353" t="s">
         <v>58</v>
       </c>
@@ -9432,7 +9393,7 @@
         <v>55381383</v>
       </c>
     </row>
-    <row r="354" spans="8:11">
+    <row r="354" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H354" t="s">
         <v>58</v>
       </c>
@@ -9446,7 +9407,7 @@
         <v>55609278</v>
       </c>
     </row>
-    <row r="355" spans="8:11">
+    <row r="355" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H355" t="s">
         <v>90</v>
       </c>
@@ -9460,7 +9421,7 @@
         <v>55356212</v>
       </c>
     </row>
-    <row r="356" spans="8:11">
+    <row r="356" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H356" t="s">
         <v>90</v>
       </c>
@@ -9474,7 +9435,7 @@
         <v>55449180</v>
       </c>
     </row>
-    <row r="357" spans="8:11">
+    <row r="357" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H357" t="s">
         <v>58</v>
       </c>
@@ -9488,7 +9449,7 @@
         <v>55357095</v>
       </c>
     </row>
-    <row r="358" spans="8:11">
+    <row r="358" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H358" t="s">
         <v>58</v>
       </c>
@@ -9502,7 +9463,7 @@
         <v>55384739</v>
       </c>
     </row>
-    <row r="359" spans="8:11">
+    <row r="359" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H359" t="s">
         <v>58</v>
       </c>
@@ -9516,7 +9477,7 @@
         <v>55357155</v>
       </c>
     </row>
-    <row r="360" spans="8:11">
+    <row r="360" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H360" t="s">
         <v>58</v>
       </c>
@@ -9530,7 +9491,7 @@
         <v>55389336</v>
       </c>
     </row>
-    <row r="361" spans="8:11">
+    <row r="361" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H361" t="s">
         <v>171</v>
       </c>
@@ -9544,7 +9505,7 @@
         <v>55356388</v>
       </c>
     </row>
-    <row r="362" spans="8:11">
+    <row r="362" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H362" t="s">
         <v>171</v>
       </c>
@@ -9558,7 +9519,7 @@
         <v>55610213</v>
       </c>
     </row>
-    <row r="363" spans="8:11">
+    <row r="363" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H363" t="s">
         <v>92</v>
       </c>
@@ -9572,7 +9533,7 @@
         <v>55462718</v>
       </c>
     </row>
-    <row r="364" spans="8:11">
+    <row r="364" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H364" t="s">
         <v>58</v>
       </c>
@@ -9586,7 +9547,7 @@
         <v>58084222</v>
       </c>
     </row>
-    <row r="365" spans="8:11">
+    <row r="365" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H365" t="s">
         <v>58</v>
       </c>
@@ -9600,7 +9561,7 @@
         <v>56651433</v>
       </c>
     </row>
-    <row r="366" spans="8:11">
+    <row r="366" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H366" t="s">
         <v>94</v>
       </c>
@@ -9614,7 +9575,7 @@
         <v>56479851</v>
       </c>
     </row>
-    <row r="367" spans="8:11">
+    <row r="367" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H367" t="s">
         <v>90</v>
       </c>
@@ -9628,7 +9589,7 @@
         <v>56667264</v>
       </c>
     </row>
-    <row r="368" spans="8:11">
+    <row r="368" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H368" t="s">
         <v>143</v>
       </c>
@@ -9642,7 +9603,7 @@
         <v>56896464</v>
       </c>
     </row>
-    <row r="369" spans="8:11">
+    <row r="369" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H369" t="s">
         <v>98</v>
       </c>
@@ -9656,7 +9617,7 @@
         <v>57592449</v>
       </c>
     </row>
-    <row r="370" spans="8:11">
+    <row r="370" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H370" t="s">
         <v>92</v>
       </c>
@@ -9670,7 +9631,7 @@
         <v>56183402</v>
       </c>
     </row>
-    <row r="371" spans="8:11">
+    <row r="371" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H371" t="s">
         <v>92</v>
       </c>
@@ -9684,7 +9645,7 @@
         <v>56651667</v>
       </c>
     </row>
-    <row r="372" spans="8:11">
+    <row r="372" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H372" t="s">
         <v>92</v>
       </c>
@@ -9698,7 +9659,7 @@
         <v>58987730</v>
       </c>
     </row>
-    <row r="373" spans="8:11">
+    <row r="373" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H373" t="s">
         <v>171</v>
       </c>
@@ -9712,7 +9673,7 @@
         <v>57422656</v>
       </c>
     </row>
-    <row r="374" spans="8:11">
+    <row r="374" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H374" t="s">
         <v>92</v>
       </c>
@@ -9726,7 +9687,7 @@
         <v>58040260</v>
       </c>
     </row>
-    <row r="375" spans="8:11">
+    <row r="375" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H375" t="s">
         <v>90</v>
       </c>
@@ -9740,7 +9701,7 @@
         <v>59070986</v>
       </c>
     </row>
-    <row r="376" spans="8:11">
+    <row r="376" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H376" t="s">
         <v>98</v>
       </c>
@@ -9754,7 +9715,7 @@
         <v>59058036</v>
       </c>
     </row>
-    <row r="377" spans="8:11">
+    <row r="377" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H377" t="s">
         <v>90</v>
       </c>
@@ -9768,7 +9729,7 @@
         <v>58505144</v>
       </c>
     </row>
-    <row r="378" spans="8:11">
+    <row r="378" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H378" t="s">
         <v>115</v>
       </c>
@@ -9782,7 +9743,7 @@
         <v>58610450</v>
       </c>
     </row>
-    <row r="379" spans="8:11">
+    <row r="379" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H379" t="s">
         <v>143</v>
       </c>
@@ -9796,7 +9757,7 @@
         <v>59056260</v>
       </c>
     </row>
-    <row r="380" spans="8:11">
+    <row r="380" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H380" t="s">
         <v>115</v>
       </c>
@@ -9810,7 +9771,7 @@
         <v>58722261</v>
       </c>
     </row>
-    <row r="381" spans="8:11">
+    <row r="381" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H381" t="s">
         <v>115</v>
       </c>
@@ -9824,7 +9785,7 @@
         <v>58716097</v>
       </c>
     </row>
-    <row r="382" spans="8:11">
+    <row r="382" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H382" t="s">
         <v>115</v>
       </c>
@@ -9838,7 +9799,7 @@
         <v>58730204</v>
       </c>
     </row>
-    <row r="383" spans="8:11">
+    <row r="383" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H383" t="s">
         <v>115</v>
       </c>
@@ -9852,7 +9813,7 @@
         <v>59199875</v>
       </c>
     </row>
-    <row r="384" spans="8:11">
+    <row r="384" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H384" t="s">
         <v>115</v>
       </c>
@@ -9866,7 +9827,7 @@
         <v>59759466</v>
       </c>
     </row>
-    <row r="385" spans="8:11">
+    <row r="385" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H385" t="s">
         <v>92</v>
       </c>
@@ -9880,7 +9841,7 @@
         <v>59332927</v>
       </c>
     </row>
-    <row r="386" spans="8:11">
+    <row r="386" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H386" t="s">
         <v>92</v>
       </c>
@@ -9894,7 +9855,7 @@
         <v>59944694</v>
       </c>
     </row>
-    <row r="387" spans="8:11">
+    <row r="387" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H387" t="s">
         <v>115</v>
       </c>
@@ -9908,7 +9869,7 @@
         <v>60019261</v>
       </c>
     </row>
-    <row r="388" spans="8:11">
+    <row r="388" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H388" t="s">
         <v>143</v>
       </c>
@@ -9922,7 +9883,7 @@
         <v>59932138</v>
       </c>
     </row>
-    <row r="389" spans="8:11">
+    <row r="389" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H389" t="s">
         <v>115</v>
       </c>
@@ -9936,7 +9897,7 @@
         <v>59924956</v>
       </c>
     </row>
-    <row r="390" spans="8:11">
+    <row r="390" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H390" t="s">
         <v>115</v>
       </c>
@@ -9950,7 +9911,7 @@
         <v>59927382</v>
       </c>
     </row>
-    <row r="391" spans="8:11">
+    <row r="391" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H391" t="s">
         <v>115</v>
       </c>
@@ -9964,7 +9925,7 @@
         <v>59836396</v>
       </c>
     </row>
-    <row r="392" spans="8:11">
+    <row r="392" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H392" t="s">
         <v>115</v>
       </c>
@@ -9978,7 +9939,7 @@
         <v>60015061</v>
       </c>
     </row>
-    <row r="393" spans="8:11">
+    <row r="393" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H393" t="s">
         <v>115</v>
       </c>
@@ -9992,7 +9953,7 @@
         <v>60023938</v>
       </c>
     </row>
-    <row r="394" spans="8:11">
+    <row r="394" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H394" t="s">
         <v>115</v>
       </c>
@@ -10006,7 +9967,7 @@
         <v>60025950</v>
       </c>
     </row>
-    <row r="395" spans="8:11">
+    <row r="395" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H395" t="s">
         <v>115</v>
       </c>
@@ -10020,7 +9981,7 @@
         <v>60024864</v>
       </c>
     </row>
-    <row r="396" spans="8:11">
+    <row r="396" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H396" t="s">
         <v>115</v>
       </c>
@@ -10034,7 +9995,7 @@
         <v>60084208</v>
       </c>
     </row>
-    <row r="397" spans="8:11">
+    <row r="397" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H397" t="s">
         <v>92</v>
       </c>
@@ -10048,7 +10009,7 @@
         <v>60085614</v>
       </c>
     </row>
-    <row r="398" spans="8:11">
+    <row r="398" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H398" t="s">
         <v>171</v>
       </c>
@@ -10062,7 +10023,7 @@
         <v>60133592</v>
       </c>
     </row>
-    <row r="399" spans="8:11">
+    <row r="399" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H399" t="s">
         <v>143</v>
       </c>
@@ -10076,7 +10037,7 @@
         <v>60450424</v>
       </c>
     </row>
-    <row r="400" spans="8:11">
+    <row r="400" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H400" t="s">
         <v>143</v>
       </c>
@@ -10090,7 +10051,7 @@
         <v>60380162</v>
       </c>
     </row>
-    <row r="401" spans="8:11">
+    <row r="401" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H401" t="s">
         <v>152</v>
       </c>
@@ -10104,7 +10065,7 @@
         <v>60541542</v>
       </c>
     </row>
-    <row r="402" spans="8:11">
+    <row r="402" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H402" t="s">
         <v>152</v>
       </c>
@@ -10118,7 +10079,7 @@
         <v>60541171</v>
       </c>
     </row>
-    <row r="403" spans="8:11">
+    <row r="403" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H403" t="s">
         <v>90</v>
       </c>
@@ -10132,7 +10093,7 @@
         <v>60543356</v>
       </c>
     </row>
-    <row r="404" spans="8:11">
+    <row r="404" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H404" t="s">
         <v>115</v>
       </c>
@@ -10146,7 +10107,7 @@
         <v>60530655</v>
       </c>
     </row>
-    <row r="405" spans="8:11">
+    <row r="405" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H405" t="s">
         <v>90</v>
       </c>
@@ -10160,7 +10121,7 @@
         <v>60615380</v>
       </c>
     </row>
-    <row r="406" spans="8:11">
+    <row r="406" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H406" t="s">
         <v>58</v>
       </c>
@@ -10174,7 +10135,7 @@
         <v>60725132</v>
       </c>
     </row>
-    <row r="407" spans="8:11">
+    <row r="407" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H407" t="s">
         <v>58</v>
       </c>
@@ -10188,7 +10149,7 @@
         <v>62575565</v>
       </c>
     </row>
-    <row r="408" spans="8:11">
+    <row r="408" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H408" t="s">
         <v>171</v>
       </c>
@@ -10202,7 +10163,7 @@
         <v>61766007</v>
       </c>
     </row>
-    <row r="409" spans="8:11">
+    <row r="409" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H409" t="s">
         <v>98</v>
       </c>
@@ -10216,7 +10177,7 @@
         <v>61089339</v>
       </c>
     </row>
-    <row r="410" spans="8:11">
+    <row r="410" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H410" t="s">
         <v>98</v>
       </c>
@@ -10230,7 +10191,7 @@
         <v>62377903</v>
       </c>
     </row>
-    <row r="411" spans="8:11">
+    <row r="411" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H411" t="s">
         <v>92</v>
       </c>
@@ -10244,7 +10205,7 @@
         <v>60542212</v>
       </c>
     </row>
-    <row r="412" spans="8:11">
+    <row r="412" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H412" t="s">
         <v>109</v>
       </c>
@@ -10258,7 +10219,7 @@
         <v>61044622</v>
       </c>
     </row>
-    <row r="413" spans="8:11">
+    <row r="413" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H413" t="s">
         <v>92</v>
       </c>
@@ -10272,7 +10233,7 @@
         <v>61199642</v>
       </c>
     </row>
-    <row r="414" spans="8:11">
+    <row r="414" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H414" t="s">
         <v>143</v>
       </c>
@@ -10286,7 +10247,7 @@
         <v>61760291</v>
       </c>
     </row>
-    <row r="415" spans="8:11">
+    <row r="415" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H415" t="s">
         <v>109</v>
       </c>
@@ -10300,7 +10261,7 @@
         <v>61923953</v>
       </c>
     </row>
-    <row r="416" spans="8:11">
+    <row r="416" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H416" t="s">
         <v>143</v>
       </c>
@@ -10314,7 +10275,7 @@
         <v>61760141</v>
       </c>
     </row>
-    <row r="417" spans="8:11">
+    <row r="417" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H417" t="s">
         <v>143</v>
       </c>
@@ -10328,7 +10289,7 @@
         <v>61929592</v>
       </c>
     </row>
-    <row r="418" spans="8:11">
+    <row r="418" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H418" t="s">
         <v>143</v>
       </c>
@@ -10342,7 +10303,7 @@
         <v>61929727</v>
       </c>
     </row>
-    <row r="419" spans="8:11">
+    <row r="419" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H419" t="s">
         <v>92</v>
       </c>
@@ -10356,7 +10317,7 @@
         <v>61929494</v>
       </c>
     </row>
-    <row r="420" spans="8:11">
+    <row r="420" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H420" t="s">
         <v>92</v>
       </c>
@@ -10370,7 +10331,7 @@
         <v>61929493</v>
       </c>
     </row>
-    <row r="421" spans="8:11">
+    <row r="421" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H421" t="s">
         <v>98</v>
       </c>
@@ -10384,7 +10345,7 @@
         <v>61879892</v>
       </c>
     </row>
-    <row r="422" spans="8:11">
+    <row r="422" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H422" t="s">
         <v>58</v>
       </c>
@@ -10398,7 +10359,7 @@
         <v>62378988</v>
       </c>
     </row>
-    <row r="423" spans="8:11">
+    <row r="423" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H423" t="s">
         <v>58</v>
       </c>
@@ -10412,7 +10373,7 @@
         <v>62375802</v>
       </c>
     </row>
-    <row r="424" spans="8:11">
+    <row r="424" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H424" t="s">
         <v>58</v>
       </c>
@@ -10426,7 +10387,7 @@
         <v>62379668</v>
       </c>
     </row>
-    <row r="425" spans="8:11">
+    <row r="425" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H425" t="s">
         <v>211</v>
       </c>
@@ -10440,7 +10401,7 @@
         <v>62221331</v>
       </c>
     </row>
-    <row r="426" spans="8:11">
+    <row r="426" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H426" t="s">
         <v>143</v>
       </c>
@@ -10454,7 +10415,7 @@
         <v>62385013</v>
       </c>
     </row>
-    <row r="427" spans="8:11">
+    <row r="427" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H427" t="s">
         <v>143</v>
       </c>
@@ -10468,7 +10429,7 @@
         <v>62380995</v>
       </c>
     </row>
-    <row r="428" spans="8:11">
+    <row r="428" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H428" t="s">
         <v>98</v>
       </c>
@@ -10482,7 +10443,7 @@
         <v>62421723</v>
       </c>
     </row>
-    <row r="429" spans="8:11">
+    <row r="429" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H429" t="s">
         <v>98</v>
       </c>
@@ -10496,7 +10457,7 @@
         <v>62374813</v>
       </c>
     </row>
-    <row r="430" spans="8:11">
+    <row r="430" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H430" t="s">
         <v>98</v>
       </c>
@@ -10510,7 +10471,7 @@
         <v>62499786</v>
       </c>
     </row>
-    <row r="431" spans="8:11">
+    <row r="431" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H431" t="s">
         <v>98</v>
       </c>
@@ -10524,7 +10485,7 @@
         <v>62498583</v>
       </c>
     </row>
-    <row r="432" spans="8:11">
+    <row r="432" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H432" t="s">
         <v>143</v>
       </c>
@@ -10538,7 +10499,7 @@
         <v>63346456</v>
       </c>
     </row>
-    <row r="433" spans="8:11">
+    <row r="433" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H433" t="s">
         <v>143</v>
       </c>
@@ -10552,7 +10513,7 @@
         <v>63100963</v>
       </c>
     </row>
-    <row r="434" spans="8:11">
+    <row r="434" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H434" t="s">
         <v>90</v>
       </c>
@@ -10566,7 +10527,7 @@
         <v>63396496</v>
       </c>
     </row>
-    <row r="435" spans="8:11">
+    <row r="435" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H435" t="s">
         <v>58</v>
       </c>
@@ -10580,7 +10541,7 @@
         <v>64270608</v>
       </c>
     </row>
-    <row r="436" spans="8:11">
+    <row r="436" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H436" t="s">
         <v>92</v>
       </c>
@@ -10594,7 +10555,7 @@
         <v>63573761</v>
       </c>
     </row>
-    <row r="437" spans="8:11">
+    <row r="437" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H437" t="s">
         <v>92</v>
       </c>
@@ -10608,7 +10569,7 @@
         <v>64330763</v>
       </c>
     </row>
-    <row r="438" spans="8:11">
+    <row r="438" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H438" t="s">
         <v>92</v>
       </c>
@@ -10622,7 +10583,7 @@
         <v>64330764</v>
       </c>
     </row>
-    <row r="439" spans="8:11">
+    <row r="439" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H439" t="s">
         <v>92</v>
       </c>
@@ -10636,7 +10597,7 @@
         <v>64212552</v>
       </c>
     </row>
-    <row r="440" spans="8:11">
+    <row r="440" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H440" t="s">
         <v>92</v>
       </c>
@@ -10650,7 +10611,7 @@
         <v>64212544</v>
       </c>
     </row>
-    <row r="441" spans="8:11">
+    <row r="441" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H441" t="s">
         <v>92</v>
       </c>
@@ -10664,7 +10625,7 @@
         <v>64212543</v>
       </c>
     </row>
-    <row r="442" spans="8:11">
+    <row r="442" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H442" t="s">
         <v>92</v>
       </c>
@@ -10678,7 +10639,7 @@
         <v>64212381</v>
       </c>
     </row>
-    <row r="443" spans="8:11">
+    <row r="443" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H443" t="s">
         <v>109</v>
       </c>
@@ -10692,7 +10653,7 @@
         <v>64114088</v>
       </c>
     </row>
-    <row r="444" spans="8:11">
+    <row r="444" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H444" t="s">
         <v>171</v>
       </c>
@@ -10706,7 +10667,7 @@
         <v>64223250</v>
       </c>
     </row>
-    <row r="445" spans="8:11">
+    <row r="445" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H445" t="s">
         <v>171</v>
       </c>
@@ -10720,7 +10681,7 @@
         <v>64214259</v>
       </c>
     </row>
-    <row r="446" spans="8:11">
+    <row r="446" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H446" t="s">
         <v>171</v>
       </c>
@@ -10734,7 +10695,7 @@
         <v>64214258</v>
       </c>
     </row>
-    <row r="447" spans="8:11">
+    <row r="447" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H447" t="s">
         <v>143</v>
       </c>
@@ -10748,7 +10709,7 @@
         <v>63742200</v>
       </c>
     </row>
-    <row r="448" spans="8:11">
+    <row r="448" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H448" t="s">
         <v>90</v>
       </c>
@@ -10762,7 +10723,7 @@
         <v>64606094</v>
       </c>
     </row>
-    <row r="449" spans="8:11">
+    <row r="449" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H449" t="s">
         <v>98</v>
       </c>
@@ -10776,7 +10737,7 @@
         <v>64287980</v>
       </c>
     </row>
-    <row r="450" spans="8:11">
+    <row r="450" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H450" t="s">
         <v>98</v>
       </c>
@@ -10790,7 +10751,7 @@
         <v>64257297</v>
       </c>
     </row>
-    <row r="451" spans="8:11">
+    <row r="451" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H451" t="s">
         <v>98</v>
       </c>
@@ -10804,7 +10765,7 @@
         <v>66097436</v>
       </c>
     </row>
-    <row r="452" spans="8:11">
+    <row r="452" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H452" t="s">
         <v>143</v>
       </c>
@@ -10818,7 +10779,7 @@
         <v>64330309</v>
       </c>
     </row>
-    <row r="453" spans="8:11">
+    <row r="453" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H453" t="s">
         <v>211</v>
       </c>
@@ -10832,7 +10793,7 @@
         <v>64846264</v>
       </c>
     </row>
-    <row r="454" spans="8:11">
+    <row r="454" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H454" t="s">
         <v>109</v>
       </c>
@@ -10846,7 +10807,7 @@
         <v>64753996</v>
       </c>
     </row>
-    <row r="455" spans="8:11">
+    <row r="455" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H455" t="s">
         <v>92</v>
       </c>
@@ -10860,7 +10821,7 @@
         <v>64778162</v>
       </c>
     </row>
-    <row r="456" spans="8:11">
+    <row r="456" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H456" t="s">
         <v>92</v>
       </c>
@@ -10874,7 +10835,7 @@
         <v>64778161</v>
       </c>
     </row>
-    <row r="457" spans="8:11">
+    <row r="457" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H457" t="s">
         <v>92</v>
       </c>
@@ -10888,7 +10849,7 @@
         <v>64808932</v>
       </c>
     </row>
-    <row r="458" spans="8:11">
+    <row r="458" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H458" t="s">
         <v>109</v>
       </c>
@@ -10902,7 +10863,7 @@
         <v>64789478</v>
       </c>
     </row>
-    <row r="459" spans="8:11">
+    <row r="459" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H459" t="s">
         <v>98</v>
       </c>
@@ -10916,7 +10877,7 @@
         <v>64912430</v>
       </c>
     </row>
-    <row r="460" spans="8:11">
+    <row r="460" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H460" t="s">
         <v>98</v>
       </c>
@@ -10930,7 +10891,7 @@
         <v>64971361</v>
       </c>
     </row>
-    <row r="461" spans="8:11">
+    <row r="461" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H461" t="s">
         <v>143</v>
       </c>
@@ -10944,7 +10905,7 @@
         <v>65145714</v>
       </c>
     </row>
-    <row r="462" spans="8:11">
+    <row r="462" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H462" t="s">
         <v>92</v>
       </c>
@@ -10958,7 +10919,7 @@
         <v>65081124</v>
       </c>
     </row>
-    <row r="463" spans="8:11">
+    <row r="463" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H463" t="s">
         <v>29</v>
       </c>
@@ -10972,7 +10933,7 @@
         <v>65181042</v>
       </c>
     </row>
-    <row r="464" spans="8:11">
+    <row r="464" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H464" t="s">
         <v>29</v>
       </c>
@@ -10986,7 +10947,7 @@
         <v>65179405</v>
       </c>
     </row>
-    <row r="465" spans="8:11">
+    <row r="465" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H465" t="s">
         <v>29</v>
       </c>
@@ -11000,7 +10961,7 @@
         <v>65566244</v>
       </c>
     </row>
-    <row r="466" spans="8:11">
+    <row r="466" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H466" t="s">
         <v>29</v>
       </c>
@@ -11014,7 +10975,7 @@
         <v>65566541</v>
       </c>
     </row>
-    <row r="467" spans="8:11">
+    <row r="467" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H467" t="s">
         <v>29</v>
       </c>
@@ -11028,7 +10989,7 @@
         <v>65656468</v>
       </c>
     </row>
-    <row r="468" spans="8:11">
+    <row r="468" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H468" t="s">
         <v>29</v>
       </c>
@@ -11042,7 +11003,7 @@
         <v>65657039</v>
       </c>
     </row>
-    <row r="469" spans="8:11">
+    <row r="469" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H469" t="s">
         <v>98</v>
       </c>
@@ -11056,7 +11017,7 @@
         <v>66217025</v>
       </c>
     </row>
-    <row r="470" spans="8:11">
+    <row r="470" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H470" t="s">
         <v>98</v>
       </c>
@@ -11070,7 +11031,7 @@
         <v>66214618</v>
       </c>
     </row>
-    <row r="471" spans="8:11">
+    <row r="471" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H471" t="s">
         <v>29</v>
       </c>
@@ -11084,7 +11045,7 @@
         <v>65935700</v>
       </c>
     </row>
-    <row r="472" spans="8:11">
+    <row r="472" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H472" t="s">
         <v>29</v>
       </c>
@@ -11098,7 +11059,7 @@
         <v>65934564</v>
       </c>
     </row>
-    <row r="473" spans="8:11">
+    <row r="473" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H473" t="s">
         <v>29</v>
       </c>
@@ -11112,7 +11073,7 @@
         <v>65933937</v>
       </c>
     </row>
-    <row r="474" spans="8:11">
+    <row r="474" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H474" t="s">
         <v>29</v>
       </c>
@@ -11126,7 +11087,7 @@
         <v>66046959</v>
       </c>
     </row>
-    <row r="475" spans="8:11">
+    <row r="475" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H475" t="s">
         <v>98</v>
       </c>
@@ -11140,7 +11101,7 @@
         <v>65969750</v>
       </c>
     </row>
-    <row r="476" spans="8:11">
+    <row r="476" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H476" t="s">
         <v>171</v>
       </c>
@@ -11154,7 +11115,7 @@
         <v>66358440</v>
       </c>
     </row>
-    <row r="477" spans="8:11">
+    <row r="477" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H477" t="s">
         <v>143</v>
       </c>
@@ -11168,7 +11129,7 @@
         <v>66417803</v>
       </c>
     </row>
-    <row r="478" spans="8:11">
+    <row r="478" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H478" t="s">
         <v>143</v>
       </c>
@@ -11182,7 +11143,7 @@
         <v>66417801</v>
       </c>
     </row>
-    <row r="479" spans="8:11">
+    <row r="479" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H479" t="s">
         <v>92</v>
       </c>
@@ -11196,7 +11157,7 @@
         <v>66357977</v>
       </c>
     </row>
-    <row r="480" spans="8:11">
+    <row r="480" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H480" t="s">
         <v>171</v>
       </c>
@@ -11210,7 +11171,7 @@
         <v>67191572</v>
       </c>
     </row>
-    <row r="481" spans="8:11">
+    <row r="481" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H481" t="s">
         <v>171</v>
       </c>
@@ -11224,7 +11185,7 @@
         <v>66546178</v>
       </c>
     </row>
-    <row r="482" spans="8:11">
+    <row r="482" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H482" t="s">
         <v>171</v>
       </c>
@@ -11238,7 +11199,7 @@
         <v>67627331</v>
       </c>
     </row>
-    <row r="483" spans="8:11">
+    <row r="483" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H483" t="s">
         <v>92</v>
       </c>
@@ -11252,7 +11213,7 @@
         <v>66778787</v>
       </c>
     </row>
-    <row r="484" spans="8:11">
+    <row r="484" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H484" t="s">
         <v>92</v>
       </c>
@@ -11266,7 +11227,7 @@
         <v>66778788</v>
       </c>
     </row>
-    <row r="485" spans="8:11">
+    <row r="485" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H485" t="s">
         <v>92</v>
       </c>
@@ -11280,7 +11241,7 @@
         <v>66778789</v>
       </c>
     </row>
-    <row r="486" spans="8:11">
+    <row r="486" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H486" t="s">
         <v>90</v>
       </c>
@@ -11294,7 +11255,7 @@
         <v>66896364</v>
       </c>
     </row>
-    <row r="487" spans="8:11">
+    <row r="487" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H487" t="s">
         <v>29</v>
       </c>
@@ -11308,7 +11269,7 @@
         <v>66607099</v>
       </c>
     </row>
-    <row r="488" spans="8:11">
+    <row r="488" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H488" t="s">
         <v>29</v>
       </c>
@@ -11322,7 +11283,7 @@
         <v>66864708</v>
       </c>
     </row>
-    <row r="489" spans="8:11">
+    <row r="489" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H489" t="s">
         <v>29</v>
       </c>
@@ -11336,7 +11297,7 @@
         <v>66850322</v>
       </c>
     </row>
-    <row r="490" spans="8:11">
+    <row r="490" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H490" t="s">
         <v>109</v>
       </c>
@@ -11350,7 +11311,7 @@
         <v>67268341</v>
       </c>
     </row>
-    <row r="491" spans="8:11">
+    <row r="491" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H491" t="s">
         <v>109</v>
       </c>
@@ -11364,7 +11325,7 @@
         <v>67268348</v>
       </c>
     </row>
-    <row r="492" spans="8:11">
+    <row r="492" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H492" t="s">
         <v>109</v>
       </c>
@@ -11378,7 +11339,7 @@
         <v>67268349</v>
       </c>
     </row>
-    <row r="493" spans="8:11">
+    <row r="493" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H493" t="s">
         <v>109</v>
       </c>
@@ -11392,7 +11353,7 @@
         <v>67268350</v>
       </c>
     </row>
-    <row r="494" spans="8:11">
+    <row r="494" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H494" t="s">
         <v>109</v>
       </c>
@@ -11406,7 +11367,7 @@
         <v>67272047</v>
       </c>
     </row>
-    <row r="495" spans="8:11">
+    <row r="495" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H495" t="s">
         <v>109</v>
       </c>
@@ -11420,7 +11381,7 @@
         <v>67272046</v>
       </c>
     </row>
-    <row r="496" spans="8:11">
+    <row r="496" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H496" t="s">
         <v>92</v>
       </c>
@@ -11434,7 +11395,7 @@
         <v>67438488</v>
       </c>
     </row>
-    <row r="497" spans="8:11">
+    <row r="497" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H497" t="s">
         <v>92</v>
       </c>
@@ -11448,7 +11409,7 @@
         <v>67438487</v>
       </c>
     </row>
-    <row r="498" spans="8:11">
+    <row r="498" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H498" t="s">
         <v>92</v>
       </c>
@@ -11462,7 +11423,7 @@
         <v>68253037</v>
       </c>
     </row>
-    <row r="499" spans="8:11">
+    <row r="499" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H499" t="s">
         <v>171</v>
       </c>
@@ -11476,7 +11437,7 @@
         <v>67891311</v>
       </c>
     </row>
-    <row r="500" spans="8:11">
+    <row r="500" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H500" t="s">
         <v>143</v>
       </c>
@@ -11490,7 +11451,7 @@
         <v>67900090</v>
       </c>
     </row>
-    <row r="501" spans="8:11">
+    <row r="501" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H501" t="s">
         <v>29</v>
       </c>
@@ -11504,7 +11465,7 @@
         <v>67630646</v>
       </c>
     </row>
-    <row r="502" spans="8:11">
+    <row r="502" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H502" t="s">
         <v>98</v>
       </c>
@@ -11518,7 +11479,7 @@
         <v>67974104</v>
       </c>
     </row>
-    <row r="503" spans="8:11">
+    <row r="503" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H503" t="s">
         <v>109</v>
       </c>
@@ -11532,7 +11493,7 @@
         <v>67989839</v>
       </c>
     </row>
-    <row r="504" spans="8:11">
+    <row r="504" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H504" t="s">
         <v>109</v>
       </c>
@@ -11546,7 +11507,7 @@
         <v>67988468</v>
       </c>
     </row>
-    <row r="505" spans="8:11">
+    <row r="505" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H505" t="s">
         <v>98</v>
       </c>
@@ -11560,7 +11521,7 @@
         <v>68466892</v>
       </c>
     </row>
-    <row r="506" spans="8:11">
+    <row r="506" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H506" t="s">
         <v>98</v>
       </c>
@@ -11574,7 +11535,7 @@
         <v>69040158</v>
       </c>
     </row>
-    <row r="507" spans="8:11">
+    <row r="507" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H507" t="s">
         <v>98</v>
       </c>
@@ -11588,7 +11549,7 @@
         <v>68462854</v>
       </c>
     </row>
-    <row r="508" spans="8:11">
+    <row r="508" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H508" t="s">
         <v>92</v>
       </c>
@@ -11602,7 +11563,7 @@
         <v>68677002</v>
       </c>
     </row>
-    <row r="509" spans="8:11">
+    <row r="509" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H509" t="s">
         <v>171</v>
       </c>
@@ -11616,7 +11577,7 @@
         <v>68880617</v>
       </c>
     </row>
-    <row r="510" spans="8:11">
+    <row r="510" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H510" t="s">
         <v>98</v>
       </c>
@@ -11630,7 +11591,7 @@
         <v>68934411</v>
       </c>
     </row>
-    <row r="511" spans="8:11">
+    <row r="511" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H511" t="s">
         <v>98</v>
       </c>
@@ -11644,7 +11605,7 @@
         <v>68924611</v>
       </c>
     </row>
-    <row r="512" spans="8:11">
+    <row r="512" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H512" t="s">
         <v>92</v>
       </c>
@@ -11658,7 +11619,7 @@
         <v>69039437</v>
       </c>
     </row>
-    <row r="513" spans="8:11">
+    <row r="513" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H513" t="s">
         <v>92</v>
       </c>
@@ -11672,7 +11633,7 @@
         <v>69039778</v>
       </c>
     </row>
-    <row r="514" spans="8:11">
+    <row r="514" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H514" t="s">
         <v>58</v>
       </c>
@@ -11686,7 +11647,7 @@
         <v>69279032</v>
       </c>
     </row>
-    <row r="515" spans="8:11">
+    <row r="515" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H515" t="s">
         <v>92</v>
       </c>
@@ -11700,7 +11661,7 @@
         <v>68938743</v>
       </c>
     </row>
-    <row r="516" spans="8:11">
+    <row r="516" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H516" t="s">
         <v>58</v>
       </c>
@@ -11714,7 +11675,7 @@
         <v>69772629</v>
       </c>
     </row>
-    <row r="517" spans="8:11">
+    <row r="517" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H517" t="s">
         <v>58</v>
       </c>
@@ -11728,7 +11689,7 @@
         <v>69772627</v>
       </c>
     </row>
-    <row r="518" spans="8:11">
+    <row r="518" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H518" t="s">
         <v>58</v>
       </c>
@@ -11742,7 +11703,7 @@
         <v>69772625</v>
       </c>
     </row>
-    <row r="519" spans="8:11">
+    <row r="519" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H519" t="s">
         <v>98</v>
       </c>
@@ -11756,7 +11717,7 @@
         <v>69292187</v>
       </c>
     </row>
-    <row r="520" spans="8:11">
+    <row r="520" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H520" t="s">
         <v>98</v>
       </c>
@@ -11770,7 +11731,7 @@
         <v>69292186</v>
       </c>
     </row>
-    <row r="521" spans="8:11">
+    <row r="521" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H521" t="s">
         <v>98</v>
       </c>
@@ -11784,7 +11745,7 @@
         <v>69292185</v>
       </c>
     </row>
-    <row r="522" spans="8:11">
+    <row r="522" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H522" t="s">
         <v>58</v>
       </c>
@@ -11798,7 +11759,7 @@
         <v>69096297</v>
       </c>
     </row>
-    <row r="523" spans="8:11">
+    <row r="523" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H523" t="s">
         <v>58</v>
       </c>
@@ -11812,7 +11773,7 @@
         <v>69096296</v>
       </c>
     </row>
-    <row r="524" spans="8:11">
+    <row r="524" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H524" t="s">
         <v>143</v>
       </c>
@@ -11826,7 +11787,7 @@
         <v>69594684</v>
       </c>
     </row>
-    <row r="525" spans="8:11">
+    <row r="525" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H525" t="s">
         <v>98</v>
       </c>
@@ -11840,7 +11801,7 @@
         <v>70204974</v>
       </c>
     </row>
-    <row r="526" spans="8:11">
+    <row r="526" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H526" t="s">
         <v>98</v>
       </c>
@@ -11854,7 +11815,7 @@
         <v>70204975</v>
       </c>
     </row>
-    <row r="527" spans="8:11">
+    <row r="527" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H527" t="s">
         <v>143</v>
       </c>
@@ -11868,7 +11829,7 @@
         <v>69767288</v>
       </c>
     </row>
-    <row r="528" spans="8:11">
+    <row r="528" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H528" t="s">
         <v>98</v>
       </c>
@@ -11882,7 +11843,7 @@
         <v>69766464</v>
       </c>
     </row>
-    <row r="529" spans="8:11">
+    <row r="529" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H529" t="s">
         <v>98</v>
       </c>
@@ -11896,7 +11857,7 @@
         <v>69803799</v>
       </c>
     </row>
-    <row r="530" spans="8:11">
+    <row r="530" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H530" t="s">
         <v>143</v>
       </c>
@@ -11910,7 +11871,7 @@
         <v>70251147</v>
       </c>
     </row>
-    <row r="531" spans="8:11">
+    <row r="531" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H531" t="s">
         <v>171</v>
       </c>
@@ -11924,7 +11885,7 @@
         <v>69770093</v>
       </c>
     </row>
-    <row r="532" spans="8:11">
+    <row r="532" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H532" t="s">
         <v>92</v>
       </c>
@@ -11938,7 +11899,7 @@
         <v>70205079</v>
       </c>
     </row>
-    <row r="533" spans="8:11">
+    <row r="533" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H533" t="s">
         <v>98</v>
       </c>
@@ -11952,7 +11913,7 @@
         <v>70530577</v>
       </c>
     </row>
-    <row r="534" spans="8:11">
+    <row r="534" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H534" t="s">
         <v>98</v>
       </c>
@@ -11966,7 +11927,7 @@
         <v>70530576</v>
       </c>
     </row>
-    <row r="535" spans="8:11">
+    <row r="535" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H535" t="s">
         <v>109</v>
       </c>
@@ -11980,7 +11941,7 @@
         <v>71030052</v>
       </c>
     </row>
-    <row r="536" spans="8:11">
+    <row r="536" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H536" t="s">
         <v>115</v>
       </c>
@@ -11994,7 +11955,7 @@
         <v>70770186</v>
       </c>
     </row>
-    <row r="537" spans="8:11">
+    <row r="537" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H537" t="s">
         <v>115</v>
       </c>
@@ -12008,7 +11969,7 @@
         <v>71173111</v>
       </c>
     </row>
-    <row r="538" spans="8:11">
+    <row r="538" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H538" t="s">
         <v>115</v>
       </c>
@@ -12022,7 +11983,7 @@
         <v>71156871</v>
       </c>
     </row>
-    <row r="539" spans="8:11">
+    <row r="539" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H539" t="s">
         <v>115</v>
       </c>
@@ -12036,7 +11997,7 @@
         <v>71291488</v>
       </c>
     </row>
-    <row r="540" spans="8:11">
+    <row r="540" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I540">
         <v>71042279</v>
       </c>
@@ -12047,7 +12008,7 @@
         <v>71042279</v>
       </c>
     </row>
-    <row r="541" spans="8:11">
+    <row r="541" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H541" t="s">
         <v>115</v>
       </c>
@@ -12061,7 +12022,7 @@
         <v>71947627</v>
       </c>
     </row>
-    <row r="542" spans="8:11">
+    <row r="542" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H542" t="s">
         <v>115</v>
       </c>
@@ -12075,7 +12036,7 @@
         <v>72182444</v>
       </c>
     </row>
-    <row r="543" spans="8:11">
+    <row r="543" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H543" t="s">
         <v>115</v>
       </c>
@@ -12089,7 +12050,7 @@
         <v>72300747</v>
       </c>
     </row>
-    <row r="544" spans="8:11">
+    <row r="544" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H544" t="s">
         <v>115</v>
       </c>
@@ -12103,7 +12064,7 @@
         <v>72417582</v>
       </c>
     </row>
-    <row r="545" spans="8:11">
+    <row r="545" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H545" t="s">
         <v>115</v>
       </c>
@@ -12117,7 +12078,7 @@
         <v>72614935</v>
       </c>
     </row>
-    <row r="546" spans="8:11">
+    <row r="546" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H546" t="s">
         <v>115</v>
       </c>
@@ -12131,7 +12092,7 @@
         <v>72614936</v>
       </c>
     </row>
-    <row r="547" spans="8:11">
+    <row r="547" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H547" t="s">
         <v>115</v>
       </c>
@@ -12145,7 +12106,7 @@
         <v>72614937</v>
       </c>
     </row>
-    <row r="548" spans="8:11">
+    <row r="548" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H548" t="s">
         <v>92</v>
       </c>
@@ -12159,7 +12120,7 @@
         <v>73226633</v>
       </c>
     </row>
-    <row r="549" spans="8:11">
+    <row r="549" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H549" t="s">
         <v>92</v>
       </c>
@@ -12173,7 +12134,7 @@
         <v>73226632</v>
       </c>
     </row>
-    <row r="550" spans="8:11">
+    <row r="550" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H550" t="s">
         <v>143</v>
       </c>
@@ -12187,7 +12148,7 @@
         <v>73316683</v>
       </c>
     </row>
-    <row r="551" spans="8:11">
+    <row r="551" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H551" t="s">
         <v>143</v>
       </c>
@@ -12201,7 +12162,7 @@
         <v>73316684</v>
       </c>
     </row>
-    <row r="552" spans="8:11">
+    <row r="552" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H552" t="s">
         <v>143</v>
       </c>
@@ -12215,7 +12176,7 @@
         <v>73316685</v>
       </c>
     </row>
-    <row r="553" spans="8:11">
+    <row r="553" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H553" t="s">
         <v>115</v>
       </c>
@@ -12229,7 +12190,7 @@
         <v>72699936</v>
       </c>
     </row>
-    <row r="554" spans="8:11">
+    <row r="554" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H554" t="s">
         <v>115</v>
       </c>
@@ -12243,7 +12204,7 @@
         <v>72699935</v>
       </c>
     </row>
-    <row r="555" spans="8:11">
+    <row r="555" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H555" t="s">
         <v>115</v>
       </c>
@@ -12257,7 +12218,7 @@
         <v>72828733</v>
       </c>
     </row>
-    <row r="556" spans="8:11">
+    <row r="556" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H556" t="s">
         <v>115</v>
       </c>
@@ -12271,7 +12232,7 @@
         <v>72828734</v>
       </c>
     </row>
-    <row r="557" spans="8:11">
+    <row r="557" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H557" t="s">
         <v>90</v>
       </c>
@@ -12285,7 +12246,7 @@
         <v>72683872</v>
       </c>
     </row>
-    <row r="558" spans="8:11">
+    <row r="558" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H558" t="s">
         <v>58</v>
       </c>
@@ -12299,7 +12260,7 @@
         <v>72910681</v>
       </c>
     </row>
-    <row r="559" spans="8:11">
+    <row r="559" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H559" t="s">
         <v>58</v>
       </c>
@@ -12313,7 +12274,7 @@
         <v>72910683</v>
       </c>
     </row>
-    <row r="560" spans="8:11">
+    <row r="560" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H560" t="s">
         <v>98</v>
       </c>
@@ -12327,7 +12288,7 @@
         <v>73523448</v>
       </c>
     </row>
-    <row r="561" spans="8:11">
+    <row r="561" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H561" t="s">
         <v>58</v>
       </c>
@@ -12341,7 +12302,7 @@
         <v>73461995</v>
       </c>
     </row>
-    <row r="562" spans="8:11">
+    <row r="562" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H562" t="s">
         <v>98</v>
       </c>
@@ -12355,7 +12316,7 @@
         <v>73956460</v>
       </c>
     </row>
-    <row r="563" spans="8:11">
+    <row r="563" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H563" t="s">
         <v>98</v>
       </c>
@@ -12369,7 +12330,7 @@
         <v>73956461</v>
       </c>
     </row>
-    <row r="564" spans="8:11">
+    <row r="564" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H564" t="s">
         <v>98</v>
       </c>
@@ -12383,7 +12344,7 @@
         <v>73956459</v>
       </c>
     </row>
-    <row r="565" spans="8:11">
+    <row r="565" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H565" t="s">
         <v>58</v>
       </c>
@@ -12397,7 +12358,7 @@
         <v>74685916</v>
       </c>
     </row>
-    <row r="566" spans="8:11">
+    <row r="566" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H566" t="s">
         <v>98</v>
       </c>
@@ -12411,7 +12372,7 @@
         <v>73975553</v>
       </c>
     </row>
-    <row r="567" spans="8:11">
+    <row r="567" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H567" t="s">
         <v>98</v>
       </c>
@@ -12425,7 +12386,7 @@
         <v>73952843</v>
       </c>
     </row>
-    <row r="568" spans="8:11">
+    <row r="568" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H568" t="s">
         <v>115</v>
       </c>
@@ -12439,7 +12400,7 @@
         <v>74550323</v>
       </c>
     </row>
-    <row r="569" spans="8:11">
+    <row r="569" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H569" t="s">
         <v>98</v>
       </c>
@@ -12453,7 +12414,7 @@
         <v>75989703</v>
       </c>
     </row>
-    <row r="570" spans="8:11">
+    <row r="570" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H570" t="s">
         <v>143</v>
       </c>
@@ -12467,7 +12428,7 @@
         <v>74693807</v>
       </c>
     </row>
-    <row r="571" spans="8:11">
+    <row r="571" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H571" t="s">
         <v>143</v>
       </c>
@@ -12481,7 +12442,7 @@
         <v>73893263</v>
       </c>
     </row>
-    <row r="572" spans="8:11">
+    <row r="572" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H572" t="s">
         <v>143</v>
       </c>
@@ -12495,7 +12456,7 @@
         <v>74884452</v>
       </c>
     </row>
-    <row r="573" spans="8:11">
+    <row r="573" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H573" t="s">
         <v>98</v>
       </c>
@@ -12509,7 +12470,7 @@
         <v>74826973</v>
       </c>
     </row>
-    <row r="574" spans="8:11">
+    <row r="574" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H574" t="s">
         <v>98</v>
       </c>
@@ -12523,7 +12484,7 @@
         <v>74826974</v>
       </c>
     </row>
-    <row r="575" spans="8:11">
+    <row r="575" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H575" t="s">
         <v>90</v>
       </c>
@@ -12537,7 +12498,7 @@
         <v>75077119</v>
       </c>
     </row>
-    <row r="576" spans="8:11">
+    <row r="576" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H576" t="s">
         <v>92</v>
       </c>
@@ -12551,7 +12512,7 @@
         <v>78867502</v>
       </c>
     </row>
-    <row r="577" spans="8:11">
+    <row r="577" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H577" t="s">
         <v>92</v>
       </c>
@@ -12565,7 +12526,7 @@
         <v>80192305</v>
       </c>
     </row>
-    <row r="578" spans="8:11">
+    <row r="578" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H578" t="s">
         <v>92</v>
       </c>
@@ -12579,7 +12540,7 @@
         <v>75741354</v>
       </c>
     </row>
-    <row r="579" spans="8:11">
+    <row r="579" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H579" t="s">
         <v>143</v>
       </c>
@@ -12593,7 +12554,7 @@
         <v>78625461</v>
       </c>
     </row>
-    <row r="580" spans="8:11">
+    <row r="580" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H580" t="s">
         <v>92</v>
       </c>
@@ -12607,7 +12568,7 @@
         <v>76375598</v>
       </c>
     </row>
-    <row r="581" spans="8:11">
+    <row r="581" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H581" t="s">
         <v>92</v>
       </c>
@@ -12621,7 +12582,7 @@
         <v>76375597</v>
       </c>
     </row>
-    <row r="582" spans="8:11">
+    <row r="582" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H582" t="s">
         <v>92</v>
       </c>
@@ -12635,7 +12596,7 @@
         <v>76374400</v>
       </c>
     </row>
-    <row r="583" spans="8:11">
+    <row r="583" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H583" t="s">
         <v>92</v>
       </c>
@@ -12649,7 +12610,7 @@
         <v>76374401</v>
       </c>
     </row>
-    <row r="584" spans="8:11">
+    <row r="584" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H584" t="s">
         <v>92</v>
       </c>
@@ -12663,7 +12624,7 @@
         <v>76241042</v>
       </c>
     </row>
-    <row r="585" spans="8:11">
+    <row r="585" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H585" t="s">
         <v>90</v>
       </c>
@@ -12677,7 +12638,7 @@
         <v>76533940</v>
       </c>
     </row>
-    <row r="586" spans="8:11">
+    <row r="586" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H586" t="s">
         <v>92</v>
       </c>
@@ -12691,7 +12652,7 @@
         <v>77463489</v>
       </c>
     </row>
-    <row r="587" spans="8:11">
+    <row r="587" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H587" t="s">
         <v>92</v>
       </c>
@@ -12705,7 +12666,7 @@
         <v>77463490</v>
       </c>
     </row>
-    <row r="588" spans="8:11">
+    <row r="588" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H588" t="s">
         <v>58</v>
       </c>
@@ -12719,7 +12680,7 @@
         <v>78907466</v>
       </c>
     </row>
-    <row r="589" spans="8:11">
+    <row r="589" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H589" t="s">
         <v>58</v>
       </c>
@@ -12733,7 +12694,7 @@
         <v>78907465</v>
       </c>
     </row>
-    <row r="590" spans="8:11">
+    <row r="590" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H590" t="s">
         <v>58</v>
       </c>
@@ -12747,7 +12708,7 @@
         <v>78903848</v>
       </c>
     </row>
-    <row r="591" spans="8:11">
+    <row r="591" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H591" t="s">
         <v>58</v>
       </c>
@@ -12761,7 +12722,7 @@
         <v>78903849</v>
       </c>
     </row>
-    <row r="592" spans="8:11">
+    <row r="592" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H592" t="s">
         <v>58</v>
       </c>
@@ -12775,7 +12736,7 @@
         <v>78621004</v>
       </c>
     </row>
-    <row r="593" spans="8:11">
+    <row r="593" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H593" t="s">
         <v>92</v>
       </c>
@@ -12789,7 +12750,7 @@
         <v>80629877</v>
       </c>
     </row>
-    <row r="594" spans="8:11">
+    <row r="594" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H594" t="s">
         <v>92</v>
       </c>
@@ -12803,7 +12764,7 @@
         <v>80629881</v>
       </c>
     </row>
-    <row r="595" spans="8:11">
+    <row r="595" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H595" s="7" t="s">
         <v>98</v>
       </c>
@@ -12811,13 +12772,13 @@
         <v>80915325</v>
       </c>
       <c r="J595" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="K595" s="6">
         <v>80915325</v>
       </c>
     </row>
-    <row r="596" spans="8:11">
+    <row r="596" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H596" s="7" t="s">
         <v>98</v>
       </c>
@@ -12825,41 +12786,41 @@
         <v>80915326</v>
       </c>
       <c r="J596" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="K596" s="6">
         <v>80915326</v>
       </c>
     </row>
-    <row r="597" spans="8:11">
+    <row r="597" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H597" s="7" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="I597" s="6">
         <v>80953015</v>
       </c>
       <c r="J597" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="K597" s="6">
         <v>80953015</v>
       </c>
     </row>
-    <row r="598" spans="8:11">
+    <row r="598" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H598" s="7" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="I598" s="6">
         <v>80953016</v>
       </c>
       <c r="J598" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K598" s="6">
         <v>80953016</v>
       </c>
     </row>
-    <row r="599" spans="8:11">
+    <row r="599" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H599" s="7" t="s">
         <v>29</v>
       </c>
@@ -12873,7 +12834,7 @@
         <v>81675750</v>
       </c>
     </row>
-    <row r="600" spans="8:11">
+    <row r="600" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H600" s="7" t="s">
         <v>171</v>
       </c>
@@ -12881,27 +12842,27 @@
         <v>81638306</v>
       </c>
       <c r="J600" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="K600" s="6">
         <v>81638306</v>
       </c>
     </row>
-    <row r="601" spans="8:11">
+    <row r="601" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H601" s="7" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="I601" s="6">
         <v>81918457</v>
       </c>
       <c r="J601" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="K601" s="6">
         <v>81918457</v>
       </c>
     </row>
-    <row r="602" spans="8:11">
+    <row r="602" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H602" s="7" t="s">
         <v>29</v>
       </c>
@@ -12909,13 +12870,13 @@
         <v>81538523</v>
       </c>
       <c r="J602" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="K602" s="6">
         <v>81538523</v>
       </c>
     </row>
-    <row r="603" spans="8:11">
+    <row r="603" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H603" s="7" t="s">
         <v>171</v>
       </c>
@@ -12923,13 +12884,13 @@
         <v>79040263</v>
       </c>
       <c r="J603" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K603" s="6">
         <v>79040263</v>
       </c>
     </row>
-    <row r="604" spans="8:11">
+    <row r="604" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H604" s="7" t="s">
         <v>211</v>
       </c>
@@ -12937,13 +12898,13 @@
         <v>79475749</v>
       </c>
       <c r="J604" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="K604" s="6">
         <v>79475749</v>
       </c>
     </row>
-    <row r="605" spans="8:11">
+    <row r="605" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H605" s="7" t="s">
         <v>143</v>
       </c>
@@ -12951,13 +12912,13 @@
         <v>79944232</v>
       </c>
       <c r="J605" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K605" s="6">
         <v>79944232</v>
       </c>
     </row>
-    <row r="606" spans="8:11">
+    <row r="606" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H606" s="7" t="s">
         <v>211</v>
       </c>
@@ -12965,13 +12926,13 @@
         <v>80460979</v>
       </c>
       <c r="J606" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="K606" s="6">
         <v>80460979</v>
       </c>
     </row>
-    <row r="607" spans="8:11">
+    <row r="607" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H607" s="7" t="s">
         <v>143</v>
       </c>
@@ -12979,15 +12940,15 @@
         <v>81340922</v>
       </c>
       <c r="J607" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="K607" s="6">
         <v>81340922</v>
       </c>
     </row>
-    <row r="608" spans="8:11">
+    <row r="608" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H608" s="7" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="I608" s="6">
         <v>38157908</v>
@@ -12999,9 +12960,9 @@
         <v>38157908</v>
       </c>
     </row>
-    <row r="609" spans="8:11">
+    <row r="609" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H609" s="7" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="I609" s="6">
         <v>41662266</v>
@@ -13013,7 +12974,7 @@
         <v>41662266</v>
       </c>
     </row>
-    <row r="610" spans="8:11">
+    <row r="610" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H610" s="7" t="s">
         <v>29</v>
       </c>
@@ -13021,13 +12982,13 @@
         <v>81988924</v>
       </c>
       <c r="J610" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="K610" s="6">
         <v>81988924</v>
       </c>
     </row>
-    <row r="611" spans="8:11">
+    <row r="611" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H611" s="7" t="s">
         <v>29</v>
       </c>
@@ -13035,13 +12996,13 @@
         <v>82014131</v>
       </c>
       <c r="J611" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="K611" s="6">
         <v>82014131</v>
       </c>
     </row>
-    <row r="612" spans="8:11">
+    <row r="612" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H612" s="7" t="s">
         <v>29</v>
       </c>
@@ -13049,21 +13010,21 @@
         <v>82118965</v>
       </c>
       <c r="J612" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="K612">
         <v>82118965</v>
       </c>
     </row>
-    <row r="613" spans="8:11">
+    <row r="613" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H613" s="7" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="I613">
         <v>82521123</v>
       </c>
       <c r="J613" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="K613">
         <v>82521123</v>
@@ -13131,13 +13092,13 @@
     <cfRule type="duplicateValues" dxfId="5" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A63 A72:A74 A76:A197 A199:A206 A209:A1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K612">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K613">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -13147,14 +13108,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A13:C27"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="1:3" ht="20.25">
+    <row r="13" spans="1:3" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>640</v>
       </c>
@@ -13165,7 +13126,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>13101217</v>
       </c>
@@ -13176,7 +13137,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>4125377</v>
       </c>
@@ -13187,7 +13148,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>26426530</v>
       </c>
@@ -13198,7 +13159,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>43252471</v>
       </c>
@@ -13209,7 +13170,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>64789478</v>
       </c>
@@ -13220,7 +13181,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>71030052</v>
       </c>
@@ -13231,7 +13192,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>11229298</v>
       </c>
@@ -13242,7 +13203,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="21" spans="1:3" hidden="1">
+    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>75077119</v>
       </c>
@@ -13253,7 +13214,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>42519088</v>
       </c>
@@ -13264,7 +13225,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>17579394</v>
       </c>
@@ -13275,7 +13236,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>53569741</v>
       </c>
@@ -13286,7 +13247,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>53583387</v>
       </c>
@@ -13297,7 +13258,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>12439390</v>
       </c>
@@ -13308,7 +13269,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>14107560</v>
       </c>
@@ -13327,10 +13288,10 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A26:A27 A14:A24">
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A25">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/이슈제품.xlsx
+++ b/data/이슈제품.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OA\Desktop\쿠팡업로드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37BCEC90-8DB6-4BB2-959C-BE0B7E9E2CEB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B013238D-7BE6-4B0C-BF5A-514ED8A3B800}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1640" uniqueCount="675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1655" uniqueCount="678">
   <si>
     <t>오아디머무드등-화이트</t>
   </si>
@@ -2003,10 +2003,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>입고확정</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>오아터치무선접이식키보드-포그밀크</t>
   </si>
   <si>
@@ -2092,13 +2088,29 @@
   <si>
     <t>생활가전</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>재고X, 10/20 생산완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입고X, 11/4 입고예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>단종예정</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>단종</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2140,32 +2152,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="8"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -2182,7 +2181,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2207,11 +2206,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4037,7 +4031,7 @@
         <v>573</v>
       </c>
       <c r="C58" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H58" t="s">
         <v>58</v>
@@ -4057,10 +4051,10 @@
         <v>80915325</v>
       </c>
       <c r="B59" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C59" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H59" t="s">
         <v>58</v>
@@ -4080,10 +4074,10 @@
         <v>80915326</v>
       </c>
       <c r="B60" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C60" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H60" t="s">
         <v>58</v>
@@ -4106,7 +4100,7 @@
         <v>15</v>
       </c>
       <c r="C61" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H61" t="s">
         <v>58</v>
@@ -4129,7 +4123,7 @@
         <v>345</v>
       </c>
       <c r="C62" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H62" t="s">
         <v>90</v>
@@ -4152,7 +4146,7 @@
         <v>346</v>
       </c>
       <c r="C63" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H63" t="s">
         <v>92</v>
@@ -4175,7 +4169,7 @@
         <v>573</v>
       </c>
       <c r="C64" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H64" t="s">
         <v>94</v>
@@ -4198,7 +4192,7 @@
         <v>457</v>
       </c>
       <c r="C65" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H65" t="s">
         <v>94</v>
@@ -4221,7 +4215,7 @@
         <v>553</v>
       </c>
       <c r="C66" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H66" t="s">
         <v>94</v>
@@ -4244,7 +4238,7 @@
         <v>336</v>
       </c>
       <c r="C67" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H67" t="s">
         <v>98</v>
@@ -4260,6 +4254,15 @@
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>61923953</v>
+      </c>
+      <c r="B68" t="s">
+        <v>441</v>
+      </c>
+      <c r="C68" t="s">
+        <v>674</v>
+      </c>
       <c r="H68" t="s">
         <v>98</v>
       </c>
@@ -4274,6 +4277,15 @@
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>10324264</v>
+      </c>
+      <c r="B69" t="s">
+        <v>57</v>
+      </c>
+      <c r="C69" t="s">
+        <v>675</v>
+      </c>
       <c r="H69" t="s">
         <v>98</v>
       </c>
@@ -7194,7 +7206,7 @@
         <v>564</v>
       </c>
       <c r="C198" s="10" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H198" t="s">
         <v>92</v>
@@ -7210,6 +7222,15 @@
       </c>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A199" s="6">
+        <v>11104533</v>
+      </c>
+      <c r="B199" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="C199" s="7" t="s">
+        <v>676</v>
+      </c>
       <c r="H199" t="s">
         <v>92</v>
       </c>
@@ -7224,11 +7245,15 @@
       </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A200" s="13" t="s">
-        <v>648</v>
-      </c>
-      <c r="B200" s="13"/>
-      <c r="C200" s="13"/>
+      <c r="A200" s="6">
+        <v>39270777</v>
+      </c>
+      <c r="B200" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C200" s="7" t="s">
+        <v>677</v>
+      </c>
       <c r="H200" t="s">
         <v>92</v>
       </c>
@@ -7243,7 +7268,15 @@
       </c>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B201" s="11"/>
+      <c r="A201" s="6">
+        <v>50875168</v>
+      </c>
+      <c r="B201" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="C201" s="7" t="s">
+        <v>676</v>
+      </c>
       <c r="H201" t="s">
         <v>92</v>
       </c>
@@ -7258,7 +7291,15 @@
       </c>
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B202" s="12"/>
+      <c r="A202" s="6">
+        <v>58505144</v>
+      </c>
+      <c r="B202" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C202" s="7" t="s">
+        <v>676</v>
+      </c>
       <c r="H202" t="s">
         <v>92</v>
       </c>
@@ -7273,7 +7314,15 @@
       </c>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B203" s="12"/>
+      <c r="A203" s="6">
+        <v>65969750</v>
+      </c>
+      <c r="B203" s="7" t="s">
+        <v>501</v>
+      </c>
+      <c r="C203" s="7" t="s">
+        <v>676</v>
+      </c>
       <c r="H203" t="s">
         <v>92</v>
       </c>
@@ -7288,7 +7337,15 @@
       </c>
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B204" s="12"/>
+      <c r="A204" s="6">
+        <v>71291488</v>
+      </c>
+      <c r="B204" s="7" t="s">
+        <v>564</v>
+      </c>
+      <c r="C204" s="7" t="s">
+        <v>677</v>
+      </c>
       <c r="H204" t="s">
         <v>92</v>
       </c>
@@ -7303,7 +7360,9 @@
       </c>
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B205" s="12"/>
+      <c r="A205" s="6"/>
+      <c r="B205" s="7"/>
+      <c r="C205" s="7"/>
       <c r="H205" t="s">
         <v>92</v>
       </c>
@@ -7318,7 +7377,6 @@
       </c>
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B206" s="12"/>
       <c r="H206" t="s">
         <v>92</v>
       </c>
@@ -7360,8 +7418,10 @@
         <v>36577826</v>
       </c>
     </row>
-    <row r="209" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B209" s="12"/>
+    <row r="209" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A209" s="6"/>
+      <c r="B209" s="7"/>
+      <c r="C209" s="7"/>
       <c r="H209" t="s">
         <v>92</v>
       </c>
@@ -7375,8 +7435,10 @@
         <v>35149611</v>
       </c>
     </row>
-    <row r="210" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B210" s="12"/>
+    <row r="210" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A210" s="6"/>
+      <c r="B210" s="7"/>
+      <c r="C210" s="7"/>
       <c r="H210" t="s">
         <v>92</v>
       </c>
@@ -7390,8 +7452,10 @@
         <v>26196255</v>
       </c>
     </row>
-    <row r="211" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B211" s="12"/>
+    <row r="211" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A211" s="6"/>
+      <c r="B211" s="7"/>
+      <c r="C211" s="7"/>
       <c r="H211" t="s">
         <v>92</v>
       </c>
@@ -7405,7 +7469,10 @@
         <v>11156528</v>
       </c>
     </row>
-    <row r="212" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A212" s="6"/>
+      <c r="B212" s="7"/>
+      <c r="C212" s="7"/>
       <c r="H212" t="s">
         <v>92</v>
       </c>
@@ -7419,7 +7486,7 @@
         <v>38415503</v>
       </c>
     </row>
-    <row r="213" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H213" t="s">
         <v>92</v>
       </c>
@@ -7433,7 +7500,10 @@
         <v>37244806</v>
       </c>
     </row>
-    <row r="214" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A214" s="6"/>
+      <c r="B214" s="7"/>
+      <c r="C214" s="7"/>
       <c r="H214" t="s">
         <v>92</v>
       </c>
@@ -7447,7 +7517,7 @@
         <v>27011098</v>
       </c>
     </row>
-    <row r="215" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H215" t="s">
         <v>92</v>
       </c>
@@ -7461,7 +7531,10 @@
         <v>26019234</v>
       </c>
     </row>
-    <row r="216" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A216" s="6"/>
+      <c r="B216" s="7"/>
+      <c r="C216" s="7"/>
       <c r="H216" t="s">
         <v>92</v>
       </c>
@@ -7475,7 +7548,10 @@
         <v>13959023</v>
       </c>
     </row>
-    <row r="217" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A217" s="6"/>
+      <c r="B217" s="7"/>
+      <c r="C217" s="7"/>
       <c r="H217" t="s">
         <v>92</v>
       </c>
@@ -7489,7 +7565,10 @@
         <v>12496637</v>
       </c>
     </row>
-    <row r="218" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A218" s="6"/>
+      <c r="B218" s="7"/>
+      <c r="C218" s="7"/>
       <c r="H218" t="s">
         <v>92</v>
       </c>
@@ -7503,7 +7582,10 @@
         <v>25411238</v>
       </c>
     </row>
-    <row r="219" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A219" s="6"/>
+      <c r="B219" s="7"/>
+      <c r="C219" s="7"/>
       <c r="H219" t="s">
         <v>92</v>
       </c>
@@ -7517,7 +7599,10 @@
         <v>38312169</v>
       </c>
     </row>
-    <row r="220" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A220" s="6"/>
+      <c r="B220" s="7"/>
+      <c r="C220" s="7"/>
       <c r="H220" t="s">
         <v>92</v>
       </c>
@@ -7531,7 +7616,10 @@
         <v>31886592</v>
       </c>
     </row>
-    <row r="221" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A221" s="6"/>
+      <c r="B221" s="7"/>
+      <c r="C221" s="7"/>
       <c r="H221" t="s">
         <v>92</v>
       </c>
@@ -7545,7 +7633,10 @@
         <v>11670520</v>
       </c>
     </row>
-    <row r="222" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A222" s="6"/>
+      <c r="B222" s="7"/>
+      <c r="C222" s="7"/>
       <c r="H222" t="s">
         <v>92</v>
       </c>
@@ -7559,7 +7650,10 @@
         <v>26500515</v>
       </c>
     </row>
-    <row r="223" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A223" s="6"/>
+      <c r="B223" s="7"/>
+      <c r="C223" s="7"/>
       <c r="H223" t="s">
         <v>92</v>
       </c>
@@ -7573,7 +7667,10 @@
         <v>36162739</v>
       </c>
     </row>
-    <row r="224" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A224" s="6"/>
+      <c r="B224" s="7"/>
+      <c r="C224" s="7"/>
       <c r="H224" t="s">
         <v>92</v>
       </c>
@@ -7587,7 +7684,10 @@
         <v>39893389</v>
       </c>
     </row>
-    <row r="225" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A225" s="6"/>
+      <c r="B225" s="7"/>
+      <c r="C225" s="7"/>
       <c r="H225" t="s">
         <v>92</v>
       </c>
@@ -7601,7 +7701,10 @@
         <v>39296173</v>
       </c>
     </row>
-    <row r="226" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A226" s="6"/>
+      <c r="B226" s="7"/>
+      <c r="C226" s="7"/>
       <c r="H226" t="s">
         <v>92</v>
       </c>
@@ -7615,7 +7718,10 @@
         <v>26491140</v>
       </c>
     </row>
-    <row r="227" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A227" s="6"/>
+      <c r="B227" s="7"/>
+      <c r="C227" s="7"/>
       <c r="H227" t="s">
         <v>56</v>
       </c>
@@ -7629,7 +7735,10 @@
         <v>49473587</v>
       </c>
     </row>
-    <row r="228" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A228" s="6"/>
+      <c r="B228" s="7"/>
+      <c r="C228" s="7"/>
       <c r="H228" t="s">
         <v>92</v>
       </c>
@@ -7643,7 +7752,10 @@
         <v>50326931</v>
       </c>
     </row>
-    <row r="229" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A229" s="6"/>
+      <c r="B229" s="7"/>
+      <c r="C229" s="7"/>
       <c r="H229" t="s">
         <v>152</v>
       </c>
@@ -7657,7 +7769,10 @@
         <v>12095120</v>
       </c>
     </row>
-    <row r="230" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A230" s="6"/>
+      <c r="B230" s="7"/>
+      <c r="C230" s="7"/>
       <c r="H230" t="s">
         <v>152</v>
       </c>
@@ -7671,7 +7786,10 @@
         <v>11765770</v>
       </c>
     </row>
-    <row r="231" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A231" s="6"/>
+      <c r="B231" s="7"/>
+      <c r="C231" s="7"/>
       <c r="H231" t="s">
         <v>152</v>
       </c>
@@ -7685,7 +7803,10 @@
         <v>15757638</v>
       </c>
     </row>
-    <row r="232" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A232" s="6"/>
+      <c r="B232" s="7"/>
+      <c r="C232" s="7"/>
       <c r="H232" t="s">
         <v>152</v>
       </c>
@@ -7699,7 +7820,10 @@
         <v>12038103</v>
       </c>
     </row>
-    <row r="233" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A233" s="6"/>
+      <c r="B233" s="7"/>
+      <c r="C233" s="7"/>
       <c r="H233" t="s">
         <v>152</v>
       </c>
@@ -7713,7 +7837,10 @@
         <v>46801171</v>
       </c>
     </row>
-    <row r="234" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A234" s="6"/>
+      <c r="B234" s="7"/>
+      <c r="C234" s="7"/>
       <c r="H234" t="s">
         <v>152</v>
       </c>
@@ -7727,7 +7854,10 @@
         <v>10155238</v>
       </c>
     </row>
-    <row r="235" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A235" s="6"/>
+      <c r="B235" s="7"/>
+      <c r="C235" s="7"/>
       <c r="H235" t="s">
         <v>152</v>
       </c>
@@ -7741,7 +7871,10 @@
         <v>10816066</v>
       </c>
     </row>
-    <row r="236" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A236" s="6"/>
+      <c r="B236" s="7"/>
+      <c r="C236" s="7"/>
       <c r="H236" t="s">
         <v>152</v>
       </c>
@@ -7755,7 +7888,10 @@
         <v>8668649</v>
       </c>
     </row>
-    <row r="237" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A237" s="6"/>
+      <c r="B237" s="7"/>
+      <c r="C237" s="7"/>
       <c r="H237" t="s">
         <v>152</v>
       </c>
@@ -7769,7 +7905,10 @@
         <v>36635604</v>
       </c>
     </row>
-    <row r="238" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A238" s="6"/>
+      <c r="B238" s="7"/>
+      <c r="C238" s="7"/>
       <c r="H238" t="s">
         <v>109</v>
       </c>
@@ -7783,7 +7922,10 @@
         <v>8837870</v>
       </c>
     </row>
-    <row r="239" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A239" s="6"/>
+      <c r="B239" s="7"/>
+      <c r="C239" s="7"/>
       <c r="H239" t="s">
         <v>109</v>
       </c>
@@ -7797,7 +7939,10 @@
         <v>5359040</v>
       </c>
     </row>
-    <row r="240" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A240" s="6"/>
+      <c r="B240" s="7"/>
+      <c r="C240" s="7"/>
       <c r="H240" t="s">
         <v>109</v>
       </c>
@@ -7811,7 +7956,10 @@
         <v>42373723</v>
       </c>
     </row>
-    <row r="241" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A241" s="6"/>
+      <c r="B241" s="7"/>
+      <c r="C241" s="7"/>
       <c r="H241" t="s">
         <v>109</v>
       </c>
@@ -7825,7 +7973,10 @@
         <v>16303007</v>
       </c>
     </row>
-    <row r="242" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A242" s="6"/>
+      <c r="B242" s="7"/>
+      <c r="C242" s="7"/>
       <c r="H242" t="s">
         <v>109</v>
       </c>
@@ -7839,7 +7990,10 @@
         <v>27303665</v>
       </c>
     </row>
-    <row r="243" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A243" s="6"/>
+      <c r="B243" s="7"/>
+      <c r="C243" s="7"/>
       <c r="H243" t="s">
         <v>109</v>
       </c>
@@ -7853,7 +8007,10 @@
         <v>5462299</v>
       </c>
     </row>
-    <row r="244" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A244" s="6"/>
+      <c r="B244" s="7"/>
+      <c r="C244" s="7"/>
       <c r="H244" t="s">
         <v>109</v>
       </c>
@@ -7867,7 +8024,10 @@
         <v>47220150</v>
       </c>
     </row>
-    <row r="245" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A245" s="6"/>
+      <c r="B245" s="7"/>
+      <c r="C245" s="7"/>
       <c r="H245" t="s">
         <v>109</v>
       </c>
@@ -7881,7 +8041,10 @@
         <v>42265154</v>
       </c>
     </row>
-    <row r="246" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A246" s="6"/>
+      <c r="B246" s="7"/>
+      <c r="C246" s="7"/>
       <c r="H246" t="s">
         <v>109</v>
       </c>
@@ -7895,7 +8058,10 @@
         <v>48105600</v>
       </c>
     </row>
-    <row r="247" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A247" s="6"/>
+      <c r="B247" s="7"/>
+      <c r="C247" s="7"/>
       <c r="H247" t="s">
         <v>109</v>
       </c>
@@ -7909,7 +8075,10 @@
         <v>34991467</v>
       </c>
     </row>
-    <row r="248" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A248" s="6"/>
+      <c r="B248" s="7"/>
+      <c r="C248" s="7"/>
       <c r="H248" t="s">
         <v>109</v>
       </c>
@@ -7923,7 +8092,10 @@
         <v>34348663</v>
       </c>
     </row>
-    <row r="249" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A249" s="6"/>
+      <c r="B249" s="7"/>
+      <c r="C249" s="7"/>
       <c r="H249" t="s">
         <v>109</v>
       </c>
@@ -7937,7 +8109,10 @@
         <v>34535085</v>
       </c>
     </row>
-    <row r="250" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A250" s="6"/>
+      <c r="B250" s="7"/>
+      <c r="C250" s="7"/>
       <c r="H250" t="s">
         <v>109</v>
       </c>
@@ -7951,7 +8126,10 @@
         <v>41140508</v>
       </c>
     </row>
-    <row r="251" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A251" s="6"/>
+      <c r="B251" s="7"/>
+      <c r="C251" s="7"/>
       <c r="H251" t="s">
         <v>109</v>
       </c>
@@ -7965,7 +8143,10 @@
         <v>22441147</v>
       </c>
     </row>
-    <row r="252" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A252" s="6"/>
+      <c r="B252" s="7"/>
+      <c r="C252" s="7"/>
       <c r="H252" t="s">
         <v>109</v>
       </c>
@@ -7979,7 +8160,10 @@
         <v>36811022</v>
       </c>
     </row>
-    <row r="253" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A253" s="6"/>
+      <c r="B253" s="7"/>
+      <c r="C253" s="7"/>
       <c r="H253" t="s">
         <v>109</v>
       </c>
@@ -7993,7 +8177,10 @@
         <v>36811023</v>
       </c>
     </row>
-    <row r="254" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A254" s="6"/>
+      <c r="B254" s="7"/>
+      <c r="C254" s="7"/>
       <c r="H254" t="s">
         <v>143</v>
       </c>
@@ -8007,7 +8194,10 @@
         <v>42217758</v>
       </c>
     </row>
-    <row r="255" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A255" s="6"/>
+      <c r="B255" s="7"/>
+      <c r="C255" s="7"/>
       <c r="H255" t="s">
         <v>143</v>
       </c>
@@ -8021,7 +8211,10 @@
         <v>39384055</v>
       </c>
     </row>
-    <row r="256" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A256" s="6"/>
+      <c r="B256" s="7"/>
+      <c r="C256" s="7"/>
       <c r="H256" t="s">
         <v>143</v>
       </c>
@@ -8035,7 +8228,10 @@
         <v>11681261</v>
       </c>
     </row>
-    <row r="257" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A257" s="6"/>
+      <c r="B257" s="7"/>
+      <c r="C257" s="7"/>
       <c r="H257" t="s">
         <v>211</v>
       </c>
@@ -8049,7 +8245,10 @@
         <v>37161537</v>
       </c>
     </row>
-    <row r="258" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A258" s="6"/>
+      <c r="B258" s="7"/>
+      <c r="C258" s="7"/>
       <c r="H258" t="s">
         <v>143</v>
       </c>
@@ -8063,7 +8262,10 @@
         <v>30405071</v>
       </c>
     </row>
-    <row r="259" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A259" s="6"/>
+      <c r="B259" s="7"/>
+      <c r="C259" s="7"/>
       <c r="H259" t="s">
         <v>143</v>
       </c>
@@ -8077,7 +8279,10 @@
         <v>22403445</v>
       </c>
     </row>
-    <row r="260" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A260" s="6"/>
+      <c r="B260" s="7"/>
+      <c r="C260" s="7"/>
       <c r="H260" t="s">
         <v>143</v>
       </c>
@@ -8091,7 +8296,10 @@
         <v>26257716</v>
       </c>
     </row>
-    <row r="261" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A261" s="6"/>
+      <c r="B261" s="7"/>
+      <c r="C261" s="7"/>
       <c r="H261" t="s">
         <v>143</v>
       </c>
@@ -8105,7 +8313,10 @@
         <v>12481760</v>
       </c>
     </row>
-    <row r="262" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A262" s="6"/>
+      <c r="B262" s="7"/>
+      <c r="C262" s="7"/>
       <c r="H262" t="s">
         <v>143</v>
       </c>
@@ -8119,7 +8330,10 @@
         <v>12481759</v>
       </c>
     </row>
-    <row r="263" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A263" s="6"/>
+      <c r="B263" s="7"/>
+      <c r="C263" s="7"/>
       <c r="H263" t="s">
         <v>143</v>
       </c>
@@ -8133,7 +8347,10 @@
         <v>36682232</v>
       </c>
     </row>
-    <row r="264" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A264" s="6"/>
+      <c r="B264" s="7"/>
+      <c r="C264" s="7"/>
       <c r="H264" t="s">
         <v>143</v>
       </c>
@@ -8147,7 +8364,10 @@
         <v>46727700</v>
       </c>
     </row>
-    <row r="265" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A265" s="6"/>
+      <c r="B265" s="7"/>
+      <c r="C265" s="7"/>
       <c r="H265" t="s">
         <v>143</v>
       </c>
@@ -8161,7 +8381,10 @@
         <v>40771157</v>
       </c>
     </row>
-    <row r="266" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A266" s="6"/>
+      <c r="B266" s="7"/>
+      <c r="C266" s="7"/>
       <c r="H266" t="s">
         <v>143</v>
       </c>
@@ -8175,7 +8398,10 @@
         <v>19104731</v>
       </c>
     </row>
-    <row r="267" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A267" s="6"/>
+      <c r="B267" s="7"/>
+      <c r="C267" s="7"/>
       <c r="H267" t="s">
         <v>143</v>
       </c>
@@ -8189,7 +8415,10 @@
         <v>39944753</v>
       </c>
     </row>
-    <row r="268" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A268" s="6"/>
+      <c r="B268" s="7"/>
+      <c r="C268" s="7"/>
       <c r="H268" t="s">
         <v>143</v>
       </c>
@@ -8203,7 +8432,10 @@
         <v>48449253</v>
       </c>
     </row>
-    <row r="269" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A269" s="6"/>
+      <c r="B269" s="7"/>
+      <c r="C269" s="7"/>
       <c r="H269" t="s">
         <v>143</v>
       </c>
@@ -8217,7 +8449,10 @@
         <v>42051062</v>
       </c>
     </row>
-    <row r="270" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A270" s="6"/>
+      <c r="B270" s="7"/>
+      <c r="C270" s="7"/>
       <c r="H270" t="s">
         <v>143</v>
       </c>
@@ -8231,7 +8466,10 @@
         <v>18291047</v>
       </c>
     </row>
-    <row r="271" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A271" s="6"/>
+      <c r="B271" s="7"/>
+      <c r="C271" s="7"/>
       <c r="H271" t="s">
         <v>143</v>
       </c>
@@ -8245,7 +8483,10 @@
         <v>10727917</v>
       </c>
     </row>
-    <row r="272" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A272" s="6"/>
+      <c r="B272" s="7"/>
+      <c r="C272" s="7"/>
       <c r="H272" t="s">
         <v>143</v>
       </c>
@@ -8259,7 +8500,10 @@
         <v>46543317</v>
       </c>
     </row>
-    <row r="273" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A273" s="6"/>
+      <c r="B273" s="7"/>
+      <c r="C273" s="7"/>
       <c r="H273" t="s">
         <v>143</v>
       </c>
@@ -8273,7 +8517,10 @@
         <v>13644995</v>
       </c>
     </row>
-    <row r="274" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A274" s="6"/>
+      <c r="B274" s="7"/>
+      <c r="C274" s="7"/>
       <c r="H274" t="s">
         <v>143</v>
       </c>
@@ -8287,7 +8534,10 @@
         <v>42486414</v>
       </c>
     </row>
-    <row r="275" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A275" s="6"/>
+      <c r="B275" s="7"/>
+      <c r="C275" s="7"/>
       <c r="H275" t="s">
         <v>143</v>
       </c>
@@ -8301,7 +8551,10 @@
         <v>44695653</v>
       </c>
     </row>
-    <row r="276" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A276" s="6"/>
+      <c r="B276" s="7"/>
+      <c r="C276" s="7"/>
       <c r="H276" t="s">
         <v>143</v>
       </c>
@@ -8315,7 +8568,10 @@
         <v>44374810</v>
       </c>
     </row>
-    <row r="277" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A277" s="6"/>
+      <c r="B277" s="7"/>
+      <c r="C277" s="7"/>
       <c r="H277" t="s">
         <v>143</v>
       </c>
@@ -8329,7 +8585,10 @@
         <v>29258063</v>
       </c>
     </row>
-    <row r="278" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A278" s="6"/>
+      <c r="B278" s="7"/>
+      <c r="C278" s="7"/>
       <c r="H278" t="s">
         <v>143</v>
       </c>
@@ -8343,7 +8602,10 @@
         <v>13405604</v>
       </c>
     </row>
-    <row r="279" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A279" s="6"/>
+      <c r="B279" s="7"/>
+      <c r="C279" s="7"/>
       <c r="H279" t="s">
         <v>143</v>
       </c>
@@ -8357,7 +8619,10 @@
         <v>10646862</v>
       </c>
     </row>
-    <row r="280" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A280" s="6"/>
+      <c r="B280" s="7"/>
+      <c r="C280" s="7"/>
       <c r="H280" t="s">
         <v>143</v>
       </c>
@@ -8371,7 +8636,10 @@
         <v>12362063</v>
       </c>
     </row>
-    <row r="281" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A281" s="6"/>
+      <c r="B281" s="7"/>
+      <c r="C281" s="7"/>
       <c r="H281" t="s">
         <v>90</v>
       </c>
@@ -8385,7 +8653,10 @@
         <v>40185196</v>
       </c>
     </row>
-    <row r="282" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A282" s="6"/>
+      <c r="B282" s="7"/>
+      <c r="C282" s="7"/>
       <c r="H282" t="s">
         <v>90</v>
       </c>
@@ -8399,7 +8670,10 @@
         <v>15825326</v>
       </c>
     </row>
-    <row r="283" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A283" s="6"/>
+      <c r="B283" s="7"/>
+      <c r="C283" s="7"/>
       <c r="H283" t="s">
         <v>90</v>
       </c>
@@ -8413,7 +8687,10 @@
         <v>26375455</v>
       </c>
     </row>
-    <row r="284" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A284" s="6"/>
+      <c r="B284" s="7"/>
+      <c r="C284" s="7"/>
       <c r="H284" t="s">
         <v>90</v>
       </c>
@@ -8427,7 +8704,10 @@
         <v>42803850</v>
       </c>
     </row>
-    <row r="285" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A285" s="6"/>
+      <c r="B285" s="7"/>
+      <c r="C285" s="7"/>
       <c r="H285" t="s">
         <v>90</v>
       </c>
@@ -8441,7 +8721,10 @@
         <v>50154913</v>
       </c>
     </row>
-    <row r="286" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A286" s="6"/>
+      <c r="B286" s="7"/>
+      <c r="C286" s="7"/>
       <c r="H286" t="s">
         <v>90</v>
       </c>
@@ -8455,7 +8738,10 @@
         <v>16806254</v>
       </c>
     </row>
-    <row r="287" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A287" s="6"/>
+      <c r="B287" s="7"/>
+      <c r="C287" s="7"/>
       <c r="H287" t="s">
         <v>90</v>
       </c>
@@ -8469,7 +8755,10 @@
         <v>40501253</v>
       </c>
     </row>
-    <row r="288" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A288" s="6"/>
+      <c r="B288" s="7"/>
+      <c r="C288" s="7"/>
       <c r="H288" t="s">
         <v>90</v>
       </c>
@@ -8483,7 +8772,10 @@
         <v>14878740</v>
       </c>
     </row>
-    <row r="289" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A289" s="6"/>
+      <c r="B289" s="7"/>
+      <c r="C289" s="7"/>
       <c r="H289" t="s">
         <v>90</v>
       </c>
@@ -8497,7 +8789,10 @@
         <v>12673237</v>
       </c>
     </row>
-    <row r="290" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A290" s="6"/>
+      <c r="B290" s="7"/>
+      <c r="C290" s="7"/>
       <c r="H290" t="s">
         <v>90</v>
       </c>
@@ -8511,7 +8806,10 @@
         <v>17579662</v>
       </c>
     </row>
-    <row r="291" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A291" s="6"/>
+      <c r="B291" s="7"/>
+      <c r="C291" s="7"/>
       <c r="H291" t="s">
         <v>90</v>
       </c>
@@ -8525,7 +8823,10 @@
         <v>14719737</v>
       </c>
     </row>
-    <row r="292" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A292" s="6"/>
+      <c r="B292" s="7"/>
+      <c r="C292" s="7"/>
       <c r="H292" t="s">
         <v>90</v>
       </c>
@@ -8539,7 +8840,10 @@
         <v>22119013</v>
       </c>
     </row>
-    <row r="293" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A293" s="6"/>
+      <c r="B293" s="7"/>
+      <c r="C293" s="7"/>
       <c r="H293" t="s">
         <v>90</v>
       </c>
@@ -8553,7 +8857,10 @@
         <v>15795597</v>
       </c>
     </row>
-    <row r="294" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A294" s="6"/>
+      <c r="B294" s="7"/>
+      <c r="C294" s="7"/>
       <c r="H294" t="s">
         <v>90</v>
       </c>
@@ -8567,7 +8874,10 @@
         <v>12126317</v>
       </c>
     </row>
-    <row r="295" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A295" s="6"/>
+      <c r="B295" s="7"/>
+      <c r="C295" s="7"/>
       <c r="H295" t="s">
         <v>90</v>
       </c>
@@ -8581,7 +8891,10 @@
         <v>39239709</v>
       </c>
     </row>
-    <row r="296" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A296" s="6"/>
+      <c r="B296" s="7"/>
+      <c r="C296" s="7"/>
       <c r="H296" t="s">
         <v>90</v>
       </c>
@@ -8595,7 +8908,10 @@
         <v>14488275</v>
       </c>
     </row>
-    <row r="297" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A297" s="6"/>
+      <c r="B297" s="7"/>
+      <c r="C297" s="7"/>
       <c r="H297" t="s">
         <v>90</v>
       </c>
@@ -8609,7 +8925,10 @@
         <v>42519088</v>
       </c>
     </row>
-    <row r="298" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A298" s="6"/>
+      <c r="B298" s="7"/>
+      <c r="C298" s="7"/>
       <c r="H298" t="s">
         <v>90</v>
       </c>
@@ -8623,7 +8942,10 @@
         <v>17579394</v>
       </c>
     </row>
-    <row r="299" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A299" s="6"/>
+      <c r="B299" s="7"/>
+      <c r="C299" s="7"/>
       <c r="H299" t="s">
         <v>90</v>
       </c>
@@ -8637,7 +8959,10 @@
         <v>27056005</v>
       </c>
     </row>
-    <row r="300" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A300" s="6"/>
+      <c r="B300" s="7"/>
+      <c r="C300" s="7"/>
       <c r="H300" t="s">
         <v>90</v>
       </c>
@@ -8651,7 +8976,10 @@
         <v>24832169</v>
       </c>
     </row>
-    <row r="301" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A301" s="6"/>
+      <c r="B301" s="7"/>
+      <c r="C301" s="7"/>
       <c r="H301" t="s">
         <v>171</v>
       </c>
@@ -8665,7 +8993,10 @@
         <v>39147133</v>
       </c>
     </row>
-    <row r="302" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A302" s="6"/>
+      <c r="B302" s="7"/>
+      <c r="C302" s="7"/>
       <c r="H302" t="s">
         <v>171</v>
       </c>
@@ -8679,7 +9010,10 @@
         <v>39030281</v>
       </c>
     </row>
-    <row r="303" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A303" s="6"/>
+      <c r="B303" s="7"/>
+      <c r="C303" s="7"/>
       <c r="H303" t="s">
         <v>171</v>
       </c>
@@ -8693,7 +9027,10 @@
         <v>13373616</v>
       </c>
     </row>
-    <row r="304" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A304" s="6"/>
+      <c r="B304" s="7"/>
+      <c r="C304" s="7"/>
       <c r="H304" t="s">
         <v>171</v>
       </c>
@@ -8707,7 +9044,10 @@
         <v>12757668</v>
       </c>
     </row>
-    <row r="305" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A305" s="6"/>
+      <c r="B305" s="7"/>
+      <c r="C305" s="7"/>
       <c r="H305" t="s">
         <v>171</v>
       </c>
@@ -8721,7 +9061,10 @@
         <v>38977260</v>
       </c>
     </row>
-    <row r="306" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A306" s="6"/>
+      <c r="B306" s="7"/>
+      <c r="C306" s="7"/>
       <c r="H306" t="s">
         <v>29</v>
       </c>
@@ -8735,7 +9078,10 @@
         <v>38676914</v>
       </c>
     </row>
-    <row r="307" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A307" s="6"/>
+      <c r="B307" s="7"/>
+      <c r="C307" s="7"/>
       <c r="H307" t="s">
         <v>29</v>
       </c>
@@ -8749,7 +9095,10 @@
         <v>39911056</v>
       </c>
     </row>
-    <row r="308" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A308" s="6"/>
+      <c r="B308" s="7"/>
+      <c r="C308" s="7"/>
       <c r="H308" t="s">
         <v>29</v>
       </c>
@@ -8763,7 +9112,10 @@
         <v>40102936</v>
       </c>
     </row>
-    <row r="309" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A309" s="6"/>
+      <c r="B309" s="7"/>
+      <c r="C309" s="7"/>
       <c r="H309" t="s">
         <v>29</v>
       </c>
@@ -8777,7 +9129,10 @@
         <v>10929274</v>
       </c>
     </row>
-    <row r="310" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A310" s="6"/>
+      <c r="B310" s="7"/>
+      <c r="C310" s="7"/>
       <c r="H310" t="s">
         <v>29</v>
       </c>
@@ -8791,7 +9146,10 @@
         <v>10929273</v>
       </c>
     </row>
-    <row r="311" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A311" s="6"/>
+      <c r="B311" s="7"/>
+      <c r="C311" s="7"/>
       <c r="H311" t="s">
         <v>29</v>
       </c>
@@ -8805,7 +9163,10 @@
         <v>38412071</v>
       </c>
     </row>
-    <row r="312" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A312" s="6"/>
+      <c r="B312" s="7"/>
+      <c r="C312" s="7"/>
       <c r="H312" t="s">
         <v>29</v>
       </c>
@@ -8819,7 +9180,10 @@
         <v>29280326</v>
       </c>
     </row>
-    <row r="313" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A313" s="6"/>
+      <c r="B313" s="7"/>
+      <c r="C313" s="7"/>
       <c r="H313" t="s">
         <v>29</v>
       </c>
@@ -8833,7 +9197,10 @@
         <v>38412101</v>
       </c>
     </row>
-    <row r="314" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A314" s="6"/>
+      <c r="B314" s="7"/>
+      <c r="C314" s="7"/>
       <c r="H314" t="s">
         <v>98</v>
       </c>
@@ -8847,7 +9214,10 @@
         <v>5332788</v>
       </c>
     </row>
-    <row r="315" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A315" s="6"/>
+      <c r="B315" s="7"/>
+      <c r="C315" s="7"/>
       <c r="H315" t="s">
         <v>98</v>
       </c>
@@ -8861,7 +9231,10 @@
         <v>5332789</v>
       </c>
     </row>
-    <row r="316" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A316" s="6"/>
+      <c r="B316" s="7"/>
+      <c r="C316" s="7"/>
       <c r="H316" t="s">
         <v>98</v>
       </c>
@@ -8875,7 +9248,10 @@
         <v>51016959</v>
       </c>
     </row>
-    <row r="317" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A317" s="6"/>
+      <c r="B317" s="7"/>
+      <c r="C317" s="7"/>
       <c r="H317" t="s">
         <v>90</v>
       </c>
@@ -8889,7 +9265,10 @@
         <v>40636333</v>
       </c>
     </row>
-    <row r="318" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A318" s="6"/>
+      <c r="B318" s="7"/>
+      <c r="C318" s="7"/>
       <c r="H318" t="s">
         <v>171</v>
       </c>
@@ -8903,7 +9282,10 @@
         <v>50875168</v>
       </c>
     </row>
-    <row r="319" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A319" s="6"/>
+      <c r="B319" s="7"/>
+      <c r="C319" s="7"/>
       <c r="H319" t="s">
         <v>58</v>
       </c>
@@ -8917,7 +9299,10 @@
         <v>51623281</v>
       </c>
     </row>
-    <row r="320" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A320" s="6"/>
+      <c r="B320" s="7"/>
+      <c r="C320" s="7"/>
       <c r="H320" t="s">
         <v>92</v>
       </c>
@@ -8931,7 +9316,10 @@
         <v>51897600</v>
       </c>
     </row>
-    <row r="321" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A321" s="6"/>
+      <c r="B321" s="7"/>
+      <c r="C321" s="7"/>
       <c r="H321" t="s">
         <v>58</v>
       </c>
@@ -8945,7 +9333,10 @@
         <v>51989601</v>
       </c>
     </row>
-    <row r="322" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A322" s="6"/>
+      <c r="B322" s="7"/>
+      <c r="C322" s="7"/>
       <c r="H322" t="s">
         <v>109</v>
       </c>
@@ -8959,7 +9350,10 @@
         <v>52390638</v>
       </c>
     </row>
-    <row r="323" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A323" s="6"/>
+      <c r="B323" s="7"/>
+      <c r="C323" s="7"/>
       <c r="H323" t="s">
         <v>109</v>
       </c>
@@ -8973,7 +9367,10 @@
         <v>52362395</v>
       </c>
     </row>
-    <row r="324" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A324" s="6"/>
+      <c r="B324" s="7"/>
+      <c r="C324" s="7"/>
       <c r="H324" t="s">
         <v>90</v>
       </c>
@@ -8987,7 +9384,10 @@
         <v>52155415</v>
       </c>
     </row>
-    <row r="325" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A325" s="6"/>
+      <c r="B325" s="7"/>
+      <c r="C325" s="7"/>
       <c r="H325" t="s">
         <v>92</v>
       </c>
@@ -9001,7 +9401,10 @@
         <v>52162444</v>
       </c>
     </row>
-    <row r="326" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A326" s="6"/>
+      <c r="B326" s="7"/>
+      <c r="C326" s="7"/>
       <c r="H326" t="s">
         <v>171</v>
       </c>
@@ -9015,7 +9418,10 @@
         <v>52270898</v>
       </c>
     </row>
-    <row r="327" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A327" s="6"/>
+      <c r="B327" s="7"/>
+      <c r="C327" s="7"/>
       <c r="H327" t="s">
         <v>98</v>
       </c>
@@ -9029,7 +9435,10 @@
         <v>52211558</v>
       </c>
     </row>
-    <row r="328" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A328" s="6"/>
+      <c r="B328" s="7"/>
+      <c r="C328" s="7"/>
       <c r="H328" t="s">
         <v>98</v>
       </c>
@@ -9043,7 +9452,10 @@
         <v>52217000</v>
       </c>
     </row>
-    <row r="329" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A329" s="6"/>
+      <c r="B329" s="7"/>
+      <c r="C329" s="7"/>
       <c r="H329" t="s">
         <v>29</v>
       </c>
@@ -9057,7 +9469,7 @@
         <v>51689222</v>
       </c>
     </row>
-    <row r="330" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H330" t="s">
         <v>29</v>
       </c>
@@ -9071,7 +9483,7 @@
         <v>51684787</v>
       </c>
     </row>
-    <row r="331" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H331" t="s">
         <v>29</v>
       </c>
@@ -9085,7 +9497,7 @@
         <v>51883980</v>
       </c>
     </row>
-    <row r="332" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H332" t="s">
         <v>29</v>
       </c>
@@ -9099,7 +9511,7 @@
         <v>51898514</v>
       </c>
     </row>
-    <row r="333" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H333" t="s">
         <v>98</v>
       </c>
@@ -9113,7 +9525,7 @@
         <v>52990015</v>
       </c>
     </row>
-    <row r="334" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H334" t="s">
         <v>29</v>
       </c>
@@ -9127,7 +9539,7 @@
         <v>52581507</v>
       </c>
     </row>
-    <row r="335" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H335" t="s">
         <v>29</v>
       </c>
@@ -9141,7 +9553,7 @@
         <v>52613211</v>
       </c>
     </row>
-    <row r="336" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H336" t="s">
         <v>29</v>
       </c>
@@ -12772,7 +13184,7 @@
         <v>80915325</v>
       </c>
       <c r="J595" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="K595" s="6">
         <v>80915325</v>
@@ -12786,7 +13198,7 @@
         <v>80915326</v>
       </c>
       <c r="J596" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="K596" s="6">
         <v>80915326</v>
@@ -12794,13 +13206,13 @@
     </row>
     <row r="597" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H597" s="7" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="I597" s="6">
         <v>80953015</v>
       </c>
       <c r="J597" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="K597" s="6">
         <v>80953015</v>
@@ -12808,13 +13220,13 @@
     </row>
     <row r="598" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H598" s="7" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="I598" s="6">
         <v>80953016</v>
       </c>
       <c r="J598" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="K598" s="6">
         <v>80953016</v>
@@ -12842,7 +13254,7 @@
         <v>81638306</v>
       </c>
       <c r="J600" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K600" s="6">
         <v>81638306</v>
@@ -12850,13 +13262,13 @@
     </row>
     <row r="601" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H601" s="7" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="I601" s="6">
         <v>81918457</v>
       </c>
       <c r="J601" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="K601" s="6">
         <v>81918457</v>
@@ -12870,7 +13282,7 @@
         <v>81538523</v>
       </c>
       <c r="J602" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="K602" s="6">
         <v>81538523</v>
@@ -12884,7 +13296,7 @@
         <v>79040263</v>
       </c>
       <c r="J603" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="K603" s="6">
         <v>79040263</v>
@@ -12898,7 +13310,7 @@
         <v>79475749</v>
       </c>
       <c r="J604" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K604" s="6">
         <v>79475749</v>
@@ -12912,7 +13324,7 @@
         <v>79944232</v>
       </c>
       <c r="J605" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="K605" s="6">
         <v>79944232</v>
@@ -12926,7 +13338,7 @@
         <v>80460979</v>
       </c>
       <c r="J606" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K606" s="6">
         <v>80460979</v>
@@ -12940,7 +13352,7 @@
         <v>81340922</v>
       </c>
       <c r="J607" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="K607" s="6">
         <v>81340922</v>
@@ -12948,7 +13360,7 @@
     </row>
     <row r="608" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H608" s="7" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="I608" s="6">
         <v>38157908</v>
@@ -12962,7 +13374,7 @@
     </row>
     <row r="609" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H609" s="7" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="I609" s="6">
         <v>41662266</v>
@@ -12982,7 +13394,7 @@
         <v>81988924</v>
       </c>
       <c r="J610" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="K610" s="6">
         <v>81988924</v>
@@ -12996,7 +13408,7 @@
         <v>82014131</v>
       </c>
       <c r="J611" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="K611" s="6">
         <v>82014131</v>
@@ -13010,7 +13422,7 @@
         <v>82118965</v>
       </c>
       <c r="J612" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="K612">
         <v>82118965</v>
@@ -13018,13 +13430,13 @@
     </row>
     <row r="613" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H613" s="7" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="I613">
         <v>82521123</v>
       </c>
       <c r="J613" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="K613">
         <v>82521123</v>
@@ -13036,69 +13448,66 @@
       <sortCondition descending="1" ref="C1"/>
     </sortState>
   </autoFilter>
-  <mergeCells count="1">
-    <mergeCell ref="A200:C200"/>
-  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A62:A63 A199:A206 A1:A58 A72:A74 A76:A197 A209:A1048576">
-    <cfRule type="duplicateValues" dxfId="21" priority="18"/>
+  <conditionalFormatting sqref="I1:I1048576">
+    <cfRule type="duplicateValues" dxfId="21" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A62:A63 A202:A206 A1:A58 A72:A74 A76:A197 A209:A1048576">
-    <cfRule type="duplicateValues" dxfId="20" priority="34"/>
+  <conditionalFormatting sqref="K595:K611">
+    <cfRule type="duplicateValues" dxfId="20" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I1048576">
+  <conditionalFormatting sqref="A59:A60">
     <cfRule type="duplicateValues" dxfId="19" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K595:K611">
+  <conditionalFormatting sqref="A61">
     <cfRule type="duplicateValues" dxfId="18" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A59:A60">
-    <cfRule type="duplicateValues" dxfId="17" priority="15"/>
+  <conditionalFormatting sqref="A64">
+    <cfRule type="duplicateValues" dxfId="17" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A61">
-    <cfRule type="duplicateValues" dxfId="16" priority="14"/>
+  <conditionalFormatting sqref="A75">
+    <cfRule type="duplicateValues" dxfId="16" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A64">
+  <conditionalFormatting sqref="A198">
     <cfRule type="duplicateValues" dxfId="15" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A75">
+  <conditionalFormatting sqref="A201">
     <cfRule type="duplicateValues" dxfId="14" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A198">
+  <conditionalFormatting sqref="A202">
     <cfRule type="duplicateValues" dxfId="13" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A207">
+  <conditionalFormatting sqref="A65">
     <cfRule type="duplicateValues" dxfId="12" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A208">
+  <conditionalFormatting sqref="A66">
     <cfRule type="duplicateValues" dxfId="11" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A65">
+  <conditionalFormatting sqref="A67">
     <cfRule type="duplicateValues" dxfId="10" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A66">
-    <cfRule type="duplicateValues" dxfId="9" priority="6"/>
+  <conditionalFormatting sqref="K612">
+    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A67">
-    <cfRule type="duplicateValues" dxfId="8" priority="5"/>
+  <conditionalFormatting sqref="K613">
+    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A68">
-    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A69">
-    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A77:A197 A202:A206 A1:A54 A209:A1048576">
-    <cfRule type="duplicateValues" dxfId="5" priority="35"/>
+  <conditionalFormatting sqref="A62:A63 A199:A200 A1:A58 A72:A74 A76:A197 A209:A212 A216:A1048576 A214 A203:A205">
+    <cfRule type="duplicateValues" dxfId="5" priority="52"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A63 A72:A74 A76:A197 A199:A206 A209:A1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="49"/>
+  <conditionalFormatting sqref="A62:A63 A200 A1:A58 A72:A74 A76:A197 A209:A212 A216:A1048576 A214 A203:A205">
+    <cfRule type="duplicateValues" dxfId="4" priority="60"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K612">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+  <conditionalFormatting sqref="A77:A197 A200 A1:A54 A209:A212 A216:A1048576 A214 A203:A205">
+    <cfRule type="duplicateValues" dxfId="3" priority="68"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K613">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+  <conditionalFormatting sqref="A1:A63 A72:A74 A76:A197 A199:A200 A209:A212 A216:A1048576 A214 A203:A205">
+    <cfRule type="duplicateValues" dxfId="2" priority="73"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data/이슈제품.xlsx
+++ b/data/이슈제품.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OA\Desktop\쿠팡업로드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B013238D-7BE6-4B0C-BF5A-514ED8A3B800}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6AB23DC-A360-423A-B425-3D2A8D4A4A60}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1655" uniqueCount="678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1657" uniqueCount="679">
   <si>
     <t>오아디머무드등-화이트</t>
   </si>
@@ -2104,6 +2104,10 @@
   <si>
     <t>단종</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>단종</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2159,12 +2163,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -2181,7 +2191,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2207,11 +2217,26 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="23">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -7222,7 +7247,7 @@
       </c>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A199" s="6">
+      <c r="A199" s="11">
         <v>11104533</v>
       </c>
       <c r="B199" s="7" t="s">
@@ -7245,10 +7270,10 @@
       </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A200" s="6">
+      <c r="A200" s="11">
         <v>39270777</v>
       </c>
-      <c r="B200" s="7" t="s">
+      <c r="B200" s="12" t="s">
         <v>106</v>
       </c>
       <c r="C200" s="7" t="s">
@@ -7268,7 +7293,7 @@
       </c>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A201" s="6">
+      <c r="A201" s="11">
         <v>50875168</v>
       </c>
       <c r="B201" s="7" t="s">
@@ -7291,7 +7316,7 @@
       </c>
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A202" s="6">
+      <c r="A202" s="11">
         <v>58505144</v>
       </c>
       <c r="B202" s="7" t="s">
@@ -7314,7 +7339,7 @@
       </c>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A203" s="6">
+      <c r="A203" s="11">
         <v>65969750</v>
       </c>
       <c r="B203" s="7" t="s">
@@ -7337,7 +7362,7 @@
       </c>
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A204" s="6">
+      <c r="A204" s="11">
         <v>71291488</v>
       </c>
       <c r="B204" s="7" t="s">
@@ -7360,9 +7385,15 @@
       </c>
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A205" s="6"/>
-      <c r="B205" s="7"/>
-      <c r="C205" s="7"/>
+      <c r="A205">
+        <v>68462854</v>
+      </c>
+      <c r="B205" s="13" t="s">
+        <v>532</v>
+      </c>
+      <c r="C205" s="7" t="s">
+        <v>678</v>
+      </c>
       <c r="H205" t="s">
         <v>92</v>
       </c>
@@ -13450,64 +13481,67 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="I1:I1048576">
+    <cfRule type="duplicateValues" dxfId="22" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K595:K611">
     <cfRule type="duplicateValues" dxfId="21" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K595:K611">
+  <conditionalFormatting sqref="A59:A60">
     <cfRule type="duplicateValues" dxfId="20" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A59:A60">
+  <conditionalFormatting sqref="A61">
     <cfRule type="duplicateValues" dxfId="19" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A61">
-    <cfRule type="duplicateValues" dxfId="18" priority="16"/>
+  <conditionalFormatting sqref="A64">
+    <cfRule type="duplicateValues" dxfId="18" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A64">
+  <conditionalFormatting sqref="A75">
     <cfRule type="duplicateValues" dxfId="17" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A75">
+  <conditionalFormatting sqref="A198">
     <cfRule type="duplicateValues" dxfId="16" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A198">
+  <conditionalFormatting sqref="A201">
     <cfRule type="duplicateValues" dxfId="15" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A201">
+  <conditionalFormatting sqref="A202">
     <cfRule type="duplicateValues" dxfId="14" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A202">
+  <conditionalFormatting sqref="A65">
     <cfRule type="duplicateValues" dxfId="13" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A65">
+  <conditionalFormatting sqref="A66">
     <cfRule type="duplicateValues" dxfId="12" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A66">
+  <conditionalFormatting sqref="A67">
     <cfRule type="duplicateValues" dxfId="11" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A67">
-    <cfRule type="duplicateValues" dxfId="10" priority="7"/>
+  <conditionalFormatting sqref="K612">
+    <cfRule type="duplicateValues" dxfId="10" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K612">
+  <conditionalFormatting sqref="K613">
     <cfRule type="duplicateValues" dxfId="9" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K613">
+  <conditionalFormatting sqref="A68">
     <cfRule type="duplicateValues" dxfId="8" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A68">
+  <conditionalFormatting sqref="A69">
     <cfRule type="duplicateValues" dxfId="7" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A69">
-    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
+  <conditionalFormatting sqref="A62:A63 A199:A200 A1:A58 A72:A74 A76:A197 A209:A212 A216:A1048576 A214 A203:A204">
+    <cfRule type="duplicateValues" dxfId="6" priority="53"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A62:A63 A199:A200 A1:A58 A72:A74 A76:A197 A209:A212 A216:A1048576 A214 A203:A205">
-    <cfRule type="duplicateValues" dxfId="5" priority="52"/>
+  <conditionalFormatting sqref="A62:A63 A200 A1:A58 A72:A74 A76:A197 A209:A212 A216:A1048576 A214 A203:A204">
+    <cfRule type="duplicateValues" dxfId="5" priority="61"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A62:A63 A200 A1:A58 A72:A74 A76:A197 A209:A212 A216:A1048576 A214 A203:A205">
-    <cfRule type="duplicateValues" dxfId="4" priority="60"/>
+  <conditionalFormatting sqref="A77:A197 A200 A1:A54 A209:A212 A216:A1048576 A214 A203:A204">
+    <cfRule type="duplicateValues" dxfId="4" priority="69"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A77:A197 A200 A1:A54 A209:A212 A216:A1048576 A214 A203:A205">
-    <cfRule type="duplicateValues" dxfId="3" priority="68"/>
+  <conditionalFormatting sqref="A1:A63 A72:A74 A76:A197 A199:A200 A209:A212 A216:A1048576 A214 A203:A204">
+    <cfRule type="duplicateValues" dxfId="3" priority="74"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A63 A72:A74 A76:A197 A199:A200 A209:A212 A216:A1048576 A214 A203:A205">
-    <cfRule type="duplicateValues" dxfId="2" priority="73"/>
+  <conditionalFormatting sqref="A205">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -13697,10 +13731,10 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A26:A27 A14:A24">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A25">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/이슈제품.xlsx
+++ b/data/이슈제품.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OA\Desktop\쿠팡업로드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6AB23DC-A360-423A-B425-3D2A8D4A4A60}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22F6BB21-3F5F-476D-8B9C-F13137340AF2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1657" uniqueCount="679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1647" uniqueCount="676">
   <si>
     <t>오아디머무드등-화이트</t>
   </si>
@@ -1920,10 +1920,6 @@
   </si>
   <si>
     <t>운영X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>협의, 11월 초</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2048,10 +2044,6 @@
     <t>뷰티</t>
   </si>
   <si>
-    <t>10/20 생산완료</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>입고X, 인증번호 오류로 다음 발주건부터 입고 가능</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2060,10 +2052,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>협의, 11/4 입고예정</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>협의, 11/12 예정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2090,10 +2078,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>재고X, 10/20 생산완료</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>입고X, 11/4 입고예정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2107,6 +2091,10 @@
   </si>
   <si>
     <t>단종</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>재고X, 11/12 입고</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2771,13 +2759,13 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>4152606</v>
+        <v>68880617</v>
       </c>
       <c r="B2" t="s">
-        <v>222</v>
+        <v>622</v>
       </c>
       <c r="C2" t="s">
-        <v>628</v>
+        <v>619</v>
       </c>
       <c r="H2" t="s">
         <v>29</v>
@@ -2794,13 +2782,13 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>12263239</v>
+        <v>65933937</v>
       </c>
       <c r="B3" t="s">
-        <v>206</v>
+        <v>499</v>
       </c>
       <c r="C3" t="s">
-        <v>619</v>
+        <v>630</v>
       </c>
       <c r="H3" t="s">
         <v>29</v>
@@ -2817,13 +2805,13 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>68880617</v>
+        <v>76375597</v>
       </c>
       <c r="B4" t="s">
-        <v>622</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>619</v>
+        <v>22</v>
       </c>
       <c r="H4" t="s">
         <v>29</v>
@@ -2840,13 +2828,13 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>65933937</v>
+        <v>60015061</v>
       </c>
       <c r="B5" t="s">
-        <v>499</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>631</v>
+        <v>1</v>
       </c>
       <c r="H5" t="s">
         <v>29</v>
@@ -2863,13 +2851,13 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>76375597</v>
+        <v>50725354</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>207</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>618</v>
       </c>
       <c r="H6" t="s">
         <v>29</v>
@@ -2886,13 +2874,13 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>60015061</v>
+        <v>50153946</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>114</v>
       </c>
       <c r="C7" t="s">
-        <v>1</v>
+        <v>621</v>
       </c>
       <c r="H7" t="s">
         <v>29</v>
@@ -2909,13 +2897,13 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>50725354</v>
+        <v>75741354</v>
       </c>
       <c r="B8" t="s">
-        <v>207</v>
+        <v>601</v>
       </c>
       <c r="C8" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="H8" t="s">
         <v>29</v>
@@ -2932,13 +2920,13 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>50153946</v>
+        <v>75077119</v>
       </c>
       <c r="B9" t="s">
-        <v>114</v>
+        <v>598</v>
       </c>
       <c r="C9" t="s">
-        <v>621</v>
+        <v>642</v>
       </c>
       <c r="H9" t="s">
         <v>29</v>
@@ -2955,13 +2943,13 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>75741354</v>
-      </c>
-      <c r="B10" t="s">
-        <v>601</v>
+        <v>51623281</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>624</v>
       </c>
       <c r="C10" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="H10" t="s">
         <v>29</v>
@@ -2978,13 +2966,13 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>75077119</v>
-      </c>
-      <c r="B11" t="s">
-        <v>598</v>
+        <v>51989601</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>625</v>
       </c>
       <c r="C11" t="s">
-        <v>643</v>
+        <v>626</v>
       </c>
       <c r="H11" t="s">
         <v>29</v>
@@ -3001,10 +2989,10 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>51623281</v>
+        <v>11192166</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>624</v>
+        <v>166</v>
       </c>
       <c r="C12" t="s">
         <v>626</v>
@@ -3024,10 +3012,10 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>51989601</v>
+        <v>15812678</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>625</v>
+        <v>145</v>
       </c>
       <c r="C13" t="s">
         <v>626</v>
@@ -3047,10 +3035,10 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>11192166</v>
+        <v>12091621</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="C14" t="s">
         <v>626</v>
@@ -3070,10 +3058,10 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>15812678</v>
+        <v>12143584</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C15" t="s">
         <v>626</v>
@@ -3093,10 +3081,10 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>12091621</v>
+        <v>11192167</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="C16" t="s">
         <v>626</v>
@@ -3116,10 +3104,10 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>12143584</v>
+        <v>12143581</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C17" t="s">
         <v>626</v>
@@ -3139,10 +3127,10 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>11192167</v>
+        <v>11192165</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C18" t="s">
         <v>626</v>
@@ -3162,10 +3150,10 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>12143581</v>
+        <v>11192163</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C19" t="s">
         <v>626</v>
@@ -3185,10 +3173,10 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>11192165</v>
+        <v>11291291</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="C20" t="s">
         <v>626</v>
@@ -3208,10 +3196,10 @@
     </row>
     <row r="21" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>11192163</v>
+        <v>16171214</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C21" t="s">
         <v>626</v>
@@ -3231,10 +3219,10 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>11291291</v>
+        <v>12218847</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C22" t="s">
         <v>626</v>
@@ -3254,10 +3242,10 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>16171214</v>
+        <v>15838517</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C23" t="s">
         <v>626</v>
@@ -3277,10 +3265,10 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>12218847</v>
+        <v>12673238</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C24" t="s">
         <v>626</v>
@@ -3300,10 +3288,10 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>15838517</v>
+        <v>37790051</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C25" t="s">
         <v>626</v>
@@ -3323,10 +3311,10 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>12673238</v>
+        <v>37594934</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="C26" t="s">
         <v>626</v>
@@ -3346,10 +3334,10 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>37790051</v>
+        <v>15702671</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="C27" t="s">
         <v>626</v>
@@ -3369,10 +3357,10 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>37594934</v>
+        <v>39071990</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C28" t="s">
         <v>626</v>
@@ -3392,10 +3380,10 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>15702671</v>
+        <v>52204284</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>173</v>
+        <v>91</v>
       </c>
       <c r="C29" t="s">
         <v>626</v>
@@ -3415,10 +3403,10 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>39071990</v>
+        <v>39006854</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C30" t="s">
         <v>626</v>
@@ -3438,10 +3426,10 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>52204284</v>
+        <v>39006857</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>91</v>
+        <v>161</v>
       </c>
       <c r="C31" t="s">
         <v>626</v>
@@ -3461,10 +3449,10 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>39006854</v>
+        <v>39006855</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C32" t="s">
         <v>626</v>
@@ -3484,10 +3472,10 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>39006857</v>
+        <v>51883980</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>161</v>
+        <v>361</v>
       </c>
       <c r="C33" t="s">
         <v>626</v>
@@ -3507,10 +3495,10 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>39006855</v>
+        <v>52578670</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>162</v>
+        <v>366</v>
       </c>
       <c r="C34" t="s">
         <v>626</v>
@@ -3530,10 +3518,10 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>51883980</v>
+        <v>52155531</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>361</v>
+        <v>93</v>
       </c>
       <c r="C35" t="s">
         <v>626</v>
@@ -3553,10 +3541,10 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>52578670</v>
+        <v>15831347</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>366</v>
+        <v>141</v>
       </c>
       <c r="C36" t="s">
         <v>626</v>
@@ -3576,10 +3564,10 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>52155531</v>
+        <v>32548061</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>93</v>
+        <v>168</v>
       </c>
       <c r="C37" t="s">
         <v>626</v>
@@ -3599,10 +3587,10 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>15831347</v>
+        <v>35876282</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="C38" t="s">
         <v>626</v>
@@ -3622,10 +3610,10 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>32548061</v>
+        <v>16805855</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="C39" t="s">
         <v>626</v>
@@ -3645,10 +3633,10 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>35876282</v>
+        <v>55381383</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>172</v>
+        <v>383</v>
       </c>
       <c r="C40" t="s">
         <v>626</v>
@@ -3668,10 +3656,10 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>16805855</v>
+        <v>55449180</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>144</v>
+        <v>385</v>
       </c>
       <c r="C41" t="s">
         <v>626</v>
@@ -3691,10 +3679,10 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>55381383</v>
+        <v>55384739</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C42" t="s">
         <v>626</v>
@@ -3714,10 +3702,10 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>55449180</v>
+        <v>55389336</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>385</v>
+        <v>623</v>
       </c>
       <c r="C43" t="s">
         <v>626</v>
@@ -3737,10 +3725,10 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>55384739</v>
+        <v>55609278</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C44" t="s">
         <v>626</v>
@@ -3760,13 +3748,13 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>55389336</v>
+        <v>71042279</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>623</v>
+        <v>565</v>
       </c>
       <c r="C45" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H45" t="s">
         <v>58</v>
@@ -3783,13 +3771,13 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>55609278</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>384</v>
+        <v>67630646</v>
+      </c>
+      <c r="B46" t="s">
+        <v>526</v>
       </c>
       <c r="C46" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="H46" t="s">
         <v>58</v>
@@ -3806,13 +3794,13 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>71042279</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>565</v>
+        <v>64971361</v>
+      </c>
+      <c r="B47" t="s">
+        <v>486</v>
       </c>
       <c r="C47" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="H47" t="s">
         <v>58</v>
@@ -3829,13 +3817,13 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>67630646</v>
+        <v>62421723</v>
       </c>
       <c r="B48" t="s">
-        <v>526</v>
+        <v>454</v>
       </c>
       <c r="C48" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H48" t="s">
         <v>58</v>
@@ -3852,13 +3840,13 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>64971361</v>
+        <v>62374813</v>
       </c>
       <c r="B49" t="s">
-        <v>486</v>
+        <v>455</v>
       </c>
       <c r="C49" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H49" t="s">
         <v>58</v>
@@ -3875,13 +3863,13 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>62421723</v>
+        <v>68462854</v>
       </c>
       <c r="B50" t="s">
-        <v>454</v>
+        <v>532</v>
       </c>
       <c r="C50" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H50" t="s">
         <v>58</v>
@@ -3898,13 +3886,13 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>62374813</v>
+        <v>64114088</v>
       </c>
       <c r="B51" t="s">
-        <v>455</v>
+        <v>469</v>
       </c>
       <c r="C51" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H51" t="s">
         <v>58</v>
@@ -3921,13 +3909,13 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>68462854</v>
+        <v>19213859</v>
       </c>
       <c r="B52" t="s">
-        <v>532</v>
+        <v>34</v>
       </c>
       <c r="C52" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H52" t="s">
         <v>58</v>
@@ -3944,13 +3932,13 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>64114088</v>
+        <v>13004238</v>
       </c>
       <c r="B53" t="s">
-        <v>469</v>
+        <v>36</v>
       </c>
       <c r="C53" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H53" t="s">
         <v>58</v>
@@ -3965,15 +3953,15 @@
         <v>12674973</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>19213859</v>
+        <v>37161537</v>
       </c>
       <c r="B54" t="s">
-        <v>34</v>
-      </c>
-      <c r="C54" t="s">
-        <v>630</v>
+        <v>288</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>643</v>
       </c>
       <c r="H54" t="s">
         <v>58</v>
@@ -3989,15 +3977,6 @@
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A55">
-        <v>13004238</v>
-      </c>
-      <c r="B55" t="s">
-        <v>36</v>
-      </c>
-      <c r="C55" t="s">
-        <v>630</v>
-      </c>
       <c r="H55" t="s">
         <v>58</v>
       </c>
@@ -4011,15 +3990,15 @@
         <v>18928667</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="82.5" x14ac:dyDescent="0.3">
-      <c r="A56">
-        <v>37161537</v>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A56" s="6">
+        <v>80915325</v>
       </c>
       <c r="B56" t="s">
-        <v>288</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>644</v>
+        <v>647</v>
+      </c>
+      <c r="C56" t="s">
+        <v>662</v>
       </c>
       <c r="H56" t="s">
         <v>58</v>
@@ -4035,6 +4014,15 @@
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A57" s="6">
+        <v>80915326</v>
+      </c>
+      <c r="B57" t="s">
+        <v>648</v>
+      </c>
+      <c r="C57" t="s">
+        <v>662</v>
+      </c>
       <c r="H57" t="s">
         <v>58</v>
       </c>
@@ -4050,10 +4038,10 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>73226633</v>
+        <v>73893263</v>
       </c>
       <c r="B58" t="s">
-        <v>573</v>
+        <v>15</v>
       </c>
       <c r="C58" t="s">
         <v>663</v>
@@ -4072,11 +4060,11 @@
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A59" s="6">
-        <v>80915325</v>
+      <c r="A59">
+        <v>73226633</v>
       </c>
       <c r="B59" t="s">
-        <v>648</v>
+        <v>573</v>
       </c>
       <c r="C59" t="s">
         <v>664</v>
@@ -4095,14 +4083,14 @@
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A60" s="6">
-        <v>80915326</v>
+      <c r="A60">
+        <v>62498583</v>
       </c>
       <c r="B60" t="s">
-        <v>649</v>
+        <v>457</v>
       </c>
       <c r="C60" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="H60" t="s">
         <v>58</v>
@@ -4119,13 +4107,13 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>73893263</v>
+        <v>69766464</v>
       </c>
       <c r="B61" t="s">
-        <v>15</v>
+        <v>553</v>
       </c>
       <c r="C61" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H61" t="s">
         <v>58</v>
@@ -4142,13 +4130,13 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>5332789</v>
+        <v>38676914</v>
       </c>
       <c r="B62" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="C62" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H62" t="s">
         <v>90</v>
@@ -4165,13 +4153,13 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>51016959</v>
+        <v>61923953</v>
       </c>
       <c r="B63" t="s">
-        <v>346</v>
+        <v>441</v>
       </c>
       <c r="C63" t="s">
-        <v>666</v>
+        <v>675</v>
       </c>
       <c r="H63" t="s">
         <v>92</v>
@@ -4188,13 +4176,13 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>73226633</v>
+        <v>10324264</v>
       </c>
       <c r="B64" t="s">
-        <v>573</v>
+        <v>57</v>
       </c>
       <c r="C64" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="H64" t="s">
         <v>94</v>
@@ -4210,15 +4198,6 @@
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A65">
-        <v>62498583</v>
-      </c>
-      <c r="B65" t="s">
-        <v>457</v>
-      </c>
-      <c r="C65" t="s">
-        <v>669</v>
-      </c>
       <c r="H65" t="s">
         <v>94</v>
       </c>
@@ -4233,15 +4212,6 @@
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A66">
-        <v>69766464</v>
-      </c>
-      <c r="B66" t="s">
-        <v>553</v>
-      </c>
-      <c r="C66" t="s">
-        <v>669</v>
-      </c>
       <c r="H66" t="s">
         <v>94</v>
       </c>
@@ -4256,15 +4226,6 @@
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A67">
-        <v>38676914</v>
-      </c>
-      <c r="B67" t="s">
-        <v>336</v>
-      </c>
-      <c r="C67" t="s">
-        <v>670</v>
-      </c>
       <c r="H67" t="s">
         <v>98</v>
       </c>
@@ -4279,15 +4240,6 @@
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A68">
-        <v>61923953</v>
-      </c>
-      <c r="B68" t="s">
-        <v>441</v>
-      </c>
-      <c r="C68" t="s">
-        <v>674</v>
-      </c>
       <c r="H68" t="s">
         <v>98</v>
       </c>
@@ -4302,15 +4254,6 @@
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A69">
-        <v>10324264</v>
-      </c>
-      <c r="B69" t="s">
-        <v>57</v>
-      </c>
-      <c r="C69" t="s">
-        <v>675</v>
-      </c>
       <c r="H69" t="s">
         <v>98</v>
       </c>
@@ -4402,7 +4345,7 @@
         <v>491</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H75" t="s">
         <v>90</v>
@@ -4425,7 +4368,7 @@
         <v>236</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H76" t="s">
         <v>90</v>
@@ -4448,7 +4391,7 @@
         <v>16</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H77" t="s">
         <v>109</v>
@@ -4471,7 +4414,7 @@
         <v>439</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H78" t="s">
         <v>90</v>
@@ -4494,7 +4437,7 @@
         <v>485</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H79" t="s">
         <v>90</v>
@@ -4517,7 +4460,7 @@
         <v>185</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H80" t="s">
         <v>90</v>
@@ -4540,7 +4483,7 @@
         <v>340</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H81" t="s">
         <v>90</v>
@@ -4563,7 +4506,7 @@
         <v>339</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H82" t="s">
         <v>90</v>
@@ -4586,7 +4529,7 @@
         <v>10</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H83" t="s">
         <v>115</v>
@@ -4609,7 +4552,7 @@
         <v>117</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H84" t="s">
         <v>115</v>
@@ -4632,7 +4575,7 @@
         <v>264</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H85" t="s">
         <v>115</v>
@@ -4655,7 +4598,7 @@
         <v>261</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H86" t="s">
         <v>115</v>
@@ -4678,7 +4621,7 @@
         <v>292</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H87" t="s">
         <v>115</v>
@@ -4701,7 +4644,7 @@
         <v>8</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H88" t="s">
         <v>115</v>
@@ -4724,7 +4667,7 @@
         <v>177</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H89" t="s">
         <v>115</v>
@@ -4747,7 +4690,7 @@
         <v>87</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H90" t="s">
         <v>115</v>
@@ -4770,7 +4713,7 @@
         <v>263</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H91" t="s">
         <v>115</v>
@@ -4793,7 +4736,7 @@
         <v>317</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H92" t="s">
         <v>115</v>
@@ -4816,7 +4759,7 @@
         <v>37</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H93" t="s">
         <v>115</v>
@@ -4839,7 +4782,7 @@
         <v>322</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H94" t="s">
         <v>115</v>
@@ -4862,7 +4805,7 @@
         <v>88</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H95" t="s">
         <v>115</v>
@@ -4885,7 +4828,7 @@
         <v>20</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H96" t="s">
         <v>115</v>
@@ -4908,7 +4851,7 @@
         <v>119</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H97" t="s">
         <v>115</v>
@@ -4931,7 +4874,7 @@
         <v>308</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H98" t="s">
         <v>115</v>
@@ -4954,7 +4897,7 @@
         <v>40</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H99" t="s">
         <v>115</v>
@@ -4977,7 +4920,7 @@
         <v>279</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H100" t="s">
         <v>115</v>
@@ -5000,7 +4943,7 @@
         <v>229</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H101" t="s">
         <v>115</v>
@@ -5023,7 +4966,7 @@
         <v>110</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H102" t="s">
         <v>115</v>
@@ -5046,7 +4989,7 @@
         <v>230</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H103" t="s">
         <v>115</v>
@@ -5069,7 +5012,7 @@
         <v>46</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H104" t="s">
         <v>115</v>
@@ -5092,7 +5035,7 @@
         <v>43</v>
       </c>
       <c r="C105" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H105" t="s">
         <v>115</v>
@@ -5115,7 +5058,7 @@
         <v>325</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H106" t="s">
         <v>115</v>
@@ -5138,7 +5081,7 @@
         <v>298</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H107" t="s">
         <v>115</v>
@@ -5161,7 +5104,7 @@
         <v>9</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H108" t="s">
         <v>115</v>
@@ -5184,7 +5127,7 @@
         <v>135</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H109" t="s">
         <v>115</v>
@@ -5207,7 +5150,7 @@
         <v>265</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H110" t="s">
         <v>115</v>
@@ -5230,7 +5173,7 @@
         <v>299</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H111" t="s">
         <v>29</v>
@@ -5253,7 +5196,7 @@
         <v>377</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H112" t="s">
         <v>56</v>
@@ -5276,7 +5219,7 @@
         <v>378</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H113" t="s">
         <v>56</v>
@@ -5299,7 +5242,7 @@
         <v>412</v>
       </c>
       <c r="C114" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H114" t="s">
         <v>143</v>
@@ -5322,7 +5265,7 @@
         <v>421</v>
       </c>
       <c r="C115" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H115" t="s">
         <v>56</v>
@@ -5345,7 +5288,7 @@
         <v>420</v>
       </c>
       <c r="C116" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H116" t="s">
         <v>56</v>
@@ -5368,7 +5311,7 @@
         <v>428</v>
       </c>
       <c r="C117" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H117" t="s">
         <v>56</v>
@@ -5391,7 +5334,7 @@
         <v>429</v>
       </c>
       <c r="C118" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H118" t="s">
         <v>56</v>
@@ -5414,7 +5357,7 @@
         <v>431</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H119" t="s">
         <v>56</v>
@@ -5437,7 +5380,7 @@
         <v>440</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H120" t="s">
         <v>56</v>
@@ -5460,7 +5403,7 @@
         <v>452</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H121" t="s">
         <v>90</v>
@@ -5483,7 +5426,7 @@
         <v>474</v>
       </c>
       <c r="C122" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H122" t="s">
         <v>152</v>
@@ -5506,7 +5449,7 @@
         <v>479</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H123" t="s">
         <v>152</v>
@@ -5529,7 +5472,7 @@
         <v>492</v>
       </c>
       <c r="C124" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H124" t="s">
         <v>152</v>
@@ -5552,7 +5495,7 @@
         <v>512</v>
       </c>
       <c r="C125" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H125" t="s">
         <v>152</v>
@@ -5575,7 +5518,7 @@
         <v>417</v>
       </c>
       <c r="C126" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H126" t="s">
         <v>58</v>
@@ -5598,7 +5541,7 @@
         <v>67</v>
       </c>
       <c r="C127" s="9" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H127" t="s">
         <v>58</v>
@@ -5621,7 +5564,7 @@
         <v>68</v>
       </c>
       <c r="C128" s="9" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H128" t="s">
         <v>90</v>
@@ -5644,7 +5587,7 @@
         <v>284</v>
       </c>
       <c r="C129" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H129" t="s">
         <v>90</v>
@@ -5667,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="C130" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H130" t="s">
         <v>29</v>
@@ -5690,7 +5633,7 @@
         <v>419</v>
       </c>
       <c r="C131" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H131" t="s">
         <v>29</v>
@@ -5713,7 +5656,7 @@
         <v>445</v>
       </c>
       <c r="C132" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H132" t="s">
         <v>29</v>
@@ -5736,7 +5679,7 @@
         <v>503</v>
       </c>
       <c r="C133" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H133" t="s">
         <v>58</v>
@@ -5759,7 +5702,7 @@
         <v>35</v>
       </c>
       <c r="C134" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H134" t="s">
         <v>58</v>
@@ -5782,7 +5725,7 @@
         <v>41</v>
       </c>
       <c r="C135" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H135" t="s">
         <v>56</v>
@@ -5805,7 +5748,7 @@
         <v>42</v>
       </c>
       <c r="C136" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H136" t="s">
         <v>90</v>
@@ -5828,7 +5771,7 @@
         <v>48</v>
       </c>
       <c r="C137" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H137" t="s">
         <v>29</v>
@@ -5851,7 +5794,7 @@
         <v>59</v>
       </c>
       <c r="C138" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H138" t="s">
         <v>58</v>
@@ -5874,7 +5817,7 @@
         <v>63</v>
       </c>
       <c r="C139" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H139" t="s">
         <v>58</v>
@@ -5897,7 +5840,7 @@
         <v>64</v>
       </c>
       <c r="C140" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H140" t="s">
         <v>171</v>
@@ -5920,7 +5863,7 @@
         <v>100</v>
       </c>
       <c r="C141" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H141" t="s">
         <v>90</v>
@@ -5943,7 +5886,7 @@
         <v>108</v>
       </c>
       <c r="C142" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H142" t="s">
         <v>171</v>
@@ -5966,7 +5909,7 @@
         <v>140</v>
       </c>
       <c r="C143" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H143" t="s">
         <v>171</v>
@@ -5989,7 +5932,7 @@
         <v>186</v>
       </c>
       <c r="C144" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H144" t="s">
         <v>171</v>
@@ -6012,7 +5955,7 @@
         <v>187</v>
       </c>
       <c r="C145" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H145" t="s">
         <v>171</v>
@@ -6035,7 +5978,7 @@
         <v>188</v>
       </c>
       <c r="C146" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H146" t="s">
         <v>171</v>
@@ -6058,7 +6001,7 @@
         <v>192</v>
       </c>
       <c r="C147" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H147" t="s">
         <v>171</v>
@@ -6081,7 +6024,7 @@
         <v>212</v>
       </c>
       <c r="C148" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H148" t="s">
         <v>171</v>
@@ -6104,7 +6047,7 @@
         <v>217</v>
       </c>
       <c r="C149" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H149" t="s">
         <v>171</v>
@@ -6127,7 +6070,7 @@
         <v>218</v>
       </c>
       <c r="C150" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H150" t="s">
         <v>171</v>
@@ -6150,7 +6093,7 @@
         <v>223</v>
       </c>
       <c r="C151" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H151" t="s">
         <v>171</v>
@@ -6173,7 +6116,7 @@
         <v>227</v>
       </c>
       <c r="C152" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H152" t="s">
         <v>171</v>
@@ -6196,7 +6139,7 @@
         <v>228</v>
       </c>
       <c r="C153" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H153" t="s">
         <v>171</v>
@@ -6219,7 +6162,7 @@
         <v>231</v>
       </c>
       <c r="C154" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H154" t="s">
         <v>171</v>
@@ -6242,7 +6185,7 @@
         <v>237</v>
       </c>
       <c r="C155" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H155" t="s">
         <v>171</v>
@@ -6265,7 +6208,7 @@
         <v>238</v>
       </c>
       <c r="C156" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H156" t="s">
         <v>171</v>
@@ -6288,7 +6231,7 @@
         <v>239</v>
       </c>
       <c r="C157" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H157" t="s">
         <v>171</v>
@@ -6311,7 +6254,7 @@
         <v>240</v>
       </c>
       <c r="C158" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H158" t="s">
         <v>171</v>
@@ -6334,7 +6277,7 @@
         <v>241</v>
       </c>
       <c r="C159" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H159" t="s">
         <v>171</v>
@@ -6357,7 +6300,7 @@
         <v>242</v>
       </c>
       <c r="C160" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H160" t="s">
         <v>171</v>
@@ -6380,7 +6323,7 @@
         <v>243</v>
       </c>
       <c r="C161" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H161" t="s">
         <v>171</v>
@@ -6403,7 +6346,7 @@
         <v>248</v>
       </c>
       <c r="C162" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H162" t="s">
         <v>171</v>
@@ -6426,7 +6369,7 @@
         <v>251</v>
       </c>
       <c r="C163" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H163" t="s">
         <v>171</v>
@@ -6449,7 +6392,7 @@
         <v>254</v>
       </c>
       <c r="C164" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H164" t="s">
         <v>171</v>
@@ -6472,7 +6415,7 @@
         <v>255</v>
       </c>
       <c r="C165" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H165" t="s">
         <v>171</v>
@@ -6495,7 +6438,7 @@
         <v>256</v>
       </c>
       <c r="C166" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H166" t="s">
         <v>171</v>
@@ -6518,7 +6461,7 @@
         <v>257</v>
       </c>
       <c r="C167" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H167" t="s">
         <v>171</v>
@@ -6541,7 +6484,7 @@
         <v>285</v>
       </c>
       <c r="C168" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H168" t="s">
         <v>171</v>
@@ -6564,7 +6507,7 @@
         <v>290</v>
       </c>
       <c r="C169" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H169" t="s">
         <v>171</v>
@@ -6587,7 +6530,7 @@
         <v>291</v>
       </c>
       <c r="C170" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H170" t="s">
         <v>171</v>
@@ -6610,7 +6553,7 @@
         <v>305</v>
       </c>
       <c r="C171" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H171" t="s">
         <v>171</v>
@@ -6633,7 +6576,7 @@
         <v>306</v>
       </c>
       <c r="C172" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H172" t="s">
         <v>171</v>
@@ -6656,7 +6599,7 @@
         <v>309</v>
       </c>
       <c r="C173" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H173" t="s">
         <v>171</v>
@@ -6679,7 +6622,7 @@
         <v>337</v>
       </c>
       <c r="C174" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H174" t="s">
         <v>171</v>
@@ -6702,7 +6645,7 @@
         <v>350</v>
       </c>
       <c r="C175" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H175" t="s">
         <v>171</v>
@@ -6725,7 +6668,7 @@
         <v>363</v>
       </c>
       <c r="C176" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H176" t="s">
         <v>171</v>
@@ -6748,7 +6691,7 @@
         <v>382</v>
       </c>
       <c r="C177" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H177" t="s">
         <v>208</v>
@@ -6771,7 +6714,7 @@
         <v>390</v>
       </c>
       <c r="C178" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H178" t="s">
         <v>208</v>
@@ -6794,7 +6737,7 @@
         <v>436</v>
       </c>
       <c r="C179" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H179" t="s">
         <v>208</v>
@@ -6817,7 +6760,7 @@
         <v>477</v>
       </c>
       <c r="C180" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H180" t="s">
         <v>211</v>
@@ -6840,7 +6783,7 @@
         <v>287</v>
       </c>
       <c r="C181" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H181" t="s">
         <v>211</v>
@@ -6863,7 +6806,7 @@
         <v>6</v>
       </c>
       <c r="C182" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H182" t="s">
         <v>211</v>
@@ -6886,7 +6829,7 @@
         <v>4</v>
       </c>
       <c r="C183" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H183" t="s">
         <v>98</v>
@@ -6909,7 +6852,7 @@
         <v>12</v>
       </c>
       <c r="C184" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H184" t="s">
         <v>98</v>
@@ -6932,7 +6875,7 @@
         <v>209</v>
       </c>
       <c r="C185" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H185" t="s">
         <v>98</v>
@@ -6955,7 +6898,7 @@
         <v>289</v>
       </c>
       <c r="C186" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H186" t="s">
         <v>98</v>
@@ -6978,7 +6921,7 @@
         <v>139</v>
       </c>
       <c r="C187" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H187" t="s">
         <v>98</v>
@@ -7001,7 +6944,7 @@
         <v>2</v>
       </c>
       <c r="C188" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H188" t="s">
         <v>98</v>
@@ -7024,7 +6967,7 @@
         <v>219</v>
       </c>
       <c r="C189" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H189" t="s">
         <v>98</v>
@@ -7047,7 +6990,7 @@
         <v>294</v>
       </c>
       <c r="C190" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H190" t="s">
         <v>98</v>
@@ -7070,7 +7013,7 @@
         <v>136</v>
       </c>
       <c r="C191" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H191" t="s">
         <v>98</v>
@@ -7093,7 +7036,7 @@
         <v>307</v>
       </c>
       <c r="C192" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H192" t="s">
         <v>92</v>
@@ -7116,7 +7059,7 @@
         <v>7</v>
       </c>
       <c r="C193" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H193" t="s">
         <v>92</v>
@@ -7139,7 +7082,7 @@
         <v>418</v>
       </c>
       <c r="C194" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H194" t="s">
         <v>92</v>
@@ -7162,7 +7105,7 @@
         <v>11</v>
       </c>
       <c r="C195" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H195" t="s">
         <v>92</v>
@@ -7185,7 +7128,7 @@
         <v>427</v>
       </c>
       <c r="C196" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H196" t="s">
         <v>92</v>
@@ -7208,7 +7151,7 @@
         <v>3</v>
       </c>
       <c r="C197" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H197" t="s">
         <v>92</v>
@@ -7231,7 +7174,7 @@
         <v>564</v>
       </c>
       <c r="C198" s="10" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="H198" t="s">
         <v>92</v>
@@ -7254,7 +7197,7 @@
         <v>184</v>
       </c>
       <c r="C199" s="7" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="H199" t="s">
         <v>92</v>
@@ -7277,7 +7220,7 @@
         <v>106</v>
       </c>
       <c r="C200" s="7" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="H200" t="s">
         <v>92</v>
@@ -7300,7 +7243,7 @@
         <v>348</v>
       </c>
       <c r="C201" s="7" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="H201" t="s">
         <v>92</v>
@@ -7323,7 +7266,7 @@
         <v>16</v>
       </c>
       <c r="C202" s="7" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="H202" t="s">
         <v>92</v>
@@ -7346,7 +7289,7 @@
         <v>501</v>
       </c>
       <c r="C203" s="7" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="H203" t="s">
         <v>92</v>
@@ -7369,7 +7312,7 @@
         <v>564</v>
       </c>
       <c r="C204" s="7" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="H204" t="s">
         <v>92</v>
@@ -7392,7 +7335,7 @@
         <v>532</v>
       </c>
       <c r="C205" s="7" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="H205" t="s">
         <v>92</v>
@@ -13215,7 +13158,7 @@
         <v>80915325</v>
       </c>
       <c r="J595" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="K595" s="6">
         <v>80915325</v>
@@ -13229,7 +13172,7 @@
         <v>80915326</v>
       </c>
       <c r="J596" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="K596" s="6">
         <v>80915326</v>
@@ -13237,13 +13180,13 @@
     </row>
     <row r="597" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H597" s="7" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I597" s="6">
         <v>80953015</v>
       </c>
       <c r="J597" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="K597" s="6">
         <v>80953015</v>
@@ -13251,13 +13194,13 @@
     </row>
     <row r="598" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H598" s="7" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I598" s="6">
         <v>80953016</v>
       </c>
       <c r="J598" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="K598" s="6">
         <v>80953016</v>
@@ -13285,7 +13228,7 @@
         <v>81638306</v>
       </c>
       <c r="J600" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="K600" s="6">
         <v>81638306</v>
@@ -13293,13 +13236,13 @@
     </row>
     <row r="601" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H601" s="7" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I601" s="6">
         <v>81918457</v>
       </c>
       <c r="J601" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K601" s="6">
         <v>81918457</v>
@@ -13313,7 +13256,7 @@
         <v>81538523</v>
       </c>
       <c r="J602" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="K602" s="6">
         <v>81538523</v>
@@ -13327,7 +13270,7 @@
         <v>79040263</v>
       </c>
       <c r="J603" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="K603" s="6">
         <v>79040263</v>
@@ -13341,7 +13284,7 @@
         <v>79475749</v>
       </c>
       <c r="J604" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="K604" s="6">
         <v>79475749</v>
@@ -13355,7 +13298,7 @@
         <v>79944232</v>
       </c>
       <c r="J605" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K605" s="6">
         <v>79944232</v>
@@ -13369,7 +13312,7 @@
         <v>80460979</v>
       </c>
       <c r="J606" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="K606" s="6">
         <v>80460979</v>
@@ -13383,7 +13326,7 @@
         <v>81340922</v>
       </c>
       <c r="J607" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K607" s="6">
         <v>81340922</v>
@@ -13391,7 +13334,7 @@
     </row>
     <row r="608" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H608" s="7" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I608" s="6">
         <v>38157908</v>
@@ -13405,7 +13348,7 @@
     </row>
     <row r="609" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H609" s="7" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I609" s="6">
         <v>41662266</v>
@@ -13425,7 +13368,7 @@
         <v>81988924</v>
       </c>
       <c r="J610" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="K610" s="6">
         <v>81988924</v>
@@ -13439,7 +13382,7 @@
         <v>82014131</v>
       </c>
       <c r="J611" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="K611" s="6">
         <v>82014131</v>
@@ -13453,7 +13396,7 @@
         <v>82118965</v>
       </c>
       <c r="J612" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="K612">
         <v>82118965</v>
@@ -13461,13 +13404,13 @@
     </row>
     <row r="613" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H613" s="7" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="I613">
         <v>82521123</v>
       </c>
       <c r="J613" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="K613">
         <v>82521123</v>
@@ -13486,13 +13429,13 @@
   <conditionalFormatting sqref="K595:K611">
     <cfRule type="duplicateValues" dxfId="21" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A59:A60">
+  <conditionalFormatting sqref="A56:A57">
     <cfRule type="duplicateValues" dxfId="20" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A61">
+  <conditionalFormatting sqref="A58">
     <cfRule type="duplicateValues" dxfId="19" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A64">
+  <conditionalFormatting sqref="A59">
     <cfRule type="duplicateValues" dxfId="18" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A75">
@@ -13507,13 +13450,13 @@
   <conditionalFormatting sqref="A202">
     <cfRule type="duplicateValues" dxfId="14" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A65">
+  <conditionalFormatting sqref="A60">
     <cfRule type="duplicateValues" dxfId="13" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A66">
+  <conditionalFormatting sqref="A61">
     <cfRule type="duplicateValues" dxfId="12" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A67">
+  <conditionalFormatting sqref="A62">
     <cfRule type="duplicateValues" dxfId="11" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K612">
@@ -13522,26 +13465,26 @@
   <conditionalFormatting sqref="K613">
     <cfRule type="duplicateValues" dxfId="9" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A68">
+  <conditionalFormatting sqref="A63">
     <cfRule type="duplicateValues" dxfId="8" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A69">
+  <conditionalFormatting sqref="A64">
     <cfRule type="duplicateValues" dxfId="7" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A62:A63 A199:A200 A1:A58 A72:A74 A76:A197 A209:A212 A216:A1048576 A214 A203:A204">
-    <cfRule type="duplicateValues" dxfId="6" priority="53"/>
+  <conditionalFormatting sqref="A205">
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A62:A63 A200 A1:A58 A72:A74 A76:A197 A209:A212 A216:A1048576 A214 A203:A204">
-    <cfRule type="duplicateValues" dxfId="5" priority="61"/>
+  <conditionalFormatting sqref="A77:A197 A200 A1:A52 A209:A212 A216:A1048576 A214 A203:A204">
+    <cfRule type="duplicateValues" dxfId="3" priority="128"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A77:A197 A200 A1:A54 A209:A212 A216:A1048576 A214 A203:A204">
-    <cfRule type="duplicateValues" dxfId="4" priority="69"/>
+  <conditionalFormatting sqref="A199:A200 A1:A55 A72:A74 A76:A197 A209:A212 A216:A1048576 A214 A203:A204">
+    <cfRule type="duplicateValues" dxfId="2" priority="136"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A63 A72:A74 A76:A197 A199:A200 A209:A212 A216:A1048576 A214 A203:A204">
-    <cfRule type="duplicateValues" dxfId="3" priority="74"/>
+  <conditionalFormatting sqref="A200 A1:A55 A72:A74 A76:A197 A209:A212 A216:A1048576 A214 A203:A204">
+    <cfRule type="duplicateValues" dxfId="1" priority="145"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A205">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="A1:A58 A72:A74 A76:A197 A199:A200 A209:A212 A216:A1048576 A214 A203:A204">
+    <cfRule type="duplicateValues" dxfId="0" priority="154"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -13560,13 +13503,13 @@
   <sheetData>
     <row r="13" spans="1:3" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>640</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="C13" s="4" t="s">
         <v>641</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -13577,7 +13520,7 @@
         <v>70</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -13588,7 +13531,7 @@
         <v>202</v>
       </c>
       <c r="C15" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -13599,7 +13542,7 @@
         <v>203</v>
       </c>
       <c r="C16" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -13610,7 +13553,7 @@
         <v>191</v>
       </c>
       <c r="C17" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -13621,7 +13564,7 @@
         <v>484</v>
       </c>
       <c r="C18" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -13632,7 +13575,7 @@
         <v>560</v>
       </c>
       <c r="C19" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -13643,7 +13586,7 @@
         <v>174</v>
       </c>
       <c r="C20" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
@@ -13654,7 +13597,7 @@
         <v>598</v>
       </c>
       <c r="C21" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -13665,7 +13608,7 @@
         <v>327</v>
       </c>
       <c r="C22" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -13676,7 +13619,7 @@
         <v>328</v>
       </c>
       <c r="C23" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -13687,7 +13630,7 @@
         <v>374</v>
       </c>
       <c r="C24" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -13698,7 +13641,7 @@
         <v>372</v>
       </c>
       <c r="C25" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -13709,7 +13652,7 @@
         <v>205</v>
       </c>
       <c r="C26" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -13720,7 +13663,7 @@
         <v>194</v>
       </c>
       <c r="C27" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
   </sheetData>
@@ -13731,10 +13674,10 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A26:A27 A14:A24">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A25">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/이슈제품.xlsx
+++ b/data/이슈제품.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OA\Desktop\쿠팡업로드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22F6BB21-3F5F-476D-8B9C-F13137340AF2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B60532A-9AFB-4187-8682-BB1470310449}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1647" uniqueCount="676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1649" uniqueCount="678">
   <si>
     <t>오아디머무드등-화이트</t>
   </si>
@@ -2060,10 +2060,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>조절, 11월 3째주 예정</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>입고X, 11/23 예정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2095,6 +2091,18 @@
   </si>
   <si>
     <t>재고X, 11/12 입고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조절, 11/6 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조절 11월 중순예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조절 11/6 예정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2214,7 +2222,17 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="24">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -4090,7 +4108,7 @@
         <v>457</v>
       </c>
       <c r="C60" t="s">
-        <v>666</v>
+        <v>676</v>
       </c>
       <c r="H60" t="s">
         <v>58</v>
@@ -4113,7 +4131,7 @@
         <v>553</v>
       </c>
       <c r="C61" t="s">
-        <v>666</v>
+        <v>675</v>
       </c>
       <c r="H61" t="s">
         <v>58</v>
@@ -4136,7 +4154,7 @@
         <v>336</v>
       </c>
       <c r="C62" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H62" t="s">
         <v>90</v>
@@ -4159,7 +4177,7 @@
         <v>441</v>
       </c>
       <c r="C63" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H63" t="s">
         <v>92</v>
@@ -4182,7 +4200,7 @@
         <v>57</v>
       </c>
       <c r="C64" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H64" t="s">
         <v>94</v>
@@ -4198,6 +4216,15 @@
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>69766464</v>
+      </c>
+      <c r="B65" t="s">
+        <v>553</v>
+      </c>
+      <c r="C65" t="s">
+        <v>677</v>
+      </c>
       <c r="H65" t="s">
         <v>94</v>
       </c>
@@ -7197,7 +7224,7 @@
         <v>184</v>
       </c>
       <c r="C199" s="7" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H199" t="s">
         <v>92</v>
@@ -7220,7 +7247,7 @@
         <v>106</v>
       </c>
       <c r="C200" s="7" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H200" t="s">
         <v>92</v>
@@ -7243,7 +7270,7 @@
         <v>348</v>
       </c>
       <c r="C201" s="7" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H201" t="s">
         <v>92</v>
@@ -7266,7 +7293,7 @@
         <v>16</v>
       </c>
       <c r="C202" s="7" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H202" t="s">
         <v>92</v>
@@ -7289,7 +7316,7 @@
         <v>501</v>
       </c>
       <c r="C203" s="7" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H203" t="s">
         <v>92</v>
@@ -7312,7 +7339,7 @@
         <v>564</v>
       </c>
       <c r="C204" s="7" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H204" t="s">
         <v>92</v>
@@ -7335,7 +7362,7 @@
         <v>532</v>
       </c>
       <c r="C205" s="7" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H205" t="s">
         <v>92</v>
@@ -13396,7 +13423,7 @@
         <v>82118965</v>
       </c>
       <c r="J612" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="K612">
         <v>82118965</v>
@@ -13404,13 +13431,13 @@
     </row>
     <row r="613" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H613" s="7" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="I613">
         <v>82521123</v>
       </c>
       <c r="J613" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="K613">
         <v>82521123</v>
@@ -13424,67 +13451,70 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="I1:I1048576">
+    <cfRule type="duplicateValues" dxfId="23" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K595:K611">
     <cfRule type="duplicateValues" dxfId="22" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K595:K611">
+  <conditionalFormatting sqref="A56:A57">
     <cfRule type="duplicateValues" dxfId="21" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A56:A57">
+  <conditionalFormatting sqref="A58">
     <cfRule type="duplicateValues" dxfId="20" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A58">
-    <cfRule type="duplicateValues" dxfId="19" priority="17"/>
+  <conditionalFormatting sqref="A59">
+    <cfRule type="duplicateValues" dxfId="19" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A59">
+  <conditionalFormatting sqref="A75">
     <cfRule type="duplicateValues" dxfId="18" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A75">
+  <conditionalFormatting sqref="A198">
     <cfRule type="duplicateValues" dxfId="17" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A198">
+  <conditionalFormatting sqref="A201">
     <cfRule type="duplicateValues" dxfId="16" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A201">
+  <conditionalFormatting sqref="A202">
     <cfRule type="duplicateValues" dxfId="15" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A202">
+  <conditionalFormatting sqref="A60">
     <cfRule type="duplicateValues" dxfId="14" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A60">
+  <conditionalFormatting sqref="A61">
     <cfRule type="duplicateValues" dxfId="13" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A61">
+  <conditionalFormatting sqref="A62">
     <cfRule type="duplicateValues" dxfId="12" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A62">
-    <cfRule type="duplicateValues" dxfId="11" priority="8"/>
+  <conditionalFormatting sqref="K612">
+    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K612">
+  <conditionalFormatting sqref="K613">
     <cfRule type="duplicateValues" dxfId="10" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K613">
+  <conditionalFormatting sqref="A63">
     <cfRule type="duplicateValues" dxfId="9" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A63">
+  <conditionalFormatting sqref="A64">
     <cfRule type="duplicateValues" dxfId="8" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A64">
+  <conditionalFormatting sqref="A205">
     <cfRule type="duplicateValues" dxfId="7" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A205">
-    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A77:A197 A200 A1:A52 A209:A212 A216:A1048576 A214 A203:A204">
-    <cfRule type="duplicateValues" dxfId="3" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="129"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A199:A200 A1:A55 A72:A74 A76:A197 A209:A212 A216:A1048576 A214 A203:A204">
-    <cfRule type="duplicateValues" dxfId="2" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="137"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A200 A1:A55 A72:A74 A76:A197 A209:A212 A216:A1048576 A214 A203:A204">
-    <cfRule type="duplicateValues" dxfId="1" priority="145"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="146"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A58 A72:A74 A76:A197 A199:A200 A209:A212 A216:A1048576 A214 A203:A204">
-    <cfRule type="duplicateValues" dxfId="0" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="155"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A65">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -13674,10 +13704,10 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A26:A27 A14:A24">
-    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A25">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
